--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="4"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -344,7 +344,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1360" uniqueCount="720">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="724">
   <si>
     <t>_Id</t>
   </si>
@@ -2483,6 +2483,18 @@
   </si>
   <si>
     <t>极·卖身契</t>
+  </si>
+  <si>
+    <t>极·圣者遗物</t>
+  </si>
+  <si>
+    <t>极·副本契约</t>
+  </si>
+  <si>
+    <t>极·BOSS契约</t>
+  </si>
+  <si>
+    <t>极.财富契约</t>
   </si>
   <si>
     <t>麻痹戒指</t>
@@ -2708,12 +2720,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -17943,7 +17955,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:M34"/>
+  <dimension ref="C1:M33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="4" max="4" width="9.625" customWidth="1"/>
@@ -18670,28 +18682,114 @@
         <v>0</v>
       </c>
       <c r="J28" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
     </row>
-    <row r="29" s="2" customFormat="1" customHeight="1" spans="4:13">
-      <c r="D29" s="3"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" s="2" customFormat="1" customHeight="1" spans="4:13">
-      <c r="D30" s="3"/>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" s="2" customFormat="1" customHeight="1" spans="4:13">
-      <c r="D31" s="3"/>
-      <c r="L31" s="3"/>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" s="2" customFormat="1" customHeight="1" spans="4:13">
-      <c r="D32" s="3"/>
+    <row r="29" s="3" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C29" s="2">
+        <v>180031</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="E29" s="2">
+        <v>18</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="G29" s="3">
+        <v>1</v>
+      </c>
+      <c r="H29" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I29" s="2">
+        <v>0</v>
+      </c>
+      <c r="J29" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" s="3" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C30" s="2">
+        <v>180032</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="E30" s="2">
+        <v>18</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="G30" s="3">
+        <v>1</v>
+      </c>
+      <c r="H30" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I30" s="2">
+        <v>0</v>
+      </c>
+      <c r="J30" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" s="3" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C31" s="2">
+        <v>180033</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="E31" s="2">
+        <v>18</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="G31" s="3">
+        <v>1</v>
+      </c>
+      <c r="H31" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I31" s="2">
+        <v>0</v>
+      </c>
+      <c r="J31" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C32" s="2">
+        <v>180034</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="E32" s="2">
+        <v>18</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="G32" s="3">
+        <v>1</v>
+      </c>
+      <c r="H32" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I32" s="2">
+        <v>0</v>
+      </c>
+      <c r="J32" s="2">
+        <v>7</v>
+      </c>
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
     </row>
@@ -18699,11 +18797,6 @@
       <c r="D33" s="3"/>
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
-    </row>
-    <row r="34" s="2" customFormat="1" customHeight="1" spans="4:13">
-      <c r="D34" s="3"/>
-      <c r="L34" s="3"/>
-      <c r="M34" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -18849,13 +18942,13 @@
         <v>190001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="E6" s="2">
         <v>19</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -18875,13 +18968,13 @@
         <v>190002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="E7" s="2">
         <v>19</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -18901,13 +18994,13 @@
         <v>190003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="E8" s="2">
         <v>19</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -18927,13 +19020,13 @@
         <v>190004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="E9" s="2">
         <v>19</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -18953,13 +19046,13 @@
         <v>190005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="E10" s="2">
         <v>19</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -18979,13 +19072,13 @@
         <v>190006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="E11" s="2">
         <v>19</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="6"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -344,7 +344,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="724">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="728">
   <si>
     <t>_Id</t>
   </si>
@@ -1051,10 +1051,22 @@
     <t>魔鲸王骨</t>
   </si>
   <si>
+    <t>龙之怒</t>
+  </si>
+  <si>
+    <t>激活对应图鉴</t>
+  </si>
+  <si>
+    <t>龙之刀</t>
+  </si>
+  <si>
+    <t>龙之杖</t>
+  </si>
+  <si>
+    <t>龙之剑</t>
+  </si>
+  <si>
     <t>龙之血</t>
-  </si>
-  <si>
-    <t>激活对应图鉴</t>
   </si>
   <si>
     <t>龙之御</t>
@@ -2720,12 +2732,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -6989,7 +7001,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:M120"/>
+  <dimension ref="C1:M124"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="4" max="4" width="9.625" customWidth="1"/>
@@ -7112,7 +7124,7 @@
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C6" s="2">
-        <v>1999993</v>
+        <v>1999989</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>235</v>
@@ -7135,12 +7147,13 @@
       <c r="J6" s="2">
         <v>6</v>
       </c>
+      <c r="K6" s="2"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C7" s="2">
-        <v>1999994</v>
+        <v>1999990</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>237</v>
@@ -7163,12 +7176,13 @@
       <c r="J7" s="2">
         <v>6</v>
       </c>
+      <c r="K7" s="2"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C8" s="2">
-        <v>1999995</v>
+        <v>1999991</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>238</v>
@@ -7196,7 +7210,7 @@
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C9" s="2">
-        <v>1999996</v>
+        <v>1999992</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>239</v>
@@ -7224,7 +7238,7 @@
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C10" s="2">
-        <v>1999997</v>
+        <v>1999993</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>240</v>
@@ -7252,16 +7266,16 @@
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C11" s="2">
-        <v>2000000</v>
-      </c>
-      <c r="D11" s="2" t="s">
+        <v>1999994</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>241</v>
       </c>
       <c r="E11" s="2">
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -7273,17 +7287,17 @@
         <v>0</v>
       </c>
       <c r="J11" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C12" s="2">
-        <v>2000001</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>243</v>
+        <v>1999995</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>242</v>
       </c>
       <c r="E12" s="2">
         <v>11</v>
@@ -7301,17 +7315,17 @@
         <v>0</v>
       </c>
       <c r="J12" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C13" s="2">
-        <v>2000002</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>244</v>
+        <v>1999996</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>243</v>
       </c>
       <c r="E13" s="2">
         <v>11</v>
@@ -7329,17 +7343,17 @@
         <v>0</v>
       </c>
       <c r="J13" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C14" s="2">
-        <v>2000003</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>245</v>
+        <v>1999997</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>244</v>
       </c>
       <c r="E14" s="2">
         <v>11</v>
@@ -7357,23 +7371,23 @@
         <v>0</v>
       </c>
       <c r="J14" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C15" s="2">
-        <v>2000004</v>
+        <v>2000000</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E15" s="2">
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -7392,7 +7406,7 @@
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C16" s="2">
-        <v>2000005</v>
+        <v>2000001</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>247</v>
@@ -7420,7 +7434,7 @@
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C17" s="2">
-        <v>2000006</v>
+        <v>2000002</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>248</v>
@@ -7448,7 +7462,7 @@
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C18" s="2">
-        <v>2000007</v>
+        <v>2000003</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>249</v>
@@ -7476,7 +7490,7 @@
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C19" s="2">
-        <v>2000008</v>
+        <v>2000004</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>250</v>
@@ -7504,7 +7518,7 @@
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C20" s="2">
-        <v>2000009</v>
+        <v>2000005</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>251</v>
@@ -7532,7 +7546,7 @@
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C21" s="2">
-        <v>2000010</v>
+        <v>2000006</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>252</v>
@@ -7558,19 +7572,115 @@
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
     </row>
-    <row r="22" s="2" customFormat="1" customHeight="1" spans="12:13">
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C22" s="2">
+        <v>2000007</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E22" s="2">
+        <v>11</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G22" s="2">
+        <v>1</v>
+      </c>
+      <c r="H22" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I22" s="2">
+        <v>0</v>
+      </c>
+      <c r="J22" s="2">
+        <v>5</v>
+      </c>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
     </row>
-    <row r="23" s="2" customFormat="1" customHeight="1" spans="12:13">
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C23" s="2">
+        <v>2000008</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="E23" s="2">
+        <v>11</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G23" s="2">
+        <v>1</v>
+      </c>
+      <c r="H23" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I23" s="2">
+        <v>0</v>
+      </c>
+      <c r="J23" s="2">
+        <v>5</v>
+      </c>
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
     </row>
-    <row r="24" s="2" customFormat="1" customHeight="1" spans="12:13">
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C24" s="2">
+        <v>2000009</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E24" s="2">
+        <v>11</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G24" s="2">
+        <v>1</v>
+      </c>
+      <c r="H24" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I24" s="2">
+        <v>0</v>
+      </c>
+      <c r="J24" s="2">
+        <v>5</v>
+      </c>
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
     </row>
-    <row r="25" s="2" customFormat="1" customHeight="1" spans="12:13">
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C25" s="2">
+        <v>2000010</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E25" s="2">
+        <v>11</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G25" s="2">
+        <v>1</v>
+      </c>
+      <c r="H25" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I25" s="2">
+        <v>0</v>
+      </c>
+      <c r="J25" s="2">
+        <v>5</v>
+      </c>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
     </row>
@@ -7582,121 +7692,25 @@
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
     </row>
-    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C28" s="2">
-        <v>2000100</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="E28" s="2">
-        <v>11</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="G28" s="2">
-        <v>1</v>
-      </c>
-      <c r="H28" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I28" s="2">
-        <v>0</v>
-      </c>
-      <c r="J28" s="2">
-        <v>1</v>
-      </c>
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="12:13">
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
     </row>
-    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C29" s="2">
-        <v>2000101</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="E29" s="2">
-        <v>11</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="G29" s="2">
-        <v>1</v>
-      </c>
-      <c r="H29" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I29" s="2">
-        <v>0</v>
-      </c>
-      <c r="J29" s="2">
-        <v>1</v>
-      </c>
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="12:13">
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
     </row>
-    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C30" s="2">
-        <v>2000102</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="E30" s="2">
-        <v>11</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="G30" s="2">
-        <v>1</v>
-      </c>
-      <c r="H30" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I30" s="2">
-        <v>0</v>
-      </c>
-      <c r="J30" s="2">
-        <v>1</v>
-      </c>
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="12:13">
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
     </row>
-    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C31" s="2">
-        <v>2000103</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="E31" s="2">
-        <v>11</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="G31" s="2">
-        <v>1</v>
-      </c>
-      <c r="H31" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I31" s="2">
-        <v>0</v>
-      </c>
-      <c r="J31" s="2">
-        <v>1</v>
-      </c>
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="12:13">
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
     </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C32" s="2">
-        <v>2000104</v>
+        <v>2000100</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>257</v>
@@ -7724,7 +7738,7 @@
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C33" s="2">
-        <v>2000105</v>
+        <v>2000101</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>258</v>
@@ -7752,7 +7766,7 @@
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C34" s="2">
-        <v>2000106</v>
+        <v>2000102</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>259</v>
@@ -7780,7 +7794,7 @@
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C35" s="2">
-        <v>2000107</v>
+        <v>2000103</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>260</v>
@@ -7808,7 +7822,7 @@
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C36" s="2">
-        <v>2000108</v>
+        <v>2000104</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>261</v>
@@ -7836,7 +7850,7 @@
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C37" s="2">
-        <v>2000109</v>
+        <v>2000105</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>262</v>
@@ -7864,7 +7878,7 @@
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C38" s="2">
-        <v>2000110</v>
+        <v>2000106</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>263</v>
@@ -7892,7 +7906,7 @@
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C39" s="2">
-        <v>2000111</v>
+        <v>2000107</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>264</v>
@@ -7920,7 +7934,7 @@
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C40" s="2">
-        <v>2000112</v>
+        <v>2000108</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>265</v>
@@ -7941,14 +7955,14 @@
         <v>0</v>
       </c>
       <c r="J40" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C41" s="2">
-        <v>2000113</v>
+        <v>2000109</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>266</v>
@@ -7969,14 +7983,14 @@
         <v>0</v>
       </c>
       <c r="J41" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C42" s="2">
-        <v>2000114</v>
+        <v>2000110</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>267</v>
@@ -7997,14 +8011,14 @@
         <v>0</v>
       </c>
       <c r="J42" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L42" s="3"/>
       <c r="M42" s="3"/>
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C43" s="2">
-        <v>2000115</v>
+        <v>2000111</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>268</v>
@@ -8025,14 +8039,14 @@
         <v>0</v>
       </c>
       <c r="J43" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C44" s="2">
-        <v>2000116</v>
+        <v>2000112</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>269</v>
@@ -8060,7 +8074,7 @@
     </row>
     <row r="45" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C45" s="2">
-        <v>2000117</v>
+        <v>2000113</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>270</v>
@@ -8088,7 +8102,7 @@
     </row>
     <row r="46" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C46" s="2">
-        <v>2000118</v>
+        <v>2000114</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>271</v>
@@ -8116,7 +8130,7 @@
     </row>
     <row r="47" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C47" s="2">
-        <v>2000119</v>
+        <v>2000115</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>272</v>
@@ -8144,7 +8158,7 @@
     </row>
     <row r="48" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C48" s="2">
-        <v>2000120</v>
+        <v>2000116</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>273</v>
@@ -8172,7 +8186,7 @@
     </row>
     <row r="49" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C49" s="2">
-        <v>2000121</v>
+        <v>2000117</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>274</v>
@@ -8193,14 +8207,14 @@
         <v>0</v>
       </c>
       <c r="J49" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L49" s="3"/>
       <c r="M49" s="3"/>
     </row>
     <row r="50" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C50" s="2">
-        <v>2000122</v>
+        <v>2000118</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>275</v>
@@ -8221,14 +8235,14 @@
         <v>0</v>
       </c>
       <c r="J50" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
     </row>
     <row r="51" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C51" s="2">
-        <v>2000123</v>
+        <v>2000119</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>276</v>
@@ -8249,14 +8263,14 @@
         <v>0</v>
       </c>
       <c r="J51" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
     </row>
     <row r="52" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C52" s="2">
-        <v>2000124</v>
+        <v>2000120</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>277</v>
@@ -8277,14 +8291,14 @@
         <v>0</v>
       </c>
       <c r="J52" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L52" s="3"/>
       <c r="M52" s="3"/>
     </row>
     <row r="53" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C53" s="2">
-        <v>2000125</v>
+        <v>2000121</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>278</v>
@@ -8312,7 +8326,7 @@
     </row>
     <row r="54" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C54" s="2">
-        <v>2000126</v>
+        <v>2000122</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>279</v>
@@ -8340,7 +8354,7 @@
     </row>
     <row r="55" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C55" s="2">
-        <v>2000127</v>
+        <v>2000123</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>280</v>
@@ -8361,14 +8375,14 @@
         <v>0</v>
       </c>
       <c r="J55" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
     </row>
     <row r="56" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C56" s="2">
-        <v>2000128</v>
+        <v>2000124</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>281</v>
@@ -8389,14 +8403,14 @@
         <v>0</v>
       </c>
       <c r="J56" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
     </row>
     <row r="57" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C57" s="2">
-        <v>2000129</v>
+        <v>2000125</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>282</v>
@@ -8417,17 +8431,45 @@
         <v>0</v>
       </c>
       <c r="J57" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L57" s="3"/>
       <c r="M57" s="3"/>
     </row>
-    <row r="59" customHeight="1" spans="3:10">
+    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C58" s="2">
+        <v>2000126</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E58" s="2">
+        <v>11</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G58" s="2">
+        <v>1</v>
+      </c>
+      <c r="H58" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I58" s="2">
+        <v>0</v>
+      </c>
+      <c r="J58" s="2">
+        <v>3</v>
+      </c>
+      <c r="L58" s="3"/>
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C59" s="2">
-        <v>2000200</v>
+        <v>2000127</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E59" s="2">
         <v>11</v>
@@ -8445,15 +8487,17 @@
         <v>0</v>
       </c>
       <c r="J59" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" customHeight="1" spans="3:10">
+        <v>4</v>
+      </c>
+      <c r="L59" s="3"/>
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C60" s="2">
-        <v>2000201</v>
+        <v>2000128</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E60" s="2">
         <v>11</v>
@@ -8471,15 +8515,17 @@
         <v>0</v>
       </c>
       <c r="J60" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" customHeight="1" spans="3:10">
+        <v>4</v>
+      </c>
+      <c r="L60" s="3"/>
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C61" s="2">
-        <v>2000202</v>
+        <v>2000129</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E61" s="2">
         <v>11</v>
@@ -8497,38 +8543,14 @@
         <v>0</v>
       </c>
       <c r="J61" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" customHeight="1" spans="3:10">
-      <c r="C62" s="2">
-        <v>2000203</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="E62" s="2">
-        <v>11</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="G62" s="2">
-        <v>1</v>
-      </c>
-      <c r="H62" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I62" s="2">
-        <v>0</v>
-      </c>
-      <c r="J62" s="2">
-        <v>1</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="L61" s="3"/>
+      <c r="M61" s="3"/>
     </row>
     <row r="63" customHeight="1" spans="3:10">
       <c r="C63" s="2">
-        <v>2000204</v>
+        <v>2000200</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>287</v>
@@ -8554,7 +8576,7 @@
     </row>
     <row r="64" customHeight="1" spans="3:10">
       <c r="C64" s="2">
-        <v>2000205</v>
+        <v>2000201</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>288</v>
@@ -8580,7 +8602,7 @@
     </row>
     <row r="65" customHeight="1" spans="3:10">
       <c r="C65" s="2">
-        <v>2000206</v>
+        <v>2000202</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>289</v>
@@ -8606,7 +8628,7 @@
     </row>
     <row r="66" customHeight="1" spans="3:10">
       <c r="C66" s="2">
-        <v>2000207</v>
+        <v>2000203</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>290</v>
@@ -8632,7 +8654,7 @@
     </row>
     <row r="67" customHeight="1" spans="3:10">
       <c r="C67" s="2">
-        <v>2000208</v>
+        <v>2000204</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>291</v>
@@ -8658,7 +8680,7 @@
     </row>
     <row r="68" customHeight="1" spans="3:10">
       <c r="C68" s="2">
-        <v>2000209</v>
+        <v>2000205</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>292</v>
@@ -8684,7 +8706,7 @@
     </row>
     <row r="69" customHeight="1" spans="3:10">
       <c r="C69" s="2">
-        <v>2000210</v>
+        <v>2000206</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>293</v>
@@ -8710,7 +8732,7 @@
     </row>
     <row r="70" customHeight="1" spans="3:10">
       <c r="C70" s="2">
-        <v>2000211</v>
+        <v>2000207</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>294</v>
@@ -8736,7 +8758,7 @@
     </row>
     <row r="71" customHeight="1" spans="3:10">
       <c r="C71" s="2">
-        <v>2000212</v>
+        <v>2000208</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>295</v>
@@ -8757,12 +8779,12 @@
         <v>0</v>
       </c>
       <c r="J71" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:10">
       <c r="C72" s="2">
-        <v>2000213</v>
+        <v>2000209</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>296</v>
@@ -8783,12 +8805,12 @@
         <v>0</v>
       </c>
       <c r="J72" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:10">
       <c r="C73" s="2">
-        <v>2000214</v>
+        <v>2000210</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>297</v>
@@ -8809,12 +8831,12 @@
         <v>0</v>
       </c>
       <c r="J73" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:10">
       <c r="C74" s="2">
-        <v>2000215</v>
+        <v>2000211</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>298</v>
@@ -8835,12 +8857,12 @@
         <v>0</v>
       </c>
       <c r="J74" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:10">
       <c r="C75" s="2">
-        <v>2000216</v>
+        <v>2000212</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>299</v>
@@ -8866,7 +8888,7 @@
     </row>
     <row r="76" customHeight="1" spans="3:10">
       <c r="C76" s="2">
-        <v>2000217</v>
+        <v>2000213</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>300</v>
@@ -8892,7 +8914,7 @@
     </row>
     <row r="77" customHeight="1" spans="3:10">
       <c r="C77" s="2">
-        <v>2000218</v>
+        <v>2000214</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>301</v>
@@ -8918,7 +8940,7 @@
     </row>
     <row r="78" customHeight="1" spans="3:10">
       <c r="C78" s="2">
-        <v>2000219</v>
+        <v>2000215</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>302</v>
@@ -8944,7 +8966,7 @@
     </row>
     <row r="79" customHeight="1" spans="3:10">
       <c r="C79" s="2">
-        <v>2000220</v>
+        <v>2000216</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>303</v>
@@ -8970,7 +8992,7 @@
     </row>
     <row r="80" customHeight="1" spans="3:10">
       <c r="C80" s="2">
-        <v>2000221</v>
+        <v>2000217</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>304</v>
@@ -8991,12 +9013,12 @@
         <v>0</v>
       </c>
       <c r="J80" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="3:10">
       <c r="C81" s="2">
-        <v>2000222</v>
+        <v>2000218</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>305</v>
@@ -9017,12 +9039,12 @@
         <v>0</v>
       </c>
       <c r="J81" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:10">
       <c r="C82" s="2">
-        <v>2000223</v>
+        <v>2000219</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>306</v>
@@ -9043,12 +9065,12 @@
         <v>0</v>
       </c>
       <c r="J82" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:10">
       <c r="C83" s="2">
-        <v>2000224</v>
+        <v>2000220</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>307</v>
@@ -9069,12 +9091,12 @@
         <v>0</v>
       </c>
       <c r="J83" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="3:10">
       <c r="C84" s="2">
-        <v>2000225</v>
+        <v>2000221</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>308</v>
@@ -9100,7 +9122,7 @@
     </row>
     <row r="85" customHeight="1" spans="3:10">
       <c r="C85" s="2">
-        <v>2000226</v>
+        <v>2000222</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>309</v>
@@ -9126,7 +9148,7 @@
     </row>
     <row r="86" customHeight="1" spans="3:10">
       <c r="C86" s="2">
-        <v>2000227</v>
+        <v>2000223</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>310</v>
@@ -9147,12 +9169,12 @@
         <v>0</v>
       </c>
       <c r="J86" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="3:10">
       <c r="C87" s="2">
-        <v>2000228</v>
+        <v>2000224</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>311</v>
@@ -9173,12 +9195,12 @@
         <v>0</v>
       </c>
       <c r="J87" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="3:10">
       <c r="C88" s="2">
-        <v>2000229</v>
+        <v>2000225</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>312</v>
@@ -9199,15 +9221,67 @@
         <v>0</v>
       </c>
       <c r="J88" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" spans="3:10">
+      <c r="C89" s="2">
+        <v>2000226</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="E89" s="2">
+        <v>11</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G89" s="2">
+        <v>1</v>
+      </c>
+      <c r="H89" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I89" s="2">
+        <v>0</v>
+      </c>
+      <c r="J89" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" customHeight="1" spans="3:10">
+      <c r="C90" s="2">
+        <v>2000227</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="E90" s="2">
+        <v>11</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G90" s="2">
+        <v>1</v>
+      </c>
+      <c r="H90" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I90" s="2">
+        <v>0</v>
+      </c>
+      <c r="J90" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="3:10">
       <c r="C91" s="2">
-        <v>2000300</v>
+        <v>2000228</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E91" s="2">
         <v>11</v>
@@ -9225,15 +9299,15 @@
         <v>0</v>
       </c>
       <c r="J91" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="3:10">
       <c r="C92" s="2">
-        <v>2000301</v>
+        <v>2000229</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E92" s="2">
         <v>11</v>
@@ -9251,64 +9325,12 @@
         <v>0</v>
       </c>
       <c r="J92" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" customHeight="1" spans="3:10">
-      <c r="C93" s="2">
-        <v>2000302</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="E93" s="2">
-        <v>11</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="G93" s="2">
-        <v>1</v>
-      </c>
-      <c r="H93" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I93" s="2">
-        <v>0</v>
-      </c>
-      <c r="J93" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" customHeight="1" spans="3:10">
-      <c r="C94" s="2">
-        <v>2000303</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="E94" s="2">
-        <v>11</v>
-      </c>
-      <c r="F94" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="G94" s="2">
-        <v>1</v>
-      </c>
-      <c r="H94" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I94" s="2">
-        <v>0</v>
-      </c>
-      <c r="J94" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="3:10">
       <c r="C95" s="2">
-        <v>2000304</v>
+        <v>2000300</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>317</v>
@@ -9334,7 +9356,7 @@
     </row>
     <row r="96" customHeight="1" spans="3:10">
       <c r="C96" s="2">
-        <v>2000305</v>
+        <v>2000301</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>318</v>
@@ -9360,7 +9382,7 @@
     </row>
     <row r="97" customHeight="1" spans="3:10">
       <c r="C97" s="2">
-        <v>2000306</v>
+        <v>2000302</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>319</v>
@@ -9386,7 +9408,7 @@
     </row>
     <row r="98" customHeight="1" spans="3:10">
       <c r="C98" s="2">
-        <v>2000307</v>
+        <v>2000303</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>320</v>
@@ -9412,7 +9434,7 @@
     </row>
     <row r="99" customHeight="1" spans="3:10">
       <c r="C99" s="2">
-        <v>2000308</v>
+        <v>2000304</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>321</v>
@@ -9438,7 +9460,7 @@
     </row>
     <row r="100" customHeight="1" spans="3:10">
       <c r="C100" s="2">
-        <v>2000309</v>
+        <v>2000305</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>322</v>
@@ -9464,7 +9486,7 @@
     </row>
     <row r="101" customHeight="1" spans="3:10">
       <c r="C101" s="2">
-        <v>2000310</v>
+        <v>2000306</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>323</v>
@@ -9490,7 +9512,7 @@
     </row>
     <row r="102" customHeight="1" spans="3:10">
       <c r="C102" s="2">
-        <v>2000311</v>
+        <v>2000307</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>324</v>
@@ -9516,7 +9538,7 @@
     </row>
     <row r="103" customHeight="1" spans="3:10">
       <c r="C103" s="2">
-        <v>2000312</v>
+        <v>2000308</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>325</v>
@@ -9537,12 +9559,12 @@
         <v>0</v>
       </c>
       <c r="J103" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="3:10">
       <c r="C104" s="2">
-        <v>2000313</v>
+        <v>2000309</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>326</v>
@@ -9563,12 +9585,12 @@
         <v>0</v>
       </c>
       <c r="J104" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="3:10">
       <c r="C105" s="2">
-        <v>2000314</v>
+        <v>2000310</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>327</v>
@@ -9589,12 +9611,12 @@
         <v>0</v>
       </c>
       <c r="J105" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="3:10">
       <c r="C106" s="2">
-        <v>2000315</v>
+        <v>2000311</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>328</v>
@@ -9615,12 +9637,12 @@
         <v>0</v>
       </c>
       <c r="J106" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107" customHeight="1" spans="3:10">
       <c r="C107" s="2">
-        <v>2000316</v>
+        <v>2000312</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>329</v>
@@ -9646,7 +9668,7 @@
     </row>
     <row r="108" customHeight="1" spans="3:10">
       <c r="C108" s="2">
-        <v>2000317</v>
+        <v>2000313</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>330</v>
@@ -9672,7 +9694,7 @@
     </row>
     <row r="109" customHeight="1" spans="3:10">
       <c r="C109" s="2">
-        <v>2000318</v>
+        <v>2000314</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>331</v>
@@ -9698,7 +9720,7 @@
     </row>
     <row r="110" customHeight="1" spans="3:10">
       <c r="C110" s="2">
-        <v>2000319</v>
+        <v>2000315</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>332</v>
@@ -9724,7 +9746,7 @@
     </row>
     <row r="111" customHeight="1" spans="3:10">
       <c r="C111" s="2">
-        <v>2000320</v>
+        <v>2000316</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>333</v>
@@ -9750,7 +9772,7 @@
     </row>
     <row r="112" customHeight="1" spans="3:10">
       <c r="C112" s="2">
-        <v>2000321</v>
+        <v>2000317</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>334</v>
@@ -9771,12 +9793,12 @@
         <v>0</v>
       </c>
       <c r="J112" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113" customHeight="1" spans="3:10">
       <c r="C113" s="2">
-        <v>2000322</v>
+        <v>2000318</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>335</v>
@@ -9797,12 +9819,12 @@
         <v>0</v>
       </c>
       <c r="J113" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114" customHeight="1" spans="3:10">
       <c r="C114" s="2">
-        <v>2000323</v>
+        <v>2000319</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>336</v>
@@ -9823,12 +9845,12 @@
         <v>0</v>
       </c>
       <c r="J114" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115" customHeight="1" spans="3:10">
       <c r="C115" s="2">
-        <v>2000324</v>
+        <v>2000320</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>337</v>
@@ -9849,12 +9871,12 @@
         <v>0</v>
       </c>
       <c r="J115" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116" customHeight="1" spans="3:10">
       <c r="C116" s="2">
-        <v>2000325</v>
+        <v>2000321</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>338</v>
@@ -9880,7 +9902,7 @@
     </row>
     <row r="117" customHeight="1" spans="3:10">
       <c r="C117" s="2">
-        <v>2000326</v>
+        <v>2000322</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>339</v>
@@ -9906,7 +9928,7 @@
     </row>
     <row r="118" customHeight="1" spans="3:10">
       <c r="C118" s="2">
-        <v>2000327</v>
+        <v>2000323</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>340</v>
@@ -9927,12 +9949,12 @@
         <v>0</v>
       </c>
       <c r="J118" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119" customHeight="1" spans="3:10">
       <c r="C119" s="2">
-        <v>2000328</v>
+        <v>2000324</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>341</v>
@@ -9953,12 +9975,12 @@
         <v>0</v>
       </c>
       <c r="J119" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120" customHeight="1" spans="3:10">
       <c r="C120" s="2">
-        <v>2000329</v>
+        <v>2000325</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>342</v>
@@ -9979,6 +10001,110 @@
         <v>0</v>
       </c>
       <c r="J120" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="121" customHeight="1" spans="3:10">
+      <c r="C121" s="2">
+        <v>2000326</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="E121" s="2">
+        <v>11</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G121" s="2">
+        <v>1</v>
+      </c>
+      <c r="H121" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I121" s="2">
+        <v>0</v>
+      </c>
+      <c r="J121" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="122" customHeight="1" spans="3:10">
+      <c r="C122" s="2">
+        <v>2000327</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="E122" s="2">
+        <v>11</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G122" s="2">
+        <v>1</v>
+      </c>
+      <c r="H122" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I122" s="2">
+        <v>0</v>
+      </c>
+      <c r="J122" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123" customHeight="1" spans="3:10">
+      <c r="C123" s="2">
+        <v>2000328</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="E123" s="2">
+        <v>11</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G123" s="2">
+        <v>1</v>
+      </c>
+      <c r="H123" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I123" s="2">
+        <v>0</v>
+      </c>
+      <c r="J123" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" customHeight="1" spans="3:10">
+      <c r="C124" s="2">
+        <v>2000329</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="E124" s="2">
+        <v>11</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G124" s="2">
+        <v>1</v>
+      </c>
+      <c r="H124" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I124" s="2">
+        <v>0</v>
+      </c>
+      <c r="J124" s="2">
         <v>4</v>
       </c>
     </row>
@@ -10126,13 +10252,13 @@
         <v>3000001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="E6" s="2">
         <v>13</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -10154,13 +10280,13 @@
         <v>3000002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="E7" s="2">
         <v>13</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -10182,13 +10308,13 @@
         <v>3000003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="E8" s="2">
         <v>13</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -10210,13 +10336,13 @@
         <v>3000004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="E9" s="2">
         <v>13</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -10238,13 +10364,13 @@
         <v>3000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="E10" s="2">
         <v>13</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -10266,13 +10392,13 @@
         <v>3000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="E11" s="2">
         <v>13</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -10294,13 +10420,13 @@
         <v>3000007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="E12" s="2">
         <v>13</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -10322,13 +10448,13 @@
         <v>3000008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E13" s="2">
         <v>13</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -10350,13 +10476,13 @@
         <v>3000009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="E14" s="2">
         <v>13</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -10378,13 +10504,13 @@
         <v>3000010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="E15" s="2">
         <v>13</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -10406,13 +10532,13 @@
         <v>3000011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="E16" s="2">
         <v>13</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -10434,13 +10560,13 @@
         <v>3000012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="E17" s="2">
         <v>13</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -10462,13 +10588,13 @@
         <v>3000013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="E18" s="2">
         <v>13</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -10490,13 +10616,13 @@
         <v>3000014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="E19" s="2">
         <v>13</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -10518,13 +10644,13 @@
         <v>3000015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="E20" s="2">
         <v>13</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -10546,13 +10672,13 @@
         <v>3000016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="E21" s="2">
         <v>13</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -10574,13 +10700,13 @@
         <v>3000017</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="E22" s="2">
         <v>13</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -10602,13 +10728,13 @@
         <v>3000018</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="E23" s="2">
         <v>13</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -10630,13 +10756,13 @@
         <v>3000019</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="E24" s="2">
         <v>13</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -10658,13 +10784,13 @@
         <v>3000020</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="E25" s="2">
         <v>13</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -10686,13 +10812,13 @@
         <v>3000021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="E26" s="2">
         <v>13</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -10714,13 +10840,13 @@
         <v>3000022</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="E27" s="2">
         <v>13</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -10742,13 +10868,13 @@
         <v>3000023</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="E28" s="2">
         <v>13</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -10770,13 +10896,13 @@
         <v>3000024</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E29" s="2">
         <v>13</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -10798,13 +10924,13 @@
         <v>3000025</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="E30" s="2">
         <v>13</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -10826,13 +10952,13 @@
         <v>3000026</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E31" s="2">
         <v>13</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -10854,13 +10980,13 @@
         <v>3000027</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="E32" s="2">
         <v>13</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -10882,13 +11008,13 @@
         <v>3000028</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E33" s="2">
         <v>13</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -10910,13 +11036,13 @@
         <v>3000029</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="E34" s="2">
         <v>13</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -10938,13 +11064,13 @@
         <v>3000030</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="E35" s="2">
         <v>13</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -10966,13 +11092,13 @@
         <v>3000031</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="E36" s="2">
         <v>13</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -10994,13 +11120,13 @@
         <v>3000032</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E37" s="2">
         <v>13</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G37" s="2">
         <v>1</v>
@@ -11022,13 +11148,13 @@
         <v>3000033</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="E38" s="2">
         <v>13</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G38" s="2">
         <v>1</v>
@@ -11050,13 +11176,13 @@
         <v>3000034</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="E39" s="2">
         <v>13</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -11078,13 +11204,13 @@
         <v>3000035</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="E40" s="2">
         <v>13</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -11106,13 +11232,13 @@
         <v>3000036</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="E41" s="2">
         <v>13</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -11134,13 +11260,13 @@
         <v>3000037</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="E42" s="2">
         <v>13</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -11162,13 +11288,13 @@
         <v>3000038</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="E43" s="2">
         <v>13</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -11190,13 +11316,13 @@
         <v>3000039</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="E44" s="2">
         <v>13</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -11218,13 +11344,13 @@
         <v>3000040</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="E45" s="2">
         <v>13</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G45" s="2">
         <v>1</v>
@@ -11246,13 +11372,13 @@
         <v>3000041</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="E46" s="2">
         <v>13</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -11274,13 +11400,13 @@
         <v>3000042</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="E47" s="2">
         <v>13</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -11302,13 +11428,13 @@
         <v>3000043</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="E48" s="2">
         <v>13</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -11330,13 +11456,13 @@
         <v>3000044</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="E49" s="2">
         <v>13</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -11358,13 +11484,13 @@
         <v>3000045</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="E50" s="2">
         <v>13</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -11386,13 +11512,13 @@
         <v>3000046</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="E51" s="2">
         <v>13</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -11414,13 +11540,13 @@
         <v>3000047</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E52" s="2">
         <v>13</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -11442,13 +11568,13 @@
         <v>3000048</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="E53" s="2">
         <v>13</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G53" s="2">
         <v>1</v>
@@ -11607,13 +11733,13 @@
         <v>40000051</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="E7" s="2">
         <v>14</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -11639,13 +11765,13 @@
         <v>40000052</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="E8" s="2">
         <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -11671,13 +11797,13 @@
         <v>40000053</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="E9" s="2">
         <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -11703,13 +11829,13 @@
         <v>40000054</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="E10" s="2">
         <v>14</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -11735,13 +11861,13 @@
         <v>40000055</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="E11" s="2">
         <v>14</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -11767,13 +11893,13 @@
         <v>40000056</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="E12" s="2">
         <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -11799,13 +11925,13 @@
         <v>40000057</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="E13" s="2">
         <v>14</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -11831,13 +11957,13 @@
         <v>40000058</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="E14" s="2">
         <v>14</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -11863,13 +11989,13 @@
         <v>40000059</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="E15" s="2">
         <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -11895,13 +12021,13 @@
         <v>40000060</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="E16" s="2">
         <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -11927,13 +12053,13 @@
         <v>40000061</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="E17" s="2">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -11959,13 +12085,13 @@
         <v>40000062</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E18" s="2">
         <v>14</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -11991,13 +12117,13 @@
         <v>40000063</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="E19" s="2">
         <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -12023,13 +12149,13 @@
         <v>40000064</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="E20" s="2">
         <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -12055,13 +12181,13 @@
         <v>40000065</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="E21" s="2">
         <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -12087,13 +12213,13 @@
         <v>40000066</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="E22" s="2">
         <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -12119,13 +12245,13 @@
         <v>40000067</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="E23" s="2">
         <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -12151,13 +12277,13 @@
         <v>40000068</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="E24" s="2">
         <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -12183,13 +12309,13 @@
         <v>40000069</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="E25" s="2">
         <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -12215,13 +12341,13 @@
         <v>40000070</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="E26" s="2">
         <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -12247,13 +12373,13 @@
         <v>40000071</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="E27" s="2">
         <v>14</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -12279,13 +12405,13 @@
         <v>40000072</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="E28" s="2">
         <v>14</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -12311,13 +12437,13 @@
         <v>40000073</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="E29" s="2">
         <v>14</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -12343,13 +12469,13 @@
         <v>40000074</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="E30" s="2">
         <v>14</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -12375,13 +12501,13 @@
         <v>40000075</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="E31" s="2">
         <v>14</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -12407,13 +12533,13 @@
         <v>40000076</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="E32" s="2">
         <v>14</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -12439,13 +12565,13 @@
         <v>40000077</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="E33" s="2">
         <v>14</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -12471,13 +12597,13 @@
         <v>40000078</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="E34" s="2">
         <v>14</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -12503,13 +12629,13 @@
         <v>40000079</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="E35" s="2">
         <v>14</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -12535,13 +12661,13 @@
         <v>40000080</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E36" s="2">
         <v>14</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -12567,13 +12693,13 @@
         <v>40000081</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="E37" s="2">
         <v>14</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G37" s="2">
         <v>1</v>
@@ -12599,13 +12725,13 @@
         <v>40000082</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="E38" s="2">
         <v>14</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G38" s="2">
         <v>1</v>
@@ -12631,13 +12757,13 @@
         <v>40000083</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="E39" s="2">
         <v>14</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -12663,13 +12789,13 @@
         <v>40000084</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="E40" s="2">
         <v>14</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -12695,13 +12821,13 @@
         <v>40000085</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="E41" s="2">
         <v>14</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -12727,13 +12853,13 @@
         <v>40000086</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="E42" s="2">
         <v>14</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -12759,13 +12885,13 @@
         <v>40000087</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="E43" s="2">
         <v>14</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -12791,13 +12917,13 @@
         <v>40000088</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="E44" s="2">
         <v>14</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -12823,13 +12949,13 @@
         <v>40000089</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="E45" s="2">
         <v>14</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G45" s="2">
         <v>1</v>
@@ -12855,13 +12981,13 @@
         <v>40000090</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="E46" s="2">
         <v>14</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -12887,13 +13013,13 @@
         <v>40000091</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="E47" s="2">
         <v>14</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -12919,13 +13045,13 @@
         <v>40000092</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="E48" s="2">
         <v>14</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -12951,13 +13077,13 @@
         <v>40000093</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E49" s="2">
         <v>14</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -12983,13 +13109,13 @@
         <v>40000094</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="E50" s="2">
         <v>14</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -13015,13 +13141,13 @@
         <v>40000095</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="E51" s="2">
         <v>14</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -13047,13 +13173,13 @@
         <v>40000096</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E52" s="2">
         <v>14</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -13079,13 +13205,13 @@
         <v>40000097</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="E53" s="2">
         <v>14</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G53" s="2">
         <v>1</v>
@@ -13111,13 +13237,13 @@
         <v>40000098</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="E54" s="2">
         <v>14</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G54" s="2">
         <v>1</v>
@@ -13143,13 +13269,13 @@
         <v>40000099</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="E55" s="2">
         <v>14</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G55" s="2">
         <v>1</v>
@@ -13175,13 +13301,13 @@
         <v>40000100</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="E56" s="2">
         <v>14</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G56" s="2">
         <v>1</v>
@@ -13207,13 +13333,13 @@
         <v>40000101</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E57" s="2">
         <v>14</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G57" s="2">
         <v>1</v>
@@ -13239,13 +13365,13 @@
         <v>40000102</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="E58" s="2">
         <v>14</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G58" s="2">
         <v>1</v>
@@ -13271,13 +13397,13 @@
         <v>40000103</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="E59" s="2">
         <v>14</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G59" s="2">
         <v>1</v>
@@ -13303,13 +13429,13 @@
         <v>40000104</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E60" s="2">
         <v>14</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G60" s="2">
         <v>1</v>
@@ -13335,13 +13461,13 @@
         <v>40000105</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="E61" s="7">
         <v>14</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G61" s="7">
         <v>1</v>
@@ -13368,13 +13494,13 @@
         <v>40000106</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="E62" s="2">
         <v>14</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G62" s="2">
         <v>1</v>
@@ -13401,13 +13527,13 @@
         <v>40000107</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="E63" s="2">
         <v>14</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G63" s="2">
         <v>1</v>
@@ -13434,13 +13560,13 @@
         <v>40000108</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="E64" s="2">
         <v>14</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G64" s="2">
         <v>1</v>
@@ -13467,13 +13593,13 @@
         <v>40000109</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="E65" s="2">
         <v>14</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G65" s="2">
         <v>1</v>
@@ -13500,13 +13626,13 @@
         <v>40000110</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="E66" s="2">
         <v>14</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G66" s="2">
         <v>1</v>
@@ -13533,13 +13659,13 @@
         <v>40000111</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="E67" s="2">
         <v>14</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G67" s="2">
         <v>1</v>
@@ -13566,13 +13692,13 @@
         <v>40000112</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="E68" s="2">
         <v>14</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G68" s="2">
         <v>1</v>
@@ -13599,13 +13725,13 @@
         <v>40000113</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="E69" s="2">
         <v>14</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G69" s="2">
         <v>1</v>
@@ -13632,13 +13758,13 @@
         <v>40000114</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="E70" s="2">
         <v>14</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G70" s="2">
         <v>1</v>
@@ -13665,13 +13791,13 @@
         <v>40000115</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="E71" s="2">
         <v>14</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G71" s="2">
         <v>1</v>
@@ -13698,13 +13824,13 @@
         <v>40000116</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="E72" s="2">
         <v>14</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G72" s="2">
         <v>1</v>
@@ -13731,13 +13857,13 @@
         <v>40000117</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="E73" s="2">
         <v>14</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G73" s="2">
         <v>1</v>
@@ -13764,13 +13890,13 @@
         <v>40000118</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="E74" s="2">
         <v>14</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G74" s="2">
         <v>1</v>
@@ -13797,13 +13923,13 @@
         <v>40000119</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E75" s="2">
         <v>14</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G75" s="2">
         <v>1</v>
@@ -13830,13 +13956,13 @@
         <v>40000120</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="E76" s="2">
         <v>14</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G76" s="2">
         <v>1</v>
@@ -13863,13 +13989,13 @@
         <v>40000121</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="E77" s="2">
         <v>14</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G77" s="2">
         <v>1</v>
@@ -13896,13 +14022,13 @@
         <v>40000122</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="E78" s="2">
         <v>14</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G78" s="2">
         <v>1</v>
@@ -13929,13 +14055,13 @@
         <v>40000123</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="E79" s="2">
         <v>14</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G79" s="2">
         <v>1</v>
@@ -13962,13 +14088,13 @@
         <v>40000124</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E80" s="2">
         <v>14</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G80" s="2">
         <v>1</v>
@@ -13995,13 +14121,13 @@
         <v>40000125</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="E81" s="2">
         <v>14</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G81" s="2">
         <v>1</v>
@@ -14027,13 +14153,13 @@
         <v>40000126</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="E82" s="2">
         <v>14</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G82" s="2">
         <v>1</v>
@@ -14059,13 +14185,13 @@
         <v>40000127</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="E83" s="2">
         <v>14</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G83" s="2">
         <v>1</v>
@@ -14091,13 +14217,13 @@
         <v>40000128</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="E84" s="2">
         <v>14</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G84" s="2">
         <v>1</v>
@@ -14123,13 +14249,13 @@
         <v>40000129</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="E85" s="2">
         <v>14</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G85" s="2">
         <v>1</v>
@@ -14155,13 +14281,13 @@
         <v>40000130</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="E86" s="2">
         <v>14</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G86" s="2">
         <v>1</v>
@@ -14187,13 +14313,13 @@
         <v>40000131</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="E87" s="2">
         <v>14</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G87" s="2">
         <v>1</v>
@@ -14219,13 +14345,13 @@
         <v>40000132</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="E88" s="2">
         <v>14</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G88" s="2">
         <v>1</v>
@@ -14251,13 +14377,13 @@
         <v>40000133</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="E89" s="2">
         <v>14</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G89" s="2">
         <v>1</v>
@@ -14283,13 +14409,13 @@
         <v>40000134</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E90" s="2">
         <v>14</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G90" s="2">
         <v>1</v>
@@ -14315,13 +14441,13 @@
         <v>40000135</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="E91" s="2">
         <v>14</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G91" s="2">
         <v>1</v>
@@ -14347,13 +14473,13 @@
         <v>40000136</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="E92" s="2">
         <v>14</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G92" s="2">
         <v>1</v>
@@ -14379,13 +14505,13 @@
         <v>40000137</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="E93" s="2">
         <v>14</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G93" s="2">
         <v>1</v>
@@ -14411,13 +14537,13 @@
         <v>40000138</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="E94" s="2">
         <v>14</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G94" s="2">
         <v>1</v>
@@ -14443,13 +14569,13 @@
         <v>40000139</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="E95" s="2">
         <v>14</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G95" s="2">
         <v>1</v>
@@ -14614,13 +14740,13 @@
         <v>50000001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="E6" s="2">
         <v>5</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -14646,13 +14772,13 @@
         <v>50000002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="E7" s="2">
         <v>5</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -14678,13 +14804,13 @@
         <v>50000003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="E8" s="2">
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -14710,13 +14836,13 @@
         <v>50000004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="E9" s="2">
         <v>5</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -14742,13 +14868,13 @@
         <v>50000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="E10" s="2">
         <v>5</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -14774,13 +14900,13 @@
         <v>50000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="E11" s="2">
         <v>5</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -14806,13 +14932,13 @@
         <v>50000007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="E12" s="2">
         <v>5</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -14838,13 +14964,13 @@
         <v>50000008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="E13" s="2">
         <v>5</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -14870,13 +14996,13 @@
         <v>50000009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="E14" s="2">
         <v>5</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -14902,13 +15028,13 @@
         <v>50000010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="E15" s="2">
         <v>5</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -14934,13 +15060,13 @@
         <v>50000011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="E16" s="2">
         <v>5</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -14966,13 +15092,13 @@
         <v>50000012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="E17" s="2">
         <v>5</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -14998,13 +15124,13 @@
         <v>50000013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="E18" s="2">
         <v>5</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -15030,13 +15156,13 @@
         <v>50000014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="E19" s="2">
         <v>5</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -15062,13 +15188,13 @@
         <v>50000015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="E20" s="2">
         <v>5</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -15094,13 +15220,13 @@
         <v>50000016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="E21" s="2">
         <v>5</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -15126,13 +15252,13 @@
         <v>50000017</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="E22" s="2">
         <v>5</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -15158,13 +15284,13 @@
         <v>50000018</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="E23" s="2">
         <v>5</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -15190,13 +15316,13 @@
         <v>50000019</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="E24" s="2">
         <v>5</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -15222,13 +15348,13 @@
         <v>50000020</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="E25" s="2">
         <v>5</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -15254,13 +15380,13 @@
         <v>50000021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E26" s="2">
         <v>5</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -15286,13 +15412,13 @@
         <v>50000022</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="E27" s="2">
         <v>5</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -15318,13 +15444,13 @@
         <v>50000023</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="E28" s="2">
         <v>5</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -15350,13 +15476,13 @@
         <v>50000024</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="E29" s="2">
         <v>5</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -15382,13 +15508,13 @@
         <v>50000025</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="E30" s="2">
         <v>5</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -15414,13 +15540,13 @@
         <v>50000026</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="E31" s="2">
         <v>5</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -15446,13 +15572,13 @@
         <v>50000027</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="E32" s="2">
         <v>5</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -15478,13 +15604,13 @@
         <v>50000028</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="E33" s="2">
         <v>5</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -15510,13 +15636,13 @@
         <v>50000029</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="E34" s="2">
         <v>5</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -15542,13 +15668,13 @@
         <v>50000030</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="E35" s="2">
         <v>5</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -15574,13 +15700,13 @@
         <v>50000031</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="E36" s="2">
         <v>5</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -15606,13 +15732,13 @@
         <v>50000032</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="E37" s="2">
         <v>5</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G37" s="2">
         <v>1</v>
@@ -15638,13 +15764,13 @@
         <v>50000033</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="E38" s="2">
         <v>5</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="G38" s="2">
         <v>1</v>
@@ -15670,13 +15796,13 @@
         <v>50000034</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="E39" s="2">
         <v>5</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -15702,13 +15828,13 @@
         <v>50000035</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="E40" s="2">
         <v>5</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -15734,13 +15860,13 @@
         <v>50000036</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="E41" s="2">
         <v>5</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -15766,13 +15892,13 @@
         <v>50000037</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="E42" s="2">
         <v>5</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -15798,13 +15924,13 @@
         <v>50000038</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="E43" s="2">
         <v>5</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -15830,13 +15956,13 @@
         <v>50000039</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="E44" s="2">
         <v>5</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -15862,13 +15988,13 @@
         <v>50000040</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="E45" s="2">
         <v>5</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="G45" s="2">
         <v>1</v>
@@ -15894,13 +16020,13 @@
         <v>50000041</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="E46" s="2">
         <v>5</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -15926,13 +16052,13 @@
         <v>50000042</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="E47" s="2">
         <v>5</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -15958,13 +16084,13 @@
         <v>50000043</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="E48" s="2">
         <v>5</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -15990,13 +16116,13 @@
         <v>50000044</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="E49" s="2">
         <v>5</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -16022,13 +16148,13 @@
         <v>50000045</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="E50" s="2">
         <v>5</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -16054,13 +16180,13 @@
         <v>50000046</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="E51" s="2">
         <v>5</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -16086,13 +16212,13 @@
         <v>50000047</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="E52" s="2">
         <v>5</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -16118,13 +16244,13 @@
         <v>50000048</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="E53" s="2">
         <v>5</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="G53" s="2">
         <v>1</v>
@@ -16150,13 +16276,13 @@
         <v>50000049</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="E54" s="2">
         <v>5</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="G54" s="2">
         <v>1</v>
@@ -16182,13 +16308,13 @@
         <v>50000050</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E55" s="2">
         <v>5</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="G55" s="2">
         <v>1</v>
@@ -16214,13 +16340,13 @@
         <v>50000051</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="E56" s="2">
         <v>5</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="G56" s="2">
         <v>1</v>
@@ -16246,13 +16372,13 @@
         <v>50000052</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="E57" s="2">
         <v>5</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="G57" s="2">
         <v>1</v>
@@ -16278,13 +16404,13 @@
         <v>50000053</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="E58" s="2">
         <v>5</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="G58" s="2">
         <v>1</v>
@@ -16310,13 +16436,13 @@
         <v>50000054</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="E59" s="2">
         <v>5</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="G59" s="2">
         <v>1</v>
@@ -16342,13 +16468,13 @@
         <v>50000055</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="E60" s="2">
         <v>5</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="G60" s="2">
         <v>1</v>
@@ -16374,13 +16500,13 @@
         <v>50000056</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="E61" s="2">
         <v>5</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="G61" s="2">
         <v>1</v>
@@ -16406,13 +16532,13 @@
         <v>50000057</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="E62" s="2">
         <v>5</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="G62" s="2">
         <v>1</v>
@@ -16438,13 +16564,13 @@
         <v>50000058</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="E63" s="2">
         <v>5</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="G63" s="2">
         <v>1</v>
@@ -16470,13 +16596,13 @@
         <v>50000059</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="E64" s="2">
         <v>5</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="G64" s="2">
         <v>1</v>
@@ -16502,13 +16628,13 @@
         <v>50000060</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="E65" s="2">
         <v>5</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="G65" s="2">
         <v>1</v>
@@ -16534,13 +16660,13 @@
         <v>50000061</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="E66" s="2">
         <v>5</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="G66" s="2">
         <v>1</v>
@@ -16566,13 +16692,13 @@
         <v>50000062</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="E67" s="2">
         <v>5</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="G67" s="2">
         <v>1</v>
@@ -16598,13 +16724,13 @@
         <v>50000063</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="E68" s="2">
         <v>5</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="G68" s="2">
         <v>1</v>
@@ -16630,13 +16756,13 @@
         <v>50000064</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="E69" s="2">
         <v>5</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="G69" s="2">
         <v>1</v>
@@ -16662,13 +16788,13 @@
         <v>50000065</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="E70" s="2">
         <v>5</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="G70" s="2">
         <v>1</v>
@@ -16694,13 +16820,13 @@
         <v>50000066</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="E71" s="2">
         <v>5</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="G71" s="2">
         <v>1</v>
@@ -16726,13 +16852,13 @@
         <v>50000067</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="E72" s="2">
         <v>5</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="G72" s="2">
         <v>1</v>
@@ -16758,13 +16884,13 @@
         <v>50000068</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="E73" s="2">
         <v>5</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="G73" s="2">
         <v>1</v>
@@ -16790,13 +16916,13 @@
         <v>50000069</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="E74" s="2">
         <v>5</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="G74" s="2">
         <v>1</v>
@@ -16822,13 +16948,13 @@
         <v>50000070</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="E75" s="2">
         <v>5</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="G75" s="2">
         <v>1</v>
@@ -16854,13 +16980,13 @@
         <v>50000071</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="E76" s="2">
         <v>5</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="G76" s="2">
         <v>1</v>
@@ -16886,13 +17012,13 @@
         <v>50000072</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="E77" s="2">
         <v>5</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="G77" s="2">
         <v>1</v>
@@ -16918,13 +17044,13 @@
         <v>50000073</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="E78" s="2">
         <v>5</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="G78" s="2">
         <v>1</v>
@@ -16950,13 +17076,13 @@
         <v>50000074</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="E79" s="2">
         <v>5</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="G79" s="2">
         <v>1</v>
@@ -16982,13 +17108,13 @@
         <v>50000075</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="E80" s="2">
         <v>5</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="G80" s="2">
         <v>1</v>
@@ -17014,13 +17140,13 @@
         <v>50000076</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="E81" s="2">
         <v>5</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="G81" s="2">
         <v>1</v>
@@ -17046,13 +17172,13 @@
         <v>50000077</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="E82" s="2">
         <v>5</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="G82" s="2">
         <v>1</v>
@@ -17078,13 +17204,13 @@
         <v>50000078</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="E83" s="2">
         <v>5</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="G83" s="2">
         <v>1</v>
@@ -17110,13 +17236,13 @@
         <v>50000079</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="E84" s="2">
         <v>5</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G84" s="2">
         <v>1</v>
@@ -17142,13 +17268,13 @@
         <v>50000080</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="E85" s="2">
         <v>5</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="G85" s="2">
         <v>1</v>
@@ -17174,13 +17300,13 @@
         <v>50000081</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="E86" s="2">
         <v>5</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G86" s="2">
         <v>1</v>
@@ -17206,13 +17332,13 @@
         <v>50000082</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="E87" s="2">
         <v>5</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="G87" s="2">
         <v>1</v>
@@ -17238,13 +17364,13 @@
         <v>50000083</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="E88" s="2">
         <v>5</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="G88" s="2">
         <v>1</v>
@@ -17270,13 +17396,13 @@
         <v>50000084</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="E89" s="2">
         <v>5</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="G89" s="2">
         <v>1</v>
@@ -17302,13 +17428,13 @@
         <v>50000085</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="E90" s="2">
         <v>5</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="G90" s="2">
         <v>1</v>
@@ -17334,13 +17460,13 @@
         <v>50000086</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="E91" s="2">
         <v>5</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="G91" s="2">
         <v>1</v>
@@ -17366,13 +17492,13 @@
         <v>50000087</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="E92" s="2">
         <v>5</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="G92" s="2">
         <v>1</v>
@@ -17398,13 +17524,13 @@
         <v>50000088</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="E93" s="2">
         <v>5</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="G93" s="2">
         <v>1</v>
@@ -17430,13 +17556,13 @@
         <v>50000089</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="E94" s="2">
         <v>5</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="G94" s="2">
         <v>1</v>
@@ -17462,13 +17588,13 @@
         <v>50000090</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="E95" s="2">
         <v>5</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="G95" s="2">
         <v>1</v>
@@ -17494,13 +17620,13 @@
         <v>50000091</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="E96" s="2">
         <v>5</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="G96" s="2">
         <v>1</v>
@@ -17526,13 +17652,13 @@
         <v>50000092</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="E97" s="2">
         <v>5</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="G97" s="2">
         <v>1</v>
@@ -17558,13 +17684,13 @@
         <v>50000093</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="E98" s="2">
         <v>5</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="G98" s="2">
         <v>1</v>
@@ -17590,13 +17716,13 @@
         <v>50000094</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="E99" s="2">
         <v>5</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="G99" s="2">
         <v>1</v>
@@ -17622,13 +17748,13 @@
         <v>50000095</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="E100" s="2">
         <v>5</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="G100" s="2">
         <v>1</v>
@@ -17654,13 +17780,13 @@
         <v>50000096</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="E101" s="2">
         <v>5</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="G101" s="2">
         <v>1</v>
@@ -17686,13 +17812,13 @@
         <v>50000097</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="E102" s="2">
         <v>5</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="G102" s="2">
         <v>1</v>
@@ -17718,13 +17844,13 @@
         <v>50000098</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="E103" s="2">
         <v>5</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="G103" s="2">
         <v>1</v>
@@ -17750,13 +17876,13 @@
         <v>50000099</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="E104" s="2">
         <v>5</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="G104" s="2">
         <v>1</v>
@@ -17782,13 +17908,13 @@
         <v>50000100</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="E105" s="2">
         <v>5</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="G105" s="2">
         <v>1</v>
@@ -17814,13 +17940,13 @@
         <v>50000101</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="E106" s="2">
         <v>5</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="G106" s="2">
         <v>1</v>
@@ -17846,13 +17972,13 @@
         <v>50000102</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="E107" s="2">
         <v>5</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="G107" s="2">
         <v>1</v>
@@ -17878,13 +18004,13 @@
         <v>50000103</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="E108" s="2">
         <v>5</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="G108" s="2">
         <v>1</v>
@@ -17910,13 +18036,13 @@
         <v>50000104</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="E109" s="2">
         <v>5</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="G109" s="2">
         <v>1</v>
@@ -18081,13 +18207,13 @@
         <v>180001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="E6" s="2">
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -18107,13 +18233,13 @@
         <v>180002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="E7" s="2">
         <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -18133,13 +18259,13 @@
         <v>180003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="E8" s="2">
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -18159,13 +18285,13 @@
         <v>180004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="E9" s="2">
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -18185,13 +18311,13 @@
         <v>180005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="E10" s="2">
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -18211,13 +18337,13 @@
         <v>180006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="E11" s="2">
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -18239,13 +18365,13 @@
         <v>180007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="E12" s="2">
         <v>18</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -18267,13 +18393,13 @@
         <v>180008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="E13" s="2">
         <v>18</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -18295,13 +18421,13 @@
         <v>180009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="E14" s="2">
         <v>18</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -18323,13 +18449,13 @@
         <v>180010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="E15" s="2">
         <v>18</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -18351,13 +18477,13 @@
         <v>180011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="E16" s="2">
         <v>18</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -18379,13 +18505,13 @@
         <v>180012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="E17" s="2">
         <v>18</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -18407,13 +18533,13 @@
         <v>180013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="E18" s="2">
         <v>18</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -18435,13 +18561,13 @@
         <v>180014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="E19" s="2">
         <v>18</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -18463,13 +18589,13 @@
         <v>180015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="E20" s="2">
         <v>18</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -18491,13 +18617,13 @@
         <v>180016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="E21" s="2">
         <v>18</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -18519,13 +18645,13 @@
         <v>180017</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="E22" s="2">
         <v>18</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -18547,13 +18673,13 @@
         <v>180018</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="E23" s="2">
         <v>18</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -18575,13 +18701,13 @@
         <v>180019</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="E24" s="2">
         <v>18</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -18603,13 +18729,13 @@
         <v>180020</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="E25" s="2">
         <v>18</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -18631,13 +18757,13 @@
         <v>180021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="E26" s="2">
         <v>18</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -18664,13 +18790,13 @@
         <v>180030</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="E28" s="2">
         <v>18</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -18692,13 +18818,13 @@
         <v>180031</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="E29" s="2">
         <v>18</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="G29" s="3">
         <v>1</v>
@@ -18718,13 +18844,13 @@
         <v>180032</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="E30" s="2">
         <v>18</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="G30" s="3">
         <v>1</v>
@@ -18744,13 +18870,13 @@
         <v>180033</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="E31" s="2">
         <v>18</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="G31" s="3">
         <v>1</v>
@@ -18770,13 +18896,13 @@
         <v>180034</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="E32" s="2">
         <v>18</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="G32" s="3">
         <v>1</v>
@@ -18942,13 +19068,13 @@
         <v>190001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="E6" s="2">
         <v>19</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -18968,13 +19094,13 @@
         <v>190002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="E7" s="2">
         <v>19</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -18994,13 +19120,13 @@
         <v>190003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="E8" s="2">
         <v>19</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -19020,13 +19146,13 @@
         <v>190004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="E9" s="2">
         <v>19</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -19046,13 +19172,13 @@
         <v>190005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="E10" s="2">
         <v>19</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -19072,13 +19198,13 @@
         <v>190006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="E11" s="2">
         <v>19</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="2"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -344,7 +344,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="731">
   <si>
     <t>_Id</t>
   </si>
@@ -1115,6 +1115,15 @@
   </si>
   <si>
     <t>龙城减伤</t>
+  </si>
+  <si>
+    <t>龙城物伤</t>
+  </si>
+  <si>
+    <t>龙城法伤</t>
+  </si>
+  <si>
+    <t>龙城道伤</t>
   </si>
   <si>
     <t>狗头黄金</t>
@@ -2540,7 +2549,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2580,6 +2589,12 @@
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
@@ -2732,12 +2747,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3073,16 +3088,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3091,119 +3103,122 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3217,7 +3232,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -3902,7 +3918,7 @@
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:13">
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="11" t="s">
         <v>53</v>
       </c>
       <c r="D13" s="3" t="s">
@@ -3920,7 +3936,7 @@
       <c r="H13" s="3">
         <v>99999999</v>
       </c>
-      <c r="I13" s="10" t="s">
+      <c r="I13" s="11" t="s">
         <v>56</v>
       </c>
       <c r="J13" s="3">
@@ -3937,7 +3953,7 @@
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:13">
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="11" t="s">
         <v>57</v>
       </c>
       <c r="D14" s="3" t="s">
@@ -3955,7 +3971,7 @@
       <c r="H14" s="3">
         <v>99999999</v>
       </c>
-      <c r="I14" s="10" t="s">
+      <c r="I14" s="11" t="s">
         <v>56</v>
       </c>
       <c r="J14" s="3">
@@ -3972,7 +3988,7 @@
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:13">
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="11" t="s">
         <v>60</v>
       </c>
       <c r="D15" s="3" t="s">
@@ -3990,7 +4006,7 @@
       <c r="H15" s="3">
         <v>99999999</v>
       </c>
-      <c r="I15" s="10" t="s">
+      <c r="I15" s="11" t="s">
         <v>56</v>
       </c>
       <c r="J15" s="3">
@@ -4007,7 +4023,7 @@
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:13">
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="11" t="s">
         <v>63</v>
       </c>
       <c r="D16" s="3" t="s">
@@ -4025,7 +4041,7 @@
       <c r="H16" s="3">
         <v>99999999</v>
       </c>
-      <c r="I16" s="10" t="s">
+      <c r="I16" s="11" t="s">
         <v>56</v>
       </c>
       <c r="J16" s="3">
@@ -4287,7 +4303,7 @@
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:13">
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="11" t="s">
         <v>87</v>
       </c>
       <c r="D25" s="3" t="s">
@@ -4305,7 +4321,7 @@
       <c r="H25" s="3">
         <v>99999999</v>
       </c>
-      <c r="I25" s="10" t="s">
+      <c r="I25" s="11" t="s">
         <v>56</v>
       </c>
       <c r="J25" s="3">
@@ -4322,7 +4338,7 @@
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:13">
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="11" t="s">
         <v>90</v>
       </c>
       <c r="D26" s="3" t="s">
@@ -4340,7 +4356,7 @@
       <c r="H26" s="3">
         <v>99999999</v>
       </c>
-      <c r="I26" s="10" t="s">
+      <c r="I26" s="11" t="s">
         <v>56</v>
       </c>
       <c r="J26" s="3">
@@ -4357,7 +4373,7 @@
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:13">
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="11" t="s">
         <v>93</v>
       </c>
       <c r="D27" s="3" t="s">
@@ -4375,7 +4391,7 @@
       <c r="H27" s="3">
         <v>99999999</v>
       </c>
-      <c r="I27" s="10" t="s">
+      <c r="I27" s="11" t="s">
         <v>56</v>
       </c>
       <c r="J27" s="3">
@@ -4392,7 +4408,7 @@
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:13">
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="11" t="s">
         <v>96</v>
       </c>
       <c r="D28" s="3" t="s">
@@ -4410,7 +4426,7 @@
       <c r="H28" s="3">
         <v>99999999</v>
       </c>
-      <c r="I28" s="10" t="s">
+      <c r="I28" s="11" t="s">
         <v>56</v>
       </c>
       <c r="J28" s="3">
@@ -4672,7 +4688,7 @@
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:13">
-      <c r="C37" s="10" t="s">
+      <c r="C37" s="11" t="s">
         <v>120</v>
       </c>
       <c r="D37" s="3" t="s">
@@ -4690,7 +4706,7 @@
       <c r="H37" s="3">
         <v>99999999</v>
       </c>
-      <c r="I37" s="10" t="s">
+      <c r="I37" s="11" t="s">
         <v>56</v>
       </c>
       <c r="J37" s="3">
@@ -4707,7 +4723,7 @@
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:13">
-      <c r="C38" s="10" t="s">
+      <c r="C38" s="11" t="s">
         <v>123</v>
       </c>
       <c r="D38" s="3" t="s">
@@ -4725,7 +4741,7 @@
       <c r="H38" s="3">
         <v>99999999</v>
       </c>
-      <c r="I38" s="10" t="s">
+      <c r="I38" s="11" t="s">
         <v>56</v>
       </c>
       <c r="J38" s="3">
@@ -4742,7 +4758,7 @@
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:13">
-      <c r="C39" s="10" t="s">
+      <c r="C39" s="11" t="s">
         <v>126</v>
       </c>
       <c r="D39" s="3" t="s">
@@ -4760,7 +4776,7 @@
       <c r="H39" s="3">
         <v>99999999</v>
       </c>
-      <c r="I39" s="10" t="s">
+      <c r="I39" s="11" t="s">
         <v>56</v>
       </c>
       <c r="J39" s="3">
@@ -4777,7 +4793,7 @@
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:13">
-      <c r="C40" s="10" t="s">
+      <c r="C40" s="11" t="s">
         <v>129</v>
       </c>
       <c r="D40" s="3" t="s">
@@ -4795,7 +4811,7 @@
       <c r="H40" s="3">
         <v>99999999</v>
       </c>
-      <c r="I40" s="10" t="s">
+      <c r="I40" s="11" t="s">
         <v>56</v>
       </c>
       <c r="J40" s="3">
@@ -6731,7 +6747,7 @@
       <c r="C67" s="3">
         <v>8101</v>
       </c>
-      <c r="D67" s="9" t="s">
+      <c r="D67" s="10" t="s">
         <v>226</v>
       </c>
       <c r="E67" s="3">
@@ -6763,7 +6779,7 @@
       <c r="C68" s="3">
         <v>8102</v>
       </c>
-      <c r="D68" s="9" t="s">
+      <c r="D68" s="10" t="s">
         <v>228</v>
       </c>
       <c r="E68" s="3">
@@ -6795,7 +6811,7 @@
       <c r="C69" s="3">
         <v>8103</v>
       </c>
-      <c r="D69" s="9" t="s">
+      <c r="D69" s="10" t="s">
         <v>229</v>
       </c>
       <c r="E69" s="3">
@@ -6827,7 +6843,7 @@
       <c r="C70" s="3">
         <v>8104</v>
       </c>
-      <c r="D70" s="9" t="s">
+      <c r="D70" s="10" t="s">
         <v>230</v>
       </c>
       <c r="E70" s="3">
@@ -6859,7 +6875,7 @@
       <c r="C71" s="3">
         <v>8105</v>
       </c>
-      <c r="D71" s="9" t="s">
+      <c r="D71" s="10" t="s">
         <v>231</v>
       </c>
       <c r="E71" s="3">
@@ -6891,7 +6907,7 @@
       <c r="C72" s="3">
         <v>8106</v>
       </c>
-      <c r="D72" s="9" t="s">
+      <c r="D72" s="10" t="s">
         <v>232</v>
       </c>
       <c r="E72" s="3">
@@ -6923,7 +6939,7 @@
       <c r="C73" s="3">
         <v>8107</v>
       </c>
-      <c r="D73" s="9" t="s">
+      <c r="D73" s="10" t="s">
         <v>233</v>
       </c>
       <c r="E73" s="3">
@@ -6955,7 +6971,7 @@
       <c r="C74" s="3">
         <v>8108</v>
       </c>
-      <c r="D74" s="9" t="s">
+      <c r="D74" s="10" t="s">
         <v>234</v>
       </c>
       <c r="E74" s="3">
@@ -7684,15 +7700,87 @@
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
     </row>
-    <row r="26" s="2" customFormat="1" customHeight="1" spans="12:13">
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C26" s="2">
+        <v>2000011</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="E26" s="2">
+        <v>11</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G26" s="2">
+        <v>1</v>
+      </c>
+      <c r="H26" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I26" s="2">
+        <v>0</v>
+      </c>
+      <c r="J26" s="2">
+        <v>5</v>
+      </c>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
     </row>
-    <row r="27" s="2" customFormat="1" customHeight="1" spans="12:13">
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C27" s="2">
+        <v>2000012</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="E27" s="2">
+        <v>11</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G27" s="2">
+        <v>1</v>
+      </c>
+      <c r="H27" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I27" s="2">
+        <v>0</v>
+      </c>
+      <c r="J27" s="2">
+        <v>5</v>
+      </c>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
     </row>
-    <row r="28" s="2" customFormat="1" customHeight="1" spans="12:13">
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C28" s="2">
+        <v>2000013</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="E28" s="2">
+        <v>11</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G28" s="2">
+        <v>1</v>
+      </c>
+      <c r="H28" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I28" s="2">
+        <v>0</v>
+      </c>
+      <c r="J28" s="2">
+        <v>5</v>
+      </c>
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
     </row>
@@ -7713,7 +7801,7 @@
         <v>2000100</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E32" s="2">
         <v>11</v>
@@ -7741,7 +7829,7 @@
         <v>2000101</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E33" s="2">
         <v>11</v>
@@ -7769,7 +7857,7 @@
         <v>2000102</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E34" s="2">
         <v>11</v>
@@ -7797,7 +7885,7 @@
         <v>2000103</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E35" s="2">
         <v>11</v>
@@ -7825,7 +7913,7 @@
         <v>2000104</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E36" s="2">
         <v>11</v>
@@ -7853,7 +7941,7 @@
         <v>2000105</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E37" s="2">
         <v>11</v>
@@ -7881,7 +7969,7 @@
         <v>2000106</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E38" s="2">
         <v>11</v>
@@ -7909,7 +7997,7 @@
         <v>2000107</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E39" s="2">
         <v>11</v>
@@ -7937,7 +8025,7 @@
         <v>2000108</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E40" s="2">
         <v>11</v>
@@ -7965,7 +8053,7 @@
         <v>2000109</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E41" s="2">
         <v>11</v>
@@ -7993,7 +8081,7 @@
         <v>2000110</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E42" s="2">
         <v>11</v>
@@ -8021,7 +8109,7 @@
         <v>2000111</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="E43" s="2">
         <v>11</v>
@@ -8049,7 +8137,7 @@
         <v>2000112</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="E44" s="2">
         <v>11</v>
@@ -8077,7 +8165,7 @@
         <v>2000113</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E45" s="2">
         <v>11</v>
@@ -8105,7 +8193,7 @@
         <v>2000114</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E46" s="2">
         <v>11</v>
@@ -8133,7 +8221,7 @@
         <v>2000115</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E47" s="2">
         <v>11</v>
@@ -8161,7 +8249,7 @@
         <v>2000116</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E48" s="2">
         <v>11</v>
@@ -8189,7 +8277,7 @@
         <v>2000117</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E49" s="2">
         <v>11</v>
@@ -8217,7 +8305,7 @@
         <v>2000118</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E50" s="2">
         <v>11</v>
@@ -8245,7 +8333,7 @@
         <v>2000119</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E51" s="2">
         <v>11</v>
@@ -8273,7 +8361,7 @@
         <v>2000120</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E52" s="2">
         <v>11</v>
@@ -8301,7 +8389,7 @@
         <v>2000121</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E53" s="2">
         <v>11</v>
@@ -8329,7 +8417,7 @@
         <v>2000122</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E54" s="2">
         <v>11</v>
@@ -8357,7 +8445,7 @@
         <v>2000123</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E55" s="2">
         <v>11</v>
@@ -8385,7 +8473,7 @@
         <v>2000124</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E56" s="2">
         <v>11</v>
@@ -8413,7 +8501,7 @@
         <v>2000125</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="E57" s="2">
         <v>11</v>
@@ -8441,7 +8529,7 @@
         <v>2000126</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="E58" s="2">
         <v>11</v>
@@ -8469,7 +8557,7 @@
         <v>2000127</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E59" s="2">
         <v>11</v>
@@ -8497,7 +8585,7 @@
         <v>2000128</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E60" s="2">
         <v>11</v>
@@ -8525,7 +8613,7 @@
         <v>2000129</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E61" s="2">
         <v>11</v>
@@ -8553,7 +8641,7 @@
         <v>2000200</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="E63" s="2">
         <v>11</v>
@@ -8579,7 +8667,7 @@
         <v>2000201</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E64" s="2">
         <v>11</v>
@@ -8605,7 +8693,7 @@
         <v>2000202</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E65" s="2">
         <v>11</v>
@@ -8631,7 +8719,7 @@
         <v>2000203</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="E66" s="2">
         <v>11</v>
@@ -8657,7 +8745,7 @@
         <v>2000204</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="E67" s="2">
         <v>11</v>
@@ -8683,7 +8771,7 @@
         <v>2000205</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="E68" s="2">
         <v>11</v>
@@ -8709,7 +8797,7 @@
         <v>2000206</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E69" s="2">
         <v>11</v>
@@ -8735,7 +8823,7 @@
         <v>2000207</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E70" s="2">
         <v>11</v>
@@ -8761,7 +8849,7 @@
         <v>2000208</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="E71" s="2">
         <v>11</v>
@@ -8787,7 +8875,7 @@
         <v>2000209</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E72" s="2">
         <v>11</v>
@@ -8813,7 +8901,7 @@
         <v>2000210</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="E73" s="2">
         <v>11</v>
@@ -8839,7 +8927,7 @@
         <v>2000211</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E74" s="2">
         <v>11</v>
@@ -8865,7 +8953,7 @@
         <v>2000212</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E75" s="2">
         <v>11</v>
@@ -8891,7 +8979,7 @@
         <v>2000213</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="E76" s="2">
         <v>11</v>
@@ -8917,7 +9005,7 @@
         <v>2000214</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E77" s="2">
         <v>11</v>
@@ -8943,7 +9031,7 @@
         <v>2000215</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="E78" s="2">
         <v>11</v>
@@ -8969,7 +9057,7 @@
         <v>2000216</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E79" s="2">
         <v>11</v>
@@ -8995,7 +9083,7 @@
         <v>2000217</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="E80" s="2">
         <v>11</v>
@@ -9021,7 +9109,7 @@
         <v>2000218</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E81" s="2">
         <v>11</v>
@@ -9047,7 +9135,7 @@
         <v>2000219</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E82" s="2">
         <v>11</v>
@@ -9073,7 +9161,7 @@
         <v>2000220</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="E83" s="2">
         <v>11</v>
@@ -9099,7 +9187,7 @@
         <v>2000221</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E84" s="2">
         <v>11</v>
@@ -9125,7 +9213,7 @@
         <v>2000222</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E85" s="2">
         <v>11</v>
@@ -9151,7 +9239,7 @@
         <v>2000223</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E86" s="2">
         <v>11</v>
@@ -9177,7 +9265,7 @@
         <v>2000224</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E87" s="2">
         <v>11</v>
@@ -9203,7 +9291,7 @@
         <v>2000225</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="E88" s="2">
         <v>11</v>
@@ -9229,7 +9317,7 @@
         <v>2000226</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E89" s="2">
         <v>11</v>
@@ -9255,7 +9343,7 @@
         <v>2000227</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E90" s="2">
         <v>11</v>
@@ -9281,7 +9369,7 @@
         <v>2000228</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="E91" s="2">
         <v>11</v>
@@ -9307,7 +9395,7 @@
         <v>2000229</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E92" s="2">
         <v>11</v>
@@ -9333,7 +9421,7 @@
         <v>2000300</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E95" s="2">
         <v>11</v>
@@ -9359,7 +9447,7 @@
         <v>2000301</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E96" s="2">
         <v>11</v>
@@ -9385,7 +9473,7 @@
         <v>2000302</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E97" s="2">
         <v>11</v>
@@ -9411,7 +9499,7 @@
         <v>2000303</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="E98" s="2">
         <v>11</v>
@@ -9437,7 +9525,7 @@
         <v>2000304</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="E99" s="2">
         <v>11</v>
@@ -9463,7 +9551,7 @@
         <v>2000305</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E100" s="2">
         <v>11</v>
@@ -9489,7 +9577,7 @@
         <v>2000306</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="E101" s="2">
         <v>11</v>
@@ -9515,7 +9603,7 @@
         <v>2000307</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E102" s="2">
         <v>11</v>
@@ -9541,7 +9629,7 @@
         <v>2000308</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E103" s="2">
         <v>11</v>
@@ -9567,7 +9655,7 @@
         <v>2000309</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E104" s="2">
         <v>11</v>
@@ -9593,7 +9681,7 @@
         <v>2000310</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E105" s="2">
         <v>11</v>
@@ -9619,7 +9707,7 @@
         <v>2000311</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="E106" s="2">
         <v>11</v>
@@ -9645,7 +9733,7 @@
         <v>2000312</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="E107" s="2">
         <v>11</v>
@@ -9671,7 +9759,7 @@
         <v>2000313</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="E108" s="2">
         <v>11</v>
@@ -9697,7 +9785,7 @@
         <v>2000314</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E109" s="2">
         <v>11</v>
@@ -9723,7 +9811,7 @@
         <v>2000315</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E110" s="2">
         <v>11</v>
@@ -9749,7 +9837,7 @@
         <v>2000316</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E111" s="2">
         <v>11</v>
@@ -9775,7 +9863,7 @@
         <v>2000317</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="E112" s="2">
         <v>11</v>
@@ -9801,7 +9889,7 @@
         <v>2000318</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E113" s="2">
         <v>11</v>
@@ -9827,7 +9915,7 @@
         <v>2000319</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E114" s="2">
         <v>11</v>
@@ -9853,7 +9941,7 @@
         <v>2000320</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="E115" s="2">
         <v>11</v>
@@ -9879,7 +9967,7 @@
         <v>2000321</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="E116" s="2">
         <v>11</v>
@@ -9905,7 +9993,7 @@
         <v>2000322</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="E117" s="2">
         <v>11</v>
@@ -9931,7 +10019,7 @@
         <v>2000323</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E118" s="2">
         <v>11</v>
@@ -9957,7 +10045,7 @@
         <v>2000324</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="E119" s="2">
         <v>11</v>
@@ -9983,7 +10071,7 @@
         <v>2000325</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E120" s="2">
         <v>11</v>
@@ -10009,7 +10097,7 @@
         <v>2000326</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E121" s="2">
         <v>11</v>
@@ -10035,7 +10123,7 @@
         <v>2000327</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E122" s="2">
         <v>11</v>
@@ -10061,7 +10149,7 @@
         <v>2000328</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="E123" s="2">
         <v>11</v>
@@ -10087,7 +10175,7 @@
         <v>2000329</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="E124" s="2">
         <v>11</v>
@@ -10252,13 +10340,13 @@
         <v>3000001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="E6" s="2">
         <v>13</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -10280,13 +10368,13 @@
         <v>3000002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="E7" s="2">
         <v>13</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -10308,13 +10396,13 @@
         <v>3000003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E8" s="2">
         <v>13</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -10336,13 +10424,13 @@
         <v>3000004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="E9" s="2">
         <v>13</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -10364,13 +10452,13 @@
         <v>3000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="E10" s="2">
         <v>13</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -10392,13 +10480,13 @@
         <v>3000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="E11" s="2">
         <v>13</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -10420,13 +10508,13 @@
         <v>3000007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="E12" s="2">
         <v>13</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -10448,13 +10536,13 @@
         <v>3000008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="E13" s="2">
         <v>13</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -10476,13 +10564,13 @@
         <v>3000009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E14" s="2">
         <v>13</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -10504,13 +10592,13 @@
         <v>3000010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="E15" s="2">
         <v>13</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -10532,13 +10620,13 @@
         <v>3000011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E16" s="2">
         <v>13</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -10560,13 +10648,13 @@
         <v>3000012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E17" s="2">
         <v>13</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -10588,13 +10676,13 @@
         <v>3000013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E18" s="2">
         <v>13</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -10616,13 +10704,13 @@
         <v>3000014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="E19" s="2">
         <v>13</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -10644,13 +10732,13 @@
         <v>3000015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="E20" s="2">
         <v>13</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -10672,13 +10760,13 @@
         <v>3000016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E21" s="2">
         <v>13</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -10700,13 +10788,13 @@
         <v>3000017</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E22" s="2">
         <v>13</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -10728,13 +10816,13 @@
         <v>3000018</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E23" s="2">
         <v>13</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -10756,13 +10844,13 @@
         <v>3000019</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E24" s="2">
         <v>13</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -10784,13 +10872,13 @@
         <v>3000020</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E25" s="2">
         <v>13</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -10812,13 +10900,13 @@
         <v>3000021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="E26" s="2">
         <v>13</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -10840,13 +10928,13 @@
         <v>3000022</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E27" s="2">
         <v>13</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -10868,13 +10956,13 @@
         <v>3000023</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="E28" s="2">
         <v>13</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -10896,13 +10984,13 @@
         <v>3000024</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="E29" s="2">
         <v>13</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -10924,13 +11012,13 @@
         <v>3000025</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E30" s="2">
         <v>13</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -10952,13 +11040,13 @@
         <v>3000026</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="E31" s="2">
         <v>13</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -10980,13 +11068,13 @@
         <v>3000027</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="E32" s="2">
         <v>13</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -11008,13 +11096,13 @@
         <v>3000028</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E33" s="2">
         <v>13</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -11036,13 +11124,13 @@
         <v>3000029</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E34" s="2">
         <v>13</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -11064,13 +11152,13 @@
         <v>3000030</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E35" s="2">
         <v>13</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -11092,13 +11180,13 @@
         <v>3000031</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="E36" s="2">
         <v>13</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -11120,13 +11208,13 @@
         <v>3000032</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="E37" s="2">
         <v>13</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G37" s="2">
         <v>1</v>
@@ -11148,13 +11236,13 @@
         <v>3000033</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="E38" s="2">
         <v>13</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G38" s="2">
         <v>1</v>
@@ -11176,13 +11264,13 @@
         <v>3000034</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E39" s="2">
         <v>13</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -11204,13 +11292,13 @@
         <v>3000035</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="E40" s="2">
         <v>13</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -11232,13 +11320,13 @@
         <v>3000036</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E41" s="2">
         <v>13</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -11260,13 +11348,13 @@
         <v>3000037</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="E42" s="2">
         <v>13</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -11288,13 +11376,13 @@
         <v>3000038</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="E43" s="2">
         <v>13</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -11316,13 +11404,13 @@
         <v>3000039</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="E44" s="2">
         <v>13</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -11344,13 +11432,13 @@
         <v>3000040</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E45" s="2">
         <v>13</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G45" s="2">
         <v>1</v>
@@ -11372,13 +11460,13 @@
         <v>3000041</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="E46" s="2">
         <v>13</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -11400,13 +11488,13 @@
         <v>3000042</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="E47" s="2">
         <v>13</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -11428,13 +11516,13 @@
         <v>3000043</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="E48" s="2">
         <v>13</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -11456,13 +11544,13 @@
         <v>3000044</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="E49" s="2">
         <v>13</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -11484,13 +11572,13 @@
         <v>3000045</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E50" s="2">
         <v>13</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -11512,13 +11600,13 @@
         <v>3000046</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E51" s="2">
         <v>13</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -11540,13 +11628,13 @@
         <v>3000047</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E52" s="2">
         <v>13</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -11568,13 +11656,13 @@
         <v>3000048</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="E53" s="2">
         <v>13</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G53" s="2">
         <v>1</v>
@@ -11733,13 +11821,13 @@
         <v>40000051</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E7" s="2">
         <v>14</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -11765,13 +11853,13 @@
         <v>40000052</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E8" s="2">
         <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -11797,13 +11885,13 @@
         <v>40000053</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E9" s="2">
         <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -11829,13 +11917,13 @@
         <v>40000054</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E10" s="2">
         <v>14</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -11861,13 +11949,13 @@
         <v>40000055</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="E11" s="2">
         <v>14</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -11893,13 +11981,13 @@
         <v>40000056</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="E12" s="2">
         <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -11925,13 +12013,13 @@
         <v>40000057</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="E13" s="2">
         <v>14</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -11957,13 +12045,13 @@
         <v>40000058</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="E14" s="2">
         <v>14</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -11989,13 +12077,13 @@
         <v>40000059</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E15" s="2">
         <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -12021,13 +12109,13 @@
         <v>40000060</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="E16" s="2">
         <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -12053,13 +12141,13 @@
         <v>40000061</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="E17" s="2">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -12085,13 +12173,13 @@
         <v>40000062</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="E18" s="2">
         <v>14</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -12117,13 +12205,13 @@
         <v>40000063</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="E19" s="2">
         <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -12149,13 +12237,13 @@
         <v>40000064</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="E20" s="2">
         <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -12181,13 +12269,13 @@
         <v>40000065</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="E21" s="2">
         <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -12213,13 +12301,13 @@
         <v>40000066</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="E22" s="2">
         <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -12245,13 +12333,13 @@
         <v>40000067</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E23" s="2">
         <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -12277,13 +12365,13 @@
         <v>40000068</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E24" s="2">
         <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -12309,13 +12397,13 @@
         <v>40000069</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E25" s="2">
         <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -12341,13 +12429,13 @@
         <v>40000070</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E26" s="2">
         <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -12373,13 +12461,13 @@
         <v>40000071</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E27" s="2">
         <v>14</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -12405,13 +12493,13 @@
         <v>40000072</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="E28" s="2">
         <v>14</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -12437,13 +12525,13 @@
         <v>40000073</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E29" s="2">
         <v>14</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -12469,13 +12557,13 @@
         <v>40000074</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="E30" s="2">
         <v>14</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -12501,13 +12589,13 @@
         <v>40000075</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E31" s="2">
         <v>14</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -12533,13 +12621,13 @@
         <v>40000076</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="E32" s="2">
         <v>14</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -12565,13 +12653,13 @@
         <v>40000077</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="E33" s="2">
         <v>14</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -12597,13 +12685,13 @@
         <v>40000078</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="E34" s="2">
         <v>14</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -12629,13 +12717,13 @@
         <v>40000079</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="E35" s="2">
         <v>14</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -12661,13 +12749,13 @@
         <v>40000080</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="E36" s="2">
         <v>14</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -12693,13 +12781,13 @@
         <v>40000081</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="E37" s="2">
         <v>14</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G37" s="2">
         <v>1</v>
@@ -12725,13 +12813,13 @@
         <v>40000082</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="E38" s="2">
         <v>14</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G38" s="2">
         <v>1</v>
@@ -12757,13 +12845,13 @@
         <v>40000083</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="E39" s="2">
         <v>14</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -12789,13 +12877,13 @@
         <v>40000084</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="E40" s="2">
         <v>14</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -12821,13 +12909,13 @@
         <v>40000085</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="E41" s="2">
         <v>14</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -12853,13 +12941,13 @@
         <v>40000086</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="E42" s="2">
         <v>14</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -12885,13 +12973,13 @@
         <v>40000087</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E43" s="2">
         <v>14</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -12917,13 +13005,13 @@
         <v>40000088</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="E44" s="2">
         <v>14</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -12949,13 +13037,13 @@
         <v>40000089</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="E45" s="2">
         <v>14</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G45" s="2">
         <v>1</v>
@@ -12981,13 +13069,13 @@
         <v>40000090</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E46" s="2">
         <v>14</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -13013,13 +13101,13 @@
         <v>40000091</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="E47" s="2">
         <v>14</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -13045,13 +13133,13 @@
         <v>40000092</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E48" s="2">
         <v>14</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -13077,13 +13165,13 @@
         <v>40000093</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E49" s="2">
         <v>14</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -13109,13 +13197,13 @@
         <v>40000094</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E50" s="2">
         <v>14</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -13141,13 +13229,13 @@
         <v>40000095</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="E51" s="2">
         <v>14</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -13173,13 +13261,13 @@
         <v>40000096</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="E52" s="2">
         <v>14</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -13205,13 +13293,13 @@
         <v>40000097</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E53" s="2">
         <v>14</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G53" s="2">
         <v>1</v>
@@ -13237,13 +13325,13 @@
         <v>40000098</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E54" s="2">
         <v>14</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G54" s="2">
         <v>1</v>
@@ -13269,13 +13357,13 @@
         <v>40000099</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E55" s="2">
         <v>14</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G55" s="2">
         <v>1</v>
@@ -13301,13 +13389,13 @@
         <v>40000100</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="E56" s="2">
         <v>14</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G56" s="2">
         <v>1</v>
@@ -13333,13 +13421,13 @@
         <v>40000101</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="E57" s="2">
         <v>14</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G57" s="2">
         <v>1</v>
@@ -13365,13 +13453,13 @@
         <v>40000102</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="E58" s="2">
         <v>14</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G58" s="2">
         <v>1</v>
@@ -13397,13 +13485,13 @@
         <v>40000103</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="E59" s="2">
         <v>14</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G59" s="2">
         <v>1</v>
@@ -13429,13 +13517,13 @@
         <v>40000104</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="E60" s="2">
         <v>14</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G60" s="2">
         <v>1</v>
@@ -13461,13 +13549,13 @@
         <v>40000105</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="E61" s="7">
         <v>14</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G61" s="7">
         <v>1</v>
@@ -13494,13 +13582,13 @@
         <v>40000106</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E62" s="2">
         <v>14</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G62" s="2">
         <v>1</v>
@@ -13527,13 +13615,13 @@
         <v>40000107</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="E63" s="2">
         <v>14</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G63" s="2">
         <v>1</v>
@@ -13560,13 +13648,13 @@
         <v>40000108</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="E64" s="2">
         <v>14</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G64" s="2">
         <v>1</v>
@@ -13593,13 +13681,13 @@
         <v>40000109</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="E65" s="2">
         <v>14</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G65" s="2">
         <v>1</v>
@@ -13626,13 +13714,13 @@
         <v>40000110</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="E66" s="2">
         <v>14</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G66" s="2">
         <v>1</v>
@@ -13659,13 +13747,13 @@
         <v>40000111</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="E67" s="2">
         <v>14</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G67" s="2">
         <v>1</v>
@@ -13692,13 +13780,13 @@
         <v>40000112</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="E68" s="2">
         <v>14</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G68" s="2">
         <v>1</v>
@@ -13725,13 +13813,13 @@
         <v>40000113</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="E69" s="2">
         <v>14</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G69" s="2">
         <v>1</v>
@@ -13758,13 +13846,13 @@
         <v>40000114</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="E70" s="2">
         <v>14</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G70" s="2">
         <v>1</v>
@@ -13791,13 +13879,13 @@
         <v>40000115</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="E71" s="2">
         <v>14</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G71" s="2">
         <v>1</v>
@@ -13824,13 +13912,13 @@
         <v>40000116</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="E72" s="2">
         <v>14</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G72" s="2">
         <v>1</v>
@@ -13857,13 +13945,13 @@
         <v>40000117</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="E73" s="2">
         <v>14</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G73" s="2">
         <v>1</v>
@@ -13890,13 +13978,13 @@
         <v>40000118</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="E74" s="2">
         <v>14</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G74" s="2">
         <v>1</v>
@@ -13923,13 +14011,13 @@
         <v>40000119</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="E75" s="2">
         <v>14</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G75" s="2">
         <v>1</v>
@@ -13956,13 +14044,13 @@
         <v>40000120</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="E76" s="2">
         <v>14</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G76" s="2">
         <v>1</v>
@@ -13989,13 +14077,13 @@
         <v>40000121</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="E77" s="2">
         <v>14</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G77" s="2">
         <v>1</v>
@@ -14022,13 +14110,13 @@
         <v>40000122</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="E78" s="2">
         <v>14</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G78" s="2">
         <v>1</v>
@@ -14055,13 +14143,13 @@
         <v>40000123</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="E79" s="2">
         <v>14</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G79" s="2">
         <v>1</v>
@@ -14088,13 +14176,13 @@
         <v>40000124</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="E80" s="2">
         <v>14</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G80" s="2">
         <v>1</v>
@@ -14121,13 +14209,13 @@
         <v>40000125</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="E81" s="2">
         <v>14</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G81" s="2">
         <v>1</v>
@@ -14153,13 +14241,13 @@
         <v>40000126</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="E82" s="2">
         <v>14</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G82" s="2">
         <v>1</v>
@@ -14185,13 +14273,13 @@
         <v>40000127</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="E83" s="2">
         <v>14</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G83" s="2">
         <v>1</v>
@@ -14217,13 +14305,13 @@
         <v>40000128</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="E84" s="2">
         <v>14</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G84" s="2">
         <v>1</v>
@@ -14249,13 +14337,13 @@
         <v>40000129</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E85" s="2">
         <v>14</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G85" s="2">
         <v>1</v>
@@ -14281,13 +14369,13 @@
         <v>40000130</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="E86" s="2">
         <v>14</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G86" s="2">
         <v>1</v>
@@ -14313,13 +14401,13 @@
         <v>40000131</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="E87" s="2">
         <v>14</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G87" s="2">
         <v>1</v>
@@ -14345,13 +14433,13 @@
         <v>40000132</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="E88" s="2">
         <v>14</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G88" s="2">
         <v>1</v>
@@ -14377,13 +14465,13 @@
         <v>40000133</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="E89" s="2">
         <v>14</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G89" s="2">
         <v>1</v>
@@ -14409,13 +14497,13 @@
         <v>40000134</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="E90" s="2">
         <v>14</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G90" s="2">
         <v>1</v>
@@ -14441,13 +14529,13 @@
         <v>40000135</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="E91" s="2">
         <v>14</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G91" s="2">
         <v>1</v>
@@ -14473,13 +14561,13 @@
         <v>40000136</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="E92" s="2">
         <v>14</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G92" s="2">
         <v>1</v>
@@ -14505,13 +14593,13 @@
         <v>40000137</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="E93" s="2">
         <v>14</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G93" s="2">
         <v>1</v>
@@ -14537,13 +14625,13 @@
         <v>40000138</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="E94" s="2">
         <v>14</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G94" s="2">
         <v>1</v>
@@ -14569,13 +14657,13 @@
         <v>40000139</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="E95" s="2">
         <v>14</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G95" s="2">
         <v>1</v>
@@ -14740,13 +14828,13 @@
         <v>50000001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E6" s="2">
         <v>5</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -14772,13 +14860,13 @@
         <v>50000002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="E7" s="2">
         <v>5</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -14804,13 +14892,13 @@
         <v>50000003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E8" s="2">
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -14836,13 +14924,13 @@
         <v>50000004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="E9" s="2">
         <v>5</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -14868,13 +14956,13 @@
         <v>50000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E10" s="2">
         <v>5</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -14900,13 +14988,13 @@
         <v>50000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="E11" s="2">
         <v>5</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -14932,13 +15020,13 @@
         <v>50000007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="E12" s="2">
         <v>5</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -14964,13 +15052,13 @@
         <v>50000008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="E13" s="2">
         <v>5</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -14996,13 +15084,13 @@
         <v>50000009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="E14" s="2">
         <v>5</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -15028,13 +15116,13 @@
         <v>50000010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E15" s="2">
         <v>5</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -15060,13 +15148,13 @@
         <v>50000011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="E16" s="2">
         <v>5</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -15092,13 +15180,13 @@
         <v>50000012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="E17" s="2">
         <v>5</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -15124,13 +15212,13 @@
         <v>50000013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E18" s="2">
         <v>5</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -15156,13 +15244,13 @@
         <v>50000014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="E19" s="2">
         <v>5</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -15188,13 +15276,13 @@
         <v>50000015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="E20" s="2">
         <v>5</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -15220,13 +15308,13 @@
         <v>50000016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="E21" s="2">
         <v>5</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -15252,13 +15340,13 @@
         <v>50000017</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E22" s="2">
         <v>5</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -15284,13 +15372,13 @@
         <v>50000018</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="E23" s="2">
         <v>5</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -15316,13 +15404,13 @@
         <v>50000019</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="E24" s="2">
         <v>5</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -15348,13 +15436,13 @@
         <v>50000020</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="E25" s="2">
         <v>5</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -15380,13 +15468,13 @@
         <v>50000021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E26" s="2">
         <v>5</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -15412,13 +15500,13 @@
         <v>50000022</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="E27" s="2">
         <v>5</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -15444,13 +15532,13 @@
         <v>50000023</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="E28" s="2">
         <v>5</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -15476,13 +15564,13 @@
         <v>50000024</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="E29" s="2">
         <v>5</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -15508,13 +15596,13 @@
         <v>50000025</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="E30" s="2">
         <v>5</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -15540,13 +15628,13 @@
         <v>50000026</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="E31" s="2">
         <v>5</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -15572,13 +15660,13 @@
         <v>50000027</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="E32" s="2">
         <v>5</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -15604,13 +15692,13 @@
         <v>50000028</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="E33" s="2">
         <v>5</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -15636,13 +15724,13 @@
         <v>50000029</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="E34" s="2">
         <v>5</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -15668,13 +15756,13 @@
         <v>50000030</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="E35" s="2">
         <v>5</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -15700,13 +15788,13 @@
         <v>50000031</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="E36" s="2">
         <v>5</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -15732,13 +15820,13 @@
         <v>50000032</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="E37" s="2">
         <v>5</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="G37" s="2">
         <v>1</v>
@@ -15764,13 +15852,13 @@
         <v>50000033</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="E38" s="2">
         <v>5</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="G38" s="2">
         <v>1</v>
@@ -15796,13 +15884,13 @@
         <v>50000034</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="E39" s="2">
         <v>5</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -15828,13 +15916,13 @@
         <v>50000035</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="E40" s="2">
         <v>5</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -15860,13 +15948,13 @@
         <v>50000036</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="E41" s="2">
         <v>5</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -15892,13 +15980,13 @@
         <v>50000037</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="E42" s="2">
         <v>5</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -15924,13 +16012,13 @@
         <v>50000038</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="E43" s="2">
         <v>5</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -15956,13 +16044,13 @@
         <v>50000039</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="E44" s="2">
         <v>5</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -15988,13 +16076,13 @@
         <v>50000040</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="E45" s="2">
         <v>5</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="G45" s="2">
         <v>1</v>
@@ -16020,13 +16108,13 @@
         <v>50000041</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="E46" s="2">
         <v>5</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -16052,13 +16140,13 @@
         <v>50000042</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="E47" s="2">
         <v>5</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -16084,13 +16172,13 @@
         <v>50000043</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="E48" s="2">
         <v>5</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -16116,13 +16204,13 @@
         <v>50000044</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="E49" s="2">
         <v>5</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -16148,13 +16236,13 @@
         <v>50000045</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="E50" s="2">
         <v>5</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -16180,13 +16268,13 @@
         <v>50000046</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="E51" s="2">
         <v>5</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -16212,13 +16300,13 @@
         <v>50000047</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="E52" s="2">
         <v>5</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -16244,13 +16332,13 @@
         <v>50000048</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="E53" s="2">
         <v>5</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="G53" s="2">
         <v>1</v>
@@ -16276,13 +16364,13 @@
         <v>50000049</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="E54" s="2">
         <v>5</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="G54" s="2">
         <v>1</v>
@@ -16308,13 +16396,13 @@
         <v>50000050</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="E55" s="2">
         <v>5</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="G55" s="2">
         <v>1</v>
@@ -16340,13 +16428,13 @@
         <v>50000051</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="E56" s="2">
         <v>5</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="G56" s="2">
         <v>1</v>
@@ -16372,13 +16460,13 @@
         <v>50000052</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="E57" s="2">
         <v>5</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="G57" s="2">
         <v>1</v>
@@ -16404,13 +16492,13 @@
         <v>50000053</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="E58" s="2">
         <v>5</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="G58" s="2">
         <v>1</v>
@@ -16436,13 +16524,13 @@
         <v>50000054</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="E59" s="2">
         <v>5</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="G59" s="2">
         <v>1</v>
@@ -16468,13 +16556,13 @@
         <v>50000055</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="E60" s="2">
         <v>5</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="G60" s="2">
         <v>1</v>
@@ -16500,13 +16588,13 @@
         <v>50000056</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="E61" s="2">
         <v>5</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="G61" s="2">
         <v>1</v>
@@ -16532,13 +16620,13 @@
         <v>50000057</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="E62" s="2">
         <v>5</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="G62" s="2">
         <v>1</v>
@@ -16564,13 +16652,13 @@
         <v>50000058</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="E63" s="2">
         <v>5</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="G63" s="2">
         <v>1</v>
@@ -16596,13 +16684,13 @@
         <v>50000059</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="E64" s="2">
         <v>5</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="G64" s="2">
         <v>1</v>
@@ -16628,13 +16716,13 @@
         <v>50000060</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="E65" s="2">
         <v>5</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="G65" s="2">
         <v>1</v>
@@ -16660,13 +16748,13 @@
         <v>50000061</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="E66" s="2">
         <v>5</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="G66" s="2">
         <v>1</v>
@@ -16692,13 +16780,13 @@
         <v>50000062</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="E67" s="2">
         <v>5</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="G67" s="2">
         <v>1</v>
@@ -16724,13 +16812,13 @@
         <v>50000063</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="E68" s="2">
         <v>5</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="G68" s="2">
         <v>1</v>
@@ -16756,13 +16844,13 @@
         <v>50000064</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="E69" s="2">
         <v>5</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="G69" s="2">
         <v>1</v>
@@ -16788,13 +16876,13 @@
         <v>50000065</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="E70" s="2">
         <v>5</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="G70" s="2">
         <v>1</v>
@@ -16820,13 +16908,13 @@
         <v>50000066</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="E71" s="2">
         <v>5</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="G71" s="2">
         <v>1</v>
@@ -16852,13 +16940,13 @@
         <v>50000067</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="E72" s="2">
         <v>5</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="G72" s="2">
         <v>1</v>
@@ -16884,13 +16972,13 @@
         <v>50000068</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="E73" s="2">
         <v>5</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="G73" s="2">
         <v>1</v>
@@ -16916,13 +17004,13 @@
         <v>50000069</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="E74" s="2">
         <v>5</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="G74" s="2">
         <v>1</v>
@@ -16948,13 +17036,13 @@
         <v>50000070</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="E75" s="2">
         <v>5</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="G75" s="2">
         <v>1</v>
@@ -16980,13 +17068,13 @@
         <v>50000071</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="E76" s="2">
         <v>5</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="G76" s="2">
         <v>1</v>
@@ -17012,13 +17100,13 @@
         <v>50000072</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="E77" s="2">
         <v>5</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="G77" s="2">
         <v>1</v>
@@ -17044,13 +17132,13 @@
         <v>50000073</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="E78" s="2">
         <v>5</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="G78" s="2">
         <v>1</v>
@@ -17076,13 +17164,13 @@
         <v>50000074</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="E79" s="2">
         <v>5</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="G79" s="2">
         <v>1</v>
@@ -17108,13 +17196,13 @@
         <v>50000075</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="E80" s="2">
         <v>5</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="G80" s="2">
         <v>1</v>
@@ -17140,13 +17228,13 @@
         <v>50000076</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="E81" s="2">
         <v>5</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="G81" s="2">
         <v>1</v>
@@ -17172,13 +17260,13 @@
         <v>50000077</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="E82" s="2">
         <v>5</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="G82" s="2">
         <v>1</v>
@@ -17204,13 +17292,13 @@
         <v>50000078</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="E83" s="2">
         <v>5</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="G83" s="2">
         <v>1</v>
@@ -17236,13 +17324,13 @@
         <v>50000079</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="E84" s="2">
         <v>5</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="G84" s="2">
         <v>1</v>
@@ -17268,13 +17356,13 @@
         <v>50000080</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="E85" s="2">
         <v>5</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="G85" s="2">
         <v>1</v>
@@ -17300,13 +17388,13 @@
         <v>50000081</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="E86" s="2">
         <v>5</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="G86" s="2">
         <v>1</v>
@@ -17332,13 +17420,13 @@
         <v>50000082</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="E87" s="2">
         <v>5</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="G87" s="2">
         <v>1</v>
@@ -17364,13 +17452,13 @@
         <v>50000083</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="E88" s="2">
         <v>5</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="G88" s="2">
         <v>1</v>
@@ -17396,13 +17484,13 @@
         <v>50000084</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="E89" s="2">
         <v>5</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="G89" s="2">
         <v>1</v>
@@ -17428,13 +17516,13 @@
         <v>50000085</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="E90" s="2">
         <v>5</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="G90" s="2">
         <v>1</v>
@@ -17460,13 +17548,13 @@
         <v>50000086</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="E91" s="2">
         <v>5</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="G91" s="2">
         <v>1</v>
@@ -17492,13 +17580,13 @@
         <v>50000087</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="E92" s="2">
         <v>5</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="G92" s="2">
         <v>1</v>
@@ -17524,13 +17612,13 @@
         <v>50000088</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="E93" s="2">
         <v>5</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="G93" s="2">
         <v>1</v>
@@ -17556,13 +17644,13 @@
         <v>50000089</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="E94" s="2">
         <v>5</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="G94" s="2">
         <v>1</v>
@@ -17588,13 +17676,13 @@
         <v>50000090</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="E95" s="2">
         <v>5</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="G95" s="2">
         <v>1</v>
@@ -17620,13 +17708,13 @@
         <v>50000091</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="E96" s="2">
         <v>5</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="G96" s="2">
         <v>1</v>
@@ -17652,13 +17740,13 @@
         <v>50000092</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="E97" s="2">
         <v>5</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="G97" s="2">
         <v>1</v>
@@ -17684,13 +17772,13 @@
         <v>50000093</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="E98" s="2">
         <v>5</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="G98" s="2">
         <v>1</v>
@@ -17716,13 +17804,13 @@
         <v>50000094</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="E99" s="2">
         <v>5</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="G99" s="2">
         <v>1</v>
@@ -17748,13 +17836,13 @@
         <v>50000095</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="E100" s="2">
         <v>5</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="G100" s="2">
         <v>1</v>
@@ -17780,13 +17868,13 @@
         <v>50000096</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="E101" s="2">
         <v>5</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="G101" s="2">
         <v>1</v>
@@ -17812,13 +17900,13 @@
         <v>50000097</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="E102" s="2">
         <v>5</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G102" s="2">
         <v>1</v>
@@ -17844,13 +17932,13 @@
         <v>50000098</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="E103" s="2">
         <v>5</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="G103" s="2">
         <v>1</v>
@@ -17876,13 +17964,13 @@
         <v>50000099</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="E104" s="2">
         <v>5</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="G104" s="2">
         <v>1</v>
@@ -17908,13 +17996,13 @@
         <v>50000100</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E105" s="2">
         <v>5</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="G105" s="2">
         <v>1</v>
@@ -17940,13 +18028,13 @@
         <v>50000101</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="E106" s="2">
         <v>5</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="G106" s="2">
         <v>1</v>
@@ -17972,13 +18060,13 @@
         <v>50000102</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="E107" s="2">
         <v>5</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="G107" s="2">
         <v>1</v>
@@ -18004,13 +18092,13 @@
         <v>50000103</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="E108" s="2">
         <v>5</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="G108" s="2">
         <v>1</v>
@@ -18036,13 +18124,13 @@
         <v>50000104</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="E109" s="2">
         <v>5</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="G109" s="2">
         <v>1</v>
@@ -18207,13 +18295,13 @@
         <v>180001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="E6" s="2">
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -18233,13 +18321,13 @@
         <v>180002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="E7" s="2">
         <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -18259,13 +18347,13 @@
         <v>180003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="E8" s="2">
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -18285,13 +18373,13 @@
         <v>180004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="E9" s="2">
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -18311,13 +18399,13 @@
         <v>180005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="E10" s="2">
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -18337,13 +18425,13 @@
         <v>180006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="E11" s="2">
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -18365,13 +18453,13 @@
         <v>180007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="E12" s="2">
         <v>18</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -18393,13 +18481,13 @@
         <v>180008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="E13" s="2">
         <v>18</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -18421,13 +18509,13 @@
         <v>180009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="E14" s="2">
         <v>18</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -18449,13 +18537,13 @@
         <v>180010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="E15" s="2">
         <v>18</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -18477,13 +18565,13 @@
         <v>180011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="E16" s="2">
         <v>18</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -18505,13 +18593,13 @@
         <v>180012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="E17" s="2">
         <v>18</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -18533,13 +18621,13 @@
         <v>180013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="E18" s="2">
         <v>18</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -18561,13 +18649,13 @@
         <v>180014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="E19" s="2">
         <v>18</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -18589,13 +18677,13 @@
         <v>180015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="E20" s="2">
         <v>18</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -18617,13 +18705,13 @@
         <v>180016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="E21" s="2">
         <v>18</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -18645,13 +18733,13 @@
         <v>180017</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="E22" s="2">
         <v>18</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -18673,13 +18761,13 @@
         <v>180018</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="E23" s="2">
         <v>18</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -18701,13 +18789,13 @@
         <v>180019</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="E24" s="2">
         <v>18</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -18729,13 +18817,13 @@
         <v>180020</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="E25" s="2">
         <v>18</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -18757,13 +18845,13 @@
         <v>180021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="E26" s="2">
         <v>18</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -18790,13 +18878,13 @@
         <v>180030</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="E28" s="2">
         <v>18</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -18818,13 +18906,13 @@
         <v>180031</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="E29" s="2">
         <v>18</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="G29" s="3">
         <v>1</v>
@@ -18844,13 +18932,13 @@
         <v>180032</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="E30" s="2">
         <v>18</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="G30" s="3">
         <v>1</v>
@@ -18870,13 +18958,13 @@
         <v>180033</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="E31" s="2">
         <v>18</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="G31" s="3">
         <v>1</v>
@@ -18896,13 +18984,13 @@
         <v>180034</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="E32" s="2">
         <v>18</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="G32" s="3">
         <v>1</v>
@@ -19068,13 +19156,13 @@
         <v>190001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="E6" s="2">
         <v>19</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -19094,13 +19182,13 @@
         <v>190002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="E7" s="2">
         <v>19</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -19120,13 +19208,13 @@
         <v>190003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="E8" s="2">
         <v>19</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -19146,13 +19234,13 @@
         <v>190004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="E9" s="2">
         <v>19</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -19172,13 +19260,13 @@
         <v>190005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="E10" s="2">
         <v>19</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -19198,13 +19286,13 @@
         <v>190006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="E11" s="2">
         <v>19</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -344,7 +344,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="737">
   <si>
     <t>_Id</t>
   </si>
@@ -1051,10 +1051,28 @@
     <t>魔鲸王骨</t>
   </si>
   <si>
+    <t>神鉴·白</t>
+  </si>
+  <si>
+    <t>激活对应图鉴</t>
+  </si>
+  <si>
+    <t>神鉴·绿</t>
+  </si>
+  <si>
+    <t>神鉴·蓝</t>
+  </si>
+  <si>
+    <t>神鉴·紫</t>
+  </si>
+  <si>
+    <t>神鉴·橙</t>
+  </si>
+  <si>
+    <t>神鉴·红</t>
+  </si>
+  <si>
     <t>龙之怒</t>
-  </si>
-  <si>
-    <t>激活对应图鉴</t>
   </si>
   <si>
     <t>龙之刀</t>
@@ -2747,12 +2765,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -7017,7 +7035,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:M124"/>
+  <dimension ref="C1:M131"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="4" max="4" width="9.625" customWidth="1"/>
@@ -7140,7 +7158,7 @@
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C6" s="2">
-        <v>1999989</v>
+        <v>1999001</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>235</v>
@@ -7169,7 +7187,7 @@
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C7" s="2">
-        <v>1999990</v>
+        <v>1999002</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>237</v>
@@ -7198,7 +7216,7 @@
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C8" s="2">
-        <v>1999991</v>
+        <v>1999003</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>238</v>
@@ -7221,12 +7239,13 @@
       <c r="J8" s="2">
         <v>6</v>
       </c>
+      <c r="K8" s="2"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C9" s="2">
-        <v>1999992</v>
+        <v>1999004</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>239</v>
@@ -7254,7 +7273,7 @@
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C10" s="2">
-        <v>1999993</v>
+        <v>1999005</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>240</v>
@@ -7282,7 +7301,7 @@
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C11" s="2">
-        <v>1999994</v>
+        <v>1999006</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>241</v>
@@ -7305,43 +7324,21 @@
       <c r="J11" s="2">
         <v>6</v>
       </c>
+      <c r="K11" s="2"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
     </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C12" s="2">
-        <v>1999995</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="E12" s="2">
-        <v>11</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="G12" s="2">
-        <v>1</v>
-      </c>
-      <c r="H12" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I12" s="2">
-        <v>0</v>
-      </c>
-      <c r="J12" s="2">
-        <v>6</v>
-      </c>
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C13" s="2">
-        <v>1999996</v>
+        <v>1999989</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E13" s="2">
         <v>11</v>
@@ -7361,15 +7358,16 @@
       <c r="J13" s="2">
         <v>6</v>
       </c>
+      <c r="K13" s="2"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C14" s="2">
-        <v>1999997</v>
+        <v>1999990</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E14" s="2">
         <v>11</v>
@@ -7389,21 +7387,22 @@
       <c r="J14" s="2">
         <v>6</v>
       </c>
+      <c r="K14" s="2"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C15" s="2">
-        <v>2000000</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>245</v>
+        <v>1999991</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>244</v>
       </c>
       <c r="E15" s="2">
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -7415,17 +7414,17 @@
         <v>0</v>
       </c>
       <c r="J15" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C16" s="2">
-        <v>2000001</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>247</v>
+        <v>1999992</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>245</v>
       </c>
       <c r="E16" s="2">
         <v>11</v>
@@ -7443,17 +7442,17 @@
         <v>0</v>
       </c>
       <c r="J16" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C17" s="2">
-        <v>2000002</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>248</v>
+        <v>1999993</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>246</v>
       </c>
       <c r="E17" s="2">
         <v>11</v>
@@ -7471,17 +7470,17 @@
         <v>0</v>
       </c>
       <c r="J17" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C18" s="2">
-        <v>2000003</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>249</v>
+        <v>1999994</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="E18" s="2">
         <v>11</v>
@@ -7499,17 +7498,17 @@
         <v>0</v>
       </c>
       <c r="J18" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C19" s="2">
-        <v>2000004</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>250</v>
+        <v>1999995</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>248</v>
       </c>
       <c r="E19" s="2">
         <v>11</v>
@@ -7527,17 +7526,17 @@
         <v>0</v>
       </c>
       <c r="J19" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C20" s="2">
-        <v>2000005</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>251</v>
+        <v>1999996</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>249</v>
       </c>
       <c r="E20" s="2">
         <v>11</v>
@@ -7555,17 +7554,17 @@
         <v>0</v>
       </c>
       <c r="J20" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C21" s="2">
-        <v>2000006</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>252</v>
+        <v>1999997</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>250</v>
       </c>
       <c r="E21" s="2">
         <v>11</v>
@@ -7583,23 +7582,23 @@
         <v>0</v>
       </c>
       <c r="J21" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C22" s="2">
-        <v>2000007</v>
+        <v>2000000</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E22" s="2">
         <v>11</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -7618,10 +7617,10 @@
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C23" s="2">
-        <v>2000008</v>
+        <v>2000001</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E23" s="2">
         <v>11</v>
@@ -7646,10 +7645,10 @@
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C24" s="2">
-        <v>2000009</v>
+        <v>2000002</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E24" s="2">
         <v>11</v>
@@ -7674,10 +7673,10 @@
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C25" s="2">
-        <v>2000010</v>
+        <v>2000003</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E25" s="2">
         <v>11</v>
@@ -7702,10 +7701,10 @@
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C26" s="2">
-        <v>2000011</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>257</v>
+        <v>2000004</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>256</v>
       </c>
       <c r="E26" s="2">
         <v>11</v>
@@ -7730,10 +7729,10 @@
     </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C27" s="2">
-        <v>2000012</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>258</v>
+        <v>2000005</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>257</v>
       </c>
       <c r="E27" s="2">
         <v>11</v>
@@ -7758,10 +7757,10 @@
     </row>
     <row r="28" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C28" s="2">
-        <v>2000013</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>259</v>
+        <v>2000006</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>258</v>
       </c>
       <c r="E28" s="2">
         <v>11</v>
@@ -7784,24 +7783,96 @@
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
     </row>
-    <row r="29" s="2" customFormat="1" customHeight="1" spans="12:13">
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C29" s="2">
+        <v>2000007</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="E29" s="2">
+        <v>11</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G29" s="2">
+        <v>1</v>
+      </c>
+      <c r="H29" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I29" s="2">
+        <v>0</v>
+      </c>
+      <c r="J29" s="2">
+        <v>5</v>
+      </c>
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
     </row>
-    <row r="30" s="2" customFormat="1" customHeight="1" spans="12:13">
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C30" s="2">
+        <v>2000008</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E30" s="2">
+        <v>11</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G30" s="2">
+        <v>1</v>
+      </c>
+      <c r="H30" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I30" s="2">
+        <v>0</v>
+      </c>
+      <c r="J30" s="2">
+        <v>5</v>
+      </c>
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
     </row>
-    <row r="31" s="2" customFormat="1" customHeight="1" spans="12:13">
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C31" s="2">
+        <v>2000009</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E31" s="2">
+        <v>11</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G31" s="2">
+        <v>1</v>
+      </c>
+      <c r="H31" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I31" s="2">
+        <v>0</v>
+      </c>
+      <c r="J31" s="2">
+        <v>5</v>
+      </c>
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
     </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C32" s="2">
-        <v>2000100</v>
+        <v>2000010</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E32" s="2">
         <v>11</v>
@@ -7819,17 +7890,17 @@
         <v>0</v>
       </c>
       <c r="J32" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C33" s="2">
-        <v>2000101</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>261</v>
+        <v>2000011</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>263</v>
       </c>
       <c r="E33" s="2">
         <v>11</v>
@@ -7847,17 +7918,17 @@
         <v>0</v>
       </c>
       <c r="J33" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C34" s="2">
-        <v>2000102</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>262</v>
+        <v>2000012</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>264</v>
       </c>
       <c r="E34" s="2">
         <v>11</v>
@@ -7875,17 +7946,17 @@
         <v>0</v>
       </c>
       <c r="J34" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C35" s="2">
-        <v>2000103</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>263</v>
+        <v>2000013</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>265</v>
       </c>
       <c r="E35" s="2">
         <v>11</v>
@@ -7903,101 +7974,29 @@
         <v>0</v>
       </c>
       <c r="J35" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L35" s="3"/>
       <c r="M35" s="3"/>
     </row>
-    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C36" s="2">
-        <v>2000104</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="E36" s="2">
-        <v>11</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="G36" s="2">
-        <v>1</v>
-      </c>
-      <c r="H36" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I36" s="2">
-        <v>0</v>
-      </c>
-      <c r="J36" s="2">
-        <v>1</v>
-      </c>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="12:13">
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
     </row>
-    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C37" s="2">
-        <v>2000105</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="E37" s="2">
-        <v>11</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="G37" s="2">
-        <v>1</v>
-      </c>
-      <c r="H37" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I37" s="2">
-        <v>0</v>
-      </c>
-      <c r="J37" s="2">
-        <v>1</v>
-      </c>
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="12:13">
       <c r="L37" s="3"/>
       <c r="M37" s="3"/>
     </row>
-    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C38" s="2">
-        <v>2000106</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="E38" s="2">
-        <v>11</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="G38" s="2">
-        <v>1</v>
-      </c>
-      <c r="H38" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I38" s="2">
-        <v>0</v>
-      </c>
-      <c r="J38" s="2">
-        <v>1</v>
-      </c>
+    <row r="38" s="2" customFormat="1" customHeight="1" spans="12:13">
       <c r="L38" s="3"/>
       <c r="M38" s="3"/>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C39" s="2">
-        <v>2000107</v>
+        <v>2000100</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E39" s="2">
         <v>11</v>
@@ -8022,10 +8021,10 @@
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C40" s="2">
-        <v>2000108</v>
+        <v>2000101</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E40" s="2">
         <v>11</v>
@@ -8050,10 +8049,10 @@
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C41" s="2">
-        <v>2000109</v>
+        <v>2000102</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E41" s="2">
         <v>11</v>
@@ -8078,10 +8077,10 @@
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C42" s="2">
-        <v>2000110</v>
+        <v>2000103</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E42" s="2">
         <v>11</v>
@@ -8106,10 +8105,10 @@
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C43" s="2">
-        <v>2000111</v>
+        <v>2000104</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E43" s="2">
         <v>11</v>
@@ -8134,10 +8133,10 @@
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C44" s="2">
-        <v>2000112</v>
+        <v>2000105</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E44" s="2">
         <v>11</v>
@@ -8155,17 +8154,17 @@
         <v>0</v>
       </c>
       <c r="J44" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
     </row>
     <row r="45" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C45" s="2">
-        <v>2000113</v>
+        <v>2000106</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E45" s="2">
         <v>11</v>
@@ -8183,17 +8182,17 @@
         <v>0</v>
       </c>
       <c r="J45" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
     </row>
     <row r="46" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C46" s="2">
-        <v>2000114</v>
+        <v>2000107</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E46" s="2">
         <v>11</v>
@@ -8211,17 +8210,17 @@
         <v>0</v>
       </c>
       <c r="J46" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L46" s="3"/>
       <c r="M46" s="3"/>
     </row>
     <row r="47" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C47" s="2">
-        <v>2000115</v>
+        <v>2000108</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E47" s="2">
         <v>11</v>
@@ -8239,17 +8238,17 @@
         <v>0</v>
       </c>
       <c r="J47" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L47" s="3"/>
       <c r="M47" s="3"/>
     </row>
     <row r="48" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C48" s="2">
-        <v>2000116</v>
+        <v>2000109</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E48" s="2">
         <v>11</v>
@@ -8267,17 +8266,17 @@
         <v>0</v>
       </c>
       <c r="J48" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L48" s="3"/>
       <c r="M48" s="3"/>
     </row>
     <row r="49" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C49" s="2">
-        <v>2000117</v>
+        <v>2000110</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E49" s="2">
         <v>11</v>
@@ -8295,17 +8294,17 @@
         <v>0</v>
       </c>
       <c r="J49" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L49" s="3"/>
       <c r="M49" s="3"/>
     </row>
     <row r="50" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C50" s="2">
-        <v>2000118</v>
+        <v>2000111</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E50" s="2">
         <v>11</v>
@@ -8323,17 +8322,17 @@
         <v>0</v>
       </c>
       <c r="J50" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
     </row>
     <row r="51" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C51" s="2">
-        <v>2000119</v>
+        <v>2000112</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E51" s="2">
         <v>11</v>
@@ -8358,10 +8357,10 @@
     </row>
     <row r="52" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C52" s="2">
-        <v>2000120</v>
+        <v>2000113</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E52" s="2">
         <v>11</v>
@@ -8386,10 +8385,10 @@
     </row>
     <row r="53" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C53" s="2">
-        <v>2000121</v>
+        <v>2000114</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E53" s="2">
         <v>11</v>
@@ -8407,17 +8406,17 @@
         <v>0</v>
       </c>
       <c r="J53" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
     </row>
     <row r="54" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C54" s="2">
-        <v>2000122</v>
+        <v>2000115</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E54" s="2">
         <v>11</v>
@@ -8435,17 +8434,17 @@
         <v>0</v>
       </c>
       <c r="J54" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L54" s="3"/>
       <c r="M54" s="3"/>
     </row>
     <row r="55" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C55" s="2">
-        <v>2000123</v>
+        <v>2000116</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E55" s="2">
         <v>11</v>
@@ -8463,17 +8462,17 @@
         <v>0</v>
       </c>
       <c r="J55" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
     </row>
     <row r="56" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C56" s="2">
-        <v>2000124</v>
+        <v>2000117</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E56" s="2">
         <v>11</v>
@@ -8491,17 +8490,17 @@
         <v>0</v>
       </c>
       <c r="J56" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
     </row>
     <row r="57" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C57" s="2">
-        <v>2000125</v>
+        <v>2000118</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E57" s="2">
         <v>11</v>
@@ -8519,17 +8518,17 @@
         <v>0</v>
       </c>
       <c r="J57" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L57" s="3"/>
       <c r="M57" s="3"/>
     </row>
     <row r="58" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C58" s="2">
-        <v>2000126</v>
+        <v>2000119</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E58" s="2">
         <v>11</v>
@@ -8547,17 +8546,17 @@
         <v>0</v>
       </c>
       <c r="J58" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L58" s="3"/>
       <c r="M58" s="3"/>
     </row>
     <row r="59" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C59" s="2">
-        <v>2000127</v>
+        <v>2000120</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E59" s="2">
         <v>11</v>
@@ -8575,17 +8574,17 @@
         <v>0</v>
       </c>
       <c r="J59" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L59" s="3"/>
       <c r="M59" s="3"/>
     </row>
     <row r="60" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C60" s="2">
-        <v>2000128</v>
+        <v>2000121</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E60" s="2">
         <v>11</v>
@@ -8603,17 +8602,17 @@
         <v>0</v>
       </c>
       <c r="J60" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L60" s="3"/>
       <c r="M60" s="3"/>
     </row>
     <row r="61" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C61" s="2">
-        <v>2000129</v>
+        <v>2000122</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E61" s="2">
         <v>11</v>
@@ -8631,14 +8630,42 @@
         <v>0</v>
       </c>
       <c r="J61" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L61" s="3"/>
       <c r="M61" s="3"/>
     </row>
-    <row r="63" customHeight="1" spans="3:10">
+    <row r="62" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C62" s="2">
+        <v>2000123</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E62" s="2">
+        <v>11</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G62" s="2">
+        <v>1</v>
+      </c>
+      <c r="H62" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I62" s="2">
+        <v>0</v>
+      </c>
+      <c r="J62" s="2">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3"/>
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C63" s="2">
-        <v>2000200</v>
+        <v>2000124</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>290</v>
@@ -8659,12 +8686,14 @@
         <v>0</v>
       </c>
       <c r="J63" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" customHeight="1" spans="3:10">
+        <v>3</v>
+      </c>
+      <c r="L63" s="3"/>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C64" s="2">
-        <v>2000201</v>
+        <v>2000125</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>291</v>
@@ -8685,12 +8714,14 @@
         <v>0</v>
       </c>
       <c r="J64" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" customHeight="1" spans="3:10">
+        <v>3</v>
+      </c>
+      <c r="L64" s="3"/>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C65" s="2">
-        <v>2000202</v>
+        <v>2000126</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>292</v>
@@ -8711,12 +8742,14 @@
         <v>0</v>
       </c>
       <c r="J65" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" customHeight="1" spans="3:10">
+        <v>3</v>
+      </c>
+      <c r="L65" s="3"/>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C66" s="2">
-        <v>2000203</v>
+        <v>2000127</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>293</v>
@@ -8737,12 +8770,14 @@
         <v>0</v>
       </c>
       <c r="J66" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" customHeight="1" spans="3:10">
+        <v>4</v>
+      </c>
+      <c r="L66" s="3"/>
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C67" s="2">
-        <v>2000204</v>
+        <v>2000128</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>294</v>
@@ -8763,12 +8798,14 @@
         <v>0</v>
       </c>
       <c r="J67" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" customHeight="1" spans="3:10">
+        <v>4</v>
+      </c>
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C68" s="2">
-        <v>2000205</v>
+        <v>2000129</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>295</v>
@@ -8789,41 +8826,17 @@
         <v>0</v>
       </c>
       <c r="J68" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" customHeight="1" spans="3:10">
-      <c r="C69" s="2">
-        <v>2000206</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="E69" s="2">
-        <v>11</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="G69" s="2">
-        <v>1</v>
-      </c>
-      <c r="H69" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I69" s="2">
-        <v>0</v>
-      </c>
-      <c r="J69" s="2">
-        <v>1</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="L68" s="3"/>
+      <c r="M68" s="3"/>
     </row>
     <row r="70" customHeight="1" spans="3:10">
       <c r="C70" s="2">
-        <v>2000207</v>
+        <v>2000200</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E70" s="2">
         <v>11</v>
@@ -8846,10 +8859,10 @@
     </row>
     <row r="71" customHeight="1" spans="3:10">
       <c r="C71" s="2">
-        <v>2000208</v>
+        <v>2000201</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E71" s="2">
         <v>11</v>
@@ -8872,10 +8885,10 @@
     </row>
     <row r="72" customHeight="1" spans="3:10">
       <c r="C72" s="2">
-        <v>2000209</v>
+        <v>2000202</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E72" s="2">
         <v>11</v>
@@ -8898,10 +8911,10 @@
     </row>
     <row r="73" customHeight="1" spans="3:10">
       <c r="C73" s="2">
-        <v>2000210</v>
+        <v>2000203</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E73" s="2">
         <v>11</v>
@@ -8924,10 +8937,10 @@
     </row>
     <row r="74" customHeight="1" spans="3:10">
       <c r="C74" s="2">
-        <v>2000211</v>
+        <v>2000204</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E74" s="2">
         <v>11</v>
@@ -8950,10 +8963,10 @@
     </row>
     <row r="75" customHeight="1" spans="3:10">
       <c r="C75" s="2">
-        <v>2000212</v>
+        <v>2000205</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E75" s="2">
         <v>11</v>
@@ -8971,15 +8984,15 @@
         <v>0</v>
       </c>
       <c r="J75" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:10">
       <c r="C76" s="2">
-        <v>2000213</v>
+        <v>2000206</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E76" s="2">
         <v>11</v>
@@ -8997,15 +9010,15 @@
         <v>0</v>
       </c>
       <c r="J76" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:10">
       <c r="C77" s="2">
-        <v>2000214</v>
+        <v>2000207</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E77" s="2">
         <v>11</v>
@@ -9023,15 +9036,15 @@
         <v>0</v>
       </c>
       <c r="J77" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:10">
       <c r="C78" s="2">
-        <v>2000215</v>
+        <v>2000208</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E78" s="2">
         <v>11</v>
@@ -9049,15 +9062,15 @@
         <v>0</v>
       </c>
       <c r="J78" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:10">
       <c r="C79" s="2">
-        <v>2000216</v>
+        <v>2000209</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E79" s="2">
         <v>11</v>
@@ -9075,15 +9088,15 @@
         <v>0</v>
       </c>
       <c r="J79" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:10">
       <c r="C80" s="2">
-        <v>2000217</v>
+        <v>2000210</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E80" s="2">
         <v>11</v>
@@ -9101,15 +9114,15 @@
         <v>0</v>
       </c>
       <c r="J80" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="3:10">
       <c r="C81" s="2">
-        <v>2000218</v>
+        <v>2000211</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E81" s="2">
         <v>11</v>
@@ -9127,15 +9140,15 @@
         <v>0</v>
       </c>
       <c r="J81" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:10">
       <c r="C82" s="2">
-        <v>2000219</v>
+        <v>2000212</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E82" s="2">
         <v>11</v>
@@ -9158,10 +9171,10 @@
     </row>
     <row r="83" customHeight="1" spans="3:10">
       <c r="C83" s="2">
-        <v>2000220</v>
+        <v>2000213</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E83" s="2">
         <v>11</v>
@@ -9184,10 +9197,10 @@
     </row>
     <row r="84" customHeight="1" spans="3:10">
       <c r="C84" s="2">
-        <v>2000221</v>
+        <v>2000214</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E84" s="2">
         <v>11</v>
@@ -9205,15 +9218,15 @@
         <v>0</v>
       </c>
       <c r="J84" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="3:10">
       <c r="C85" s="2">
-        <v>2000222</v>
+        <v>2000215</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E85" s="2">
         <v>11</v>
@@ -9231,15 +9244,15 @@
         <v>0</v>
       </c>
       <c r="J85" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="3:10">
       <c r="C86" s="2">
-        <v>2000223</v>
+        <v>2000216</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E86" s="2">
         <v>11</v>
@@ -9257,15 +9270,15 @@
         <v>0</v>
       </c>
       <c r="J86" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="3:10">
       <c r="C87" s="2">
-        <v>2000224</v>
+        <v>2000217</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E87" s="2">
         <v>11</v>
@@ -9283,15 +9296,15 @@
         <v>0</v>
       </c>
       <c r="J87" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="3:10">
       <c r="C88" s="2">
-        <v>2000225</v>
+        <v>2000218</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E88" s="2">
         <v>11</v>
@@ -9309,15 +9322,15 @@
         <v>0</v>
       </c>
       <c r="J88" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="3:10">
       <c r="C89" s="2">
-        <v>2000226</v>
+        <v>2000219</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E89" s="2">
         <v>11</v>
@@ -9335,15 +9348,15 @@
         <v>0</v>
       </c>
       <c r="J89" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="3:10">
       <c r="C90" s="2">
-        <v>2000227</v>
+        <v>2000220</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E90" s="2">
         <v>11</v>
@@ -9361,15 +9374,15 @@
         <v>0</v>
       </c>
       <c r="J90" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="3:10">
       <c r="C91" s="2">
-        <v>2000228</v>
+        <v>2000221</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E91" s="2">
         <v>11</v>
@@ -9387,15 +9400,15 @@
         <v>0</v>
       </c>
       <c r="J91" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="3:10">
       <c r="C92" s="2">
-        <v>2000229</v>
+        <v>2000222</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E92" s="2">
         <v>11</v>
@@ -9413,15 +9426,67 @@
         <v>0</v>
       </c>
       <c r="J92" s="2">
-        <v>4</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93" customHeight="1" spans="3:10">
+      <c r="C93" s="2">
+        <v>2000223</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E93" s="2">
+        <v>11</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G93" s="2">
+        <v>1</v>
+      </c>
+      <c r="H93" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I93" s="2">
+        <v>0</v>
+      </c>
+      <c r="J93" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="94" customHeight="1" spans="3:10">
+      <c r="C94" s="2">
+        <v>2000224</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="E94" s="2">
+        <v>11</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G94" s="2">
+        <v>1</v>
+      </c>
+      <c r="H94" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I94" s="2">
+        <v>0</v>
+      </c>
+      <c r="J94" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="3:10">
       <c r="C95" s="2">
-        <v>2000300</v>
+        <v>2000225</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E95" s="2">
         <v>11</v>
@@ -9439,15 +9504,15 @@
         <v>0</v>
       </c>
       <c r="J95" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="3:10">
       <c r="C96" s="2">
-        <v>2000301</v>
+        <v>2000226</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E96" s="2">
         <v>11</v>
@@ -9465,15 +9530,15 @@
         <v>0</v>
       </c>
       <c r="J96" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="3:10">
       <c r="C97" s="2">
-        <v>2000302</v>
+        <v>2000227</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E97" s="2">
         <v>11</v>
@@ -9491,15 +9556,15 @@
         <v>0</v>
       </c>
       <c r="J97" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="3:10">
       <c r="C98" s="2">
-        <v>2000303</v>
+        <v>2000228</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E98" s="2">
         <v>11</v>
@@ -9517,15 +9582,15 @@
         <v>0</v>
       </c>
       <c r="J98" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="3:10">
       <c r="C99" s="2">
-        <v>2000304</v>
+        <v>2000229</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E99" s="2">
         <v>11</v>
@@ -9543,67 +9608,15 @@
         <v>0</v>
       </c>
       <c r="J99" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" customHeight="1" spans="3:10">
-      <c r="C100" s="2">
-        <v>2000305</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="E100" s="2">
-        <v>11</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="G100" s="2">
-        <v>1</v>
-      </c>
-      <c r="H100" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I100" s="2">
-        <v>0</v>
-      </c>
-      <c r="J100" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" customHeight="1" spans="3:10">
-      <c r="C101" s="2">
-        <v>2000306</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="E101" s="2">
-        <v>11</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="G101" s="2">
-        <v>1</v>
-      </c>
-      <c r="H101" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I101" s="2">
-        <v>0</v>
-      </c>
-      <c r="J101" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="3:10">
       <c r="C102" s="2">
-        <v>2000307</v>
+        <v>2000300</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E102" s="2">
         <v>11</v>
@@ -9626,10 +9639,10 @@
     </row>
     <row r="103" customHeight="1" spans="3:10">
       <c r="C103" s="2">
-        <v>2000308</v>
+        <v>2000301</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E103" s="2">
         <v>11</v>
@@ -9652,10 +9665,10 @@
     </row>
     <row r="104" customHeight="1" spans="3:10">
       <c r="C104" s="2">
-        <v>2000309</v>
+        <v>2000302</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E104" s="2">
         <v>11</v>
@@ -9678,10 +9691,10 @@
     </row>
     <row r="105" customHeight="1" spans="3:10">
       <c r="C105" s="2">
-        <v>2000310</v>
+        <v>2000303</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E105" s="2">
         <v>11</v>
@@ -9704,10 +9717,10 @@
     </row>
     <row r="106" customHeight="1" spans="3:10">
       <c r="C106" s="2">
-        <v>2000311</v>
+        <v>2000304</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E106" s="2">
         <v>11</v>
@@ -9730,10 +9743,10 @@
     </row>
     <row r="107" customHeight="1" spans="3:10">
       <c r="C107" s="2">
-        <v>2000312</v>
+        <v>2000305</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E107" s="2">
         <v>11</v>
@@ -9751,15 +9764,15 @@
         <v>0</v>
       </c>
       <c r="J107" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108" customHeight="1" spans="3:10">
       <c r="C108" s="2">
-        <v>2000313</v>
+        <v>2000306</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E108" s="2">
         <v>11</v>
@@ -9777,15 +9790,15 @@
         <v>0</v>
       </c>
       <c r="J108" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109" customHeight="1" spans="3:10">
       <c r="C109" s="2">
-        <v>2000314</v>
+        <v>2000307</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E109" s="2">
         <v>11</v>
@@ -9803,15 +9816,15 @@
         <v>0</v>
       </c>
       <c r="J109" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110" customHeight="1" spans="3:10">
       <c r="C110" s="2">
-        <v>2000315</v>
+        <v>2000308</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E110" s="2">
         <v>11</v>
@@ -9829,15 +9842,15 @@
         <v>0</v>
       </c>
       <c r="J110" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="3:10">
       <c r="C111" s="2">
-        <v>2000316</v>
+        <v>2000309</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E111" s="2">
         <v>11</v>
@@ -9855,15 +9868,15 @@
         <v>0</v>
       </c>
       <c r="J111" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112" customHeight="1" spans="3:10">
       <c r="C112" s="2">
-        <v>2000317</v>
+        <v>2000310</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E112" s="2">
         <v>11</v>
@@ -9881,15 +9894,15 @@
         <v>0</v>
       </c>
       <c r="J112" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113" customHeight="1" spans="3:10">
       <c r="C113" s="2">
-        <v>2000318</v>
+        <v>2000311</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E113" s="2">
         <v>11</v>
@@ -9907,15 +9920,15 @@
         <v>0</v>
       </c>
       <c r="J113" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114" customHeight="1" spans="3:10">
       <c r="C114" s="2">
-        <v>2000319</v>
+        <v>2000312</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E114" s="2">
         <v>11</v>
@@ -9938,10 +9951,10 @@
     </row>
     <row r="115" customHeight="1" spans="3:10">
       <c r="C115" s="2">
-        <v>2000320</v>
+        <v>2000313</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E115" s="2">
         <v>11</v>
@@ -9964,10 +9977,10 @@
     </row>
     <row r="116" customHeight="1" spans="3:10">
       <c r="C116" s="2">
-        <v>2000321</v>
+        <v>2000314</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E116" s="2">
         <v>11</v>
@@ -9985,15 +9998,15 @@
         <v>0</v>
       </c>
       <c r="J116" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117" customHeight="1" spans="3:10">
       <c r="C117" s="2">
-        <v>2000322</v>
+        <v>2000315</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E117" s="2">
         <v>11</v>
@@ -10011,15 +10024,15 @@
         <v>0</v>
       </c>
       <c r="J117" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118" customHeight="1" spans="3:10">
       <c r="C118" s="2">
-        <v>2000323</v>
+        <v>2000316</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E118" s="2">
         <v>11</v>
@@ -10037,15 +10050,15 @@
         <v>0</v>
       </c>
       <c r="J118" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119" customHeight="1" spans="3:10">
       <c r="C119" s="2">
-        <v>2000324</v>
+        <v>2000317</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E119" s="2">
         <v>11</v>
@@ -10063,15 +10076,15 @@
         <v>0</v>
       </c>
       <c r="J119" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120" customHeight="1" spans="3:10">
       <c r="C120" s="2">
-        <v>2000325</v>
+        <v>2000318</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E120" s="2">
         <v>11</v>
@@ -10089,15 +10102,15 @@
         <v>0</v>
       </c>
       <c r="J120" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121" customHeight="1" spans="3:10">
       <c r="C121" s="2">
-        <v>2000326</v>
+        <v>2000319</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E121" s="2">
         <v>11</v>
@@ -10115,15 +10128,15 @@
         <v>0</v>
       </c>
       <c r="J121" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122" customHeight="1" spans="3:10">
       <c r="C122" s="2">
-        <v>2000327</v>
+        <v>2000320</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E122" s="2">
         <v>11</v>
@@ -10141,15 +10154,15 @@
         <v>0</v>
       </c>
       <c r="J122" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123" customHeight="1" spans="3:10">
       <c r="C123" s="2">
-        <v>2000328</v>
+        <v>2000321</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E123" s="2">
         <v>11</v>
@@ -10167,15 +10180,15 @@
         <v>0</v>
       </c>
       <c r="J123" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124" customHeight="1" spans="3:10">
       <c r="C124" s="2">
-        <v>2000329</v>
+        <v>2000322</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E124" s="2">
         <v>11</v>
@@ -10193,6 +10206,188 @@
         <v>0</v>
       </c>
       <c r="J124" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="125" customHeight="1" spans="3:10">
+      <c r="C125" s="2">
+        <v>2000323</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="E125" s="2">
+        <v>11</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G125" s="2">
+        <v>1</v>
+      </c>
+      <c r="H125" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I125" s="2">
+        <v>0</v>
+      </c>
+      <c r="J125" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="126" customHeight="1" spans="3:10">
+      <c r="C126" s="2">
+        <v>2000324</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="E126" s="2">
+        <v>11</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G126" s="2">
+        <v>1</v>
+      </c>
+      <c r="H126" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I126" s="2">
+        <v>0</v>
+      </c>
+      <c r="J126" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="127" customHeight="1" spans="3:10">
+      <c r="C127" s="2">
+        <v>2000325</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="E127" s="2">
+        <v>11</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G127" s="2">
+        <v>1</v>
+      </c>
+      <c r="H127" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I127" s="2">
+        <v>0</v>
+      </c>
+      <c r="J127" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="128" customHeight="1" spans="3:10">
+      <c r="C128" s="2">
+        <v>2000326</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E128" s="2">
+        <v>11</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G128" s="2">
+        <v>1</v>
+      </c>
+      <c r="H128" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I128" s="2">
+        <v>0</v>
+      </c>
+      <c r="J128" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="129" customHeight="1" spans="3:10">
+      <c r="C129" s="2">
+        <v>2000327</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="E129" s="2">
+        <v>11</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G129" s="2">
+        <v>1</v>
+      </c>
+      <c r="H129" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I129" s="2">
+        <v>0</v>
+      </c>
+      <c r="J129" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130" customHeight="1" spans="3:10">
+      <c r="C130" s="2">
+        <v>2000328</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E130" s="2">
+        <v>11</v>
+      </c>
+      <c r="F130" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G130" s="2">
+        <v>1</v>
+      </c>
+      <c r="H130" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I130" s="2">
+        <v>0</v>
+      </c>
+      <c r="J130" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" customHeight="1" spans="3:10">
+      <c r="C131" s="2">
+        <v>2000329</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="E131" s="2">
+        <v>11</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G131" s="2">
+        <v>1</v>
+      </c>
+      <c r="H131" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I131" s="2">
+        <v>0</v>
+      </c>
+      <c r="J131" s="2">
         <v>4</v>
       </c>
     </row>
@@ -10340,13 +10535,13 @@
         <v>3000001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="E6" s="2">
         <v>13</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -10368,13 +10563,13 @@
         <v>3000002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="E7" s="2">
         <v>13</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -10396,13 +10591,13 @@
         <v>3000003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="E8" s="2">
         <v>13</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -10424,13 +10619,13 @@
         <v>3000004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="E9" s="2">
         <v>13</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -10452,13 +10647,13 @@
         <v>3000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="E10" s="2">
         <v>13</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -10480,13 +10675,13 @@
         <v>3000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="E11" s="2">
         <v>13</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -10508,13 +10703,13 @@
         <v>3000007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="E12" s="2">
         <v>13</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -10536,13 +10731,13 @@
         <v>3000008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="E13" s="2">
         <v>13</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -10564,13 +10759,13 @@
         <v>3000009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="E14" s="2">
         <v>13</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -10592,13 +10787,13 @@
         <v>3000010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="E15" s="2">
         <v>13</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -10620,13 +10815,13 @@
         <v>3000011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="E16" s="2">
         <v>13</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -10648,13 +10843,13 @@
         <v>3000012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="E17" s="2">
         <v>13</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -10676,13 +10871,13 @@
         <v>3000013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="E18" s="2">
         <v>13</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -10704,13 +10899,13 @@
         <v>3000014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="E19" s="2">
         <v>13</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -10732,13 +10927,13 @@
         <v>3000015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="E20" s="2">
         <v>13</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -10760,13 +10955,13 @@
         <v>3000016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="E21" s="2">
         <v>13</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -10788,13 +10983,13 @@
         <v>3000017</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="E22" s="2">
         <v>13</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -10816,13 +11011,13 @@
         <v>3000018</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="E23" s="2">
         <v>13</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -10844,13 +11039,13 @@
         <v>3000019</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="E24" s="2">
         <v>13</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -10872,13 +11067,13 @@
         <v>3000020</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="E25" s="2">
         <v>13</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -10900,13 +11095,13 @@
         <v>3000021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="E26" s="2">
         <v>13</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -10928,13 +11123,13 @@
         <v>3000022</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="E27" s="2">
         <v>13</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -10956,13 +11151,13 @@
         <v>3000023</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="E28" s="2">
         <v>13</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -10984,13 +11179,13 @@
         <v>3000024</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="E29" s="2">
         <v>13</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -11012,13 +11207,13 @@
         <v>3000025</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="E30" s="2">
         <v>13</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -11040,13 +11235,13 @@
         <v>3000026</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="E31" s="2">
         <v>13</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -11068,13 +11263,13 @@
         <v>3000027</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="E32" s="2">
         <v>13</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -11096,13 +11291,13 @@
         <v>3000028</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="E33" s="2">
         <v>13</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -11124,13 +11319,13 @@
         <v>3000029</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="E34" s="2">
         <v>13</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -11152,13 +11347,13 @@
         <v>3000030</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="E35" s="2">
         <v>13</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -11180,13 +11375,13 @@
         <v>3000031</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="E36" s="2">
         <v>13</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -11208,13 +11403,13 @@
         <v>3000032</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="E37" s="2">
         <v>13</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G37" s="2">
         <v>1</v>
@@ -11236,13 +11431,13 @@
         <v>3000033</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="E38" s="2">
         <v>13</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G38" s="2">
         <v>1</v>
@@ -11264,13 +11459,13 @@
         <v>3000034</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="E39" s="2">
         <v>13</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -11292,13 +11487,13 @@
         <v>3000035</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="E40" s="2">
         <v>13</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -11320,13 +11515,13 @@
         <v>3000036</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="E41" s="2">
         <v>13</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -11348,13 +11543,13 @@
         <v>3000037</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="E42" s="2">
         <v>13</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -11376,13 +11571,13 @@
         <v>3000038</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="E43" s="2">
         <v>13</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -11404,13 +11599,13 @@
         <v>3000039</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="E44" s="2">
         <v>13</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -11432,13 +11627,13 @@
         <v>3000040</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="E45" s="2">
         <v>13</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G45" s="2">
         <v>1</v>
@@ -11460,13 +11655,13 @@
         <v>3000041</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="E46" s="2">
         <v>13</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -11488,13 +11683,13 @@
         <v>3000042</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="E47" s="2">
         <v>13</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -11516,13 +11711,13 @@
         <v>3000043</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="E48" s="2">
         <v>13</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -11544,13 +11739,13 @@
         <v>3000044</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="E49" s="2">
         <v>13</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -11572,13 +11767,13 @@
         <v>3000045</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="E50" s="2">
         <v>13</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -11600,13 +11795,13 @@
         <v>3000046</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="E51" s="2">
         <v>13</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -11628,13 +11823,13 @@
         <v>3000047</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="E52" s="2">
         <v>13</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -11656,13 +11851,13 @@
         <v>3000048</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="E53" s="2">
         <v>13</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G53" s="2">
         <v>1</v>
@@ -11821,13 +12016,13 @@
         <v>40000051</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="E7" s="2">
         <v>14</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -11853,13 +12048,13 @@
         <v>40000052</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="E8" s="2">
         <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -11885,13 +12080,13 @@
         <v>40000053</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="E9" s="2">
         <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -11917,13 +12112,13 @@
         <v>40000054</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="E10" s="2">
         <v>14</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -11949,13 +12144,13 @@
         <v>40000055</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="E11" s="2">
         <v>14</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -11981,13 +12176,13 @@
         <v>40000056</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="E12" s="2">
         <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -12013,13 +12208,13 @@
         <v>40000057</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="E13" s="2">
         <v>14</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -12045,13 +12240,13 @@
         <v>40000058</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="E14" s="2">
         <v>14</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -12077,13 +12272,13 @@
         <v>40000059</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="E15" s="2">
         <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -12109,13 +12304,13 @@
         <v>40000060</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="E16" s="2">
         <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -12141,13 +12336,13 @@
         <v>40000061</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="E17" s="2">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -12173,13 +12368,13 @@
         <v>40000062</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="E18" s="2">
         <v>14</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -12205,13 +12400,13 @@
         <v>40000063</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="E19" s="2">
         <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -12237,13 +12432,13 @@
         <v>40000064</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="E20" s="2">
         <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -12269,13 +12464,13 @@
         <v>40000065</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="E21" s="2">
         <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -12301,13 +12496,13 @@
         <v>40000066</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="E22" s="2">
         <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -12333,13 +12528,13 @@
         <v>40000067</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="E23" s="2">
         <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -12365,13 +12560,13 @@
         <v>40000068</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="E24" s="2">
         <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -12397,13 +12592,13 @@
         <v>40000069</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="E25" s="2">
         <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -12429,13 +12624,13 @@
         <v>40000070</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="E26" s="2">
         <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -12461,13 +12656,13 @@
         <v>40000071</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="E27" s="2">
         <v>14</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -12493,13 +12688,13 @@
         <v>40000072</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="E28" s="2">
         <v>14</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -12525,13 +12720,13 @@
         <v>40000073</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="E29" s="2">
         <v>14</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -12557,13 +12752,13 @@
         <v>40000074</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="E30" s="2">
         <v>14</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -12589,13 +12784,13 @@
         <v>40000075</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="E31" s="2">
         <v>14</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -12621,13 +12816,13 @@
         <v>40000076</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="E32" s="2">
         <v>14</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -12653,13 +12848,13 @@
         <v>40000077</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="E33" s="2">
         <v>14</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -12685,13 +12880,13 @@
         <v>40000078</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="E34" s="2">
         <v>14</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -12717,13 +12912,13 @@
         <v>40000079</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="E35" s="2">
         <v>14</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -12749,13 +12944,13 @@
         <v>40000080</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="E36" s="2">
         <v>14</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -12781,13 +12976,13 @@
         <v>40000081</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="E37" s="2">
         <v>14</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G37" s="2">
         <v>1</v>
@@ -12813,13 +13008,13 @@
         <v>40000082</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="E38" s="2">
         <v>14</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G38" s="2">
         <v>1</v>
@@ -12845,13 +13040,13 @@
         <v>40000083</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="E39" s="2">
         <v>14</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -12877,13 +13072,13 @@
         <v>40000084</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="E40" s="2">
         <v>14</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -12909,13 +13104,13 @@
         <v>40000085</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="E41" s="2">
         <v>14</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -12941,13 +13136,13 @@
         <v>40000086</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="E42" s="2">
         <v>14</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -12973,13 +13168,13 @@
         <v>40000087</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="E43" s="2">
         <v>14</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -13005,13 +13200,13 @@
         <v>40000088</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="E44" s="2">
         <v>14</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -13037,13 +13232,13 @@
         <v>40000089</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="E45" s="2">
         <v>14</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G45" s="2">
         <v>1</v>
@@ -13069,13 +13264,13 @@
         <v>40000090</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="E46" s="2">
         <v>14</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -13101,13 +13296,13 @@
         <v>40000091</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="E47" s="2">
         <v>14</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -13133,13 +13328,13 @@
         <v>40000092</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="E48" s="2">
         <v>14</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -13165,13 +13360,13 @@
         <v>40000093</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="E49" s="2">
         <v>14</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -13197,13 +13392,13 @@
         <v>40000094</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="E50" s="2">
         <v>14</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -13229,13 +13424,13 @@
         <v>40000095</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="E51" s="2">
         <v>14</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -13261,13 +13456,13 @@
         <v>40000096</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="E52" s="2">
         <v>14</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -13293,13 +13488,13 @@
         <v>40000097</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="E53" s="2">
         <v>14</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G53" s="2">
         <v>1</v>
@@ -13325,13 +13520,13 @@
         <v>40000098</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="E54" s="2">
         <v>14</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G54" s="2">
         <v>1</v>
@@ -13357,13 +13552,13 @@
         <v>40000099</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="E55" s="2">
         <v>14</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G55" s="2">
         <v>1</v>
@@ -13389,13 +13584,13 @@
         <v>40000100</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="E56" s="2">
         <v>14</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G56" s="2">
         <v>1</v>
@@ -13421,13 +13616,13 @@
         <v>40000101</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="E57" s="2">
         <v>14</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G57" s="2">
         <v>1</v>
@@ -13453,13 +13648,13 @@
         <v>40000102</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="E58" s="2">
         <v>14</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G58" s="2">
         <v>1</v>
@@ -13485,13 +13680,13 @@
         <v>40000103</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="E59" s="2">
         <v>14</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G59" s="2">
         <v>1</v>
@@ -13517,13 +13712,13 @@
         <v>40000104</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="E60" s="2">
         <v>14</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G60" s="2">
         <v>1</v>
@@ -13549,13 +13744,13 @@
         <v>40000105</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="E61" s="7">
         <v>14</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G61" s="7">
         <v>1</v>
@@ -13582,13 +13777,13 @@
         <v>40000106</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="E62" s="2">
         <v>14</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G62" s="2">
         <v>1</v>
@@ -13615,13 +13810,13 @@
         <v>40000107</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="E63" s="2">
         <v>14</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G63" s="2">
         <v>1</v>
@@ -13648,13 +13843,13 @@
         <v>40000108</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="E64" s="2">
         <v>14</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G64" s="2">
         <v>1</v>
@@ -13681,13 +13876,13 @@
         <v>40000109</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="E65" s="2">
         <v>14</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G65" s="2">
         <v>1</v>
@@ -13714,13 +13909,13 @@
         <v>40000110</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="E66" s="2">
         <v>14</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G66" s="2">
         <v>1</v>
@@ -13747,13 +13942,13 @@
         <v>40000111</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="E67" s="2">
         <v>14</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G67" s="2">
         <v>1</v>
@@ -13780,13 +13975,13 @@
         <v>40000112</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="E68" s="2">
         <v>14</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G68" s="2">
         <v>1</v>
@@ -13813,13 +14008,13 @@
         <v>40000113</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="E69" s="2">
         <v>14</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G69" s="2">
         <v>1</v>
@@ -13846,13 +14041,13 @@
         <v>40000114</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="E70" s="2">
         <v>14</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G70" s="2">
         <v>1</v>
@@ -13879,13 +14074,13 @@
         <v>40000115</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="E71" s="2">
         <v>14</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G71" s="2">
         <v>1</v>
@@ -13912,13 +14107,13 @@
         <v>40000116</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="E72" s="2">
         <v>14</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G72" s="2">
         <v>1</v>
@@ -13945,13 +14140,13 @@
         <v>40000117</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="E73" s="2">
         <v>14</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G73" s="2">
         <v>1</v>
@@ -13978,13 +14173,13 @@
         <v>40000118</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="E74" s="2">
         <v>14</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G74" s="2">
         <v>1</v>
@@ -14011,13 +14206,13 @@
         <v>40000119</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="E75" s="2">
         <v>14</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G75" s="2">
         <v>1</v>
@@ -14044,13 +14239,13 @@
         <v>40000120</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="E76" s="2">
         <v>14</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G76" s="2">
         <v>1</v>
@@ -14077,13 +14272,13 @@
         <v>40000121</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="E77" s="2">
         <v>14</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G77" s="2">
         <v>1</v>
@@ -14110,13 +14305,13 @@
         <v>40000122</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="E78" s="2">
         <v>14</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G78" s="2">
         <v>1</v>
@@ -14143,13 +14338,13 @@
         <v>40000123</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="E79" s="2">
         <v>14</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G79" s="2">
         <v>1</v>
@@ -14176,13 +14371,13 @@
         <v>40000124</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="E80" s="2">
         <v>14</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G80" s="2">
         <v>1</v>
@@ -14209,13 +14404,13 @@
         <v>40000125</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="E81" s="2">
         <v>14</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G81" s="2">
         <v>1</v>
@@ -14241,13 +14436,13 @@
         <v>40000126</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="E82" s="2">
         <v>14</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G82" s="2">
         <v>1</v>
@@ -14273,13 +14468,13 @@
         <v>40000127</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="E83" s="2">
         <v>14</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G83" s="2">
         <v>1</v>
@@ -14305,13 +14500,13 @@
         <v>40000128</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="E84" s="2">
         <v>14</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G84" s="2">
         <v>1</v>
@@ -14337,13 +14532,13 @@
         <v>40000129</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="E85" s="2">
         <v>14</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G85" s="2">
         <v>1</v>
@@ -14369,13 +14564,13 @@
         <v>40000130</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="E86" s="2">
         <v>14</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G86" s="2">
         <v>1</v>
@@ -14401,13 +14596,13 @@
         <v>40000131</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="E87" s="2">
         <v>14</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G87" s="2">
         <v>1</v>
@@ -14433,13 +14628,13 @@
         <v>40000132</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="E88" s="2">
         <v>14</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G88" s="2">
         <v>1</v>
@@ -14465,13 +14660,13 @@
         <v>40000133</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="E89" s="2">
         <v>14</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G89" s="2">
         <v>1</v>
@@ -14497,13 +14692,13 @@
         <v>40000134</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="E90" s="2">
         <v>14</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G90" s="2">
         <v>1</v>
@@ -14529,13 +14724,13 @@
         <v>40000135</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="E91" s="2">
         <v>14</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G91" s="2">
         <v>1</v>
@@ -14561,13 +14756,13 @@
         <v>40000136</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="E92" s="2">
         <v>14</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G92" s="2">
         <v>1</v>
@@ -14593,13 +14788,13 @@
         <v>40000137</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="E93" s="2">
         <v>14</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G93" s="2">
         <v>1</v>
@@ -14625,13 +14820,13 @@
         <v>40000138</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="E94" s="2">
         <v>14</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G94" s="2">
         <v>1</v>
@@ -14657,13 +14852,13 @@
         <v>40000139</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="E95" s="2">
         <v>14</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G95" s="2">
         <v>1</v>
@@ -14828,13 +15023,13 @@
         <v>50000001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="E6" s="2">
         <v>5</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -14860,13 +15055,13 @@
         <v>50000002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="E7" s="2">
         <v>5</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -14892,13 +15087,13 @@
         <v>50000003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="E8" s="2">
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -14924,13 +15119,13 @@
         <v>50000004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="E9" s="2">
         <v>5</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -14956,13 +15151,13 @@
         <v>50000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="E10" s="2">
         <v>5</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -14988,13 +15183,13 @@
         <v>50000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="E11" s="2">
         <v>5</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -15020,13 +15215,13 @@
         <v>50000007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="E12" s="2">
         <v>5</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -15052,13 +15247,13 @@
         <v>50000008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="E13" s="2">
         <v>5</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -15084,13 +15279,13 @@
         <v>50000009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="E14" s="2">
         <v>5</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -15116,13 +15311,13 @@
         <v>50000010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="E15" s="2">
         <v>5</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -15148,13 +15343,13 @@
         <v>50000011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="E16" s="2">
         <v>5</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -15180,13 +15375,13 @@
         <v>50000012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="E17" s="2">
         <v>5</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -15212,13 +15407,13 @@
         <v>50000013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="E18" s="2">
         <v>5</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -15244,13 +15439,13 @@
         <v>50000014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="E19" s="2">
         <v>5</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -15276,13 +15471,13 @@
         <v>50000015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="E20" s="2">
         <v>5</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -15308,13 +15503,13 @@
         <v>50000016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="E21" s="2">
         <v>5</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -15340,13 +15535,13 @@
         <v>50000017</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="E22" s="2">
         <v>5</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -15372,13 +15567,13 @@
         <v>50000018</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="E23" s="2">
         <v>5</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -15404,13 +15599,13 @@
         <v>50000019</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="E24" s="2">
         <v>5</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -15436,13 +15631,13 @@
         <v>50000020</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="E25" s="2">
         <v>5</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -15468,13 +15663,13 @@
         <v>50000021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="E26" s="2">
         <v>5</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -15500,13 +15695,13 @@
         <v>50000022</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="E27" s="2">
         <v>5</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -15532,13 +15727,13 @@
         <v>50000023</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="E28" s="2">
         <v>5</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -15564,13 +15759,13 @@
         <v>50000024</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="E29" s="2">
         <v>5</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -15596,13 +15791,13 @@
         <v>50000025</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="E30" s="2">
         <v>5</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -15628,13 +15823,13 @@
         <v>50000026</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="E31" s="2">
         <v>5</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -15660,13 +15855,13 @@
         <v>50000027</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="E32" s="2">
         <v>5</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -15692,13 +15887,13 @@
         <v>50000028</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="E33" s="2">
         <v>5</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -15724,13 +15919,13 @@
         <v>50000029</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="E34" s="2">
         <v>5</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -15756,13 +15951,13 @@
         <v>50000030</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="E35" s="2">
         <v>5</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -15788,13 +15983,13 @@
         <v>50000031</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="E36" s="2">
         <v>5</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -15820,13 +16015,13 @@
         <v>50000032</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="E37" s="2">
         <v>5</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="G37" s="2">
         <v>1</v>
@@ -15852,13 +16047,13 @@
         <v>50000033</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="E38" s="2">
         <v>5</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="G38" s="2">
         <v>1</v>
@@ -15884,13 +16079,13 @@
         <v>50000034</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="E39" s="2">
         <v>5</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -15916,13 +16111,13 @@
         <v>50000035</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="E40" s="2">
         <v>5</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -15948,13 +16143,13 @@
         <v>50000036</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="E41" s="2">
         <v>5</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -15980,13 +16175,13 @@
         <v>50000037</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="E42" s="2">
         <v>5</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -16012,13 +16207,13 @@
         <v>50000038</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="E43" s="2">
         <v>5</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -16044,13 +16239,13 @@
         <v>50000039</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="E44" s="2">
         <v>5</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -16076,13 +16271,13 @@
         <v>50000040</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="E45" s="2">
         <v>5</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="G45" s="2">
         <v>1</v>
@@ -16108,13 +16303,13 @@
         <v>50000041</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="E46" s="2">
         <v>5</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -16140,13 +16335,13 @@
         <v>50000042</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="E47" s="2">
         <v>5</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -16172,13 +16367,13 @@
         <v>50000043</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="E48" s="2">
         <v>5</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -16204,13 +16399,13 @@
         <v>50000044</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="E49" s="2">
         <v>5</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -16236,13 +16431,13 @@
         <v>50000045</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="E50" s="2">
         <v>5</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -16268,13 +16463,13 @@
         <v>50000046</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="E51" s="2">
         <v>5</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -16300,13 +16495,13 @@
         <v>50000047</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="E52" s="2">
         <v>5</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -16332,13 +16527,13 @@
         <v>50000048</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="E53" s="2">
         <v>5</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="G53" s="2">
         <v>1</v>
@@ -16364,13 +16559,13 @@
         <v>50000049</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="E54" s="2">
         <v>5</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="G54" s="2">
         <v>1</v>
@@ -16396,13 +16591,13 @@
         <v>50000050</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="E55" s="2">
         <v>5</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="G55" s="2">
         <v>1</v>
@@ -16428,13 +16623,13 @@
         <v>50000051</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="E56" s="2">
         <v>5</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="G56" s="2">
         <v>1</v>
@@ -16460,13 +16655,13 @@
         <v>50000052</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="E57" s="2">
         <v>5</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="G57" s="2">
         <v>1</v>
@@ -16492,13 +16687,13 @@
         <v>50000053</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="E58" s="2">
         <v>5</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="G58" s="2">
         <v>1</v>
@@ -16524,13 +16719,13 @@
         <v>50000054</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="E59" s="2">
         <v>5</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="G59" s="2">
         <v>1</v>
@@ -16556,13 +16751,13 @@
         <v>50000055</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="E60" s="2">
         <v>5</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="G60" s="2">
         <v>1</v>
@@ -16588,13 +16783,13 @@
         <v>50000056</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="E61" s="2">
         <v>5</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="G61" s="2">
         <v>1</v>
@@ -16620,13 +16815,13 @@
         <v>50000057</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="E62" s="2">
         <v>5</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="G62" s="2">
         <v>1</v>
@@ -16652,13 +16847,13 @@
         <v>50000058</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="E63" s="2">
         <v>5</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="G63" s="2">
         <v>1</v>
@@ -16684,13 +16879,13 @@
         <v>50000059</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="E64" s="2">
         <v>5</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="G64" s="2">
         <v>1</v>
@@ -16716,13 +16911,13 @@
         <v>50000060</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="E65" s="2">
         <v>5</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="G65" s="2">
         <v>1</v>
@@ -16748,13 +16943,13 @@
         <v>50000061</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="E66" s="2">
         <v>5</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="G66" s="2">
         <v>1</v>
@@ -16780,13 +16975,13 @@
         <v>50000062</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="E67" s="2">
         <v>5</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="G67" s="2">
         <v>1</v>
@@ -16812,13 +17007,13 @@
         <v>50000063</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="E68" s="2">
         <v>5</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="G68" s="2">
         <v>1</v>
@@ -16844,13 +17039,13 @@
         <v>50000064</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="E69" s="2">
         <v>5</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="G69" s="2">
         <v>1</v>
@@ -16876,13 +17071,13 @@
         <v>50000065</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="E70" s="2">
         <v>5</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="G70" s="2">
         <v>1</v>
@@ -16908,13 +17103,13 @@
         <v>50000066</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="E71" s="2">
         <v>5</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="G71" s="2">
         <v>1</v>
@@ -16940,13 +17135,13 @@
         <v>50000067</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="E72" s="2">
         <v>5</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="G72" s="2">
         <v>1</v>
@@ -16972,13 +17167,13 @@
         <v>50000068</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="E73" s="2">
         <v>5</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="G73" s="2">
         <v>1</v>
@@ -17004,13 +17199,13 @@
         <v>50000069</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="E74" s="2">
         <v>5</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="G74" s="2">
         <v>1</v>
@@ -17036,13 +17231,13 @@
         <v>50000070</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="E75" s="2">
         <v>5</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="G75" s="2">
         <v>1</v>
@@ -17068,13 +17263,13 @@
         <v>50000071</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="E76" s="2">
         <v>5</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="G76" s="2">
         <v>1</v>
@@ -17100,13 +17295,13 @@
         <v>50000072</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="E77" s="2">
         <v>5</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="G77" s="2">
         <v>1</v>
@@ -17132,13 +17327,13 @@
         <v>50000073</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="E78" s="2">
         <v>5</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="G78" s="2">
         <v>1</v>
@@ -17164,13 +17359,13 @@
         <v>50000074</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="E79" s="2">
         <v>5</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="G79" s="2">
         <v>1</v>
@@ -17196,13 +17391,13 @@
         <v>50000075</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="E80" s="2">
         <v>5</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="G80" s="2">
         <v>1</v>
@@ -17228,13 +17423,13 @@
         <v>50000076</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="E81" s="2">
         <v>5</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="G81" s="2">
         <v>1</v>
@@ -17260,13 +17455,13 @@
         <v>50000077</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="E82" s="2">
         <v>5</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="G82" s="2">
         <v>1</v>
@@ -17292,13 +17487,13 @@
         <v>50000078</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="E83" s="2">
         <v>5</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="G83" s="2">
         <v>1</v>
@@ -17324,13 +17519,13 @@
         <v>50000079</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="E84" s="2">
         <v>5</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="G84" s="2">
         <v>1</v>
@@ -17356,13 +17551,13 @@
         <v>50000080</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="E85" s="2">
         <v>5</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="G85" s="2">
         <v>1</v>
@@ -17388,13 +17583,13 @@
         <v>50000081</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="E86" s="2">
         <v>5</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="G86" s="2">
         <v>1</v>
@@ -17420,13 +17615,13 @@
         <v>50000082</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="E87" s="2">
         <v>5</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="G87" s="2">
         <v>1</v>
@@ -17452,13 +17647,13 @@
         <v>50000083</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="E88" s="2">
         <v>5</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="G88" s="2">
         <v>1</v>
@@ -17484,13 +17679,13 @@
         <v>50000084</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="E89" s="2">
         <v>5</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="G89" s="2">
         <v>1</v>
@@ -17516,13 +17711,13 @@
         <v>50000085</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="E90" s="2">
         <v>5</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="G90" s="2">
         <v>1</v>
@@ -17548,13 +17743,13 @@
         <v>50000086</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="E91" s="2">
         <v>5</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="G91" s="2">
         <v>1</v>
@@ -17580,13 +17775,13 @@
         <v>50000087</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="E92" s="2">
         <v>5</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="G92" s="2">
         <v>1</v>
@@ -17612,13 +17807,13 @@
         <v>50000088</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="E93" s="2">
         <v>5</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="G93" s="2">
         <v>1</v>
@@ -17644,13 +17839,13 @@
         <v>50000089</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="E94" s="2">
         <v>5</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="G94" s="2">
         <v>1</v>
@@ -17676,13 +17871,13 @@
         <v>50000090</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="E95" s="2">
         <v>5</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="G95" s="2">
         <v>1</v>
@@ -17708,13 +17903,13 @@
         <v>50000091</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="E96" s="2">
         <v>5</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="G96" s="2">
         <v>1</v>
@@ -17740,13 +17935,13 @@
         <v>50000092</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="E97" s="2">
         <v>5</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="G97" s="2">
         <v>1</v>
@@ -17772,13 +17967,13 @@
         <v>50000093</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="E98" s="2">
         <v>5</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="G98" s="2">
         <v>1</v>
@@ -17804,13 +17999,13 @@
         <v>50000094</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="E99" s="2">
         <v>5</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G99" s="2">
         <v>1</v>
@@ -17836,13 +18031,13 @@
         <v>50000095</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="E100" s="2">
         <v>5</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="G100" s="2">
         <v>1</v>
@@ -17868,13 +18063,13 @@
         <v>50000096</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="E101" s="2">
         <v>5</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="G101" s="2">
         <v>1</v>
@@ -17900,13 +18095,13 @@
         <v>50000097</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E102" s="2">
         <v>5</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="G102" s="2">
         <v>1</v>
@@ -17932,13 +18127,13 @@
         <v>50000098</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="E103" s="2">
         <v>5</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="G103" s="2">
         <v>1</v>
@@ -17964,13 +18159,13 @@
         <v>50000099</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="E104" s="2">
         <v>5</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="G104" s="2">
         <v>1</v>
@@ -17996,13 +18191,13 @@
         <v>50000100</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="E105" s="2">
         <v>5</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="G105" s="2">
         <v>1</v>
@@ -18028,13 +18223,13 @@
         <v>50000101</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="E106" s="2">
         <v>5</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="G106" s="2">
         <v>1</v>
@@ -18060,13 +18255,13 @@
         <v>50000102</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="E107" s="2">
         <v>5</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="G107" s="2">
         <v>1</v>
@@ -18092,13 +18287,13 @@
         <v>50000103</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="E108" s="2">
         <v>5</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="G108" s="2">
         <v>1</v>
@@ -18124,13 +18319,13 @@
         <v>50000104</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="E109" s="2">
         <v>5</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="G109" s="2">
         <v>1</v>
@@ -18295,13 +18490,13 @@
         <v>180001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="E6" s="2">
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -18321,13 +18516,13 @@
         <v>180002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="E7" s="2">
         <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -18347,13 +18542,13 @@
         <v>180003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="E8" s="2">
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -18373,13 +18568,13 @@
         <v>180004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="E9" s="2">
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -18399,13 +18594,13 @@
         <v>180005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="E10" s="2">
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -18425,13 +18620,13 @@
         <v>180006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="E11" s="2">
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -18453,13 +18648,13 @@
         <v>180007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="E12" s="2">
         <v>18</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -18481,13 +18676,13 @@
         <v>180008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="E13" s="2">
         <v>18</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -18509,13 +18704,13 @@
         <v>180009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="E14" s="2">
         <v>18</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -18537,13 +18732,13 @@
         <v>180010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="E15" s="2">
         <v>18</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -18565,13 +18760,13 @@
         <v>180011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="E16" s="2">
         <v>18</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -18593,13 +18788,13 @@
         <v>180012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="E17" s="2">
         <v>18</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -18621,13 +18816,13 @@
         <v>180013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="E18" s="2">
         <v>18</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -18649,13 +18844,13 @@
         <v>180014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="E19" s="2">
         <v>18</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -18677,13 +18872,13 @@
         <v>180015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="E20" s="2">
         <v>18</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -18705,13 +18900,13 @@
         <v>180016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="E21" s="2">
         <v>18</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -18733,13 +18928,13 @@
         <v>180017</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="E22" s="2">
         <v>18</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -18761,13 +18956,13 @@
         <v>180018</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="E23" s="2">
         <v>18</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -18789,13 +18984,13 @@
         <v>180019</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="E24" s="2">
         <v>18</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -18817,13 +19012,13 @@
         <v>180020</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="E25" s="2">
         <v>18</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -18845,13 +19040,13 @@
         <v>180021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="E26" s="2">
         <v>18</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -18878,13 +19073,13 @@
         <v>180030</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="E28" s="2">
         <v>18</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -18906,13 +19101,13 @@
         <v>180031</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="E29" s="2">
         <v>18</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="G29" s="3">
         <v>1</v>
@@ -18932,13 +19127,13 @@
         <v>180032</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="E30" s="2">
         <v>18</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="G30" s="3">
         <v>1</v>
@@ -18958,13 +19153,13 @@
         <v>180033</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="E31" s="2">
         <v>18</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="G31" s="3">
         <v>1</v>
@@ -18984,13 +19179,13 @@
         <v>180034</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="E32" s="2">
         <v>18</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="G32" s="3">
         <v>1</v>
@@ -19156,13 +19351,13 @@
         <v>190001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="E6" s="2">
         <v>19</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -19182,13 +19377,13 @@
         <v>190002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="E7" s="2">
         <v>19</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -19208,13 +19403,13 @@
         <v>190003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="E8" s="2">
         <v>19</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -19234,13 +19429,13 @@
         <v>190004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="E9" s="2">
         <v>19</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -19260,13 +19455,13 @@
         <v>190005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="E10" s="2">
         <v>19</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -19286,13 +19481,13 @@
         <v>190006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="E11" s="2">
         <v>19</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -344,7 +344,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="737">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="739">
   <si>
     <t>_Id</t>
   </si>
@@ -854,6 +854,12 @@
   </si>
   <si>
     <t>分解金装获取，金装升阶材料</t>
+  </si>
+  <si>
+    <t>天赋书</t>
+  </si>
+  <si>
+    <t>天赋经验+500</t>
   </si>
   <si>
     <t>图鉴碎片</t>
@@ -4864,7 +4870,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:M74"/>
+  <dimension ref="C3:M75"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="3"/>
@@ -5593,53 +5599,53 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C26" s="3">
-        <v>4101</v>
-      </c>
-      <c r="D26" s="3" t="s">
+    <row r="25" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C25" s="3">
+        <v>4020</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="E26" s="3">
-        <v>5</v>
-      </c>
-      <c r="F26" s="3" t="s">
+      <c r="E25" s="3">
+        <v>15</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="G26" s="3">
-        <v>1</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="G25" s="3">
+        <v>1</v>
+      </c>
+      <c r="H25" s="3">
         <v>9999999</v>
       </c>
-      <c r="I26" s="3">
-        <v>0</v>
-      </c>
-      <c r="J26" s="3">
-        <v>5</v>
-      </c>
-      <c r="L26" s="3">
-        <v>0</v>
-      </c>
-      <c r="M26" s="3">
-        <v>0</v>
-      </c>
+      <c r="I25" s="3">
+        <v>0</v>
+      </c>
+      <c r="J25" s="3">
+        <v>7</v>
+      </c>
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3"/>
     </row>
     <row r="27" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C27" s="3">
-        <v>4102</v>
+        <v>4101</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>172</v>
@@ -5671,7 +5677,7 @@
     </row>
     <row r="28" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C28" s="3">
-        <v>4103</v>
+        <v>4102</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>174</v>
@@ -5680,7 +5686,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="G28" s="3">
         <v>1</v>
@@ -5703,10 +5709,10 @@
     </row>
     <row r="29" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C29" s="3">
-        <v>4104</v>
+        <v>4103</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E29" s="3">
         <v>5</v>
@@ -5735,10 +5741,10 @@
     </row>
     <row r="30" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C30" s="3">
-        <v>4105</v>
+        <v>4104</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E30" s="3">
         <v>5</v>
@@ -5767,16 +5773,16 @@
     </row>
     <row r="31" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C31" s="3">
-        <v>4106</v>
+        <v>4105</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E31" s="3">
         <v>5</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>176</v>
+        <v>149</v>
       </c>
       <c r="G31" s="3">
         <v>1</v>
@@ -5799,7 +5805,7 @@
     </row>
     <row r="32" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C32" s="3">
-        <v>4107</v>
+        <v>4106</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>177</v>
@@ -5831,7 +5837,7 @@
     </row>
     <row r="33" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C33" s="3">
-        <v>4108</v>
+        <v>4107</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>179</v>
@@ -5863,7 +5869,7 @@
     </row>
     <row r="34" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C34" s="3">
-        <v>4109</v>
+        <v>4108</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>181</v>
@@ -5895,7 +5901,7 @@
     </row>
     <row r="35" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C35" s="3">
-        <v>4110</v>
+        <v>4109</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>183</v>
@@ -5927,7 +5933,7 @@
     </row>
     <row r="36" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C36" s="3">
-        <v>4111</v>
+        <v>4110</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>185</v>
@@ -5957,41 +5963,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C38" s="3">
-        <v>4201</v>
-      </c>
-      <c r="D38" s="3" t="s">
+    <row r="37" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C37" s="3">
+        <v>4111</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="E38" s="3">
-        <v>5</v>
-      </c>
-      <c r="F38" s="3" t="s">
+      <c r="E37" s="3">
+        <v>5</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="G38" s="3">
-        <v>1</v>
-      </c>
-      <c r="H38" s="3">
-        <v>2000000</v>
-      </c>
-      <c r="I38" s="3">
-        <v>0</v>
-      </c>
-      <c r="J38" s="3">
-        <v>5</v>
-      </c>
-      <c r="L38" s="3">
-        <v>4002</v>
-      </c>
-      <c r="M38" s="3">
-        <v>1000</v>
+      <c r="G37" s="3">
+        <v>1</v>
+      </c>
+      <c r="H37" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I37" s="3">
+        <v>0</v>
+      </c>
+      <c r="J37" s="3">
+        <v>5</v>
+      </c>
+      <c r="L37" s="3">
+        <v>0</v>
+      </c>
+      <c r="M37" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="39" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C39" s="3">
-        <v>4202</v>
+        <v>4201</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>189</v>
@@ -6006,7 +6012,7 @@
         <v>1</v>
       </c>
       <c r="H39" s="3">
-        <v>99999</v>
+        <v>2000000</v>
       </c>
       <c r="I39" s="3">
         <v>0</v>
@@ -6015,50 +6021,47 @@
         <v>5</v>
       </c>
       <c r="L39" s="3">
-        <v>0</v>
+        <v>4002</v>
       </c>
       <c r="M39" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C41" s="3">
-        <v>6101</v>
-      </c>
-      <c r="D41" s="3" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="40" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C40" s="3">
+        <v>4202</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="E41" s="3">
-        <v>7</v>
-      </c>
-      <c r="F41" s="3" t="s">
+      <c r="E40" s="3">
+        <v>5</v>
+      </c>
+      <c r="F40" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="G41" s="3">
-        <v>1</v>
-      </c>
-      <c r="H41" s="3">
-        <v>99999</v>
-      </c>
-      <c r="I41" s="3">
-        <v>0</v>
-      </c>
-      <c r="J41" s="3">
-        <v>4</v>
-      </c>
-      <c r="K41" s="3">
-        <v>1</v>
-      </c>
-      <c r="L41" s="3">
-        <v>0</v>
-      </c>
-      <c r="M41" s="3">
+      <c r="G40" s="3">
+        <v>1</v>
+      </c>
+      <c r="H40" s="3">
+        <v>99999</v>
+      </c>
+      <c r="I40" s="3">
+        <v>0</v>
+      </c>
+      <c r="J40" s="3">
+        <v>5</v>
+      </c>
+      <c r="L40" s="3">
+        <v>0</v>
+      </c>
+      <c r="M40" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="42" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C42" s="3">
-        <v>6102</v>
+        <v>6101</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>193</v>
@@ -6082,7 +6085,7 @@
         <v>4</v>
       </c>
       <c r="K42" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L42" s="3">
         <v>0</v>
@@ -6093,7 +6096,7 @@
     </row>
     <row r="43" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C43" s="3">
-        <v>6103</v>
+        <v>6102</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>195</v>
@@ -6117,7 +6120,7 @@
         <v>4</v>
       </c>
       <c r="K43" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -6128,7 +6131,7 @@
     </row>
     <row r="44" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C44" s="3">
-        <v>6104</v>
+        <v>6103</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>197</v>
@@ -6152,7 +6155,7 @@
         <v>4</v>
       </c>
       <c r="K44" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -6161,9 +6164,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" customHeight="1" spans="3:13">
+    <row r="45" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C45" s="3">
-        <v>6105</v>
+        <v>6104</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>199</v>
@@ -6187,7 +6190,7 @@
         <v>4</v>
       </c>
       <c r="K45" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
@@ -6196,9 +6199,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" s="3" customFormat="1" customHeight="1" spans="3:13">
+    <row r="46" customHeight="1" spans="3:13">
       <c r="C46" s="3">
-        <v>6106</v>
+        <v>6105</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>201</v>
@@ -6222,7 +6225,7 @@
         <v>4</v>
       </c>
       <c r="K46" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L46" s="3">
         <v>0</v>
@@ -6231,15 +6234,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" customHeight="1" spans="3:13">
+    <row r="47" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C47" s="3">
-        <v>7101</v>
+        <v>6106</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>203</v>
       </c>
       <c r="E47" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>204</v>
@@ -6257,7 +6260,7 @@
         <v>4</v>
       </c>
       <c r="K47" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -6268,7 +6271,7 @@
     </row>
     <row r="48" customHeight="1" spans="3:13">
       <c r="C48" s="3">
-        <v>7102</v>
+        <v>7101</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>205</v>
@@ -6292,7 +6295,7 @@
         <v>4</v>
       </c>
       <c r="K48" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L48" s="3">
         <v>0</v>
@@ -6303,7 +6306,7 @@
     </row>
     <row r="49" customHeight="1" spans="3:13">
       <c r="C49" s="3">
-        <v>7103</v>
+        <v>7102</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>207</v>
@@ -6327,7 +6330,7 @@
         <v>4</v>
       </c>
       <c r="K49" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
@@ -6338,7 +6341,7 @@
     </row>
     <row r="50" customHeight="1" spans="3:13">
       <c r="C50" s="3">
-        <v>7104</v>
+        <v>7103</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>209</v>
@@ -6362,7 +6365,7 @@
         <v>4</v>
       </c>
       <c r="K50" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L50" s="3">
         <v>0</v>
@@ -6373,7 +6376,7 @@
     </row>
     <row r="51" customHeight="1" spans="3:13">
       <c r="C51" s="3">
-        <v>7105</v>
+        <v>7104</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>211</v>
@@ -6397,7 +6400,7 @@
         <v>4</v>
       </c>
       <c r="K51" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L51" s="3">
         <v>0</v>
@@ -6408,7 +6411,7 @@
     </row>
     <row r="52" customHeight="1" spans="3:13">
       <c r="C52" s="3">
-        <v>7107</v>
+        <v>7105</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>213</v>
@@ -6432,7 +6435,7 @@
         <v>4</v>
       </c>
       <c r="K52" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -6441,41 +6444,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C56" s="3">
-        <v>8001</v>
-      </c>
-      <c r="D56" s="3" t="s">
+    <row r="53" customHeight="1" spans="3:13">
+      <c r="C53" s="3">
+        <v>7107</v>
+      </c>
+      <c r="D53" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="E56" s="3">
-        <v>5</v>
-      </c>
-      <c r="F56" s="3" t="s">
+      <c r="E53" s="3">
+        <v>8</v>
+      </c>
+      <c r="F53" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="G56" s="3">
-        <v>1</v>
-      </c>
-      <c r="H56" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="I56" s="3">
-        <v>0</v>
-      </c>
-      <c r="J56" s="3">
-        <v>6</v>
-      </c>
-      <c r="L56" s="3">
-        <v>0</v>
-      </c>
-      <c r="M56" s="3">
+      <c r="G53" s="3">
+        <v>1</v>
+      </c>
+      <c r="H53" s="3">
+        <v>99999</v>
+      </c>
+      <c r="I53" s="3">
+        <v>0</v>
+      </c>
+      <c r="J53" s="3">
+        <v>4</v>
+      </c>
+      <c r="K53" s="3">
+        <v>6</v>
+      </c>
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="57" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C57" s="3">
-        <v>8002</v>
+        <v>8001</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>217</v>
@@ -6484,7 +6490,7 @@
         <v>5</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G57" s="3">
         <v>1</v>
@@ -6507,16 +6513,16 @@
     </row>
     <row r="58" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C58" s="3">
-        <v>8003</v>
+        <v>8002</v>
       </c>
       <c r="D58" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E58" s="3">
+        <v>5</v>
+      </c>
+      <c r="F58" s="3" t="s">
         <v>218</v>
-      </c>
-      <c r="E58" s="3">
-        <v>5</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>216</v>
       </c>
       <c r="G58" s="3">
         <v>1</v>
@@ -6539,16 +6545,16 @@
     </row>
     <row r="59" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C59" s="3">
-        <v>8004</v>
+        <v>8003</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E59" s="3">
         <v>5</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G59" s="3">
         <v>1</v>
@@ -6571,16 +6577,16 @@
     </row>
     <row r="60" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C60" s="3">
-        <v>8005</v>
+        <v>8004</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E60" s="3">
         <v>5</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G60" s="3">
         <v>1</v>
@@ -6603,16 +6609,16 @@
     </row>
     <row r="61" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C61" s="3">
-        <v>8006</v>
+        <v>8005</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E61" s="3">
         <v>5</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G61" s="3">
         <v>1</v>
@@ -6635,16 +6641,16 @@
     </row>
     <row r="62" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C62" s="3">
-        <v>8007</v>
+        <v>8006</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E62" s="3">
         <v>5</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G62" s="3">
         <v>1</v>
@@ -6667,16 +6673,16 @@
     </row>
     <row r="63" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C63" s="3">
-        <v>8008</v>
+        <v>8007</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E63" s="3">
         <v>5</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G63" s="3">
         <v>1</v>
@@ -6699,16 +6705,16 @@
     </row>
     <row r="64" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C64" s="3">
-        <v>8009</v>
+        <v>8008</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E64" s="3">
         <v>5</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G64" s="3">
         <v>1</v>
@@ -6731,16 +6737,16 @@
     </row>
     <row r="65" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C65" s="3">
-        <v>8010</v>
+        <v>8009</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E65" s="3">
         <v>5</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G65" s="3">
         <v>1</v>
@@ -6761,41 +6767,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C67" s="3">
-        <v>8101</v>
-      </c>
-      <c r="D67" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="E67" s="3">
-        <v>5</v>
-      </c>
-      <c r="F67" s="3" t="s">
+    <row r="66" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C66" s="3">
+        <v>8010</v>
+      </c>
+      <c r="D66" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="G67" s="3">
-        <v>1</v>
-      </c>
-      <c r="H67" s="3">
+      <c r="E66" s="3">
+        <v>5</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="G66" s="3">
+        <v>1</v>
+      </c>
+      <c r="H66" s="3">
         <v>9999999</v>
       </c>
-      <c r="I67" s="3">
-        <v>0</v>
-      </c>
-      <c r="J67" s="3">
-        <v>7</v>
-      </c>
-      <c r="L67" s="3">
-        <v>0</v>
-      </c>
-      <c r="M67" s="3">
+      <c r="I66" s="3">
+        <v>0</v>
+      </c>
+      <c r="J66" s="3">
+        <v>6</v>
+      </c>
+      <c r="L66" s="3">
+        <v>0</v>
+      </c>
+      <c r="M66" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="68" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C68" s="3">
-        <v>8102</v>
+        <v>8101</v>
       </c>
       <c r="D68" s="10" t="s">
         <v>228</v>
@@ -6804,7 +6810,7 @@
         <v>5</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G68" s="3">
         <v>1</v>
@@ -6827,16 +6833,16 @@
     </row>
     <row r="69" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C69" s="3">
-        <v>8103</v>
+        <v>8102</v>
       </c>
       <c r="D69" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="E69" s="3">
+        <v>5</v>
+      </c>
+      <c r="F69" s="3" t="s">
         <v>229</v>
-      </c>
-      <c r="E69" s="3">
-        <v>5</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>227</v>
       </c>
       <c r="G69" s="3">
         <v>1</v>
@@ -6859,16 +6865,16 @@
     </row>
     <row r="70" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C70" s="3">
-        <v>8104</v>
+        <v>8103</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E70" s="3">
         <v>5</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G70" s="3">
         <v>1</v>
@@ -6891,16 +6897,16 @@
     </row>
     <row r="71" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C71" s="3">
-        <v>8105</v>
+        <v>8104</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E71" s="3">
         <v>5</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G71" s="3">
         <v>1</v>
@@ -6923,16 +6929,16 @@
     </row>
     <row r="72" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C72" s="3">
-        <v>8106</v>
+        <v>8105</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E72" s="3">
         <v>5</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G72" s="3">
         <v>1</v>
@@ -6955,16 +6961,16 @@
     </row>
     <row r="73" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C73" s="3">
-        <v>8107</v>
+        <v>8106</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E73" s="3">
         <v>5</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G73" s="3">
         <v>1</v>
@@ -6987,16 +6993,16 @@
     </row>
     <row r="74" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C74" s="3">
-        <v>8108</v>
+        <v>8107</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E74" s="3">
         <v>5</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G74" s="3">
         <v>1</v>
@@ -7014,6 +7020,38 @@
         <v>0</v>
       </c>
       <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C75" s="3">
+        <v>8108</v>
+      </c>
+      <c r="D75" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="E75" s="3">
+        <v>5</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="G75" s="3">
+        <v>1</v>
+      </c>
+      <c r="H75" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I75" s="3">
+        <v>0</v>
+      </c>
+      <c r="J75" s="3">
+        <v>7</v>
+      </c>
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
         <v>0</v>
       </c>
     </row>
@@ -7161,13 +7199,13 @@
         <v>1999001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E6" s="2">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -7181,7 +7219,6 @@
       <c r="J6" s="2">
         <v>6</v>
       </c>
-      <c r="K6" s="2"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
     </row>
@@ -7190,13 +7227,13 @@
         <v>1999002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E7" s="2">
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -7210,7 +7247,6 @@
       <c r="J7" s="2">
         <v>6</v>
       </c>
-      <c r="K7" s="2"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
     </row>
@@ -7219,13 +7255,13 @@
         <v>1999003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E8" s="2">
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -7239,7 +7275,6 @@
       <c r="J8" s="2">
         <v>6</v>
       </c>
-      <c r="K8" s="2"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
     </row>
@@ -7248,13 +7283,13 @@
         <v>1999004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E9" s="2">
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -7276,13 +7311,13 @@
         <v>1999005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E10" s="2">
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -7304,13 +7339,13 @@
         <v>1999006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E11" s="2">
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -7324,7 +7359,6 @@
       <c r="J11" s="2">
         <v>6</v>
       </c>
-      <c r="K11" s="2"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
     </row>
@@ -7338,13 +7372,13 @@
         <v>1999989</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E13" s="2">
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -7358,7 +7392,6 @@
       <c r="J13" s="2">
         <v>6</v>
       </c>
-      <c r="K13" s="2"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
     </row>
@@ -7367,13 +7400,13 @@
         <v>1999990</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E14" s="2">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -7387,7 +7420,6 @@
       <c r="J14" s="2">
         <v>6</v>
       </c>
-      <c r="K14" s="2"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
     </row>
@@ -7396,13 +7428,13 @@
         <v>1999991</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E15" s="2">
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -7424,13 +7456,13 @@
         <v>1999992</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E16" s="2">
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -7452,13 +7484,13 @@
         <v>1999993</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E17" s="2">
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -7480,13 +7512,13 @@
         <v>1999994</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E18" s="2">
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -7508,13 +7540,13 @@
         <v>1999995</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E19" s="2">
         <v>11</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -7536,13 +7568,13 @@
         <v>1999996</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E20" s="2">
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -7564,13 +7596,13 @@
         <v>1999997</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E21" s="2">
         <v>11</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -7592,13 +7624,13 @@
         <v>2000000</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E22" s="2">
         <v>11</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -7620,13 +7652,13 @@
         <v>2000001</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E23" s="2">
         <v>11</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -7648,13 +7680,13 @@
         <v>2000002</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E24" s="2">
         <v>11</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -7676,13 +7708,13 @@
         <v>2000003</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E25" s="2">
         <v>11</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -7704,13 +7736,13 @@
         <v>2000004</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E26" s="2">
         <v>11</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -7732,13 +7764,13 @@
         <v>2000005</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E27" s="2">
         <v>11</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -7760,13 +7792,13 @@
         <v>2000006</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E28" s="2">
         <v>11</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -7788,13 +7820,13 @@
         <v>2000007</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E29" s="2">
         <v>11</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -7816,13 +7848,13 @@
         <v>2000008</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E30" s="2">
         <v>11</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -7844,13 +7876,13 @@
         <v>2000009</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E31" s="2">
         <v>11</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -7872,13 +7904,13 @@
         <v>2000010</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E32" s="2">
         <v>11</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -7900,13 +7932,13 @@
         <v>2000011</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E33" s="2">
         <v>11</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -7928,13 +7960,13 @@
         <v>2000012</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E34" s="2">
         <v>11</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -7956,13 +7988,13 @@
         <v>2000013</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E35" s="2">
         <v>11</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -7996,13 +8028,13 @@
         <v>2000100</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E39" s="2">
         <v>11</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -8024,13 +8056,13 @@
         <v>2000101</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E40" s="2">
         <v>11</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -8052,13 +8084,13 @@
         <v>2000102</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E41" s="2">
         <v>11</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -8080,13 +8112,13 @@
         <v>2000103</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E42" s="2">
         <v>11</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -8108,13 +8140,13 @@
         <v>2000104</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E43" s="2">
         <v>11</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -8136,13 +8168,13 @@
         <v>2000105</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E44" s="2">
         <v>11</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -8164,13 +8196,13 @@
         <v>2000106</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E45" s="2">
         <v>11</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G45" s="2">
         <v>1</v>
@@ -8192,13 +8224,13 @@
         <v>2000107</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E46" s="2">
         <v>11</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -8220,13 +8252,13 @@
         <v>2000108</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E47" s="2">
         <v>11</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -8248,13 +8280,13 @@
         <v>2000109</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E48" s="2">
         <v>11</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -8276,13 +8308,13 @@
         <v>2000110</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E49" s="2">
         <v>11</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -8304,13 +8336,13 @@
         <v>2000111</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E50" s="2">
         <v>11</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -8332,13 +8364,13 @@
         <v>2000112</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E51" s="2">
         <v>11</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -8360,13 +8392,13 @@
         <v>2000113</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E52" s="2">
         <v>11</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -8388,13 +8420,13 @@
         <v>2000114</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E53" s="2">
         <v>11</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G53" s="2">
         <v>1</v>
@@ -8416,13 +8448,13 @@
         <v>2000115</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E54" s="2">
         <v>11</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G54" s="2">
         <v>1</v>
@@ -8444,13 +8476,13 @@
         <v>2000116</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E55" s="2">
         <v>11</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G55" s="2">
         <v>1</v>
@@ -8472,13 +8504,13 @@
         <v>2000117</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E56" s="2">
         <v>11</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G56" s="2">
         <v>1</v>
@@ -8500,13 +8532,13 @@
         <v>2000118</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E57" s="2">
         <v>11</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G57" s="2">
         <v>1</v>
@@ -8528,13 +8560,13 @@
         <v>2000119</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E58" s="2">
         <v>11</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G58" s="2">
         <v>1</v>
@@ -8556,13 +8588,13 @@
         <v>2000120</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E59" s="2">
         <v>11</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G59" s="2">
         <v>1</v>
@@ -8584,13 +8616,13 @@
         <v>2000121</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E60" s="2">
         <v>11</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G60" s="2">
         <v>1</v>
@@ -8612,13 +8644,13 @@
         <v>2000122</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E61" s="2">
         <v>11</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G61" s="2">
         <v>1</v>
@@ -8640,13 +8672,13 @@
         <v>2000123</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E62" s="2">
         <v>11</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G62" s="2">
         <v>1</v>
@@ -8668,13 +8700,13 @@
         <v>2000124</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E63" s="2">
         <v>11</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G63" s="2">
         <v>1</v>
@@ -8696,13 +8728,13 @@
         <v>2000125</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E64" s="2">
         <v>11</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G64" s="2">
         <v>1</v>
@@ -8724,13 +8756,13 @@
         <v>2000126</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E65" s="2">
         <v>11</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G65" s="2">
         <v>1</v>
@@ -8752,13 +8784,13 @@
         <v>2000127</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E66" s="2">
         <v>11</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G66" s="2">
         <v>1</v>
@@ -8780,13 +8812,13 @@
         <v>2000128</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E67" s="2">
         <v>11</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G67" s="2">
         <v>1</v>
@@ -8808,13 +8840,13 @@
         <v>2000129</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E68" s="2">
         <v>11</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G68" s="2">
         <v>1</v>
@@ -8836,13 +8868,13 @@
         <v>2000200</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E70" s="2">
         <v>11</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G70" s="2">
         <v>1</v>
@@ -8862,13 +8894,13 @@
         <v>2000201</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E71" s="2">
         <v>11</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G71" s="2">
         <v>1</v>
@@ -8888,13 +8920,13 @@
         <v>2000202</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E72" s="2">
         <v>11</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G72" s="2">
         <v>1</v>
@@ -8914,13 +8946,13 @@
         <v>2000203</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E73" s="2">
         <v>11</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G73" s="2">
         <v>1</v>
@@ -8940,13 +8972,13 @@
         <v>2000204</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E74" s="2">
         <v>11</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G74" s="2">
         <v>1</v>
@@ -8966,13 +8998,13 @@
         <v>2000205</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E75" s="2">
         <v>11</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G75" s="2">
         <v>1</v>
@@ -8992,13 +9024,13 @@
         <v>2000206</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E76" s="2">
         <v>11</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G76" s="2">
         <v>1</v>
@@ -9018,13 +9050,13 @@
         <v>2000207</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E77" s="2">
         <v>11</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G77" s="2">
         <v>1</v>
@@ -9044,13 +9076,13 @@
         <v>2000208</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E78" s="2">
         <v>11</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G78" s="2">
         <v>1</v>
@@ -9070,13 +9102,13 @@
         <v>2000209</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E79" s="2">
         <v>11</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G79" s="2">
         <v>1</v>
@@ -9096,13 +9128,13 @@
         <v>2000210</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E80" s="2">
         <v>11</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G80" s="2">
         <v>1</v>
@@ -9122,13 +9154,13 @@
         <v>2000211</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E81" s="2">
         <v>11</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G81" s="2">
         <v>1</v>
@@ -9148,13 +9180,13 @@
         <v>2000212</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E82" s="2">
         <v>11</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G82" s="2">
         <v>1</v>
@@ -9174,13 +9206,13 @@
         <v>2000213</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E83" s="2">
         <v>11</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G83" s="2">
         <v>1</v>
@@ -9200,13 +9232,13 @@
         <v>2000214</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E84" s="2">
         <v>11</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G84" s="2">
         <v>1</v>
@@ -9226,13 +9258,13 @@
         <v>2000215</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E85" s="2">
         <v>11</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G85" s="2">
         <v>1</v>
@@ -9252,13 +9284,13 @@
         <v>2000216</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E86" s="2">
         <v>11</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G86" s="2">
         <v>1</v>
@@ -9278,13 +9310,13 @@
         <v>2000217</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E87" s="2">
         <v>11</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G87" s="2">
         <v>1</v>
@@ -9304,13 +9336,13 @@
         <v>2000218</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E88" s="2">
         <v>11</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G88" s="2">
         <v>1</v>
@@ -9330,13 +9362,13 @@
         <v>2000219</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E89" s="2">
         <v>11</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G89" s="2">
         <v>1</v>
@@ -9356,13 +9388,13 @@
         <v>2000220</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E90" s="2">
         <v>11</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G90" s="2">
         <v>1</v>
@@ -9382,13 +9414,13 @@
         <v>2000221</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E91" s="2">
         <v>11</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G91" s="2">
         <v>1</v>
@@ -9408,13 +9440,13 @@
         <v>2000222</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E92" s="2">
         <v>11</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G92" s="2">
         <v>1</v>
@@ -9434,13 +9466,13 @@
         <v>2000223</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E93" s="2">
         <v>11</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G93" s="2">
         <v>1</v>
@@ -9460,13 +9492,13 @@
         <v>2000224</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E94" s="2">
         <v>11</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G94" s="2">
         <v>1</v>
@@ -9486,13 +9518,13 @@
         <v>2000225</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E95" s="2">
         <v>11</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G95" s="2">
         <v>1</v>
@@ -9512,13 +9544,13 @@
         <v>2000226</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E96" s="2">
         <v>11</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G96" s="2">
         <v>1</v>
@@ -9538,13 +9570,13 @@
         <v>2000227</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E97" s="2">
         <v>11</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G97" s="2">
         <v>1</v>
@@ -9564,13 +9596,13 @@
         <v>2000228</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E98" s="2">
         <v>11</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G98" s="2">
         <v>1</v>
@@ -9590,13 +9622,13 @@
         <v>2000229</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E99" s="2">
         <v>11</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G99" s="2">
         <v>1</v>
@@ -9616,13 +9648,13 @@
         <v>2000300</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E102" s="2">
         <v>11</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G102" s="2">
         <v>1</v>
@@ -9642,13 +9674,13 @@
         <v>2000301</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E103" s="2">
         <v>11</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G103" s="2">
         <v>1</v>
@@ -9668,13 +9700,13 @@
         <v>2000302</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E104" s="2">
         <v>11</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G104" s="2">
         <v>1</v>
@@ -9694,13 +9726,13 @@
         <v>2000303</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E105" s="2">
         <v>11</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G105" s="2">
         <v>1</v>
@@ -9720,13 +9752,13 @@
         <v>2000304</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E106" s="2">
         <v>11</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G106" s="2">
         <v>1</v>
@@ -9746,13 +9778,13 @@
         <v>2000305</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E107" s="2">
         <v>11</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G107" s="2">
         <v>1</v>
@@ -9772,13 +9804,13 @@
         <v>2000306</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E108" s="2">
         <v>11</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G108" s="2">
         <v>1</v>
@@ -9798,13 +9830,13 @@
         <v>2000307</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E109" s="2">
         <v>11</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G109" s="2">
         <v>1</v>
@@ -9824,13 +9856,13 @@
         <v>2000308</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E110" s="2">
         <v>11</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G110" s="2">
         <v>1</v>
@@ -9850,13 +9882,13 @@
         <v>2000309</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E111" s="2">
         <v>11</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G111" s="2">
         <v>1</v>
@@ -9876,13 +9908,13 @@
         <v>2000310</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E112" s="2">
         <v>11</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G112" s="2">
         <v>1</v>
@@ -9902,13 +9934,13 @@
         <v>2000311</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E113" s="2">
         <v>11</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G113" s="2">
         <v>1</v>
@@ -9928,13 +9960,13 @@
         <v>2000312</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E114" s="2">
         <v>11</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G114" s="2">
         <v>1</v>
@@ -9954,13 +9986,13 @@
         <v>2000313</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E115" s="2">
         <v>11</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G115" s="2">
         <v>1</v>
@@ -9980,13 +10012,13 @@
         <v>2000314</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E116" s="2">
         <v>11</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G116" s="2">
         <v>1</v>
@@ -10006,13 +10038,13 @@
         <v>2000315</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E117" s="2">
         <v>11</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G117" s="2">
         <v>1</v>
@@ -10032,13 +10064,13 @@
         <v>2000316</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E118" s="2">
         <v>11</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G118" s="2">
         <v>1</v>
@@ -10058,13 +10090,13 @@
         <v>2000317</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E119" s="2">
         <v>11</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G119" s="2">
         <v>1</v>
@@ -10084,13 +10116,13 @@
         <v>2000318</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E120" s="2">
         <v>11</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G120" s="2">
         <v>1</v>
@@ -10110,13 +10142,13 @@
         <v>2000319</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E121" s="2">
         <v>11</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G121" s="2">
         <v>1</v>
@@ -10136,13 +10168,13 @@
         <v>2000320</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E122" s="2">
         <v>11</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G122" s="2">
         <v>1</v>
@@ -10162,13 +10194,13 @@
         <v>2000321</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E123" s="2">
         <v>11</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G123" s="2">
         <v>1</v>
@@ -10188,13 +10220,13 @@
         <v>2000322</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E124" s="2">
         <v>11</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G124" s="2">
         <v>1</v>
@@ -10214,13 +10246,13 @@
         <v>2000323</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E125" s="2">
         <v>11</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G125" s="2">
         <v>1</v>
@@ -10240,13 +10272,13 @@
         <v>2000324</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E126" s="2">
         <v>11</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G126" s="2">
         <v>1</v>
@@ -10266,13 +10298,13 @@
         <v>2000325</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E127" s="2">
         <v>11</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G127" s="2">
         <v>1</v>
@@ -10292,13 +10324,13 @@
         <v>2000326</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E128" s="2">
         <v>11</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G128" s="2">
         <v>1</v>
@@ -10318,13 +10350,13 @@
         <v>2000327</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E129" s="2">
         <v>11</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G129" s="2">
         <v>1</v>
@@ -10344,13 +10376,13 @@
         <v>2000328</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E130" s="2">
         <v>11</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G130" s="2">
         <v>1</v>
@@ -10370,13 +10402,13 @@
         <v>2000329</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E131" s="2">
         <v>11</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G131" s="2">
         <v>1</v>
@@ -10535,13 +10567,13 @@
         <v>3000001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E6" s="2">
         <v>13</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -10563,13 +10595,13 @@
         <v>3000002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E7" s="2">
         <v>13</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -10591,13 +10623,13 @@
         <v>3000003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E8" s="2">
         <v>13</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -10619,13 +10651,13 @@
         <v>3000004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E9" s="2">
         <v>13</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -10647,13 +10679,13 @@
         <v>3000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E10" s="2">
         <v>13</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -10675,13 +10707,13 @@
         <v>3000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E11" s="2">
         <v>13</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -10703,13 +10735,13 @@
         <v>3000007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E12" s="2">
         <v>13</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -10731,13 +10763,13 @@
         <v>3000008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E13" s="2">
         <v>13</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -10759,13 +10791,13 @@
         <v>3000009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E14" s="2">
         <v>13</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -10787,13 +10819,13 @@
         <v>3000010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E15" s="2">
         <v>13</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -10815,13 +10847,13 @@
         <v>3000011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E16" s="2">
         <v>13</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -10843,13 +10875,13 @@
         <v>3000012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E17" s="2">
         <v>13</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -10871,13 +10903,13 @@
         <v>3000013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E18" s="2">
         <v>13</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -10899,13 +10931,13 @@
         <v>3000014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E19" s="2">
         <v>13</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -10927,13 +10959,13 @@
         <v>3000015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E20" s="2">
         <v>13</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -10955,13 +10987,13 @@
         <v>3000016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E21" s="2">
         <v>13</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -10983,13 +11015,13 @@
         <v>3000017</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E22" s="2">
         <v>13</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -11011,13 +11043,13 @@
         <v>3000018</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E23" s="2">
         <v>13</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -11039,13 +11071,13 @@
         <v>3000019</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E24" s="2">
         <v>13</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -11067,13 +11099,13 @@
         <v>3000020</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E25" s="2">
         <v>13</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -11095,13 +11127,13 @@
         <v>3000021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E26" s="2">
         <v>13</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -11123,13 +11155,13 @@
         <v>3000022</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E27" s="2">
         <v>13</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -11151,13 +11183,13 @@
         <v>3000023</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E28" s="2">
         <v>13</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -11179,13 +11211,13 @@
         <v>3000024</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E29" s="2">
         <v>13</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -11207,13 +11239,13 @@
         <v>3000025</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E30" s="2">
         <v>13</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -11235,13 +11267,13 @@
         <v>3000026</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E31" s="2">
         <v>13</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -11263,13 +11295,13 @@
         <v>3000027</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E32" s="2">
         <v>13</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -11291,13 +11323,13 @@
         <v>3000028</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E33" s="2">
         <v>13</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -11319,13 +11351,13 @@
         <v>3000029</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E34" s="2">
         <v>13</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -11347,13 +11379,13 @@
         <v>3000030</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E35" s="2">
         <v>13</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -11375,13 +11407,13 @@
         <v>3000031</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E36" s="2">
         <v>13</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -11403,13 +11435,13 @@
         <v>3000032</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E37" s="2">
         <v>13</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G37" s="2">
         <v>1</v>
@@ -11431,13 +11463,13 @@
         <v>3000033</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E38" s="2">
         <v>13</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G38" s="2">
         <v>1</v>
@@ -11459,13 +11491,13 @@
         <v>3000034</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E39" s="2">
         <v>13</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -11487,13 +11519,13 @@
         <v>3000035</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E40" s="2">
         <v>13</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -11515,13 +11547,13 @@
         <v>3000036</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E41" s="2">
         <v>13</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -11543,13 +11575,13 @@
         <v>3000037</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E42" s="2">
         <v>13</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -11571,13 +11603,13 @@
         <v>3000038</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E43" s="2">
         <v>13</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -11599,13 +11631,13 @@
         <v>3000039</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E44" s="2">
         <v>13</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -11627,13 +11659,13 @@
         <v>3000040</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E45" s="2">
         <v>13</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G45" s="2">
         <v>1</v>
@@ -11655,13 +11687,13 @@
         <v>3000041</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E46" s="2">
         <v>13</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -11683,13 +11715,13 @@
         <v>3000042</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E47" s="2">
         <v>13</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -11711,13 +11743,13 @@
         <v>3000043</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E48" s="2">
         <v>13</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -11739,13 +11771,13 @@
         <v>3000044</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E49" s="2">
         <v>13</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -11767,13 +11799,13 @@
         <v>3000045</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E50" s="2">
         <v>13</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -11795,13 +11827,13 @@
         <v>3000046</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E51" s="2">
         <v>13</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -11823,13 +11855,13 @@
         <v>3000047</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E52" s="2">
         <v>13</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -11851,13 +11883,13 @@
         <v>3000048</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E53" s="2">
         <v>13</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G53" s="2">
         <v>1</v>
@@ -12016,13 +12048,13 @@
         <v>40000051</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E7" s="2">
         <v>14</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -12048,13 +12080,13 @@
         <v>40000052</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E8" s="2">
         <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -12080,13 +12112,13 @@
         <v>40000053</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E9" s="2">
         <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -12112,13 +12144,13 @@
         <v>40000054</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="E10" s="2">
         <v>14</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -12144,13 +12176,13 @@
         <v>40000055</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E11" s="2">
         <v>14</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -12176,13 +12208,13 @@
         <v>40000056</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E12" s="2">
         <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -12208,13 +12240,13 @@
         <v>40000057</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E13" s="2">
         <v>14</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -12240,13 +12272,13 @@
         <v>40000058</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E14" s="2">
         <v>14</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -12272,13 +12304,13 @@
         <v>40000059</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E15" s="2">
         <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -12304,13 +12336,13 @@
         <v>40000060</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E16" s="2">
         <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -12336,13 +12368,13 @@
         <v>40000061</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E17" s="2">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -12368,13 +12400,13 @@
         <v>40000062</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E18" s="2">
         <v>14</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -12400,13 +12432,13 @@
         <v>40000063</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E19" s="2">
         <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -12432,13 +12464,13 @@
         <v>40000064</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E20" s="2">
         <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -12464,13 +12496,13 @@
         <v>40000065</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E21" s="2">
         <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -12496,13 +12528,13 @@
         <v>40000066</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E22" s="2">
         <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -12528,13 +12560,13 @@
         <v>40000067</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E23" s="2">
         <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -12560,13 +12592,13 @@
         <v>40000068</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E24" s="2">
         <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -12592,13 +12624,13 @@
         <v>40000069</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E25" s="2">
         <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -12624,13 +12656,13 @@
         <v>40000070</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E26" s="2">
         <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -12656,13 +12688,13 @@
         <v>40000071</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E27" s="2">
         <v>14</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -12688,13 +12720,13 @@
         <v>40000072</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E28" s="2">
         <v>14</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -12720,13 +12752,13 @@
         <v>40000073</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E29" s="2">
         <v>14</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -12752,13 +12784,13 @@
         <v>40000074</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E30" s="2">
         <v>14</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -12784,13 +12816,13 @@
         <v>40000075</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E31" s="2">
         <v>14</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -12816,13 +12848,13 @@
         <v>40000076</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E32" s="2">
         <v>14</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -12848,13 +12880,13 @@
         <v>40000077</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E33" s="2">
         <v>14</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -12880,13 +12912,13 @@
         <v>40000078</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E34" s="2">
         <v>14</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -12912,13 +12944,13 @@
         <v>40000079</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E35" s="2">
         <v>14</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -12944,13 +12976,13 @@
         <v>40000080</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E36" s="2">
         <v>14</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -12976,13 +13008,13 @@
         <v>40000081</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E37" s="2">
         <v>14</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G37" s="2">
         <v>1</v>
@@ -13008,13 +13040,13 @@
         <v>40000082</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E38" s="2">
         <v>14</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G38" s="2">
         <v>1</v>
@@ -13040,13 +13072,13 @@
         <v>40000083</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E39" s="2">
         <v>14</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -13072,13 +13104,13 @@
         <v>40000084</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="E40" s="2">
         <v>14</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -13104,13 +13136,13 @@
         <v>40000085</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E41" s="2">
         <v>14</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -13136,13 +13168,13 @@
         <v>40000086</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E42" s="2">
         <v>14</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -13168,13 +13200,13 @@
         <v>40000087</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E43" s="2">
         <v>14</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -13200,13 +13232,13 @@
         <v>40000088</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E44" s="2">
         <v>14</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -13232,13 +13264,13 @@
         <v>40000089</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E45" s="2">
         <v>14</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G45" s="2">
         <v>1</v>
@@ -13264,13 +13296,13 @@
         <v>40000090</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E46" s="2">
         <v>14</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -13296,13 +13328,13 @@
         <v>40000091</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E47" s="2">
         <v>14</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -13328,13 +13360,13 @@
         <v>40000092</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E48" s="2">
         <v>14</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -13360,13 +13392,13 @@
         <v>40000093</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E49" s="2">
         <v>14</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -13392,13 +13424,13 @@
         <v>40000094</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E50" s="2">
         <v>14</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -13424,13 +13456,13 @@
         <v>40000095</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E51" s="2">
         <v>14</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -13456,13 +13488,13 @@
         <v>40000096</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E52" s="2">
         <v>14</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -13488,13 +13520,13 @@
         <v>40000097</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E53" s="2">
         <v>14</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G53" s="2">
         <v>1</v>
@@ -13520,13 +13552,13 @@
         <v>40000098</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E54" s="2">
         <v>14</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G54" s="2">
         <v>1</v>
@@ -13552,13 +13584,13 @@
         <v>40000099</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E55" s="2">
         <v>14</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G55" s="2">
         <v>1</v>
@@ -13584,13 +13616,13 @@
         <v>40000100</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E56" s="2">
         <v>14</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G56" s="2">
         <v>1</v>
@@ -13616,13 +13648,13 @@
         <v>40000101</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E57" s="2">
         <v>14</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G57" s="2">
         <v>1</v>
@@ -13648,13 +13680,13 @@
         <v>40000102</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E58" s="2">
         <v>14</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G58" s="2">
         <v>1</v>
@@ -13680,13 +13712,13 @@
         <v>40000103</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E59" s="2">
         <v>14</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G59" s="2">
         <v>1</v>
@@ -13712,13 +13744,13 @@
         <v>40000104</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E60" s="2">
         <v>14</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G60" s="2">
         <v>1</v>
@@ -13744,13 +13776,13 @@
         <v>40000105</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E61" s="7">
         <v>14</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G61" s="7">
         <v>1</v>
@@ -13777,13 +13809,13 @@
         <v>40000106</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E62" s="2">
         <v>14</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G62" s="2">
         <v>1</v>
@@ -13810,13 +13842,13 @@
         <v>40000107</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E63" s="2">
         <v>14</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G63" s="2">
         <v>1</v>
@@ -13843,13 +13875,13 @@
         <v>40000108</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E64" s="2">
         <v>14</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G64" s="2">
         <v>1</v>
@@ -13876,13 +13908,13 @@
         <v>40000109</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E65" s="2">
         <v>14</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G65" s="2">
         <v>1</v>
@@ -13909,13 +13941,13 @@
         <v>40000110</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E66" s="2">
         <v>14</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G66" s="2">
         <v>1</v>
@@ -13942,13 +13974,13 @@
         <v>40000111</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="E67" s="2">
         <v>14</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G67" s="2">
         <v>1</v>
@@ -13975,13 +14007,13 @@
         <v>40000112</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E68" s="2">
         <v>14</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G68" s="2">
         <v>1</v>
@@ -14008,13 +14040,13 @@
         <v>40000113</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E69" s="2">
         <v>14</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G69" s="2">
         <v>1</v>
@@ -14041,13 +14073,13 @@
         <v>40000114</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E70" s="2">
         <v>14</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G70" s="2">
         <v>1</v>
@@ -14074,13 +14106,13 @@
         <v>40000115</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E71" s="2">
         <v>14</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G71" s="2">
         <v>1</v>
@@ -14107,13 +14139,13 @@
         <v>40000116</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E72" s="2">
         <v>14</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G72" s="2">
         <v>1</v>
@@ -14140,13 +14172,13 @@
         <v>40000117</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E73" s="2">
         <v>14</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G73" s="2">
         <v>1</v>
@@ -14173,13 +14205,13 @@
         <v>40000118</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E74" s="2">
         <v>14</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G74" s="2">
         <v>1</v>
@@ -14206,13 +14238,13 @@
         <v>40000119</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E75" s="2">
         <v>14</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G75" s="2">
         <v>1</v>
@@ -14239,13 +14271,13 @@
         <v>40000120</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E76" s="2">
         <v>14</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G76" s="2">
         <v>1</v>
@@ -14272,13 +14304,13 @@
         <v>40000121</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E77" s="2">
         <v>14</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G77" s="2">
         <v>1</v>
@@ -14305,13 +14337,13 @@
         <v>40000122</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="E78" s="2">
         <v>14</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G78" s="2">
         <v>1</v>
@@ -14338,13 +14370,13 @@
         <v>40000123</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E79" s="2">
         <v>14</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G79" s="2">
         <v>1</v>
@@ -14371,13 +14403,13 @@
         <v>40000124</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E80" s="2">
         <v>14</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G80" s="2">
         <v>1</v>
@@ -14404,13 +14436,13 @@
         <v>40000125</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E81" s="2">
         <v>14</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G81" s="2">
         <v>1</v>
@@ -14436,13 +14468,13 @@
         <v>40000126</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E82" s="2">
         <v>14</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G82" s="2">
         <v>1</v>
@@ -14468,13 +14500,13 @@
         <v>40000127</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E83" s="2">
         <v>14</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G83" s="2">
         <v>1</v>
@@ -14500,13 +14532,13 @@
         <v>40000128</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E84" s="2">
         <v>14</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G84" s="2">
         <v>1</v>
@@ -14532,13 +14564,13 @@
         <v>40000129</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E85" s="2">
         <v>14</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G85" s="2">
         <v>1</v>
@@ -14564,13 +14596,13 @@
         <v>40000130</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="E86" s="2">
         <v>14</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G86" s="2">
         <v>1</v>
@@ -14596,13 +14628,13 @@
         <v>40000131</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E87" s="2">
         <v>14</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G87" s="2">
         <v>1</v>
@@ -14628,13 +14660,13 @@
         <v>40000132</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E88" s="2">
         <v>14</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G88" s="2">
         <v>1</v>
@@ -14660,13 +14692,13 @@
         <v>40000133</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="E89" s="2">
         <v>14</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G89" s="2">
         <v>1</v>
@@ -14692,13 +14724,13 @@
         <v>40000134</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E90" s="2">
         <v>14</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G90" s="2">
         <v>1</v>
@@ -14724,13 +14756,13 @@
         <v>40000135</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E91" s="2">
         <v>14</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G91" s="2">
         <v>1</v>
@@ -14756,13 +14788,13 @@
         <v>40000136</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E92" s="2">
         <v>14</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G92" s="2">
         <v>1</v>
@@ -14788,13 +14820,13 @@
         <v>40000137</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E93" s="2">
         <v>14</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G93" s="2">
         <v>1</v>
@@ -14820,13 +14852,13 @@
         <v>40000138</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="E94" s="2">
         <v>14</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G94" s="2">
         <v>1</v>
@@ -14852,13 +14884,13 @@
         <v>40000139</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E95" s="2">
         <v>14</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G95" s="2">
         <v>1</v>
@@ -15023,13 +15055,13 @@
         <v>50000001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E6" s="2">
         <v>5</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -15055,13 +15087,13 @@
         <v>50000002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E7" s="2">
         <v>5</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -15087,13 +15119,13 @@
         <v>50000003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E8" s="2">
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -15119,13 +15151,13 @@
         <v>50000004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="E9" s="2">
         <v>5</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -15151,13 +15183,13 @@
         <v>50000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E10" s="2">
         <v>5</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -15183,13 +15215,13 @@
         <v>50000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="E11" s="2">
         <v>5</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -15215,13 +15247,13 @@
         <v>50000007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E12" s="2">
         <v>5</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -15247,13 +15279,13 @@
         <v>50000008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="E13" s="2">
         <v>5</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -15279,13 +15311,13 @@
         <v>50000009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="E14" s="2">
         <v>5</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -15311,13 +15343,13 @@
         <v>50000010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E15" s="2">
         <v>5</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -15343,13 +15375,13 @@
         <v>50000011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E16" s="2">
         <v>5</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -15375,13 +15407,13 @@
         <v>50000012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E17" s="2">
         <v>5</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -15407,13 +15439,13 @@
         <v>50000013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E18" s="2">
         <v>5</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -15439,13 +15471,13 @@
         <v>50000014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E19" s="2">
         <v>5</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -15471,13 +15503,13 @@
         <v>50000015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E20" s="2">
         <v>5</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -15503,13 +15535,13 @@
         <v>50000016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="E21" s="2">
         <v>5</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -15535,13 +15567,13 @@
         <v>50000017</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="E22" s="2">
         <v>5</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -15567,13 +15599,13 @@
         <v>50000018</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E23" s="2">
         <v>5</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -15599,13 +15631,13 @@
         <v>50000019</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E24" s="2">
         <v>5</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -15631,13 +15663,13 @@
         <v>50000020</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="E25" s="2">
         <v>5</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -15663,13 +15695,13 @@
         <v>50000021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="E26" s="2">
         <v>5</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -15695,13 +15727,13 @@
         <v>50000022</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E27" s="2">
         <v>5</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -15727,13 +15759,13 @@
         <v>50000023</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="E28" s="2">
         <v>5</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -15759,13 +15791,13 @@
         <v>50000024</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="E29" s="2">
         <v>5</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -15791,13 +15823,13 @@
         <v>50000025</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E30" s="2">
         <v>5</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -15823,13 +15855,13 @@
         <v>50000026</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="E31" s="2">
         <v>5</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -15855,13 +15887,13 @@
         <v>50000027</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E32" s="2">
         <v>5</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -15887,13 +15919,13 @@
         <v>50000028</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="E33" s="2">
         <v>5</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -15919,13 +15951,13 @@
         <v>50000029</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="E34" s="2">
         <v>5</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -15951,13 +15983,13 @@
         <v>50000030</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="E35" s="2">
         <v>5</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -15983,13 +16015,13 @@
         <v>50000031</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="E36" s="2">
         <v>5</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -16015,13 +16047,13 @@
         <v>50000032</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E37" s="2">
         <v>5</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="G37" s="2">
         <v>1</v>
@@ -16047,13 +16079,13 @@
         <v>50000033</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E38" s="2">
         <v>5</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="G38" s="2">
         <v>1</v>
@@ -16079,13 +16111,13 @@
         <v>50000034</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="E39" s="2">
         <v>5</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -16111,13 +16143,13 @@
         <v>50000035</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="E40" s="2">
         <v>5</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -16143,13 +16175,13 @@
         <v>50000036</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E41" s="2">
         <v>5</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -16175,13 +16207,13 @@
         <v>50000037</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="E42" s="2">
         <v>5</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -16207,13 +16239,13 @@
         <v>50000038</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E43" s="2">
         <v>5</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -16239,13 +16271,13 @@
         <v>50000039</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E44" s="2">
         <v>5</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -16271,13 +16303,13 @@
         <v>50000040</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E45" s="2">
         <v>5</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="G45" s="2">
         <v>1</v>
@@ -16303,13 +16335,13 @@
         <v>50000041</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="E46" s="2">
         <v>5</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -16335,13 +16367,13 @@
         <v>50000042</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="E47" s="2">
         <v>5</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -16367,13 +16399,13 @@
         <v>50000043</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="E48" s="2">
         <v>5</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -16399,13 +16431,13 @@
         <v>50000044</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="E49" s="2">
         <v>5</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -16431,13 +16463,13 @@
         <v>50000045</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="E50" s="2">
         <v>5</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -16463,13 +16495,13 @@
         <v>50000046</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="E51" s="2">
         <v>5</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -16495,13 +16527,13 @@
         <v>50000047</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="E52" s="2">
         <v>5</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -16527,13 +16559,13 @@
         <v>50000048</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="E53" s="2">
         <v>5</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="G53" s="2">
         <v>1</v>
@@ -16559,13 +16591,13 @@
         <v>50000049</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E54" s="2">
         <v>5</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="G54" s="2">
         <v>1</v>
@@ -16591,13 +16623,13 @@
         <v>50000050</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="E55" s="2">
         <v>5</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="G55" s="2">
         <v>1</v>
@@ -16623,13 +16655,13 @@
         <v>50000051</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="E56" s="2">
         <v>5</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="G56" s="2">
         <v>1</v>
@@ -16655,13 +16687,13 @@
         <v>50000052</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="E57" s="2">
         <v>5</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="G57" s="2">
         <v>1</v>
@@ -16687,13 +16719,13 @@
         <v>50000053</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="E58" s="2">
         <v>5</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="G58" s="2">
         <v>1</v>
@@ -16719,13 +16751,13 @@
         <v>50000054</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E59" s="2">
         <v>5</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="G59" s="2">
         <v>1</v>
@@ -16751,13 +16783,13 @@
         <v>50000055</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="E60" s="2">
         <v>5</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="G60" s="2">
         <v>1</v>
@@ -16783,13 +16815,13 @@
         <v>50000056</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="E61" s="2">
         <v>5</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="G61" s="2">
         <v>1</v>
@@ -16815,13 +16847,13 @@
         <v>50000057</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E62" s="2">
         <v>5</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="G62" s="2">
         <v>1</v>
@@ -16847,13 +16879,13 @@
         <v>50000058</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="E63" s="2">
         <v>5</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="G63" s="2">
         <v>1</v>
@@ -16879,13 +16911,13 @@
         <v>50000059</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="E64" s="2">
         <v>5</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="G64" s="2">
         <v>1</v>
@@ -16911,13 +16943,13 @@
         <v>50000060</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="E65" s="2">
         <v>5</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="G65" s="2">
         <v>1</v>
@@ -16943,13 +16975,13 @@
         <v>50000061</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="E66" s="2">
         <v>5</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="G66" s="2">
         <v>1</v>
@@ -16975,13 +17007,13 @@
         <v>50000062</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="E67" s="2">
         <v>5</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="G67" s="2">
         <v>1</v>
@@ -17007,13 +17039,13 @@
         <v>50000063</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="E68" s="2">
         <v>5</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="G68" s="2">
         <v>1</v>
@@ -17039,13 +17071,13 @@
         <v>50000064</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="E69" s="2">
         <v>5</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="G69" s="2">
         <v>1</v>
@@ -17071,13 +17103,13 @@
         <v>50000065</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="E70" s="2">
         <v>5</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="G70" s="2">
         <v>1</v>
@@ -17103,13 +17135,13 @@
         <v>50000066</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="E71" s="2">
         <v>5</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="G71" s="2">
         <v>1</v>
@@ -17135,13 +17167,13 @@
         <v>50000067</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="E72" s="2">
         <v>5</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="G72" s="2">
         <v>1</v>
@@ -17167,13 +17199,13 @@
         <v>50000068</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="E73" s="2">
         <v>5</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="G73" s="2">
         <v>1</v>
@@ -17199,13 +17231,13 @@
         <v>50000069</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="E74" s="2">
         <v>5</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="G74" s="2">
         <v>1</v>
@@ -17231,13 +17263,13 @@
         <v>50000070</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="E75" s="2">
         <v>5</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="G75" s="2">
         <v>1</v>
@@ -17263,13 +17295,13 @@
         <v>50000071</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="E76" s="2">
         <v>5</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="G76" s="2">
         <v>1</v>
@@ -17295,13 +17327,13 @@
         <v>50000072</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E77" s="2">
         <v>5</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="G77" s="2">
         <v>1</v>
@@ -17327,13 +17359,13 @@
         <v>50000073</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="E78" s="2">
         <v>5</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="G78" s="2">
         <v>1</v>
@@ -17359,13 +17391,13 @@
         <v>50000074</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="E79" s="2">
         <v>5</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="G79" s="2">
         <v>1</v>
@@ -17391,13 +17423,13 @@
         <v>50000075</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="E80" s="2">
         <v>5</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="G80" s="2">
         <v>1</v>
@@ -17423,13 +17455,13 @@
         <v>50000076</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="E81" s="2">
         <v>5</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="G81" s="2">
         <v>1</v>
@@ -17455,13 +17487,13 @@
         <v>50000077</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="E82" s="2">
         <v>5</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="G82" s="2">
         <v>1</v>
@@ -17487,13 +17519,13 @@
         <v>50000078</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="E83" s="2">
         <v>5</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="G83" s="2">
         <v>1</v>
@@ -17519,13 +17551,13 @@
         <v>50000079</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E84" s="2">
         <v>5</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="G84" s="2">
         <v>1</v>
@@ -17551,13 +17583,13 @@
         <v>50000080</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="E85" s="2">
         <v>5</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="G85" s="2">
         <v>1</v>
@@ -17583,13 +17615,13 @@
         <v>50000081</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="E86" s="2">
         <v>5</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="G86" s="2">
         <v>1</v>
@@ -17615,13 +17647,13 @@
         <v>50000082</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E87" s="2">
         <v>5</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="G87" s="2">
         <v>1</v>
@@ -17647,13 +17679,13 @@
         <v>50000083</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="E88" s="2">
         <v>5</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="G88" s="2">
         <v>1</v>
@@ -17679,13 +17711,13 @@
         <v>50000084</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="E89" s="2">
         <v>5</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="G89" s="2">
         <v>1</v>
@@ -17711,13 +17743,13 @@
         <v>50000085</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="E90" s="2">
         <v>5</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="G90" s="2">
         <v>1</v>
@@ -17743,13 +17775,13 @@
         <v>50000086</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="E91" s="2">
         <v>5</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="G91" s="2">
         <v>1</v>
@@ -17775,13 +17807,13 @@
         <v>50000087</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="E92" s="2">
         <v>5</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="G92" s="2">
         <v>1</v>
@@ -17807,13 +17839,13 @@
         <v>50000088</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="E93" s="2">
         <v>5</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="G93" s="2">
         <v>1</v>
@@ -17839,13 +17871,13 @@
         <v>50000089</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="E94" s="2">
         <v>5</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="G94" s="2">
         <v>1</v>
@@ -17871,13 +17903,13 @@
         <v>50000090</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E95" s="2">
         <v>5</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="G95" s="2">
         <v>1</v>
@@ -17903,13 +17935,13 @@
         <v>50000091</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E96" s="2">
         <v>5</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="G96" s="2">
         <v>1</v>
@@ -17935,13 +17967,13 @@
         <v>50000092</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E97" s="2">
         <v>5</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="G97" s="2">
         <v>1</v>
@@ -17967,13 +17999,13 @@
         <v>50000093</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E98" s="2">
         <v>5</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="G98" s="2">
         <v>1</v>
@@ -17999,13 +18031,13 @@
         <v>50000094</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="E99" s="2">
         <v>5</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="G99" s="2">
         <v>1</v>
@@ -18031,13 +18063,13 @@
         <v>50000095</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="E100" s="2">
         <v>5</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="G100" s="2">
         <v>1</v>
@@ -18063,13 +18095,13 @@
         <v>50000096</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="E101" s="2">
         <v>5</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="G101" s="2">
         <v>1</v>
@@ -18095,13 +18127,13 @@
         <v>50000097</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="E102" s="2">
         <v>5</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="G102" s="2">
         <v>1</v>
@@ -18127,13 +18159,13 @@
         <v>50000098</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="E103" s="2">
         <v>5</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="G103" s="2">
         <v>1</v>
@@ -18159,13 +18191,13 @@
         <v>50000099</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="E104" s="2">
         <v>5</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="G104" s="2">
         <v>1</v>
@@ -18191,13 +18223,13 @@
         <v>50000100</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="E105" s="2">
         <v>5</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="G105" s="2">
         <v>1</v>
@@ -18223,13 +18255,13 @@
         <v>50000101</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="E106" s="2">
         <v>5</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="G106" s="2">
         <v>1</v>
@@ -18255,13 +18287,13 @@
         <v>50000102</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="E107" s="2">
         <v>5</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="G107" s="2">
         <v>1</v>
@@ -18287,13 +18319,13 @@
         <v>50000103</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="E108" s="2">
         <v>5</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="G108" s="2">
         <v>1</v>
@@ -18319,13 +18351,13 @@
         <v>50000104</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="E109" s="2">
         <v>5</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="G109" s="2">
         <v>1</v>
@@ -18490,13 +18522,13 @@
         <v>180001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="E6" s="2">
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -18516,13 +18548,13 @@
         <v>180002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="E7" s="2">
         <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -18542,13 +18574,13 @@
         <v>180003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="E8" s="2">
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -18568,13 +18600,13 @@
         <v>180004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="E9" s="2">
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -18594,13 +18626,13 @@
         <v>180005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="E10" s="2">
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -18620,13 +18652,13 @@
         <v>180006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="E11" s="2">
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -18648,13 +18680,13 @@
         <v>180007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="E12" s="2">
         <v>18</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -18676,13 +18708,13 @@
         <v>180008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="E13" s="2">
         <v>18</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -18704,13 +18736,13 @@
         <v>180009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E14" s="2">
         <v>18</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -18732,13 +18764,13 @@
         <v>180010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="E15" s="2">
         <v>18</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -18760,13 +18792,13 @@
         <v>180011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E16" s="2">
         <v>18</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -18788,13 +18820,13 @@
         <v>180012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="E17" s="2">
         <v>18</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -18816,13 +18848,13 @@
         <v>180013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="E18" s="2">
         <v>18</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -18844,13 +18876,13 @@
         <v>180014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="E19" s="2">
         <v>18</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -18872,13 +18904,13 @@
         <v>180015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="E20" s="2">
         <v>18</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -18900,13 +18932,13 @@
         <v>180016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="E21" s="2">
         <v>18</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -18928,13 +18960,13 @@
         <v>180017</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="E22" s="2">
         <v>18</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -18956,13 +18988,13 @@
         <v>180018</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="E23" s="2">
         <v>18</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -18984,13 +19016,13 @@
         <v>180019</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="E24" s="2">
         <v>18</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -19012,13 +19044,13 @@
         <v>180020</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="E25" s="2">
         <v>18</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -19040,13 +19072,13 @@
         <v>180021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="E26" s="2">
         <v>18</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -19073,13 +19105,13 @@
         <v>180030</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="E28" s="2">
         <v>18</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -19101,13 +19133,13 @@
         <v>180031</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="E29" s="2">
         <v>18</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="G29" s="3">
         <v>1</v>
@@ -19127,13 +19159,13 @@
         <v>180032</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="E30" s="2">
         <v>18</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="G30" s="3">
         <v>1</v>
@@ -19153,13 +19185,13 @@
         <v>180033</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="E31" s="2">
         <v>18</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="G31" s="3">
         <v>1</v>
@@ -19179,13 +19211,13 @@
         <v>180034</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="E32" s="2">
         <v>18</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="G32" s="3">
         <v>1</v>
@@ -19351,13 +19383,13 @@
         <v>190001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="E6" s="2">
         <v>19</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -19377,13 +19409,13 @@
         <v>190002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E7" s="2">
         <v>19</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -19403,13 +19435,13 @@
         <v>190003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="E8" s="2">
         <v>19</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -19429,13 +19461,13 @@
         <v>190004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="E9" s="2">
         <v>19</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -19455,13 +19487,13 @@
         <v>190005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="E10" s="2">
         <v>19</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -19481,13 +19513,13 @@
         <v>190006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="E11" s="2">
         <v>19</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -5624,6 +5624,9 @@
       <c r="J25" s="3">
         <v>7</v>
       </c>
+      <c r="K25" s="3">
+        <v>500</v>
+      </c>
       <c r="L25" s="3">
         <v>0</v>
       </c>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -856,7 +856,7 @@
     <t>分解金装获取，金装升阶材料</t>
   </si>
   <si>
-    <t>天赋书</t>
+    <t>天赋秘籍</t>
   </si>
   <si>
     <t>天赋经验+500</t>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -436,10 +436,10 @@
     <t>1002</t>
   </si>
   <si>
-    <t>刺杀剑术</t>
-  </si>
-  <si>
-    <t>学习或者升级战士技能刺杀剑术</t>
+    <t>穿刺剑术</t>
+  </si>
+  <si>
+    <t>学习或者升级战士技能穿刺剑术</t>
   </si>
   <si>
     <t>20</t>
@@ -448,10 +448,10 @@
     <t>1003</t>
   </si>
   <si>
-    <t>半月弯刀</t>
-  </si>
-  <si>
-    <t>学习或者升级战士技能半月弯刀</t>
+    <t>圆月弯刀</t>
+  </si>
+  <si>
+    <t>学习或者升级战士技能圆月弯刀</t>
   </si>
   <si>
     <t>30</t>
@@ -460,10 +460,10 @@
     <t>1004</t>
   </si>
   <si>
-    <t>野蛮撞击</t>
-  </si>
-  <si>
-    <t>学习或者升级战士技能野蛮撞击</t>
+    <t>蛮力撞击</t>
+  </si>
+  <si>
+    <t>学习或者升级战士技能蛮力撞击</t>
   </si>
   <si>
     <t>100000</t>
@@ -496,10 +496,10 @@
     <t>1007</t>
   </si>
   <si>
-    <t>烈火剑法</t>
-  </si>
-  <si>
-    <t>学习或者升级战士技能烈火剑法</t>
+    <t>火焰剑法</t>
+  </si>
+  <si>
+    <t>学习或者升级战士技能火焰剑法</t>
   </si>
   <si>
     <t>70</t>
@@ -520,19 +520,19 @@
     <t>1009</t>
   </si>
   <si>
-    <t>开天斩</t>
-  </si>
-  <si>
-    <t>学习或者升级战士技能开天斩</t>
+    <t>开天辟地</t>
+  </si>
+  <si>
+    <t>学习或者升级战士技能开天辟地</t>
   </si>
   <si>
     <t>1010</t>
   </si>
   <si>
-    <t>彻地钉</t>
-  </si>
-  <si>
-    <t>学习或者升级战士技能彻地钉</t>
+    <t>地刺术</t>
+  </si>
+  <si>
+    <t>学习或者升级战士技能地刺术</t>
   </si>
   <si>
     <t>1011</t>
@@ -547,37 +547,37 @@
     <t>2001</t>
   </si>
   <si>
-    <t>小火球</t>
-  </si>
-  <si>
-    <t>学习或者升级法师技能小火球</t>
+    <t>火球术</t>
+  </si>
+  <si>
+    <t>学习或者升级法师技能火球术</t>
   </si>
   <si>
     <t>2002</t>
   </si>
   <si>
-    <t>雷电术</t>
-  </si>
-  <si>
-    <t>学习或者升级法师技能雷电术</t>
+    <t>神雷术</t>
+  </si>
+  <si>
+    <t>学习或者升级法师技能神雷术</t>
   </si>
   <si>
     <t>2003</t>
   </si>
   <si>
-    <t>火墙</t>
-  </si>
-  <si>
-    <t>学习或者升级法师技能火墙</t>
+    <t>火墙术</t>
+  </si>
+  <si>
+    <t>学习或者升级法师技能火墙术</t>
   </si>
   <si>
     <t>2004</t>
   </si>
   <si>
-    <t>爆裂火焰</t>
-  </si>
-  <si>
-    <t>学习或者升级法师技能爆裂火焰</t>
+    <t>火焰术</t>
+  </si>
+  <si>
+    <t>学习或者升级法师技能火焰术</t>
   </si>
   <si>
     <t>2005</t>
@@ -601,28 +601,28 @@
     <t>2007</t>
   </si>
   <si>
-    <t>冰咆哮</t>
-  </si>
-  <si>
-    <t>学习或者升级法师技能冰咆哮</t>
+    <t>冰冻术</t>
+  </si>
+  <si>
+    <t>学习或者升级法师技能冰冻术</t>
   </si>
   <si>
     <t>2008</t>
   </si>
   <si>
-    <t>瞬息移动</t>
-  </si>
-  <si>
-    <t>学习或者升级法师技能瞬息移动ing</t>
+    <t>闪烁术</t>
+  </si>
+  <si>
+    <t>学习或者升级法师技能闪烁术</t>
   </si>
   <si>
     <t>2009</t>
   </si>
   <si>
-    <t>流星火雨</t>
-  </si>
-  <si>
-    <t>学习或者升级法师技能流星火雨</t>
+    <t>火雨术</t>
+  </si>
+  <si>
+    <t>学习或者升级法师技能火雨术</t>
   </si>
   <si>
     <t>2010</t>
@@ -646,37 +646,37 @@
     <t>3001</t>
   </si>
   <si>
-    <t>治疗术</t>
-  </si>
-  <si>
-    <t>学习或者升级道士技能治疗术</t>
+    <t>治疗道法</t>
+  </si>
+  <si>
+    <t>学习或者升级道士技能治疗道法</t>
   </si>
   <si>
     <t>3002</t>
   </si>
   <si>
-    <t>火符术</t>
-  </si>
-  <si>
-    <t>学习或者升级道士技能火符术</t>
+    <t>火符道法</t>
+  </si>
+  <si>
+    <t>学习或者升级道士技能火符道法</t>
   </si>
   <si>
     <t>3003</t>
   </si>
   <si>
-    <t>施毒术</t>
-  </si>
-  <si>
-    <t>学习或者升级道士技能施毒术</t>
+    <t>毒咒道法</t>
+  </si>
+  <si>
+    <t>学习或者升级道士技能施毒道法</t>
   </si>
   <si>
     <t>3004</t>
   </si>
   <si>
-    <t>召唤骷髅</t>
-  </si>
-  <si>
-    <t>学习或者升级道士技能召唤骷髅</t>
+    <t>召唤金刚</t>
+  </si>
+  <si>
+    <t>学习或者升级道士技能召唤金刚</t>
   </si>
   <si>
     <t>3005</t>
@@ -700,28 +700,28 @@
     <t>3007</t>
   </si>
   <si>
-    <t>召唤神兽</t>
-  </si>
-  <si>
-    <t>学习或者升级道士技能召唤神兽</t>
+    <t>召唤魔兽</t>
+  </si>
+  <si>
+    <t>学习或者升级道士技能召唤魔兽</t>
   </si>
   <si>
     <t>3008</t>
   </si>
   <si>
-    <t>隐身术</t>
-  </si>
-  <si>
-    <t>学习或者升级道士技能隐身术</t>
+    <t>隐身道法</t>
+  </si>
+  <si>
+    <t>学习或者升级道士技能隐身道法</t>
   </si>
   <si>
     <t>3009</t>
   </si>
   <si>
-    <t>召唤月灵</t>
-  </si>
-  <si>
-    <t>学习或者升级道士技能召唤月灵</t>
+    <t>召唤护法</t>
+  </si>
+  <si>
+    <t>学习或者升级道士技能召唤护法</t>
   </si>
   <si>
     <t>3010</t>
@@ -1447,78 +1447,6 @@
     <t>战神之靴</t>
   </si>
   <si>
-    <t>恶魔之杖</t>
-  </si>
-  <si>
-    <t>恶魔之衣</t>
-  </si>
-  <si>
-    <t>恶魔之头</t>
-  </si>
-  <si>
-    <t>恶魔之链</t>
-  </si>
-  <si>
-    <t>恶魔之镯</t>
-  </si>
-  <si>
-    <t>恶魔之戒</t>
-  </si>
-  <si>
-    <t>恶魔之带</t>
-  </si>
-  <si>
-    <t>恶魔之靴</t>
-  </si>
-  <si>
-    <t>幽灵之剑</t>
-  </si>
-  <si>
-    <t>幽灵之袍</t>
-  </si>
-  <si>
-    <t>幽灵之头</t>
-  </si>
-  <si>
-    <t>幽灵之链</t>
-  </si>
-  <si>
-    <t>幽灵之镯</t>
-  </si>
-  <si>
-    <t>幽灵之戒</t>
-  </si>
-  <si>
-    <t>幽灵之带</t>
-  </si>
-  <si>
-    <t>幽灵之靴</t>
-  </si>
-  <si>
-    <t>圣战之刃</t>
-  </si>
-  <si>
-    <t>圣战之甲</t>
-  </si>
-  <si>
-    <t>圣战之头</t>
-  </si>
-  <si>
-    <t>圣战之链</t>
-  </si>
-  <si>
-    <t>圣战之镯</t>
-  </si>
-  <si>
-    <t>圣战之戒</t>
-  </si>
-  <si>
-    <t>圣战之带</t>
-  </si>
-  <si>
-    <t>圣战之靴</t>
-  </si>
-  <si>
     <t>法神之杖</t>
   </si>
   <si>
@@ -1543,28 +1471,100 @@
     <t>法神之靴</t>
   </si>
   <si>
-    <t>天尊之剑</t>
-  </si>
-  <si>
-    <t>天尊之袍</t>
-  </si>
-  <si>
-    <t>天尊之头</t>
-  </si>
-  <si>
-    <t>天尊之链</t>
-  </si>
-  <si>
-    <t>天尊之镯</t>
-  </si>
-  <si>
-    <t>天尊之戒</t>
-  </si>
-  <si>
-    <t>天尊之带</t>
-  </si>
-  <si>
-    <t>天尊之靴</t>
+    <t>道神之剑</t>
+  </si>
+  <si>
+    <t>道神之袍</t>
+  </si>
+  <si>
+    <t>道神之头</t>
+  </si>
+  <si>
+    <t>道神之链</t>
+  </si>
+  <si>
+    <t>道神之镯</t>
+  </si>
+  <si>
+    <t>道神之戒</t>
+  </si>
+  <si>
+    <t>道神之带</t>
+  </si>
+  <si>
+    <t>道神之靴</t>
+  </si>
+  <si>
+    <t>战尊之刃</t>
+  </si>
+  <si>
+    <t>战尊之甲</t>
+  </si>
+  <si>
+    <t>战尊之头</t>
+  </si>
+  <si>
+    <t>战尊之链</t>
+  </si>
+  <si>
+    <t>战尊之镯</t>
+  </si>
+  <si>
+    <t>战尊之戒</t>
+  </si>
+  <si>
+    <t>战尊之带</t>
+  </si>
+  <si>
+    <t>战尊之靴</t>
+  </si>
+  <si>
+    <t>法尊之杖</t>
+  </si>
+  <si>
+    <t>法尊之衣</t>
+  </si>
+  <si>
+    <t>法尊之头</t>
+  </si>
+  <si>
+    <t>法尊之链</t>
+  </si>
+  <si>
+    <t>法尊之镯</t>
+  </si>
+  <si>
+    <t>法尊之戒</t>
+  </si>
+  <si>
+    <t>法尊之带</t>
+  </si>
+  <si>
+    <t>法尊之靴</t>
+  </si>
+  <si>
+    <t>道尊之剑</t>
+  </si>
+  <si>
+    <t>道尊之袍</t>
+  </si>
+  <si>
+    <t>道尊之头</t>
+  </si>
+  <si>
+    <t>道尊之链</t>
+  </si>
+  <si>
+    <t>道尊之镯</t>
+  </si>
+  <si>
+    <t>道尊之戒</t>
+  </si>
+  <si>
+    <t>道尊之带</t>
+  </si>
+  <si>
+    <t>道尊之靴</t>
   </si>
   <si>
     <t>触龙之心</t>
@@ -2542,25 +2542,25 @@
     <t>极.财富契约</t>
   </si>
   <si>
-    <t>麻痹戒指</t>
+    <t>定身神戒</t>
   </si>
   <si>
     <t>激活或者升级对应神戒</t>
   </si>
   <si>
-    <t>护身戒指</t>
-  </si>
-  <si>
-    <t>复活戒指</t>
-  </si>
-  <si>
-    <t>防御戒指</t>
-  </si>
-  <si>
-    <t>传送神戒</t>
-  </si>
-  <si>
-    <t>隐身戒指</t>
+    <t>护体神戒</t>
+  </si>
+  <si>
+    <t>重生神戒</t>
+  </si>
+  <si>
+    <t>防御神戒</t>
+  </si>
+  <si>
+    <t>闪烁神戒</t>
+  </si>
+  <si>
+    <t>隐身神戒</t>
   </si>
 </sst>
 </file>
@@ -2771,12 +2771,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3242,7 +3242,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3258,6 +3258,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -3700,7 +3701,7 @@
       <c r="C6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="11" t="s">
         <v>23</v>
       </c>
       <c r="E6" s="3" t="s">
@@ -3735,7 +3736,7 @@
       <c r="C7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E7" s="3" t="s">
@@ -3770,7 +3771,7 @@
       <c r="C8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="1" t="s">
         <v>34</v>
       </c>
       <c r="E8" s="3" t="s">
@@ -3805,7 +3806,7 @@
       <c r="C9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="11" t="s">
         <v>38</v>
       </c>
       <c r="E9" s="3" t="s">
@@ -3840,7 +3841,7 @@
       <c r="C10" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="1" t="s">
         <v>43</v>
       </c>
       <c r="E10" s="3" t="s">
@@ -3875,7 +3876,7 @@
       <c r="C11" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="1" t="s">
         <v>46</v>
       </c>
       <c r="E11" s="3" t="s">
@@ -3910,7 +3911,7 @@
       <c r="C12" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="1" t="s">
         <v>50</v>
       </c>
       <c r="E12" s="3" t="s">
@@ -3942,10 +3943,10 @@
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:13">
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E13" s="3" t="s">
@@ -3960,7 +3961,7 @@
       <c r="H13" s="3">
         <v>99999999</v>
       </c>
-      <c r="I13" s="11" t="s">
+      <c r="I13" s="12" t="s">
         <v>56</v>
       </c>
       <c r="J13" s="3">
@@ -3977,10 +3978,10 @@
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:13">
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E14" s="3" t="s">
@@ -3995,7 +3996,7 @@
       <c r="H14" s="3">
         <v>99999999</v>
       </c>
-      <c r="I14" s="11" t="s">
+      <c r="I14" s="12" t="s">
         <v>56</v>
       </c>
       <c r="J14" s="3">
@@ -4012,10 +4013,10 @@
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:13">
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="1" t="s">
         <v>61</v>
       </c>
       <c r="E15" s="3" t="s">
@@ -4030,7 +4031,7 @@
       <c r="H15" s="3">
         <v>99999999</v>
       </c>
-      <c r="I15" s="11" t="s">
+      <c r="I15" s="12" t="s">
         <v>56</v>
       </c>
       <c r="J15" s="3">
@@ -4047,10 +4048,10 @@
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:13">
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="1" t="s">
         <v>64</v>
       </c>
       <c r="E16" s="3" t="s">
@@ -4065,7 +4066,7 @@
       <c r="H16" s="3">
         <v>99999999</v>
       </c>
-      <c r="I16" s="11" t="s">
+      <c r="I16" s="12" t="s">
         <v>56</v>
       </c>
       <c r="J16" s="3">
@@ -4085,7 +4086,7 @@
       <c r="C18" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="11" t="s">
         <v>67</v>
       </c>
       <c r="E18" s="3" t="s">
@@ -4120,7 +4121,7 @@
       <c r="C19" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="1" t="s">
         <v>70</v>
       </c>
       <c r="E19" s="3" t="s">
@@ -4155,7 +4156,7 @@
       <c r="C20" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="1" t="s">
         <v>73</v>
       </c>
       <c r="E20" s="3" t="s">
@@ -4190,7 +4191,7 @@
       <c r="C21" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="1" t="s">
         <v>76</v>
       </c>
       <c r="E21" s="3" t="s">
@@ -4225,7 +4226,7 @@
       <c r="C22" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="1" t="s">
         <v>79</v>
       </c>
       <c r="E22" s="3" t="s">
@@ -4260,7 +4261,7 @@
       <c r="C23" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" s="11" t="s">
         <v>82</v>
       </c>
       <c r="E23" s="3" t="s">
@@ -4295,7 +4296,7 @@
       <c r="C24" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="1" t="s">
         <v>85</v>
       </c>
       <c r="E24" s="3" t="s">
@@ -4327,10 +4328,10 @@
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:13">
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="1" t="s">
         <v>88</v>
       </c>
       <c r="E25" s="3" t="s">
@@ -4345,7 +4346,7 @@
       <c r="H25" s="3">
         <v>99999999</v>
       </c>
-      <c r="I25" s="11" t="s">
+      <c r="I25" s="12" t="s">
         <v>56</v>
       </c>
       <c r="J25" s="3">
@@ -4362,10 +4363,10 @@
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:13">
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="1" t="s">
         <v>91</v>
       </c>
       <c r="E26" s="3" t="s">
@@ -4380,7 +4381,7 @@
       <c r="H26" s="3">
         <v>99999999</v>
       </c>
-      <c r="I26" s="11" t="s">
+      <c r="I26" s="12" t="s">
         <v>56</v>
       </c>
       <c r="J26" s="3">
@@ -4397,10 +4398,10 @@
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:13">
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="1" t="s">
         <v>94</v>
       </c>
       <c r="E27" s="3" t="s">
@@ -4415,7 +4416,7 @@
       <c r="H27" s="3">
         <v>99999999</v>
       </c>
-      <c r="I27" s="11" t="s">
+      <c r="I27" s="12" t="s">
         <v>56</v>
       </c>
       <c r="J27" s="3">
@@ -4432,10 +4433,10 @@
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:13">
-      <c r="C28" s="11" t="s">
+      <c r="C28" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="1" t="s">
         <v>97</v>
       </c>
       <c r="E28" s="3" t="s">
@@ -4450,7 +4451,7 @@
       <c r="H28" s="3">
         <v>99999999</v>
       </c>
-      <c r="I28" s="11" t="s">
+      <c r="I28" s="12" t="s">
         <v>56</v>
       </c>
       <c r="J28" s="3">
@@ -4470,7 +4471,7 @@
       <c r="C30" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D30" s="1" t="s">
         <v>100</v>
       </c>
       <c r="E30" s="3" t="s">
@@ -4505,7 +4506,7 @@
       <c r="C31" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="D31" s="11" t="s">
         <v>103</v>
       </c>
       <c r="E31" s="3" t="s">
@@ -4540,7 +4541,7 @@
       <c r="C32" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" s="1" t="s">
         <v>106</v>
       </c>
       <c r="E32" s="3" t="s">
@@ -4575,7 +4576,7 @@
       <c r="C33" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D33" s="1" t="s">
         <v>109</v>
       </c>
       <c r="E33" s="3" t="s">
@@ -4610,7 +4611,7 @@
       <c r="C34" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D34" s="1" t="s">
         <v>112</v>
       </c>
       <c r="E34" s="3" t="s">
@@ -4645,7 +4646,7 @@
       <c r="C35" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D35" s="11" t="s">
         <v>115</v>
       </c>
       <c r="E35" s="3" t="s">
@@ -4680,7 +4681,7 @@
       <c r="C36" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D36" s="1" t="s">
         <v>118</v>
       </c>
       <c r="E36" s="3" t="s">
@@ -4712,10 +4713,10 @@
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:13">
-      <c r="C37" s="11" t="s">
+      <c r="C37" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="D37" s="1" t="s">
         <v>121</v>
       </c>
       <c r="E37" s="3" t="s">
@@ -4730,7 +4731,7 @@
       <c r="H37" s="3">
         <v>99999999</v>
       </c>
-      <c r="I37" s="11" t="s">
+      <c r="I37" s="12" t="s">
         <v>56</v>
       </c>
       <c r="J37" s="3">
@@ -4747,10 +4748,10 @@
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:13">
-      <c r="C38" s="11" t="s">
+      <c r="C38" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D38" s="1" t="s">
         <v>124</v>
       </c>
       <c r="E38" s="3" t="s">
@@ -4765,7 +4766,7 @@
       <c r="H38" s="3">
         <v>99999999</v>
       </c>
-      <c r="I38" s="11" t="s">
+      <c r="I38" s="12" t="s">
         <v>56</v>
       </c>
       <c r="J38" s="3">
@@ -4782,10 +4783,10 @@
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:13">
-      <c r="C39" s="11" t="s">
+      <c r="C39" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="D39" s="1" t="s">
         <v>127</v>
       </c>
       <c r="E39" s="3" t="s">
@@ -4800,7 +4801,7 @@
       <c r="H39" s="3">
         <v>99999999</v>
       </c>
-      <c r="I39" s="11" t="s">
+      <c r="I39" s="12" t="s">
         <v>56</v>
       </c>
       <c r="J39" s="3">
@@ -4817,10 +4818,10 @@
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:13">
-      <c r="C40" s="11" t="s">
+      <c r="C40" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="D40" s="1" t="s">
         <v>130</v>
       </c>
       <c r="E40" s="3" t="s">
@@ -4835,7 +4836,7 @@
       <c r="H40" s="3">
         <v>99999999</v>
       </c>
-      <c r="I40" s="11" t="s">
+      <c r="I40" s="12" t="s">
         <v>56</v>
       </c>
       <c r="J40" s="3">

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="7"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -673,10 +673,10 @@
     <t>3004</t>
   </si>
   <si>
-    <t>召唤金刚</t>
-  </si>
-  <si>
-    <t>学习或者升级道士技能召唤金刚</t>
+    <t>召唤小兵</t>
+  </si>
+  <si>
+    <t>学习或者升级道士技能召唤小兵</t>
   </si>
   <si>
     <t>3005</t>
@@ -718,10 +718,10 @@
     <t>3009</t>
   </si>
   <si>
-    <t>召唤护法</t>
-  </si>
-  <si>
-    <t>学习或者升级道士技能召唤护法</t>
+    <t>召唤月神</t>
+  </si>
+  <si>
+    <t>学习或者升级道士技能召唤月神</t>
   </si>
   <si>
     <t>3010</t>
@@ -2771,12 +2771,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -344,7 +344,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="739">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1398" uniqueCount="741">
   <si>
     <t>_Id</t>
   </si>
@@ -860,6 +860,12 @@
   </si>
   <si>
     <t>天赋经验+500</t>
+  </si>
+  <si>
+    <t>改造石</t>
+  </si>
+  <si>
+    <t>装备改造材料</t>
   </si>
   <si>
     <t>图鉴碎片</t>
@@ -4871,7 +4877,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:M75"/>
+  <dimension ref="C3:M76"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="3"/>
@@ -5635,53 +5641,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C27" s="3">
-        <v>4101</v>
-      </c>
-      <c r="D27" s="3" t="s">
+    <row r="26" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C26" s="3">
+        <v>4021</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="E27" s="3">
-        <v>5</v>
-      </c>
-      <c r="F27" s="3" t="s">
+      <c r="E26" s="3">
+        <v>5</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="G27" s="3">
-        <v>1</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="G26" s="3">
+        <v>1</v>
+      </c>
+      <c r="H26" s="3">
         <v>9999999</v>
       </c>
-      <c r="I27" s="3">
-        <v>0</v>
-      </c>
-      <c r="J27" s="3">
-        <v>5</v>
-      </c>
-      <c r="L27" s="3">
-        <v>0</v>
-      </c>
-      <c r="M27" s="3">
-        <v>0</v>
-      </c>
+      <c r="I26" s="3">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3">
+        <v>7</v>
+      </c>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3">
+        <v>0</v>
+      </c>
+      <c r="M26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
     </row>
     <row r="28" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C28" s="3">
-        <v>4102</v>
+        <v>4101</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>174</v>
@@ -5713,7 +5720,7 @@
     </row>
     <row r="29" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C29" s="3">
-        <v>4103</v>
+        <v>4102</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>176</v>
@@ -5722,7 +5729,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>149</v>
+        <v>177</v>
       </c>
       <c r="G29" s="3">
         <v>1</v>
@@ -5745,10 +5752,10 @@
     </row>
     <row r="30" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C30" s="3">
-        <v>4104</v>
+        <v>4103</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E30" s="3">
         <v>5</v>
@@ -5777,10 +5784,10 @@
     </row>
     <row r="31" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C31" s="3">
-        <v>4105</v>
+        <v>4104</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E31" s="3">
         <v>5</v>
@@ -5809,16 +5816,16 @@
     </row>
     <row r="32" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C32" s="3">
-        <v>4106</v>
+        <v>4105</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E32" s="3">
         <v>5</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>178</v>
+        <v>149</v>
       </c>
       <c r="G32" s="3">
         <v>1</v>
@@ -5841,7 +5848,7 @@
     </row>
     <row r="33" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C33" s="3">
-        <v>4107</v>
+        <v>4106</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>179</v>
@@ -5873,7 +5880,7 @@
     </row>
     <row r="34" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C34" s="3">
-        <v>4108</v>
+        <v>4107</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>181</v>
@@ -5905,7 +5912,7 @@
     </row>
     <row r="35" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C35" s="3">
-        <v>4109</v>
+        <v>4108</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>183</v>
@@ -5937,7 +5944,7 @@
     </row>
     <row r="36" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C36" s="3">
-        <v>4110</v>
+        <v>4109</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>185</v>
@@ -5969,7 +5976,7 @@
     </row>
     <row r="37" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C37" s="3">
-        <v>4111</v>
+        <v>4110</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>187</v>
@@ -5999,41 +6006,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C39" s="3">
-        <v>4201</v>
-      </c>
-      <c r="D39" s="3" t="s">
+    <row r="38" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C38" s="3">
+        <v>4111</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="E39" s="3">
-        <v>5</v>
-      </c>
-      <c r="F39" s="3" t="s">
+      <c r="E38" s="3">
+        <v>5</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="G39" s="3">
-        <v>1</v>
-      </c>
-      <c r="H39" s="3">
-        <v>2000000</v>
-      </c>
-      <c r="I39" s="3">
-        <v>0</v>
-      </c>
-      <c r="J39" s="3">
-        <v>5</v>
-      </c>
-      <c r="L39" s="3">
-        <v>4002</v>
-      </c>
-      <c r="M39" s="3">
-        <v>1000</v>
+      <c r="G38" s="3">
+        <v>1</v>
+      </c>
+      <c r="H38" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I38" s="3">
+        <v>0</v>
+      </c>
+      <c r="J38" s="3">
+        <v>5</v>
+      </c>
+      <c r="L38" s="3">
+        <v>0</v>
+      </c>
+      <c r="M38" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="40" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C40" s="3">
-        <v>4202</v>
+        <v>4201</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>191</v>
@@ -6048,7 +6055,7 @@
         <v>1</v>
       </c>
       <c r="H40" s="3">
-        <v>99999</v>
+        <v>2000000</v>
       </c>
       <c r="I40" s="3">
         <v>0</v>
@@ -6057,50 +6064,47 @@
         <v>5</v>
       </c>
       <c r="L40" s="3">
-        <v>0</v>
+        <v>4002</v>
       </c>
       <c r="M40" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C42" s="3">
-        <v>6101</v>
-      </c>
-      <c r="D42" s="3" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="41" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C41" s="3">
+        <v>4202</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="E42" s="3">
-        <v>7</v>
-      </c>
-      <c r="F42" s="3" t="s">
+      <c r="E41" s="3">
+        <v>5</v>
+      </c>
+      <c r="F41" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="G42" s="3">
-        <v>1</v>
-      </c>
-      <c r="H42" s="3">
-        <v>99999</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3">
-        <v>4</v>
-      </c>
-      <c r="K42" s="3">
-        <v>1</v>
-      </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3">
+      <c r="G41" s="3">
+        <v>1</v>
+      </c>
+      <c r="H41" s="3">
+        <v>99999</v>
+      </c>
+      <c r="I41" s="3">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3">
+        <v>5</v>
+      </c>
+      <c r="L41" s="3">
+        <v>0</v>
+      </c>
+      <c r="M41" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="43" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C43" s="3">
-        <v>6102</v>
+        <v>6101</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>195</v>
@@ -6124,7 +6128,7 @@
         <v>4</v>
       </c>
       <c r="K43" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -6135,7 +6139,7 @@
     </row>
     <row r="44" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C44" s="3">
-        <v>6103</v>
+        <v>6102</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>197</v>
@@ -6159,7 +6163,7 @@
         <v>4</v>
       </c>
       <c r="K44" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -6170,7 +6174,7 @@
     </row>
     <row r="45" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C45" s="3">
-        <v>6104</v>
+        <v>6103</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>199</v>
@@ -6194,7 +6198,7 @@
         <v>4</v>
       </c>
       <c r="K45" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
@@ -6203,9 +6207,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" customHeight="1" spans="3:13">
+    <row r="46" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C46" s="3">
-        <v>6105</v>
+        <v>6104</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>201</v>
@@ -6229,7 +6233,7 @@
         <v>4</v>
       </c>
       <c r="K46" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L46" s="3">
         <v>0</v>
@@ -6238,9 +6242,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" s="3" customFormat="1" customHeight="1" spans="3:13">
+    <row r="47" customHeight="1" spans="3:13">
       <c r="C47" s="3">
-        <v>6106</v>
+        <v>6105</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>203</v>
@@ -6264,7 +6268,7 @@
         <v>4</v>
       </c>
       <c r="K47" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -6273,15 +6277,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" customHeight="1" spans="3:13">
+    <row r="48" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C48" s="3">
-        <v>7101</v>
+        <v>6106</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>205</v>
       </c>
       <c r="E48" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>206</v>
@@ -6299,7 +6303,7 @@
         <v>4</v>
       </c>
       <c r="K48" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L48" s="3">
         <v>0</v>
@@ -6310,7 +6314,7 @@
     </row>
     <row r="49" customHeight="1" spans="3:13">
       <c r="C49" s="3">
-        <v>7102</v>
+        <v>7101</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>207</v>
@@ -6334,7 +6338,7 @@
         <v>4</v>
       </c>
       <c r="K49" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
@@ -6345,7 +6349,7 @@
     </row>
     <row r="50" customHeight="1" spans="3:13">
       <c r="C50" s="3">
-        <v>7103</v>
+        <v>7102</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>209</v>
@@ -6369,7 +6373,7 @@
         <v>4</v>
       </c>
       <c r="K50" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L50" s="3">
         <v>0</v>
@@ -6380,7 +6384,7 @@
     </row>
     <row r="51" customHeight="1" spans="3:13">
       <c r="C51" s="3">
-        <v>7104</v>
+        <v>7103</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>211</v>
@@ -6404,7 +6408,7 @@
         <v>4</v>
       </c>
       <c r="K51" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L51" s="3">
         <v>0</v>
@@ -6415,7 +6419,7 @@
     </row>
     <row r="52" customHeight="1" spans="3:13">
       <c r="C52" s="3">
-        <v>7105</v>
+        <v>7104</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>213</v>
@@ -6439,7 +6443,7 @@
         <v>4</v>
       </c>
       <c r="K52" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -6450,7 +6454,7 @@
     </row>
     <row r="53" customHeight="1" spans="3:13">
       <c r="C53" s="3">
-        <v>7107</v>
+        <v>7105</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>215</v>
@@ -6474,7 +6478,7 @@
         <v>4</v>
       </c>
       <c r="K53" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L53" s="3">
         <v>0</v>
@@ -6483,41 +6487,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C57" s="3">
-        <v>8001</v>
-      </c>
-      <c r="D57" s="3" t="s">
+    <row r="54" customHeight="1" spans="3:13">
+      <c r="C54" s="3">
+        <v>7107</v>
+      </c>
+      <c r="D54" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="E57" s="3">
-        <v>5</v>
-      </c>
-      <c r="F57" s="3" t="s">
+      <c r="E54" s="3">
+        <v>8</v>
+      </c>
+      <c r="F54" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="G57" s="3">
-        <v>1</v>
-      </c>
-      <c r="H57" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3">
-        <v>6</v>
-      </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
-      <c r="M57" s="3">
+      <c r="G54" s="3">
+        <v>1</v>
+      </c>
+      <c r="H54" s="3">
+        <v>99999</v>
+      </c>
+      <c r="I54" s="3">
+        <v>0</v>
+      </c>
+      <c r="J54" s="3">
+        <v>4</v>
+      </c>
+      <c r="K54" s="3">
+        <v>6</v>
+      </c>
+      <c r="L54" s="3">
+        <v>0</v>
+      </c>
+      <c r="M54" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="58" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C58" s="3">
-        <v>8002</v>
+        <v>8001</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>219</v>
@@ -6526,7 +6533,7 @@
         <v>5</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G58" s="3">
         <v>1</v>
@@ -6549,16 +6556,16 @@
     </row>
     <row r="59" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C59" s="3">
-        <v>8003</v>
+        <v>8002</v>
       </c>
       <c r="D59" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E59" s="3">
+        <v>5</v>
+      </c>
+      <c r="F59" s="3" t="s">
         <v>220</v>
-      </c>
-      <c r="E59" s="3">
-        <v>5</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>218</v>
       </c>
       <c r="G59" s="3">
         <v>1</v>
@@ -6581,16 +6588,16 @@
     </row>
     <row r="60" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C60" s="3">
-        <v>8004</v>
+        <v>8003</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E60" s="3">
         <v>5</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G60" s="3">
         <v>1</v>
@@ -6613,16 +6620,16 @@
     </row>
     <row r="61" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C61" s="3">
-        <v>8005</v>
+        <v>8004</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E61" s="3">
         <v>5</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G61" s="3">
         <v>1</v>
@@ -6645,16 +6652,16 @@
     </row>
     <row r="62" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C62" s="3">
-        <v>8006</v>
+        <v>8005</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E62" s="3">
         <v>5</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G62" s="3">
         <v>1</v>
@@ -6677,16 +6684,16 @@
     </row>
     <row r="63" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C63" s="3">
-        <v>8007</v>
+        <v>8006</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E63" s="3">
         <v>5</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G63" s="3">
         <v>1</v>
@@ -6709,16 +6716,16 @@
     </row>
     <row r="64" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C64" s="3">
-        <v>8008</v>
+        <v>8007</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E64" s="3">
         <v>5</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G64" s="3">
         <v>1</v>
@@ -6741,16 +6748,16 @@
     </row>
     <row r="65" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C65" s="3">
-        <v>8009</v>
+        <v>8008</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E65" s="3">
         <v>5</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G65" s="3">
         <v>1</v>
@@ -6773,16 +6780,16 @@
     </row>
     <row r="66" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C66" s="3">
-        <v>8010</v>
+        <v>8009</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E66" s="3">
         <v>5</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G66" s="3">
         <v>1</v>
@@ -6803,41 +6810,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C68" s="3">
-        <v>8101</v>
-      </c>
-      <c r="D68" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="E68" s="3">
-        <v>5</v>
-      </c>
-      <c r="F68" s="3" t="s">
+    <row r="67" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C67" s="3">
+        <v>8010</v>
+      </c>
+      <c r="D67" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="G68" s="3">
-        <v>1</v>
-      </c>
-      <c r="H68" s="3">
+      <c r="E67" s="3">
+        <v>5</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="G67" s="3">
+        <v>1</v>
+      </c>
+      <c r="H67" s="3">
         <v>9999999</v>
       </c>
-      <c r="I68" s="3">
-        <v>0</v>
-      </c>
-      <c r="J68" s="3">
-        <v>7</v>
-      </c>
-      <c r="L68" s="3">
-        <v>0</v>
-      </c>
-      <c r="M68" s="3">
+      <c r="I67" s="3">
+        <v>0</v>
+      </c>
+      <c r="J67" s="3">
+        <v>6</v>
+      </c>
+      <c r="L67" s="3">
+        <v>0</v>
+      </c>
+      <c r="M67" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="69" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C69" s="3">
-        <v>8102</v>
+        <v>8101</v>
       </c>
       <c r="D69" s="10" t="s">
         <v>230</v>
@@ -6846,7 +6853,7 @@
         <v>5</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G69" s="3">
         <v>1</v>
@@ -6869,16 +6876,16 @@
     </row>
     <row r="70" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C70" s="3">
-        <v>8103</v>
+        <v>8102</v>
       </c>
       <c r="D70" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="E70" s="3">
+        <v>5</v>
+      </c>
+      <c r="F70" s="3" t="s">
         <v>231</v>
-      </c>
-      <c r="E70" s="3">
-        <v>5</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>229</v>
       </c>
       <c r="G70" s="3">
         <v>1</v>
@@ -6901,16 +6908,16 @@
     </row>
     <row r="71" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C71" s="3">
-        <v>8104</v>
+        <v>8103</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E71" s="3">
         <v>5</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G71" s="3">
         <v>1</v>
@@ -6933,16 +6940,16 @@
     </row>
     <row r="72" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C72" s="3">
-        <v>8105</v>
+        <v>8104</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E72" s="3">
         <v>5</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G72" s="3">
         <v>1</v>
@@ -6965,16 +6972,16 @@
     </row>
     <row r="73" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C73" s="3">
-        <v>8106</v>
+        <v>8105</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E73" s="3">
         <v>5</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G73" s="3">
         <v>1</v>
@@ -6997,16 +7004,16 @@
     </row>
     <row r="74" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C74" s="3">
-        <v>8107</v>
+        <v>8106</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E74" s="3">
         <v>5</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G74" s="3">
         <v>1</v>
@@ -7029,16 +7036,16 @@
     </row>
     <row r="75" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C75" s="3">
-        <v>8108</v>
+        <v>8107</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E75" s="3">
         <v>5</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G75" s="3">
         <v>1</v>
@@ -7056,6 +7063,38 @@
         <v>0</v>
       </c>
       <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C76" s="3">
+        <v>8108</v>
+      </c>
+      <c r="D76" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="E76" s="3">
+        <v>5</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="G76" s="3">
+        <v>1</v>
+      </c>
+      <c r="H76" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I76" s="3">
+        <v>0</v>
+      </c>
+      <c r="J76" s="3">
+        <v>7</v>
+      </c>
+      <c r="L76" s="3">
+        <v>0</v>
+      </c>
+      <c r="M76" s="3">
         <v>0</v>
       </c>
     </row>
@@ -7203,13 +7242,13 @@
         <v>1999001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E6" s="2">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -7231,13 +7270,13 @@
         <v>1999002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E7" s="2">
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -7259,13 +7298,13 @@
         <v>1999003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E8" s="2">
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -7287,13 +7326,13 @@
         <v>1999004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E9" s="2">
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -7315,13 +7354,13 @@
         <v>1999005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E10" s="2">
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -7343,13 +7382,13 @@
         <v>1999006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E11" s="2">
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -7376,13 +7415,13 @@
         <v>1999989</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E13" s="2">
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -7404,13 +7443,13 @@
         <v>1999990</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E14" s="2">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -7432,13 +7471,13 @@
         <v>1999991</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E15" s="2">
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -7460,13 +7499,13 @@
         <v>1999992</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E16" s="2">
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -7488,13 +7527,13 @@
         <v>1999993</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E17" s="2">
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -7516,13 +7555,13 @@
         <v>1999994</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E18" s="2">
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -7544,13 +7583,13 @@
         <v>1999995</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E19" s="2">
         <v>11</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -7572,13 +7611,13 @@
         <v>1999996</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E20" s="2">
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -7600,13 +7639,13 @@
         <v>1999997</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E21" s="2">
         <v>11</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -7628,13 +7667,13 @@
         <v>2000000</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E22" s="2">
         <v>11</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -7656,13 +7695,13 @@
         <v>2000001</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E23" s="2">
         <v>11</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -7684,13 +7723,13 @@
         <v>2000002</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E24" s="2">
         <v>11</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -7712,13 +7751,13 @@
         <v>2000003</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E25" s="2">
         <v>11</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -7740,13 +7779,13 @@
         <v>2000004</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E26" s="2">
         <v>11</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -7768,13 +7807,13 @@
         <v>2000005</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E27" s="2">
         <v>11</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -7796,13 +7835,13 @@
         <v>2000006</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E28" s="2">
         <v>11</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -7824,13 +7863,13 @@
         <v>2000007</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E29" s="2">
         <v>11</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -7852,13 +7891,13 @@
         <v>2000008</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E30" s="2">
         <v>11</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -7880,13 +7919,13 @@
         <v>2000009</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E31" s="2">
         <v>11</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -7908,13 +7947,13 @@
         <v>2000010</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E32" s="2">
         <v>11</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -7936,13 +7975,13 @@
         <v>2000011</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E33" s="2">
         <v>11</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -7964,13 +8003,13 @@
         <v>2000012</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E34" s="2">
         <v>11</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -7992,13 +8031,13 @@
         <v>2000013</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E35" s="2">
         <v>11</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -8032,13 +8071,13 @@
         <v>2000100</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E39" s="2">
         <v>11</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -8060,13 +8099,13 @@
         <v>2000101</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E40" s="2">
         <v>11</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -8088,13 +8127,13 @@
         <v>2000102</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E41" s="2">
         <v>11</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -8116,13 +8155,13 @@
         <v>2000103</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E42" s="2">
         <v>11</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -8144,13 +8183,13 @@
         <v>2000104</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E43" s="2">
         <v>11</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -8172,13 +8211,13 @@
         <v>2000105</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E44" s="2">
         <v>11</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -8200,13 +8239,13 @@
         <v>2000106</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E45" s="2">
         <v>11</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G45" s="2">
         <v>1</v>
@@ -8228,13 +8267,13 @@
         <v>2000107</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E46" s="2">
         <v>11</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -8256,13 +8295,13 @@
         <v>2000108</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E47" s="2">
         <v>11</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -8284,13 +8323,13 @@
         <v>2000109</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E48" s="2">
         <v>11</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -8312,13 +8351,13 @@
         <v>2000110</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E49" s="2">
         <v>11</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -8340,13 +8379,13 @@
         <v>2000111</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E50" s="2">
         <v>11</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -8368,13 +8407,13 @@
         <v>2000112</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E51" s="2">
         <v>11</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -8396,13 +8435,13 @@
         <v>2000113</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E52" s="2">
         <v>11</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -8424,13 +8463,13 @@
         <v>2000114</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E53" s="2">
         <v>11</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G53" s="2">
         <v>1</v>
@@ -8452,13 +8491,13 @@
         <v>2000115</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E54" s="2">
         <v>11</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G54" s="2">
         <v>1</v>
@@ -8480,13 +8519,13 @@
         <v>2000116</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E55" s="2">
         <v>11</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G55" s="2">
         <v>1</v>
@@ -8508,13 +8547,13 @@
         <v>2000117</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E56" s="2">
         <v>11</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G56" s="2">
         <v>1</v>
@@ -8536,13 +8575,13 @@
         <v>2000118</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E57" s="2">
         <v>11</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G57" s="2">
         <v>1</v>
@@ -8564,13 +8603,13 @@
         <v>2000119</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E58" s="2">
         <v>11</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G58" s="2">
         <v>1</v>
@@ -8592,13 +8631,13 @@
         <v>2000120</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E59" s="2">
         <v>11</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G59" s="2">
         <v>1</v>
@@ -8620,13 +8659,13 @@
         <v>2000121</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E60" s="2">
         <v>11</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G60" s="2">
         <v>1</v>
@@ -8648,13 +8687,13 @@
         <v>2000122</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E61" s="2">
         <v>11</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G61" s="2">
         <v>1</v>
@@ -8676,13 +8715,13 @@
         <v>2000123</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E62" s="2">
         <v>11</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G62" s="2">
         <v>1</v>
@@ -8704,13 +8743,13 @@
         <v>2000124</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E63" s="2">
         <v>11</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G63" s="2">
         <v>1</v>
@@ -8732,13 +8771,13 @@
         <v>2000125</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E64" s="2">
         <v>11</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G64" s="2">
         <v>1</v>
@@ -8760,13 +8799,13 @@
         <v>2000126</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E65" s="2">
         <v>11</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G65" s="2">
         <v>1</v>
@@ -8788,13 +8827,13 @@
         <v>2000127</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E66" s="2">
         <v>11</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G66" s="2">
         <v>1</v>
@@ -8816,13 +8855,13 @@
         <v>2000128</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E67" s="2">
         <v>11</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G67" s="2">
         <v>1</v>
@@ -8844,13 +8883,13 @@
         <v>2000129</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E68" s="2">
         <v>11</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G68" s="2">
         <v>1</v>
@@ -8872,13 +8911,13 @@
         <v>2000200</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E70" s="2">
         <v>11</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G70" s="2">
         <v>1</v>
@@ -8898,13 +8937,13 @@
         <v>2000201</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E71" s="2">
         <v>11</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G71" s="2">
         <v>1</v>
@@ -8924,13 +8963,13 @@
         <v>2000202</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E72" s="2">
         <v>11</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G72" s="2">
         <v>1</v>
@@ -8950,13 +8989,13 @@
         <v>2000203</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E73" s="2">
         <v>11</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G73" s="2">
         <v>1</v>
@@ -8976,13 +9015,13 @@
         <v>2000204</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E74" s="2">
         <v>11</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G74" s="2">
         <v>1</v>
@@ -9002,13 +9041,13 @@
         <v>2000205</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E75" s="2">
         <v>11</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G75" s="2">
         <v>1</v>
@@ -9028,13 +9067,13 @@
         <v>2000206</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E76" s="2">
         <v>11</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G76" s="2">
         <v>1</v>
@@ -9054,13 +9093,13 @@
         <v>2000207</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E77" s="2">
         <v>11</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G77" s="2">
         <v>1</v>
@@ -9080,13 +9119,13 @@
         <v>2000208</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E78" s="2">
         <v>11</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G78" s="2">
         <v>1</v>
@@ -9106,13 +9145,13 @@
         <v>2000209</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E79" s="2">
         <v>11</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G79" s="2">
         <v>1</v>
@@ -9132,13 +9171,13 @@
         <v>2000210</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E80" s="2">
         <v>11</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G80" s="2">
         <v>1</v>
@@ -9158,13 +9197,13 @@
         <v>2000211</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E81" s="2">
         <v>11</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G81" s="2">
         <v>1</v>
@@ -9184,13 +9223,13 @@
         <v>2000212</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E82" s="2">
         <v>11</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G82" s="2">
         <v>1</v>
@@ -9210,13 +9249,13 @@
         <v>2000213</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E83" s="2">
         <v>11</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G83" s="2">
         <v>1</v>
@@ -9236,13 +9275,13 @@
         <v>2000214</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E84" s="2">
         <v>11</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G84" s="2">
         <v>1</v>
@@ -9262,13 +9301,13 @@
         <v>2000215</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E85" s="2">
         <v>11</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G85" s="2">
         <v>1</v>
@@ -9288,13 +9327,13 @@
         <v>2000216</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E86" s="2">
         <v>11</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G86" s="2">
         <v>1</v>
@@ -9314,13 +9353,13 @@
         <v>2000217</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E87" s="2">
         <v>11</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G87" s="2">
         <v>1</v>
@@ -9340,13 +9379,13 @@
         <v>2000218</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E88" s="2">
         <v>11</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G88" s="2">
         <v>1</v>
@@ -9366,13 +9405,13 @@
         <v>2000219</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E89" s="2">
         <v>11</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G89" s="2">
         <v>1</v>
@@ -9392,13 +9431,13 @@
         <v>2000220</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E90" s="2">
         <v>11</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G90" s="2">
         <v>1</v>
@@ -9418,13 +9457,13 @@
         <v>2000221</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E91" s="2">
         <v>11</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G91" s="2">
         <v>1</v>
@@ -9444,13 +9483,13 @@
         <v>2000222</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E92" s="2">
         <v>11</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G92" s="2">
         <v>1</v>
@@ -9470,13 +9509,13 @@
         <v>2000223</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E93" s="2">
         <v>11</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G93" s="2">
         <v>1</v>
@@ -9496,13 +9535,13 @@
         <v>2000224</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E94" s="2">
         <v>11</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G94" s="2">
         <v>1</v>
@@ -9522,13 +9561,13 @@
         <v>2000225</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E95" s="2">
         <v>11</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G95" s="2">
         <v>1</v>
@@ -9548,13 +9587,13 @@
         <v>2000226</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E96" s="2">
         <v>11</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G96" s="2">
         <v>1</v>
@@ -9574,13 +9613,13 @@
         <v>2000227</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E97" s="2">
         <v>11</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G97" s="2">
         <v>1</v>
@@ -9600,13 +9639,13 @@
         <v>2000228</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E98" s="2">
         <v>11</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G98" s="2">
         <v>1</v>
@@ -9626,13 +9665,13 @@
         <v>2000229</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E99" s="2">
         <v>11</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G99" s="2">
         <v>1</v>
@@ -9652,13 +9691,13 @@
         <v>2000300</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E102" s="2">
         <v>11</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G102" s="2">
         <v>1</v>
@@ -9678,13 +9717,13 @@
         <v>2000301</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E103" s="2">
         <v>11</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G103" s="2">
         <v>1</v>
@@ -9704,13 +9743,13 @@
         <v>2000302</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E104" s="2">
         <v>11</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G104" s="2">
         <v>1</v>
@@ -9730,13 +9769,13 @@
         <v>2000303</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E105" s="2">
         <v>11</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G105" s="2">
         <v>1</v>
@@ -9756,13 +9795,13 @@
         <v>2000304</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E106" s="2">
         <v>11</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G106" s="2">
         <v>1</v>
@@ -9782,13 +9821,13 @@
         <v>2000305</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E107" s="2">
         <v>11</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G107" s="2">
         <v>1</v>
@@ -9808,13 +9847,13 @@
         <v>2000306</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E108" s="2">
         <v>11</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G108" s="2">
         <v>1</v>
@@ -9834,13 +9873,13 @@
         <v>2000307</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E109" s="2">
         <v>11</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G109" s="2">
         <v>1</v>
@@ -9860,13 +9899,13 @@
         <v>2000308</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E110" s="2">
         <v>11</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G110" s="2">
         <v>1</v>
@@ -9886,13 +9925,13 @@
         <v>2000309</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E111" s="2">
         <v>11</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G111" s="2">
         <v>1</v>
@@ -9912,13 +9951,13 @@
         <v>2000310</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E112" s="2">
         <v>11</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G112" s="2">
         <v>1</v>
@@ -9938,13 +9977,13 @@
         <v>2000311</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E113" s="2">
         <v>11</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G113" s="2">
         <v>1</v>
@@ -9964,13 +10003,13 @@
         <v>2000312</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E114" s="2">
         <v>11</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G114" s="2">
         <v>1</v>
@@ -9990,13 +10029,13 @@
         <v>2000313</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E115" s="2">
         <v>11</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G115" s="2">
         <v>1</v>
@@ -10016,13 +10055,13 @@
         <v>2000314</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E116" s="2">
         <v>11</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G116" s="2">
         <v>1</v>
@@ -10042,13 +10081,13 @@
         <v>2000315</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E117" s="2">
         <v>11</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G117" s="2">
         <v>1</v>
@@ -10068,13 +10107,13 @@
         <v>2000316</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E118" s="2">
         <v>11</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G118" s="2">
         <v>1</v>
@@ -10094,13 +10133,13 @@
         <v>2000317</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E119" s="2">
         <v>11</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G119" s="2">
         <v>1</v>
@@ -10120,13 +10159,13 @@
         <v>2000318</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E120" s="2">
         <v>11</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G120" s="2">
         <v>1</v>
@@ -10146,13 +10185,13 @@
         <v>2000319</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E121" s="2">
         <v>11</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G121" s="2">
         <v>1</v>
@@ -10172,13 +10211,13 @@
         <v>2000320</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E122" s="2">
         <v>11</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G122" s="2">
         <v>1</v>
@@ -10198,13 +10237,13 @@
         <v>2000321</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E123" s="2">
         <v>11</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G123" s="2">
         <v>1</v>
@@ -10224,13 +10263,13 @@
         <v>2000322</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E124" s="2">
         <v>11</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G124" s="2">
         <v>1</v>
@@ -10250,13 +10289,13 @@
         <v>2000323</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E125" s="2">
         <v>11</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G125" s="2">
         <v>1</v>
@@ -10276,13 +10315,13 @@
         <v>2000324</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E126" s="2">
         <v>11</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G126" s="2">
         <v>1</v>
@@ -10302,13 +10341,13 @@
         <v>2000325</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E127" s="2">
         <v>11</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G127" s="2">
         <v>1</v>
@@ -10328,13 +10367,13 @@
         <v>2000326</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E128" s="2">
         <v>11</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G128" s="2">
         <v>1</v>
@@ -10354,13 +10393,13 @@
         <v>2000327</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E129" s="2">
         <v>11</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G129" s="2">
         <v>1</v>
@@ -10380,13 +10419,13 @@
         <v>2000328</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E130" s="2">
         <v>11</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G130" s="2">
         <v>1</v>
@@ -10406,13 +10445,13 @@
         <v>2000329</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E131" s="2">
         <v>11</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G131" s="2">
         <v>1</v>
@@ -10571,13 +10610,13 @@
         <v>3000001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E6" s="2">
         <v>13</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -10599,13 +10638,13 @@
         <v>3000002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E7" s="2">
         <v>13</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -10627,13 +10666,13 @@
         <v>3000003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E8" s="2">
         <v>13</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -10655,13 +10694,13 @@
         <v>3000004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E9" s="2">
         <v>13</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -10683,13 +10722,13 @@
         <v>3000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E10" s="2">
         <v>13</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -10711,13 +10750,13 @@
         <v>3000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E11" s="2">
         <v>13</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -10739,13 +10778,13 @@
         <v>3000007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E12" s="2">
         <v>13</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -10767,13 +10806,13 @@
         <v>3000008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E13" s="2">
         <v>13</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -10795,13 +10834,13 @@
         <v>3000009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E14" s="2">
         <v>13</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -10823,13 +10862,13 @@
         <v>3000010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E15" s="2">
         <v>13</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -10851,13 +10890,13 @@
         <v>3000011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E16" s="2">
         <v>13</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -10879,13 +10918,13 @@
         <v>3000012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E17" s="2">
         <v>13</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -10907,13 +10946,13 @@
         <v>3000013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E18" s="2">
         <v>13</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -10935,13 +10974,13 @@
         <v>3000014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E19" s="2">
         <v>13</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -10963,13 +11002,13 @@
         <v>3000015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E20" s="2">
         <v>13</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -10991,13 +11030,13 @@
         <v>3000016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E21" s="2">
         <v>13</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -11019,13 +11058,13 @@
         <v>3000017</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E22" s="2">
         <v>13</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -11047,13 +11086,13 @@
         <v>3000018</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E23" s="2">
         <v>13</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -11075,13 +11114,13 @@
         <v>3000019</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E24" s="2">
         <v>13</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -11103,13 +11142,13 @@
         <v>3000020</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E25" s="2">
         <v>13</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -11131,13 +11170,13 @@
         <v>3000021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E26" s="2">
         <v>13</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -11159,13 +11198,13 @@
         <v>3000022</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E27" s="2">
         <v>13</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -11187,13 +11226,13 @@
         <v>3000023</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E28" s="2">
         <v>13</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -11215,13 +11254,13 @@
         <v>3000024</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E29" s="2">
         <v>13</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -11243,13 +11282,13 @@
         <v>3000025</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E30" s="2">
         <v>13</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -11271,13 +11310,13 @@
         <v>3000026</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E31" s="2">
         <v>13</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -11299,13 +11338,13 @@
         <v>3000027</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E32" s="2">
         <v>13</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -11327,13 +11366,13 @@
         <v>3000028</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E33" s="2">
         <v>13</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -11355,13 +11394,13 @@
         <v>3000029</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E34" s="2">
         <v>13</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -11383,13 +11422,13 @@
         <v>3000030</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E35" s="2">
         <v>13</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -11411,13 +11450,13 @@
         <v>3000031</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E36" s="2">
         <v>13</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -11439,13 +11478,13 @@
         <v>3000032</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E37" s="2">
         <v>13</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G37" s="2">
         <v>1</v>
@@ -11467,13 +11506,13 @@
         <v>3000033</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E38" s="2">
         <v>13</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G38" s="2">
         <v>1</v>
@@ -11495,13 +11534,13 @@
         <v>3000034</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E39" s="2">
         <v>13</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -11523,13 +11562,13 @@
         <v>3000035</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E40" s="2">
         <v>13</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -11551,13 +11590,13 @@
         <v>3000036</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E41" s="2">
         <v>13</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -11579,13 +11618,13 @@
         <v>3000037</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E42" s="2">
         <v>13</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -11607,13 +11646,13 @@
         <v>3000038</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E43" s="2">
         <v>13</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -11635,13 +11674,13 @@
         <v>3000039</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E44" s="2">
         <v>13</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -11663,13 +11702,13 @@
         <v>3000040</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E45" s="2">
         <v>13</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G45" s="2">
         <v>1</v>
@@ -11691,13 +11730,13 @@
         <v>3000041</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E46" s="2">
         <v>13</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -11719,13 +11758,13 @@
         <v>3000042</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E47" s="2">
         <v>13</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -11747,13 +11786,13 @@
         <v>3000043</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E48" s="2">
         <v>13</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -11775,13 +11814,13 @@
         <v>3000044</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E49" s="2">
         <v>13</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -11803,13 +11842,13 @@
         <v>3000045</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E50" s="2">
         <v>13</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -11831,13 +11870,13 @@
         <v>3000046</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E51" s="2">
         <v>13</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -11859,13 +11898,13 @@
         <v>3000047</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E52" s="2">
         <v>13</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -11887,13 +11926,13 @@
         <v>3000048</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E53" s="2">
         <v>13</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G53" s="2">
         <v>1</v>
@@ -12052,13 +12091,13 @@
         <v>40000051</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E7" s="2">
         <v>14</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -12084,13 +12123,13 @@
         <v>40000052</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="E8" s="2">
         <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -12116,13 +12155,13 @@
         <v>40000053</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E9" s="2">
         <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -12148,13 +12187,13 @@
         <v>40000054</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E10" s="2">
         <v>14</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -12180,13 +12219,13 @@
         <v>40000055</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E11" s="2">
         <v>14</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -12212,13 +12251,13 @@
         <v>40000056</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E12" s="2">
         <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -12244,13 +12283,13 @@
         <v>40000057</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E13" s="2">
         <v>14</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -12276,13 +12315,13 @@
         <v>40000058</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E14" s="2">
         <v>14</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -12308,13 +12347,13 @@
         <v>40000059</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E15" s="2">
         <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -12340,13 +12379,13 @@
         <v>40000060</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E16" s="2">
         <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -12372,13 +12411,13 @@
         <v>40000061</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E17" s="2">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -12404,13 +12443,13 @@
         <v>40000062</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E18" s="2">
         <v>14</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -12436,13 +12475,13 @@
         <v>40000063</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E19" s="2">
         <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -12468,13 +12507,13 @@
         <v>40000064</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E20" s="2">
         <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -12500,13 +12539,13 @@
         <v>40000065</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E21" s="2">
         <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -12532,13 +12571,13 @@
         <v>40000066</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E22" s="2">
         <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -12564,13 +12603,13 @@
         <v>40000067</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E23" s="2">
         <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -12596,13 +12635,13 @@
         <v>40000068</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E24" s="2">
         <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -12628,13 +12667,13 @@
         <v>40000069</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E25" s="2">
         <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -12660,13 +12699,13 @@
         <v>40000070</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E26" s="2">
         <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -12692,13 +12731,13 @@
         <v>40000071</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E27" s="2">
         <v>14</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -12724,13 +12763,13 @@
         <v>40000072</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E28" s="2">
         <v>14</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -12756,13 +12795,13 @@
         <v>40000073</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E29" s="2">
         <v>14</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -12788,13 +12827,13 @@
         <v>40000074</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E30" s="2">
         <v>14</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -12820,13 +12859,13 @@
         <v>40000075</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E31" s="2">
         <v>14</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -12852,13 +12891,13 @@
         <v>40000076</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E32" s="2">
         <v>14</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -12884,13 +12923,13 @@
         <v>40000077</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E33" s="2">
         <v>14</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -12916,13 +12955,13 @@
         <v>40000078</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E34" s="2">
         <v>14</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -12948,13 +12987,13 @@
         <v>40000079</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E35" s="2">
         <v>14</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -12980,13 +13019,13 @@
         <v>40000080</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E36" s="2">
         <v>14</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -13012,13 +13051,13 @@
         <v>40000081</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E37" s="2">
         <v>14</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G37" s="2">
         <v>1</v>
@@ -13044,13 +13083,13 @@
         <v>40000082</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="E38" s="2">
         <v>14</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G38" s="2">
         <v>1</v>
@@ -13076,13 +13115,13 @@
         <v>40000083</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E39" s="2">
         <v>14</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -13108,13 +13147,13 @@
         <v>40000084</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E40" s="2">
         <v>14</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -13140,13 +13179,13 @@
         <v>40000085</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E41" s="2">
         <v>14</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -13172,13 +13211,13 @@
         <v>40000086</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E42" s="2">
         <v>14</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -13204,13 +13243,13 @@
         <v>40000087</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E43" s="2">
         <v>14</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -13236,13 +13275,13 @@
         <v>40000088</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E44" s="2">
         <v>14</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -13268,13 +13307,13 @@
         <v>40000089</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E45" s="2">
         <v>14</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G45" s="2">
         <v>1</v>
@@ -13300,13 +13339,13 @@
         <v>40000090</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E46" s="2">
         <v>14</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -13332,13 +13371,13 @@
         <v>40000091</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E47" s="2">
         <v>14</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -13364,13 +13403,13 @@
         <v>40000092</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E48" s="2">
         <v>14</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -13396,13 +13435,13 @@
         <v>40000093</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E49" s="2">
         <v>14</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -13428,13 +13467,13 @@
         <v>40000094</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E50" s="2">
         <v>14</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -13460,13 +13499,13 @@
         <v>40000095</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E51" s="2">
         <v>14</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -13492,13 +13531,13 @@
         <v>40000096</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E52" s="2">
         <v>14</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -13524,13 +13563,13 @@
         <v>40000097</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E53" s="2">
         <v>14</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G53" s="2">
         <v>1</v>
@@ -13556,13 +13595,13 @@
         <v>40000098</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E54" s="2">
         <v>14</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G54" s="2">
         <v>1</v>
@@ -13588,13 +13627,13 @@
         <v>40000099</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E55" s="2">
         <v>14</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G55" s="2">
         <v>1</v>
@@ -13620,13 +13659,13 @@
         <v>40000100</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E56" s="2">
         <v>14</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G56" s="2">
         <v>1</v>
@@ -13652,13 +13691,13 @@
         <v>40000101</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E57" s="2">
         <v>14</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G57" s="2">
         <v>1</v>
@@ -13684,13 +13723,13 @@
         <v>40000102</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E58" s="2">
         <v>14</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G58" s="2">
         <v>1</v>
@@ -13716,13 +13755,13 @@
         <v>40000103</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E59" s="2">
         <v>14</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G59" s="2">
         <v>1</v>
@@ -13748,13 +13787,13 @@
         <v>40000104</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E60" s="2">
         <v>14</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G60" s="2">
         <v>1</v>
@@ -13780,13 +13819,13 @@
         <v>40000105</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E61" s="7">
         <v>14</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G61" s="7">
         <v>1</v>
@@ -13813,13 +13852,13 @@
         <v>40000106</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E62" s="2">
         <v>14</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G62" s="2">
         <v>1</v>
@@ -13846,13 +13885,13 @@
         <v>40000107</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E63" s="2">
         <v>14</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G63" s="2">
         <v>1</v>
@@ -13879,13 +13918,13 @@
         <v>40000108</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E64" s="2">
         <v>14</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G64" s="2">
         <v>1</v>
@@ -13912,13 +13951,13 @@
         <v>40000109</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="E65" s="2">
         <v>14</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G65" s="2">
         <v>1</v>
@@ -13945,13 +13984,13 @@
         <v>40000110</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E66" s="2">
         <v>14</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G66" s="2">
         <v>1</v>
@@ -13978,13 +14017,13 @@
         <v>40000111</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E67" s="2">
         <v>14</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G67" s="2">
         <v>1</v>
@@ -14011,13 +14050,13 @@
         <v>40000112</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E68" s="2">
         <v>14</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G68" s="2">
         <v>1</v>
@@ -14044,13 +14083,13 @@
         <v>40000113</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E69" s="2">
         <v>14</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G69" s="2">
         <v>1</v>
@@ -14077,13 +14116,13 @@
         <v>40000114</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E70" s="2">
         <v>14</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G70" s="2">
         <v>1</v>
@@ -14110,13 +14149,13 @@
         <v>40000115</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E71" s="2">
         <v>14</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G71" s="2">
         <v>1</v>
@@ -14143,13 +14182,13 @@
         <v>40000116</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E72" s="2">
         <v>14</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G72" s="2">
         <v>1</v>
@@ -14176,13 +14215,13 @@
         <v>40000117</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E73" s="2">
         <v>14</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G73" s="2">
         <v>1</v>
@@ -14209,13 +14248,13 @@
         <v>40000118</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E74" s="2">
         <v>14</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G74" s="2">
         <v>1</v>
@@ -14242,13 +14281,13 @@
         <v>40000119</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E75" s="2">
         <v>14</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G75" s="2">
         <v>1</v>
@@ -14275,13 +14314,13 @@
         <v>40000120</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="E76" s="2">
         <v>14</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G76" s="2">
         <v>1</v>
@@ -14308,13 +14347,13 @@
         <v>40000121</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E77" s="2">
         <v>14</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G77" s="2">
         <v>1</v>
@@ -14341,13 +14380,13 @@
         <v>40000122</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E78" s="2">
         <v>14</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G78" s="2">
         <v>1</v>
@@ -14374,13 +14413,13 @@
         <v>40000123</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E79" s="2">
         <v>14</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G79" s="2">
         <v>1</v>
@@ -14407,13 +14446,13 @@
         <v>40000124</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E80" s="2">
         <v>14</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G80" s="2">
         <v>1</v>
@@ -14440,13 +14479,13 @@
         <v>40000125</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E81" s="2">
         <v>14</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G81" s="2">
         <v>1</v>
@@ -14472,13 +14511,13 @@
         <v>40000126</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E82" s="2">
         <v>14</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G82" s="2">
         <v>1</v>
@@ -14504,13 +14543,13 @@
         <v>40000127</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E83" s="2">
         <v>14</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G83" s="2">
         <v>1</v>
@@ -14536,13 +14575,13 @@
         <v>40000128</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="E84" s="2">
         <v>14</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G84" s="2">
         <v>1</v>
@@ -14568,13 +14607,13 @@
         <v>40000129</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E85" s="2">
         <v>14</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G85" s="2">
         <v>1</v>
@@ -14600,13 +14639,13 @@
         <v>40000130</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E86" s="2">
         <v>14</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G86" s="2">
         <v>1</v>
@@ -14632,13 +14671,13 @@
         <v>40000131</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="E87" s="2">
         <v>14</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G87" s="2">
         <v>1</v>
@@ -14664,13 +14703,13 @@
         <v>40000132</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E88" s="2">
         <v>14</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G88" s="2">
         <v>1</v>
@@ -14696,13 +14735,13 @@
         <v>40000133</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E89" s="2">
         <v>14</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G89" s="2">
         <v>1</v>
@@ -14728,13 +14767,13 @@
         <v>40000134</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E90" s="2">
         <v>14</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G90" s="2">
         <v>1</v>
@@ -14760,13 +14799,13 @@
         <v>40000135</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E91" s="2">
         <v>14</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G91" s="2">
         <v>1</v>
@@ -14792,13 +14831,13 @@
         <v>40000136</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="E92" s="2">
         <v>14</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G92" s="2">
         <v>1</v>
@@ -14824,13 +14863,13 @@
         <v>40000137</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E93" s="2">
         <v>14</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G93" s="2">
         <v>1</v>
@@ -14856,13 +14895,13 @@
         <v>40000138</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E94" s="2">
         <v>14</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G94" s="2">
         <v>1</v>
@@ -14888,13 +14927,13 @@
         <v>40000139</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="E95" s="2">
         <v>14</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G95" s="2">
         <v>1</v>
@@ -15059,13 +15098,13 @@
         <v>50000001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E6" s="2">
         <v>5</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -15091,13 +15130,13 @@
         <v>50000002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E7" s="2">
         <v>5</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -15123,13 +15162,13 @@
         <v>50000003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="E8" s="2">
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -15155,13 +15194,13 @@
         <v>50000004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E9" s="2">
         <v>5</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -15187,13 +15226,13 @@
         <v>50000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="E10" s="2">
         <v>5</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -15219,13 +15258,13 @@
         <v>50000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E11" s="2">
         <v>5</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -15251,13 +15290,13 @@
         <v>50000007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="E12" s="2">
         <v>5</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -15283,13 +15322,13 @@
         <v>50000008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="E13" s="2">
         <v>5</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -15315,13 +15354,13 @@
         <v>50000009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E14" s="2">
         <v>5</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -15347,13 +15386,13 @@
         <v>50000010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E15" s="2">
         <v>5</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -15379,13 +15418,13 @@
         <v>50000011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E16" s="2">
         <v>5</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -15411,13 +15450,13 @@
         <v>50000012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E17" s="2">
         <v>5</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -15443,13 +15482,13 @@
         <v>50000013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E18" s="2">
         <v>5</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -15475,13 +15514,13 @@
         <v>50000014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E19" s="2">
         <v>5</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -15507,13 +15546,13 @@
         <v>50000015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="E20" s="2">
         <v>5</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -15539,13 +15578,13 @@
         <v>50000016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="E21" s="2">
         <v>5</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -15571,13 +15610,13 @@
         <v>50000017</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E22" s="2">
         <v>5</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -15603,13 +15642,13 @@
         <v>50000018</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E23" s="2">
         <v>5</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -15635,13 +15674,13 @@
         <v>50000019</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="E24" s="2">
         <v>5</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -15667,13 +15706,13 @@
         <v>50000020</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="E25" s="2">
         <v>5</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -15699,13 +15738,13 @@
         <v>50000021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E26" s="2">
         <v>5</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -15731,13 +15770,13 @@
         <v>50000022</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="E27" s="2">
         <v>5</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -15763,13 +15802,13 @@
         <v>50000023</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="E28" s="2">
         <v>5</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -15795,13 +15834,13 @@
         <v>50000024</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E29" s="2">
         <v>5</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -15827,13 +15866,13 @@
         <v>50000025</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="E30" s="2">
         <v>5</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -15859,13 +15898,13 @@
         <v>50000026</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E31" s="2">
         <v>5</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -15891,13 +15930,13 @@
         <v>50000027</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="E32" s="2">
         <v>5</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -15923,13 +15962,13 @@
         <v>50000028</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="E33" s="2">
         <v>5</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -15955,13 +15994,13 @@
         <v>50000029</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="E34" s="2">
         <v>5</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -15987,13 +16026,13 @@
         <v>50000030</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="E35" s="2">
         <v>5</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -16019,13 +16058,13 @@
         <v>50000031</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E36" s="2">
         <v>5</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -16051,13 +16090,13 @@
         <v>50000032</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E37" s="2">
         <v>5</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="G37" s="2">
         <v>1</v>
@@ -16083,13 +16122,13 @@
         <v>50000033</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="E38" s="2">
         <v>5</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="G38" s="2">
         <v>1</v>
@@ -16115,13 +16154,13 @@
         <v>50000034</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="E39" s="2">
         <v>5</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -16147,13 +16186,13 @@
         <v>50000035</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E40" s="2">
         <v>5</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -16179,13 +16218,13 @@
         <v>50000036</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="E41" s="2">
         <v>5</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -16211,13 +16250,13 @@
         <v>50000037</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E42" s="2">
         <v>5</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -16243,13 +16282,13 @@
         <v>50000038</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E43" s="2">
         <v>5</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -16275,13 +16314,13 @@
         <v>50000039</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E44" s="2">
         <v>5</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -16307,13 +16346,13 @@
         <v>50000040</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="E45" s="2">
         <v>5</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="G45" s="2">
         <v>1</v>
@@ -16339,13 +16378,13 @@
         <v>50000041</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="E46" s="2">
         <v>5</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -16371,13 +16410,13 @@
         <v>50000042</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="E47" s="2">
         <v>5</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -16403,13 +16442,13 @@
         <v>50000043</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="E48" s="2">
         <v>5</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -16435,13 +16474,13 @@
         <v>50000044</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="E49" s="2">
         <v>5</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -16467,13 +16506,13 @@
         <v>50000045</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="E50" s="2">
         <v>5</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -16499,13 +16538,13 @@
         <v>50000046</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="E51" s="2">
         <v>5</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -16531,13 +16570,13 @@
         <v>50000047</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="E52" s="2">
         <v>5</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -16563,13 +16602,13 @@
         <v>50000048</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E53" s="2">
         <v>5</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="G53" s="2">
         <v>1</v>
@@ -16595,13 +16634,13 @@
         <v>50000049</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="E54" s="2">
         <v>5</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="G54" s="2">
         <v>1</v>
@@ -16627,13 +16666,13 @@
         <v>50000050</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="E55" s="2">
         <v>5</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="G55" s="2">
         <v>1</v>
@@ -16659,13 +16698,13 @@
         <v>50000051</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="E56" s="2">
         <v>5</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="G56" s="2">
         <v>1</v>
@@ -16691,13 +16730,13 @@
         <v>50000052</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="E57" s="2">
         <v>5</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="G57" s="2">
         <v>1</v>
@@ -16723,13 +16762,13 @@
         <v>50000053</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E58" s="2">
         <v>5</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="G58" s="2">
         <v>1</v>
@@ -16755,13 +16794,13 @@
         <v>50000054</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="E59" s="2">
         <v>5</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="G59" s="2">
         <v>1</v>
@@ -16787,13 +16826,13 @@
         <v>50000055</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="E60" s="2">
         <v>5</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="G60" s="2">
         <v>1</v>
@@ -16819,13 +16858,13 @@
         <v>50000056</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E61" s="2">
         <v>5</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="G61" s="2">
         <v>1</v>
@@ -16851,13 +16890,13 @@
         <v>50000057</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="E62" s="2">
         <v>5</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="G62" s="2">
         <v>1</v>
@@ -16883,13 +16922,13 @@
         <v>50000058</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="E63" s="2">
         <v>5</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="G63" s="2">
         <v>1</v>
@@ -16915,13 +16954,13 @@
         <v>50000059</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="E64" s="2">
         <v>5</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="G64" s="2">
         <v>1</v>
@@ -16947,13 +16986,13 @@
         <v>50000060</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="E65" s="2">
         <v>5</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="G65" s="2">
         <v>1</v>
@@ -16979,13 +17018,13 @@
         <v>50000061</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="E66" s="2">
         <v>5</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="G66" s="2">
         <v>1</v>
@@ -17011,13 +17050,13 @@
         <v>50000062</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="E67" s="2">
         <v>5</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="G67" s="2">
         <v>1</v>
@@ -17043,13 +17082,13 @@
         <v>50000063</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="E68" s="2">
         <v>5</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="G68" s="2">
         <v>1</v>
@@ -17075,13 +17114,13 @@
         <v>50000064</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="E69" s="2">
         <v>5</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="G69" s="2">
         <v>1</v>
@@ -17107,13 +17146,13 @@
         <v>50000065</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="E70" s="2">
         <v>5</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="G70" s="2">
         <v>1</v>
@@ -17139,13 +17178,13 @@
         <v>50000066</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="E71" s="2">
         <v>5</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="G71" s="2">
         <v>1</v>
@@ -17171,13 +17210,13 @@
         <v>50000067</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="E72" s="2">
         <v>5</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="G72" s="2">
         <v>1</v>
@@ -17203,13 +17242,13 @@
         <v>50000068</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="E73" s="2">
         <v>5</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="G73" s="2">
         <v>1</v>
@@ -17235,13 +17274,13 @@
         <v>50000069</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="E74" s="2">
         <v>5</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="G74" s="2">
         <v>1</v>
@@ -17267,13 +17306,13 @@
         <v>50000070</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="E75" s="2">
         <v>5</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="G75" s="2">
         <v>1</v>
@@ -17299,13 +17338,13 @@
         <v>50000071</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E76" s="2">
         <v>5</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="G76" s="2">
         <v>1</v>
@@ -17331,13 +17370,13 @@
         <v>50000072</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="E77" s="2">
         <v>5</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="G77" s="2">
         <v>1</v>
@@ -17363,13 +17402,13 @@
         <v>50000073</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="E78" s="2">
         <v>5</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="G78" s="2">
         <v>1</v>
@@ -17395,13 +17434,13 @@
         <v>50000074</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="E79" s="2">
         <v>5</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="G79" s="2">
         <v>1</v>
@@ -17427,13 +17466,13 @@
         <v>50000075</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="E80" s="2">
         <v>5</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="G80" s="2">
         <v>1</v>
@@ -17459,13 +17498,13 @@
         <v>50000076</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="E81" s="2">
         <v>5</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="G81" s="2">
         <v>1</v>
@@ -17491,13 +17530,13 @@
         <v>50000077</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="E82" s="2">
         <v>5</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="G82" s="2">
         <v>1</v>
@@ -17523,13 +17562,13 @@
         <v>50000078</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E83" s="2">
         <v>5</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="G83" s="2">
         <v>1</v>
@@ -17555,13 +17594,13 @@
         <v>50000079</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="E84" s="2">
         <v>5</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="G84" s="2">
         <v>1</v>
@@ -17587,13 +17626,13 @@
         <v>50000080</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="E85" s="2">
         <v>5</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="G85" s="2">
         <v>1</v>
@@ -17619,13 +17658,13 @@
         <v>50000081</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E86" s="2">
         <v>5</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="G86" s="2">
         <v>1</v>
@@ -17651,13 +17690,13 @@
         <v>50000082</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="E87" s="2">
         <v>5</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="G87" s="2">
         <v>1</v>
@@ -17683,13 +17722,13 @@
         <v>50000083</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="E88" s="2">
         <v>5</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="G88" s="2">
         <v>1</v>
@@ -17715,13 +17754,13 @@
         <v>50000084</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="E89" s="2">
         <v>5</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="G89" s="2">
         <v>1</v>
@@ -17747,13 +17786,13 @@
         <v>50000085</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="E90" s="2">
         <v>5</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="G90" s="2">
         <v>1</v>
@@ -17779,13 +17818,13 @@
         <v>50000086</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="E91" s="2">
         <v>5</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="G91" s="2">
         <v>1</v>
@@ -17811,13 +17850,13 @@
         <v>50000087</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="E92" s="2">
         <v>5</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="G92" s="2">
         <v>1</v>
@@ -17843,13 +17882,13 @@
         <v>50000088</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="E93" s="2">
         <v>5</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="G93" s="2">
         <v>1</v>
@@ -17875,13 +17914,13 @@
         <v>50000089</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E94" s="2">
         <v>5</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="G94" s="2">
         <v>1</v>
@@ -17907,13 +17946,13 @@
         <v>50000090</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E95" s="2">
         <v>5</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="G95" s="2">
         <v>1</v>
@@ -17939,13 +17978,13 @@
         <v>50000091</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E96" s="2">
         <v>5</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="G96" s="2">
         <v>1</v>
@@ -17971,13 +18010,13 @@
         <v>50000092</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E97" s="2">
         <v>5</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="G97" s="2">
         <v>1</v>
@@ -18003,13 +18042,13 @@
         <v>50000093</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="E98" s="2">
         <v>5</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="G98" s="2">
         <v>1</v>
@@ -18035,13 +18074,13 @@
         <v>50000094</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="E99" s="2">
         <v>5</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="G99" s="2">
         <v>1</v>
@@ -18067,13 +18106,13 @@
         <v>50000095</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="E100" s="2">
         <v>5</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="G100" s="2">
         <v>1</v>
@@ -18099,13 +18138,13 @@
         <v>50000096</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="E101" s="2">
         <v>5</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="G101" s="2">
         <v>1</v>
@@ -18131,13 +18170,13 @@
         <v>50000097</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="E102" s="2">
         <v>5</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="G102" s="2">
         <v>1</v>
@@ -18163,13 +18202,13 @@
         <v>50000098</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="E103" s="2">
         <v>5</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="G103" s="2">
         <v>1</v>
@@ -18195,13 +18234,13 @@
         <v>50000099</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="E104" s="2">
         <v>5</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="G104" s="2">
         <v>1</v>
@@ -18227,13 +18266,13 @@
         <v>50000100</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="E105" s="2">
         <v>5</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="G105" s="2">
         <v>1</v>
@@ -18259,13 +18298,13 @@
         <v>50000101</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="E106" s="2">
         <v>5</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="G106" s="2">
         <v>1</v>
@@ -18291,13 +18330,13 @@
         <v>50000102</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="E107" s="2">
         <v>5</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="G107" s="2">
         <v>1</v>
@@ -18323,13 +18362,13 @@
         <v>50000103</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="E108" s="2">
         <v>5</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="G108" s="2">
         <v>1</v>
@@ -18355,13 +18394,13 @@
         <v>50000104</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="E109" s="2">
         <v>5</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="G109" s="2">
         <v>1</v>
@@ -18526,13 +18565,13 @@
         <v>180001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="E6" s="2">
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -18552,13 +18591,13 @@
         <v>180002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="E7" s="2">
         <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -18578,13 +18617,13 @@
         <v>180003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="E8" s="2">
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -18604,13 +18643,13 @@
         <v>180004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="E9" s="2">
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -18630,13 +18669,13 @@
         <v>180005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="E10" s="2">
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -18656,13 +18695,13 @@
         <v>180006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="E11" s="2">
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -18684,13 +18723,13 @@
         <v>180007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E12" s="2">
         <v>18</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -18712,13 +18751,13 @@
         <v>180008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="E13" s="2">
         <v>18</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -18740,13 +18779,13 @@
         <v>180009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E14" s="2">
         <v>18</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -18768,13 +18807,13 @@
         <v>180010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="E15" s="2">
         <v>18</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -18796,13 +18835,13 @@
         <v>180011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="E16" s="2">
         <v>18</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -18824,13 +18863,13 @@
         <v>180012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="E17" s="2">
         <v>18</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -18852,13 +18891,13 @@
         <v>180013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="E18" s="2">
         <v>18</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -18880,13 +18919,13 @@
         <v>180014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="E19" s="2">
         <v>18</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -18908,13 +18947,13 @@
         <v>180015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="E20" s="2">
         <v>18</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -18936,13 +18975,13 @@
         <v>180016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="E21" s="2">
         <v>18</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -18964,13 +19003,13 @@
         <v>180017</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="E22" s="2">
         <v>18</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -18992,13 +19031,13 @@
         <v>180018</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="E23" s="2">
         <v>18</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -19020,13 +19059,13 @@
         <v>180019</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="E24" s="2">
         <v>18</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -19048,13 +19087,13 @@
         <v>180020</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="E25" s="2">
         <v>18</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -19076,13 +19115,13 @@
         <v>180021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="E26" s="2">
         <v>18</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -19109,13 +19148,13 @@
         <v>180030</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="E28" s="2">
         <v>18</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -19137,13 +19176,13 @@
         <v>180031</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="E29" s="2">
         <v>18</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="G29" s="3">
         <v>1</v>
@@ -19163,13 +19202,13 @@
         <v>180032</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="E30" s="2">
         <v>18</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="G30" s="3">
         <v>1</v>
@@ -19189,13 +19228,13 @@
         <v>180033</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="E31" s="2">
         <v>18</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="G31" s="3">
         <v>1</v>
@@ -19215,13 +19254,13 @@
         <v>180034</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="E32" s="2">
         <v>18</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="G32" s="3">
         <v>1</v>
@@ -19387,13 +19426,13 @@
         <v>190001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E6" s="2">
         <v>19</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -19413,13 +19452,13 @@
         <v>190002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="E7" s="2">
         <v>19</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -19439,13 +19478,13 @@
         <v>190003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="E8" s="2">
         <v>19</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -19465,13 +19504,13 @@
         <v>190004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="E9" s="2">
         <v>19</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -19491,13 +19530,13 @@
         <v>190005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="E10" s="2">
         <v>19</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -19517,13 +19556,13 @@
         <v>190006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="E11" s="2">
         <v>19</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -344,7 +344,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1398" uniqueCount="741">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1402" uniqueCount="743">
   <si>
     <t>_Id</t>
   </si>
@@ -2546,6 +2546,12 @@
   </si>
   <si>
     <t>极.财富契约</t>
+  </si>
+  <si>
+    <t>极.魔法书</t>
+  </si>
+  <si>
+    <t>极.无限之魂</t>
   </si>
   <si>
     <t>定身神戒</t>
@@ -18439,7 +18445,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:M33"/>
+  <dimension ref="C1:M34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="4" max="4" width="9.625" customWidth="1"/>
@@ -19277,10 +19283,61 @@
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
     </row>
-    <row r="33" s="2" customFormat="1" customHeight="1" spans="4:13">
-      <c r="D33" s="3"/>
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C33" s="2">
+        <v>180035</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="E33" s="2">
+        <v>18</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="G33" s="3">
+        <v>1</v>
+      </c>
+      <c r="H33" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I33" s="2">
+        <v>0</v>
+      </c>
+      <c r="J33" s="2">
+        <v>7</v>
+      </c>
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
+    </row>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C34" s="2">
+        <v>180036</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>735</v>
+      </c>
+      <c r="E34" s="2">
+        <v>18</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="G34" s="3">
+        <v>1</v>
+      </c>
+      <c r="H34" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I34" s="2">
+        <v>0</v>
+      </c>
+      <c r="J34" s="2">
+        <v>7</v>
+      </c>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -19426,13 +19483,13 @@
         <v>190001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="E6" s="2">
         <v>19</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -19452,13 +19509,13 @@
         <v>190002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="E7" s="2">
         <v>19</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -19478,13 +19535,13 @@
         <v>190003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="E8" s="2">
         <v>19</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -19504,13 +19561,13 @@
         <v>190004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="E9" s="2">
         <v>19</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -19530,13 +19587,13 @@
         <v>190005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="E10" s="2">
         <v>19</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -19556,13 +19613,13 @@
         <v>190006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="E11" s="2">
         <v>19</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="6"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -5672,7 +5672,6 @@
       <c r="J26" s="3">
         <v>7</v>
       </c>
-      <c r="K26" s="3"/>
       <c r="L26" s="3">
         <v>0</v>
       </c>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -583,10 +583,10 @@
     <t>2005</t>
   </si>
   <si>
-    <t>魔法盾</t>
-  </si>
-  <si>
-    <t>学习或者升级法师技能魔法盾</t>
+    <t>法力盾</t>
+  </si>
+  <si>
+    <t>学习或者升级法师技能法力盾</t>
   </si>
   <si>
     <t>2006</t>
@@ -610,10 +610,10 @@
     <t>2008</t>
   </si>
   <si>
-    <t>闪烁术</t>
-  </si>
-  <si>
-    <t>学习或者升级法师技能闪烁术</t>
+    <t>瞬移术</t>
+  </si>
+  <si>
+    <t>学习或者升级法师技能瞬移术</t>
   </si>
   <si>
     <t>2009</t>
@@ -1426,151 +1426,151 @@
     <t>金枝玉叶</t>
   </si>
   <si>
-    <t>战神之刃</t>
+    <t>斩仙之刃</t>
   </si>
   <si>
     <t>激活或者升级对应部位时装</t>
   </si>
   <si>
-    <t>战神之甲</t>
-  </si>
-  <si>
-    <t>战神之头</t>
-  </si>
-  <si>
-    <t>战神之链</t>
-  </si>
-  <si>
-    <t>战神之镯</t>
-  </si>
-  <si>
-    <t>战神之戒</t>
-  </si>
-  <si>
-    <t>战神之带</t>
-  </si>
-  <si>
-    <t>战神之靴</t>
-  </si>
-  <si>
-    <t>法神之杖</t>
-  </si>
-  <si>
-    <t>法神之衣</t>
-  </si>
-  <si>
-    <t>法神之头</t>
-  </si>
-  <si>
-    <t>法神之链</t>
-  </si>
-  <si>
-    <t>法神之镯</t>
-  </si>
-  <si>
-    <t>法神之戒</t>
-  </si>
-  <si>
-    <t>法神之带</t>
-  </si>
-  <si>
-    <t>法神之靴</t>
-  </si>
-  <si>
-    <t>道神之剑</t>
-  </si>
-  <si>
-    <t>道神之袍</t>
-  </si>
-  <si>
-    <t>道神之头</t>
-  </si>
-  <si>
-    <t>道神之链</t>
-  </si>
-  <si>
-    <t>道神之镯</t>
-  </si>
-  <si>
-    <t>道神之戒</t>
-  </si>
-  <si>
-    <t>道神之带</t>
-  </si>
-  <si>
-    <t>道神之靴</t>
-  </si>
-  <si>
-    <t>战尊之刃</t>
-  </si>
-  <si>
-    <t>战尊之甲</t>
-  </si>
-  <si>
-    <t>战尊之头</t>
-  </si>
-  <si>
-    <t>战尊之链</t>
-  </si>
-  <si>
-    <t>战尊之镯</t>
-  </si>
-  <si>
-    <t>战尊之戒</t>
-  </si>
-  <si>
-    <t>战尊之带</t>
-  </si>
-  <si>
-    <t>战尊之靴</t>
-  </si>
-  <si>
-    <t>法尊之杖</t>
-  </si>
-  <si>
-    <t>法尊之衣</t>
-  </si>
-  <si>
-    <t>法尊之头</t>
-  </si>
-  <si>
-    <t>法尊之链</t>
-  </si>
-  <si>
-    <t>法尊之镯</t>
-  </si>
-  <si>
-    <t>法尊之戒</t>
-  </si>
-  <si>
-    <t>法尊之带</t>
-  </si>
-  <si>
-    <t>法尊之靴</t>
-  </si>
-  <si>
-    <t>道尊之剑</t>
-  </si>
-  <si>
-    <t>道尊之袍</t>
-  </si>
-  <si>
-    <t>道尊之头</t>
-  </si>
-  <si>
-    <t>道尊之链</t>
-  </si>
-  <si>
-    <t>道尊之镯</t>
-  </si>
-  <si>
-    <t>道尊之戒</t>
-  </si>
-  <si>
-    <t>道尊之带</t>
-  </si>
-  <si>
-    <t>道尊之靴</t>
+    <t>斩仙之甲</t>
+  </si>
+  <si>
+    <t>斩仙之头</t>
+  </si>
+  <si>
+    <t>斩仙之链</t>
+  </si>
+  <si>
+    <t>斩仙之镯</t>
+  </si>
+  <si>
+    <t>斩仙之戒</t>
+  </si>
+  <si>
+    <t>斩仙之带</t>
+  </si>
+  <si>
+    <t>斩仙之靴</t>
+  </si>
+  <si>
+    <t>魔尊之杖</t>
+  </si>
+  <si>
+    <t>魔尊之衣</t>
+  </si>
+  <si>
+    <t>魔尊之头</t>
+  </si>
+  <si>
+    <t>魔尊之链</t>
+  </si>
+  <si>
+    <t>魔尊之镯</t>
+  </si>
+  <si>
+    <t>魔尊之戒</t>
+  </si>
+  <si>
+    <t>魔尊之带</t>
+  </si>
+  <si>
+    <t>魔尊之靴</t>
+  </si>
+  <si>
+    <t>幽冥之剑</t>
+  </si>
+  <si>
+    <t>幽冥之袍</t>
+  </si>
+  <si>
+    <t>幽冥之头</t>
+  </si>
+  <si>
+    <t>幽冥之链</t>
+  </si>
+  <si>
+    <t>幽冥之镯</t>
+  </si>
+  <si>
+    <t>幽冥之戒</t>
+  </si>
+  <si>
+    <t>幽冥之带</t>
+  </si>
+  <si>
+    <t>幽冥之靴</t>
+  </si>
+  <si>
+    <t>战魂之刃</t>
+  </si>
+  <si>
+    <t>战魂之甲</t>
+  </si>
+  <si>
+    <t>战魂之头</t>
+  </si>
+  <si>
+    <t>战魂之链</t>
+  </si>
+  <si>
+    <t>战魂之镯</t>
+  </si>
+  <si>
+    <t>战魂之戒</t>
+  </si>
+  <si>
+    <t>战魂之带</t>
+  </si>
+  <si>
+    <t>战魂之靴</t>
+  </si>
+  <si>
+    <t>法魂之杖</t>
+  </si>
+  <si>
+    <t>法魂之衣</t>
+  </si>
+  <si>
+    <t>法魂之头</t>
+  </si>
+  <si>
+    <t>法魂之链</t>
+  </si>
+  <si>
+    <t>法魂之镯</t>
+  </si>
+  <si>
+    <t>法魂之戒</t>
+  </si>
+  <si>
+    <t>法魂之带</t>
+  </si>
+  <si>
+    <t>法魂之靴</t>
+  </si>
+  <si>
+    <t>道魂之剑</t>
+  </si>
+  <si>
+    <t>道魂之袍</t>
+  </si>
+  <si>
+    <t>道魂之头</t>
+  </si>
+  <si>
+    <t>道魂之链</t>
+  </si>
+  <si>
+    <t>道魂之镯</t>
+  </si>
+  <si>
+    <t>道魂之戒</t>
+  </si>
+  <si>
+    <t>道魂之带</t>
+  </si>
+  <si>
+    <t>道魂之靴</t>
   </si>
   <si>
     <t>触龙之心</t>
@@ -2554,25 +2554,25 @@
     <t>极.无限之魂</t>
   </si>
   <si>
-    <t>定身神戒</t>
+    <t>定身指环</t>
   </si>
   <si>
     <t>激活或者升级对应神戒</t>
   </si>
   <si>
-    <t>护体神戒</t>
-  </si>
-  <si>
-    <t>重生神戒</t>
-  </si>
-  <si>
-    <t>防御神戒</t>
-  </si>
-  <si>
-    <t>闪烁神戒</t>
-  </si>
-  <si>
-    <t>隐身神戒</t>
+    <t>神盾指环</t>
+  </si>
+  <si>
+    <t>复生指环</t>
+  </si>
+  <si>
+    <t>护体指环</t>
+  </si>
+  <si>
+    <t>破空指环</t>
+  </si>
+  <si>
+    <t>须弥指环</t>
   </si>
 </sst>
 </file>
@@ -3254,7 +3254,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3268,6 +3268,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -3713,7 +3714,7 @@
       <c r="C6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="12" t="s">
         <v>23</v>
       </c>
       <c r="E6" s="3" t="s">
@@ -3818,7 +3819,7 @@
       <c r="C9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="12" t="s">
         <v>38</v>
       </c>
       <c r="E9" s="3" t="s">
@@ -3955,7 +3956,7 @@
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:13">
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="13" t="s">
         <v>53</v>
       </c>
       <c r="D13" s="1" t="s">
@@ -3973,7 +3974,7 @@
       <c r="H13" s="3">
         <v>99999999</v>
       </c>
-      <c r="I13" s="12" t="s">
+      <c r="I13" s="13" t="s">
         <v>56</v>
       </c>
       <c r="J13" s="3">
@@ -3990,7 +3991,7 @@
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:13">
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="13" t="s">
         <v>57</v>
       </c>
       <c r="D14" s="1" t="s">
@@ -4008,7 +4009,7 @@
       <c r="H14" s="3">
         <v>99999999</v>
       </c>
-      <c r="I14" s="12" t="s">
+      <c r="I14" s="13" t="s">
         <v>56</v>
       </c>
       <c r="J14" s="3">
@@ -4025,7 +4026,7 @@
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:13">
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="13" t="s">
         <v>60</v>
       </c>
       <c r="D15" s="1" t="s">
@@ -4043,7 +4044,7 @@
       <c r="H15" s="3">
         <v>99999999</v>
       </c>
-      <c r="I15" s="12" t="s">
+      <c r="I15" s="13" t="s">
         <v>56</v>
       </c>
       <c r="J15" s="3">
@@ -4060,7 +4061,7 @@
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:13">
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="13" t="s">
         <v>63</v>
       </c>
       <c r="D16" s="1" t="s">
@@ -4078,7 +4079,7 @@
       <c r="H16" s="3">
         <v>99999999</v>
       </c>
-      <c r="I16" s="12" t="s">
+      <c r="I16" s="13" t="s">
         <v>56</v>
       </c>
       <c r="J16" s="3">
@@ -4098,7 +4099,7 @@
       <c r="C18" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="12" t="s">
         <v>67</v>
       </c>
       <c r="E18" s="3" t="s">
@@ -4273,7 +4274,7 @@
       <c r="C23" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="12" t="s">
         <v>82</v>
       </c>
       <c r="E23" s="3" t="s">
@@ -4340,7 +4341,7 @@
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:13">
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="13" t="s">
         <v>87</v>
       </c>
       <c r="D25" s="1" t="s">
@@ -4358,7 +4359,7 @@
       <c r="H25" s="3">
         <v>99999999</v>
       </c>
-      <c r="I25" s="12" t="s">
+      <c r="I25" s="13" t="s">
         <v>56</v>
       </c>
       <c r="J25" s="3">
@@ -4375,7 +4376,7 @@
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:13">
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="13" t="s">
         <v>90</v>
       </c>
       <c r="D26" s="1" t="s">
@@ -4393,7 +4394,7 @@
       <c r="H26" s="3">
         <v>99999999</v>
       </c>
-      <c r="I26" s="12" t="s">
+      <c r="I26" s="13" t="s">
         <v>56</v>
       </c>
       <c r="J26" s="3">
@@ -4410,7 +4411,7 @@
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:13">
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="13" t="s">
         <v>93</v>
       </c>
       <c r="D27" s="1" t="s">
@@ -4428,7 +4429,7 @@
       <c r="H27" s="3">
         <v>99999999</v>
       </c>
-      <c r="I27" s="12" t="s">
+      <c r="I27" s="13" t="s">
         <v>56</v>
       </c>
       <c r="J27" s="3">
@@ -4445,7 +4446,7 @@
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:13">
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="13" t="s">
         <v>96</v>
       </c>
       <c r="D28" s="1" t="s">
@@ -4463,7 +4464,7 @@
       <c r="H28" s="3">
         <v>99999999</v>
       </c>
-      <c r="I28" s="12" t="s">
+      <c r="I28" s="13" t="s">
         <v>56</v>
       </c>
       <c r="J28" s="3">
@@ -4518,7 +4519,7 @@
       <c r="C31" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D31" s="11" t="s">
+      <c r="D31" s="12" t="s">
         <v>103</v>
       </c>
       <c r="E31" s="3" t="s">
@@ -4658,7 +4659,7 @@
       <c r="C35" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D35" s="11" t="s">
+      <c r="D35" s="12" t="s">
         <v>115</v>
       </c>
       <c r="E35" s="3" t="s">
@@ -4725,7 +4726,7 @@
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:13">
-      <c r="C37" s="12" t="s">
+      <c r="C37" s="13" t="s">
         <v>120</v>
       </c>
       <c r="D37" s="1" t="s">
@@ -4743,7 +4744,7 @@
       <c r="H37" s="3">
         <v>99999999</v>
       </c>
-      <c r="I37" s="12" t="s">
+      <c r="I37" s="13" t="s">
         <v>56</v>
       </c>
       <c r="J37" s="3">
@@ -4760,7 +4761,7 @@
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:13">
-      <c r="C38" s="12" t="s">
+      <c r="C38" s="13" t="s">
         <v>123</v>
       </c>
       <c r="D38" s="1" t="s">
@@ -4778,7 +4779,7 @@
       <c r="H38" s="3">
         <v>99999999</v>
       </c>
-      <c r="I38" s="12" t="s">
+      <c r="I38" s="13" t="s">
         <v>56</v>
       </c>
       <c r="J38" s="3">
@@ -4795,7 +4796,7 @@
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:13">
-      <c r="C39" s="12" t="s">
+      <c r="C39" s="13" t="s">
         <v>126</v>
       </c>
       <c r="D39" s="1" t="s">
@@ -4813,7 +4814,7 @@
       <c r="H39" s="3">
         <v>99999999</v>
       </c>
-      <c r="I39" s="12" t="s">
+      <c r="I39" s="13" t="s">
         <v>56</v>
       </c>
       <c r="J39" s="3">
@@ -4830,7 +4831,7 @@
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:13">
-      <c r="C40" s="12" t="s">
+      <c r="C40" s="13" t="s">
         <v>129</v>
       </c>
       <c r="D40" s="1" t="s">
@@ -4848,7 +4849,7 @@
       <c r="H40" s="3">
         <v>99999999</v>
       </c>
-      <c r="I40" s="12" t="s">
+      <c r="I40" s="13" t="s">
         <v>56</v>
       </c>
       <c r="J40" s="3">
@@ -6851,7 +6852,7 @@
       <c r="C69" s="3">
         <v>8101</v>
       </c>
-      <c r="D69" s="10" t="s">
+      <c r="D69" s="11" t="s">
         <v>230</v>
       </c>
       <c r="E69" s="3">
@@ -6883,7 +6884,7 @@
       <c r="C70" s="3">
         <v>8102</v>
       </c>
-      <c r="D70" s="10" t="s">
+      <c r="D70" s="11" t="s">
         <v>232</v>
       </c>
       <c r="E70" s="3">
@@ -6915,7 +6916,7 @@
       <c r="C71" s="3">
         <v>8103</v>
       </c>
-      <c r="D71" s="10" t="s">
+      <c r="D71" s="11" t="s">
         <v>233</v>
       </c>
       <c r="E71" s="3">
@@ -6947,7 +6948,7 @@
       <c r="C72" s="3">
         <v>8104</v>
       </c>
-      <c r="D72" s="10" t="s">
+      <c r="D72" s="11" t="s">
         <v>234</v>
       </c>
       <c r="E72" s="3">
@@ -6979,7 +6980,7 @@
       <c r="C73" s="3">
         <v>8105</v>
       </c>
-      <c r="D73" s="10" t="s">
+      <c r="D73" s="11" t="s">
         <v>235</v>
       </c>
       <c r="E73" s="3">
@@ -7011,7 +7012,7 @@
       <c r="C74" s="3">
         <v>8106</v>
       </c>
-      <c r="D74" s="10" t="s">
+      <c r="D74" s="11" t="s">
         <v>236</v>
       </c>
       <c r="E74" s="3">
@@ -7043,7 +7044,7 @@
       <c r="C75" s="3">
         <v>8107</v>
       </c>
-      <c r="D75" s="10" t="s">
+      <c r="D75" s="11" t="s">
         <v>237</v>
       </c>
       <c r="E75" s="3">
@@ -7075,7 +7076,7 @@
       <c r="C76" s="3">
         <v>8108</v>
       </c>
-      <c r="D76" s="10" t="s">
+      <c r="D76" s="11" t="s">
         <v>238</v>
       </c>
       <c r="E76" s="3">
@@ -7979,7 +7980,7 @@
       <c r="C33" s="2">
         <v>2000011</v>
       </c>
-      <c r="D33" s="9" t="s">
+      <c r="D33" s="10" t="s">
         <v>267</v>
       </c>
       <c r="E33" s="2">
@@ -8007,7 +8008,7 @@
       <c r="C34" s="2">
         <v>2000012</v>
       </c>
-      <c r="D34" s="9" t="s">
+      <c r="D34" s="10" t="s">
         <v>268</v>
       </c>
       <c r="E34" s="2">
@@ -8035,7 +8036,7 @@
       <c r="C35" s="2">
         <v>2000013</v>
       </c>
-      <c r="D35" s="9" t="s">
+      <c r="D35" s="10" t="s">
         <v>269</v>
       </c>
       <c r="E35" s="2">
@@ -11062,7 +11063,7 @@
       <c r="C22" s="2">
         <v>3000017</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="9" t="s">
         <v>377</v>
       </c>
       <c r="E22" s="2">
@@ -11090,7 +11091,7 @@
       <c r="C23" s="2">
         <v>3000018</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" s="9" t="s">
         <v>378</v>
       </c>
       <c r="E23" s="2">
@@ -11118,7 +11119,7 @@
       <c r="C24" s="2">
         <v>3000019</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="9" t="s">
         <v>379</v>
       </c>
       <c r="E24" s="2">
@@ -11146,7 +11147,7 @@
       <c r="C25" s="2">
         <v>3000020</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="9" t="s">
         <v>380</v>
       </c>
       <c r="E25" s="2">
@@ -11174,7 +11175,7 @@
       <c r="C26" s="2">
         <v>3000021</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="9" t="s">
         <v>381</v>
       </c>
       <c r="E26" s="2">
@@ -11202,7 +11203,7 @@
       <c r="C27" s="2">
         <v>3000022</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="9" t="s">
         <v>382</v>
       </c>
       <c r="E27" s="2">
@@ -11230,7 +11231,7 @@
       <c r="C28" s="2">
         <v>3000023</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="9" t="s">
         <v>383</v>
       </c>
       <c r="E28" s="2">
@@ -11258,7 +11259,7 @@
       <c r="C29" s="2">
         <v>3000024</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" s="9" t="s">
         <v>384</v>
       </c>
       <c r="E29" s="2">
@@ -19481,7 +19482,7 @@
       <c r="C6" s="2">
         <v>190001</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>736</v>
       </c>
       <c r="E6" s="2">
@@ -19507,7 +19508,7 @@
       <c r="C7" s="2">
         <v>190002</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>738</v>
       </c>
       <c r="E7" s="2">
@@ -19533,7 +19534,7 @@
       <c r="C8" s="2">
         <v>190003</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="2" t="s">
         <v>739</v>
       </c>
       <c r="E8" s="2">
@@ -19559,7 +19560,7 @@
       <c r="C9" s="2">
         <v>190004</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>740</v>
       </c>
       <c r="E9" s="2">
@@ -19585,7 +19586,7 @@
       <c r="C10" s="2">
         <v>190005</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="2" t="s">
         <v>741</v>
       </c>
       <c r="E10" s="2">
@@ -19611,7 +19612,7 @@
       <c r="C11" s="2">
         <v>190006</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>742</v>
       </c>
       <c r="E11" s="2">

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -436,10 +436,10 @@
     <t>1002</t>
   </si>
   <si>
-    <t>穿刺剑术</t>
-  </si>
-  <si>
-    <t>学习或者升级战士技能穿刺剑术</t>
+    <t>流光剑法</t>
+  </si>
+  <si>
+    <t>学习或者升级战士技能流光剑法</t>
   </si>
   <si>
     <t>20</t>
@@ -448,10 +448,10 @@
     <t>1003</t>
   </si>
   <si>
-    <t>圆月弯刀</t>
-  </si>
-  <si>
-    <t>学习或者升级战士技能圆月弯刀</t>
+    <t>旋风斩</t>
+  </si>
+  <si>
+    <t>学习或者升级战士技能旋风斩</t>
   </si>
   <si>
     <t>30</t>
@@ -460,10 +460,10 @@
     <t>1004</t>
   </si>
   <si>
-    <t>蛮力撞击</t>
-  </si>
-  <si>
-    <t>学习或者升级战士技能蛮力撞击</t>
+    <t>腾空斩</t>
+  </si>
+  <si>
+    <t>学习或者升级战士技能腾空斩</t>
   </si>
   <si>
     <t>100000</t>
@@ -475,10 +475,10 @@
     <t>1005</t>
   </si>
   <si>
-    <t>武力盾</t>
-  </si>
-  <si>
-    <t>学习或者升级战士技能武力盾</t>
+    <t>武神盾</t>
+  </si>
+  <si>
+    <t>学习或者升级战士技能武神盾</t>
   </si>
   <si>
     <t>1006</t>
@@ -496,10 +496,10 @@
     <t>1007</t>
   </si>
   <si>
-    <t>火焰剑法</t>
-  </si>
-  <si>
-    <t>学习或者升级战士技能火焰剑法</t>
+    <t>烈焰斩</t>
+  </si>
+  <si>
+    <t>学习或者升级战士技能烈焰斩</t>
   </si>
   <si>
     <t>70</t>
@@ -508,10 +508,10 @@
     <t>1008</t>
   </si>
   <si>
-    <t>护体神盾</t>
-  </si>
-  <si>
-    <t>学习或者升级战士技能护体神盾</t>
+    <t>战吼</t>
+  </si>
+  <si>
+    <t>学习或者升级战士技能战吼</t>
   </si>
   <si>
     <t>80</t>
@@ -520,10 +520,10 @@
     <t>1009</t>
   </si>
   <si>
-    <t>开天辟地</t>
-  </si>
-  <si>
-    <t>学习或者升级战士技能开天辟地</t>
+    <t>裂天斩</t>
+  </si>
+  <si>
+    <t>学习或者升级战士技能裂天斩</t>
   </si>
   <si>
     <t>1010</t>
@@ -556,28 +556,28 @@
     <t>2002</t>
   </si>
   <si>
-    <t>神雷术</t>
-  </si>
-  <si>
-    <t>学习或者升级法师技能神雷术</t>
+    <t>落雷术</t>
+  </si>
+  <si>
+    <t>学习或者升级法师技能落雷术</t>
   </si>
   <si>
     <t>2003</t>
   </si>
   <si>
-    <t>火墙术</t>
-  </si>
-  <si>
-    <t>学习或者升级法师技能火墙术</t>
+    <t>火焰墙</t>
+  </si>
+  <si>
+    <t>学习或者升级法师技能火焰墙</t>
   </si>
   <si>
     <t>2004</t>
   </si>
   <si>
-    <t>火焰术</t>
-  </si>
-  <si>
-    <t>学习或者升级法师技能火焰术</t>
+    <t>烈焰环</t>
+  </si>
+  <si>
+    <t>学习或者升级法师技能烈焰环</t>
   </si>
   <si>
     <t>2005</t>
@@ -601,28 +601,28 @@
     <t>2007</t>
   </si>
   <si>
-    <t>冰冻术</t>
-  </si>
-  <si>
-    <t>学习或者升级法师技能冰冻术</t>
+    <t>冰爆术</t>
+  </si>
+  <si>
+    <t>学习或者升级法师技能冰爆术</t>
   </si>
   <si>
     <t>2008</t>
   </si>
   <si>
-    <t>瞬移术</t>
-  </si>
-  <si>
-    <t>学习或者升级法师技能瞬移术</t>
+    <t>心灵传送</t>
+  </si>
+  <si>
+    <t>学习或者升级法师技能心灵传送</t>
   </si>
   <si>
     <t>2009</t>
   </si>
   <si>
-    <t>火雨术</t>
-  </si>
-  <si>
-    <t>学习或者升级法师技能火雨术</t>
+    <t>毁灭流星</t>
+  </si>
+  <si>
+    <t>学习或者升级法师技能毁灭流星</t>
   </si>
   <si>
     <t>2010</t>
@@ -646,28 +646,28 @@
     <t>3001</t>
   </si>
   <si>
-    <t>治疗道法</t>
-  </si>
-  <si>
-    <t>学习或者升级道士技能治疗道法</t>
+    <t>疗伤术</t>
+  </si>
+  <si>
+    <t>学习或者升级道士技能疗伤术</t>
   </si>
   <si>
     <t>3002</t>
   </si>
   <si>
-    <t>火符道法</t>
-  </si>
-  <si>
-    <t>学习或者升级道士技能火符道法</t>
+    <t>驱魔符</t>
+  </si>
+  <si>
+    <t>学习或者升级道士技能驱魔符</t>
   </si>
   <si>
     <t>3003</t>
   </si>
   <si>
-    <t>毒咒道法</t>
-  </si>
-  <si>
-    <t>学习或者升级道士技能施毒道法</t>
+    <t>毒咒术</t>
+  </si>
+  <si>
+    <t>学习或者升级道士技能毒咒术</t>
   </si>
   <si>
     <t>3004</t>
@@ -3749,7 +3749,7 @@
       <c r="C7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E7" s="3" t="s">
@@ -3784,7 +3784,7 @@
       <c r="C8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="12" t="s">
         <v>34</v>
       </c>
       <c r="E8" s="3" t="s">
@@ -3854,7 +3854,7 @@
       <c r="C10" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="12" t="s">
         <v>43</v>
       </c>
       <c r="E10" s="3" t="s">
@@ -3889,7 +3889,7 @@
       <c r="C11" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="12" t="s">
         <v>46</v>
       </c>
       <c r="E11" s="3" t="s">
@@ -3924,7 +3924,7 @@
       <c r="C12" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="12" t="s">
         <v>50</v>
       </c>
       <c r="E12" s="3" t="s">
@@ -3959,7 +3959,7 @@
       <c r="C13" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="12" t="s">
         <v>54</v>
       </c>
       <c r="E13" s="3" t="s">
@@ -3994,7 +3994,7 @@
       <c r="C14" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="12" t="s">
         <v>58</v>
       </c>
       <c r="E14" s="3" t="s">
@@ -4029,7 +4029,7 @@
       <c r="C15" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="12" t="s">
         <v>61</v>
       </c>
       <c r="E15" s="3" t="s">
@@ -4064,7 +4064,7 @@
       <c r="C16" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="12" t="s">
         <v>64</v>
       </c>
       <c r="E16" s="3" t="s">
@@ -4134,7 +4134,7 @@
       <c r="C19" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="12" t="s">
         <v>70</v>
       </c>
       <c r="E19" s="3" t="s">
@@ -4169,7 +4169,7 @@
       <c r="C20" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E20" s="3" t="s">
@@ -4204,7 +4204,7 @@
       <c r="C21" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="12" t="s">
         <v>76</v>
       </c>
       <c r="E21" s="3" t="s">
@@ -4239,7 +4239,7 @@
       <c r="C22" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="12" t="s">
         <v>79</v>
       </c>
       <c r="E22" s="3" t="s">
@@ -4309,7 +4309,7 @@
       <c r="C24" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="12" t="s">
         <v>85</v>
       </c>
       <c r="E24" s="3" t="s">
@@ -4344,7 +4344,7 @@
       <c r="C25" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" s="12" t="s">
         <v>88</v>
       </c>
       <c r="E25" s="3" t="s">
@@ -4379,7 +4379,7 @@
       <c r="C26" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" s="12" t="s">
         <v>91</v>
       </c>
       <c r="E26" s="3" t="s">
@@ -4414,7 +4414,7 @@
       <c r="C27" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" s="12" t="s">
         <v>94</v>
       </c>
       <c r="E27" s="3" t="s">
@@ -4449,7 +4449,7 @@
       <c r="C28" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="12" t="s">
         <v>97</v>
       </c>
       <c r="E28" s="3" t="s">
@@ -4484,7 +4484,7 @@
       <c r="C30" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" s="12" t="s">
         <v>100</v>
       </c>
       <c r="E30" s="3" t="s">
@@ -4554,7 +4554,7 @@
       <c r="C32" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" s="12" t="s">
         <v>106</v>
       </c>
       <c r="E32" s="3" t="s">
@@ -4589,7 +4589,7 @@
       <c r="C33" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" s="12" t="s">
         <v>109</v>
       </c>
       <c r="E33" s="3" t="s">
@@ -4624,7 +4624,7 @@
       <c r="C34" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" s="12" t="s">
         <v>112</v>
       </c>
       <c r="E34" s="3" t="s">
@@ -4694,7 +4694,7 @@
       <c r="C36" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" s="12" t="s">
         <v>118</v>
       </c>
       <c r="E36" s="3" t="s">
@@ -4729,7 +4729,7 @@
       <c r="C37" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E37" s="3" t="s">
@@ -4764,7 +4764,7 @@
       <c r="C38" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D38" s="12" t="s">
         <v>124</v>
       </c>
       <c r="E38" s="3" t="s">
@@ -4799,7 +4799,7 @@
       <c r="C39" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D39" s="12" t="s">
         <v>127</v>
       </c>
       <c r="E39" s="3" t="s">
@@ -4834,7 +4834,7 @@
       <c r="C40" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D40" s="12" t="s">
         <v>130</v>
       </c>
       <c r="E40" s="3" t="s">

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -344,7 +344,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1402" uniqueCount="743">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1416" uniqueCount="757">
   <si>
     <t>_Id</t>
   </si>
@@ -529,10 +529,10 @@
     <t>1010</t>
   </si>
   <si>
-    <t>地刺术</t>
-  </si>
-  <si>
-    <t>学习或者升级战士技能地刺术</t>
+    <t>裂地斩</t>
+  </si>
+  <si>
+    <t>学习或者升级战士技能裂地斩</t>
   </si>
   <si>
     <t>1011</t>
@@ -1061,6 +1061,48 @@
   </si>
   <si>
     <t>魔鲸王骨</t>
+  </si>
+  <si>
+    <t>白色宠蛋</t>
+  </si>
+  <si>
+    <t>开启一个白色到金色之间的宠物</t>
+  </si>
+  <si>
+    <t>绿色宠蛋</t>
+  </si>
+  <si>
+    <t>开启一个绿到金色之间的宠物</t>
+  </si>
+  <si>
+    <t>蓝色宠蛋</t>
+  </si>
+  <si>
+    <t>开启一个蓝色到金色之间的宠物</t>
+  </si>
+  <si>
+    <t>紫色宠蛋</t>
+  </si>
+  <si>
+    <t>开启一个紫色到金色之间的宠物</t>
+  </si>
+  <si>
+    <t>橙色宠蛋</t>
+  </si>
+  <si>
+    <t>开启一个橙色到金色之间的宠物</t>
+  </si>
+  <si>
+    <t>红色宠蛋</t>
+  </si>
+  <si>
+    <t>开启一个红色到金色之间的宠物</t>
+  </si>
+  <si>
+    <t>金色宠蛋</t>
+  </si>
+  <si>
+    <t>开启一个金色宠物</t>
   </si>
   <si>
     <t>神鉴·白</t>
@@ -4884,7 +4926,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:M76"/>
+  <dimension ref="C3:M84"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="3"/>
@@ -7101,6 +7143,230 @@
         <v>0</v>
       </c>
       <c r="M76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="3:13">
+      <c r="C78" s="3">
+        <v>8201</v>
+      </c>
+      <c r="D78" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="E78" s="3">
+        <v>5</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="G78" s="3">
+        <v>1</v>
+      </c>
+      <c r="H78" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I78" s="3">
+        <v>0</v>
+      </c>
+      <c r="J78" s="3">
+        <v>1</v>
+      </c>
+      <c r="L78" s="3">
+        <v>0</v>
+      </c>
+      <c r="M78" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="3:13">
+      <c r="C79" s="3">
+        <v>8202</v>
+      </c>
+      <c r="D79" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="E79" s="3">
+        <v>5</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="G79" s="3">
+        <v>1</v>
+      </c>
+      <c r="H79" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I79" s="3">
+        <v>0</v>
+      </c>
+      <c r="J79" s="3">
+        <v>2</v>
+      </c>
+      <c r="L79" s="3">
+        <v>0</v>
+      </c>
+      <c r="M79" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="3:13">
+      <c r="C80" s="3">
+        <v>8203</v>
+      </c>
+      <c r="D80" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="E80" s="3">
+        <v>5</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="G80" s="3">
+        <v>1</v>
+      </c>
+      <c r="H80" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I80" s="3">
+        <v>0</v>
+      </c>
+      <c r="J80" s="3">
+        <v>3</v>
+      </c>
+      <c r="L80" s="3">
+        <v>0</v>
+      </c>
+      <c r="M80" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="3:13">
+      <c r="C81" s="3">
+        <v>8204</v>
+      </c>
+      <c r="D81" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="E81" s="3">
+        <v>5</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="G81" s="3">
+        <v>1</v>
+      </c>
+      <c r="H81" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I81" s="3">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3">
+        <v>4</v>
+      </c>
+      <c r="L81" s="3">
+        <v>0</v>
+      </c>
+      <c r="M81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="3:13">
+      <c r="C82" s="3">
+        <v>8205</v>
+      </c>
+      <c r="D82" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="E82" s="3">
+        <v>5</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="G82" s="3">
+        <v>1</v>
+      </c>
+      <c r="H82" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I82" s="3">
+        <v>0</v>
+      </c>
+      <c r="J82" s="3">
+        <v>5</v>
+      </c>
+      <c r="L82" s="3">
+        <v>0</v>
+      </c>
+      <c r="M82" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="3:13">
+      <c r="C83" s="3">
+        <v>8206</v>
+      </c>
+      <c r="D83" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="E83" s="3">
+        <v>5</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G83" s="3">
+        <v>1</v>
+      </c>
+      <c r="H83" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
+        <v>6</v>
+      </c>
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" customHeight="1" spans="3:13">
+      <c r="C84" s="3">
+        <v>8207</v>
+      </c>
+      <c r="D84" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="E84" s="3">
+        <v>5</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="G84" s="3">
+        <v>1</v>
+      </c>
+      <c r="H84" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I84" s="3">
+        <v>0</v>
+      </c>
+      <c r="J84" s="3">
+        <v>7</v>
+      </c>
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
         <v>0</v>
       </c>
     </row>
@@ -7248,13 +7514,13 @@
         <v>1999001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="E6" s="2">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -7276,13 +7542,13 @@
         <v>1999002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="E7" s="2">
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -7304,13 +7570,13 @@
         <v>1999003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="E8" s="2">
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -7332,13 +7598,13 @@
         <v>1999004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="E9" s="2">
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -7360,13 +7626,13 @@
         <v>1999005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="E10" s="2">
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -7388,13 +7654,13 @@
         <v>1999006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="E11" s="2">
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -7421,13 +7687,13 @@
         <v>1999989</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="E13" s="2">
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -7449,13 +7715,13 @@
         <v>1999990</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="E14" s="2">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -7477,13 +7743,13 @@
         <v>1999991</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="E15" s="2">
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -7505,13 +7771,13 @@
         <v>1999992</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="E16" s="2">
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -7533,13 +7799,13 @@
         <v>1999993</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="E17" s="2">
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -7561,13 +7827,13 @@
         <v>1999994</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="E18" s="2">
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -7589,13 +7855,13 @@
         <v>1999995</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="E19" s="2">
         <v>11</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -7617,13 +7883,13 @@
         <v>1999996</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="E20" s="2">
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -7645,13 +7911,13 @@
         <v>1999997</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="E21" s="2">
         <v>11</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -7673,13 +7939,13 @@
         <v>2000000</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="E22" s="2">
         <v>11</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -7701,13 +7967,13 @@
         <v>2000001</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="E23" s="2">
         <v>11</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -7729,13 +7995,13 @@
         <v>2000002</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E24" s="2">
         <v>11</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -7757,13 +8023,13 @@
         <v>2000003</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="E25" s="2">
         <v>11</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -7785,13 +8051,13 @@
         <v>2000004</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="E26" s="2">
         <v>11</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -7813,13 +8079,13 @@
         <v>2000005</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="E27" s="2">
         <v>11</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -7841,13 +8107,13 @@
         <v>2000006</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E28" s="2">
         <v>11</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -7869,13 +8135,13 @@
         <v>2000007</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="E29" s="2">
         <v>11</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -7897,13 +8163,13 @@
         <v>2000008</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="E30" s="2">
         <v>11</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -7925,13 +8191,13 @@
         <v>2000009</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="E31" s="2">
         <v>11</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -7953,13 +8219,13 @@
         <v>2000010</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="E32" s="2">
         <v>11</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -7981,13 +8247,13 @@
         <v>2000011</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="E33" s="2">
         <v>11</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -8009,13 +8275,13 @@
         <v>2000012</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="E34" s="2">
         <v>11</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -8037,13 +8303,13 @@
         <v>2000013</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="E35" s="2">
         <v>11</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -8077,13 +8343,13 @@
         <v>2000100</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="E39" s="2">
         <v>11</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -8105,13 +8371,13 @@
         <v>2000101</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="E40" s="2">
         <v>11</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -8133,13 +8399,13 @@
         <v>2000102</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="E41" s="2">
         <v>11</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -8161,13 +8427,13 @@
         <v>2000103</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="E42" s="2">
         <v>11</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -8189,13 +8455,13 @@
         <v>2000104</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="E43" s="2">
         <v>11</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -8217,13 +8483,13 @@
         <v>2000105</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="E44" s="2">
         <v>11</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -8245,13 +8511,13 @@
         <v>2000106</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="E45" s="2">
         <v>11</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G45" s="2">
         <v>1</v>
@@ -8273,13 +8539,13 @@
         <v>2000107</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="E46" s="2">
         <v>11</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -8301,13 +8567,13 @@
         <v>2000108</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="E47" s="2">
         <v>11</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -8329,13 +8595,13 @@
         <v>2000109</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="E48" s="2">
         <v>11</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -8357,13 +8623,13 @@
         <v>2000110</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="E49" s="2">
         <v>11</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -8385,13 +8651,13 @@
         <v>2000111</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="E50" s="2">
         <v>11</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -8413,13 +8679,13 @@
         <v>2000112</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="E51" s="2">
         <v>11</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -8441,13 +8707,13 @@
         <v>2000113</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="E52" s="2">
         <v>11</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -8469,13 +8735,13 @@
         <v>2000114</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="E53" s="2">
         <v>11</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G53" s="2">
         <v>1</v>
@@ -8497,13 +8763,13 @@
         <v>2000115</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="E54" s="2">
         <v>11</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G54" s="2">
         <v>1</v>
@@ -8525,13 +8791,13 @@
         <v>2000116</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="E55" s="2">
         <v>11</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G55" s="2">
         <v>1</v>
@@ -8553,13 +8819,13 @@
         <v>2000117</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="E56" s="2">
         <v>11</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G56" s="2">
         <v>1</v>
@@ -8581,13 +8847,13 @@
         <v>2000118</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="E57" s="2">
         <v>11</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G57" s="2">
         <v>1</v>
@@ -8609,13 +8875,13 @@
         <v>2000119</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="E58" s="2">
         <v>11</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G58" s="2">
         <v>1</v>
@@ -8637,13 +8903,13 @@
         <v>2000120</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="E59" s="2">
         <v>11</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G59" s="2">
         <v>1</v>
@@ -8665,13 +8931,13 @@
         <v>2000121</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="E60" s="2">
         <v>11</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G60" s="2">
         <v>1</v>
@@ -8693,13 +8959,13 @@
         <v>2000122</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="E61" s="2">
         <v>11</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G61" s="2">
         <v>1</v>
@@ -8721,13 +8987,13 @@
         <v>2000123</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="E62" s="2">
         <v>11</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G62" s="2">
         <v>1</v>
@@ -8749,13 +9015,13 @@
         <v>2000124</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="E63" s="2">
         <v>11</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G63" s="2">
         <v>1</v>
@@ -8777,13 +9043,13 @@
         <v>2000125</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="E64" s="2">
         <v>11</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G64" s="2">
         <v>1</v>
@@ -8805,13 +9071,13 @@
         <v>2000126</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="E65" s="2">
         <v>11</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G65" s="2">
         <v>1</v>
@@ -8833,13 +9099,13 @@
         <v>2000127</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="E66" s="2">
         <v>11</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G66" s="2">
         <v>1</v>
@@ -8861,13 +9127,13 @@
         <v>2000128</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="E67" s="2">
         <v>11</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G67" s="2">
         <v>1</v>
@@ -8889,13 +9155,13 @@
         <v>2000129</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="E68" s="2">
         <v>11</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G68" s="2">
         <v>1</v>
@@ -8917,13 +9183,13 @@
         <v>2000200</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="E70" s="2">
         <v>11</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G70" s="2">
         <v>1</v>
@@ -8943,13 +9209,13 @@
         <v>2000201</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="E71" s="2">
         <v>11</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G71" s="2">
         <v>1</v>
@@ -8969,13 +9235,13 @@
         <v>2000202</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E72" s="2">
         <v>11</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G72" s="2">
         <v>1</v>
@@ -8995,13 +9261,13 @@
         <v>2000203</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="E73" s="2">
         <v>11</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G73" s="2">
         <v>1</v>
@@ -9021,13 +9287,13 @@
         <v>2000204</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="E74" s="2">
         <v>11</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G74" s="2">
         <v>1</v>
@@ -9047,13 +9313,13 @@
         <v>2000205</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="E75" s="2">
         <v>11</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G75" s="2">
         <v>1</v>
@@ -9073,13 +9339,13 @@
         <v>2000206</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="E76" s="2">
         <v>11</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G76" s="2">
         <v>1</v>
@@ -9099,13 +9365,13 @@
         <v>2000207</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="E77" s="2">
         <v>11</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G77" s="2">
         <v>1</v>
@@ -9125,13 +9391,13 @@
         <v>2000208</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="E78" s="2">
         <v>11</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G78" s="2">
         <v>1</v>
@@ -9151,13 +9417,13 @@
         <v>2000209</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="E79" s="2">
         <v>11</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G79" s="2">
         <v>1</v>
@@ -9177,13 +9443,13 @@
         <v>2000210</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="E80" s="2">
         <v>11</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G80" s="2">
         <v>1</v>
@@ -9203,13 +9469,13 @@
         <v>2000211</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="E81" s="2">
         <v>11</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G81" s="2">
         <v>1</v>
@@ -9229,13 +9495,13 @@
         <v>2000212</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="E82" s="2">
         <v>11</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G82" s="2">
         <v>1</v>
@@ -9255,13 +9521,13 @@
         <v>2000213</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="E83" s="2">
         <v>11</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G83" s="2">
         <v>1</v>
@@ -9281,13 +9547,13 @@
         <v>2000214</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="E84" s="2">
         <v>11</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G84" s="2">
         <v>1</v>
@@ -9307,13 +9573,13 @@
         <v>2000215</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="E85" s="2">
         <v>11</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G85" s="2">
         <v>1</v>
@@ -9333,13 +9599,13 @@
         <v>2000216</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="E86" s="2">
         <v>11</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G86" s="2">
         <v>1</v>
@@ -9359,13 +9625,13 @@
         <v>2000217</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="E87" s="2">
         <v>11</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G87" s="2">
         <v>1</v>
@@ -9385,13 +9651,13 @@
         <v>2000218</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="E88" s="2">
         <v>11</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G88" s="2">
         <v>1</v>
@@ -9411,13 +9677,13 @@
         <v>2000219</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="E89" s="2">
         <v>11</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G89" s="2">
         <v>1</v>
@@ -9437,13 +9703,13 @@
         <v>2000220</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="E90" s="2">
         <v>11</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G90" s="2">
         <v>1</v>
@@ -9463,13 +9729,13 @@
         <v>2000221</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="E91" s="2">
         <v>11</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G91" s="2">
         <v>1</v>
@@ -9489,13 +9755,13 @@
         <v>2000222</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="E92" s="2">
         <v>11</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G92" s="2">
         <v>1</v>
@@ -9515,13 +9781,13 @@
         <v>2000223</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="E93" s="2">
         <v>11</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G93" s="2">
         <v>1</v>
@@ -9541,13 +9807,13 @@
         <v>2000224</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="E94" s="2">
         <v>11</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G94" s="2">
         <v>1</v>
@@ -9567,13 +9833,13 @@
         <v>2000225</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="E95" s="2">
         <v>11</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G95" s="2">
         <v>1</v>
@@ -9593,13 +9859,13 @@
         <v>2000226</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="E96" s="2">
         <v>11</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G96" s="2">
         <v>1</v>
@@ -9619,13 +9885,13 @@
         <v>2000227</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="E97" s="2">
         <v>11</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G97" s="2">
         <v>1</v>
@@ -9645,13 +9911,13 @@
         <v>2000228</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="E98" s="2">
         <v>11</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G98" s="2">
         <v>1</v>
@@ -9671,13 +9937,13 @@
         <v>2000229</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="E99" s="2">
         <v>11</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G99" s="2">
         <v>1</v>
@@ -9697,13 +9963,13 @@
         <v>2000300</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="E102" s="2">
         <v>11</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G102" s="2">
         <v>1</v>
@@ -9723,13 +9989,13 @@
         <v>2000301</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="E103" s="2">
         <v>11</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G103" s="2">
         <v>1</v>
@@ -9749,13 +10015,13 @@
         <v>2000302</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="E104" s="2">
         <v>11</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G104" s="2">
         <v>1</v>
@@ -9775,13 +10041,13 @@
         <v>2000303</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="E105" s="2">
         <v>11</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G105" s="2">
         <v>1</v>
@@ -9801,13 +10067,13 @@
         <v>2000304</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="E106" s="2">
         <v>11</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G106" s="2">
         <v>1</v>
@@ -9827,13 +10093,13 @@
         <v>2000305</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="E107" s="2">
         <v>11</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G107" s="2">
         <v>1</v>
@@ -9853,13 +10119,13 @@
         <v>2000306</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="E108" s="2">
         <v>11</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G108" s="2">
         <v>1</v>
@@ -9879,13 +10145,13 @@
         <v>2000307</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="E109" s="2">
         <v>11</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G109" s="2">
         <v>1</v>
@@ -9905,13 +10171,13 @@
         <v>2000308</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="E110" s="2">
         <v>11</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G110" s="2">
         <v>1</v>
@@ -9931,13 +10197,13 @@
         <v>2000309</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="E111" s="2">
         <v>11</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G111" s="2">
         <v>1</v>
@@ -9957,13 +10223,13 @@
         <v>2000310</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="E112" s="2">
         <v>11</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G112" s="2">
         <v>1</v>
@@ -9983,13 +10249,13 @@
         <v>2000311</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="E113" s="2">
         <v>11</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G113" s="2">
         <v>1</v>
@@ -10009,13 +10275,13 @@
         <v>2000312</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="E114" s="2">
         <v>11</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G114" s="2">
         <v>1</v>
@@ -10035,13 +10301,13 @@
         <v>2000313</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="E115" s="2">
         <v>11</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G115" s="2">
         <v>1</v>
@@ -10061,13 +10327,13 @@
         <v>2000314</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="E116" s="2">
         <v>11</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G116" s="2">
         <v>1</v>
@@ -10087,13 +10353,13 @@
         <v>2000315</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="E117" s="2">
         <v>11</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G117" s="2">
         <v>1</v>
@@ -10113,13 +10379,13 @@
         <v>2000316</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="E118" s="2">
         <v>11</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G118" s="2">
         <v>1</v>
@@ -10139,13 +10405,13 @@
         <v>2000317</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="E119" s="2">
         <v>11</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G119" s="2">
         <v>1</v>
@@ -10165,13 +10431,13 @@
         <v>2000318</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="E120" s="2">
         <v>11</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G120" s="2">
         <v>1</v>
@@ -10191,13 +10457,13 @@
         <v>2000319</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="E121" s="2">
         <v>11</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G121" s="2">
         <v>1</v>
@@ -10217,13 +10483,13 @@
         <v>2000320</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="E122" s="2">
         <v>11</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G122" s="2">
         <v>1</v>
@@ -10243,13 +10509,13 @@
         <v>2000321</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="E123" s="2">
         <v>11</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G123" s="2">
         <v>1</v>
@@ -10269,13 +10535,13 @@
         <v>2000322</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="E124" s="2">
         <v>11</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G124" s="2">
         <v>1</v>
@@ -10295,13 +10561,13 @@
         <v>2000323</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="E125" s="2">
         <v>11</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G125" s="2">
         <v>1</v>
@@ -10321,13 +10587,13 @@
         <v>2000324</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="E126" s="2">
         <v>11</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G126" s="2">
         <v>1</v>
@@ -10347,13 +10613,13 @@
         <v>2000325</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="E127" s="2">
         <v>11</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G127" s="2">
         <v>1</v>
@@ -10373,13 +10639,13 @@
         <v>2000326</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="E128" s="2">
         <v>11</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G128" s="2">
         <v>1</v>
@@ -10399,13 +10665,13 @@
         <v>2000327</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="E129" s="2">
         <v>11</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G129" s="2">
         <v>1</v>
@@ -10425,13 +10691,13 @@
         <v>2000328</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="E130" s="2">
         <v>11</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G130" s="2">
         <v>1</v>
@@ -10451,13 +10717,13 @@
         <v>2000329</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="E131" s="2">
         <v>11</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G131" s="2">
         <v>1</v>
@@ -10616,13 +10882,13 @@
         <v>3000001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="E6" s="2">
         <v>13</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -10644,13 +10910,13 @@
         <v>3000002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="E7" s="2">
         <v>13</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -10672,13 +10938,13 @@
         <v>3000003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="E8" s="2">
         <v>13</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -10700,13 +10966,13 @@
         <v>3000004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="E9" s="2">
         <v>13</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -10728,13 +10994,13 @@
         <v>3000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="E10" s="2">
         <v>13</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -10756,13 +11022,13 @@
         <v>3000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="E11" s="2">
         <v>13</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -10784,13 +11050,13 @@
         <v>3000007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="E12" s="2">
         <v>13</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -10812,13 +11078,13 @@
         <v>3000008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="E13" s="2">
         <v>13</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -10840,13 +11106,13 @@
         <v>3000009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>369</v>
+        <v>383</v>
       </c>
       <c r="E14" s="2">
         <v>13</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -10868,13 +11134,13 @@
         <v>3000010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>370</v>
+        <v>384</v>
       </c>
       <c r="E15" s="2">
         <v>13</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -10896,13 +11162,13 @@
         <v>3000011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>371</v>
+        <v>385</v>
       </c>
       <c r="E16" s="2">
         <v>13</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -10924,13 +11190,13 @@
         <v>3000012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>372</v>
+        <v>386</v>
       </c>
       <c r="E17" s="2">
         <v>13</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -10952,13 +11218,13 @@
         <v>3000013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="E18" s="2">
         <v>13</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -10980,13 +11246,13 @@
         <v>3000014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>374</v>
+        <v>388</v>
       </c>
       <c r="E19" s="2">
         <v>13</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -11008,13 +11274,13 @@
         <v>3000015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>375</v>
+        <v>389</v>
       </c>
       <c r="E20" s="2">
         <v>13</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -11036,13 +11302,13 @@
         <v>3000016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="E21" s="2">
         <v>13</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -11064,13 +11330,13 @@
         <v>3000017</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="E22" s="2">
         <v>13</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -11092,13 +11358,13 @@
         <v>3000018</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="E23" s="2">
         <v>13</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -11120,13 +11386,13 @@
         <v>3000019</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="E24" s="2">
         <v>13</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -11148,13 +11414,13 @@
         <v>3000020</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="E25" s="2">
         <v>13</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -11176,13 +11442,13 @@
         <v>3000021</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="E26" s="2">
         <v>13</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -11204,13 +11470,13 @@
         <v>3000022</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="E27" s="2">
         <v>13</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -11232,13 +11498,13 @@
         <v>3000023</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="E28" s="2">
         <v>13</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -11260,13 +11526,13 @@
         <v>3000024</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="E29" s="2">
         <v>13</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -11288,13 +11554,13 @@
         <v>3000025</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="E30" s="2">
         <v>13</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -11316,13 +11582,13 @@
         <v>3000026</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="E31" s="2">
         <v>13</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -11344,13 +11610,13 @@
         <v>3000027</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="E32" s="2">
         <v>13</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -11372,13 +11638,13 @@
         <v>3000028</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="E33" s="2">
         <v>13</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -11400,13 +11666,13 @@
         <v>3000029</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="E34" s="2">
         <v>13</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -11428,13 +11694,13 @@
         <v>3000030</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="E35" s="2">
         <v>13</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -11456,13 +11722,13 @@
         <v>3000031</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="E36" s="2">
         <v>13</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -11484,13 +11750,13 @@
         <v>3000032</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="E37" s="2">
         <v>13</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G37" s="2">
         <v>1</v>
@@ -11512,13 +11778,13 @@
         <v>3000033</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="E38" s="2">
         <v>13</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G38" s="2">
         <v>1</v>
@@ -11540,13 +11806,13 @@
         <v>3000034</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="E39" s="2">
         <v>13</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -11568,13 +11834,13 @@
         <v>3000035</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="E40" s="2">
         <v>13</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -11596,13 +11862,13 @@
         <v>3000036</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="E41" s="2">
         <v>13</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -11624,13 +11890,13 @@
         <v>3000037</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>397</v>
+        <v>411</v>
       </c>
       <c r="E42" s="2">
         <v>13</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -11652,13 +11918,13 @@
         <v>3000038</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="E43" s="2">
         <v>13</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -11680,13 +11946,13 @@
         <v>3000039</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="E44" s="2">
         <v>13</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -11708,13 +11974,13 @@
         <v>3000040</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>400</v>
+        <v>414</v>
       </c>
       <c r="E45" s="2">
         <v>13</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G45" s="2">
         <v>1</v>
@@ -11736,13 +12002,13 @@
         <v>3000041</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>401</v>
+        <v>415</v>
       </c>
       <c r="E46" s="2">
         <v>13</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -11764,13 +12030,13 @@
         <v>3000042</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="E47" s="2">
         <v>13</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -11792,13 +12058,13 @@
         <v>3000043</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="E48" s="2">
         <v>13</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -11820,13 +12086,13 @@
         <v>3000044</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="E49" s="2">
         <v>13</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -11848,13 +12114,13 @@
         <v>3000045</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="E50" s="2">
         <v>13</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -11876,13 +12142,13 @@
         <v>3000046</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="E51" s="2">
         <v>13</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -11904,13 +12170,13 @@
         <v>3000047</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="E52" s="2">
         <v>13</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -11932,13 +12198,13 @@
         <v>3000048</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="E53" s="2">
         <v>13</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="G53" s="2">
         <v>1</v>
@@ -12097,13 +12363,13 @@
         <v>40000051</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="E7" s="2">
         <v>14</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -12129,13 +12395,13 @@
         <v>40000052</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="E8" s="2">
         <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -12161,13 +12427,13 @@
         <v>40000053</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="E9" s="2">
         <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -12193,13 +12459,13 @@
         <v>40000054</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="E10" s="2">
         <v>14</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -12225,13 +12491,13 @@
         <v>40000055</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="E11" s="2">
         <v>14</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -12257,13 +12523,13 @@
         <v>40000056</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>415</v>
+        <v>429</v>
       </c>
       <c r="E12" s="2">
         <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -12289,13 +12555,13 @@
         <v>40000057</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="E13" s="2">
         <v>14</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -12321,13 +12587,13 @@
         <v>40000058</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>417</v>
+        <v>431</v>
       </c>
       <c r="E14" s="2">
         <v>14</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -12353,13 +12619,13 @@
         <v>40000059</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="E15" s="2">
         <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -12385,13 +12651,13 @@
         <v>40000060</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="E16" s="2">
         <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -12417,13 +12683,13 @@
         <v>40000061</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="E17" s="2">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -12449,13 +12715,13 @@
         <v>40000062</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="E18" s="2">
         <v>14</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -12481,13 +12747,13 @@
         <v>40000063</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="E19" s="2">
         <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -12513,13 +12779,13 @@
         <v>40000064</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>423</v>
+        <v>437</v>
       </c>
       <c r="E20" s="2">
         <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -12545,13 +12811,13 @@
         <v>40000065</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="E21" s="2">
         <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -12577,13 +12843,13 @@
         <v>40000066</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="E22" s="2">
         <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -12609,13 +12875,13 @@
         <v>40000067</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>426</v>
+        <v>440</v>
       </c>
       <c r="E23" s="2">
         <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -12641,13 +12907,13 @@
         <v>40000068</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="E24" s="2">
         <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -12673,13 +12939,13 @@
         <v>40000069</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>428</v>
+        <v>442</v>
       </c>
       <c r="E25" s="2">
         <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -12705,13 +12971,13 @@
         <v>40000070</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>429</v>
+        <v>443</v>
       </c>
       <c r="E26" s="2">
         <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -12737,13 +13003,13 @@
         <v>40000071</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="E27" s="2">
         <v>14</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -12769,13 +13035,13 @@
         <v>40000072</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>431</v>
+        <v>445</v>
       </c>
       <c r="E28" s="2">
         <v>14</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -12801,13 +13067,13 @@
         <v>40000073</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>432</v>
+        <v>446</v>
       </c>
       <c r="E29" s="2">
         <v>14</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -12833,13 +13099,13 @@
         <v>40000074</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>433</v>
+        <v>447</v>
       </c>
       <c r="E30" s="2">
         <v>14</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -12865,13 +13131,13 @@
         <v>40000075</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>434</v>
+        <v>448</v>
       </c>
       <c r="E31" s="2">
         <v>14</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -12897,13 +13163,13 @@
         <v>40000076</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="E32" s="2">
         <v>14</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -12929,13 +13195,13 @@
         <v>40000077</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="E33" s="2">
         <v>14</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -12961,13 +13227,13 @@
         <v>40000078</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>437</v>
+        <v>451</v>
       </c>
       <c r="E34" s="2">
         <v>14</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -12993,13 +13259,13 @@
         <v>40000079</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>438</v>
+        <v>452</v>
       </c>
       <c r="E35" s="2">
         <v>14</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -13025,13 +13291,13 @@
         <v>40000080</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>439</v>
+        <v>453</v>
       </c>
       <c r="E36" s="2">
         <v>14</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -13057,13 +13323,13 @@
         <v>40000081</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>440</v>
+        <v>454</v>
       </c>
       <c r="E37" s="2">
         <v>14</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G37" s="2">
         <v>1</v>
@@ -13089,13 +13355,13 @@
         <v>40000082</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>441</v>
+        <v>455</v>
       </c>
       <c r="E38" s="2">
         <v>14</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G38" s="2">
         <v>1</v>
@@ -13121,13 +13387,13 @@
         <v>40000083</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>442</v>
+        <v>456</v>
       </c>
       <c r="E39" s="2">
         <v>14</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -13153,13 +13419,13 @@
         <v>40000084</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>443</v>
+        <v>457</v>
       </c>
       <c r="E40" s="2">
         <v>14</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -13185,13 +13451,13 @@
         <v>40000085</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="E41" s="2">
         <v>14</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -13217,13 +13483,13 @@
         <v>40000086</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E42" s="2">
         <v>14</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -13249,13 +13515,13 @@
         <v>40000087</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="E43" s="2">
         <v>14</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -13281,13 +13547,13 @@
         <v>40000088</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>447</v>
+        <v>461</v>
       </c>
       <c r="E44" s="2">
         <v>14</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -13313,13 +13579,13 @@
         <v>40000089</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>448</v>
+        <v>462</v>
       </c>
       <c r="E45" s="2">
         <v>14</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G45" s="2">
         <v>1</v>
@@ -13345,13 +13611,13 @@
         <v>40000090</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="E46" s="2">
         <v>14</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -13377,13 +13643,13 @@
         <v>40000091</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="E47" s="2">
         <v>14</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -13409,13 +13675,13 @@
         <v>40000092</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>451</v>
+        <v>465</v>
       </c>
       <c r="E48" s="2">
         <v>14</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -13441,13 +13707,13 @@
         <v>40000093</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>452</v>
+        <v>466</v>
       </c>
       <c r="E49" s="2">
         <v>14</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -13473,13 +13739,13 @@
         <v>40000094</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>453</v>
+        <v>467</v>
       </c>
       <c r="E50" s="2">
         <v>14</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -13505,13 +13771,13 @@
         <v>40000095</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>454</v>
+        <v>468</v>
       </c>
       <c r="E51" s="2">
         <v>14</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -13537,13 +13803,13 @@
         <v>40000096</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>455</v>
+        <v>469</v>
       </c>
       <c r="E52" s="2">
         <v>14</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -13569,13 +13835,13 @@
         <v>40000097</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>456</v>
+        <v>470</v>
       </c>
       <c r="E53" s="2">
         <v>14</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G53" s="2">
         <v>1</v>
@@ -13601,13 +13867,13 @@
         <v>40000098</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="E54" s="2">
         <v>14</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G54" s="2">
         <v>1</v>
@@ -13633,13 +13899,13 @@
         <v>40000099</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>458</v>
+        <v>472</v>
       </c>
       <c r="E55" s="2">
         <v>14</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G55" s="2">
         <v>1</v>
@@ -13665,13 +13931,13 @@
         <v>40000100</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>459</v>
+        <v>473</v>
       </c>
       <c r="E56" s="2">
         <v>14</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G56" s="2">
         <v>1</v>
@@ -13697,13 +13963,13 @@
         <v>40000101</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>460</v>
+        <v>474</v>
       </c>
       <c r="E57" s="2">
         <v>14</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G57" s="2">
         <v>1</v>
@@ -13729,13 +13995,13 @@
         <v>40000102</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>461</v>
+        <v>475</v>
       </c>
       <c r="E58" s="2">
         <v>14</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G58" s="2">
         <v>1</v>
@@ -13761,13 +14027,13 @@
         <v>40000103</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="E59" s="2">
         <v>14</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G59" s="2">
         <v>1</v>
@@ -13793,13 +14059,13 @@
         <v>40000104</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>463</v>
+        <v>477</v>
       </c>
       <c r="E60" s="2">
         <v>14</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G60" s="2">
         <v>1</v>
@@ -13825,13 +14091,13 @@
         <v>40000105</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="E61" s="7">
         <v>14</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G61" s="7">
         <v>1</v>
@@ -13858,13 +14124,13 @@
         <v>40000106</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>465</v>
+        <v>479</v>
       </c>
       <c r="E62" s="2">
         <v>14</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G62" s="2">
         <v>1</v>
@@ -13891,13 +14157,13 @@
         <v>40000107</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="E63" s="2">
         <v>14</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G63" s="2">
         <v>1</v>
@@ -13924,13 +14190,13 @@
         <v>40000108</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>467</v>
+        <v>481</v>
       </c>
       <c r="E64" s="2">
         <v>14</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G64" s="2">
         <v>1</v>
@@ -13957,13 +14223,13 @@
         <v>40000109</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>468</v>
+        <v>482</v>
       </c>
       <c r="E65" s="2">
         <v>14</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G65" s="2">
         <v>1</v>
@@ -13990,13 +14256,13 @@
         <v>40000110</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>469</v>
+        <v>483</v>
       </c>
       <c r="E66" s="2">
         <v>14</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G66" s="2">
         <v>1</v>
@@ -14023,13 +14289,13 @@
         <v>40000111</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="E67" s="2">
         <v>14</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G67" s="2">
         <v>1</v>
@@ -14056,13 +14322,13 @@
         <v>40000112</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>471</v>
+        <v>485</v>
       </c>
       <c r="E68" s="2">
         <v>14</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G68" s="2">
         <v>1</v>
@@ -14089,13 +14355,13 @@
         <v>40000113</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>472</v>
+        <v>486</v>
       </c>
       <c r="E69" s="2">
         <v>14</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G69" s="2">
         <v>1</v>
@@ -14122,13 +14388,13 @@
         <v>40000114</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>473</v>
+        <v>487</v>
       </c>
       <c r="E70" s="2">
         <v>14</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G70" s="2">
         <v>1</v>
@@ -14155,13 +14421,13 @@
         <v>40000115</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>474</v>
+        <v>488</v>
       </c>
       <c r="E71" s="2">
         <v>14</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G71" s="2">
         <v>1</v>
@@ -14188,13 +14454,13 @@
         <v>40000116</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>475</v>
+        <v>489</v>
       </c>
       <c r="E72" s="2">
         <v>14</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G72" s="2">
         <v>1</v>
@@ -14221,13 +14487,13 @@
         <v>40000117</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>476</v>
+        <v>490</v>
       </c>
       <c r="E73" s="2">
         <v>14</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G73" s="2">
         <v>1</v>
@@ -14254,13 +14520,13 @@
         <v>40000118</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>477</v>
+        <v>491</v>
       </c>
       <c r="E74" s="2">
         <v>14</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G74" s="2">
         <v>1</v>
@@ -14287,13 +14553,13 @@
         <v>40000119</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>478</v>
+        <v>492</v>
       </c>
       <c r="E75" s="2">
         <v>14</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G75" s="2">
         <v>1</v>
@@ -14320,13 +14586,13 @@
         <v>40000120</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>479</v>
+        <v>493</v>
       </c>
       <c r="E76" s="2">
         <v>14</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G76" s="2">
         <v>1</v>
@@ -14353,13 +14619,13 @@
         <v>40000121</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>480</v>
+        <v>494</v>
       </c>
       <c r="E77" s="2">
         <v>14</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G77" s="2">
         <v>1</v>
@@ -14386,13 +14652,13 @@
         <v>40000122</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>481</v>
+        <v>495</v>
       </c>
       <c r="E78" s="2">
         <v>14</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G78" s="2">
         <v>1</v>
@@ -14419,13 +14685,13 @@
         <v>40000123</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>482</v>
+        <v>496</v>
       </c>
       <c r="E79" s="2">
         <v>14</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G79" s="2">
         <v>1</v>
@@ -14452,13 +14718,13 @@
         <v>40000124</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>483</v>
+        <v>497</v>
       </c>
       <c r="E80" s="2">
         <v>14</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G80" s="2">
         <v>1</v>
@@ -14485,13 +14751,13 @@
         <v>40000125</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>484</v>
+        <v>498</v>
       </c>
       <c r="E81" s="2">
         <v>14</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G81" s="2">
         <v>1</v>
@@ -14517,13 +14783,13 @@
         <v>40000126</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>485</v>
+        <v>499</v>
       </c>
       <c r="E82" s="2">
         <v>14</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G82" s="2">
         <v>1</v>
@@ -14549,13 +14815,13 @@
         <v>40000127</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>486</v>
+        <v>500</v>
       </c>
       <c r="E83" s="2">
         <v>14</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G83" s="2">
         <v>1</v>
@@ -14581,13 +14847,13 @@
         <v>40000128</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>487</v>
+        <v>501</v>
       </c>
       <c r="E84" s="2">
         <v>14</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G84" s="2">
         <v>1</v>
@@ -14613,13 +14879,13 @@
         <v>40000129</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>488</v>
+        <v>502</v>
       </c>
       <c r="E85" s="2">
         <v>14</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G85" s="2">
         <v>1</v>
@@ -14645,13 +14911,13 @@
         <v>40000130</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>489</v>
+        <v>503</v>
       </c>
       <c r="E86" s="2">
         <v>14</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G86" s="2">
         <v>1</v>
@@ -14677,13 +14943,13 @@
         <v>40000131</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>490</v>
+        <v>504</v>
       </c>
       <c r="E87" s="2">
         <v>14</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G87" s="2">
         <v>1</v>
@@ -14709,13 +14975,13 @@
         <v>40000132</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>491</v>
+        <v>505</v>
       </c>
       <c r="E88" s="2">
         <v>14</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G88" s="2">
         <v>1</v>
@@ -14741,13 +15007,13 @@
         <v>40000133</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>492</v>
+        <v>506</v>
       </c>
       <c r="E89" s="2">
         <v>14</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G89" s="2">
         <v>1</v>
@@ -14773,13 +15039,13 @@
         <v>40000134</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>493</v>
+        <v>507</v>
       </c>
       <c r="E90" s="2">
         <v>14</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G90" s="2">
         <v>1</v>
@@ -14805,13 +15071,13 @@
         <v>40000135</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>494</v>
+        <v>508</v>
       </c>
       <c r="E91" s="2">
         <v>14</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G91" s="2">
         <v>1</v>
@@ -14837,13 +15103,13 @@
         <v>40000136</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>495</v>
+        <v>509</v>
       </c>
       <c r="E92" s="2">
         <v>14</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G92" s="2">
         <v>1</v>
@@ -14869,13 +15135,13 @@
         <v>40000137</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>496</v>
+        <v>510</v>
       </c>
       <c r="E93" s="2">
         <v>14</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G93" s="2">
         <v>1</v>
@@ -14901,13 +15167,13 @@
         <v>40000138</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>497</v>
+        <v>511</v>
       </c>
       <c r="E94" s="2">
         <v>14</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G94" s="2">
         <v>1</v>
@@ -14933,13 +15199,13 @@
         <v>40000139</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>498</v>
+        <v>512</v>
       </c>
       <c r="E95" s="2">
         <v>14</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="G95" s="2">
         <v>1</v>
@@ -15104,13 +15370,13 @@
         <v>50000001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>499</v>
+        <v>513</v>
       </c>
       <c r="E6" s="2">
         <v>5</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -15136,13 +15402,13 @@
         <v>50000002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>501</v>
+        <v>515</v>
       </c>
       <c r="E7" s="2">
         <v>5</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>502</v>
+        <v>516</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -15168,13 +15434,13 @@
         <v>50000003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>503</v>
+        <v>517</v>
       </c>
       <c r="E8" s="2">
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>504</v>
+        <v>518</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -15200,13 +15466,13 @@
         <v>50000004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="E9" s="2">
         <v>5</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -15232,13 +15498,13 @@
         <v>50000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>507</v>
+        <v>521</v>
       </c>
       <c r="E10" s="2">
         <v>5</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -15264,13 +15530,13 @@
         <v>50000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E11" s="2">
         <v>5</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>510</v>
+        <v>524</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -15296,13 +15562,13 @@
         <v>50000007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>511</v>
+        <v>525</v>
       </c>
       <c r="E12" s="2">
         <v>5</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>512</v>
+        <v>526</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -15328,13 +15594,13 @@
         <v>50000008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>513</v>
+        <v>527</v>
       </c>
       <c r="E13" s="2">
         <v>5</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>514</v>
+        <v>528</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -15360,13 +15626,13 @@
         <v>50000009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>515</v>
+        <v>529</v>
       </c>
       <c r="E14" s="2">
         <v>5</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>516</v>
+        <v>530</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -15392,13 +15658,13 @@
         <v>50000010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>517</v>
+        <v>531</v>
       </c>
       <c r="E15" s="2">
         <v>5</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -15424,13 +15690,13 @@
         <v>50000011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>519</v>
+        <v>533</v>
       </c>
       <c r="E16" s="2">
         <v>5</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>520</v>
+        <v>534</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -15456,13 +15722,13 @@
         <v>50000012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>521</v>
+        <v>535</v>
       </c>
       <c r="E17" s="2">
         <v>5</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>522</v>
+        <v>536</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -15488,13 +15754,13 @@
         <v>50000013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>523</v>
+        <v>537</v>
       </c>
       <c r="E18" s="2">
         <v>5</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>524</v>
+        <v>538</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -15520,13 +15786,13 @@
         <v>50000014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>525</v>
+        <v>539</v>
       </c>
       <c r="E19" s="2">
         <v>5</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>526</v>
+        <v>540</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -15552,13 +15818,13 @@
         <v>50000015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>527</v>
+        <v>541</v>
       </c>
       <c r="E20" s="2">
         <v>5</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>528</v>
+        <v>542</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -15584,13 +15850,13 @@
         <v>50000016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>529</v>
+        <v>543</v>
       </c>
       <c r="E21" s="2">
         <v>5</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>530</v>
+        <v>544</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -15616,13 +15882,13 @@
         <v>50000017</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>531</v>
+        <v>545</v>
       </c>
       <c r="E22" s="2">
         <v>5</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>532</v>
+        <v>546</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -15648,13 +15914,13 @@
         <v>50000018</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>533</v>
+        <v>547</v>
       </c>
       <c r="E23" s="2">
         <v>5</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>534</v>
+        <v>548</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -15680,13 +15946,13 @@
         <v>50000019</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>535</v>
+        <v>549</v>
       </c>
       <c r="E24" s="2">
         <v>5</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>536</v>
+        <v>550</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -15712,13 +15978,13 @@
         <v>50000020</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>537</v>
+        <v>551</v>
       </c>
       <c r="E25" s="2">
         <v>5</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>538</v>
+        <v>552</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -15744,13 +16010,13 @@
         <v>50000021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>539</v>
+        <v>553</v>
       </c>
       <c r="E26" s="2">
         <v>5</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>540</v>
+        <v>554</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -15776,13 +16042,13 @@
         <v>50000022</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>541</v>
+        <v>555</v>
       </c>
       <c r="E27" s="2">
         <v>5</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>542</v>
+        <v>556</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -15808,13 +16074,13 @@
         <v>50000023</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>543</v>
+        <v>557</v>
       </c>
       <c r="E28" s="2">
         <v>5</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>544</v>
+        <v>558</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -15840,13 +16106,13 @@
         <v>50000024</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>545</v>
+        <v>559</v>
       </c>
       <c r="E29" s="2">
         <v>5</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>546</v>
+        <v>560</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -15872,13 +16138,13 @@
         <v>50000025</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>547</v>
+        <v>561</v>
       </c>
       <c r="E30" s="2">
         <v>5</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>548</v>
+        <v>562</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -15904,13 +16170,13 @@
         <v>50000026</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>549</v>
+        <v>563</v>
       </c>
       <c r="E31" s="2">
         <v>5</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>550</v>
+        <v>564</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -15936,13 +16202,13 @@
         <v>50000027</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>551</v>
+        <v>565</v>
       </c>
       <c r="E32" s="2">
         <v>5</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>552</v>
+        <v>566</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -15968,13 +16234,13 @@
         <v>50000028</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>553</v>
+        <v>567</v>
       </c>
       <c r="E33" s="2">
         <v>5</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>554</v>
+        <v>568</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -16000,13 +16266,13 @@
         <v>50000029</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>555</v>
+        <v>569</v>
       </c>
       <c r="E34" s="2">
         <v>5</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>556</v>
+        <v>570</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -16032,13 +16298,13 @@
         <v>50000030</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>557</v>
+        <v>571</v>
       </c>
       <c r="E35" s="2">
         <v>5</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>558</v>
+        <v>572</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -16064,13 +16330,13 @@
         <v>50000031</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>559</v>
+        <v>573</v>
       </c>
       <c r="E36" s="2">
         <v>5</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>560</v>
+        <v>574</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -16096,13 +16362,13 @@
         <v>50000032</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>561</v>
+        <v>575</v>
       </c>
       <c r="E37" s="2">
         <v>5</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>562</v>
+        <v>576</v>
       </c>
       <c r="G37" s="2">
         <v>1</v>
@@ -16128,13 +16394,13 @@
         <v>50000033</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>563</v>
+        <v>577</v>
       </c>
       <c r="E38" s="2">
         <v>5</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>564</v>
+        <v>578</v>
       </c>
       <c r="G38" s="2">
         <v>1</v>
@@ -16160,13 +16426,13 @@
         <v>50000034</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>565</v>
+        <v>579</v>
       </c>
       <c r="E39" s="2">
         <v>5</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>566</v>
+        <v>580</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -16192,13 +16458,13 @@
         <v>50000035</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>567</v>
+        <v>581</v>
       </c>
       <c r="E40" s="2">
         <v>5</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>568</v>
+        <v>582</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -16224,13 +16490,13 @@
         <v>50000036</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>569</v>
+        <v>583</v>
       </c>
       <c r="E41" s="2">
         <v>5</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>570</v>
+        <v>584</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -16256,13 +16522,13 @@
         <v>50000037</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>571</v>
+        <v>585</v>
       </c>
       <c r="E42" s="2">
         <v>5</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>572</v>
+        <v>586</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -16288,13 +16554,13 @@
         <v>50000038</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>573</v>
+        <v>587</v>
       </c>
       <c r="E43" s="2">
         <v>5</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>574</v>
+        <v>588</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -16320,13 +16586,13 @@
         <v>50000039</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>575</v>
+        <v>589</v>
       </c>
       <c r="E44" s="2">
         <v>5</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>576</v>
+        <v>590</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -16352,13 +16618,13 @@
         <v>50000040</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>577</v>
+        <v>591</v>
       </c>
       <c r="E45" s="2">
         <v>5</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>578</v>
+        <v>592</v>
       </c>
       <c r="G45" s="2">
         <v>1</v>
@@ -16384,13 +16650,13 @@
         <v>50000041</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>579</v>
+        <v>593</v>
       </c>
       <c r="E46" s="2">
         <v>5</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>580</v>
+        <v>594</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -16416,13 +16682,13 @@
         <v>50000042</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>581</v>
+        <v>595</v>
       </c>
       <c r="E47" s="2">
         <v>5</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>582</v>
+        <v>596</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -16448,13 +16714,13 @@
         <v>50000043</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>583</v>
+        <v>597</v>
       </c>
       <c r="E48" s="2">
         <v>5</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>584</v>
+        <v>598</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -16480,13 +16746,13 @@
         <v>50000044</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>585</v>
+        <v>599</v>
       </c>
       <c r="E49" s="2">
         <v>5</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>586</v>
+        <v>600</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -16512,13 +16778,13 @@
         <v>50000045</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>587</v>
+        <v>601</v>
       </c>
       <c r="E50" s="2">
         <v>5</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>588</v>
+        <v>602</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -16544,13 +16810,13 @@
         <v>50000046</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>589</v>
+        <v>603</v>
       </c>
       <c r="E51" s="2">
         <v>5</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>590</v>
+        <v>604</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -16576,13 +16842,13 @@
         <v>50000047</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>591</v>
+        <v>605</v>
       </c>
       <c r="E52" s="2">
         <v>5</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>592</v>
+        <v>606</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -16608,13 +16874,13 @@
         <v>50000048</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>593</v>
+        <v>607</v>
       </c>
       <c r="E53" s="2">
         <v>5</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>594</v>
+        <v>608</v>
       </c>
       <c r="G53" s="2">
         <v>1</v>
@@ -16640,13 +16906,13 @@
         <v>50000049</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>595</v>
+        <v>609</v>
       </c>
       <c r="E54" s="2">
         <v>5</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>596</v>
+        <v>610</v>
       </c>
       <c r="G54" s="2">
         <v>1</v>
@@ -16672,13 +16938,13 @@
         <v>50000050</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>597</v>
+        <v>611</v>
       </c>
       <c r="E55" s="2">
         <v>5</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>598</v>
+        <v>612</v>
       </c>
       <c r="G55" s="2">
         <v>1</v>
@@ -16704,13 +16970,13 @@
         <v>50000051</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>599</v>
+        <v>613</v>
       </c>
       <c r="E56" s="2">
         <v>5</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>600</v>
+        <v>614</v>
       </c>
       <c r="G56" s="2">
         <v>1</v>
@@ -16736,13 +17002,13 @@
         <v>50000052</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>601</v>
+        <v>615</v>
       </c>
       <c r="E57" s="2">
         <v>5</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>602</v>
+        <v>616</v>
       </c>
       <c r="G57" s="2">
         <v>1</v>
@@ -16768,13 +17034,13 @@
         <v>50000053</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>603</v>
+        <v>617</v>
       </c>
       <c r="E58" s="2">
         <v>5</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>604</v>
+        <v>618</v>
       </c>
       <c r="G58" s="2">
         <v>1</v>
@@ -16800,13 +17066,13 @@
         <v>50000054</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>605</v>
+        <v>619</v>
       </c>
       <c r="E59" s="2">
         <v>5</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>606</v>
+        <v>620</v>
       </c>
       <c r="G59" s="2">
         <v>1</v>
@@ -16832,13 +17098,13 @@
         <v>50000055</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>607</v>
+        <v>621</v>
       </c>
       <c r="E60" s="2">
         <v>5</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>608</v>
+        <v>622</v>
       </c>
       <c r="G60" s="2">
         <v>1</v>
@@ -16864,13 +17130,13 @@
         <v>50000056</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>609</v>
+        <v>623</v>
       </c>
       <c r="E61" s="2">
         <v>5</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>610</v>
+        <v>624</v>
       </c>
       <c r="G61" s="2">
         <v>1</v>
@@ -16896,13 +17162,13 @@
         <v>50000057</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>611</v>
+        <v>625</v>
       </c>
       <c r="E62" s="2">
         <v>5</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>612</v>
+        <v>626</v>
       </c>
       <c r="G62" s="2">
         <v>1</v>
@@ -16928,13 +17194,13 @@
         <v>50000058</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>613</v>
+        <v>627</v>
       </c>
       <c r="E63" s="2">
         <v>5</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>614</v>
+        <v>628</v>
       </c>
       <c r="G63" s="2">
         <v>1</v>
@@ -16960,13 +17226,13 @@
         <v>50000059</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>615</v>
+        <v>629</v>
       </c>
       <c r="E64" s="2">
         <v>5</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>616</v>
+        <v>630</v>
       </c>
       <c r="G64" s="2">
         <v>1</v>
@@ -16992,13 +17258,13 @@
         <v>50000060</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>617</v>
+        <v>631</v>
       </c>
       <c r="E65" s="2">
         <v>5</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>618</v>
+        <v>632</v>
       </c>
       <c r="G65" s="2">
         <v>1</v>
@@ -17024,13 +17290,13 @@
         <v>50000061</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>619</v>
+        <v>633</v>
       </c>
       <c r="E66" s="2">
         <v>5</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>620</v>
+        <v>634</v>
       </c>
       <c r="G66" s="2">
         <v>1</v>
@@ -17056,13 +17322,13 @@
         <v>50000062</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>621</v>
+        <v>635</v>
       </c>
       <c r="E67" s="2">
         <v>5</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>622</v>
+        <v>636</v>
       </c>
       <c r="G67" s="2">
         <v>1</v>
@@ -17088,13 +17354,13 @@
         <v>50000063</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>623</v>
+        <v>637</v>
       </c>
       <c r="E68" s="2">
         <v>5</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>624</v>
+        <v>638</v>
       </c>
       <c r="G68" s="2">
         <v>1</v>
@@ -17120,13 +17386,13 @@
         <v>50000064</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>625</v>
+        <v>639</v>
       </c>
       <c r="E69" s="2">
         <v>5</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>626</v>
+        <v>640</v>
       </c>
       <c r="G69" s="2">
         <v>1</v>
@@ -17152,13 +17418,13 @@
         <v>50000065</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>627</v>
+        <v>641</v>
       </c>
       <c r="E70" s="2">
         <v>5</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>628</v>
+        <v>642</v>
       </c>
       <c r="G70" s="2">
         <v>1</v>
@@ -17184,13 +17450,13 @@
         <v>50000066</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>629</v>
+        <v>643</v>
       </c>
       <c r="E71" s="2">
         <v>5</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>630</v>
+        <v>644</v>
       </c>
       <c r="G71" s="2">
         <v>1</v>
@@ -17216,13 +17482,13 @@
         <v>50000067</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>631</v>
+        <v>645</v>
       </c>
       <c r="E72" s="2">
         <v>5</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>632</v>
+        <v>646</v>
       </c>
       <c r="G72" s="2">
         <v>1</v>
@@ -17248,13 +17514,13 @@
         <v>50000068</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>633</v>
+        <v>647</v>
       </c>
       <c r="E73" s="2">
         <v>5</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>634</v>
+        <v>648</v>
       </c>
       <c r="G73" s="2">
         <v>1</v>
@@ -17280,13 +17546,13 @@
         <v>50000069</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>635</v>
+        <v>649</v>
       </c>
       <c r="E74" s="2">
         <v>5</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>636</v>
+        <v>650</v>
       </c>
       <c r="G74" s="2">
         <v>1</v>
@@ -17312,13 +17578,13 @@
         <v>50000070</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>637</v>
+        <v>651</v>
       </c>
       <c r="E75" s="2">
         <v>5</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>638</v>
+        <v>652</v>
       </c>
       <c r="G75" s="2">
         <v>1</v>
@@ -17344,13 +17610,13 @@
         <v>50000071</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="E76" s="2">
         <v>5</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>640</v>
+        <v>654</v>
       </c>
       <c r="G76" s="2">
         <v>1</v>
@@ -17376,13 +17642,13 @@
         <v>50000072</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>641</v>
+        <v>655</v>
       </c>
       <c r="E77" s="2">
         <v>5</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>642</v>
+        <v>656</v>
       </c>
       <c r="G77" s="2">
         <v>1</v>
@@ -17408,13 +17674,13 @@
         <v>50000073</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>643</v>
+        <v>657</v>
       </c>
       <c r="E78" s="2">
         <v>5</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>644</v>
+        <v>658</v>
       </c>
       <c r="G78" s="2">
         <v>1</v>
@@ -17440,13 +17706,13 @@
         <v>50000074</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>645</v>
+        <v>659</v>
       </c>
       <c r="E79" s="2">
         <v>5</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>646</v>
+        <v>660</v>
       </c>
       <c r="G79" s="2">
         <v>1</v>
@@ -17472,13 +17738,13 @@
         <v>50000075</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>647</v>
+        <v>661</v>
       </c>
       <c r="E80" s="2">
         <v>5</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>648</v>
+        <v>662</v>
       </c>
       <c r="G80" s="2">
         <v>1</v>
@@ -17504,13 +17770,13 @@
         <v>50000076</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>649</v>
+        <v>663</v>
       </c>
       <c r="E81" s="2">
         <v>5</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>650</v>
+        <v>664</v>
       </c>
       <c r="G81" s="2">
         <v>1</v>
@@ -17536,13 +17802,13 @@
         <v>50000077</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>651</v>
+        <v>665</v>
       </c>
       <c r="E82" s="2">
         <v>5</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>652</v>
+        <v>666</v>
       </c>
       <c r="G82" s="2">
         <v>1</v>
@@ -17568,13 +17834,13 @@
         <v>50000078</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>653</v>
+        <v>667</v>
       </c>
       <c r="E83" s="2">
         <v>5</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>654</v>
+        <v>668</v>
       </c>
       <c r="G83" s="2">
         <v>1</v>
@@ -17600,13 +17866,13 @@
         <v>50000079</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>655</v>
+        <v>669</v>
       </c>
       <c r="E84" s="2">
         <v>5</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>656</v>
+        <v>670</v>
       </c>
       <c r="G84" s="2">
         <v>1</v>
@@ -17632,13 +17898,13 @@
         <v>50000080</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>657</v>
+        <v>671</v>
       </c>
       <c r="E85" s="2">
         <v>5</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>658</v>
+        <v>672</v>
       </c>
       <c r="G85" s="2">
         <v>1</v>
@@ -17664,13 +17930,13 @@
         <v>50000081</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>659</v>
+        <v>673</v>
       </c>
       <c r="E86" s="2">
         <v>5</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>660</v>
+        <v>674</v>
       </c>
       <c r="G86" s="2">
         <v>1</v>
@@ -17696,13 +17962,13 @@
         <v>50000082</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>661</v>
+        <v>675</v>
       </c>
       <c r="E87" s="2">
         <v>5</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>662</v>
+        <v>676</v>
       </c>
       <c r="G87" s="2">
         <v>1</v>
@@ -17728,13 +17994,13 @@
         <v>50000083</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>663</v>
+        <v>677</v>
       </c>
       <c r="E88" s="2">
         <v>5</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>664</v>
+        <v>678</v>
       </c>
       <c r="G88" s="2">
         <v>1</v>
@@ -17760,13 +18026,13 @@
         <v>50000084</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>665</v>
+        <v>679</v>
       </c>
       <c r="E89" s="2">
         <v>5</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>666</v>
+        <v>680</v>
       </c>
       <c r="G89" s="2">
         <v>1</v>
@@ -17792,13 +18058,13 @@
         <v>50000085</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>667</v>
+        <v>681</v>
       </c>
       <c r="E90" s="2">
         <v>5</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>668</v>
+        <v>682</v>
       </c>
       <c r="G90" s="2">
         <v>1</v>
@@ -17824,13 +18090,13 @@
         <v>50000086</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>669</v>
+        <v>683</v>
       </c>
       <c r="E91" s="2">
         <v>5</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>670</v>
+        <v>684</v>
       </c>
       <c r="G91" s="2">
         <v>1</v>
@@ -17856,13 +18122,13 @@
         <v>50000087</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>671</v>
+        <v>685</v>
       </c>
       <c r="E92" s="2">
         <v>5</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>672</v>
+        <v>686</v>
       </c>
       <c r="G92" s="2">
         <v>1</v>
@@ -17888,13 +18154,13 @@
         <v>50000088</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>673</v>
+        <v>687</v>
       </c>
       <c r="E93" s="2">
         <v>5</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>674</v>
+        <v>688</v>
       </c>
       <c r="G93" s="2">
         <v>1</v>
@@ -17920,13 +18186,13 @@
         <v>50000089</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>675</v>
+        <v>689</v>
       </c>
       <c r="E94" s="2">
         <v>5</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>676</v>
+        <v>690</v>
       </c>
       <c r="G94" s="2">
         <v>1</v>
@@ -17952,13 +18218,13 @@
         <v>50000090</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>677</v>
+        <v>691</v>
       </c>
       <c r="E95" s="2">
         <v>5</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>678</v>
+        <v>692</v>
       </c>
       <c r="G95" s="2">
         <v>1</v>
@@ -17984,13 +18250,13 @@
         <v>50000091</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>679</v>
+        <v>693</v>
       </c>
       <c r="E96" s="2">
         <v>5</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>680</v>
+        <v>694</v>
       </c>
       <c r="G96" s="2">
         <v>1</v>
@@ -18016,13 +18282,13 @@
         <v>50000092</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>681</v>
+        <v>695</v>
       </c>
       <c r="E97" s="2">
         <v>5</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>682</v>
+        <v>696</v>
       </c>
       <c r="G97" s="2">
         <v>1</v>
@@ -18048,13 +18314,13 @@
         <v>50000093</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>683</v>
+        <v>697</v>
       </c>
       <c r="E98" s="2">
         <v>5</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>684</v>
+        <v>698</v>
       </c>
       <c r="G98" s="2">
         <v>1</v>
@@ -18080,13 +18346,13 @@
         <v>50000094</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>685</v>
+        <v>699</v>
       </c>
       <c r="E99" s="2">
         <v>5</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>686</v>
+        <v>700</v>
       </c>
       <c r="G99" s="2">
         <v>1</v>
@@ -18112,13 +18378,13 @@
         <v>50000095</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>687</v>
+        <v>701</v>
       </c>
       <c r="E100" s="2">
         <v>5</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>688</v>
+        <v>702</v>
       </c>
       <c r="G100" s="2">
         <v>1</v>
@@ -18144,13 +18410,13 @@
         <v>50000096</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>689</v>
+        <v>703</v>
       </c>
       <c r="E101" s="2">
         <v>5</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>690</v>
+        <v>704</v>
       </c>
       <c r="G101" s="2">
         <v>1</v>
@@ -18176,13 +18442,13 @@
         <v>50000097</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>691</v>
+        <v>705</v>
       </c>
       <c r="E102" s="2">
         <v>5</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>692</v>
+        <v>706</v>
       </c>
       <c r="G102" s="2">
         <v>1</v>
@@ -18208,13 +18474,13 @@
         <v>50000098</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>693</v>
+        <v>707</v>
       </c>
       <c r="E103" s="2">
         <v>5</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>694</v>
+        <v>708</v>
       </c>
       <c r="G103" s="2">
         <v>1</v>
@@ -18240,13 +18506,13 @@
         <v>50000099</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>695</v>
+        <v>709</v>
       </c>
       <c r="E104" s="2">
         <v>5</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>696</v>
+        <v>710</v>
       </c>
       <c r="G104" s="2">
         <v>1</v>
@@ -18272,13 +18538,13 @@
         <v>50000100</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>697</v>
+        <v>711</v>
       </c>
       <c r="E105" s="2">
         <v>5</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>698</v>
+        <v>712</v>
       </c>
       <c r="G105" s="2">
         <v>1</v>
@@ -18304,13 +18570,13 @@
         <v>50000101</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>699</v>
+        <v>713</v>
       </c>
       <c r="E106" s="2">
         <v>5</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>700</v>
+        <v>714</v>
       </c>
       <c r="G106" s="2">
         <v>1</v>
@@ -18336,13 +18602,13 @@
         <v>50000102</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>701</v>
+        <v>715</v>
       </c>
       <c r="E107" s="2">
         <v>5</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>702</v>
+        <v>716</v>
       </c>
       <c r="G107" s="2">
         <v>1</v>
@@ -18368,13 +18634,13 @@
         <v>50000103</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>703</v>
+        <v>717</v>
       </c>
       <c r="E108" s="2">
         <v>5</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>704</v>
+        <v>718</v>
       </c>
       <c r="G108" s="2">
         <v>1</v>
@@ -18400,13 +18666,13 @@
         <v>50000104</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>705</v>
+        <v>719</v>
       </c>
       <c r="E109" s="2">
         <v>5</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>706</v>
+        <v>720</v>
       </c>
       <c r="G109" s="2">
         <v>1</v>
@@ -18571,13 +18837,13 @@
         <v>180001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>707</v>
+        <v>721</v>
       </c>
       <c r="E6" s="2">
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>708</v>
+        <v>722</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -18597,13 +18863,13 @@
         <v>180002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>709</v>
+        <v>723</v>
       </c>
       <c r="E7" s="2">
         <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>708</v>
+        <v>722</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -18623,13 +18889,13 @@
         <v>180003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>710</v>
+        <v>724</v>
       </c>
       <c r="E8" s="2">
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>708</v>
+        <v>722</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -18649,13 +18915,13 @@
         <v>180004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>711</v>
+        <v>725</v>
       </c>
       <c r="E9" s="2">
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>708</v>
+        <v>722</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -18675,13 +18941,13 @@
         <v>180005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>712</v>
+        <v>726</v>
       </c>
       <c r="E10" s="2">
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>708</v>
+        <v>722</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -18701,13 +18967,13 @@
         <v>180006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>713</v>
+        <v>727</v>
       </c>
       <c r="E11" s="2">
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>708</v>
+        <v>722</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -18729,13 +18995,13 @@
         <v>180007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>714</v>
+        <v>728</v>
       </c>
       <c r="E12" s="2">
         <v>18</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>708</v>
+        <v>722</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -18757,13 +19023,13 @@
         <v>180008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>715</v>
+        <v>729</v>
       </c>
       <c r="E13" s="2">
         <v>18</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>708</v>
+        <v>722</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -18785,13 +19051,13 @@
         <v>180009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>716</v>
+        <v>730</v>
       </c>
       <c r="E14" s="2">
         <v>18</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>708</v>
+        <v>722</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -18813,13 +19079,13 @@
         <v>180010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>717</v>
+        <v>731</v>
       </c>
       <c r="E15" s="2">
         <v>18</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>708</v>
+        <v>722</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -18841,13 +19107,13 @@
         <v>180011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>718</v>
+        <v>732</v>
       </c>
       <c r="E16" s="2">
         <v>18</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>708</v>
+        <v>722</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -18869,13 +19135,13 @@
         <v>180012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>719</v>
+        <v>733</v>
       </c>
       <c r="E17" s="2">
         <v>18</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>708</v>
+        <v>722</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -18897,13 +19163,13 @@
         <v>180013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>720</v>
+        <v>734</v>
       </c>
       <c r="E18" s="2">
         <v>18</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>708</v>
+        <v>722</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -18925,13 +19191,13 @@
         <v>180014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>721</v>
+        <v>735</v>
       </c>
       <c r="E19" s="2">
         <v>18</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>708</v>
+        <v>722</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -18953,13 +19219,13 @@
         <v>180015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>722</v>
+        <v>736</v>
       </c>
       <c r="E20" s="2">
         <v>18</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>708</v>
+        <v>722</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -18981,13 +19247,13 @@
         <v>180016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>723</v>
+        <v>737</v>
       </c>
       <c r="E21" s="2">
         <v>18</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>708</v>
+        <v>722</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -19009,13 +19275,13 @@
         <v>180017</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>724</v>
+        <v>738</v>
       </c>
       <c r="E22" s="2">
         <v>18</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>708</v>
+        <v>722</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -19037,13 +19303,13 @@
         <v>180018</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>725</v>
+        <v>739</v>
       </c>
       <c r="E23" s="2">
         <v>18</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>708</v>
+        <v>722</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -19065,13 +19331,13 @@
         <v>180019</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>726</v>
+        <v>740</v>
       </c>
       <c r="E24" s="2">
         <v>18</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>708</v>
+        <v>722</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -19093,13 +19359,13 @@
         <v>180020</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>727</v>
+        <v>741</v>
       </c>
       <c r="E25" s="2">
         <v>18</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>708</v>
+        <v>722</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -19121,13 +19387,13 @@
         <v>180021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>728</v>
+        <v>742</v>
       </c>
       <c r="E26" s="2">
         <v>18</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>708</v>
+        <v>722</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -19154,13 +19420,13 @@
         <v>180030</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>729</v>
+        <v>743</v>
       </c>
       <c r="E28" s="2">
         <v>18</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>708</v>
+        <v>722</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -19182,13 +19448,13 @@
         <v>180031</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>730</v>
+        <v>744</v>
       </c>
       <c r="E29" s="2">
         <v>18</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>708</v>
+        <v>722</v>
       </c>
       <c r="G29" s="3">
         <v>1</v>
@@ -19208,13 +19474,13 @@
         <v>180032</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>731</v>
+        <v>745</v>
       </c>
       <c r="E30" s="2">
         <v>18</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>708</v>
+        <v>722</v>
       </c>
       <c r="G30" s="3">
         <v>1</v>
@@ -19234,13 +19500,13 @@
         <v>180033</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>732</v>
+        <v>746</v>
       </c>
       <c r="E31" s="2">
         <v>18</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>708</v>
+        <v>722</v>
       </c>
       <c r="G31" s="3">
         <v>1</v>
@@ -19260,13 +19526,13 @@
         <v>180034</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>733</v>
+        <v>747</v>
       </c>
       <c r="E32" s="2">
         <v>18</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>708</v>
+        <v>722</v>
       </c>
       <c r="G32" s="3">
         <v>1</v>
@@ -19288,13 +19554,13 @@
         <v>180035</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>734</v>
+        <v>748</v>
       </c>
       <c r="E33" s="2">
         <v>18</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>708</v>
+        <v>722</v>
       </c>
       <c r="G33" s="3">
         <v>1</v>
@@ -19316,13 +19582,13 @@
         <v>180036</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>735</v>
+        <v>749</v>
       </c>
       <c r="E34" s="2">
         <v>18</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>708</v>
+        <v>722</v>
       </c>
       <c r="G34" s="3">
         <v>1</v>
@@ -19483,13 +19749,13 @@
         <v>190001</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>736</v>
+        <v>750</v>
       </c>
       <c r="E6" s="2">
         <v>19</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>737</v>
+        <v>751</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -19509,13 +19775,13 @@
         <v>190002</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>738</v>
+        <v>752</v>
       </c>
       <c r="E7" s="2">
         <v>19</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>737</v>
+        <v>751</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -19535,13 +19801,13 @@
         <v>190003</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>739</v>
+        <v>753</v>
       </c>
       <c r="E8" s="2">
         <v>19</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>737</v>
+        <v>751</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -19561,13 +19827,13 @@
         <v>190004</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>740</v>
+        <v>754</v>
       </c>
       <c r="E9" s="2">
         <v>19</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>737</v>
+        <v>751</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -19587,13 +19853,13 @@
         <v>190005</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>741</v>
+        <v>755</v>
       </c>
       <c r="E10" s="2">
         <v>19</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>737</v>
+        <v>751</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -19613,13 +19879,13 @@
         <v>190006</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>742</v>
+        <v>756</v>
       </c>
       <c r="E11" s="2">
         <v>19</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>737</v>
+        <v>751</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -2825,12 +2825,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -7154,7 +7154,7 @@
         <v>239</v>
       </c>
       <c r="E78" s="3">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>240</v>
@@ -7163,7 +7163,7 @@
         <v>1</v>
       </c>
       <c r="H78" s="3">
-        <v>9999999</v>
+        <v>1</v>
       </c>
       <c r="I78" s="3">
         <v>0</v>
@@ -7186,7 +7186,7 @@
         <v>241</v>
       </c>
       <c r="E79" s="3">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>242</v>
@@ -7195,7 +7195,7 @@
         <v>1</v>
       </c>
       <c r="H79" s="3">
-        <v>9999999</v>
+        <v>1</v>
       </c>
       <c r="I79" s="3">
         <v>0</v>
@@ -7218,7 +7218,7 @@
         <v>243</v>
       </c>
       <c r="E80" s="3">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>244</v>
@@ -7227,7 +7227,7 @@
         <v>1</v>
       </c>
       <c r="H80" s="3">
-        <v>9999999</v>
+        <v>1</v>
       </c>
       <c r="I80" s="3">
         <v>0</v>
@@ -7250,7 +7250,7 @@
         <v>245</v>
       </c>
       <c r="E81" s="3">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>246</v>
@@ -7259,7 +7259,7 @@
         <v>1</v>
       </c>
       <c r="H81" s="3">
-        <v>9999999</v>
+        <v>1</v>
       </c>
       <c r="I81" s="3">
         <v>0</v>
@@ -7282,7 +7282,7 @@
         <v>247</v>
       </c>
       <c r="E82" s="3">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>248</v>
@@ -7291,7 +7291,7 @@
         <v>1</v>
       </c>
       <c r="H82" s="3">
-        <v>9999999</v>
+        <v>1</v>
       </c>
       <c r="I82" s="3">
         <v>0</v>
@@ -7314,7 +7314,7 @@
         <v>249</v>
       </c>
       <c r="E83" s="3">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>250</v>
@@ -7323,7 +7323,7 @@
         <v>1</v>
       </c>
       <c r="H83" s="3">
-        <v>9999999</v>
+        <v>1</v>
       </c>
       <c r="I83" s="3">
         <v>0</v>
@@ -7346,7 +7346,7 @@
         <v>251</v>
       </c>
       <c r="E84" s="3">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>252</v>
@@ -7355,7 +7355,7 @@
         <v>1</v>
       </c>
       <c r="H84" s="3">
-        <v>9999999</v>
+        <v>1</v>
       </c>
       <c r="I84" s="3">
         <v>0</v>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -2825,12 +2825,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -7154,7 +7154,7 @@
         <v>239</v>
       </c>
       <c r="E78" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>240</v>
@@ -7186,7 +7186,7 @@
         <v>241</v>
       </c>
       <c r="E79" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>242</v>
@@ -7218,7 +7218,7 @@
         <v>243</v>
       </c>
       <c r="E80" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>244</v>
@@ -7250,7 +7250,7 @@
         <v>245</v>
       </c>
       <c r="E81" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>246</v>
@@ -7282,7 +7282,7 @@
         <v>247</v>
       </c>
       <c r="E82" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>248</v>
@@ -7314,7 +7314,7 @@
         <v>249</v>
       </c>
       <c r="E83" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>250</v>
@@ -7346,7 +7346,7 @@
         <v>251</v>
       </c>
       <c r="E84" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>252</v>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -757,7 +757,7 @@
     <t>装备副本卷</t>
   </si>
   <si>
-    <t>装备副本次数+1，全部使用最多一次性使用200张</t>
+    <t>装备副本次数+1，全部使用最多一次性使用5000张</t>
   </si>
   <si>
     <t>BOSS挑战卷</t>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -1066,37 +1066,37 @@
     <t>白色宠蛋</t>
   </si>
   <si>
-    <t>开启一个白色到金色之间的宠物</t>
+    <t>开启一个白色宠物</t>
   </si>
   <si>
     <t>绿色宠蛋</t>
   </si>
   <si>
-    <t>开启一个绿到金色之间的宠物</t>
+    <t>开启一个绿色宠物</t>
   </si>
   <si>
     <t>蓝色宠蛋</t>
   </si>
   <si>
-    <t>开启一个蓝色到金色之间的宠物</t>
+    <t>开启一个蓝色宠物</t>
   </si>
   <si>
     <t>紫色宠蛋</t>
   </si>
   <si>
-    <t>开启一个紫色到金色之间的宠物</t>
+    <t>开启一个紫色宠物</t>
   </si>
   <si>
     <t>橙色宠蛋</t>
   </si>
   <si>
-    <t>开启一个橙色到金色之间的宠物</t>
+    <t>开启一个橙色宠物</t>
   </si>
   <si>
     <t>红色宠蛋</t>
   </si>
   <si>
-    <t>开启一个红色到金色之间的宠物</t>
+    <t>开启一个红色宠物</t>
   </si>
   <si>
     <t>金色宠蛋</t>
@@ -4926,7 +4926,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:M84"/>
+  <dimension ref="C3:M100"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="3"/>
@@ -7171,6 +7171,9 @@
       <c r="J78" s="3">
         <v>1</v>
       </c>
+      <c r="K78" s="3">
+        <v>0</v>
+      </c>
       <c r="L78" s="3">
         <v>0</v>
       </c>
@@ -7203,6 +7206,9 @@
       <c r="J79" s="3">
         <v>2</v>
       </c>
+      <c r="K79" s="3">
+        <v>0</v>
+      </c>
       <c r="L79" s="3">
         <v>0</v>
       </c>
@@ -7235,6 +7241,9 @@
       <c r="J80" s="3">
         <v>3</v>
       </c>
+      <c r="K80" s="3">
+        <v>0</v>
+      </c>
       <c r="L80" s="3">
         <v>0</v>
       </c>
@@ -7267,6 +7276,9 @@
       <c r="J81" s="3">
         <v>4</v>
       </c>
+      <c r="K81" s="3">
+        <v>0</v>
+      </c>
       <c r="L81" s="3">
         <v>0</v>
       </c>
@@ -7299,6 +7311,9 @@
       <c r="J82" s="3">
         <v>5</v>
       </c>
+      <c r="K82" s="3">
+        <v>0</v>
+      </c>
       <c r="L82" s="3">
         <v>0</v>
       </c>
@@ -7331,6 +7346,9 @@
       <c r="J83" s="3">
         <v>6</v>
       </c>
+      <c r="K83" s="3">
+        <v>0</v>
+      </c>
       <c r="L83" s="3">
         <v>0</v>
       </c>
@@ -7363,12 +7381,57 @@
       <c r="J84" s="3">
         <v>7</v>
       </c>
+      <c r="K84" s="3">
+        <v>0</v>
+      </c>
       <c r="L84" s="3">
         <v>0</v>
       </c>
       <c r="M84" s="3">
         <v>0</v>
       </c>
+    </row>
+    <row r="86" customHeight="1" spans="4:4">
+      <c r="D86" s="11"/>
+    </row>
+    <row r="87" customHeight="1" spans="4:4">
+      <c r="D87" s="11"/>
+    </row>
+    <row r="88" customHeight="1" spans="4:4">
+      <c r="D88" s="11"/>
+    </row>
+    <row r="89" customHeight="1" spans="4:4">
+      <c r="D89" s="11"/>
+    </row>
+    <row r="90" customHeight="1" spans="4:4">
+      <c r="D90" s="11"/>
+    </row>
+    <row r="91" customHeight="1" spans="4:4">
+      <c r="D91" s="11"/>
+    </row>
+    <row r="92" customHeight="1" spans="4:4">
+      <c r="D92" s="11"/>
+    </row>
+    <row r="94" customHeight="1" spans="4:4">
+      <c r="D94" s="11"/>
+    </row>
+    <row r="95" customHeight="1" spans="4:4">
+      <c r="D95" s="11"/>
+    </row>
+    <row r="96" customHeight="1" spans="4:4">
+      <c r="D96" s="11"/>
+    </row>
+    <row r="97" customHeight="1" spans="4:4">
+      <c r="D97" s="11"/>
+    </row>
+    <row r="98" customHeight="1" spans="4:4">
+      <c r="D98" s="11"/>
+    </row>
+    <row r="99" customHeight="1" spans="4:4">
+      <c r="D99" s="11"/>
+    </row>
+    <row r="100" customHeight="1" spans="4:4">
+      <c r="D100" s="11"/>
     </row>
   </sheetData>
   <dataValidations count="2">

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -344,7 +344,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1416" uniqueCount="757">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="759">
   <si>
     <t>_Id</t>
   </si>
@@ -866,6 +866,12 @@
   </si>
   <si>
     <t>装备改造材料</t>
+  </si>
+  <si>
+    <t>口粮</t>
+  </si>
+  <si>
+    <t>宠物材料</t>
   </si>
   <si>
     <t>图鉴碎片</t>
@@ -4926,7 +4932,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:M100"/>
+  <dimension ref="C3:M101"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="3"/>
@@ -5722,53 +5728,53 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C28" s="3">
-        <v>4101</v>
-      </c>
-      <c r="D28" s="3" t="s">
+    <row r="27" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C27" s="3">
+        <v>4022</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="E28" s="3">
-        <v>5</v>
-      </c>
-      <c r="F28" s="3" t="s">
+      <c r="E27" s="3">
+        <v>5</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="G28" s="3">
-        <v>1</v>
-      </c>
-      <c r="H28" s="3">
+      <c r="G27" s="3">
+        <v>1</v>
+      </c>
+      <c r="H27" s="3">
         <v>9999999</v>
       </c>
-      <c r="I28" s="3">
-        <v>0</v>
-      </c>
-      <c r="J28" s="3">
-        <v>5</v>
-      </c>
-      <c r="L28" s="3">
-        <v>0</v>
-      </c>
-      <c r="M28" s="3">
-        <v>0</v>
-      </c>
+      <c r="I27" s="3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3">
+        <v>5</v>
+      </c>
+      <c r="L27" s="3">
+        <v>0</v>
+      </c>
+      <c r="M27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
     </row>
     <row r="29" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C29" s="3">
-        <v>4102</v>
+        <v>4101</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>176</v>
@@ -5800,7 +5806,7 @@
     </row>
     <row r="30" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C30" s="3">
-        <v>4103</v>
+        <v>4102</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>178</v>
@@ -5809,7 +5815,7 @@
         <v>5</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="G30" s="3">
         <v>1</v>
@@ -5832,10 +5838,10 @@
     </row>
     <row r="31" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C31" s="3">
-        <v>4104</v>
+        <v>4103</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E31" s="3">
         <v>5</v>
@@ -5864,10 +5870,10 @@
     </row>
     <row r="32" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C32" s="3">
-        <v>4105</v>
+        <v>4104</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E32" s="3">
         <v>5</v>
@@ -5896,16 +5902,16 @@
     </row>
     <row r="33" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C33" s="3">
-        <v>4106</v>
+        <v>4105</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E33" s="3">
         <v>5</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="G33" s="3">
         <v>1</v>
@@ -5928,7 +5934,7 @@
     </row>
     <row r="34" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C34" s="3">
-        <v>4107</v>
+        <v>4106</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>181</v>
@@ -5960,7 +5966,7 @@
     </row>
     <row r="35" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C35" s="3">
-        <v>4108</v>
+        <v>4107</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>183</v>
@@ -5992,7 +5998,7 @@
     </row>
     <row r="36" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C36" s="3">
-        <v>4109</v>
+        <v>4108</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>185</v>
@@ -6024,7 +6030,7 @@
     </row>
     <row r="37" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C37" s="3">
-        <v>4110</v>
+        <v>4109</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>187</v>
@@ -6056,7 +6062,7 @@
     </row>
     <row r="38" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C38" s="3">
-        <v>4111</v>
+        <v>4110</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>189</v>
@@ -6086,41 +6092,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C40" s="3">
-        <v>4201</v>
-      </c>
-      <c r="D40" s="3" t="s">
+    <row r="39" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C39" s="3">
+        <v>4111</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="E40" s="3">
-        <v>5</v>
-      </c>
-      <c r="F40" s="3" t="s">
+      <c r="E39" s="3">
+        <v>5</v>
+      </c>
+      <c r="F39" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="G40" s="3">
-        <v>1</v>
-      </c>
-      <c r="H40" s="3">
-        <v>2000000</v>
-      </c>
-      <c r="I40" s="3">
-        <v>0</v>
-      </c>
-      <c r="J40" s="3">
-        <v>5</v>
-      </c>
-      <c r="L40" s="3">
-        <v>4002</v>
-      </c>
-      <c r="M40" s="3">
-        <v>1000</v>
+      <c r="G39" s="3">
+        <v>1</v>
+      </c>
+      <c r="H39" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I39" s="3">
+        <v>0</v>
+      </c>
+      <c r="J39" s="3">
+        <v>5</v>
+      </c>
+      <c r="L39" s="3">
+        <v>0</v>
+      </c>
+      <c r="M39" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="41" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C41" s="3">
-        <v>4202</v>
+        <v>4201</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>193</v>
@@ -6135,7 +6141,7 @@
         <v>1</v>
       </c>
       <c r="H41" s="3">
-        <v>99999</v>
+        <v>2000000</v>
       </c>
       <c r="I41" s="3">
         <v>0</v>
@@ -6144,50 +6150,47 @@
         <v>5</v>
       </c>
       <c r="L41" s="3">
-        <v>0</v>
+        <v>4002</v>
       </c>
       <c r="M41" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C43" s="3">
-        <v>6101</v>
-      </c>
-      <c r="D43" s="3" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="42" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C42" s="3">
+        <v>4202</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="E43" s="3">
-        <v>7</v>
-      </c>
-      <c r="F43" s="3" t="s">
+      <c r="E42" s="3">
+        <v>5</v>
+      </c>
+      <c r="F42" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="G43" s="3">
-        <v>1</v>
-      </c>
-      <c r="H43" s="3">
-        <v>99999</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>4</v>
-      </c>
-      <c r="K43" s="3">
-        <v>1</v>
-      </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
-      <c r="M43" s="3">
+      <c r="G42" s="3">
+        <v>1</v>
+      </c>
+      <c r="H42" s="3">
+        <v>99999</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>5</v>
+      </c>
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="44" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C44" s="3">
-        <v>6102</v>
+        <v>6101</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>197</v>
@@ -6211,7 +6214,7 @@
         <v>4</v>
       </c>
       <c r="K44" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -6222,7 +6225,7 @@
     </row>
     <row r="45" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C45" s="3">
-        <v>6103</v>
+        <v>6102</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>199</v>
@@ -6246,7 +6249,7 @@
         <v>4</v>
       </c>
       <c r="K45" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
@@ -6257,7 +6260,7 @@
     </row>
     <row r="46" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C46" s="3">
-        <v>6104</v>
+        <v>6103</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>201</v>
@@ -6281,7 +6284,7 @@
         <v>4</v>
       </c>
       <c r="K46" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L46" s="3">
         <v>0</v>
@@ -6290,9 +6293,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" customHeight="1" spans="3:13">
+    <row r="47" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C47" s="3">
-        <v>6105</v>
+        <v>6104</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>203</v>
@@ -6316,7 +6319,7 @@
         <v>4</v>
       </c>
       <c r="K47" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -6325,9 +6328,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" s="3" customFormat="1" customHeight="1" spans="3:13">
+    <row r="48" customHeight="1" spans="3:13">
       <c r="C48" s="3">
-        <v>6106</v>
+        <v>6105</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>205</v>
@@ -6351,7 +6354,7 @@
         <v>4</v>
       </c>
       <c r="K48" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L48" s="3">
         <v>0</v>
@@ -6360,15 +6363,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" customHeight="1" spans="3:13">
+    <row r="49" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C49" s="3">
-        <v>7101</v>
+        <v>6106</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>207</v>
       </c>
       <c r="E49" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>208</v>
@@ -6386,7 +6389,7 @@
         <v>4</v>
       </c>
       <c r="K49" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
@@ -6397,7 +6400,7 @@
     </row>
     <row r="50" customHeight="1" spans="3:13">
       <c r="C50" s="3">
-        <v>7102</v>
+        <v>7101</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>209</v>
@@ -6421,7 +6424,7 @@
         <v>4</v>
       </c>
       <c r="K50" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L50" s="3">
         <v>0</v>
@@ -6432,7 +6435,7 @@
     </row>
     <row r="51" customHeight="1" spans="3:13">
       <c r="C51" s="3">
-        <v>7103</v>
+        <v>7102</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>211</v>
@@ -6456,7 +6459,7 @@
         <v>4</v>
       </c>
       <c r="K51" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L51" s="3">
         <v>0</v>
@@ -6467,7 +6470,7 @@
     </row>
     <row r="52" customHeight="1" spans="3:13">
       <c r="C52" s="3">
-        <v>7104</v>
+        <v>7103</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>213</v>
@@ -6491,7 +6494,7 @@
         <v>4</v>
       </c>
       <c r="K52" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -6502,7 +6505,7 @@
     </row>
     <row r="53" customHeight="1" spans="3:13">
       <c r="C53" s="3">
-        <v>7105</v>
+        <v>7104</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>215</v>
@@ -6526,7 +6529,7 @@
         <v>4</v>
       </c>
       <c r="K53" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L53" s="3">
         <v>0</v>
@@ -6537,7 +6540,7 @@
     </row>
     <row r="54" customHeight="1" spans="3:13">
       <c r="C54" s="3">
-        <v>7107</v>
+        <v>7105</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>217</v>
@@ -6561,7 +6564,7 @@
         <v>4</v>
       </c>
       <c r="K54" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L54" s="3">
         <v>0</v>
@@ -6570,41 +6573,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C58" s="3">
-        <v>8001</v>
-      </c>
-      <c r="D58" s="3" t="s">
+    <row r="55" customHeight="1" spans="3:13">
+      <c r="C55" s="3">
+        <v>7107</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="E58" s="3">
-        <v>5</v>
-      </c>
-      <c r="F58" s="3" t="s">
+      <c r="E55" s="3">
+        <v>8</v>
+      </c>
+      <c r="F55" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="G58" s="3">
-        <v>1</v>
-      </c>
-      <c r="H58" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>6</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3">
+      <c r="G55" s="3">
+        <v>1</v>
+      </c>
+      <c r="H55" s="3">
+        <v>99999</v>
+      </c>
+      <c r="I55" s="3">
+        <v>0</v>
+      </c>
+      <c r="J55" s="3">
+        <v>4</v>
+      </c>
+      <c r="K55" s="3">
+        <v>6</v>
+      </c>
+      <c r="L55" s="3">
+        <v>0</v>
+      </c>
+      <c r="M55" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="59" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C59" s="3">
-        <v>8002</v>
+        <v>8001</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>221</v>
@@ -6613,7 +6619,7 @@
         <v>5</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G59" s="3">
         <v>1</v>
@@ -6636,16 +6642,16 @@
     </row>
     <row r="60" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C60" s="3">
-        <v>8003</v>
+        <v>8002</v>
       </c>
       <c r="D60" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E60" s="3">
+        <v>5</v>
+      </c>
+      <c r="F60" s="3" t="s">
         <v>222</v>
-      </c>
-      <c r="E60" s="3">
-        <v>5</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>220</v>
       </c>
       <c r="G60" s="3">
         <v>1</v>
@@ -6668,16 +6674,16 @@
     </row>
     <row r="61" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C61" s="3">
-        <v>8004</v>
+        <v>8003</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E61" s="3">
         <v>5</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G61" s="3">
         <v>1</v>
@@ -6700,16 +6706,16 @@
     </row>
     <row r="62" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C62" s="3">
-        <v>8005</v>
+        <v>8004</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E62" s="3">
         <v>5</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G62" s="3">
         <v>1</v>
@@ -6732,16 +6738,16 @@
     </row>
     <row r="63" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C63" s="3">
-        <v>8006</v>
+        <v>8005</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E63" s="3">
         <v>5</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G63" s="3">
         <v>1</v>
@@ -6764,16 +6770,16 @@
     </row>
     <row r="64" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C64" s="3">
-        <v>8007</v>
+        <v>8006</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E64" s="3">
         <v>5</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G64" s="3">
         <v>1</v>
@@ -6796,16 +6802,16 @@
     </row>
     <row r="65" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C65" s="3">
-        <v>8008</v>
+        <v>8007</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E65" s="3">
         <v>5</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G65" s="3">
         <v>1</v>
@@ -6828,16 +6834,16 @@
     </row>
     <row r="66" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C66" s="3">
-        <v>8009</v>
+        <v>8008</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E66" s="3">
         <v>5</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G66" s="3">
         <v>1</v>
@@ -6860,16 +6866,16 @@
     </row>
     <row r="67" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C67" s="3">
-        <v>8010</v>
+        <v>8009</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E67" s="3">
         <v>5</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G67" s="3">
         <v>1</v>
@@ -6890,41 +6896,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C69" s="3">
-        <v>8101</v>
-      </c>
-      <c r="D69" s="11" t="s">
-        <v>230</v>
-      </c>
-      <c r="E69" s="3">
-        <v>5</v>
-      </c>
-      <c r="F69" s="3" t="s">
+    <row r="68" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C68" s="3">
+        <v>8010</v>
+      </c>
+      <c r="D68" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="G69" s="3">
-        <v>1</v>
-      </c>
-      <c r="H69" s="3">
+      <c r="E68" s="3">
+        <v>5</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="G68" s="3">
+        <v>1</v>
+      </c>
+      <c r="H68" s="3">
         <v>9999999</v>
       </c>
-      <c r="I69" s="3">
-        <v>0</v>
-      </c>
-      <c r="J69" s="3">
-        <v>7</v>
-      </c>
-      <c r="L69" s="3">
-        <v>0</v>
-      </c>
-      <c r="M69" s="3">
+      <c r="I68" s="3">
+        <v>0</v>
+      </c>
+      <c r="J68" s="3">
+        <v>6</v>
+      </c>
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="70" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C70" s="3">
-        <v>8102</v>
+        <v>8101</v>
       </c>
       <c r="D70" s="11" t="s">
         <v>232</v>
@@ -6933,7 +6939,7 @@
         <v>5</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="G70" s="3">
         <v>1</v>
@@ -6956,16 +6962,16 @@
     </row>
     <row r="71" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C71" s="3">
-        <v>8103</v>
+        <v>8102</v>
       </c>
       <c r="D71" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="E71" s="3">
+        <v>5</v>
+      </c>
+      <c r="F71" s="3" t="s">
         <v>233</v>
-      </c>
-      <c r="E71" s="3">
-        <v>5</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>231</v>
       </c>
       <c r="G71" s="3">
         <v>1</v>
@@ -6988,16 +6994,16 @@
     </row>
     <row r="72" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C72" s="3">
-        <v>8104</v>
+        <v>8103</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E72" s="3">
         <v>5</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="G72" s="3">
         <v>1</v>
@@ -7020,16 +7026,16 @@
     </row>
     <row r="73" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C73" s="3">
-        <v>8105</v>
+        <v>8104</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E73" s="3">
         <v>5</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="G73" s="3">
         <v>1</v>
@@ -7052,16 +7058,16 @@
     </row>
     <row r="74" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C74" s="3">
-        <v>8106</v>
+        <v>8105</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E74" s="3">
         <v>5</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="G74" s="3">
         <v>1</v>
@@ -7084,16 +7090,16 @@
     </row>
     <row r="75" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C75" s="3">
-        <v>8107</v>
+        <v>8106</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E75" s="3">
         <v>5</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="G75" s="3">
         <v>1</v>
@@ -7116,16 +7122,16 @@
     </row>
     <row r="76" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C76" s="3">
-        <v>8108</v>
+        <v>8107</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E76" s="3">
         <v>5</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="G76" s="3">
         <v>1</v>
@@ -7146,44 +7152,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" customHeight="1" spans="3:13">
-      <c r="C78" s="3">
-        <v>8201</v>
-      </c>
-      <c r="D78" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="E78" s="3">
-        <v>16</v>
-      </c>
-      <c r="F78" s="3" t="s">
+    <row r="77" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C77" s="3">
+        <v>8108</v>
+      </c>
+      <c r="D77" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="G78" s="3">
-        <v>1</v>
-      </c>
-      <c r="H78" s="3">
-        <v>1</v>
-      </c>
-      <c r="I78" s="3">
-        <v>0</v>
-      </c>
-      <c r="J78" s="3">
-        <v>1</v>
-      </c>
-      <c r="K78" s="3">
-        <v>0</v>
-      </c>
-      <c r="L78" s="3">
-        <v>0</v>
-      </c>
-      <c r="M78" s="3">
+      <c r="E77" s="3">
+        <v>5</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G77" s="3">
+        <v>1</v>
+      </c>
+      <c r="H77" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I77" s="3">
+        <v>0</v>
+      </c>
+      <c r="J77" s="3">
+        <v>7</v>
+      </c>
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:13">
       <c r="C79" s="3">
-        <v>8202</v>
+        <v>8201</v>
       </c>
       <c r="D79" s="11" t="s">
         <v>241</v>
@@ -7204,7 +7207,7 @@
         <v>0</v>
       </c>
       <c r="J79" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K79" s="3">
         <v>0</v>
@@ -7218,7 +7221,7 @@
     </row>
     <row r="80" customHeight="1" spans="3:13">
       <c r="C80" s="3">
-        <v>8203</v>
+        <v>8202</v>
       </c>
       <c r="D80" s="11" t="s">
         <v>243</v>
@@ -7239,7 +7242,7 @@
         <v>0</v>
       </c>
       <c r="J80" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K80" s="3">
         <v>0</v>
@@ -7253,7 +7256,7 @@
     </row>
     <row r="81" customHeight="1" spans="3:13">
       <c r="C81" s="3">
-        <v>8204</v>
+        <v>8203</v>
       </c>
       <c r="D81" s="11" t="s">
         <v>245</v>
@@ -7274,7 +7277,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K81" s="3">
         <v>0</v>
@@ -7288,7 +7291,7 @@
     </row>
     <row r="82" customHeight="1" spans="3:13">
       <c r="C82" s="3">
-        <v>8205</v>
+        <v>8204</v>
       </c>
       <c r="D82" s="11" t="s">
         <v>247</v>
@@ -7309,7 +7312,7 @@
         <v>0</v>
       </c>
       <c r="J82" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K82" s="3">
         <v>0</v>
@@ -7323,7 +7326,7 @@
     </row>
     <row r="83" customHeight="1" spans="3:13">
       <c r="C83" s="3">
-        <v>8206</v>
+        <v>8205</v>
       </c>
       <c r="D83" s="11" t="s">
         <v>249</v>
@@ -7344,7 +7347,7 @@
         <v>0</v>
       </c>
       <c r="J83" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -7358,7 +7361,7 @@
     </row>
     <row r="84" customHeight="1" spans="3:13">
       <c r="C84" s="3">
-        <v>8207</v>
+        <v>8206</v>
       </c>
       <c r="D84" s="11" t="s">
         <v>251</v>
@@ -7379,20 +7382,52 @@
         <v>0</v>
       </c>
       <c r="J84" s="3">
+        <v>6</v>
+      </c>
+      <c r="K84" s="3">
+        <v>0</v>
+      </c>
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="3:13">
+      <c r="C85" s="3">
+        <v>8207</v>
+      </c>
+      <c r="D85" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="E85" s="3">
+        <v>16</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G85" s="3">
+        <v>1</v>
+      </c>
+      <c r="H85" s="3">
+        <v>1</v>
+      </c>
+      <c r="I85" s="3">
+        <v>0</v>
+      </c>
+      <c r="J85" s="3">
         <v>7</v>
       </c>
-      <c r="K84" s="3">
-        <v>0</v>
-      </c>
-      <c r="L84" s="3">
-        <v>0</v>
-      </c>
-      <c r="M84" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" customHeight="1" spans="4:4">
-      <c r="D86" s="11"/>
+      <c r="K85" s="3">
+        <v>0</v>
+      </c>
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="87" customHeight="1" spans="4:4">
       <c r="D87" s="11"/>
@@ -7412,8 +7447,8 @@
     <row r="92" customHeight="1" spans="4:4">
       <c r="D92" s="11"/>
     </row>
-    <row r="94" customHeight="1" spans="4:4">
-      <c r="D94" s="11"/>
+    <row r="93" customHeight="1" spans="4:4">
+      <c r="D93" s="11"/>
     </row>
     <row r="95" customHeight="1" spans="4:4">
       <c r="D95" s="11"/>
@@ -7432,6 +7467,9 @@
     </row>
     <row r="100" customHeight="1" spans="4:4">
       <c r="D100" s="11"/>
+    </row>
+    <row r="101" customHeight="1" spans="4:4">
+      <c r="D101" s="11"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -7577,13 +7615,13 @@
         <v>1999001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E6" s="2">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -7605,13 +7643,13 @@
         <v>1999002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E7" s="2">
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -7633,13 +7671,13 @@
         <v>1999003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E8" s="2">
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -7661,13 +7699,13 @@
         <v>1999004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E9" s="2">
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -7689,13 +7727,13 @@
         <v>1999005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E10" s="2">
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -7717,13 +7755,13 @@
         <v>1999006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E11" s="2">
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -7750,13 +7788,13 @@
         <v>1999989</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E13" s="2">
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -7778,13 +7816,13 @@
         <v>1999990</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E14" s="2">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -7806,13 +7844,13 @@
         <v>1999991</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E15" s="2">
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -7834,13 +7872,13 @@
         <v>1999992</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E16" s="2">
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -7862,13 +7900,13 @@
         <v>1999993</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E17" s="2">
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -7890,13 +7928,13 @@
         <v>1999994</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E18" s="2">
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -7918,13 +7956,13 @@
         <v>1999995</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E19" s="2">
         <v>11</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -7946,13 +7984,13 @@
         <v>1999996</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E20" s="2">
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -7974,13 +8012,13 @@
         <v>1999997</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E21" s="2">
         <v>11</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -8002,13 +8040,13 @@
         <v>2000000</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E22" s="2">
         <v>11</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -8030,13 +8068,13 @@
         <v>2000001</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E23" s="2">
         <v>11</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -8058,13 +8096,13 @@
         <v>2000002</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E24" s="2">
         <v>11</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -8086,13 +8124,13 @@
         <v>2000003</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E25" s="2">
         <v>11</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -8114,13 +8152,13 @@
         <v>2000004</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E26" s="2">
         <v>11</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -8142,13 +8180,13 @@
         <v>2000005</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E27" s="2">
         <v>11</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -8170,13 +8208,13 @@
         <v>2000006</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E28" s="2">
         <v>11</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -8198,13 +8236,13 @@
         <v>2000007</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E29" s="2">
         <v>11</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -8226,13 +8264,13 @@
         <v>2000008</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E30" s="2">
         <v>11</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -8254,13 +8292,13 @@
         <v>2000009</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E31" s="2">
         <v>11</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -8282,13 +8320,13 @@
         <v>2000010</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E32" s="2">
         <v>11</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -8310,13 +8348,13 @@
         <v>2000011</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E33" s="2">
         <v>11</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -8338,13 +8376,13 @@
         <v>2000012</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E34" s="2">
         <v>11</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -8366,13 +8404,13 @@
         <v>2000013</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E35" s="2">
         <v>11</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -8406,13 +8444,13 @@
         <v>2000100</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E39" s="2">
         <v>11</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -8434,13 +8472,13 @@
         <v>2000101</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E40" s="2">
         <v>11</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -8462,13 +8500,13 @@
         <v>2000102</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E41" s="2">
         <v>11</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -8490,13 +8528,13 @@
         <v>2000103</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E42" s="2">
         <v>11</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -8518,13 +8556,13 @@
         <v>2000104</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E43" s="2">
         <v>11</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -8546,13 +8584,13 @@
         <v>2000105</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E44" s="2">
         <v>11</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -8574,13 +8612,13 @@
         <v>2000106</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E45" s="2">
         <v>11</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G45" s="2">
         <v>1</v>
@@ -8602,13 +8640,13 @@
         <v>2000107</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E46" s="2">
         <v>11</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -8630,13 +8668,13 @@
         <v>2000108</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E47" s="2">
         <v>11</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -8658,13 +8696,13 @@
         <v>2000109</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E48" s="2">
         <v>11</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -8686,13 +8724,13 @@
         <v>2000110</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E49" s="2">
         <v>11</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -8714,13 +8752,13 @@
         <v>2000111</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E50" s="2">
         <v>11</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -8742,13 +8780,13 @@
         <v>2000112</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E51" s="2">
         <v>11</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -8770,13 +8808,13 @@
         <v>2000113</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E52" s="2">
         <v>11</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -8798,13 +8836,13 @@
         <v>2000114</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E53" s="2">
         <v>11</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G53" s="2">
         <v>1</v>
@@ -8826,13 +8864,13 @@
         <v>2000115</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E54" s="2">
         <v>11</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G54" s="2">
         <v>1</v>
@@ -8854,13 +8892,13 @@
         <v>2000116</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E55" s="2">
         <v>11</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G55" s="2">
         <v>1</v>
@@ -8882,13 +8920,13 @@
         <v>2000117</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E56" s="2">
         <v>11</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G56" s="2">
         <v>1</v>
@@ -8910,13 +8948,13 @@
         <v>2000118</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E57" s="2">
         <v>11</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G57" s="2">
         <v>1</v>
@@ -8938,13 +8976,13 @@
         <v>2000119</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E58" s="2">
         <v>11</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G58" s="2">
         <v>1</v>
@@ -8966,13 +9004,13 @@
         <v>2000120</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E59" s="2">
         <v>11</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G59" s="2">
         <v>1</v>
@@ -8994,13 +9032,13 @@
         <v>2000121</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E60" s="2">
         <v>11</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G60" s="2">
         <v>1</v>
@@ -9022,13 +9060,13 @@
         <v>2000122</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E61" s="2">
         <v>11</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G61" s="2">
         <v>1</v>
@@ -9050,13 +9088,13 @@
         <v>2000123</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E62" s="2">
         <v>11</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G62" s="2">
         <v>1</v>
@@ -9078,13 +9116,13 @@
         <v>2000124</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E63" s="2">
         <v>11</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G63" s="2">
         <v>1</v>
@@ -9106,13 +9144,13 @@
         <v>2000125</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E64" s="2">
         <v>11</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G64" s="2">
         <v>1</v>
@@ -9134,13 +9172,13 @@
         <v>2000126</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E65" s="2">
         <v>11</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G65" s="2">
         <v>1</v>
@@ -9162,13 +9200,13 @@
         <v>2000127</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E66" s="2">
         <v>11</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G66" s="2">
         <v>1</v>
@@ -9190,13 +9228,13 @@
         <v>2000128</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E67" s="2">
         <v>11</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G67" s="2">
         <v>1</v>
@@ -9218,13 +9256,13 @@
         <v>2000129</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E68" s="2">
         <v>11</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G68" s="2">
         <v>1</v>
@@ -9246,13 +9284,13 @@
         <v>2000200</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E70" s="2">
         <v>11</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G70" s="2">
         <v>1</v>
@@ -9272,13 +9310,13 @@
         <v>2000201</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E71" s="2">
         <v>11</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G71" s="2">
         <v>1</v>
@@ -9298,13 +9336,13 @@
         <v>2000202</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E72" s="2">
         <v>11</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G72" s="2">
         <v>1</v>
@@ -9324,13 +9362,13 @@
         <v>2000203</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E73" s="2">
         <v>11</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G73" s="2">
         <v>1</v>
@@ -9350,13 +9388,13 @@
         <v>2000204</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E74" s="2">
         <v>11</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G74" s="2">
         <v>1</v>
@@ -9376,13 +9414,13 @@
         <v>2000205</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E75" s="2">
         <v>11</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G75" s="2">
         <v>1</v>
@@ -9402,13 +9440,13 @@
         <v>2000206</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E76" s="2">
         <v>11</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G76" s="2">
         <v>1</v>
@@ -9428,13 +9466,13 @@
         <v>2000207</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E77" s="2">
         <v>11</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G77" s="2">
         <v>1</v>
@@ -9454,13 +9492,13 @@
         <v>2000208</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E78" s="2">
         <v>11</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G78" s="2">
         <v>1</v>
@@ -9480,13 +9518,13 @@
         <v>2000209</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E79" s="2">
         <v>11</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G79" s="2">
         <v>1</v>
@@ -9506,13 +9544,13 @@
         <v>2000210</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E80" s="2">
         <v>11</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G80" s="2">
         <v>1</v>
@@ -9532,13 +9570,13 @@
         <v>2000211</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E81" s="2">
         <v>11</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G81" s="2">
         <v>1</v>
@@ -9558,13 +9596,13 @@
         <v>2000212</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E82" s="2">
         <v>11</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G82" s="2">
         <v>1</v>
@@ -9584,13 +9622,13 @@
         <v>2000213</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E83" s="2">
         <v>11</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G83" s="2">
         <v>1</v>
@@ -9610,13 +9648,13 @@
         <v>2000214</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E84" s="2">
         <v>11</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G84" s="2">
         <v>1</v>
@@ -9636,13 +9674,13 @@
         <v>2000215</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E85" s="2">
         <v>11</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G85" s="2">
         <v>1</v>
@@ -9662,13 +9700,13 @@
         <v>2000216</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E86" s="2">
         <v>11</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G86" s="2">
         <v>1</v>
@@ -9688,13 +9726,13 @@
         <v>2000217</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E87" s="2">
         <v>11</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G87" s="2">
         <v>1</v>
@@ -9714,13 +9752,13 @@
         <v>2000218</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E88" s="2">
         <v>11</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G88" s="2">
         <v>1</v>
@@ -9740,13 +9778,13 @@
         <v>2000219</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E89" s="2">
         <v>11</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G89" s="2">
         <v>1</v>
@@ -9766,13 +9804,13 @@
         <v>2000220</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E90" s="2">
         <v>11</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G90" s="2">
         <v>1</v>
@@ -9792,13 +9830,13 @@
         <v>2000221</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E91" s="2">
         <v>11</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G91" s="2">
         <v>1</v>
@@ -9818,13 +9856,13 @@
         <v>2000222</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E92" s="2">
         <v>11</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G92" s="2">
         <v>1</v>
@@ -9844,13 +9882,13 @@
         <v>2000223</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E93" s="2">
         <v>11</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G93" s="2">
         <v>1</v>
@@ -9870,13 +9908,13 @@
         <v>2000224</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E94" s="2">
         <v>11</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G94" s="2">
         <v>1</v>
@@ -9896,13 +9934,13 @@
         <v>2000225</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E95" s="2">
         <v>11</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G95" s="2">
         <v>1</v>
@@ -9922,13 +9960,13 @@
         <v>2000226</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E96" s="2">
         <v>11</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G96" s="2">
         <v>1</v>
@@ -9948,13 +9986,13 @@
         <v>2000227</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E97" s="2">
         <v>11</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G97" s="2">
         <v>1</v>
@@ -9974,13 +10012,13 @@
         <v>2000228</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E98" s="2">
         <v>11</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G98" s="2">
         <v>1</v>
@@ -10000,13 +10038,13 @@
         <v>2000229</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E99" s="2">
         <v>11</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G99" s="2">
         <v>1</v>
@@ -10026,13 +10064,13 @@
         <v>2000300</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E102" s="2">
         <v>11</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G102" s="2">
         <v>1</v>
@@ -10052,13 +10090,13 @@
         <v>2000301</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E103" s="2">
         <v>11</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G103" s="2">
         <v>1</v>
@@ -10078,13 +10116,13 @@
         <v>2000302</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E104" s="2">
         <v>11</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G104" s="2">
         <v>1</v>
@@ -10104,13 +10142,13 @@
         <v>2000303</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E105" s="2">
         <v>11</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G105" s="2">
         <v>1</v>
@@ -10130,13 +10168,13 @@
         <v>2000304</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E106" s="2">
         <v>11</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G106" s="2">
         <v>1</v>
@@ -10156,13 +10194,13 @@
         <v>2000305</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E107" s="2">
         <v>11</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G107" s="2">
         <v>1</v>
@@ -10182,13 +10220,13 @@
         <v>2000306</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E108" s="2">
         <v>11</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G108" s="2">
         <v>1</v>
@@ -10208,13 +10246,13 @@
         <v>2000307</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E109" s="2">
         <v>11</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G109" s="2">
         <v>1</v>
@@ -10234,13 +10272,13 @@
         <v>2000308</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E110" s="2">
         <v>11</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G110" s="2">
         <v>1</v>
@@ -10260,13 +10298,13 @@
         <v>2000309</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E111" s="2">
         <v>11</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G111" s="2">
         <v>1</v>
@@ -10286,13 +10324,13 @@
         <v>2000310</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E112" s="2">
         <v>11</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G112" s="2">
         <v>1</v>
@@ -10312,13 +10350,13 @@
         <v>2000311</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E113" s="2">
         <v>11</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G113" s="2">
         <v>1</v>
@@ -10338,13 +10376,13 @@
         <v>2000312</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E114" s="2">
         <v>11</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G114" s="2">
         <v>1</v>
@@ -10364,13 +10402,13 @@
         <v>2000313</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E115" s="2">
         <v>11</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G115" s="2">
         <v>1</v>
@@ -10390,13 +10428,13 @@
         <v>2000314</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E116" s="2">
         <v>11</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G116" s="2">
         <v>1</v>
@@ -10416,13 +10454,13 @@
         <v>2000315</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E117" s="2">
         <v>11</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G117" s="2">
         <v>1</v>
@@ -10442,13 +10480,13 @@
         <v>2000316</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E118" s="2">
         <v>11</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G118" s="2">
         <v>1</v>
@@ -10468,13 +10506,13 @@
         <v>2000317</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E119" s="2">
         <v>11</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G119" s="2">
         <v>1</v>
@@ -10494,13 +10532,13 @@
         <v>2000318</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E120" s="2">
         <v>11</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G120" s="2">
         <v>1</v>
@@ -10520,13 +10558,13 @@
         <v>2000319</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E121" s="2">
         <v>11</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G121" s="2">
         <v>1</v>
@@ -10546,13 +10584,13 @@
         <v>2000320</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E122" s="2">
         <v>11</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G122" s="2">
         <v>1</v>
@@ -10572,13 +10610,13 @@
         <v>2000321</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E123" s="2">
         <v>11</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G123" s="2">
         <v>1</v>
@@ -10598,13 +10636,13 @@
         <v>2000322</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E124" s="2">
         <v>11</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G124" s="2">
         <v>1</v>
@@ -10624,13 +10662,13 @@
         <v>2000323</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E125" s="2">
         <v>11</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G125" s="2">
         <v>1</v>
@@ -10650,13 +10688,13 @@
         <v>2000324</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E126" s="2">
         <v>11</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G126" s="2">
         <v>1</v>
@@ -10676,13 +10714,13 @@
         <v>2000325</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E127" s="2">
         <v>11</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G127" s="2">
         <v>1</v>
@@ -10702,13 +10740,13 @@
         <v>2000326</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E128" s="2">
         <v>11</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G128" s="2">
         <v>1</v>
@@ -10728,13 +10766,13 @@
         <v>2000327</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E129" s="2">
         <v>11</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G129" s="2">
         <v>1</v>
@@ -10754,13 +10792,13 @@
         <v>2000328</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E130" s="2">
         <v>11</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G130" s="2">
         <v>1</v>
@@ -10780,13 +10818,13 @@
         <v>2000329</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E131" s="2">
         <v>11</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G131" s="2">
         <v>1</v>
@@ -10945,13 +10983,13 @@
         <v>3000001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E6" s="2">
         <v>13</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -10973,13 +11011,13 @@
         <v>3000002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E7" s="2">
         <v>13</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -11001,13 +11039,13 @@
         <v>3000003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E8" s="2">
         <v>13</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -11029,13 +11067,13 @@
         <v>3000004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E9" s="2">
         <v>13</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -11057,13 +11095,13 @@
         <v>3000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E10" s="2">
         <v>13</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -11085,13 +11123,13 @@
         <v>3000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E11" s="2">
         <v>13</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -11113,13 +11151,13 @@
         <v>3000007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E12" s="2">
         <v>13</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -11141,13 +11179,13 @@
         <v>3000008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E13" s="2">
         <v>13</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -11169,13 +11207,13 @@
         <v>3000009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E14" s="2">
         <v>13</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -11197,13 +11235,13 @@
         <v>3000010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E15" s="2">
         <v>13</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -11225,13 +11263,13 @@
         <v>3000011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E16" s="2">
         <v>13</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -11253,13 +11291,13 @@
         <v>3000012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E17" s="2">
         <v>13</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -11281,13 +11319,13 @@
         <v>3000013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E18" s="2">
         <v>13</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -11309,13 +11347,13 @@
         <v>3000014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E19" s="2">
         <v>13</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -11337,13 +11375,13 @@
         <v>3000015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E20" s="2">
         <v>13</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -11365,13 +11403,13 @@
         <v>3000016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E21" s="2">
         <v>13</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -11393,13 +11431,13 @@
         <v>3000017</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E22" s="2">
         <v>13</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -11421,13 +11459,13 @@
         <v>3000018</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E23" s="2">
         <v>13</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -11449,13 +11487,13 @@
         <v>3000019</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E24" s="2">
         <v>13</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -11477,13 +11515,13 @@
         <v>3000020</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E25" s="2">
         <v>13</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -11505,13 +11543,13 @@
         <v>3000021</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E26" s="2">
         <v>13</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -11533,13 +11571,13 @@
         <v>3000022</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E27" s="2">
         <v>13</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -11561,13 +11599,13 @@
         <v>3000023</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E28" s="2">
         <v>13</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -11589,13 +11627,13 @@
         <v>3000024</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E29" s="2">
         <v>13</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -11617,13 +11655,13 @@
         <v>3000025</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E30" s="2">
         <v>13</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -11645,13 +11683,13 @@
         <v>3000026</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E31" s="2">
         <v>13</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -11673,13 +11711,13 @@
         <v>3000027</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E32" s="2">
         <v>13</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -11701,13 +11739,13 @@
         <v>3000028</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E33" s="2">
         <v>13</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -11729,13 +11767,13 @@
         <v>3000029</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E34" s="2">
         <v>13</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -11757,13 +11795,13 @@
         <v>3000030</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E35" s="2">
         <v>13</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -11785,13 +11823,13 @@
         <v>3000031</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E36" s="2">
         <v>13</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -11813,13 +11851,13 @@
         <v>3000032</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E37" s="2">
         <v>13</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G37" s="2">
         <v>1</v>
@@ -11841,13 +11879,13 @@
         <v>3000033</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E38" s="2">
         <v>13</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G38" s="2">
         <v>1</v>
@@ -11869,13 +11907,13 @@
         <v>3000034</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E39" s="2">
         <v>13</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -11897,13 +11935,13 @@
         <v>3000035</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="E40" s="2">
         <v>13</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -11925,13 +11963,13 @@
         <v>3000036</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E41" s="2">
         <v>13</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -11953,13 +11991,13 @@
         <v>3000037</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E42" s="2">
         <v>13</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -11981,13 +12019,13 @@
         <v>3000038</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E43" s="2">
         <v>13</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -12009,13 +12047,13 @@
         <v>3000039</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E44" s="2">
         <v>13</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -12037,13 +12075,13 @@
         <v>3000040</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E45" s="2">
         <v>13</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G45" s="2">
         <v>1</v>
@@ -12065,13 +12103,13 @@
         <v>3000041</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E46" s="2">
         <v>13</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -12093,13 +12131,13 @@
         <v>3000042</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E47" s="2">
         <v>13</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -12121,13 +12159,13 @@
         <v>3000043</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E48" s="2">
         <v>13</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -12149,13 +12187,13 @@
         <v>3000044</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E49" s="2">
         <v>13</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -12177,13 +12215,13 @@
         <v>3000045</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E50" s="2">
         <v>13</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -12205,13 +12243,13 @@
         <v>3000046</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E51" s="2">
         <v>13</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -12233,13 +12271,13 @@
         <v>3000047</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E52" s="2">
         <v>13</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -12261,13 +12299,13 @@
         <v>3000048</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E53" s="2">
         <v>13</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G53" s="2">
         <v>1</v>
@@ -12426,13 +12464,13 @@
         <v>40000051</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E7" s="2">
         <v>14</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -12458,13 +12496,13 @@
         <v>40000052</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E8" s="2">
         <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -12490,13 +12528,13 @@
         <v>40000053</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E9" s="2">
         <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -12522,13 +12560,13 @@
         <v>40000054</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E10" s="2">
         <v>14</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -12554,13 +12592,13 @@
         <v>40000055</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E11" s="2">
         <v>14</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -12586,13 +12624,13 @@
         <v>40000056</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E12" s="2">
         <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -12618,13 +12656,13 @@
         <v>40000057</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E13" s="2">
         <v>14</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -12650,13 +12688,13 @@
         <v>40000058</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E14" s="2">
         <v>14</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -12682,13 +12720,13 @@
         <v>40000059</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E15" s="2">
         <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -12714,13 +12752,13 @@
         <v>40000060</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E16" s="2">
         <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -12746,13 +12784,13 @@
         <v>40000061</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E17" s="2">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -12778,13 +12816,13 @@
         <v>40000062</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E18" s="2">
         <v>14</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -12810,13 +12848,13 @@
         <v>40000063</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E19" s="2">
         <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -12842,13 +12880,13 @@
         <v>40000064</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E20" s="2">
         <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -12874,13 +12912,13 @@
         <v>40000065</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E21" s="2">
         <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -12906,13 +12944,13 @@
         <v>40000066</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="E22" s="2">
         <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -12938,13 +12976,13 @@
         <v>40000067</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E23" s="2">
         <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -12970,13 +13008,13 @@
         <v>40000068</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E24" s="2">
         <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -13002,13 +13040,13 @@
         <v>40000069</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E25" s="2">
         <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -13034,13 +13072,13 @@
         <v>40000070</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E26" s="2">
         <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -13066,13 +13104,13 @@
         <v>40000071</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E27" s="2">
         <v>14</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -13098,13 +13136,13 @@
         <v>40000072</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E28" s="2">
         <v>14</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -13130,13 +13168,13 @@
         <v>40000073</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E29" s="2">
         <v>14</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -13162,13 +13200,13 @@
         <v>40000074</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E30" s="2">
         <v>14</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -13194,13 +13232,13 @@
         <v>40000075</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E31" s="2">
         <v>14</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -13226,13 +13264,13 @@
         <v>40000076</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E32" s="2">
         <v>14</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -13258,13 +13296,13 @@
         <v>40000077</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E33" s="2">
         <v>14</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -13290,13 +13328,13 @@
         <v>40000078</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E34" s="2">
         <v>14</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -13322,13 +13360,13 @@
         <v>40000079</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E35" s="2">
         <v>14</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -13354,13 +13392,13 @@
         <v>40000080</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E36" s="2">
         <v>14</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -13386,13 +13424,13 @@
         <v>40000081</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E37" s="2">
         <v>14</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G37" s="2">
         <v>1</v>
@@ -13418,13 +13456,13 @@
         <v>40000082</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E38" s="2">
         <v>14</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G38" s="2">
         <v>1</v>
@@ -13450,13 +13488,13 @@
         <v>40000083</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E39" s="2">
         <v>14</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -13482,13 +13520,13 @@
         <v>40000084</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E40" s="2">
         <v>14</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -13514,13 +13552,13 @@
         <v>40000085</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E41" s="2">
         <v>14</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -13546,13 +13584,13 @@
         <v>40000086</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E42" s="2">
         <v>14</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -13578,13 +13616,13 @@
         <v>40000087</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E43" s="2">
         <v>14</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -13610,13 +13648,13 @@
         <v>40000088</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E44" s="2">
         <v>14</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -13642,13 +13680,13 @@
         <v>40000089</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E45" s="2">
         <v>14</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G45" s="2">
         <v>1</v>
@@ -13674,13 +13712,13 @@
         <v>40000090</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E46" s="2">
         <v>14</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -13706,13 +13744,13 @@
         <v>40000091</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E47" s="2">
         <v>14</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -13738,13 +13776,13 @@
         <v>40000092</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E48" s="2">
         <v>14</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -13770,13 +13808,13 @@
         <v>40000093</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="E49" s="2">
         <v>14</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -13802,13 +13840,13 @@
         <v>40000094</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E50" s="2">
         <v>14</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -13834,13 +13872,13 @@
         <v>40000095</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E51" s="2">
         <v>14</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -13866,13 +13904,13 @@
         <v>40000096</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E52" s="2">
         <v>14</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -13898,13 +13936,13 @@
         <v>40000097</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E53" s="2">
         <v>14</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G53" s="2">
         <v>1</v>
@@ -13930,13 +13968,13 @@
         <v>40000098</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E54" s="2">
         <v>14</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G54" s="2">
         <v>1</v>
@@ -13962,13 +14000,13 @@
         <v>40000099</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E55" s="2">
         <v>14</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G55" s="2">
         <v>1</v>
@@ -13994,13 +14032,13 @@
         <v>40000100</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E56" s="2">
         <v>14</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G56" s="2">
         <v>1</v>
@@ -14026,13 +14064,13 @@
         <v>40000101</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E57" s="2">
         <v>14</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G57" s="2">
         <v>1</v>
@@ -14058,13 +14096,13 @@
         <v>40000102</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E58" s="2">
         <v>14</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G58" s="2">
         <v>1</v>
@@ -14090,13 +14128,13 @@
         <v>40000103</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E59" s="2">
         <v>14</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G59" s="2">
         <v>1</v>
@@ -14122,13 +14160,13 @@
         <v>40000104</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="E60" s="2">
         <v>14</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G60" s="2">
         <v>1</v>
@@ -14154,13 +14192,13 @@
         <v>40000105</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E61" s="7">
         <v>14</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G61" s="7">
         <v>1</v>
@@ -14187,13 +14225,13 @@
         <v>40000106</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E62" s="2">
         <v>14</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G62" s="2">
         <v>1</v>
@@ -14220,13 +14258,13 @@
         <v>40000107</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E63" s="2">
         <v>14</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G63" s="2">
         <v>1</v>
@@ -14253,13 +14291,13 @@
         <v>40000108</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E64" s="2">
         <v>14</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G64" s="2">
         <v>1</v>
@@ -14286,13 +14324,13 @@
         <v>40000109</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E65" s="2">
         <v>14</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G65" s="2">
         <v>1</v>
@@ -14319,13 +14357,13 @@
         <v>40000110</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E66" s="2">
         <v>14</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G66" s="2">
         <v>1</v>
@@ -14352,13 +14390,13 @@
         <v>40000111</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E67" s="2">
         <v>14</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G67" s="2">
         <v>1</v>
@@ -14385,13 +14423,13 @@
         <v>40000112</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="E68" s="2">
         <v>14</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G68" s="2">
         <v>1</v>
@@ -14418,13 +14456,13 @@
         <v>40000113</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E69" s="2">
         <v>14</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G69" s="2">
         <v>1</v>
@@ -14451,13 +14489,13 @@
         <v>40000114</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E70" s="2">
         <v>14</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G70" s="2">
         <v>1</v>
@@ -14484,13 +14522,13 @@
         <v>40000115</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="E71" s="2">
         <v>14</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G71" s="2">
         <v>1</v>
@@ -14517,13 +14555,13 @@
         <v>40000116</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E72" s="2">
         <v>14</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G72" s="2">
         <v>1</v>
@@ -14550,13 +14588,13 @@
         <v>40000117</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E73" s="2">
         <v>14</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G73" s="2">
         <v>1</v>
@@ -14583,13 +14621,13 @@
         <v>40000118</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E74" s="2">
         <v>14</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G74" s="2">
         <v>1</v>
@@ -14616,13 +14654,13 @@
         <v>40000119</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E75" s="2">
         <v>14</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G75" s="2">
         <v>1</v>
@@ -14649,13 +14687,13 @@
         <v>40000120</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="E76" s="2">
         <v>14</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G76" s="2">
         <v>1</v>
@@ -14682,13 +14720,13 @@
         <v>40000121</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E77" s="2">
         <v>14</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G77" s="2">
         <v>1</v>
@@ -14715,13 +14753,13 @@
         <v>40000122</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E78" s="2">
         <v>14</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G78" s="2">
         <v>1</v>
@@ -14748,13 +14786,13 @@
         <v>40000123</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="E79" s="2">
         <v>14</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G79" s="2">
         <v>1</v>
@@ -14781,13 +14819,13 @@
         <v>40000124</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E80" s="2">
         <v>14</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G80" s="2">
         <v>1</v>
@@ -14814,13 +14852,13 @@
         <v>40000125</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="E81" s="2">
         <v>14</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G81" s="2">
         <v>1</v>
@@ -14846,13 +14884,13 @@
         <v>40000126</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E82" s="2">
         <v>14</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G82" s="2">
         <v>1</v>
@@ -14878,13 +14916,13 @@
         <v>40000127</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="E83" s="2">
         <v>14</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G83" s="2">
         <v>1</v>
@@ -14910,13 +14948,13 @@
         <v>40000128</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="E84" s="2">
         <v>14</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G84" s="2">
         <v>1</v>
@@ -14942,13 +14980,13 @@
         <v>40000129</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="E85" s="2">
         <v>14</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G85" s="2">
         <v>1</v>
@@ -14974,13 +15012,13 @@
         <v>40000130</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E86" s="2">
         <v>14</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G86" s="2">
         <v>1</v>
@@ -15006,13 +15044,13 @@
         <v>40000131</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E87" s="2">
         <v>14</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G87" s="2">
         <v>1</v>
@@ -15038,13 +15076,13 @@
         <v>40000132</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="E88" s="2">
         <v>14</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G88" s="2">
         <v>1</v>
@@ -15070,13 +15108,13 @@
         <v>40000133</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="E89" s="2">
         <v>14</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G89" s="2">
         <v>1</v>
@@ -15102,13 +15140,13 @@
         <v>40000134</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E90" s="2">
         <v>14</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G90" s="2">
         <v>1</v>
@@ -15134,13 +15172,13 @@
         <v>40000135</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="E91" s="2">
         <v>14</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G91" s="2">
         <v>1</v>
@@ -15166,13 +15204,13 @@
         <v>40000136</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="E92" s="2">
         <v>14</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G92" s="2">
         <v>1</v>
@@ -15198,13 +15236,13 @@
         <v>40000137</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E93" s="2">
         <v>14</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G93" s="2">
         <v>1</v>
@@ -15230,13 +15268,13 @@
         <v>40000138</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="E94" s="2">
         <v>14</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G94" s="2">
         <v>1</v>
@@ -15262,13 +15300,13 @@
         <v>40000139</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E95" s="2">
         <v>14</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G95" s="2">
         <v>1</v>
@@ -15433,13 +15471,13 @@
         <v>50000001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E6" s="2">
         <v>5</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -15465,13 +15503,13 @@
         <v>50000002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E7" s="2">
         <v>5</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -15497,13 +15535,13 @@
         <v>50000003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E8" s="2">
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -15529,13 +15567,13 @@
         <v>50000004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E9" s="2">
         <v>5</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -15561,13 +15599,13 @@
         <v>50000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E10" s="2">
         <v>5</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -15593,13 +15631,13 @@
         <v>50000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E11" s="2">
         <v>5</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -15625,13 +15663,13 @@
         <v>50000007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="E12" s="2">
         <v>5</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -15657,13 +15695,13 @@
         <v>50000008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="E13" s="2">
         <v>5</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -15689,13 +15727,13 @@
         <v>50000009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E14" s="2">
         <v>5</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -15721,13 +15759,13 @@
         <v>50000010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E15" s="2">
         <v>5</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -15753,13 +15791,13 @@
         <v>50000011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="E16" s="2">
         <v>5</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -15785,13 +15823,13 @@
         <v>50000012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="E17" s="2">
         <v>5</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -15817,13 +15855,13 @@
         <v>50000013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E18" s="2">
         <v>5</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -15849,13 +15887,13 @@
         <v>50000014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="E19" s="2">
         <v>5</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -15881,13 +15919,13 @@
         <v>50000015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="E20" s="2">
         <v>5</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -15913,13 +15951,13 @@
         <v>50000016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E21" s="2">
         <v>5</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -15945,13 +15983,13 @@
         <v>50000017</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="E22" s="2">
         <v>5</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -15977,13 +16015,13 @@
         <v>50000018</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E23" s="2">
         <v>5</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -16009,13 +16047,13 @@
         <v>50000019</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="E24" s="2">
         <v>5</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -16041,13 +16079,13 @@
         <v>50000020</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="E25" s="2">
         <v>5</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -16073,13 +16111,13 @@
         <v>50000021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="E26" s="2">
         <v>5</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -16105,13 +16143,13 @@
         <v>50000022</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="E27" s="2">
         <v>5</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -16137,13 +16175,13 @@
         <v>50000023</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E28" s="2">
         <v>5</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -16169,13 +16207,13 @@
         <v>50000024</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E29" s="2">
         <v>5</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -16201,13 +16239,13 @@
         <v>50000025</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="E30" s="2">
         <v>5</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -16233,13 +16271,13 @@
         <v>50000026</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="E31" s="2">
         <v>5</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -16265,13 +16303,13 @@
         <v>50000027</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E32" s="2">
         <v>5</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -16297,13 +16335,13 @@
         <v>50000028</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="E33" s="2">
         <v>5</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -16329,13 +16367,13 @@
         <v>50000029</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E34" s="2">
         <v>5</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -16361,13 +16399,13 @@
         <v>50000030</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E35" s="2">
         <v>5</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -16393,13 +16431,13 @@
         <v>50000031</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E36" s="2">
         <v>5</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -16425,13 +16463,13 @@
         <v>50000032</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="E37" s="2">
         <v>5</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="G37" s="2">
         <v>1</v>
@@ -16457,13 +16495,13 @@
         <v>50000033</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="E38" s="2">
         <v>5</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="G38" s="2">
         <v>1</v>
@@ -16489,13 +16527,13 @@
         <v>50000034</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="E39" s="2">
         <v>5</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -16521,13 +16559,13 @@
         <v>50000035</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="E40" s="2">
         <v>5</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -16553,13 +16591,13 @@
         <v>50000036</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="E41" s="2">
         <v>5</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -16585,13 +16623,13 @@
         <v>50000037</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="E42" s="2">
         <v>5</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -16617,13 +16655,13 @@
         <v>50000038</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="E43" s="2">
         <v>5</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -16649,13 +16687,13 @@
         <v>50000039</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="E44" s="2">
         <v>5</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -16681,13 +16719,13 @@
         <v>50000040</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E45" s="2">
         <v>5</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="G45" s="2">
         <v>1</v>
@@ -16713,13 +16751,13 @@
         <v>50000041</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="E46" s="2">
         <v>5</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -16745,13 +16783,13 @@
         <v>50000042</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="E47" s="2">
         <v>5</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -16777,13 +16815,13 @@
         <v>50000043</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="E48" s="2">
         <v>5</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -16809,13 +16847,13 @@
         <v>50000044</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="E49" s="2">
         <v>5</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -16841,13 +16879,13 @@
         <v>50000045</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E50" s="2">
         <v>5</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -16873,13 +16911,13 @@
         <v>50000046</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="E51" s="2">
         <v>5</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -16905,13 +16943,13 @@
         <v>50000047</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="E52" s="2">
         <v>5</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -16937,13 +16975,13 @@
         <v>50000048</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E53" s="2">
         <v>5</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="G53" s="2">
         <v>1</v>
@@ -16969,13 +17007,13 @@
         <v>50000049</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="E54" s="2">
         <v>5</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="G54" s="2">
         <v>1</v>
@@ -17001,13 +17039,13 @@
         <v>50000050</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="E55" s="2">
         <v>5</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="G55" s="2">
         <v>1</v>
@@ -17033,13 +17071,13 @@
         <v>50000051</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="E56" s="2">
         <v>5</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="G56" s="2">
         <v>1</v>
@@ -17065,13 +17103,13 @@
         <v>50000052</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="E57" s="2">
         <v>5</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="G57" s="2">
         <v>1</v>
@@ -17097,13 +17135,13 @@
         <v>50000053</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="E58" s="2">
         <v>5</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="G58" s="2">
         <v>1</v>
@@ -17129,13 +17167,13 @@
         <v>50000054</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="E59" s="2">
         <v>5</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="G59" s="2">
         <v>1</v>
@@ -17161,13 +17199,13 @@
         <v>50000055</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="E60" s="2">
         <v>5</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="G60" s="2">
         <v>1</v>
@@ -17193,13 +17231,13 @@
         <v>50000056</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="E61" s="2">
         <v>5</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="G61" s="2">
         <v>1</v>
@@ -17225,13 +17263,13 @@
         <v>50000057</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="E62" s="2">
         <v>5</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="G62" s="2">
         <v>1</v>
@@ -17257,13 +17295,13 @@
         <v>50000058</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="E63" s="2">
         <v>5</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="G63" s="2">
         <v>1</v>
@@ -17289,13 +17327,13 @@
         <v>50000059</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="E64" s="2">
         <v>5</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="G64" s="2">
         <v>1</v>
@@ -17321,13 +17359,13 @@
         <v>50000060</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="E65" s="2">
         <v>5</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="G65" s="2">
         <v>1</v>
@@ -17353,13 +17391,13 @@
         <v>50000061</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="E66" s="2">
         <v>5</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="G66" s="2">
         <v>1</v>
@@ -17385,13 +17423,13 @@
         <v>50000062</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="E67" s="2">
         <v>5</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="G67" s="2">
         <v>1</v>
@@ -17417,13 +17455,13 @@
         <v>50000063</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E68" s="2">
         <v>5</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="G68" s="2">
         <v>1</v>
@@ -17449,13 +17487,13 @@
         <v>50000064</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="E69" s="2">
         <v>5</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="G69" s="2">
         <v>1</v>
@@ -17481,13 +17519,13 @@
         <v>50000065</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="E70" s="2">
         <v>5</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="G70" s="2">
         <v>1</v>
@@ -17513,13 +17551,13 @@
         <v>50000066</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="E71" s="2">
         <v>5</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="G71" s="2">
         <v>1</v>
@@ -17545,13 +17583,13 @@
         <v>50000067</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="E72" s="2">
         <v>5</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="G72" s="2">
         <v>1</v>
@@ -17577,13 +17615,13 @@
         <v>50000068</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="E73" s="2">
         <v>5</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="G73" s="2">
         <v>1</v>
@@ -17609,13 +17647,13 @@
         <v>50000069</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="E74" s="2">
         <v>5</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="G74" s="2">
         <v>1</v>
@@ -17641,13 +17679,13 @@
         <v>50000070</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E75" s="2">
         <v>5</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="G75" s="2">
         <v>1</v>
@@ -17673,13 +17711,13 @@
         <v>50000071</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="E76" s="2">
         <v>5</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="G76" s="2">
         <v>1</v>
@@ -17705,13 +17743,13 @@
         <v>50000072</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="E77" s="2">
         <v>5</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="G77" s="2">
         <v>1</v>
@@ -17737,13 +17775,13 @@
         <v>50000073</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E78" s="2">
         <v>5</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="G78" s="2">
         <v>1</v>
@@ -17769,13 +17807,13 @@
         <v>50000074</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="E79" s="2">
         <v>5</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="G79" s="2">
         <v>1</v>
@@ -17801,13 +17839,13 @@
         <v>50000075</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="E80" s="2">
         <v>5</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="G80" s="2">
         <v>1</v>
@@ -17833,13 +17871,13 @@
         <v>50000076</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="E81" s="2">
         <v>5</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="G81" s="2">
         <v>1</v>
@@ -17865,13 +17903,13 @@
         <v>50000077</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="E82" s="2">
         <v>5</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="G82" s="2">
         <v>1</v>
@@ -17897,13 +17935,13 @@
         <v>50000078</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="E83" s="2">
         <v>5</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="G83" s="2">
         <v>1</v>
@@ -17929,13 +17967,13 @@
         <v>50000079</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="E84" s="2">
         <v>5</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="G84" s="2">
         <v>1</v>
@@ -17961,13 +17999,13 @@
         <v>50000080</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="E85" s="2">
         <v>5</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="G85" s="2">
         <v>1</v>
@@ -17993,13 +18031,13 @@
         <v>50000081</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E86" s="2">
         <v>5</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="G86" s="2">
         <v>1</v>
@@ -18025,13 +18063,13 @@
         <v>50000082</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E87" s="2">
         <v>5</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="G87" s="2">
         <v>1</v>
@@ -18057,13 +18095,13 @@
         <v>50000083</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E88" s="2">
         <v>5</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="G88" s="2">
         <v>1</v>
@@ -18089,13 +18127,13 @@
         <v>50000084</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E89" s="2">
         <v>5</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="G89" s="2">
         <v>1</v>
@@ -18121,13 +18159,13 @@
         <v>50000085</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="E90" s="2">
         <v>5</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="G90" s="2">
         <v>1</v>
@@ -18153,13 +18191,13 @@
         <v>50000086</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="E91" s="2">
         <v>5</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="G91" s="2">
         <v>1</v>
@@ -18185,13 +18223,13 @@
         <v>50000087</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="E92" s="2">
         <v>5</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="G92" s="2">
         <v>1</v>
@@ -18217,13 +18255,13 @@
         <v>50000088</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="E93" s="2">
         <v>5</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="G93" s="2">
         <v>1</v>
@@ -18249,13 +18287,13 @@
         <v>50000089</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="E94" s="2">
         <v>5</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="G94" s="2">
         <v>1</v>
@@ -18281,13 +18319,13 @@
         <v>50000090</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="E95" s="2">
         <v>5</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="G95" s="2">
         <v>1</v>
@@ -18313,13 +18351,13 @@
         <v>50000091</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="E96" s="2">
         <v>5</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="G96" s="2">
         <v>1</v>
@@ -18345,13 +18383,13 @@
         <v>50000092</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="E97" s="2">
         <v>5</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="G97" s="2">
         <v>1</v>
@@ -18377,13 +18415,13 @@
         <v>50000093</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="E98" s="2">
         <v>5</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="G98" s="2">
         <v>1</v>
@@ -18409,13 +18447,13 @@
         <v>50000094</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="E99" s="2">
         <v>5</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="G99" s="2">
         <v>1</v>
@@ -18441,13 +18479,13 @@
         <v>50000095</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="E100" s="2">
         <v>5</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="G100" s="2">
         <v>1</v>
@@ -18473,13 +18511,13 @@
         <v>50000096</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="E101" s="2">
         <v>5</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="G101" s="2">
         <v>1</v>
@@ -18505,13 +18543,13 @@
         <v>50000097</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="E102" s="2">
         <v>5</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="G102" s="2">
         <v>1</v>
@@ -18537,13 +18575,13 @@
         <v>50000098</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="E103" s="2">
         <v>5</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G103" s="2">
         <v>1</v>
@@ -18569,13 +18607,13 @@
         <v>50000099</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="E104" s="2">
         <v>5</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="G104" s="2">
         <v>1</v>
@@ -18601,13 +18639,13 @@
         <v>50000100</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="E105" s="2">
         <v>5</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="G105" s="2">
         <v>1</v>
@@ -18633,13 +18671,13 @@
         <v>50000101</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="E106" s="2">
         <v>5</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="G106" s="2">
         <v>1</v>
@@ -18665,13 +18703,13 @@
         <v>50000102</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="E107" s="2">
         <v>5</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="G107" s="2">
         <v>1</v>
@@ -18697,13 +18735,13 @@
         <v>50000103</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="E108" s="2">
         <v>5</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="G108" s="2">
         <v>1</v>
@@ -18729,13 +18767,13 @@
         <v>50000104</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="E109" s="2">
         <v>5</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="G109" s="2">
         <v>1</v>
@@ -18900,13 +18938,13 @@
         <v>180001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="E6" s="2">
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -18926,13 +18964,13 @@
         <v>180002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="E7" s="2">
         <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -18952,13 +18990,13 @@
         <v>180003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="E8" s="2">
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -18978,13 +19016,13 @@
         <v>180004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="E9" s="2">
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -19004,13 +19042,13 @@
         <v>180005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="E10" s="2">
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -19030,13 +19068,13 @@
         <v>180006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="E11" s="2">
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -19058,13 +19096,13 @@
         <v>180007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="E12" s="2">
         <v>18</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -19086,13 +19124,13 @@
         <v>180008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="E13" s="2">
         <v>18</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -19114,13 +19152,13 @@
         <v>180009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="E14" s="2">
         <v>18</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -19142,13 +19180,13 @@
         <v>180010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="E15" s="2">
         <v>18</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -19170,13 +19208,13 @@
         <v>180011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E16" s="2">
         <v>18</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -19198,13 +19236,13 @@
         <v>180012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="E17" s="2">
         <v>18</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -19226,13 +19264,13 @@
         <v>180013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="E18" s="2">
         <v>18</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -19254,13 +19292,13 @@
         <v>180014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="E19" s="2">
         <v>18</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -19282,13 +19320,13 @@
         <v>180015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="E20" s="2">
         <v>18</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -19310,13 +19348,13 @@
         <v>180016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="E21" s="2">
         <v>18</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -19338,13 +19376,13 @@
         <v>180017</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="E22" s="2">
         <v>18</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -19366,13 +19404,13 @@
         <v>180018</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="E23" s="2">
         <v>18</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -19394,13 +19432,13 @@
         <v>180019</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="E24" s="2">
         <v>18</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -19422,13 +19460,13 @@
         <v>180020</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="E25" s="2">
         <v>18</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -19450,13 +19488,13 @@
         <v>180021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="E26" s="2">
         <v>18</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -19483,13 +19521,13 @@
         <v>180030</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="E28" s="2">
         <v>18</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -19511,13 +19549,13 @@
         <v>180031</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="E29" s="2">
         <v>18</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="G29" s="3">
         <v>1</v>
@@ -19537,13 +19575,13 @@
         <v>180032</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="E30" s="2">
         <v>18</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="G30" s="3">
         <v>1</v>
@@ -19563,13 +19601,13 @@
         <v>180033</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="E31" s="2">
         <v>18</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="G31" s="3">
         <v>1</v>
@@ -19589,13 +19627,13 @@
         <v>180034</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="E32" s="2">
         <v>18</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="G32" s="3">
         <v>1</v>
@@ -19617,13 +19655,13 @@
         <v>180035</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="E33" s="2">
         <v>18</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="G33" s="3">
         <v>1</v>
@@ -19645,13 +19683,13 @@
         <v>180036</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="E34" s="2">
         <v>18</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="G34" s="3">
         <v>1</v>
@@ -19812,13 +19850,13 @@
         <v>190001</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E6" s="2">
         <v>19</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -19838,13 +19876,13 @@
         <v>190002</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="E7" s="2">
         <v>19</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -19864,13 +19902,13 @@
         <v>190003</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="E8" s="2">
         <v>19</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -19890,13 +19928,13 @@
         <v>190004</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="E9" s="2">
         <v>19</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -19916,13 +19954,13 @@
         <v>190005</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="E10" s="2">
         <v>19</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -19942,13 +19980,13 @@
         <v>190006</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="E11" s="2">
         <v>19</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -871,7 +871,7 @@
     <t>口粮</t>
   </si>
   <si>
-    <t>宠物材料</t>
+    <t>魂宠升级材料</t>
   </si>
   <si>
     <t>图鉴碎片</t>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -1069,43 +1069,43 @@
     <t>魔鲸王骨</t>
   </si>
   <si>
-    <t>白色宠蛋</t>
+    <t>白色宠物</t>
   </si>
   <si>
     <t>开启一个白色宠物</t>
   </si>
   <si>
-    <t>绿色宠蛋</t>
+    <t>绿色宠物</t>
   </si>
   <si>
     <t>开启一个绿色宠物</t>
   </si>
   <si>
-    <t>蓝色宠蛋</t>
+    <t>蓝色宠物</t>
   </si>
   <si>
     <t>开启一个蓝色宠物</t>
   </si>
   <si>
-    <t>紫色宠蛋</t>
+    <t>紫色宠物</t>
   </si>
   <si>
     <t>开启一个紫色宠物</t>
   </si>
   <si>
-    <t>橙色宠蛋</t>
+    <t>橙色宠物</t>
   </si>
   <si>
     <t>开启一个橙色宠物</t>
   </si>
   <si>
-    <t>红色宠蛋</t>
+    <t>红色宠物</t>
   </si>
   <si>
     <t>开启一个红色宠物</t>
   </si>
   <si>
-    <t>金色宠蛋</t>
+    <t>金色宠物</t>
   </si>
   <si>
     <t>开启一个金色宠物</t>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -344,7 +344,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="759">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1424" uniqueCount="765">
   <si>
     <t>_Id</t>
   </si>
@@ -872,6 +872,24 @@
   </si>
   <si>
     <t>魂宠升级材料</t>
+  </si>
+  <si>
+    <t>橙色魂心</t>
+  </si>
+  <si>
+    <t>橙色魂宠进阶材料</t>
+  </si>
+  <si>
+    <t>红色魂心</t>
+  </si>
+  <si>
+    <t>红色魂宠进阶材料</t>
+  </si>
+  <si>
+    <t>金色魂心</t>
+  </si>
+  <si>
+    <t>金色魂宠进阶材料</t>
   </si>
   <si>
     <t>图鉴碎片</t>
@@ -4932,7 +4950,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:M101"/>
+  <dimension ref="C3:M105"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="3"/>
@@ -5760,30 +5778,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
+    <row r="28" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C28" s="3">
+        <v>4023</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E28" s="3">
+        <v>5</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="G28" s="3">
+        <v>1</v>
+      </c>
+      <c r="H28" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I28" s="3">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3">
+        <v>5</v>
+      </c>
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="29" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C29" s="3">
-        <v>4101</v>
+        <v>4024</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E29" s="3">
         <v>5</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G29" s="3">
         <v>1</v>
@@ -5806,16 +5844,16 @@
     </row>
     <row r="30" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C30" s="3">
-        <v>4102</v>
+        <v>4025</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E30" s="3">
         <v>5</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G30" s="3">
         <v>1</v>
@@ -5836,82 +5874,42 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C31" s="3">
-        <v>4103</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="E31" s="3">
-        <v>5</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="G31" s="3">
-        <v>1</v>
-      </c>
-      <c r="H31" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="I31" s="3">
-        <v>0</v>
-      </c>
-      <c r="J31" s="3">
-        <v>5</v>
-      </c>
-      <c r="L31" s="3">
-        <v>0</v>
-      </c>
-      <c r="M31" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C32" s="3">
-        <v>4104</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="E32" s="3">
-        <v>5</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="G32" s="3">
-        <v>1</v>
-      </c>
-      <c r="H32" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>5</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
+    <row r="31" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
     </row>
     <row r="33" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C33" s="3">
-        <v>4105</v>
+        <v>4101</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E33" s="3">
         <v>5</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>149</v>
+        <v>183</v>
       </c>
       <c r="G33" s="3">
         <v>1</v>
@@ -5934,16 +5932,16 @@
     </row>
     <row r="34" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C34" s="3">
-        <v>4106</v>
+        <v>4102</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E34" s="3">
         <v>5</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="G34" s="3">
         <v>1</v>
@@ -5966,16 +5964,16 @@
     </row>
     <row r="35" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C35" s="3">
-        <v>4107</v>
+        <v>4103</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E35" s="3">
         <v>5</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>184</v>
+        <v>149</v>
       </c>
       <c r="G35" s="3">
         <v>1</v>
@@ -5998,16 +5996,16 @@
     </row>
     <row r="36" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C36" s="3">
-        <v>4108</v>
+        <v>4104</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E36" s="3">
         <v>5</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>186</v>
+        <v>149</v>
       </c>
       <c r="G36" s="3">
         <v>1</v>
@@ -6030,16 +6028,16 @@
     </row>
     <row r="37" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C37" s="3">
-        <v>4109</v>
+        <v>4105</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E37" s="3">
         <v>5</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>188</v>
+        <v>149</v>
       </c>
       <c r="G37" s="3">
         <v>1</v>
@@ -6062,16 +6060,16 @@
     </row>
     <row r="38" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C38" s="3">
-        <v>4110</v>
+        <v>4106</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E38" s="3">
         <v>5</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G38" s="3">
         <v>1</v>
@@ -6094,16 +6092,16 @@
     </row>
     <row r="39" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C39" s="3">
-        <v>4111</v>
+        <v>4107</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E39" s="3">
         <v>5</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G39" s="3">
         <v>1</v>
@@ -6124,9 +6122,41 @@
         <v>0</v>
       </c>
     </row>
+    <row r="40" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C40" s="3">
+        <v>4108</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="E40" s="3">
+        <v>5</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="G40" s="3">
+        <v>1</v>
+      </c>
+      <c r="H40" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I40" s="3">
+        <v>0</v>
+      </c>
+      <c r="J40" s="3">
+        <v>5</v>
+      </c>
+      <c r="L40" s="3">
+        <v>0</v>
+      </c>
+      <c r="M40" s="3">
+        <v>0</v>
+      </c>
+    </row>
     <row r="41" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C41" s="3">
-        <v>4201</v>
+        <v>4109</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>193</v>
@@ -6141,7 +6171,7 @@
         <v>1</v>
       </c>
       <c r="H41" s="3">
-        <v>2000000</v>
+        <v>9999999</v>
       </c>
       <c r="I41" s="3">
         <v>0</v>
@@ -6150,15 +6180,15 @@
         <v>5</v>
       </c>
       <c r="L41" s="3">
-        <v>4002</v>
+        <v>0</v>
       </c>
       <c r="M41" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C42" s="3">
-        <v>4202</v>
+        <v>4110</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>195</v>
@@ -6173,7 +6203,7 @@
         <v>1</v>
       </c>
       <c r="H42" s="3">
-        <v>99999</v>
+        <v>9999999</v>
       </c>
       <c r="I42" s="3">
         <v>0</v>
@@ -6188,50 +6218,47 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C44" s="3">
-        <v>6101</v>
-      </c>
-      <c r="D44" s="3" t="s">
+    <row r="43" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C43" s="3">
+        <v>4111</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="E44" s="3">
-        <v>7</v>
-      </c>
-      <c r="F44" s="3" t="s">
+      <c r="E43" s="3">
+        <v>5</v>
+      </c>
+      <c r="F43" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="G44" s="3">
-        <v>1</v>
-      </c>
-      <c r="H44" s="3">
-        <v>99999</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>4</v>
-      </c>
-      <c r="K44" s="3">
-        <v>1</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
-      <c r="M44" s="3">
+      <c r="G43" s="3">
+        <v>1</v>
+      </c>
+      <c r="H43" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I43" s="3">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3">
+        <v>5</v>
+      </c>
+      <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="45" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C45" s="3">
-        <v>6102</v>
+        <v>4201</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>199</v>
       </c>
       <c r="E45" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>200</v>
@@ -6240,33 +6267,30 @@
         <v>1</v>
       </c>
       <c r="H45" s="3">
-        <v>99999</v>
+        <v>2000000</v>
       </c>
       <c r="I45" s="3">
         <v>0</v>
       </c>
       <c r="J45" s="3">
-        <v>4</v>
-      </c>
-      <c r="K45" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L45" s="3">
-        <v>0</v>
+        <v>4002</v>
       </c>
       <c r="M45" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="46" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C46" s="3">
-        <v>6103</v>
+        <v>4202</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>201</v>
       </c>
       <c r="E46" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>202</v>
@@ -6281,10 +6305,7 @@
         <v>0</v>
       </c>
       <c r="J46" s="3">
-        <v>4</v>
-      </c>
-      <c r="K46" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L46" s="3">
         <v>0</v>
@@ -6293,53 +6314,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C47" s="3">
-        <v>6104</v>
-      </c>
-      <c r="D47" s="3" t="s">
+    <row r="48" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C48" s="3">
+        <v>6101</v>
+      </c>
+      <c r="D48" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="E47" s="3">
-        <v>7</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="G47" s="3">
-        <v>1</v>
-      </c>
-      <c r="H47" s="3">
-        <v>99999</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>4</v>
-      </c>
-      <c r="K47" s="3">
-        <v>4</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" customHeight="1" spans="3:13">
-      <c r="C48" s="3">
-        <v>6105</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>205</v>
       </c>
       <c r="E48" s="3">
         <v>7</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G48" s="3">
         <v>1</v>
@@ -6354,7 +6340,7 @@
         <v>4</v>
       </c>
       <c r="K48" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L48" s="3">
         <v>0</v>
@@ -6365,16 +6351,16 @@
     </row>
     <row r="49" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C49" s="3">
-        <v>6106</v>
+        <v>6102</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E49" s="3">
         <v>7</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G49" s="3">
         <v>1</v>
@@ -6389,7 +6375,7 @@
         <v>4</v>
       </c>
       <c r="K49" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
@@ -6398,18 +6384,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" customHeight="1" spans="3:13">
+    <row r="50" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C50" s="3">
-        <v>7101</v>
+        <v>6103</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E50" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G50" s="3">
         <v>1</v>
@@ -6424,7 +6410,7 @@
         <v>4</v>
       </c>
       <c r="K50" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L50" s="3">
         <v>0</v>
@@ -6433,18 +6419,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" customHeight="1" spans="3:13">
+    <row r="51" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C51" s="3">
-        <v>7102</v>
+        <v>6104</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E51" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G51" s="3">
         <v>1</v>
@@ -6459,7 +6445,7 @@
         <v>4</v>
       </c>
       <c r="K51" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L51" s="3">
         <v>0</v>
@@ -6470,16 +6456,16 @@
     </row>
     <row r="52" customHeight="1" spans="3:13">
       <c r="C52" s="3">
-        <v>7103</v>
+        <v>6105</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E52" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G52" s="3">
         <v>1</v>
@@ -6494,7 +6480,7 @@
         <v>4</v>
       </c>
       <c r="K52" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -6503,18 +6489,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" customHeight="1" spans="3:13">
+    <row r="53" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C53" s="3">
-        <v>7104</v>
+        <v>6106</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E53" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G53" s="3">
         <v>1</v>
@@ -6529,7 +6515,7 @@
         <v>4</v>
       </c>
       <c r="K53" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L53" s="3">
         <v>0</v>
@@ -6540,16 +6526,16 @@
     </row>
     <row r="54" customHeight="1" spans="3:13">
       <c r="C54" s="3">
-        <v>7105</v>
+        <v>7101</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E54" s="3">
         <v>8</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G54" s="3">
         <v>1</v>
@@ -6564,7 +6550,7 @@
         <v>4</v>
       </c>
       <c r="K54" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L54" s="3">
         <v>0</v>
@@ -6575,16 +6561,16 @@
     </row>
     <row r="55" customHeight="1" spans="3:13">
       <c r="C55" s="3">
-        <v>7107</v>
+        <v>7102</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E55" s="3">
         <v>8</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G55" s="3">
         <v>1</v>
@@ -6599,7 +6585,7 @@
         <v>4</v>
       </c>
       <c r="K55" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L55" s="3">
         <v>0</v>
@@ -6608,146 +6594,158 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" s="3" customFormat="1" customHeight="1" spans="3:13">
+    <row r="56" customHeight="1" spans="3:13">
+      <c r="C56" s="3">
+        <v>7103</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E56" s="3">
+        <v>8</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="G56" s="3">
+        <v>1</v>
+      </c>
+      <c r="H56" s="3">
+        <v>99999</v>
+      </c>
+      <c r="I56" s="3">
+        <v>0</v>
+      </c>
+      <c r="J56" s="3">
+        <v>4</v>
+      </c>
+      <c r="K56" s="3">
+        <v>3</v>
+      </c>
+      <c r="L56" s="3">
+        <v>0</v>
+      </c>
+      <c r="M56" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:13">
+      <c r="C57" s="3">
+        <v>7104</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E57" s="3">
+        <v>8</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="G57" s="3">
+        <v>1</v>
+      </c>
+      <c r="H57" s="3">
+        <v>99999</v>
+      </c>
+      <c r="I57" s="3">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3">
+        <v>4</v>
+      </c>
+      <c r="K57" s="3">
+        <v>4</v>
+      </c>
+      <c r="L57" s="3">
+        <v>0</v>
+      </c>
+      <c r="M57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:13">
+      <c r="C58" s="3">
+        <v>7105</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E58" s="3">
+        <v>8</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="G58" s="3">
+        <v>1</v>
+      </c>
+      <c r="H58" s="3">
+        <v>99999</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
+        <v>4</v>
+      </c>
+      <c r="K58" s="3">
+        <v>5</v>
+      </c>
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="3:13">
       <c r="C59" s="3">
-        <v>8001</v>
+        <v>7107</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="E59" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="G59" s="3">
         <v>1</v>
       </c>
       <c r="H59" s="3">
-        <v>9999999</v>
+        <v>99999</v>
       </c>
       <c r="I59" s="3">
         <v>0</v>
       </c>
       <c r="J59" s="3">
+        <v>4</v>
+      </c>
+      <c r="K59" s="3">
         <v>6</v>
       </c>
       <c r="L59" s="3">
         <v>0</v>
       </c>
       <c r="M59" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C60" s="3">
-        <v>8002</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="E60" s="3">
-        <v>5</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="G60" s="3">
-        <v>1</v>
-      </c>
-      <c r="H60" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="I60" s="3">
-        <v>0</v>
-      </c>
-      <c r="J60" s="3">
-        <v>6</v>
-      </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C61" s="3">
-        <v>8003</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="E61" s="3">
-        <v>5</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="G61" s="3">
-        <v>1</v>
-      </c>
-      <c r="H61" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
-      <c r="J61" s="3">
-        <v>6</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C62" s="3">
-        <v>8004</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="E62" s="3">
-        <v>5</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="G62" s="3">
-        <v>1</v>
-      </c>
-      <c r="H62" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>6</v>
-      </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
-      <c r="M62" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="63" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C63" s="3">
-        <v>8005</v>
+        <v>8001</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E63" s="3">
         <v>5</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="G63" s="3">
         <v>1</v>
@@ -6770,16 +6768,16 @@
     </row>
     <row r="64" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C64" s="3">
-        <v>8006</v>
+        <v>8002</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E64" s="3">
         <v>5</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="G64" s="3">
         <v>1</v>
@@ -6802,16 +6800,16 @@
     </row>
     <row r="65" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C65" s="3">
-        <v>8007</v>
+        <v>8003</v>
       </c>
       <c r="D65" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="E65" s="3">
+        <v>5</v>
+      </c>
+      <c r="F65" s="3" t="s">
         <v>228</v>
-      </c>
-      <c r="E65" s="3">
-        <v>5</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>222</v>
       </c>
       <c r="G65" s="3">
         <v>1</v>
@@ -6834,16 +6832,16 @@
     </row>
     <row r="66" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C66" s="3">
-        <v>8008</v>
+        <v>8004</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E66" s="3">
         <v>5</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="G66" s="3">
         <v>1</v>
@@ -6866,16 +6864,16 @@
     </row>
     <row r="67" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C67" s="3">
-        <v>8009</v>
+        <v>8005</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E67" s="3">
         <v>5</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="G67" s="3">
         <v>1</v>
@@ -6898,16 +6896,16 @@
     </row>
     <row r="68" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C68" s="3">
-        <v>8010</v>
+        <v>8006</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E68" s="3">
         <v>5</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="G68" s="3">
         <v>1</v>
@@ -6928,18 +6926,50 @@
         <v>0</v>
       </c>
     </row>
+    <row r="69" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C69" s="3">
+        <v>8007</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E69" s="3">
+        <v>5</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="G69" s="3">
+        <v>1</v>
+      </c>
+      <c r="H69" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I69" s="3">
+        <v>0</v>
+      </c>
+      <c r="J69" s="3">
+        <v>6</v>
+      </c>
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
     <row r="70" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C70" s="3">
-        <v>8101</v>
-      </c>
-      <c r="D70" s="11" t="s">
-        <v>232</v>
+        <v>8008</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>235</v>
       </c>
       <c r="E70" s="3">
         <v>5</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="G70" s="3">
         <v>1</v>
@@ -6951,7 +6981,7 @@
         <v>0</v>
       </c>
       <c r="J70" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L70" s="3">
         <v>0</v>
@@ -6962,16 +6992,16 @@
     </row>
     <row r="71" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C71" s="3">
-        <v>8102</v>
-      </c>
-      <c r="D71" s="11" t="s">
-        <v>234</v>
+        <v>8009</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>236</v>
       </c>
       <c r="E71" s="3">
         <v>5</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="G71" s="3">
         <v>1</v>
@@ -6983,7 +7013,7 @@
         <v>0</v>
       </c>
       <c r="J71" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L71" s="3">
         <v>0</v>
@@ -6994,16 +7024,16 @@
     </row>
     <row r="72" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C72" s="3">
-        <v>8103</v>
-      </c>
-      <c r="D72" s="11" t="s">
-        <v>235</v>
+        <v>8010</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>237</v>
       </c>
       <c r="E72" s="3">
         <v>5</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="G72" s="3">
         <v>1</v>
@@ -7015,59 +7045,27 @@
         <v>0</v>
       </c>
       <c r="J72" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L72" s="3">
         <v>0</v>
       </c>
       <c r="M72" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C73" s="3">
-        <v>8104</v>
-      </c>
-      <c r="D73" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="E73" s="3">
-        <v>5</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="G73" s="3">
-        <v>1</v>
-      </c>
-      <c r="H73" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="I73" s="3">
-        <v>0</v>
-      </c>
-      <c r="J73" s="3">
-        <v>7</v>
-      </c>
-      <c r="L73" s="3">
-        <v>0</v>
-      </c>
-      <c r="M73" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="74" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C74" s="3">
-        <v>8105</v>
+        <v>8101</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E74" s="3">
         <v>5</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="G74" s="3">
         <v>1</v>
@@ -7090,16 +7088,16 @@
     </row>
     <row r="75" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C75" s="3">
-        <v>8106</v>
+        <v>8102</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E75" s="3">
         <v>5</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="G75" s="3">
         <v>1</v>
@@ -7122,16 +7120,16 @@
     </row>
     <row r="76" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C76" s="3">
-        <v>8107</v>
+        <v>8103</v>
       </c>
       <c r="D76" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="E76" s="3">
+        <v>5</v>
+      </c>
+      <c r="F76" s="3" t="s">
         <v>239</v>
-      </c>
-      <c r="E76" s="3">
-        <v>5</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>233</v>
       </c>
       <c r="G76" s="3">
         <v>1</v>
@@ -7154,16 +7152,16 @@
     </row>
     <row r="77" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C77" s="3">
-        <v>8108</v>
+        <v>8104</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E77" s="3">
         <v>5</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="G77" s="3">
         <v>1</v>
@@ -7184,33 +7182,62 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" customHeight="1" spans="3:13">
+    <row r="78" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C78" s="3">
+        <v>8105</v>
+      </c>
+      <c r="D78" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="E78" s="3">
+        <v>5</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="G78" s="3">
+        <v>1</v>
+      </c>
+      <c r="H78" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I78" s="3">
+        <v>0</v>
+      </c>
+      <c r="J78" s="3">
+        <v>7</v>
+      </c>
+      <c r="L78" s="3">
+        <v>0</v>
+      </c>
+      <c r="M78" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C79" s="3">
-        <v>8201</v>
+        <v>8106</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="E79" s="3">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="G79" s="3">
         <v>1</v>
       </c>
       <c r="H79" s="3">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="I79" s="3">
         <v>0</v>
       </c>
       <c r="J79" s="3">
-        <v>1</v>
-      </c>
-      <c r="K79" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L79" s="3">
         <v>0</v>
@@ -7219,33 +7246,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" customHeight="1" spans="3:13">
+    <row r="80" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C80" s="3">
-        <v>8202</v>
+        <v>8107</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E80" s="3">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="G80" s="3">
         <v>1</v>
       </c>
       <c r="H80" s="3">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="I80" s="3">
         <v>0</v>
       </c>
       <c r="J80" s="3">
-        <v>2</v>
-      </c>
-      <c r="K80" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L80" s="3">
         <v>0</v>
@@ -7254,88 +7278,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" customHeight="1" spans="3:13">
+    <row r="81" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C81" s="3">
-        <v>8203</v>
+        <v>8108</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E81" s="3">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="G81" s="3">
         <v>1</v>
       </c>
       <c r="H81" s="3">
-        <v>1</v>
+        <v>9999999</v>
       </c>
       <c r="I81" s="3">
         <v>0</v>
       </c>
       <c r="J81" s="3">
-        <v>3</v>
-      </c>
-      <c r="K81" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L81" s="3">
         <v>0</v>
       </c>
       <c r="M81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" customHeight="1" spans="3:13">
-      <c r="C82" s="3">
-        <v>8204</v>
-      </c>
-      <c r="D82" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="E82" s="3">
-        <v>16</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="G82" s="3">
-        <v>1</v>
-      </c>
-      <c r="H82" s="3">
-        <v>1</v>
-      </c>
-      <c r="I82" s="3">
-        <v>0</v>
-      </c>
-      <c r="J82" s="3">
-        <v>4</v>
-      </c>
-      <c r="K82" s="3">
-        <v>0</v>
-      </c>
-      <c r="L82" s="3">
-        <v>0</v>
-      </c>
-      <c r="M82" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:13">
       <c r="C83" s="3">
-        <v>8205</v>
+        <v>8201</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E83" s="3">
         <v>16</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G83" s="3">
         <v>1</v>
@@ -7347,7 +7333,7 @@
         <v>0</v>
       </c>
       <c r="J83" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -7361,16 +7347,16 @@
     </row>
     <row r="84" customHeight="1" spans="3:13">
       <c r="C84" s="3">
-        <v>8206</v>
+        <v>8202</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E84" s="3">
         <v>16</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G84" s="3">
         <v>1</v>
@@ -7382,7 +7368,7 @@
         <v>0</v>
       </c>
       <c r="J84" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K84" s="3">
         <v>0</v>
@@ -7396,50 +7382,178 @@
     </row>
     <row r="85" customHeight="1" spans="3:13">
       <c r="C85" s="3">
-        <v>8207</v>
+        <v>8203</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E85" s="3">
         <v>16</v>
       </c>
       <c r="F85" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="G85" s="3">
+        <v>1</v>
+      </c>
+      <c r="H85" s="3">
+        <v>1</v>
+      </c>
+      <c r="I85" s="3">
+        <v>0</v>
+      </c>
+      <c r="J85" s="3">
+        <v>3</v>
+      </c>
+      <c r="K85" s="3">
+        <v>0</v>
+      </c>
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" spans="3:13">
+      <c r="C86" s="3">
+        <v>8204</v>
+      </c>
+      <c r="D86" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="E86" s="3">
+        <v>16</v>
+      </c>
+      <c r="F86" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="G85" s="3">
-        <v>1</v>
-      </c>
-      <c r="H85" s="3">
-        <v>1</v>
-      </c>
-      <c r="I85" s="3">
-        <v>0</v>
-      </c>
-      <c r="J85" s="3">
+      <c r="G86" s="3">
+        <v>1</v>
+      </c>
+      <c r="H86" s="3">
+        <v>1</v>
+      </c>
+      <c r="I86" s="3">
+        <v>0</v>
+      </c>
+      <c r="J86" s="3">
+        <v>4</v>
+      </c>
+      <c r="K86" s="3">
+        <v>0</v>
+      </c>
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="3:13">
+      <c r="C87" s="3">
+        <v>8205</v>
+      </c>
+      <c r="D87" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="E87" s="3">
+        <v>16</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G87" s="3">
+        <v>1</v>
+      </c>
+      <c r="H87" s="3">
+        <v>1</v>
+      </c>
+      <c r="I87" s="3">
+        <v>0</v>
+      </c>
+      <c r="J87" s="3">
+        <v>5</v>
+      </c>
+      <c r="K87" s="3">
+        <v>0</v>
+      </c>
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" customHeight="1" spans="3:13">
+      <c r="C88" s="3">
+        <v>8206</v>
+      </c>
+      <c r="D88" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="E88" s="3">
+        <v>16</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="G88" s="3">
+        <v>1</v>
+      </c>
+      <c r="H88" s="3">
+        <v>1</v>
+      </c>
+      <c r="I88" s="3">
+        <v>0</v>
+      </c>
+      <c r="J88" s="3">
+        <v>6</v>
+      </c>
+      <c r="K88" s="3">
+        <v>0</v>
+      </c>
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" spans="3:13">
+      <c r="C89" s="3">
+        <v>8207</v>
+      </c>
+      <c r="D89" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="E89" s="3">
+        <v>16</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="G89" s="3">
+        <v>1</v>
+      </c>
+      <c r="H89" s="3">
+        <v>1</v>
+      </c>
+      <c r="I89" s="3">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3">
         <v>7</v>
       </c>
-      <c r="K85" s="3">
-        <v>0</v>
-      </c>
-      <c r="L85" s="3">
-        <v>0</v>
-      </c>
-      <c r="M85" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" customHeight="1" spans="4:4">
-      <c r="D87" s="11"/>
-    </row>
-    <row r="88" customHeight="1" spans="4:4">
-      <c r="D88" s="11"/>
-    </row>
-    <row r="89" customHeight="1" spans="4:4">
-      <c r="D89" s="11"/>
-    </row>
-    <row r="90" customHeight="1" spans="4:4">
-      <c r="D90" s="11"/>
+      <c r="K89" s="3">
+        <v>0</v>
+      </c>
+      <c r="L89" s="3">
+        <v>0</v>
+      </c>
+      <c r="M89" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="91" customHeight="1" spans="4:4">
       <c r="D91" s="11"/>
@@ -7450,6 +7564,9 @@
     <row r="93" customHeight="1" spans="4:4">
       <c r="D93" s="11"/>
     </row>
+    <row r="94" customHeight="1" spans="4:4">
+      <c r="D94" s="11"/>
+    </row>
     <row r="95" customHeight="1" spans="4:4">
       <c r="D95" s="11"/>
     </row>
@@ -7459,9 +7576,6 @@
     <row r="97" customHeight="1" spans="4:4">
       <c r="D97" s="11"/>
     </row>
-    <row r="98" customHeight="1" spans="4:4">
-      <c r="D98" s="11"/>
-    </row>
     <row r="99" customHeight="1" spans="4:4">
       <c r="D99" s="11"/>
     </row>
@@ -7470,6 +7584,18 @@
     </row>
     <row r="101" customHeight="1" spans="4:4">
       <c r="D101" s="11"/>
+    </row>
+    <row r="102" customHeight="1" spans="4:4">
+      <c r="D102" s="11"/>
+    </row>
+    <row r="103" customHeight="1" spans="4:4">
+      <c r="D103" s="11"/>
+    </row>
+    <row r="104" customHeight="1" spans="4:4">
+      <c r="D104" s="11"/>
+    </row>
+    <row r="105" customHeight="1" spans="4:4">
+      <c r="D105" s="11"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -7615,13 +7741,13 @@
         <v>1999001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E6" s="2">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -7643,13 +7769,13 @@
         <v>1999002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="E7" s="2">
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -7671,13 +7797,13 @@
         <v>1999003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="E8" s="2">
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -7699,13 +7825,13 @@
         <v>1999004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="E9" s="2">
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -7727,13 +7853,13 @@
         <v>1999005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="E10" s="2">
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -7755,13 +7881,13 @@
         <v>1999006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="E11" s="2">
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -7788,13 +7914,13 @@
         <v>1999989</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="E13" s="2">
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -7816,13 +7942,13 @@
         <v>1999990</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="E14" s="2">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -7844,13 +7970,13 @@
         <v>1999991</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="E15" s="2">
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -7872,13 +7998,13 @@
         <v>1999992</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="E16" s="2">
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -7900,13 +8026,13 @@
         <v>1999993</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E17" s="2">
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -7928,13 +8054,13 @@
         <v>1999994</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="E18" s="2">
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -7956,13 +8082,13 @@
         <v>1999995</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="E19" s="2">
         <v>11</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -7984,13 +8110,13 @@
         <v>1999996</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="E20" s="2">
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -8012,13 +8138,13 @@
         <v>1999997</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="E21" s="2">
         <v>11</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -8040,13 +8166,13 @@
         <v>2000000</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="E22" s="2">
         <v>11</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -8068,13 +8194,13 @@
         <v>2000001</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="E23" s="2">
         <v>11</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -8096,13 +8222,13 @@
         <v>2000002</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="E24" s="2">
         <v>11</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -8124,13 +8250,13 @@
         <v>2000003</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="E25" s="2">
         <v>11</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -8152,13 +8278,13 @@
         <v>2000004</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="E26" s="2">
         <v>11</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -8180,13 +8306,13 @@
         <v>2000005</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="E27" s="2">
         <v>11</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -8208,13 +8334,13 @@
         <v>2000006</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="E28" s="2">
         <v>11</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -8236,13 +8362,13 @@
         <v>2000007</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E29" s="2">
         <v>11</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -8264,13 +8390,13 @@
         <v>2000008</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="E30" s="2">
         <v>11</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -8292,13 +8418,13 @@
         <v>2000009</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="E31" s="2">
         <v>11</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -8320,13 +8446,13 @@
         <v>2000010</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="E32" s="2">
         <v>11</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -8348,13 +8474,13 @@
         <v>2000011</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="E33" s="2">
         <v>11</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -8376,13 +8502,13 @@
         <v>2000012</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="E34" s="2">
         <v>11</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -8404,13 +8530,13 @@
         <v>2000013</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="E35" s="2">
         <v>11</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -8444,13 +8570,13 @@
         <v>2000100</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="E39" s="2">
         <v>11</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -8472,13 +8598,13 @@
         <v>2000101</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="E40" s="2">
         <v>11</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -8500,13 +8626,13 @@
         <v>2000102</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="E41" s="2">
         <v>11</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -8528,13 +8654,13 @@
         <v>2000103</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="E42" s="2">
         <v>11</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -8556,13 +8682,13 @@
         <v>2000104</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="E43" s="2">
         <v>11</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -8584,13 +8710,13 @@
         <v>2000105</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="E44" s="2">
         <v>11</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -8612,13 +8738,13 @@
         <v>2000106</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="E45" s="2">
         <v>11</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G45" s="2">
         <v>1</v>
@@ -8640,13 +8766,13 @@
         <v>2000107</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="E46" s="2">
         <v>11</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -8668,13 +8794,13 @@
         <v>2000108</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="E47" s="2">
         <v>11</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -8696,13 +8822,13 @@
         <v>2000109</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="E48" s="2">
         <v>11</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -8724,13 +8850,13 @@
         <v>2000110</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="E49" s="2">
         <v>11</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -8752,13 +8878,13 @@
         <v>2000111</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="E50" s="2">
         <v>11</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -8780,13 +8906,13 @@
         <v>2000112</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="E51" s="2">
         <v>11</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -8808,13 +8934,13 @@
         <v>2000113</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="E52" s="2">
         <v>11</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -8836,13 +8962,13 @@
         <v>2000114</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="E53" s="2">
         <v>11</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G53" s="2">
         <v>1</v>
@@ -8864,13 +8990,13 @@
         <v>2000115</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="E54" s="2">
         <v>11</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G54" s="2">
         <v>1</v>
@@ -8892,13 +9018,13 @@
         <v>2000116</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="E55" s="2">
         <v>11</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G55" s="2">
         <v>1</v>
@@ -8920,13 +9046,13 @@
         <v>2000117</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="E56" s="2">
         <v>11</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G56" s="2">
         <v>1</v>
@@ -8948,13 +9074,13 @@
         <v>2000118</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="E57" s="2">
         <v>11</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G57" s="2">
         <v>1</v>
@@ -8976,13 +9102,13 @@
         <v>2000119</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="E58" s="2">
         <v>11</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G58" s="2">
         <v>1</v>
@@ -9004,13 +9130,13 @@
         <v>2000120</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="E59" s="2">
         <v>11</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G59" s="2">
         <v>1</v>
@@ -9032,13 +9158,13 @@
         <v>2000121</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="E60" s="2">
         <v>11</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G60" s="2">
         <v>1</v>
@@ -9060,13 +9186,13 @@
         <v>2000122</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="E61" s="2">
         <v>11</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G61" s="2">
         <v>1</v>
@@ -9088,13 +9214,13 @@
         <v>2000123</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="E62" s="2">
         <v>11</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G62" s="2">
         <v>1</v>
@@ -9116,13 +9242,13 @@
         <v>2000124</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="E63" s="2">
         <v>11</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G63" s="2">
         <v>1</v>
@@ -9144,13 +9270,13 @@
         <v>2000125</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="E64" s="2">
         <v>11</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G64" s="2">
         <v>1</v>
@@ -9172,13 +9298,13 @@
         <v>2000126</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="E65" s="2">
         <v>11</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G65" s="2">
         <v>1</v>
@@ -9200,13 +9326,13 @@
         <v>2000127</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="E66" s="2">
         <v>11</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G66" s="2">
         <v>1</v>
@@ -9228,13 +9354,13 @@
         <v>2000128</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="E67" s="2">
         <v>11</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G67" s="2">
         <v>1</v>
@@ -9256,13 +9382,13 @@
         <v>2000129</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="E68" s="2">
         <v>11</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G68" s="2">
         <v>1</v>
@@ -9284,13 +9410,13 @@
         <v>2000200</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="E70" s="2">
         <v>11</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G70" s="2">
         <v>1</v>
@@ -9310,13 +9436,13 @@
         <v>2000201</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="E71" s="2">
         <v>11</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G71" s="2">
         <v>1</v>
@@ -9336,13 +9462,13 @@
         <v>2000202</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="E72" s="2">
         <v>11</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G72" s="2">
         <v>1</v>
@@ -9362,13 +9488,13 @@
         <v>2000203</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="E73" s="2">
         <v>11</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G73" s="2">
         <v>1</v>
@@ -9388,13 +9514,13 @@
         <v>2000204</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="E74" s="2">
         <v>11</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G74" s="2">
         <v>1</v>
@@ -9414,13 +9540,13 @@
         <v>2000205</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="E75" s="2">
         <v>11</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G75" s="2">
         <v>1</v>
@@ -9440,13 +9566,13 @@
         <v>2000206</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="E76" s="2">
         <v>11</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G76" s="2">
         <v>1</v>
@@ -9466,13 +9592,13 @@
         <v>2000207</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="E77" s="2">
         <v>11</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G77" s="2">
         <v>1</v>
@@ -9492,13 +9618,13 @@
         <v>2000208</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="E78" s="2">
         <v>11</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G78" s="2">
         <v>1</v>
@@ -9518,13 +9644,13 @@
         <v>2000209</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="E79" s="2">
         <v>11</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G79" s="2">
         <v>1</v>
@@ -9544,13 +9670,13 @@
         <v>2000210</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="E80" s="2">
         <v>11</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G80" s="2">
         <v>1</v>
@@ -9570,13 +9696,13 @@
         <v>2000211</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="E81" s="2">
         <v>11</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G81" s="2">
         <v>1</v>
@@ -9596,13 +9722,13 @@
         <v>2000212</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="E82" s="2">
         <v>11</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G82" s="2">
         <v>1</v>
@@ -9622,13 +9748,13 @@
         <v>2000213</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="E83" s="2">
         <v>11</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G83" s="2">
         <v>1</v>
@@ -9648,13 +9774,13 @@
         <v>2000214</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="E84" s="2">
         <v>11</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G84" s="2">
         <v>1</v>
@@ -9674,13 +9800,13 @@
         <v>2000215</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="E85" s="2">
         <v>11</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G85" s="2">
         <v>1</v>
@@ -9700,13 +9826,13 @@
         <v>2000216</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="E86" s="2">
         <v>11</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G86" s="2">
         <v>1</v>
@@ -9726,13 +9852,13 @@
         <v>2000217</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="E87" s="2">
         <v>11</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G87" s="2">
         <v>1</v>
@@ -9752,13 +9878,13 @@
         <v>2000218</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="E88" s="2">
         <v>11</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G88" s="2">
         <v>1</v>
@@ -9778,13 +9904,13 @@
         <v>2000219</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="E89" s="2">
         <v>11</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G89" s="2">
         <v>1</v>
@@ -9804,13 +9930,13 @@
         <v>2000220</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="E90" s="2">
         <v>11</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G90" s="2">
         <v>1</v>
@@ -9830,13 +9956,13 @@
         <v>2000221</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E91" s="2">
         <v>11</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G91" s="2">
         <v>1</v>
@@ -9856,13 +9982,13 @@
         <v>2000222</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E92" s="2">
         <v>11</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G92" s="2">
         <v>1</v>
@@ -9882,13 +10008,13 @@
         <v>2000223</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E93" s="2">
         <v>11</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G93" s="2">
         <v>1</v>
@@ -9908,13 +10034,13 @@
         <v>2000224</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E94" s="2">
         <v>11</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G94" s="2">
         <v>1</v>
@@ -9934,13 +10060,13 @@
         <v>2000225</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E95" s="2">
         <v>11</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G95" s="2">
         <v>1</v>
@@ -9960,13 +10086,13 @@
         <v>2000226</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="E96" s="2">
         <v>11</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G96" s="2">
         <v>1</v>
@@ -9986,13 +10112,13 @@
         <v>2000227</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="E97" s="2">
         <v>11</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G97" s="2">
         <v>1</v>
@@ -10012,13 +10138,13 @@
         <v>2000228</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="E98" s="2">
         <v>11</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G98" s="2">
         <v>1</v>
@@ -10038,13 +10164,13 @@
         <v>2000229</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="E99" s="2">
         <v>11</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G99" s="2">
         <v>1</v>
@@ -10064,13 +10190,13 @@
         <v>2000300</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="E102" s="2">
         <v>11</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G102" s="2">
         <v>1</v>
@@ -10090,13 +10216,13 @@
         <v>2000301</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="E103" s="2">
         <v>11</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G103" s="2">
         <v>1</v>
@@ -10116,13 +10242,13 @@
         <v>2000302</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="E104" s="2">
         <v>11</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G104" s="2">
         <v>1</v>
@@ -10142,13 +10268,13 @@
         <v>2000303</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="E105" s="2">
         <v>11</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G105" s="2">
         <v>1</v>
@@ -10168,13 +10294,13 @@
         <v>2000304</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="E106" s="2">
         <v>11</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G106" s="2">
         <v>1</v>
@@ -10194,13 +10320,13 @@
         <v>2000305</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="E107" s="2">
         <v>11</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G107" s="2">
         <v>1</v>
@@ -10220,13 +10346,13 @@
         <v>2000306</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="E108" s="2">
         <v>11</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G108" s="2">
         <v>1</v>
@@ -10246,13 +10372,13 @@
         <v>2000307</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="E109" s="2">
         <v>11</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G109" s="2">
         <v>1</v>
@@ -10272,13 +10398,13 @@
         <v>2000308</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="E110" s="2">
         <v>11</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G110" s="2">
         <v>1</v>
@@ -10298,13 +10424,13 @@
         <v>2000309</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="E111" s="2">
         <v>11</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G111" s="2">
         <v>1</v>
@@ -10324,13 +10450,13 @@
         <v>2000310</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="E112" s="2">
         <v>11</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G112" s="2">
         <v>1</v>
@@ -10350,13 +10476,13 @@
         <v>2000311</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="E113" s="2">
         <v>11</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G113" s="2">
         <v>1</v>
@@ -10376,13 +10502,13 @@
         <v>2000312</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="E114" s="2">
         <v>11</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G114" s="2">
         <v>1</v>
@@ -10402,13 +10528,13 @@
         <v>2000313</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="E115" s="2">
         <v>11</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G115" s="2">
         <v>1</v>
@@ -10428,13 +10554,13 @@
         <v>2000314</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="E116" s="2">
         <v>11</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G116" s="2">
         <v>1</v>
@@ -10454,13 +10580,13 @@
         <v>2000315</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="E117" s="2">
         <v>11</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G117" s="2">
         <v>1</v>
@@ -10480,13 +10606,13 @@
         <v>2000316</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="E118" s="2">
         <v>11</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G118" s="2">
         <v>1</v>
@@ -10506,13 +10632,13 @@
         <v>2000317</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="E119" s="2">
         <v>11</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G119" s="2">
         <v>1</v>
@@ -10532,13 +10658,13 @@
         <v>2000318</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="E120" s="2">
         <v>11</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G120" s="2">
         <v>1</v>
@@ -10558,13 +10684,13 @@
         <v>2000319</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="E121" s="2">
         <v>11</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G121" s="2">
         <v>1</v>
@@ -10584,13 +10710,13 @@
         <v>2000320</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="E122" s="2">
         <v>11</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G122" s="2">
         <v>1</v>
@@ -10610,13 +10736,13 @@
         <v>2000321</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="E123" s="2">
         <v>11</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G123" s="2">
         <v>1</v>
@@ -10636,13 +10762,13 @@
         <v>2000322</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="E124" s="2">
         <v>11</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G124" s="2">
         <v>1</v>
@@ -10662,13 +10788,13 @@
         <v>2000323</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="E125" s="2">
         <v>11</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G125" s="2">
         <v>1</v>
@@ -10688,13 +10814,13 @@
         <v>2000324</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="E126" s="2">
         <v>11</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G126" s="2">
         <v>1</v>
@@ -10714,13 +10840,13 @@
         <v>2000325</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="E127" s="2">
         <v>11</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G127" s="2">
         <v>1</v>
@@ -10740,13 +10866,13 @@
         <v>2000326</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="E128" s="2">
         <v>11</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G128" s="2">
         <v>1</v>
@@ -10766,13 +10892,13 @@
         <v>2000327</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="E129" s="2">
         <v>11</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G129" s="2">
         <v>1</v>
@@ -10792,13 +10918,13 @@
         <v>2000328</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="E130" s="2">
         <v>11</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G130" s="2">
         <v>1</v>
@@ -10818,13 +10944,13 @@
         <v>2000329</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="E131" s="2">
         <v>11</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G131" s="2">
         <v>1</v>
@@ -10983,13 +11109,13 @@
         <v>3000001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="E6" s="2">
         <v>13</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -11011,13 +11137,13 @@
         <v>3000002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="E7" s="2">
         <v>13</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -11039,13 +11165,13 @@
         <v>3000003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="E8" s="2">
         <v>13</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -11067,13 +11193,13 @@
         <v>3000004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="E9" s="2">
         <v>13</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -11095,13 +11221,13 @@
         <v>3000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="E10" s="2">
         <v>13</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -11123,13 +11249,13 @@
         <v>3000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="E11" s="2">
         <v>13</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -11151,13 +11277,13 @@
         <v>3000007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="E12" s="2">
         <v>13</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -11179,13 +11305,13 @@
         <v>3000008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="E13" s="2">
         <v>13</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -11207,13 +11333,13 @@
         <v>3000009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="E14" s="2">
         <v>13</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -11235,13 +11361,13 @@
         <v>3000010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="E15" s="2">
         <v>13</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -11263,13 +11389,13 @@
         <v>3000011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="E16" s="2">
         <v>13</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -11291,13 +11417,13 @@
         <v>3000012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="E17" s="2">
         <v>13</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -11319,13 +11445,13 @@
         <v>3000013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="E18" s="2">
         <v>13</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -11347,13 +11473,13 @@
         <v>3000014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="E19" s="2">
         <v>13</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -11375,13 +11501,13 @@
         <v>3000015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="E20" s="2">
         <v>13</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -11403,13 +11529,13 @@
         <v>3000016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="E21" s="2">
         <v>13</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -11431,13 +11557,13 @@
         <v>3000017</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="E22" s="2">
         <v>13</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -11459,13 +11585,13 @@
         <v>3000018</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="E23" s="2">
         <v>13</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -11487,13 +11613,13 @@
         <v>3000019</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="E24" s="2">
         <v>13</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -11515,13 +11641,13 @@
         <v>3000020</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="E25" s="2">
         <v>13</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -11543,13 +11669,13 @@
         <v>3000021</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="E26" s="2">
         <v>13</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -11571,13 +11697,13 @@
         <v>3000022</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="E27" s="2">
         <v>13</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -11599,13 +11725,13 @@
         <v>3000023</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="E28" s="2">
         <v>13</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -11627,13 +11753,13 @@
         <v>3000024</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="E29" s="2">
         <v>13</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -11655,13 +11781,13 @@
         <v>3000025</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="E30" s="2">
         <v>13</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -11683,13 +11809,13 @@
         <v>3000026</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="E31" s="2">
         <v>13</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -11711,13 +11837,13 @@
         <v>3000027</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="E32" s="2">
         <v>13</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -11739,13 +11865,13 @@
         <v>3000028</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="E33" s="2">
         <v>13</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -11767,13 +11893,13 @@
         <v>3000029</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="E34" s="2">
         <v>13</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -11795,13 +11921,13 @@
         <v>3000030</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="E35" s="2">
         <v>13</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -11823,13 +11949,13 @@
         <v>3000031</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="E36" s="2">
         <v>13</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -11851,13 +11977,13 @@
         <v>3000032</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="E37" s="2">
         <v>13</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G37" s="2">
         <v>1</v>
@@ -11879,13 +12005,13 @@
         <v>3000033</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="E38" s="2">
         <v>13</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G38" s="2">
         <v>1</v>
@@ -11907,13 +12033,13 @@
         <v>3000034</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="E39" s="2">
         <v>13</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -11935,13 +12061,13 @@
         <v>3000035</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="E40" s="2">
         <v>13</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -11963,13 +12089,13 @@
         <v>3000036</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="E41" s="2">
         <v>13</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -11991,13 +12117,13 @@
         <v>3000037</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="E42" s="2">
         <v>13</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -12019,13 +12145,13 @@
         <v>3000038</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="E43" s="2">
         <v>13</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -12047,13 +12173,13 @@
         <v>3000039</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="E44" s="2">
         <v>13</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -12075,13 +12201,13 @@
         <v>3000040</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="E45" s="2">
         <v>13</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G45" s="2">
         <v>1</v>
@@ -12103,13 +12229,13 @@
         <v>3000041</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="E46" s="2">
         <v>13</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -12131,13 +12257,13 @@
         <v>3000042</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="E47" s="2">
         <v>13</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -12159,13 +12285,13 @@
         <v>3000043</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="E48" s="2">
         <v>13</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -12187,13 +12313,13 @@
         <v>3000044</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="E49" s="2">
         <v>13</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -12215,13 +12341,13 @@
         <v>3000045</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="E50" s="2">
         <v>13</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -12243,13 +12369,13 @@
         <v>3000046</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="E51" s="2">
         <v>13</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -12271,13 +12397,13 @@
         <v>3000047</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="E52" s="2">
         <v>13</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -12299,13 +12425,13 @@
         <v>3000048</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="E53" s="2">
         <v>13</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G53" s="2">
         <v>1</v>
@@ -12464,13 +12590,13 @@
         <v>40000051</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="E7" s="2">
         <v>14</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -12496,13 +12622,13 @@
         <v>40000052</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="E8" s="2">
         <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -12528,13 +12654,13 @@
         <v>40000053</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="E9" s="2">
         <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -12560,13 +12686,13 @@
         <v>40000054</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="E10" s="2">
         <v>14</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -12592,13 +12718,13 @@
         <v>40000055</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="E11" s="2">
         <v>14</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -12624,13 +12750,13 @@
         <v>40000056</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="E12" s="2">
         <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -12656,13 +12782,13 @@
         <v>40000057</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="E13" s="2">
         <v>14</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -12688,13 +12814,13 @@
         <v>40000058</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="E14" s="2">
         <v>14</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -12720,13 +12846,13 @@
         <v>40000059</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="E15" s="2">
         <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -12752,13 +12878,13 @@
         <v>40000060</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="E16" s="2">
         <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -12784,13 +12910,13 @@
         <v>40000061</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="E17" s="2">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -12816,13 +12942,13 @@
         <v>40000062</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="E18" s="2">
         <v>14</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -12848,13 +12974,13 @@
         <v>40000063</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="E19" s="2">
         <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -12880,13 +13006,13 @@
         <v>40000064</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="E20" s="2">
         <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -12912,13 +13038,13 @@
         <v>40000065</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="E21" s="2">
         <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -12944,13 +13070,13 @@
         <v>40000066</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="E22" s="2">
         <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -12976,13 +13102,13 @@
         <v>40000067</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="E23" s="2">
         <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -13008,13 +13134,13 @@
         <v>40000068</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="E24" s="2">
         <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -13040,13 +13166,13 @@
         <v>40000069</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="E25" s="2">
         <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -13072,13 +13198,13 @@
         <v>40000070</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="E26" s="2">
         <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -13104,13 +13230,13 @@
         <v>40000071</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="E27" s="2">
         <v>14</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -13136,13 +13262,13 @@
         <v>40000072</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="E28" s="2">
         <v>14</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -13168,13 +13294,13 @@
         <v>40000073</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="E29" s="2">
         <v>14</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -13200,13 +13326,13 @@
         <v>40000074</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="E30" s="2">
         <v>14</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -13232,13 +13358,13 @@
         <v>40000075</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="E31" s="2">
         <v>14</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -13264,13 +13390,13 @@
         <v>40000076</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="E32" s="2">
         <v>14</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -13296,13 +13422,13 @@
         <v>40000077</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="E33" s="2">
         <v>14</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -13328,13 +13454,13 @@
         <v>40000078</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="E34" s="2">
         <v>14</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -13360,13 +13486,13 @@
         <v>40000079</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="E35" s="2">
         <v>14</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -13392,13 +13518,13 @@
         <v>40000080</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="E36" s="2">
         <v>14</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -13424,13 +13550,13 @@
         <v>40000081</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="E37" s="2">
         <v>14</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G37" s="2">
         <v>1</v>
@@ -13456,13 +13582,13 @@
         <v>40000082</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="E38" s="2">
         <v>14</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G38" s="2">
         <v>1</v>
@@ -13488,13 +13614,13 @@
         <v>40000083</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="E39" s="2">
         <v>14</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -13520,13 +13646,13 @@
         <v>40000084</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="E40" s="2">
         <v>14</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -13552,13 +13678,13 @@
         <v>40000085</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="E41" s="2">
         <v>14</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -13584,13 +13710,13 @@
         <v>40000086</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="E42" s="2">
         <v>14</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -13616,13 +13742,13 @@
         <v>40000087</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="E43" s="2">
         <v>14</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -13648,13 +13774,13 @@
         <v>40000088</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="E44" s="2">
         <v>14</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -13680,13 +13806,13 @@
         <v>40000089</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="E45" s="2">
         <v>14</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G45" s="2">
         <v>1</v>
@@ -13712,13 +13838,13 @@
         <v>40000090</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="E46" s="2">
         <v>14</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -13744,13 +13870,13 @@
         <v>40000091</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="E47" s="2">
         <v>14</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -13776,13 +13902,13 @@
         <v>40000092</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="E48" s="2">
         <v>14</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -13808,13 +13934,13 @@
         <v>40000093</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="E49" s="2">
         <v>14</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -13840,13 +13966,13 @@
         <v>40000094</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="E50" s="2">
         <v>14</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -13872,13 +13998,13 @@
         <v>40000095</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="E51" s="2">
         <v>14</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -13904,13 +14030,13 @@
         <v>40000096</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="E52" s="2">
         <v>14</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -13936,13 +14062,13 @@
         <v>40000097</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="E53" s="2">
         <v>14</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G53" s="2">
         <v>1</v>
@@ -13968,13 +14094,13 @@
         <v>40000098</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="E54" s="2">
         <v>14</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G54" s="2">
         <v>1</v>
@@ -14000,13 +14126,13 @@
         <v>40000099</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="E55" s="2">
         <v>14</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G55" s="2">
         <v>1</v>
@@ -14032,13 +14158,13 @@
         <v>40000100</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="E56" s="2">
         <v>14</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G56" s="2">
         <v>1</v>
@@ -14064,13 +14190,13 @@
         <v>40000101</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="E57" s="2">
         <v>14</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G57" s="2">
         <v>1</v>
@@ -14096,13 +14222,13 @@
         <v>40000102</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="E58" s="2">
         <v>14</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G58" s="2">
         <v>1</v>
@@ -14128,13 +14254,13 @@
         <v>40000103</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="E59" s="2">
         <v>14</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G59" s="2">
         <v>1</v>
@@ -14160,13 +14286,13 @@
         <v>40000104</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="E60" s="2">
         <v>14</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G60" s="2">
         <v>1</v>
@@ -14192,13 +14318,13 @@
         <v>40000105</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="E61" s="7">
         <v>14</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G61" s="7">
         <v>1</v>
@@ -14225,13 +14351,13 @@
         <v>40000106</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="E62" s="2">
         <v>14</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G62" s="2">
         <v>1</v>
@@ -14258,13 +14384,13 @@
         <v>40000107</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="E63" s="2">
         <v>14</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G63" s="2">
         <v>1</v>
@@ -14291,13 +14417,13 @@
         <v>40000108</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="E64" s="2">
         <v>14</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G64" s="2">
         <v>1</v>
@@ -14324,13 +14450,13 @@
         <v>40000109</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="E65" s="2">
         <v>14</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G65" s="2">
         <v>1</v>
@@ -14357,13 +14483,13 @@
         <v>40000110</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="E66" s="2">
         <v>14</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G66" s="2">
         <v>1</v>
@@ -14390,13 +14516,13 @@
         <v>40000111</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="E67" s="2">
         <v>14</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G67" s="2">
         <v>1</v>
@@ -14423,13 +14549,13 @@
         <v>40000112</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="E68" s="2">
         <v>14</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G68" s="2">
         <v>1</v>
@@ -14456,13 +14582,13 @@
         <v>40000113</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="E69" s="2">
         <v>14</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G69" s="2">
         <v>1</v>
@@ -14489,13 +14615,13 @@
         <v>40000114</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="E70" s="2">
         <v>14</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G70" s="2">
         <v>1</v>
@@ -14522,13 +14648,13 @@
         <v>40000115</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="E71" s="2">
         <v>14</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G71" s="2">
         <v>1</v>
@@ -14555,13 +14681,13 @@
         <v>40000116</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="E72" s="2">
         <v>14</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G72" s="2">
         <v>1</v>
@@ -14588,13 +14714,13 @@
         <v>40000117</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="E73" s="2">
         <v>14</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G73" s="2">
         <v>1</v>
@@ -14621,13 +14747,13 @@
         <v>40000118</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="E74" s="2">
         <v>14</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G74" s="2">
         <v>1</v>
@@ -14654,13 +14780,13 @@
         <v>40000119</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="E75" s="2">
         <v>14</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G75" s="2">
         <v>1</v>
@@ -14687,13 +14813,13 @@
         <v>40000120</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="E76" s="2">
         <v>14</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G76" s="2">
         <v>1</v>
@@ -14720,13 +14846,13 @@
         <v>40000121</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="E77" s="2">
         <v>14</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G77" s="2">
         <v>1</v>
@@ -14753,13 +14879,13 @@
         <v>40000122</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="E78" s="2">
         <v>14</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G78" s="2">
         <v>1</v>
@@ -14786,13 +14912,13 @@
         <v>40000123</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="E79" s="2">
         <v>14</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G79" s="2">
         <v>1</v>
@@ -14819,13 +14945,13 @@
         <v>40000124</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="E80" s="2">
         <v>14</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G80" s="2">
         <v>1</v>
@@ -14852,13 +14978,13 @@
         <v>40000125</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="E81" s="2">
         <v>14</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G81" s="2">
         <v>1</v>
@@ -14884,13 +15010,13 @@
         <v>40000126</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="E82" s="2">
         <v>14</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G82" s="2">
         <v>1</v>
@@ -14916,13 +15042,13 @@
         <v>40000127</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="E83" s="2">
         <v>14</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G83" s="2">
         <v>1</v>
@@ -14948,13 +15074,13 @@
         <v>40000128</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="E84" s="2">
         <v>14</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G84" s="2">
         <v>1</v>
@@ -14980,13 +15106,13 @@
         <v>40000129</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="E85" s="2">
         <v>14</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G85" s="2">
         <v>1</v>
@@ -15012,13 +15138,13 @@
         <v>40000130</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="E86" s="2">
         <v>14</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G86" s="2">
         <v>1</v>
@@ -15044,13 +15170,13 @@
         <v>40000131</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="E87" s="2">
         <v>14</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G87" s="2">
         <v>1</v>
@@ -15076,13 +15202,13 @@
         <v>40000132</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="E88" s="2">
         <v>14</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G88" s="2">
         <v>1</v>
@@ -15108,13 +15234,13 @@
         <v>40000133</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="E89" s="2">
         <v>14</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G89" s="2">
         <v>1</v>
@@ -15140,13 +15266,13 @@
         <v>40000134</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="E90" s="2">
         <v>14</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G90" s="2">
         <v>1</v>
@@ -15172,13 +15298,13 @@
         <v>40000135</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="E91" s="2">
         <v>14</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G91" s="2">
         <v>1</v>
@@ -15204,13 +15330,13 @@
         <v>40000136</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="E92" s="2">
         <v>14</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G92" s="2">
         <v>1</v>
@@ -15236,13 +15362,13 @@
         <v>40000137</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="E93" s="2">
         <v>14</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G93" s="2">
         <v>1</v>
@@ -15268,13 +15394,13 @@
         <v>40000138</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="E94" s="2">
         <v>14</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G94" s="2">
         <v>1</v>
@@ -15300,13 +15426,13 @@
         <v>40000139</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="E95" s="2">
         <v>14</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G95" s="2">
         <v>1</v>
@@ -15471,13 +15597,13 @@
         <v>50000001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="E6" s="2">
         <v>5</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -15503,13 +15629,13 @@
         <v>50000002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="E7" s="2">
         <v>5</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -15535,13 +15661,13 @@
         <v>50000003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="E8" s="2">
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -15567,13 +15693,13 @@
         <v>50000004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="E9" s="2">
         <v>5</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -15599,13 +15725,13 @@
         <v>50000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="E10" s="2">
         <v>5</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -15631,13 +15757,13 @@
         <v>50000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="E11" s="2">
         <v>5</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -15663,13 +15789,13 @@
         <v>50000007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="E12" s="2">
         <v>5</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -15695,13 +15821,13 @@
         <v>50000008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="E13" s="2">
         <v>5</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -15727,13 +15853,13 @@
         <v>50000009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="E14" s="2">
         <v>5</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -15759,13 +15885,13 @@
         <v>50000010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="E15" s="2">
         <v>5</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -15791,13 +15917,13 @@
         <v>50000011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="E16" s="2">
         <v>5</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -15823,13 +15949,13 @@
         <v>50000012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="E17" s="2">
         <v>5</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -15855,13 +15981,13 @@
         <v>50000013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="E18" s="2">
         <v>5</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -15887,13 +16013,13 @@
         <v>50000014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="E19" s="2">
         <v>5</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -15919,13 +16045,13 @@
         <v>50000015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="E20" s="2">
         <v>5</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -15951,13 +16077,13 @@
         <v>50000016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="E21" s="2">
         <v>5</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -15983,13 +16109,13 @@
         <v>50000017</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="E22" s="2">
         <v>5</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -16015,13 +16141,13 @@
         <v>50000018</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="E23" s="2">
         <v>5</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -16047,13 +16173,13 @@
         <v>50000019</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="E24" s="2">
         <v>5</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -16079,13 +16205,13 @@
         <v>50000020</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="E25" s="2">
         <v>5</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -16111,13 +16237,13 @@
         <v>50000021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="E26" s="2">
         <v>5</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -16143,13 +16269,13 @@
         <v>50000022</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="E27" s="2">
         <v>5</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -16175,13 +16301,13 @@
         <v>50000023</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="E28" s="2">
         <v>5</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -16207,13 +16333,13 @@
         <v>50000024</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="E29" s="2">
         <v>5</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -16239,13 +16365,13 @@
         <v>50000025</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="E30" s="2">
         <v>5</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -16271,13 +16397,13 @@
         <v>50000026</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="E31" s="2">
         <v>5</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -16303,13 +16429,13 @@
         <v>50000027</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="E32" s="2">
         <v>5</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -16335,13 +16461,13 @@
         <v>50000028</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="E33" s="2">
         <v>5</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -16367,13 +16493,13 @@
         <v>50000029</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="E34" s="2">
         <v>5</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -16399,13 +16525,13 @@
         <v>50000030</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="E35" s="2">
         <v>5</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -16431,13 +16557,13 @@
         <v>50000031</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="E36" s="2">
         <v>5</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -16463,13 +16589,13 @@
         <v>50000032</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="E37" s="2">
         <v>5</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="G37" s="2">
         <v>1</v>
@@ -16495,13 +16621,13 @@
         <v>50000033</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="E38" s="2">
         <v>5</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="G38" s="2">
         <v>1</v>
@@ -16527,13 +16653,13 @@
         <v>50000034</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="E39" s="2">
         <v>5</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -16559,13 +16685,13 @@
         <v>50000035</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="E40" s="2">
         <v>5</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -16591,13 +16717,13 @@
         <v>50000036</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="E41" s="2">
         <v>5</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -16623,13 +16749,13 @@
         <v>50000037</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="E42" s="2">
         <v>5</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -16655,13 +16781,13 @@
         <v>50000038</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="E43" s="2">
         <v>5</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -16687,13 +16813,13 @@
         <v>50000039</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="E44" s="2">
         <v>5</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -16719,13 +16845,13 @@
         <v>50000040</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="E45" s="2">
         <v>5</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="G45" s="2">
         <v>1</v>
@@ -16751,13 +16877,13 @@
         <v>50000041</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="E46" s="2">
         <v>5</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -16783,13 +16909,13 @@
         <v>50000042</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="E47" s="2">
         <v>5</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -16815,13 +16941,13 @@
         <v>50000043</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="E48" s="2">
         <v>5</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -16847,13 +16973,13 @@
         <v>50000044</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="E49" s="2">
         <v>5</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -16879,13 +17005,13 @@
         <v>50000045</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="E50" s="2">
         <v>5</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -16911,13 +17037,13 @@
         <v>50000046</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="E51" s="2">
         <v>5</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -16943,13 +17069,13 @@
         <v>50000047</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="E52" s="2">
         <v>5</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -16975,13 +17101,13 @@
         <v>50000048</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="E53" s="2">
         <v>5</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="G53" s="2">
         <v>1</v>
@@ -17007,13 +17133,13 @@
         <v>50000049</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="E54" s="2">
         <v>5</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="G54" s="2">
         <v>1</v>
@@ -17039,13 +17165,13 @@
         <v>50000050</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="E55" s="2">
         <v>5</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="G55" s="2">
         <v>1</v>
@@ -17071,13 +17197,13 @@
         <v>50000051</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="E56" s="2">
         <v>5</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="G56" s="2">
         <v>1</v>
@@ -17103,13 +17229,13 @@
         <v>50000052</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="E57" s="2">
         <v>5</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="G57" s="2">
         <v>1</v>
@@ -17135,13 +17261,13 @@
         <v>50000053</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="E58" s="2">
         <v>5</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="G58" s="2">
         <v>1</v>
@@ -17167,13 +17293,13 @@
         <v>50000054</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="E59" s="2">
         <v>5</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="G59" s="2">
         <v>1</v>
@@ -17199,13 +17325,13 @@
         <v>50000055</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="E60" s="2">
         <v>5</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="G60" s="2">
         <v>1</v>
@@ -17231,13 +17357,13 @@
         <v>50000056</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="E61" s="2">
         <v>5</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="G61" s="2">
         <v>1</v>
@@ -17263,13 +17389,13 @@
         <v>50000057</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="E62" s="2">
         <v>5</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="G62" s="2">
         <v>1</v>
@@ -17295,13 +17421,13 @@
         <v>50000058</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="E63" s="2">
         <v>5</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="G63" s="2">
         <v>1</v>
@@ -17327,13 +17453,13 @@
         <v>50000059</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="E64" s="2">
         <v>5</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="G64" s="2">
         <v>1</v>
@@ -17359,13 +17485,13 @@
         <v>50000060</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="E65" s="2">
         <v>5</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="G65" s="2">
         <v>1</v>
@@ -17391,13 +17517,13 @@
         <v>50000061</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="E66" s="2">
         <v>5</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="G66" s="2">
         <v>1</v>
@@ -17423,13 +17549,13 @@
         <v>50000062</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="E67" s="2">
         <v>5</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="G67" s="2">
         <v>1</v>
@@ -17455,13 +17581,13 @@
         <v>50000063</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="E68" s="2">
         <v>5</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="G68" s="2">
         <v>1</v>
@@ -17487,13 +17613,13 @@
         <v>50000064</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="E69" s="2">
         <v>5</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="G69" s="2">
         <v>1</v>
@@ -17519,13 +17645,13 @@
         <v>50000065</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="E70" s="2">
         <v>5</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="G70" s="2">
         <v>1</v>
@@ -17551,13 +17677,13 @@
         <v>50000066</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="E71" s="2">
         <v>5</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="G71" s="2">
         <v>1</v>
@@ -17583,13 +17709,13 @@
         <v>50000067</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="E72" s="2">
         <v>5</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="G72" s="2">
         <v>1</v>
@@ -17615,13 +17741,13 @@
         <v>50000068</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="E73" s="2">
         <v>5</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="G73" s="2">
         <v>1</v>
@@ -17647,13 +17773,13 @@
         <v>50000069</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="E74" s="2">
         <v>5</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="G74" s="2">
         <v>1</v>
@@ -17679,13 +17805,13 @@
         <v>50000070</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="E75" s="2">
         <v>5</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="G75" s="2">
         <v>1</v>
@@ -17711,13 +17837,13 @@
         <v>50000071</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="E76" s="2">
         <v>5</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="G76" s="2">
         <v>1</v>
@@ -17743,13 +17869,13 @@
         <v>50000072</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="E77" s="2">
         <v>5</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="G77" s="2">
         <v>1</v>
@@ -17775,13 +17901,13 @@
         <v>50000073</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="E78" s="2">
         <v>5</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="G78" s="2">
         <v>1</v>
@@ -17807,13 +17933,13 @@
         <v>50000074</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="E79" s="2">
         <v>5</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="G79" s="2">
         <v>1</v>
@@ -17839,13 +17965,13 @@
         <v>50000075</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="E80" s="2">
         <v>5</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="G80" s="2">
         <v>1</v>
@@ -17871,13 +17997,13 @@
         <v>50000076</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="E81" s="2">
         <v>5</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="G81" s="2">
         <v>1</v>
@@ -17903,13 +18029,13 @@
         <v>50000077</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="E82" s="2">
         <v>5</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="G82" s="2">
         <v>1</v>
@@ -17935,13 +18061,13 @@
         <v>50000078</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="E83" s="2">
         <v>5</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="G83" s="2">
         <v>1</v>
@@ -17967,13 +18093,13 @@
         <v>50000079</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="E84" s="2">
         <v>5</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="G84" s="2">
         <v>1</v>
@@ -17999,13 +18125,13 @@
         <v>50000080</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="E85" s="2">
         <v>5</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="G85" s="2">
         <v>1</v>
@@ -18031,13 +18157,13 @@
         <v>50000081</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="E86" s="2">
         <v>5</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G86" s="2">
         <v>1</v>
@@ -18063,13 +18189,13 @@
         <v>50000082</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="E87" s="2">
         <v>5</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="G87" s="2">
         <v>1</v>
@@ -18095,13 +18221,13 @@
         <v>50000083</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="E88" s="2">
         <v>5</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="G88" s="2">
         <v>1</v>
@@ -18127,13 +18253,13 @@
         <v>50000084</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E89" s="2">
         <v>5</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="G89" s="2">
         <v>1</v>
@@ -18159,13 +18285,13 @@
         <v>50000085</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="E90" s="2">
         <v>5</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="G90" s="2">
         <v>1</v>
@@ -18191,13 +18317,13 @@
         <v>50000086</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="E91" s="2">
         <v>5</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="G91" s="2">
         <v>1</v>
@@ -18223,13 +18349,13 @@
         <v>50000087</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="E92" s="2">
         <v>5</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="G92" s="2">
         <v>1</v>
@@ -18255,13 +18381,13 @@
         <v>50000088</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="E93" s="2">
         <v>5</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="G93" s="2">
         <v>1</v>
@@ -18287,13 +18413,13 @@
         <v>50000089</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="E94" s="2">
         <v>5</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="G94" s="2">
         <v>1</v>
@@ -18319,13 +18445,13 @@
         <v>50000090</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="E95" s="2">
         <v>5</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="G95" s="2">
         <v>1</v>
@@ -18351,13 +18477,13 @@
         <v>50000091</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="E96" s="2">
         <v>5</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="G96" s="2">
         <v>1</v>
@@ -18383,13 +18509,13 @@
         <v>50000092</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="E97" s="2">
         <v>5</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="G97" s="2">
         <v>1</v>
@@ -18415,13 +18541,13 @@
         <v>50000093</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="E98" s="2">
         <v>5</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G98" s="2">
         <v>1</v>
@@ -18447,13 +18573,13 @@
         <v>50000094</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="E99" s="2">
         <v>5</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="G99" s="2">
         <v>1</v>
@@ -18479,13 +18605,13 @@
         <v>50000095</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="E100" s="2">
         <v>5</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="G100" s="2">
         <v>1</v>
@@ -18511,13 +18637,13 @@
         <v>50000096</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="E101" s="2">
         <v>5</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="G101" s="2">
         <v>1</v>
@@ -18543,13 +18669,13 @@
         <v>50000097</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="E102" s="2">
         <v>5</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="G102" s="2">
         <v>1</v>
@@ -18575,13 +18701,13 @@
         <v>50000098</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="E103" s="2">
         <v>5</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="G103" s="2">
         <v>1</v>
@@ -18607,13 +18733,13 @@
         <v>50000099</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="E104" s="2">
         <v>5</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="G104" s="2">
         <v>1</v>
@@ -18639,13 +18765,13 @@
         <v>50000100</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="E105" s="2">
         <v>5</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="G105" s="2">
         <v>1</v>
@@ -18671,13 +18797,13 @@
         <v>50000101</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="E106" s="2">
         <v>5</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="G106" s="2">
         <v>1</v>
@@ -18703,13 +18829,13 @@
         <v>50000102</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="E107" s="2">
         <v>5</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="G107" s="2">
         <v>1</v>
@@ -18735,13 +18861,13 @@
         <v>50000103</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="E108" s="2">
         <v>5</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="G108" s="2">
         <v>1</v>
@@ -18767,13 +18893,13 @@
         <v>50000104</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="E109" s="2">
         <v>5</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="G109" s="2">
         <v>1</v>
@@ -18938,13 +19064,13 @@
         <v>180001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="E6" s="2">
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -18964,13 +19090,13 @@
         <v>180002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="E7" s="2">
         <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -18990,13 +19116,13 @@
         <v>180003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="E8" s="2">
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -19016,13 +19142,13 @@
         <v>180004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="E9" s="2">
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -19042,13 +19168,13 @@
         <v>180005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="E10" s="2">
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -19068,13 +19194,13 @@
         <v>180006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="E11" s="2">
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -19096,13 +19222,13 @@
         <v>180007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="E12" s="2">
         <v>18</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -19124,13 +19250,13 @@
         <v>180008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="E13" s="2">
         <v>18</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -19152,13 +19278,13 @@
         <v>180009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>732</v>
+        <v>738</v>
       </c>
       <c r="E14" s="2">
         <v>18</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -19180,13 +19306,13 @@
         <v>180010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="E15" s="2">
         <v>18</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -19208,13 +19334,13 @@
         <v>180011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="E16" s="2">
         <v>18</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -19236,13 +19362,13 @@
         <v>180012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="E17" s="2">
         <v>18</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -19264,13 +19390,13 @@
         <v>180013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
       <c r="E18" s="2">
         <v>18</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -19292,13 +19418,13 @@
         <v>180014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="E19" s="2">
         <v>18</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -19320,13 +19446,13 @@
         <v>180015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="E20" s="2">
         <v>18</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -19348,13 +19474,13 @@
         <v>180016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="E21" s="2">
         <v>18</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -19376,13 +19502,13 @@
         <v>180017</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="E22" s="2">
         <v>18</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -19404,13 +19530,13 @@
         <v>180018</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="E23" s="2">
         <v>18</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -19432,13 +19558,13 @@
         <v>180019</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
       <c r="E24" s="2">
         <v>18</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -19460,13 +19586,13 @@
         <v>180020</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
       <c r="E25" s="2">
         <v>18</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -19488,13 +19614,13 @@
         <v>180021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="E26" s="2">
         <v>18</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -19521,13 +19647,13 @@
         <v>180030</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="E28" s="2">
         <v>18</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -19549,13 +19675,13 @@
         <v>180031</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="E29" s="2">
         <v>18</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="G29" s="3">
         <v>1</v>
@@ -19575,13 +19701,13 @@
         <v>180032</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
       <c r="E30" s="2">
         <v>18</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="G30" s="3">
         <v>1</v>
@@ -19601,13 +19727,13 @@
         <v>180033</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>748</v>
+        <v>754</v>
       </c>
       <c r="E31" s="2">
         <v>18</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="G31" s="3">
         <v>1</v>
@@ -19627,13 +19753,13 @@
         <v>180034</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>749</v>
+        <v>755</v>
       </c>
       <c r="E32" s="2">
         <v>18</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="G32" s="3">
         <v>1</v>
@@ -19655,13 +19781,13 @@
         <v>180035</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>750</v>
+        <v>756</v>
       </c>
       <c r="E33" s="2">
         <v>18</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="G33" s="3">
         <v>1</v>
@@ -19683,13 +19809,13 @@
         <v>180036</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>751</v>
+        <v>757</v>
       </c>
       <c r="E34" s="2">
         <v>18</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="G34" s="3">
         <v>1</v>
@@ -19850,13 +19976,13 @@
         <v>190001</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>752</v>
+        <v>758</v>
       </c>
       <c r="E6" s="2">
         <v>19</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>753</v>
+        <v>759</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -19876,13 +20002,13 @@
         <v>190002</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>754</v>
+        <v>760</v>
       </c>
       <c r="E7" s="2">
         <v>19</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>753</v>
+        <v>759</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -19902,13 +20028,13 @@
         <v>190003</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>755</v>
+        <v>761</v>
       </c>
       <c r="E8" s="2">
         <v>19</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>753</v>
+        <v>759</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -19928,13 +20054,13 @@
         <v>190004</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>756</v>
+        <v>762</v>
       </c>
       <c r="E9" s="2">
         <v>19</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>753</v>
+        <v>759</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -19954,13 +20080,13 @@
         <v>190005</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>757</v>
+        <v>763</v>
       </c>
       <c r="E10" s="2">
         <v>19</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>753</v>
+        <v>759</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -19980,13 +20106,13 @@
         <v>190006</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>758</v>
+        <v>764</v>
       </c>
       <c r="E11" s="2">
         <v>19</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>753</v>
+        <v>759</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -5833,7 +5833,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -5865,7 +5865,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L30" s="3">
         <v>0</v>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -344,7 +344,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1424" uniqueCount="765">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1428" uniqueCount="767">
   <si>
     <t>_Id</t>
   </si>
@@ -2599,6 +2599,9 @@
     <t>神戒之源</t>
   </si>
   <si>
+    <t>传世契约</t>
+  </si>
+  <si>
     <t>极·卖身契</t>
   </si>
   <si>
@@ -2618,6 +2621,9 @@
   </si>
   <si>
     <t>极.无限之魂</t>
+  </si>
+  <si>
+    <t>极.传世契约</t>
   </si>
   <si>
     <t>定身指环</t>
@@ -18938,7 +18944,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:M34"/>
+  <dimension ref="C1:M36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="4" max="4" width="9.625" customWidth="1"/>
@@ -19637,42 +19643,42 @@
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
     </row>
-    <row r="27" s="2" customFormat="1" customHeight="1" spans="4:13">
-      <c r="D27" s="3"/>
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C27" s="2">
+        <v>180022</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="E27" s="2">
+        <v>18</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="G27" s="2">
+        <v>1</v>
+      </c>
+      <c r="H27" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I27" s="2">
+        <v>0</v>
+      </c>
+      <c r="J27" s="2">
+        <v>6</v>
+      </c>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
     </row>
-    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C28" s="2">
-        <v>180030</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>751</v>
-      </c>
-      <c r="E28" s="2">
-        <v>18</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>730</v>
-      </c>
-      <c r="G28" s="2">
-        <v>1</v>
-      </c>
-      <c r="H28" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I28" s="2">
-        <v>0</v>
-      </c>
-      <c r="J28" s="2">
-        <v>7</v>
-      </c>
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
     </row>
-    <row r="29" s="3" customFormat="1" customHeight="1" spans="3:10">
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C29" s="2">
-        <v>180031</v>
+        <v>180030</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>752</v>
@@ -19683,7 +19689,7 @@
       <c r="F29" s="2" t="s">
         <v>730</v>
       </c>
-      <c r="G29" s="3">
+      <c r="G29" s="2">
         <v>1</v>
       </c>
       <c r="H29" s="2">
@@ -19695,10 +19701,12 @@
       <c r="J29" s="2">
         <v>7</v>
       </c>
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
     </row>
     <row r="30" s="3" customFormat="1" customHeight="1" spans="3:10">
       <c r="C30" s="2">
-        <v>180032</v>
+        <v>180031</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>753</v>
@@ -19724,7 +19732,7 @@
     </row>
     <row r="31" s="3" customFormat="1" customHeight="1" spans="3:10">
       <c r="C31" s="2">
-        <v>180033</v>
+        <v>180032</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>754</v>
@@ -19748,9 +19756,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:13">
+    <row r="32" s="3" customFormat="1" customHeight="1" spans="3:10">
       <c r="C32" s="2">
-        <v>180034</v>
+        <v>180033</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>755</v>
@@ -19773,12 +19781,10 @@
       <c r="J32" s="2">
         <v>7</v>
       </c>
-      <c r="L32" s="3"/>
-      <c r="M32" s="3"/>
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C33" s="2">
-        <v>180035</v>
+        <v>180034</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>756</v>
@@ -19806,7 +19812,7 @@
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C34" s="2">
-        <v>180036</v>
+        <v>180035</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>757</v>
@@ -19831,6 +19837,62 @@
       </c>
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
+    </row>
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C35" s="2">
+        <v>180036</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>758</v>
+      </c>
+      <c r="E35" s="2">
+        <v>18</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="G35" s="3">
+        <v>1</v>
+      </c>
+      <c r="H35" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I35" s="2">
+        <v>0</v>
+      </c>
+      <c r="J35" s="2">
+        <v>7</v>
+      </c>
+      <c r="L35" s="3"/>
+      <c r="M35" s="3"/>
+    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C36" s="2">
+        <v>180037</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="E36" s="2">
+        <v>18</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="G36" s="3">
+        <v>1</v>
+      </c>
+      <c r="H36" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I36" s="2">
+        <v>0</v>
+      </c>
+      <c r="J36" s="2">
+        <v>7</v>
+      </c>
+      <c r="L36" s="3"/>
+      <c r="M36" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -19976,13 +20038,13 @@
         <v>190001</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="E6" s="2">
         <v>19</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -20002,13 +20064,13 @@
         <v>190002</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="E7" s="2">
         <v>19</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -20028,13 +20090,13 @@
         <v>190003</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="E8" s="2">
         <v>19</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -20054,13 +20116,13 @@
         <v>190004</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="E9" s="2">
         <v>19</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -20080,13 +20142,13 @@
         <v>190005</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="E10" s="2">
         <v>19</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -20106,13 +20168,13 @@
         <v>190006</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="E11" s="2">
         <v>19</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="6"/>
+    <workbookView windowHeight="17680" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -344,7 +344,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1428" uniqueCount="767">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="786">
   <si>
     <t>_Id</t>
   </si>
@@ -1645,58 +1645,115 @@
     <t>激活或者升级对应遗物</t>
   </si>
   <si>
+    <t>520</t>
+  </si>
+  <si>
     <t>白猪之心</t>
   </si>
   <si>
+    <t>530</t>
+  </si>
+  <si>
     <t>猪王之心</t>
   </si>
   <si>
+    <t>540</t>
+  </si>
+  <si>
     <t>蝎王宝甲</t>
   </si>
   <si>
+    <t>550</t>
+  </si>
+  <si>
     <t>沃玛宝甲</t>
   </si>
   <si>
+    <t>560</t>
+  </si>
+  <si>
     <t>沃玛号角</t>
   </si>
   <si>
+    <t>570</t>
+  </si>
+  <si>
     <t>祖玛头像</t>
   </si>
   <si>
+    <t>580</t>
+  </si>
+  <si>
     <t>祖玛号角</t>
   </si>
   <si>
+    <t>590</t>
+  </si>
+  <si>
     <t>虹猪宝甲</t>
   </si>
   <si>
+    <t>600</t>
+  </si>
+  <si>
     <t>树妖之心</t>
   </si>
   <si>
+    <t>610</t>
+  </si>
+  <si>
     <t>虹魔之心</t>
   </si>
   <si>
+    <t>620</t>
+  </si>
+  <si>
     <t>尸王之心</t>
   </si>
   <si>
+    <t>630</t>
+  </si>
+  <si>
     <t>黄泉法杖</t>
   </si>
   <si>
+    <t>640</t>
+  </si>
+  <si>
     <t>牛魔权杖</t>
   </si>
   <si>
+    <t>650</t>
+  </si>
+  <si>
     <t>金刚战锤</t>
   </si>
   <si>
+    <t>660</t>
+  </si>
+  <si>
     <t>巨人之心</t>
   </si>
   <si>
+    <t>670</t>
+  </si>
+  <si>
     <t>恶魔之心</t>
   </si>
   <si>
+    <t>680</t>
+  </si>
+  <si>
     <t>魔龙宝甲</t>
   </si>
   <si>
+    <t>690</t>
+  </si>
+  <si>
     <t>龙神利爪</t>
+  </si>
+  <si>
+    <t>700</t>
   </si>
   <si>
     <t>梦魇鸡爪</t>
@@ -2657,7 +2714,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2695,6 +2752,19 @@
       <b/>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -3196,137 +3266,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3337,12 +3407,16 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
@@ -3786,7 +3860,7 @@
       <c r="C6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="16" t="s">
         <v>23</v>
       </c>
       <c r="E6" s="3" t="s">
@@ -3821,7 +3895,7 @@
       <c r="C7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="16" t="s">
         <v>30</v>
       </c>
       <c r="E7" s="3" t="s">
@@ -3856,7 +3930,7 @@
       <c r="C8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="16" t="s">
         <v>34</v>
       </c>
       <c r="E8" s="3" t="s">
@@ -3891,7 +3965,7 @@
       <c r="C9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="16" t="s">
         <v>38</v>
       </c>
       <c r="E9" s="3" t="s">
@@ -3926,7 +4000,7 @@
       <c r="C10" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="16" t="s">
         <v>43</v>
       </c>
       <c r="E10" s="3" t="s">
@@ -3961,7 +4035,7 @@
       <c r="C11" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="16" t="s">
         <v>46</v>
       </c>
       <c r="E11" s="3" t="s">
@@ -3996,7 +4070,7 @@
       <c r="C12" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="16" t="s">
         <v>50</v>
       </c>
       <c r="E12" s="3" t="s">
@@ -4028,10 +4102,10 @@
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:13">
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="16" t="s">
         <v>54</v>
       </c>
       <c r="E13" s="3" t="s">
@@ -4046,7 +4120,7 @@
       <c r="H13" s="3">
         <v>99999999</v>
       </c>
-      <c r="I13" s="13" t="s">
+      <c r="I13" s="17" t="s">
         <v>56</v>
       </c>
       <c r="J13" s="3">
@@ -4063,10 +4137,10 @@
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:13">
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="16" t="s">
         <v>58</v>
       </c>
       <c r="E14" s="3" t="s">
@@ -4081,7 +4155,7 @@
       <c r="H14" s="3">
         <v>99999999</v>
       </c>
-      <c r="I14" s="13" t="s">
+      <c r="I14" s="17" t="s">
         <v>56</v>
       </c>
       <c r="J14" s="3">
@@ -4098,10 +4172,10 @@
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:13">
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="16" t="s">
         <v>61</v>
       </c>
       <c r="E15" s="3" t="s">
@@ -4116,7 +4190,7 @@
       <c r="H15" s="3">
         <v>99999999</v>
       </c>
-      <c r="I15" s="13" t="s">
+      <c r="I15" s="17" t="s">
         <v>56</v>
       </c>
       <c r="J15" s="3">
@@ -4133,10 +4207,10 @@
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:13">
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="16" t="s">
         <v>64</v>
       </c>
       <c r="E16" s="3" t="s">
@@ -4151,7 +4225,7 @@
       <c r="H16" s="3">
         <v>99999999</v>
       </c>
-      <c r="I16" s="13" t="s">
+      <c r="I16" s="17" t="s">
         <v>56</v>
       </c>
       <c r="J16" s="3">
@@ -4171,7 +4245,7 @@
       <c r="C18" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="16" t="s">
         <v>67</v>
       </c>
       <c r="E18" s="3" t="s">
@@ -4206,7 +4280,7 @@
       <c r="C19" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="16" t="s">
         <v>70</v>
       </c>
       <c r="E19" s="3" t="s">
@@ -4241,7 +4315,7 @@
       <c r="C20" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="16" t="s">
         <v>73</v>
       </c>
       <c r="E20" s="3" t="s">
@@ -4276,7 +4350,7 @@
       <c r="C21" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="16" t="s">
         <v>76</v>
       </c>
       <c r="E21" s="3" t="s">
@@ -4311,7 +4385,7 @@
       <c r="C22" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="16" t="s">
         <v>79</v>
       </c>
       <c r="E22" s="3" t="s">
@@ -4346,7 +4420,7 @@
       <c r="C23" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="16" t="s">
         <v>82</v>
       </c>
       <c r="E23" s="3" t="s">
@@ -4381,7 +4455,7 @@
       <c r="C24" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="16" t="s">
         <v>85</v>
       </c>
       <c r="E24" s="3" t="s">
@@ -4413,10 +4487,10 @@
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:13">
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="16" t="s">
         <v>88</v>
       </c>
       <c r="E25" s="3" t="s">
@@ -4431,7 +4505,7 @@
       <c r="H25" s="3">
         <v>99999999</v>
       </c>
-      <c r="I25" s="13" t="s">
+      <c r="I25" s="17" t="s">
         <v>56</v>
       </c>
       <c r="J25" s="3">
@@ -4448,10 +4522,10 @@
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:13">
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="16" t="s">
         <v>91</v>
       </c>
       <c r="E26" s="3" t="s">
@@ -4466,7 +4540,7 @@
       <c r="H26" s="3">
         <v>99999999</v>
       </c>
-      <c r="I26" s="13" t="s">
+      <c r="I26" s="17" t="s">
         <v>56</v>
       </c>
       <c r="J26" s="3">
@@ -4483,10 +4557,10 @@
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:13">
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="D27" s="16" t="s">
         <v>94</v>
       </c>
       <c r="E27" s="3" t="s">
@@ -4501,7 +4575,7 @@
       <c r="H27" s="3">
         <v>99999999</v>
       </c>
-      <c r="I27" s="13" t="s">
+      <c r="I27" s="17" t="s">
         <v>56</v>
       </c>
       <c r="J27" s="3">
@@ -4518,10 +4592,10 @@
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:13">
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D28" s="16" t="s">
         <v>97</v>
       </c>
       <c r="E28" s="3" t="s">
@@ -4536,7 +4610,7 @@
       <c r="H28" s="3">
         <v>99999999</v>
       </c>
-      <c r="I28" s="13" t="s">
+      <c r="I28" s="17" t="s">
         <v>56</v>
       </c>
       <c r="J28" s="3">
@@ -4556,7 +4630,7 @@
       <c r="C30" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="D30" s="16" t="s">
         <v>100</v>
       </c>
       <c r="E30" s="3" t="s">
@@ -4591,7 +4665,7 @@
       <c r="C31" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="D31" s="16" t="s">
         <v>103</v>
       </c>
       <c r="E31" s="3" t="s">
@@ -4626,7 +4700,7 @@
       <c r="C32" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="D32" s="16" t="s">
         <v>106</v>
       </c>
       <c r="E32" s="3" t="s">
@@ -4661,7 +4735,7 @@
       <c r="C33" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D33" s="12" t="s">
+      <c r="D33" s="16" t="s">
         <v>109</v>
       </c>
       <c r="E33" s="3" t="s">
@@ -4696,7 +4770,7 @@
       <c r="C34" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D34" s="12" t="s">
+      <c r="D34" s="16" t="s">
         <v>112</v>
       </c>
       <c r="E34" s="3" t="s">
@@ -4731,7 +4805,7 @@
       <c r="C35" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="D35" s="16" t="s">
         <v>115</v>
       </c>
       <c r="E35" s="3" t="s">
@@ -4766,7 +4840,7 @@
       <c r="C36" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D36" s="12" t="s">
+      <c r="D36" s="16" t="s">
         <v>118</v>
       </c>
       <c r="E36" s="3" t="s">
@@ -4798,10 +4872,10 @@
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:13">
-      <c r="C37" s="13" t="s">
+      <c r="C37" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="D37" s="12" t="s">
+      <c r="D37" s="16" t="s">
         <v>121</v>
       </c>
       <c r="E37" s="3" t="s">
@@ -4816,7 +4890,7 @@
       <c r="H37" s="3">
         <v>99999999</v>
       </c>
-      <c r="I37" s="13" t="s">
+      <c r="I37" s="17" t="s">
         <v>56</v>
       </c>
       <c r="J37" s="3">
@@ -4833,10 +4907,10 @@
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:13">
-      <c r="C38" s="13" t="s">
+      <c r="C38" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="D38" s="12" t="s">
+      <c r="D38" s="16" t="s">
         <v>124</v>
       </c>
       <c r="E38" s="3" t="s">
@@ -4851,7 +4925,7 @@
       <c r="H38" s="3">
         <v>99999999</v>
       </c>
-      <c r="I38" s="13" t="s">
+      <c r="I38" s="17" t="s">
         <v>56</v>
       </c>
       <c r="J38" s="3">
@@ -4868,10 +4942,10 @@
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:13">
-      <c r="C39" s="13" t="s">
+      <c r="C39" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="D39" s="12" t="s">
+      <c r="D39" s="16" t="s">
         <v>127</v>
       </c>
       <c r="E39" s="3" t="s">
@@ -4886,7 +4960,7 @@
       <c r="H39" s="3">
         <v>99999999</v>
       </c>
-      <c r="I39" s="13" t="s">
+      <c r="I39" s="17" t="s">
         <v>56</v>
       </c>
       <c r="J39" s="3">
@@ -4903,10 +4977,10 @@
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:13">
-      <c r="C40" s="13" t="s">
+      <c r="C40" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="D40" s="12" t="s">
+      <c r="D40" s="16" t="s">
         <v>130</v>
       </c>
       <c r="E40" s="3" t="s">
@@ -4921,7 +4995,7 @@
       <c r="H40" s="3">
         <v>99999999</v>
       </c>
-      <c r="I40" s="13" t="s">
+      <c r="I40" s="17" t="s">
         <v>56</v>
       </c>
       <c r="J40" s="3">
@@ -7064,7 +7138,7 @@
       <c r="C74" s="3">
         <v>8101</v>
       </c>
-      <c r="D74" s="11" t="s">
+      <c r="D74" s="15" t="s">
         <v>238</v>
       </c>
       <c r="E74" s="3">
@@ -7096,7 +7170,7 @@
       <c r="C75" s="3">
         <v>8102</v>
       </c>
-      <c r="D75" s="11" t="s">
+      <c r="D75" s="15" t="s">
         <v>240</v>
       </c>
       <c r="E75" s="3">
@@ -7128,7 +7202,7 @@
       <c r="C76" s="3">
         <v>8103</v>
       </c>
-      <c r="D76" s="11" t="s">
+      <c r="D76" s="15" t="s">
         <v>241</v>
       </c>
       <c r="E76" s="3">
@@ -7160,7 +7234,7 @@
       <c r="C77" s="3">
         <v>8104</v>
       </c>
-      <c r="D77" s="11" t="s">
+      <c r="D77" s="15" t="s">
         <v>242</v>
       </c>
       <c r="E77" s="3">
@@ -7192,7 +7266,7 @@
       <c r="C78" s="3">
         <v>8105</v>
       </c>
-      <c r="D78" s="11" t="s">
+      <c r="D78" s="15" t="s">
         <v>243</v>
       </c>
       <c r="E78" s="3">
@@ -7224,7 +7298,7 @@
       <c r="C79" s="3">
         <v>8106</v>
       </c>
-      <c r="D79" s="11" t="s">
+      <c r="D79" s="15" t="s">
         <v>244</v>
       </c>
       <c r="E79" s="3">
@@ -7256,7 +7330,7 @@
       <c r="C80" s="3">
         <v>8107</v>
       </c>
-      <c r="D80" s="11" t="s">
+      <c r="D80" s="15" t="s">
         <v>245</v>
       </c>
       <c r="E80" s="3">
@@ -7288,7 +7362,7 @@
       <c r="C81" s="3">
         <v>8108</v>
       </c>
-      <c r="D81" s="11" t="s">
+      <c r="D81" s="15" t="s">
         <v>246</v>
       </c>
       <c r="E81" s="3">
@@ -7320,7 +7394,7 @@
       <c r="C83" s="3">
         <v>8201</v>
       </c>
-      <c r="D83" s="11" t="s">
+      <c r="D83" s="15" t="s">
         <v>247</v>
       </c>
       <c r="E83" s="3">
@@ -7355,7 +7429,7 @@
       <c r="C84" s="3">
         <v>8202</v>
       </c>
-      <c r="D84" s="11" t="s">
+      <c r="D84" s="15" t="s">
         <v>249</v>
       </c>
       <c r="E84" s="3">
@@ -7390,7 +7464,7 @@
       <c r="C85" s="3">
         <v>8203</v>
       </c>
-      <c r="D85" s="11" t="s">
+      <c r="D85" s="15" t="s">
         <v>251</v>
       </c>
       <c r="E85" s="3">
@@ -7425,7 +7499,7 @@
       <c r="C86" s="3">
         <v>8204</v>
       </c>
-      <c r="D86" s="11" t="s">
+      <c r="D86" s="15" t="s">
         <v>253</v>
       </c>
       <c r="E86" s="3">
@@ -7460,7 +7534,7 @@
       <c r="C87" s="3">
         <v>8205</v>
       </c>
-      <c r="D87" s="11" t="s">
+      <c r="D87" s="15" t="s">
         <v>255</v>
       </c>
       <c r="E87" s="3">
@@ -7495,7 +7569,7 @@
       <c r="C88" s="3">
         <v>8206</v>
       </c>
-      <c r="D88" s="11" t="s">
+      <c r="D88" s="15" t="s">
         <v>257</v>
       </c>
       <c r="E88" s="3">
@@ -7530,7 +7604,7 @@
       <c r="C89" s="3">
         <v>8207</v>
       </c>
-      <c r="D89" s="11" t="s">
+      <c r="D89" s="15" t="s">
         <v>259</v>
       </c>
       <c r="E89" s="3">
@@ -7562,46 +7636,46 @@
       </c>
     </row>
     <row r="91" customHeight="1" spans="4:4">
-      <c r="D91" s="11"/>
+      <c r="D91" s="15"/>
     </row>
     <row r="92" customHeight="1" spans="4:4">
-      <c r="D92" s="11"/>
+      <c r="D92" s="15"/>
     </row>
     <row r="93" customHeight="1" spans="4:4">
-      <c r="D93" s="11"/>
+      <c r="D93" s="15"/>
     </row>
     <row r="94" customHeight="1" spans="4:4">
-      <c r="D94" s="11"/>
+      <c r="D94" s="15"/>
     </row>
     <row r="95" customHeight="1" spans="4:4">
-      <c r="D95" s="11"/>
+      <c r="D95" s="15"/>
     </row>
     <row r="96" customHeight="1" spans="4:4">
-      <c r="D96" s="11"/>
+      <c r="D96" s="15"/>
     </row>
     <row r="97" customHeight="1" spans="4:4">
-      <c r="D97" s="11"/>
+      <c r="D97" s="15"/>
     </row>
     <row r="99" customHeight="1" spans="4:4">
-      <c r="D99" s="11"/>
+      <c r="D99" s="15"/>
     </row>
     <row r="100" customHeight="1" spans="4:4">
-      <c r="D100" s="11"/>
+      <c r="D100" s="15"/>
     </row>
     <row r="101" customHeight="1" spans="4:4">
-      <c r="D101" s="11"/>
+      <c r="D101" s="15"/>
     </row>
     <row r="102" customHeight="1" spans="4:4">
-      <c r="D102" s="11"/>
+      <c r="D102" s="15"/>
     </row>
     <row r="103" customHeight="1" spans="4:4">
-      <c r="D103" s="11"/>
+      <c r="D103" s="15"/>
     </row>
     <row r="104" customHeight="1" spans="4:4">
-      <c r="D104" s="11"/>
+      <c r="D104" s="15"/>
     </row>
     <row r="105" customHeight="1" spans="4:4">
-      <c r="D105" s="11"/>
+      <c r="D105" s="15"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -8479,7 +8553,7 @@
       <c r="C33" s="2">
         <v>2000011</v>
       </c>
-      <c r="D33" s="10" t="s">
+      <c r="D33" s="14" t="s">
         <v>289</v>
       </c>
       <c r="E33" s="2">
@@ -8507,7 +8581,7 @@
       <c r="C34" s="2">
         <v>2000012</v>
       </c>
-      <c r="D34" s="10" t="s">
+      <c r="D34" s="14" t="s">
         <v>290</v>
       </c>
       <c r="E34" s="2">
@@ -8535,7 +8609,7 @@
       <c r="C35" s="2">
         <v>2000013</v>
       </c>
-      <c r="D35" s="10" t="s">
+      <c r="D35" s="14" t="s">
         <v>291</v>
       </c>
       <c r="E35" s="2">
@@ -11562,7 +11636,7 @@
       <c r="C22" s="2">
         <v>3000017</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D22" s="13" t="s">
         <v>399</v>
       </c>
       <c r="E22" s="2">
@@ -11590,7 +11664,7 @@
       <c r="C23" s="2">
         <v>3000018</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D23" s="13" t="s">
         <v>400</v>
       </c>
       <c r="E23" s="2">
@@ -11618,7 +11692,7 @@
       <c r="C24" s="2">
         <v>3000019</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="D24" s="13" t="s">
         <v>401</v>
       </c>
       <c r="E24" s="2">
@@ -11646,7 +11720,7 @@
       <c r="C25" s="2">
         <v>3000020</v>
       </c>
-      <c r="D25" s="9" t="s">
+      <c r="D25" s="13" t="s">
         <v>402</v>
       </c>
       <c r="E25" s="2">
@@ -11674,7 +11748,7 @@
       <c r="C26" s="2">
         <v>3000021</v>
       </c>
-      <c r="D26" s="9" t="s">
+      <c r="D26" s="13" t="s">
         <v>403</v>
       </c>
       <c r="E26" s="2">
@@ -11702,7 +11776,7 @@
       <c r="C27" s="2">
         <v>3000022</v>
       </c>
-      <c r="D27" s="9" t="s">
+      <c r="D27" s="13" t="s">
         <v>404</v>
       </c>
       <c r="E27" s="2">
@@ -11730,7 +11804,7 @@
       <c r="C28" s="2">
         <v>3000023</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="D28" s="13" t="s">
         <v>405</v>
       </c>
       <c r="E28" s="2">
@@ -11758,7 +11832,7 @@
       <c r="C29" s="2">
         <v>3000024</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="D29" s="13" t="s">
         <v>406</v>
       </c>
       <c r="E29" s="2">
@@ -12473,9 +12547,13 @@
   <dimension ref="C1:M95"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="4" max="4" width="9.625" customWidth="1"/>
-    <col min="6" max="6" width="20.875" customWidth="1"/>
+    <col min="1" max="3" width="9" style="8"/>
+    <col min="4" max="4" width="9.625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="9" style="8"/>
+    <col min="6" max="6" width="20.875" style="8" customWidth="1"/>
+    <col min="7" max="11" width="9" style="8"/>
     <col min="12" max="13" width="13.5" style="3" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="12:13">
@@ -12616,6 +12694,9 @@
       <c r="J7" s="2">
         <v>6</v>
       </c>
+      <c r="K7" s="3" t="s">
+        <v>433</v>
+      </c>
       <c r="L7" s="3">
         <v>4018</v>
       </c>
@@ -12628,7 +12709,7 @@
         <v>40000052</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E8" s="2">
         <v>14</v>
@@ -12647,6 +12728,9 @@
       </c>
       <c r="J8" s="2">
         <v>6</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>435</v>
       </c>
       <c r="L8" s="3">
         <v>4018</v>
@@ -12660,7 +12744,7 @@
         <v>40000053</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E9" s="2">
         <v>14</v>
@@ -12679,6 +12763,9 @@
       </c>
       <c r="J9" s="2">
         <v>6</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>437</v>
       </c>
       <c r="L9" s="3">
         <v>4018</v>
@@ -12692,7 +12779,7 @@
         <v>40000054</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="E10" s="2">
         <v>14</v>
@@ -12711,6 +12798,9 @@
       </c>
       <c r="J10" s="2">
         <v>6</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>439</v>
       </c>
       <c r="L10" s="3">
         <v>4018</v>
@@ -12724,7 +12814,7 @@
         <v>40000055</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="E11" s="2">
         <v>14</v>
@@ -12743,6 +12833,9 @@
       </c>
       <c r="J11" s="2">
         <v>6</v>
+      </c>
+      <c r="K11" s="13" t="s">
+        <v>441</v>
       </c>
       <c r="L11" s="3">
         <v>4018</v>
@@ -12756,7 +12849,7 @@
         <v>40000056</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="E12" s="2">
         <v>14</v>
@@ -12775,6 +12868,9 @@
       </c>
       <c r="J12" s="2">
         <v>6</v>
+      </c>
+      <c r="K12" s="13" t="s">
+        <v>443</v>
       </c>
       <c r="L12" s="3">
         <v>4018</v>
@@ -12788,7 +12884,7 @@
         <v>40000057</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="E13" s="2">
         <v>14</v>
@@ -12807,6 +12903,9 @@
       </c>
       <c r="J13" s="2">
         <v>6</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>445</v>
       </c>
       <c r="L13" s="3">
         <v>4018</v>
@@ -12820,7 +12919,7 @@
         <v>40000058</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="E14" s="2">
         <v>14</v>
@@ -12839,6 +12938,9 @@
       </c>
       <c r="J14" s="2">
         <v>6</v>
+      </c>
+      <c r="K14" s="13" t="s">
+        <v>447</v>
       </c>
       <c r="L14" s="3">
         <v>4018</v>
@@ -12852,7 +12954,7 @@
         <v>40000059</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="E15" s="2">
         <v>14</v>
@@ -12871,6 +12973,9 @@
       </c>
       <c r="J15" s="2">
         <v>6</v>
+      </c>
+      <c r="K15" s="13" t="s">
+        <v>449</v>
       </c>
       <c r="L15" s="3">
         <v>4018</v>
@@ -12884,7 +12989,7 @@
         <v>40000060</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="E16" s="2">
         <v>14</v>
@@ -12903,6 +13008,9 @@
       </c>
       <c r="J16" s="2">
         <v>6</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>451</v>
       </c>
       <c r="L16" s="3">
         <v>4018</v>
@@ -12916,7 +13024,7 @@
         <v>40000061</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="E17" s="2">
         <v>14</v>
@@ -12935,6 +13043,9 @@
       </c>
       <c r="J17" s="2">
         <v>6</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="L17" s="3">
         <v>4018</v>
@@ -12948,7 +13059,7 @@
         <v>40000062</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="E18" s="2">
         <v>14</v>
@@ -12967,6 +13078,9 @@
       </c>
       <c r="J18" s="2">
         <v>6</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>455</v>
       </c>
       <c r="L18" s="3">
         <v>4018</v>
@@ -12980,7 +13094,7 @@
         <v>40000063</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="E19" s="2">
         <v>14</v>
@@ -12999,6 +13113,9 @@
       </c>
       <c r="J19" s="2">
         <v>6</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>457</v>
       </c>
       <c r="L19" s="3">
         <v>4018</v>
@@ -13012,7 +13129,7 @@
         <v>40000064</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>445</v>
+        <v>458</v>
       </c>
       <c r="E20" s="2">
         <v>14</v>
@@ -13031,6 +13148,9 @@
       </c>
       <c r="J20" s="2">
         <v>6</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>459</v>
       </c>
       <c r="L20" s="3">
         <v>4018</v>
@@ -13044,7 +13164,7 @@
         <v>40000065</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="E21" s="2">
         <v>14</v>
@@ -13063,6 +13183,9 @@
       </c>
       <c r="J21" s="2">
         <v>6</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>461</v>
       </c>
       <c r="L21" s="3">
         <v>4018</v>
@@ -13076,7 +13199,7 @@
         <v>40000066</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>447</v>
+        <v>462</v>
       </c>
       <c r="E22" s="2">
         <v>14</v>
@@ -13095,6 +13218,9 @@
       </c>
       <c r="J22" s="2">
         <v>6</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>463</v>
       </c>
       <c r="L22" s="3">
         <v>4018</v>
@@ -13108,7 +13234,7 @@
         <v>40000067</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>448</v>
+        <v>464</v>
       </c>
       <c r="E23" s="2">
         <v>14</v>
@@ -13127,6 +13253,9 @@
       </c>
       <c r="J23" s="2">
         <v>6</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>465</v>
       </c>
       <c r="L23" s="3">
         <v>4018</v>
@@ -13140,7 +13269,7 @@
         <v>40000068</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>449</v>
+        <v>466</v>
       </c>
       <c r="E24" s="2">
         <v>14</v>
@@ -13159,6 +13288,9 @@
       </c>
       <c r="J24" s="2">
         <v>6</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>467</v>
       </c>
       <c r="L24" s="3">
         <v>4018</v>
@@ -13172,7 +13304,7 @@
         <v>40000069</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>450</v>
+        <v>468</v>
       </c>
       <c r="E25" s="2">
         <v>14</v>
@@ -13191,6 +13323,9 @@
       </c>
       <c r="J25" s="2">
         <v>6</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>469</v>
       </c>
       <c r="L25" s="3">
         <v>4018</v>
@@ -13204,7 +13339,7 @@
         <v>40000070</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>451</v>
+        <v>470</v>
       </c>
       <c r="E26" s="2">
         <v>14</v>
@@ -13223,6 +13358,9 @@
       </c>
       <c r="J26" s="2">
         <v>6</v>
+      </c>
+      <c r="K26" s="2">
+        <v>750</v>
       </c>
       <c r="L26" s="3">
         <v>4018</v>
@@ -13236,7 +13374,7 @@
         <v>40000071</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>452</v>
+        <v>471</v>
       </c>
       <c r="E27" s="2">
         <v>14</v>
@@ -13255,6 +13393,9 @@
       </c>
       <c r="J27" s="2">
         <v>6</v>
+      </c>
+      <c r="K27" s="2">
+        <v>750</v>
       </c>
       <c r="L27" s="3">
         <v>4018</v>
@@ -13268,7 +13409,7 @@
         <v>40000072</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>453</v>
+        <v>472</v>
       </c>
       <c r="E28" s="2">
         <v>14</v>
@@ -13287,6 +13428,9 @@
       </c>
       <c r="J28" s="2">
         <v>6</v>
+      </c>
+      <c r="K28" s="2">
+        <v>750</v>
       </c>
       <c r="L28" s="3">
         <v>4018</v>
@@ -13300,7 +13444,7 @@
         <v>40000073</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>454</v>
+        <v>473</v>
       </c>
       <c r="E29" s="2">
         <v>14</v>
@@ -13319,6 +13463,9 @@
       </c>
       <c r="J29" s="2">
         <v>6</v>
+      </c>
+      <c r="K29" s="2">
+        <v>750</v>
       </c>
       <c r="L29" s="3">
         <v>4018</v>
@@ -13332,7 +13479,7 @@
         <v>40000074</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>455</v>
+        <v>474</v>
       </c>
       <c r="E30" s="2">
         <v>14</v>
@@ -13351,6 +13498,9 @@
       </c>
       <c r="J30" s="2">
         <v>6</v>
+      </c>
+      <c r="K30" s="2">
+        <v>750</v>
       </c>
       <c r="L30" s="3">
         <v>4018</v>
@@ -13364,7 +13514,7 @@
         <v>40000075</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>456</v>
+        <v>475</v>
       </c>
       <c r="E31" s="2">
         <v>14</v>
@@ -13383,6 +13533,9 @@
       </c>
       <c r="J31" s="2">
         <v>6</v>
+      </c>
+      <c r="K31" s="2">
+        <v>800</v>
       </c>
       <c r="L31" s="3">
         <v>4018</v>
@@ -13396,7 +13549,7 @@
         <v>40000076</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>457</v>
+        <v>476</v>
       </c>
       <c r="E32" s="2">
         <v>14</v>
@@ -13415,6 +13568,9 @@
       </c>
       <c r="J32" s="2">
         <v>6</v>
+      </c>
+      <c r="K32" s="2">
+        <v>800</v>
       </c>
       <c r="L32" s="3">
         <v>4018</v>
@@ -13428,7 +13584,7 @@
         <v>40000077</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>458</v>
+        <v>477</v>
       </c>
       <c r="E33" s="2">
         <v>14</v>
@@ -13447,6 +13603,9 @@
       </c>
       <c r="J33" s="2">
         <v>6</v>
+      </c>
+      <c r="K33" s="2">
+        <v>800</v>
       </c>
       <c r="L33" s="3">
         <v>4018</v>
@@ -13460,7 +13619,7 @@
         <v>40000078</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>459</v>
+        <v>478</v>
       </c>
       <c r="E34" s="2">
         <v>14</v>
@@ -13479,6 +13638,9 @@
       </c>
       <c r="J34" s="2">
         <v>6</v>
+      </c>
+      <c r="K34" s="2">
+        <v>800</v>
       </c>
       <c r="L34" s="3">
         <v>4018</v>
@@ -13492,7 +13654,7 @@
         <v>40000079</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>460</v>
+        <v>479</v>
       </c>
       <c r="E35" s="2">
         <v>14</v>
@@ -13511,6 +13673,9 @@
       </c>
       <c r="J35" s="2">
         <v>6</v>
+      </c>
+      <c r="K35" s="2">
+        <v>800</v>
       </c>
       <c r="L35" s="3">
         <v>4018</v>
@@ -13524,7 +13689,7 @@
         <v>40000080</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>461</v>
+        <v>480</v>
       </c>
       <c r="E36" s="2">
         <v>14</v>
@@ -13543,6 +13708,9 @@
       </c>
       <c r="J36" s="2">
         <v>6</v>
+      </c>
+      <c r="K36" s="2">
+        <v>850</v>
       </c>
       <c r="L36" s="3">
         <v>4018</v>
@@ -13556,7 +13724,7 @@
         <v>40000081</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>462</v>
+        <v>481</v>
       </c>
       <c r="E37" s="2">
         <v>14</v>
@@ -13575,6 +13743,9 @@
       </c>
       <c r="J37" s="2">
         <v>6</v>
+      </c>
+      <c r="K37" s="2">
+        <v>850</v>
       </c>
       <c r="L37" s="3">
         <v>4018</v>
@@ -13588,7 +13759,7 @@
         <v>40000082</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>463</v>
+        <v>482</v>
       </c>
       <c r="E38" s="2">
         <v>14</v>
@@ -13607,6 +13778,9 @@
       </c>
       <c r="J38" s="2">
         <v>6</v>
+      </c>
+      <c r="K38" s="2">
+        <v>850</v>
       </c>
       <c r="L38" s="3">
         <v>4018</v>
@@ -13620,7 +13794,7 @@
         <v>40000083</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>464</v>
+        <v>483</v>
       </c>
       <c r="E39" s="2">
         <v>14</v>
@@ -13639,6 +13813,9 @@
       </c>
       <c r="J39" s="2">
         <v>6</v>
+      </c>
+      <c r="K39" s="2">
+        <v>850</v>
       </c>
       <c r="L39" s="3">
         <v>4018</v>
@@ -13652,7 +13829,7 @@
         <v>40000084</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>465</v>
+        <v>484</v>
       </c>
       <c r="E40" s="2">
         <v>14</v>
@@ -13671,6 +13848,9 @@
       </c>
       <c r="J40" s="2">
         <v>6</v>
+      </c>
+      <c r="K40" s="2">
+        <v>850</v>
       </c>
       <c r="L40" s="3">
         <v>4018</v>
@@ -13684,7 +13864,7 @@
         <v>40000085</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>466</v>
+        <v>485</v>
       </c>
       <c r="E41" s="2">
         <v>14</v>
@@ -13703,6 +13883,9 @@
       </c>
       <c r="J41" s="2">
         <v>6</v>
+      </c>
+      <c r="K41" s="2">
+        <v>900</v>
       </c>
       <c r="L41" s="3">
         <v>4018</v>
@@ -13716,7 +13899,7 @@
         <v>40000086</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>467</v>
+        <v>486</v>
       </c>
       <c r="E42" s="2">
         <v>14</v>
@@ -13735,6 +13918,9 @@
       </c>
       <c r="J42" s="2">
         <v>6</v>
+      </c>
+      <c r="K42" s="2">
+        <v>900</v>
       </c>
       <c r="L42" s="3">
         <v>4018</v>
@@ -13748,7 +13934,7 @@
         <v>40000087</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>468</v>
+        <v>487</v>
       </c>
       <c r="E43" s="2">
         <v>14</v>
@@ -13767,6 +13953,9 @@
       </c>
       <c r="J43" s="2">
         <v>6</v>
+      </c>
+      <c r="K43" s="2">
+        <v>900</v>
       </c>
       <c r="L43" s="3">
         <v>4018</v>
@@ -13780,7 +13969,7 @@
         <v>40000088</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>469</v>
+        <v>488</v>
       </c>
       <c r="E44" s="2">
         <v>14</v>
@@ -13799,6 +13988,9 @@
       </c>
       <c r="J44" s="2">
         <v>6</v>
+      </c>
+      <c r="K44" s="2">
+        <v>900</v>
       </c>
       <c r="L44" s="3">
         <v>4018</v>
@@ -13812,7 +14004,7 @@
         <v>40000089</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>470</v>
+        <v>489</v>
       </c>
       <c r="E45" s="2">
         <v>14</v>
@@ -13831,6 +14023,9 @@
       </c>
       <c r="J45" s="2">
         <v>6</v>
+      </c>
+      <c r="K45" s="2">
+        <v>900</v>
       </c>
       <c r="L45" s="3">
         <v>4018</v>
@@ -13844,7 +14039,7 @@
         <v>40000090</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>471</v>
+        <v>490</v>
       </c>
       <c r="E46" s="2">
         <v>14</v>
@@ -13863,6 +14058,9 @@
       </c>
       <c r="J46" s="2">
         <v>6</v>
+      </c>
+      <c r="K46" s="8">
+        <v>950</v>
       </c>
       <c r="L46" s="3">
         <v>4018</v>
@@ -13876,7 +14074,7 @@
         <v>40000091</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>472</v>
+        <v>491</v>
       </c>
       <c r="E47" s="2">
         <v>14</v>
@@ -13895,6 +14093,9 @@
       </c>
       <c r="J47" s="2">
         <v>6</v>
+      </c>
+      <c r="K47" s="8">
+        <v>950</v>
       </c>
       <c r="L47" s="3">
         <v>4018</v>
@@ -13908,7 +14109,7 @@
         <v>40000092</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>473</v>
+        <v>492</v>
       </c>
       <c r="E48" s="2">
         <v>14</v>
@@ -13927,6 +14128,9 @@
       </c>
       <c r="J48" s="2">
         <v>6</v>
+      </c>
+      <c r="K48" s="8">
+        <v>950</v>
       </c>
       <c r="L48" s="3">
         <v>4018</v>
@@ -13940,7 +14144,7 @@
         <v>40000093</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>474</v>
+        <v>493</v>
       </c>
       <c r="E49" s="2">
         <v>14</v>
@@ -13959,6 +14163,9 @@
       </c>
       <c r="J49" s="2">
         <v>6</v>
+      </c>
+      <c r="K49" s="8">
+        <v>950</v>
       </c>
       <c r="L49" s="3">
         <v>4018</v>
@@ -13972,7 +14179,7 @@
         <v>40000094</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>475</v>
+        <v>494</v>
       </c>
       <c r="E50" s="2">
         <v>14</v>
@@ -13991,6 +14198,9 @@
       </c>
       <c r="J50" s="2">
         <v>6</v>
+      </c>
+      <c r="K50" s="8">
+        <v>950</v>
       </c>
       <c r="L50" s="3">
         <v>4018</v>
@@ -14004,7 +14214,7 @@
         <v>40000095</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>476</v>
+        <v>495</v>
       </c>
       <c r="E51" s="2">
         <v>14</v>
@@ -14023,6 +14233,9 @@
       </c>
       <c r="J51" s="2">
         <v>6</v>
+      </c>
+      <c r="K51" s="8">
+        <v>1000</v>
       </c>
       <c r="L51" s="3">
         <v>4018</v>
@@ -14036,7 +14249,7 @@
         <v>40000096</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>477</v>
+        <v>496</v>
       </c>
       <c r="E52" s="2">
         <v>14</v>
@@ -14055,6 +14268,9 @@
       </c>
       <c r="J52" s="2">
         <v>6</v>
+      </c>
+      <c r="K52" s="8">
+        <v>1000</v>
       </c>
       <c r="L52" s="3">
         <v>4018</v>
@@ -14068,7 +14284,7 @@
         <v>40000097</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="E53" s="2">
         <v>14</v>
@@ -14087,6 +14303,9 @@
       </c>
       <c r="J53" s="2">
         <v>6</v>
+      </c>
+      <c r="K53" s="8">
+        <v>1000</v>
       </c>
       <c r="L53" s="3">
         <v>4018</v>
@@ -14100,7 +14319,7 @@
         <v>40000098</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>479</v>
+        <v>498</v>
       </c>
       <c r="E54" s="2">
         <v>14</v>
@@ -14120,6 +14339,9 @@
       <c r="J54" s="2">
         <v>6</v>
       </c>
+      <c r="K54" s="8">
+        <v>1000</v>
+      </c>
       <c r="L54" s="3">
         <v>4018</v>
       </c>
@@ -14127,12 +14349,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" customFormat="1" customHeight="1" spans="3:13">
+    <row r="55" s="8" customFormat="1" customHeight="1" spans="3:13">
       <c r="C55" s="2">
         <v>40000099</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>480</v>
+        <v>499</v>
       </c>
       <c r="E55" s="2">
         <v>14</v>
@@ -14152,6 +14374,9 @@
       <c r="J55" s="2">
         <v>6</v>
       </c>
+      <c r="K55" s="8">
+        <v>1000</v>
+      </c>
       <c r="L55" s="3">
         <v>4018</v>
       </c>
@@ -14159,12 +14384,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" customFormat="1" customHeight="1" spans="3:13">
+    <row r="56" s="8" customFormat="1" customHeight="1" spans="3:13">
       <c r="C56" s="2">
         <v>40000100</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>481</v>
+        <v>500</v>
       </c>
       <c r="E56" s="2">
         <v>14</v>
@@ -14184,6 +14409,9 @@
       <c r="J56" s="2">
         <v>6</v>
       </c>
+      <c r="K56" s="8">
+        <v>1050</v>
+      </c>
       <c r="L56" s="3">
         <v>4018</v>
       </c>
@@ -14191,12 +14419,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" customFormat="1" customHeight="1" spans="3:13">
+    <row r="57" s="8" customFormat="1" customHeight="1" spans="3:13">
       <c r="C57" s="2">
         <v>40000101</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>482</v>
+        <v>501</v>
       </c>
       <c r="E57" s="2">
         <v>14</v>
@@ -14216,6 +14444,9 @@
       <c r="J57" s="2">
         <v>6</v>
       </c>
+      <c r="K57" s="8">
+        <v>1050</v>
+      </c>
       <c r="L57" s="3">
         <v>4018</v>
       </c>
@@ -14223,12 +14454,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" customFormat="1" customHeight="1" spans="3:13">
+    <row r="58" s="8" customFormat="1" customHeight="1" spans="3:13">
       <c r="C58" s="2">
         <v>40000102</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>483</v>
+        <v>502</v>
       </c>
       <c r="E58" s="2">
         <v>14</v>
@@ -14248,6 +14479,9 @@
       <c r="J58" s="2">
         <v>6</v>
       </c>
+      <c r="K58" s="8">
+        <v>1050</v>
+      </c>
       <c r="L58" s="3">
         <v>4018</v>
       </c>
@@ -14255,12 +14489,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" customFormat="1" customHeight="1" spans="3:13">
+    <row r="59" s="8" customFormat="1" customHeight="1" spans="3:13">
       <c r="C59" s="2">
         <v>40000103</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>484</v>
+        <v>503</v>
       </c>
       <c r="E59" s="2">
         <v>14</v>
@@ -14280,6 +14514,9 @@
       <c r="J59" s="2">
         <v>6</v>
       </c>
+      <c r="K59" s="8">
+        <v>1050</v>
+      </c>
       <c r="L59" s="3">
         <v>4018</v>
       </c>
@@ -14287,12 +14524,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" customFormat="1" customHeight="1" spans="3:13">
+    <row r="60" s="8" customFormat="1" customHeight="1" spans="3:13">
       <c r="C60" s="2">
         <v>40000104</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>485</v>
+        <v>504</v>
       </c>
       <c r="E60" s="2">
         <v>14</v>
@@ -14312,6 +14549,9 @@
       <c r="J60" s="2">
         <v>6</v>
       </c>
+      <c r="K60" s="8">
+        <v>1050</v>
+      </c>
       <c r="L60" s="3">
         <v>4018</v>
       </c>
@@ -14319,36 +14559,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" s="6" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C61" s="7">
+    <row r="61" s="10" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C61" s="11">
         <v>40000105</v>
       </c>
-      <c r="D61" s="8" t="s">
-        <v>486</v>
-      </c>
-      <c r="E61" s="7">
+      <c r="D61" s="12" t="s">
+        <v>505</v>
+      </c>
+      <c r="E61" s="11">
         <v>14</v>
       </c>
-      <c r="F61" s="7" t="s">
+      <c r="F61" s="11" t="s">
         <v>432</v>
       </c>
-      <c r="G61" s="7">
-        <v>1</v>
-      </c>
-      <c r="H61" s="7">
-        <v>99999</v>
-      </c>
-      <c r="I61" s="7">
-        <v>0</v>
-      </c>
-      <c r="J61" s="7">
-        <v>6</v>
-      </c>
-      <c r="K61" s="7"/>
-      <c r="L61" s="8">
+      <c r="G61" s="11">
+        <v>1</v>
+      </c>
+      <c r="H61" s="11">
+        <v>99999</v>
+      </c>
+      <c r="I61" s="11">
+        <v>0</v>
+      </c>
+      <c r="J61" s="11">
+        <v>6</v>
+      </c>
+      <c r="K61" s="11">
+        <v>1100</v>
+      </c>
+      <c r="L61" s="12">
         <v>4018</v>
       </c>
-      <c r="M61" s="8">
+      <c r="M61" s="12">
         <v>1</v>
       </c>
     </row>
@@ -14357,7 +14599,7 @@
         <v>40000106</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>487</v>
+        <v>506</v>
       </c>
       <c r="E62" s="2">
         <v>14</v>
@@ -14377,7 +14619,9 @@
       <c r="J62" s="2">
         <v>6</v>
       </c>
-      <c r="K62" s="2"/>
+      <c r="K62" s="2">
+        <v>1100</v>
+      </c>
       <c r="L62" s="3">
         <v>4018</v>
       </c>
@@ -14390,7 +14634,7 @@
         <v>40000107</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>488</v>
+        <v>507</v>
       </c>
       <c r="E63" s="2">
         <v>14</v>
@@ -14410,7 +14654,9 @@
       <c r="J63" s="2">
         <v>6</v>
       </c>
-      <c r="K63" s="2"/>
+      <c r="K63" s="2">
+        <v>1100</v>
+      </c>
       <c r="L63" s="3">
         <v>4018</v>
       </c>
@@ -14423,7 +14669,7 @@
         <v>40000108</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>489</v>
+        <v>508</v>
       </c>
       <c r="E64" s="2">
         <v>14</v>
@@ -14443,7 +14689,9 @@
       <c r="J64" s="2">
         <v>6</v>
       </c>
-      <c r="K64" s="2"/>
+      <c r="K64" s="2">
+        <v>1100</v>
+      </c>
       <c r="L64" s="3">
         <v>4018</v>
       </c>
@@ -14456,7 +14704,7 @@
         <v>40000109</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>490</v>
+        <v>509</v>
       </c>
       <c r="E65" s="2">
         <v>14</v>
@@ -14476,7 +14724,9 @@
       <c r="J65" s="2">
         <v>6</v>
       </c>
-      <c r="K65" s="2"/>
+      <c r="K65" s="2">
+        <v>1100</v>
+      </c>
       <c r="L65" s="3">
         <v>4018</v>
       </c>
@@ -14489,7 +14739,7 @@
         <v>40000110</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>491</v>
+        <v>510</v>
       </c>
       <c r="E66" s="2">
         <v>14</v>
@@ -14509,7 +14759,9 @@
       <c r="J66" s="2">
         <v>6</v>
       </c>
-      <c r="K66" s="2"/>
+      <c r="K66" s="2">
+        <v>1150</v>
+      </c>
       <c r="L66" s="3">
         <v>4018</v>
       </c>
@@ -14522,7 +14774,7 @@
         <v>40000111</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>492</v>
+        <v>511</v>
       </c>
       <c r="E67" s="2">
         <v>14</v>
@@ -14542,7 +14794,9 @@
       <c r="J67" s="2">
         <v>6</v>
       </c>
-      <c r="K67" s="2"/>
+      <c r="K67" s="2">
+        <v>1150</v>
+      </c>
       <c r="L67" s="3">
         <v>4018</v>
       </c>
@@ -14555,7 +14809,7 @@
         <v>40000112</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>493</v>
+        <v>512</v>
       </c>
       <c r="E68" s="2">
         <v>14</v>
@@ -14575,7 +14829,9 @@
       <c r="J68" s="2">
         <v>6</v>
       </c>
-      <c r="K68" s="2"/>
+      <c r="K68" s="2">
+        <v>1150</v>
+      </c>
       <c r="L68" s="3">
         <v>4018</v>
       </c>
@@ -14588,7 +14844,7 @@
         <v>40000113</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>494</v>
+        <v>513</v>
       </c>
       <c r="E69" s="2">
         <v>14</v>
@@ -14608,7 +14864,9 @@
       <c r="J69" s="2">
         <v>6</v>
       </c>
-      <c r="K69" s="2"/>
+      <c r="K69" s="2">
+        <v>1150</v>
+      </c>
       <c r="L69" s="3">
         <v>4018</v>
       </c>
@@ -14621,7 +14879,7 @@
         <v>40000114</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>495</v>
+        <v>514</v>
       </c>
       <c r="E70" s="2">
         <v>14</v>
@@ -14641,7 +14899,9 @@
       <c r="J70" s="2">
         <v>6</v>
       </c>
-      <c r="K70" s="2"/>
+      <c r="K70" s="2">
+        <v>1150</v>
+      </c>
       <c r="L70" s="3">
         <v>4018</v>
       </c>
@@ -14654,7 +14914,7 @@
         <v>40000115</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>496</v>
+        <v>515</v>
       </c>
       <c r="E71" s="2">
         <v>14</v>
@@ -14674,7 +14934,9 @@
       <c r="J71" s="2">
         <v>6</v>
       </c>
-      <c r="K71" s="2"/>
+      <c r="K71" s="2">
+        <v>1200</v>
+      </c>
       <c r="L71" s="3">
         <v>4018</v>
       </c>
@@ -14687,7 +14949,7 @@
         <v>40000116</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>497</v>
+        <v>516</v>
       </c>
       <c r="E72" s="2">
         <v>14</v>
@@ -14707,7 +14969,9 @@
       <c r="J72" s="2">
         <v>6</v>
       </c>
-      <c r="K72" s="2"/>
+      <c r="K72" s="2">
+        <v>1200</v>
+      </c>
       <c r="L72" s="3">
         <v>4018</v>
       </c>
@@ -14720,7 +14984,7 @@
         <v>40000117</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>498</v>
+        <v>517</v>
       </c>
       <c r="E73" s="2">
         <v>14</v>
@@ -14740,7 +15004,9 @@
       <c r="J73" s="2">
         <v>6</v>
       </c>
-      <c r="K73" s="2"/>
+      <c r="K73" s="2">
+        <v>1200</v>
+      </c>
       <c r="L73" s="3">
         <v>4018</v>
       </c>
@@ -14753,7 +15019,7 @@
         <v>40000118</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>499</v>
+        <v>518</v>
       </c>
       <c r="E74" s="2">
         <v>14</v>
@@ -14773,7 +15039,9 @@
       <c r="J74" s="2">
         <v>6</v>
       </c>
-      <c r="K74" s="2"/>
+      <c r="K74" s="2">
+        <v>1200</v>
+      </c>
       <c r="L74" s="3">
         <v>4018</v>
       </c>
@@ -14786,7 +15054,7 @@
         <v>40000119</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>500</v>
+        <v>519</v>
       </c>
       <c r="E75" s="2">
         <v>14</v>
@@ -14806,7 +15074,9 @@
       <c r="J75" s="2">
         <v>6</v>
       </c>
-      <c r="K75" s="2"/>
+      <c r="K75" s="8">
+        <v>1200</v>
+      </c>
       <c r="L75" s="3">
         <v>4018</v>
       </c>
@@ -14819,7 +15089,7 @@
         <v>40000120</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>501</v>
+        <v>520</v>
       </c>
       <c r="E76" s="2">
         <v>14</v>
@@ -14839,7 +15109,9 @@
       <c r="J76" s="2">
         <v>6</v>
       </c>
-      <c r="K76" s="2"/>
+      <c r="K76" s="2">
+        <v>1250</v>
+      </c>
       <c r="L76" s="3">
         <v>4018</v>
       </c>
@@ -14852,7 +15124,7 @@
         <v>40000121</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>502</v>
+        <v>521</v>
       </c>
       <c r="E77" s="2">
         <v>14</v>
@@ -14872,7 +15144,9 @@
       <c r="J77" s="2">
         <v>6</v>
       </c>
-      <c r="K77" s="2"/>
+      <c r="K77" s="2">
+        <v>1250</v>
+      </c>
       <c r="L77" s="3">
         <v>4018</v>
       </c>
@@ -14885,7 +15159,7 @@
         <v>40000122</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>503</v>
+        <v>522</v>
       </c>
       <c r="E78" s="2">
         <v>14</v>
@@ -14905,7 +15179,9 @@
       <c r="J78" s="2">
         <v>6</v>
       </c>
-      <c r="K78" s="2"/>
+      <c r="K78" s="2">
+        <v>1250</v>
+      </c>
       <c r="L78" s="3">
         <v>4018</v>
       </c>
@@ -14918,7 +15194,7 @@
         <v>40000123</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>504</v>
+        <v>523</v>
       </c>
       <c r="E79" s="2">
         <v>14</v>
@@ -14938,7 +15214,9 @@
       <c r="J79" s="2">
         <v>6</v>
       </c>
-      <c r="K79" s="2"/>
+      <c r="K79" s="2">
+        <v>1250</v>
+      </c>
       <c r="L79" s="3">
         <v>4018</v>
       </c>
@@ -14951,7 +15229,7 @@
         <v>40000124</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>505</v>
+        <v>524</v>
       </c>
       <c r="E80" s="2">
         <v>14</v>
@@ -14971,7 +15249,9 @@
       <c r="J80" s="2">
         <v>6</v>
       </c>
-      <c r="K80" s="2"/>
+      <c r="K80" s="2">
+        <v>1250</v>
+      </c>
       <c r="L80" s="3">
         <v>4018</v>
       </c>
@@ -14984,7 +15264,7 @@
         <v>40000125</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>506</v>
+        <v>525</v>
       </c>
       <c r="E81" s="2">
         <v>14</v>
@@ -15003,6 +15283,9 @@
       </c>
       <c r="J81" s="2">
         <v>6</v>
+      </c>
+      <c r="K81" s="2">
+        <v>1300</v>
       </c>
       <c r="L81" s="3">
         <v>4018</v>
@@ -15016,7 +15299,7 @@
         <v>40000126</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>507</v>
+        <v>526</v>
       </c>
       <c r="E82" s="2">
         <v>14</v>
@@ -15035,6 +15318,9 @@
       </c>
       <c r="J82" s="2">
         <v>6</v>
+      </c>
+      <c r="K82" s="2">
+        <v>1300</v>
       </c>
       <c r="L82" s="3">
         <v>4018</v>
@@ -15048,7 +15334,7 @@
         <v>40000127</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>508</v>
+        <v>527</v>
       </c>
       <c r="E83" s="2">
         <v>14</v>
@@ -15067,6 +15353,9 @@
       </c>
       <c r="J83" s="2">
         <v>6</v>
+      </c>
+      <c r="K83" s="2">
+        <v>1300</v>
       </c>
       <c r="L83" s="3">
         <v>4018</v>
@@ -15080,7 +15369,7 @@
         <v>40000128</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>509</v>
+        <v>528</v>
       </c>
       <c r="E84" s="2">
         <v>14</v>
@@ -15099,6 +15388,9 @@
       </c>
       <c r="J84" s="2">
         <v>6</v>
+      </c>
+      <c r="K84" s="2">
+        <v>1300</v>
       </c>
       <c r="L84" s="3">
         <v>4018</v>
@@ -15112,7 +15404,7 @@
         <v>40000129</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>510</v>
+        <v>529</v>
       </c>
       <c r="E85" s="2">
         <v>14</v>
@@ -15131,6 +15423,9 @@
       </c>
       <c r="J85" s="2">
         <v>6</v>
+      </c>
+      <c r="K85" s="2">
+        <v>1300</v>
       </c>
       <c r="L85" s="3">
         <v>4018</v>
@@ -15144,7 +15439,7 @@
         <v>40000130</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>511</v>
+        <v>530</v>
       </c>
       <c r="E86" s="2">
         <v>14</v>
@@ -15163,6 +15458,9 @@
       </c>
       <c r="J86" s="2">
         <v>6</v>
+      </c>
+      <c r="K86" s="8">
+        <v>1350</v>
       </c>
       <c r="L86" s="3">
         <v>4018</v>
@@ -15176,7 +15474,7 @@
         <v>40000131</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>512</v>
+        <v>531</v>
       </c>
       <c r="E87" s="2">
         <v>14</v>
@@ -15195,6 +15493,9 @@
       </c>
       <c r="J87" s="2">
         <v>6</v>
+      </c>
+      <c r="K87" s="8">
+        <v>1350</v>
       </c>
       <c r="L87" s="3">
         <v>4018</v>
@@ -15208,7 +15509,7 @@
         <v>40000132</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>513</v>
+        <v>532</v>
       </c>
       <c r="E88" s="2">
         <v>14</v>
@@ -15227,6 +15528,9 @@
       </c>
       <c r="J88" s="2">
         <v>6</v>
+      </c>
+      <c r="K88" s="8">
+        <v>1350</v>
       </c>
       <c r="L88" s="3">
         <v>4018</v>
@@ -15240,7 +15544,7 @@
         <v>40000133</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>514</v>
+        <v>533</v>
       </c>
       <c r="E89" s="2">
         <v>14</v>
@@ -15259,6 +15563,9 @@
       </c>
       <c r="J89" s="2">
         <v>6</v>
+      </c>
+      <c r="K89" s="8">
+        <v>1350</v>
       </c>
       <c r="L89" s="3">
         <v>4018</v>
@@ -15272,7 +15579,7 @@
         <v>40000134</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>515</v>
+        <v>534</v>
       </c>
       <c r="E90" s="2">
         <v>14</v>
@@ -15291,6 +15598,9 @@
       </c>
       <c r="J90" s="2">
         <v>6</v>
+      </c>
+      <c r="K90" s="8">
+        <v>1350</v>
       </c>
       <c r="L90" s="3">
         <v>4018</v>
@@ -15304,7 +15614,7 @@
         <v>40000135</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>516</v>
+        <v>535</v>
       </c>
       <c r="E91" s="2">
         <v>14</v>
@@ -15323,6 +15633,9 @@
       </c>
       <c r="J91" s="2">
         <v>6</v>
+      </c>
+      <c r="K91" s="8">
+        <v>1400</v>
       </c>
       <c r="L91" s="3">
         <v>4018</v>
@@ -15336,7 +15649,7 @@
         <v>40000136</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>517</v>
+        <v>536</v>
       </c>
       <c r="E92" s="2">
         <v>14</v>
@@ -15355,6 +15668,9 @@
       </c>
       <c r="J92" s="2">
         <v>6</v>
+      </c>
+      <c r="K92" s="8">
+        <v>1400</v>
       </c>
       <c r="L92" s="3">
         <v>4018</v>
@@ -15368,7 +15684,7 @@
         <v>40000137</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>518</v>
+        <v>537</v>
       </c>
       <c r="E93" s="2">
         <v>14</v>
@@ -15387,6 +15703,9 @@
       </c>
       <c r="J93" s="2">
         <v>6</v>
+      </c>
+      <c r="K93" s="8">
+        <v>1400</v>
       </c>
       <c r="L93" s="3">
         <v>4018</v>
@@ -15400,7 +15719,7 @@
         <v>40000138</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="E94" s="2">
         <v>14</v>
@@ -15419,6 +15738,9 @@
       </c>
       <c r="J94" s="2">
         <v>6</v>
+      </c>
+      <c r="K94" s="8">
+        <v>1400</v>
       </c>
       <c r="L94" s="3">
         <v>4018</v>
@@ -15432,7 +15754,7 @@
         <v>40000139</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>520</v>
+        <v>539</v>
       </c>
       <c r="E95" s="2">
         <v>14</v>
@@ -15451,6 +15773,9 @@
       </c>
       <c r="J95" s="2">
         <v>6</v>
+      </c>
+      <c r="K95" s="8">
+        <v>1400</v>
       </c>
       <c r="L95" s="3">
         <v>4018</v>
@@ -15480,9 +15805,13 @@
   <dimension ref="C1:M109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
-    <col min="4" max="4" width="14.25" customWidth="1"/>
-    <col min="6" max="6" width="20.875" customWidth="1"/>
+    <col min="1" max="3" width="9" style="8"/>
+    <col min="4" max="4" width="14.25" style="8" customWidth="1"/>
+    <col min="5" max="5" width="9" style="8"/>
+    <col min="6" max="6" width="20.875" style="8" customWidth="1"/>
+    <col min="7" max="11" width="9" style="8"/>
     <col min="12" max="13" width="13.5" style="3" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="12:13">
@@ -15603,13 +15932,13 @@
         <v>50000001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>521</v>
+        <v>540</v>
       </c>
       <c r="E6" s="2">
         <v>5</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>522</v>
+        <v>541</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -15622,6 +15951,9 @@
       </c>
       <c r="J6" s="2">
         <v>6</v>
+      </c>
+      <c r="K6" s="2">
+        <v>800</v>
       </c>
       <c r="L6" s="3">
         <v>4015</v>
@@ -15635,13 +15967,13 @@
         <v>50000002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>523</v>
+        <v>542</v>
       </c>
       <c r="E7" s="2">
         <v>5</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>524</v>
+        <v>543</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -15654,6 +15986,9 @@
       </c>
       <c r="J7" s="2">
         <v>6</v>
+      </c>
+      <c r="K7" s="2">
+        <v>800</v>
       </c>
       <c r="L7" s="3">
         <v>4015</v>
@@ -15667,13 +16002,13 @@
         <v>50000003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>525</v>
+        <v>544</v>
       </c>
       <c r="E8" s="2">
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>526</v>
+        <v>545</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -15686,6 +16021,9 @@
       </c>
       <c r="J8" s="2">
         <v>6</v>
+      </c>
+      <c r="K8" s="2">
+        <v>800</v>
       </c>
       <c r="L8" s="3">
         <v>4015</v>
@@ -15699,13 +16037,13 @@
         <v>50000004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>527</v>
+        <v>546</v>
       </c>
       <c r="E9" s="2">
         <v>5</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>528</v>
+        <v>547</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -15718,6 +16056,9 @@
       </c>
       <c r="J9" s="2">
         <v>6</v>
+      </c>
+      <c r="K9" s="2">
+        <v>800</v>
       </c>
       <c r="L9" s="3">
         <v>4015</v>
@@ -15731,13 +16072,13 @@
         <v>50000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>529</v>
+        <v>548</v>
       </c>
       <c r="E10" s="2">
         <v>5</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>530</v>
+        <v>549</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -15750,6 +16091,9 @@
       </c>
       <c r="J10" s="2">
         <v>6</v>
+      </c>
+      <c r="K10" s="2">
+        <v>800</v>
       </c>
       <c r="L10" s="3">
         <v>4015</v>
@@ -15763,13 +16107,13 @@
         <v>50000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>531</v>
+        <v>550</v>
       </c>
       <c r="E11" s="2">
         <v>5</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>532</v>
+        <v>551</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -15782,6 +16126,9 @@
       </c>
       <c r="J11" s="2">
         <v>6</v>
+      </c>
+      <c r="K11" s="2">
+        <v>800</v>
       </c>
       <c r="L11" s="3">
         <v>4015</v>
@@ -15795,13 +16142,13 @@
         <v>50000007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>533</v>
+        <v>552</v>
       </c>
       <c r="E12" s="2">
         <v>5</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>534</v>
+        <v>553</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -15814,6 +16161,9 @@
       </c>
       <c r="J12" s="2">
         <v>6</v>
+      </c>
+      <c r="K12" s="2">
+        <v>800</v>
       </c>
       <c r="L12" s="3">
         <v>4015</v>
@@ -15822,35 +16172,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C13" s="2">
+    <row r="13" s="6" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C13" s="6">
         <v>50000008</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="E13" s="2">
-        <v>5</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="G13" s="2">
-        <v>1</v>
-      </c>
-      <c r="H13" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I13" s="2">
-        <v>0</v>
-      </c>
-      <c r="J13" s="2">
-        <v>6</v>
-      </c>
-      <c r="L13" s="3">
+      <c r="D13" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="E13" s="6">
+        <v>5</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="G13" s="6">
+        <v>1</v>
+      </c>
+      <c r="H13" s="6">
+        <v>99999</v>
+      </c>
+      <c r="I13" s="6">
+        <v>0</v>
+      </c>
+      <c r="J13" s="6">
+        <v>6</v>
+      </c>
+      <c r="K13" s="6">
+        <v>800</v>
+      </c>
+      <c r="L13" s="9">
         <v>4015</v>
       </c>
-      <c r="M13" s="3">
+      <c r="M13" s="9">
         <v>1</v>
       </c>
     </row>
@@ -15859,13 +16212,13 @@
         <v>50000009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>537</v>
+        <v>556</v>
       </c>
       <c r="E14" s="2">
         <v>5</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>538</v>
+        <v>557</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -15878,6 +16231,9 @@
       </c>
       <c r="J14" s="2">
         <v>6</v>
+      </c>
+      <c r="K14" s="2">
+        <v>850</v>
       </c>
       <c r="L14" s="3">
         <v>4015</v>
@@ -15891,13 +16247,13 @@
         <v>50000010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>539</v>
+        <v>558</v>
       </c>
       <c r="E15" s="2">
         <v>5</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>540</v>
+        <v>559</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -15910,6 +16266,9 @@
       </c>
       <c r="J15" s="2">
         <v>6</v>
+      </c>
+      <c r="K15" s="2">
+        <v>850</v>
       </c>
       <c r="L15" s="3">
         <v>4015</v>
@@ -15923,13 +16282,13 @@
         <v>50000011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>541</v>
+        <v>560</v>
       </c>
       <c r="E16" s="2">
         <v>5</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>542</v>
+        <v>561</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -15942,6 +16301,9 @@
       </c>
       <c r="J16" s="2">
         <v>6</v>
+      </c>
+      <c r="K16" s="2">
+        <v>850</v>
       </c>
       <c r="L16" s="3">
         <v>4015</v>
@@ -15955,13 +16317,13 @@
         <v>50000012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>543</v>
+        <v>562</v>
       </c>
       <c r="E17" s="2">
         <v>5</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>544</v>
+        <v>563</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -15974,6 +16336,9 @@
       </c>
       <c r="J17" s="2">
         <v>6</v>
+      </c>
+      <c r="K17" s="2">
+        <v>850</v>
       </c>
       <c r="L17" s="3">
         <v>4015</v>
@@ -15987,13 +16352,13 @@
         <v>50000013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>545</v>
+        <v>564</v>
       </c>
       <c r="E18" s="2">
         <v>5</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>546</v>
+        <v>565</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -16006,6 +16371,9 @@
       </c>
       <c r="J18" s="2">
         <v>6</v>
+      </c>
+      <c r="K18" s="2">
+        <v>850</v>
       </c>
       <c r="L18" s="3">
         <v>4015</v>
@@ -16019,13 +16387,13 @@
         <v>50000014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>547</v>
+        <v>566</v>
       </c>
       <c r="E19" s="2">
         <v>5</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>548</v>
+        <v>567</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -16038,6 +16406,9 @@
       </c>
       <c r="J19" s="2">
         <v>6</v>
+      </c>
+      <c r="K19" s="2">
+        <v>850</v>
       </c>
       <c r="L19" s="3">
         <v>4015</v>
@@ -16051,13 +16422,13 @@
         <v>50000015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>549</v>
+        <v>568</v>
       </c>
       <c r="E20" s="2">
         <v>5</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>550</v>
+        <v>569</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -16070,6 +16441,9 @@
       </c>
       <c r="J20" s="2">
         <v>6</v>
+      </c>
+      <c r="K20" s="2">
+        <v>850</v>
       </c>
       <c r="L20" s="3">
         <v>4015</v>
@@ -16078,35 +16452,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C21" s="2">
+    <row r="21" s="6" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C21" s="6">
         <v>50000016</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>551</v>
-      </c>
-      <c r="E21" s="2">
-        <v>5</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="G21" s="2">
-        <v>1</v>
-      </c>
-      <c r="H21" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I21" s="2">
-        <v>0</v>
-      </c>
-      <c r="J21" s="2">
-        <v>6</v>
-      </c>
-      <c r="L21" s="3">
+      <c r="D21" s="9" t="s">
+        <v>570</v>
+      </c>
+      <c r="E21" s="6">
+        <v>5</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>571</v>
+      </c>
+      <c r="G21" s="6">
+        <v>1</v>
+      </c>
+      <c r="H21" s="6">
+        <v>99999</v>
+      </c>
+      <c r="I21" s="6">
+        <v>0</v>
+      </c>
+      <c r="J21" s="6">
+        <v>6</v>
+      </c>
+      <c r="K21" s="6">
+        <v>850</v>
+      </c>
+      <c r="L21" s="9">
         <v>4015</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="9">
         <v>1</v>
       </c>
     </row>
@@ -16115,13 +16492,13 @@
         <v>50000017</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>553</v>
+        <v>572</v>
       </c>
       <c r="E22" s="2">
         <v>5</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>554</v>
+        <v>573</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -16134,6 +16511,9 @@
       </c>
       <c r="J22" s="2">
         <v>6</v>
+      </c>
+      <c r="K22" s="8">
+        <v>900</v>
       </c>
       <c r="L22" s="3">
         <v>4015</v>
@@ -16147,13 +16527,13 @@
         <v>50000018</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>555</v>
+        <v>574</v>
       </c>
       <c r="E23" s="2">
         <v>5</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>556</v>
+        <v>575</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -16166,6 +16546,9 @@
       </c>
       <c r="J23" s="2">
         <v>6</v>
+      </c>
+      <c r="K23" s="8">
+        <v>900</v>
       </c>
       <c r="L23" s="3">
         <v>4015</v>
@@ -16179,13 +16562,13 @@
         <v>50000019</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>557</v>
+        <v>576</v>
       </c>
       <c r="E24" s="2">
         <v>5</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>558</v>
+        <v>577</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -16198,6 +16581,9 @@
       </c>
       <c r="J24" s="2">
         <v>6</v>
+      </c>
+      <c r="K24" s="8">
+        <v>900</v>
       </c>
       <c r="L24" s="3">
         <v>4015</v>
@@ -16211,13 +16597,13 @@
         <v>50000020</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>559</v>
+        <v>578</v>
       </c>
       <c r="E25" s="2">
         <v>5</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>560</v>
+        <v>579</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -16230,6 +16616,9 @@
       </c>
       <c r="J25" s="2">
         <v>6</v>
+      </c>
+      <c r="K25" s="8">
+        <v>900</v>
       </c>
       <c r="L25" s="3">
         <v>4015</v>
@@ -16243,13 +16632,13 @@
         <v>50000021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>561</v>
+        <v>580</v>
       </c>
       <c r="E26" s="2">
         <v>5</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>562</v>
+        <v>581</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -16262,6 +16651,9 @@
       </c>
       <c r="J26" s="2">
         <v>6</v>
+      </c>
+      <c r="K26" s="8">
+        <v>900</v>
       </c>
       <c r="L26" s="3">
         <v>4015</v>
@@ -16275,13 +16667,13 @@
         <v>50000022</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>563</v>
+        <v>582</v>
       </c>
       <c r="E27" s="2">
         <v>5</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>564</v>
+        <v>583</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -16294,6 +16686,9 @@
       </c>
       <c r="J27" s="2">
         <v>6</v>
+      </c>
+      <c r="K27" s="8">
+        <v>900</v>
       </c>
       <c r="L27" s="3">
         <v>4015</v>
@@ -16307,13 +16702,13 @@
         <v>50000023</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>565</v>
+        <v>584</v>
       </c>
       <c r="E28" s="2">
         <v>5</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>566</v>
+        <v>585</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -16326,6 +16721,9 @@
       </c>
       <c r="J28" s="2">
         <v>6</v>
+      </c>
+      <c r="K28" s="8">
+        <v>900</v>
       </c>
       <c r="L28" s="3">
         <v>4015</v>
@@ -16334,35 +16732,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C29" s="2">
+    <row r="29" s="6" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C29" s="6">
         <v>50000024</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="E29" s="2">
-        <v>5</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="G29" s="2">
-        <v>1</v>
-      </c>
-      <c r="H29" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I29" s="2">
-        <v>0</v>
-      </c>
-      <c r="J29" s="2">
-        <v>6</v>
-      </c>
-      <c r="L29" s="3">
+      <c r="D29" s="9" t="s">
+        <v>586</v>
+      </c>
+      <c r="E29" s="6">
+        <v>5</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>587</v>
+      </c>
+      <c r="G29" s="6">
+        <v>1</v>
+      </c>
+      <c r="H29" s="6">
+        <v>99999</v>
+      </c>
+      <c r="I29" s="6">
+        <v>0</v>
+      </c>
+      <c r="J29" s="6">
+        <v>6</v>
+      </c>
+      <c r="K29" s="8">
+        <v>900</v>
+      </c>
+      <c r="L29" s="9">
         <v>4015</v>
       </c>
-      <c r="M29" s="3">
+      <c r="M29" s="9">
         <v>1</v>
       </c>
     </row>
@@ -16371,13 +16772,13 @@
         <v>50000025</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>569</v>
+        <v>588</v>
       </c>
       <c r="E30" s="2">
         <v>5</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>570</v>
+        <v>589</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -16390,6 +16791,9 @@
       </c>
       <c r="J30" s="2">
         <v>6</v>
+      </c>
+      <c r="K30" s="8">
+        <v>950</v>
       </c>
       <c r="L30" s="3">
         <v>4015</v>
@@ -16403,13 +16807,13 @@
         <v>50000026</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>571</v>
+        <v>590</v>
       </c>
       <c r="E31" s="2">
         <v>5</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>572</v>
+        <v>591</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -16422,6 +16826,9 @@
       </c>
       <c r="J31" s="2">
         <v>6</v>
+      </c>
+      <c r="K31" s="8">
+        <v>950</v>
       </c>
       <c r="L31" s="3">
         <v>4015</v>
@@ -16435,13 +16842,13 @@
         <v>50000027</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>573</v>
+        <v>592</v>
       </c>
       <c r="E32" s="2">
         <v>5</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>574</v>
+        <v>593</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -16454,6 +16861,9 @@
       </c>
       <c r="J32" s="2">
         <v>6</v>
+      </c>
+      <c r="K32" s="8">
+        <v>950</v>
       </c>
       <c r="L32" s="3">
         <v>4015</v>
@@ -16467,13 +16877,13 @@
         <v>50000028</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>575</v>
+        <v>594</v>
       </c>
       <c r="E33" s="2">
         <v>5</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>576</v>
+        <v>595</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -16486,6 +16896,9 @@
       </c>
       <c r="J33" s="2">
         <v>6</v>
+      </c>
+      <c r="K33" s="8">
+        <v>950</v>
       </c>
       <c r="L33" s="3">
         <v>4015</v>
@@ -16499,13 +16912,13 @@
         <v>50000029</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>577</v>
+        <v>596</v>
       </c>
       <c r="E34" s="2">
         <v>5</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>578</v>
+        <v>597</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -16518,6 +16931,9 @@
       </c>
       <c r="J34" s="2">
         <v>6</v>
+      </c>
+      <c r="K34" s="8">
+        <v>950</v>
       </c>
       <c r="L34" s="3">
         <v>4015</v>
@@ -16531,13 +16947,13 @@
         <v>50000030</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>579</v>
+        <v>598</v>
       </c>
       <c r="E35" s="2">
         <v>5</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>580</v>
+        <v>599</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -16550,6 +16966,9 @@
       </c>
       <c r="J35" s="2">
         <v>6</v>
+      </c>
+      <c r="K35" s="8">
+        <v>950</v>
       </c>
       <c r="L35" s="3">
         <v>4015</v>
@@ -16563,13 +16982,13 @@
         <v>50000031</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>581</v>
+        <v>600</v>
       </c>
       <c r="E36" s="2">
         <v>5</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>582</v>
+        <v>601</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -16582,6 +17001,9 @@
       </c>
       <c r="J36" s="2">
         <v>6</v>
+      </c>
+      <c r="K36" s="8">
+        <v>950</v>
       </c>
       <c r="L36" s="3">
         <v>4015</v>
@@ -16590,35 +17012,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" customHeight="1" spans="3:13">
-      <c r="C37" s="2">
+    <row r="37" s="7" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C37" s="6">
         <v>50000032</v>
       </c>
-      <c r="D37" s="3" t="s">
-        <v>583</v>
-      </c>
-      <c r="E37" s="2">
-        <v>5</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="G37" s="2">
-        <v>1</v>
-      </c>
-      <c r="H37" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I37" s="2">
-        <v>0</v>
-      </c>
-      <c r="J37" s="2">
-        <v>6</v>
-      </c>
-      <c r="L37" s="3">
+      <c r="D37" s="9" t="s">
+        <v>602</v>
+      </c>
+      <c r="E37" s="6">
+        <v>5</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="G37" s="6">
+        <v>1</v>
+      </c>
+      <c r="H37" s="6">
+        <v>99999</v>
+      </c>
+      <c r="I37" s="6">
+        <v>0</v>
+      </c>
+      <c r="J37" s="6">
+        <v>6</v>
+      </c>
+      <c r="K37" s="8">
+        <v>950</v>
+      </c>
+      <c r="L37" s="9">
         <v>4015</v>
       </c>
-      <c r="M37" s="3">
+      <c r="M37" s="9">
         <v>1</v>
       </c>
     </row>
@@ -16627,13 +17052,13 @@
         <v>50000033</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>585</v>
+        <v>604</v>
       </c>
       <c r="E38" s="2">
         <v>5</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>586</v>
+        <v>605</v>
       </c>
       <c r="G38" s="2">
         <v>1</v>
@@ -16646,6 +17071,9 @@
       </c>
       <c r="J38" s="2">
         <v>6</v>
+      </c>
+      <c r="K38" s="2">
+        <v>1000</v>
       </c>
       <c r="L38" s="3">
         <v>4015</v>
@@ -16659,13 +17087,13 @@
         <v>50000034</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>587</v>
+        <v>606</v>
       </c>
       <c r="E39" s="2">
         <v>5</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>588</v>
+        <v>607</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -16678,6 +17106,9 @@
       </c>
       <c r="J39" s="2">
         <v>6</v>
+      </c>
+      <c r="K39" s="2">
+        <v>1000</v>
       </c>
       <c r="L39" s="3">
         <v>4015</v>
@@ -16691,13 +17122,13 @@
         <v>50000035</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>589</v>
+        <v>608</v>
       </c>
       <c r="E40" s="2">
         <v>5</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>590</v>
+        <v>609</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -16710,6 +17141,9 @@
       </c>
       <c r="J40" s="2">
         <v>6</v>
+      </c>
+      <c r="K40" s="2">
+        <v>1000</v>
       </c>
       <c r="L40" s="3">
         <v>4015</v>
@@ -16723,13 +17157,13 @@
         <v>50000036</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>591</v>
+        <v>610</v>
       </c>
       <c r="E41" s="2">
         <v>5</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>592</v>
+        <v>611</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -16742,6 +17176,9 @@
       </c>
       <c r="J41" s="2">
         <v>6</v>
+      </c>
+      <c r="K41" s="2">
+        <v>1000</v>
       </c>
       <c r="L41" s="3">
         <v>4015</v>
@@ -16755,13 +17192,13 @@
         <v>50000037</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>593</v>
+        <v>612</v>
       </c>
       <c r="E42" s="2">
         <v>5</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>594</v>
+        <v>613</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -16774,6 +17211,9 @@
       </c>
       <c r="J42" s="2">
         <v>6</v>
+      </c>
+      <c r="K42" s="2">
+        <v>1000</v>
       </c>
       <c r="L42" s="3">
         <v>4015</v>
@@ -16787,13 +17227,13 @@
         <v>50000038</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>595</v>
+        <v>614</v>
       </c>
       <c r="E43" s="2">
         <v>5</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>596</v>
+        <v>615</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -16806,6 +17246,9 @@
       </c>
       <c r="J43" s="2">
         <v>6</v>
+      </c>
+      <c r="K43" s="2">
+        <v>1000</v>
       </c>
       <c r="L43" s="3">
         <v>4015</v>
@@ -16819,13 +17262,13 @@
         <v>50000039</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>597</v>
+        <v>616</v>
       </c>
       <c r="E44" s="2">
         <v>5</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>598</v>
+        <v>617</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -16838,6 +17281,9 @@
       </c>
       <c r="J44" s="2">
         <v>6</v>
+      </c>
+      <c r="K44" s="2">
+        <v>1000</v>
       </c>
       <c r="L44" s="3">
         <v>4015</v>
@@ -16846,35 +17292,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" customHeight="1" spans="3:13">
-      <c r="C45" s="2">
+    <row r="45" s="7" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C45" s="6">
         <v>50000040</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>599</v>
-      </c>
-      <c r="E45" s="2">
-        <v>5</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="G45" s="2">
-        <v>1</v>
-      </c>
-      <c r="H45" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I45" s="2">
-        <v>0</v>
-      </c>
-      <c r="J45" s="2">
-        <v>6</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="D45" s="9" t="s">
+        <v>618</v>
+      </c>
+      <c r="E45" s="6">
+        <v>5</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>619</v>
+      </c>
+      <c r="G45" s="6">
+        <v>1</v>
+      </c>
+      <c r="H45" s="6">
+        <v>99999</v>
+      </c>
+      <c r="I45" s="6">
+        <v>0</v>
+      </c>
+      <c r="J45" s="6">
+        <v>6</v>
+      </c>
+      <c r="K45" s="2">
+        <v>1000</v>
+      </c>
+      <c r="L45" s="9">
         <v>4015</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="9">
         <v>1</v>
       </c>
     </row>
@@ -16883,13 +17332,13 @@
         <v>50000041</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>601</v>
+        <v>620</v>
       </c>
       <c r="E46" s="2">
         <v>5</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>602</v>
+        <v>621</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -16902,6 +17351,9 @@
       </c>
       <c r="J46" s="2">
         <v>6</v>
+      </c>
+      <c r="K46" s="2">
+        <v>1050</v>
       </c>
       <c r="L46" s="3">
         <v>4015</v>
@@ -16915,13 +17367,13 @@
         <v>50000042</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>603</v>
+        <v>622</v>
       </c>
       <c r="E47" s="2">
         <v>5</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>604</v>
+        <v>623</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -16934,6 +17386,9 @@
       </c>
       <c r="J47" s="2">
         <v>6</v>
+      </c>
+      <c r="K47" s="2">
+        <v>1050</v>
       </c>
       <c r="L47" s="3">
         <v>4015</v>
@@ -16947,13 +17402,13 @@
         <v>50000043</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>605</v>
+        <v>624</v>
       </c>
       <c r="E48" s="2">
         <v>5</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>606</v>
+        <v>625</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -16966,6 +17421,9 @@
       </c>
       <c r="J48" s="2">
         <v>6</v>
+      </c>
+      <c r="K48" s="2">
+        <v>1050</v>
       </c>
       <c r="L48" s="3">
         <v>4015</v>
@@ -16979,13 +17437,13 @@
         <v>50000044</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>607</v>
+        <v>626</v>
       </c>
       <c r="E49" s="2">
         <v>5</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>608</v>
+        <v>627</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -16998,6 +17456,9 @@
       </c>
       <c r="J49" s="2">
         <v>6</v>
+      </c>
+      <c r="K49" s="2">
+        <v>1050</v>
       </c>
       <c r="L49" s="3">
         <v>4015</v>
@@ -17011,13 +17472,13 @@
         <v>50000045</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>609</v>
+        <v>628</v>
       </c>
       <c r="E50" s="2">
         <v>5</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>610</v>
+        <v>629</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -17030,6 +17491,9 @@
       </c>
       <c r="J50" s="2">
         <v>6</v>
+      </c>
+      <c r="K50" s="2">
+        <v>1050</v>
       </c>
       <c r="L50" s="3">
         <v>4015</v>
@@ -17043,13 +17507,13 @@
         <v>50000046</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>611</v>
+        <v>630</v>
       </c>
       <c r="E51" s="2">
         <v>5</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>612</v>
+        <v>631</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -17062,6 +17526,9 @@
       </c>
       <c r="J51" s="2">
         <v>6</v>
+      </c>
+      <c r="K51" s="2">
+        <v>1050</v>
       </c>
       <c r="L51" s="3">
         <v>4015</v>
@@ -17075,13 +17542,13 @@
         <v>50000047</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>613</v>
+        <v>632</v>
       </c>
       <c r="E52" s="2">
         <v>5</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>614</v>
+        <v>633</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -17094,6 +17561,9 @@
       </c>
       <c r="J52" s="2">
         <v>6</v>
+      </c>
+      <c r="K52" s="2">
+        <v>1050</v>
       </c>
       <c r="L52" s="3">
         <v>4015</v>
@@ -17102,35 +17572,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" customHeight="1" spans="3:13">
-      <c r="C53" s="2">
+    <row r="53" s="7" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C53" s="6">
         <v>50000048</v>
       </c>
-      <c r="D53" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="E53" s="2">
-        <v>5</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="G53" s="2">
-        <v>1</v>
-      </c>
-      <c r="H53" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I53" s="2">
-        <v>0</v>
-      </c>
-      <c r="J53" s="2">
-        <v>6</v>
-      </c>
-      <c r="L53" s="3">
+      <c r="D53" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="E53" s="6">
+        <v>5</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>635</v>
+      </c>
+      <c r="G53" s="6">
+        <v>1</v>
+      </c>
+      <c r="H53" s="6">
+        <v>99999</v>
+      </c>
+      <c r="I53" s="6">
+        <v>0</v>
+      </c>
+      <c r="J53" s="6">
+        <v>6</v>
+      </c>
+      <c r="K53" s="2">
+        <v>1050</v>
+      </c>
+      <c r="L53" s="9">
         <v>4015</v>
       </c>
-      <c r="M53" s="3">
+      <c r="M53" s="9">
         <v>1</v>
       </c>
     </row>
@@ -17139,13 +17612,13 @@
         <v>50000049</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>617</v>
+        <v>636</v>
       </c>
       <c r="E54" s="2">
         <v>5</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>618</v>
+        <v>637</v>
       </c>
       <c r="G54" s="2">
         <v>1</v>
@@ -17158,6 +17631,9 @@
       </c>
       <c r="J54" s="2">
         <v>6</v>
+      </c>
+      <c r="K54" s="2">
+        <v>1100</v>
       </c>
       <c r="L54" s="3">
         <v>4015</v>
@@ -17171,13 +17647,13 @@
         <v>50000050</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>619</v>
+        <v>638</v>
       </c>
       <c r="E55" s="2">
         <v>5</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>620</v>
+        <v>639</v>
       </c>
       <c r="G55" s="2">
         <v>1</v>
@@ -17190,6 +17666,9 @@
       </c>
       <c r="J55" s="2">
         <v>6</v>
+      </c>
+      <c r="K55" s="2">
+        <v>1100</v>
       </c>
       <c r="L55" s="3">
         <v>4015</v>
@@ -17203,13 +17682,13 @@
         <v>50000051</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>621</v>
+        <v>640</v>
       </c>
       <c r="E56" s="2">
         <v>5</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>622</v>
+        <v>641</v>
       </c>
       <c r="G56" s="2">
         <v>1</v>
@@ -17222,6 +17701,9 @@
       </c>
       <c r="J56" s="2">
         <v>6</v>
+      </c>
+      <c r="K56" s="2">
+        <v>1100</v>
       </c>
       <c r="L56" s="3">
         <v>4015</v>
@@ -17235,13 +17717,13 @@
         <v>50000052</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>623</v>
+        <v>642</v>
       </c>
       <c r="E57" s="2">
         <v>5</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>624</v>
+        <v>643</v>
       </c>
       <c r="G57" s="2">
         <v>1</v>
@@ -17254,6 +17736,9 @@
       </c>
       <c r="J57" s="2">
         <v>6</v>
+      </c>
+      <c r="K57" s="2">
+        <v>1100</v>
       </c>
       <c r="L57" s="3">
         <v>4015</v>
@@ -17267,13 +17752,13 @@
         <v>50000053</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>625</v>
+        <v>644</v>
       </c>
       <c r="E58" s="2">
         <v>5</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>626</v>
+        <v>645</v>
       </c>
       <c r="G58" s="2">
         <v>1</v>
@@ -17286,6 +17771,9 @@
       </c>
       <c r="J58" s="2">
         <v>6</v>
+      </c>
+      <c r="K58" s="2">
+        <v>1100</v>
       </c>
       <c r="L58" s="3">
         <v>4015</v>
@@ -17299,13 +17787,13 @@
         <v>50000054</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>627</v>
+        <v>646</v>
       </c>
       <c r="E59" s="2">
         <v>5</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>628</v>
+        <v>647</v>
       </c>
       <c r="G59" s="2">
         <v>1</v>
@@ -17318,6 +17806,9 @@
       </c>
       <c r="J59" s="2">
         <v>6</v>
+      </c>
+      <c r="K59" s="2">
+        <v>1100</v>
       </c>
       <c r="L59" s="3">
         <v>4015</v>
@@ -17331,13 +17822,13 @@
         <v>50000055</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>629</v>
+        <v>648</v>
       </c>
       <c r="E60" s="2">
         <v>5</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>630</v>
+        <v>649</v>
       </c>
       <c r="G60" s="2">
         <v>1</v>
@@ -17350,6 +17841,9 @@
       </c>
       <c r="J60" s="2">
         <v>6</v>
+      </c>
+      <c r="K60" s="2">
+        <v>1100</v>
       </c>
       <c r="L60" s="3">
         <v>4015</v>
@@ -17358,35 +17852,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" customHeight="1" spans="3:13">
-      <c r="C61" s="2">
+    <row r="61" s="7" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C61" s="6">
         <v>50000056</v>
       </c>
-      <c r="D61" s="3" t="s">
-        <v>631</v>
-      </c>
-      <c r="E61" s="2">
-        <v>5</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>632</v>
-      </c>
-      <c r="G61" s="2">
-        <v>1</v>
-      </c>
-      <c r="H61" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I61" s="2">
-        <v>0</v>
-      </c>
-      <c r="J61" s="2">
-        <v>6</v>
-      </c>
-      <c r="L61" s="3">
+      <c r="D61" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="E61" s="6">
+        <v>5</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>651</v>
+      </c>
+      <c r="G61" s="6">
+        <v>1</v>
+      </c>
+      <c r="H61" s="6">
+        <v>99999</v>
+      </c>
+      <c r="I61" s="6">
+        <v>0</v>
+      </c>
+      <c r="J61" s="6">
+        <v>6</v>
+      </c>
+      <c r="K61" s="2">
+        <v>1100</v>
+      </c>
+      <c r="L61" s="9">
         <v>4015</v>
       </c>
-      <c r="M61" s="3">
+      <c r="M61" s="9">
         <v>1</v>
       </c>
     </row>
@@ -17395,13 +17892,13 @@
         <v>50000057</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>633</v>
+        <v>652</v>
       </c>
       <c r="E62" s="2">
         <v>5</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>634</v>
+        <v>653</v>
       </c>
       <c r="G62" s="2">
         <v>1</v>
@@ -17414,6 +17911,9 @@
       </c>
       <c r="J62" s="2">
         <v>6</v>
+      </c>
+      <c r="K62" s="8">
+        <v>1150</v>
       </c>
       <c r="L62" s="3">
         <v>4015</v>
@@ -17427,13 +17927,13 @@
         <v>50000058</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>635</v>
+        <v>654</v>
       </c>
       <c r="E63" s="2">
         <v>5</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>636</v>
+        <v>655</v>
       </c>
       <c r="G63" s="2">
         <v>1</v>
@@ -17446,6 +17946,9 @@
       </c>
       <c r="J63" s="2">
         <v>6</v>
+      </c>
+      <c r="K63" s="8">
+        <v>1150</v>
       </c>
       <c r="L63" s="3">
         <v>4015</v>
@@ -17459,13 +17962,13 @@
         <v>50000059</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>637</v>
+        <v>656</v>
       </c>
       <c r="E64" s="2">
         <v>5</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>638</v>
+        <v>657</v>
       </c>
       <c r="G64" s="2">
         <v>1</v>
@@ -17478,6 +17981,9 @@
       </c>
       <c r="J64" s="2">
         <v>6</v>
+      </c>
+      <c r="K64" s="8">
+        <v>1150</v>
       </c>
       <c r="L64" s="3">
         <v>4015</v>
@@ -17491,13 +17997,13 @@
         <v>50000060</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>639</v>
+        <v>658</v>
       </c>
       <c r="E65" s="2">
         <v>5</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>640</v>
+        <v>659</v>
       </c>
       <c r="G65" s="2">
         <v>1</v>
@@ -17510,6 +18016,9 @@
       </c>
       <c r="J65" s="2">
         <v>6</v>
+      </c>
+      <c r="K65" s="8">
+        <v>1150</v>
       </c>
       <c r="L65" s="3">
         <v>4015</v>
@@ -17523,13 +18032,13 @@
         <v>50000061</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>641</v>
+        <v>660</v>
       </c>
       <c r="E66" s="2">
         <v>5</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>642</v>
+        <v>661</v>
       </c>
       <c r="G66" s="2">
         <v>1</v>
@@ -17542,6 +18051,9 @@
       </c>
       <c r="J66" s="2">
         <v>6</v>
+      </c>
+      <c r="K66" s="8">
+        <v>1150</v>
       </c>
       <c r="L66" s="3">
         <v>4015</v>
@@ -17555,13 +18067,13 @@
         <v>50000062</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>643</v>
+        <v>662</v>
       </c>
       <c r="E67" s="2">
         <v>5</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>644</v>
+        <v>663</v>
       </c>
       <c r="G67" s="2">
         <v>1</v>
@@ -17574,6 +18086,9 @@
       </c>
       <c r="J67" s="2">
         <v>6</v>
+      </c>
+      <c r="K67" s="8">
+        <v>1150</v>
       </c>
       <c r="L67" s="3">
         <v>4015</v>
@@ -17587,13 +18102,13 @@
         <v>50000063</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>645</v>
+        <v>664</v>
       </c>
       <c r="E68" s="2">
         <v>5</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>646</v>
+        <v>665</v>
       </c>
       <c r="G68" s="2">
         <v>1</v>
@@ -17606,6 +18121,9 @@
       </c>
       <c r="J68" s="2">
         <v>6</v>
+      </c>
+      <c r="K68" s="8">
+        <v>1150</v>
       </c>
       <c r="L68" s="3">
         <v>4015</v>
@@ -17614,35 +18132,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" customHeight="1" spans="3:13">
-      <c r="C69" s="2">
+    <row r="69" s="7" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C69" s="6">
         <v>50000064</v>
       </c>
-      <c r="D69" s="3" t="s">
-        <v>647</v>
-      </c>
-      <c r="E69" s="2">
-        <v>5</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="G69" s="2">
-        <v>1</v>
-      </c>
-      <c r="H69" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I69" s="2">
-        <v>0</v>
-      </c>
-      <c r="J69" s="2">
-        <v>6</v>
-      </c>
-      <c r="L69" s="3">
+      <c r="D69" s="9" t="s">
+        <v>666</v>
+      </c>
+      <c r="E69" s="6">
+        <v>5</v>
+      </c>
+      <c r="F69" s="6" t="s">
+        <v>667</v>
+      </c>
+      <c r="G69" s="6">
+        <v>1</v>
+      </c>
+      <c r="H69" s="6">
+        <v>99999</v>
+      </c>
+      <c r="I69" s="6">
+        <v>0</v>
+      </c>
+      <c r="J69" s="6">
+        <v>6</v>
+      </c>
+      <c r="K69" s="8">
+        <v>1150</v>
+      </c>
+      <c r="L69" s="9">
         <v>4015</v>
       </c>
-      <c r="M69" s="3">
+      <c r="M69" s="9">
         <v>1</v>
       </c>
     </row>
@@ -17651,13 +18172,13 @@
         <v>50000065</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>649</v>
+        <v>668</v>
       </c>
       <c r="E70" s="2">
         <v>5</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>650</v>
+        <v>669</v>
       </c>
       <c r="G70" s="2">
         <v>1</v>
@@ -17670,6 +18191,9 @@
       </c>
       <c r="J70" s="2">
         <v>6</v>
+      </c>
+      <c r="K70" s="8">
+        <v>1200</v>
       </c>
       <c r="L70" s="3">
         <v>4015</v>
@@ -17683,13 +18207,13 @@
         <v>50000066</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>651</v>
+        <v>670</v>
       </c>
       <c r="E71" s="2">
         <v>5</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>652</v>
+        <v>671</v>
       </c>
       <c r="G71" s="2">
         <v>1</v>
@@ -17702,6 +18226,9 @@
       </c>
       <c r="J71" s="2">
         <v>6</v>
+      </c>
+      <c r="K71" s="8">
+        <v>1200</v>
       </c>
       <c r="L71" s="3">
         <v>4015</v>
@@ -17715,13 +18242,13 @@
         <v>50000067</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>653</v>
+        <v>672</v>
       </c>
       <c r="E72" s="2">
         <v>5</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>654</v>
+        <v>673</v>
       </c>
       <c r="G72" s="2">
         <v>1</v>
@@ -17734,6 +18261,9 @@
       </c>
       <c r="J72" s="2">
         <v>6</v>
+      </c>
+      <c r="K72" s="8">
+        <v>1200</v>
       </c>
       <c r="L72" s="3">
         <v>4015</v>
@@ -17747,13 +18277,13 @@
         <v>50000068</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>655</v>
+        <v>674</v>
       </c>
       <c r="E73" s="2">
         <v>5</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>656</v>
+        <v>675</v>
       </c>
       <c r="G73" s="2">
         <v>1</v>
@@ -17766,6 +18296,9 @@
       </c>
       <c r="J73" s="2">
         <v>6</v>
+      </c>
+      <c r="K73" s="8">
+        <v>1200</v>
       </c>
       <c r="L73" s="3">
         <v>4015</v>
@@ -17779,13 +18312,13 @@
         <v>50000069</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>657</v>
+        <v>676</v>
       </c>
       <c r="E74" s="2">
         <v>5</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>658</v>
+        <v>677</v>
       </c>
       <c r="G74" s="2">
         <v>1</v>
@@ -17798,6 +18331,9 @@
       </c>
       <c r="J74" s="2">
         <v>6</v>
+      </c>
+      <c r="K74" s="8">
+        <v>1200</v>
       </c>
       <c r="L74" s="3">
         <v>4015</v>
@@ -17811,13 +18347,13 @@
         <v>50000070</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>659</v>
+        <v>678</v>
       </c>
       <c r="E75" s="2">
         <v>5</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>660</v>
+        <v>679</v>
       </c>
       <c r="G75" s="2">
         <v>1</v>
@@ -17830,6 +18366,9 @@
       </c>
       <c r="J75" s="2">
         <v>6</v>
+      </c>
+      <c r="K75" s="8">
+        <v>1200</v>
       </c>
       <c r="L75" s="3">
         <v>4015</v>
@@ -17843,13 +18382,13 @@
         <v>50000071</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>661</v>
+        <v>680</v>
       </c>
       <c r="E76" s="2">
         <v>5</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>662</v>
+        <v>681</v>
       </c>
       <c r="G76" s="2">
         <v>1</v>
@@ -17862,6 +18401,9 @@
       </c>
       <c r="J76" s="2">
         <v>6</v>
+      </c>
+      <c r="K76" s="8">
+        <v>1200</v>
       </c>
       <c r="L76" s="3">
         <v>4015</v>
@@ -17870,35 +18412,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" customHeight="1" spans="3:13">
-      <c r="C77" s="2">
+    <row r="77" s="7" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C77" s="6">
         <v>50000072</v>
       </c>
-      <c r="D77" s="3" t="s">
-        <v>663</v>
-      </c>
-      <c r="E77" s="2">
-        <v>5</v>
-      </c>
-      <c r="F77" s="2" t="s">
-        <v>664</v>
-      </c>
-      <c r="G77" s="2">
-        <v>1</v>
-      </c>
-      <c r="H77" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I77" s="2">
-        <v>0</v>
-      </c>
-      <c r="J77" s="2">
-        <v>6</v>
-      </c>
-      <c r="L77" s="3">
+      <c r="D77" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="E77" s="6">
+        <v>5</v>
+      </c>
+      <c r="F77" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="G77" s="6">
+        <v>1</v>
+      </c>
+      <c r="H77" s="6">
+        <v>99999</v>
+      </c>
+      <c r="I77" s="6">
+        <v>0</v>
+      </c>
+      <c r="J77" s="6">
+        <v>6</v>
+      </c>
+      <c r="K77" s="8">
+        <v>1200</v>
+      </c>
+      <c r="L77" s="9">
         <v>4015</v>
       </c>
-      <c r="M77" s="3">
+      <c r="M77" s="9">
         <v>1</v>
       </c>
     </row>
@@ -17907,13 +18452,13 @@
         <v>50000073</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>665</v>
+        <v>684</v>
       </c>
       <c r="E78" s="2">
         <v>5</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>666</v>
+        <v>685</v>
       </c>
       <c r="G78" s="2">
         <v>1</v>
@@ -17926,6 +18471,9 @@
       </c>
       <c r="J78" s="2">
         <v>6</v>
+      </c>
+      <c r="K78" s="8">
+        <v>1250</v>
       </c>
       <c r="L78" s="3">
         <v>4015</v>
@@ -17939,13 +18487,13 @@
         <v>50000074</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>667</v>
+        <v>686</v>
       </c>
       <c r="E79" s="2">
         <v>5</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>668</v>
+        <v>687</v>
       </c>
       <c r="G79" s="2">
         <v>1</v>
@@ -17958,6 +18506,9 @@
       </c>
       <c r="J79" s="2">
         <v>6</v>
+      </c>
+      <c r="K79" s="8">
+        <v>1250</v>
       </c>
       <c r="L79" s="3">
         <v>4015</v>
@@ -17971,13 +18522,13 @@
         <v>50000075</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>669</v>
+        <v>688</v>
       </c>
       <c r="E80" s="2">
         <v>5</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>670</v>
+        <v>689</v>
       </c>
       <c r="G80" s="2">
         <v>1</v>
@@ -17990,6 +18541,9 @@
       </c>
       <c r="J80" s="2">
         <v>6</v>
+      </c>
+      <c r="K80" s="8">
+        <v>1250</v>
       </c>
       <c r="L80" s="3">
         <v>4015</v>
@@ -18003,13 +18557,13 @@
         <v>50000076</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>671</v>
+        <v>690</v>
       </c>
       <c r="E81" s="2">
         <v>5</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>672</v>
+        <v>691</v>
       </c>
       <c r="G81" s="2">
         <v>1</v>
@@ -18022,6 +18576,9 @@
       </c>
       <c r="J81" s="2">
         <v>6</v>
+      </c>
+      <c r="K81" s="8">
+        <v>1250</v>
       </c>
       <c r="L81" s="3">
         <v>4015</v>
@@ -18035,13 +18592,13 @@
         <v>50000077</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>673</v>
+        <v>692</v>
       </c>
       <c r="E82" s="2">
         <v>5</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>674</v>
+        <v>693</v>
       </c>
       <c r="G82" s="2">
         <v>1</v>
@@ -18054,6 +18611,9 @@
       </c>
       <c r="J82" s="2">
         <v>6</v>
+      </c>
+      <c r="K82" s="8">
+        <v>1250</v>
       </c>
       <c r="L82" s="3">
         <v>4015</v>
@@ -18067,13 +18627,13 @@
         <v>50000078</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>675</v>
+        <v>694</v>
       </c>
       <c r="E83" s="2">
         <v>5</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>676</v>
+        <v>695</v>
       </c>
       <c r="G83" s="2">
         <v>1</v>
@@ -18086,6 +18646,9 @@
       </c>
       <c r="J83" s="2">
         <v>6</v>
+      </c>
+      <c r="K83" s="8">
+        <v>1250</v>
       </c>
       <c r="L83" s="3">
         <v>4015</v>
@@ -18099,13 +18662,13 @@
         <v>50000079</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>677</v>
+        <v>696</v>
       </c>
       <c r="E84" s="2">
         <v>5</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>678</v>
+        <v>697</v>
       </c>
       <c r="G84" s="2">
         <v>1</v>
@@ -18118,6 +18681,9 @@
       </c>
       <c r="J84" s="2">
         <v>6</v>
+      </c>
+      <c r="K84" s="8">
+        <v>1250</v>
       </c>
       <c r="L84" s="3">
         <v>4015</v>
@@ -18126,35 +18692,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" customHeight="1" spans="3:13">
-      <c r="C85" s="2">
+    <row r="85" s="7" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C85" s="6">
         <v>50000080</v>
       </c>
-      <c r="D85" s="3" t="s">
-        <v>679</v>
-      </c>
-      <c r="E85" s="2">
-        <v>5</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>680</v>
-      </c>
-      <c r="G85" s="2">
-        <v>1</v>
-      </c>
-      <c r="H85" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I85" s="2">
-        <v>0</v>
-      </c>
-      <c r="J85" s="2">
-        <v>6</v>
-      </c>
-      <c r="L85" s="3">
+      <c r="D85" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="E85" s="6">
+        <v>5</v>
+      </c>
+      <c r="F85" s="6" t="s">
+        <v>699</v>
+      </c>
+      <c r="G85" s="6">
+        <v>1</v>
+      </c>
+      <c r="H85" s="6">
+        <v>99999</v>
+      </c>
+      <c r="I85" s="6">
+        <v>0</v>
+      </c>
+      <c r="J85" s="6">
+        <v>6</v>
+      </c>
+      <c r="K85" s="8">
+        <v>1250</v>
+      </c>
+      <c r="L85" s="9">
         <v>4015</v>
       </c>
-      <c r="M85" s="3">
+      <c r="M85" s="9">
         <v>1</v>
       </c>
     </row>
@@ -18163,13 +18732,13 @@
         <v>50000081</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>681</v>
+        <v>700</v>
       </c>
       <c r="E86" s="2">
         <v>5</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>682</v>
+        <v>701</v>
       </c>
       <c r="G86" s="2">
         <v>1</v>
@@ -18182,6 +18751,9 @@
       </c>
       <c r="J86" s="2">
         <v>6</v>
+      </c>
+      <c r="K86" s="8">
+        <v>1300</v>
       </c>
       <c r="L86" s="3">
         <v>4015</v>
@@ -18195,13 +18767,13 @@
         <v>50000082</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>683</v>
+        <v>702</v>
       </c>
       <c r="E87" s="2">
         <v>5</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>684</v>
+        <v>703</v>
       </c>
       <c r="G87" s="2">
         <v>1</v>
@@ -18214,6 +18786,9 @@
       </c>
       <c r="J87" s="2">
         <v>6</v>
+      </c>
+      <c r="K87" s="8">
+        <v>1300</v>
       </c>
       <c r="L87" s="3">
         <v>4015</v>
@@ -18227,13 +18802,13 @@
         <v>50000083</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>685</v>
+        <v>704</v>
       </c>
       <c r="E88" s="2">
         <v>5</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>686</v>
+        <v>705</v>
       </c>
       <c r="G88" s="2">
         <v>1</v>
@@ -18246,6 +18821,9 @@
       </c>
       <c r="J88" s="2">
         <v>6</v>
+      </c>
+      <c r="K88" s="8">
+        <v>1300</v>
       </c>
       <c r="L88" s="3">
         <v>4015</v>
@@ -18259,13 +18837,13 @@
         <v>50000084</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>687</v>
+        <v>706</v>
       </c>
       <c r="E89" s="2">
         <v>5</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>688</v>
+        <v>707</v>
       </c>
       <c r="G89" s="2">
         <v>1</v>
@@ -18278,6 +18856,9 @@
       </c>
       <c r="J89" s="2">
         <v>6</v>
+      </c>
+      <c r="K89" s="8">
+        <v>1300</v>
       </c>
       <c r="L89" s="3">
         <v>4015</v>
@@ -18291,13 +18872,13 @@
         <v>50000085</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>689</v>
+        <v>708</v>
       </c>
       <c r="E90" s="2">
         <v>5</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>690</v>
+        <v>709</v>
       </c>
       <c r="G90" s="2">
         <v>1</v>
@@ -18310,6 +18891,9 @@
       </c>
       <c r="J90" s="2">
         <v>6</v>
+      </c>
+      <c r="K90" s="8">
+        <v>1300</v>
       </c>
       <c r="L90" s="3">
         <v>4015</v>
@@ -18323,13 +18907,13 @@
         <v>50000086</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>691</v>
+        <v>710</v>
       </c>
       <c r="E91" s="2">
         <v>5</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>692</v>
+        <v>711</v>
       </c>
       <c r="G91" s="2">
         <v>1</v>
@@ -18342,6 +18926,9 @@
       </c>
       <c r="J91" s="2">
         <v>6</v>
+      </c>
+      <c r="K91" s="8">
+        <v>1300</v>
       </c>
       <c r="L91" s="3">
         <v>4015</v>
@@ -18355,13 +18942,13 @@
         <v>50000087</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>693</v>
+        <v>712</v>
       </c>
       <c r="E92" s="2">
         <v>5</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>694</v>
+        <v>713</v>
       </c>
       <c r="G92" s="2">
         <v>1</v>
@@ -18374,6 +18961,9 @@
       </c>
       <c r="J92" s="2">
         <v>6</v>
+      </c>
+      <c r="K92" s="8">
+        <v>1300</v>
       </c>
       <c r="L92" s="3">
         <v>4015</v>
@@ -18382,35 +18972,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" customHeight="1" spans="3:13">
-      <c r="C93" s="2">
+    <row r="93" s="7" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C93" s="6">
         <v>50000088</v>
       </c>
-      <c r="D93" s="3" t="s">
-        <v>695</v>
-      </c>
-      <c r="E93" s="2">
-        <v>5</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>696</v>
-      </c>
-      <c r="G93" s="2">
-        <v>1</v>
-      </c>
-      <c r="H93" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I93" s="2">
-        <v>0</v>
-      </c>
-      <c r="J93" s="2">
-        <v>6</v>
-      </c>
-      <c r="L93" s="3">
+      <c r="D93" s="9" t="s">
+        <v>714</v>
+      </c>
+      <c r="E93" s="6">
+        <v>5</v>
+      </c>
+      <c r="F93" s="6" t="s">
+        <v>715</v>
+      </c>
+      <c r="G93" s="6">
+        <v>1</v>
+      </c>
+      <c r="H93" s="6">
+        <v>99999</v>
+      </c>
+      <c r="I93" s="6">
+        <v>0</v>
+      </c>
+      <c r="J93" s="6">
+        <v>6</v>
+      </c>
+      <c r="K93" s="8">
+        <v>1300</v>
+      </c>
+      <c r="L93" s="9">
         <v>4015</v>
       </c>
-      <c r="M93" s="3">
+      <c r="M93" s="9">
         <v>1</v>
       </c>
     </row>
@@ -18419,13 +19012,13 @@
         <v>50000089</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>697</v>
+        <v>716</v>
       </c>
       <c r="E94" s="2">
         <v>5</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>698</v>
+        <v>717</v>
       </c>
       <c r="G94" s="2">
         <v>1</v>
@@ -18438,6 +19031,9 @@
       </c>
       <c r="J94" s="2">
         <v>6</v>
+      </c>
+      <c r="K94" s="8">
+        <v>1350</v>
       </c>
       <c r="L94" s="3">
         <v>4015</v>
@@ -18451,13 +19047,13 @@
         <v>50000090</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>699</v>
+        <v>718</v>
       </c>
       <c r="E95" s="2">
         <v>5</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>700</v>
+        <v>719</v>
       </c>
       <c r="G95" s="2">
         <v>1</v>
@@ -18470,6 +19066,9 @@
       </c>
       <c r="J95" s="2">
         <v>6</v>
+      </c>
+      <c r="K95" s="8">
+        <v>1350</v>
       </c>
       <c r="L95" s="3">
         <v>4015</v>
@@ -18483,13 +19082,13 @@
         <v>50000091</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>701</v>
+        <v>720</v>
       </c>
       <c r="E96" s="2">
         <v>5</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>702</v>
+        <v>721</v>
       </c>
       <c r="G96" s="2">
         <v>1</v>
@@ -18502,6 +19101,9 @@
       </c>
       <c r="J96" s="2">
         <v>6</v>
+      </c>
+      <c r="K96" s="8">
+        <v>1350</v>
       </c>
       <c r="L96" s="3">
         <v>4015</v>
@@ -18515,13 +19117,13 @@
         <v>50000092</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>703</v>
+        <v>722</v>
       </c>
       <c r="E97" s="2">
         <v>5</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>704</v>
+        <v>723</v>
       </c>
       <c r="G97" s="2">
         <v>1</v>
@@ -18534,6 +19136,9 @@
       </c>
       <c r="J97" s="2">
         <v>6</v>
+      </c>
+      <c r="K97" s="8">
+        <v>1350</v>
       </c>
       <c r="L97" s="3">
         <v>4015</v>
@@ -18547,13 +19152,13 @@
         <v>50000093</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>705</v>
+        <v>724</v>
       </c>
       <c r="E98" s="2">
         <v>5</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>706</v>
+        <v>725</v>
       </c>
       <c r="G98" s="2">
         <v>1</v>
@@ -18566,6 +19171,9 @@
       </c>
       <c r="J98" s="2">
         <v>6</v>
+      </c>
+      <c r="K98" s="8">
+        <v>1350</v>
       </c>
       <c r="L98" s="3">
         <v>4015</v>
@@ -18579,13 +19187,13 @@
         <v>50000094</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>707</v>
+        <v>726</v>
       </c>
       <c r="E99" s="2">
         <v>5</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>708</v>
+        <v>727</v>
       </c>
       <c r="G99" s="2">
         <v>1</v>
@@ -18598,6 +19206,9 @@
       </c>
       <c r="J99" s="2">
         <v>6</v>
+      </c>
+      <c r="K99" s="8">
+        <v>1350</v>
       </c>
       <c r="L99" s="3">
         <v>4015</v>
@@ -18611,13 +19222,13 @@
         <v>50000095</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>709</v>
+        <v>728</v>
       </c>
       <c r="E100" s="2">
         <v>5</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>710</v>
+        <v>729</v>
       </c>
       <c r="G100" s="2">
         <v>1</v>
@@ -18630,6 +19241,9 @@
       </c>
       <c r="J100" s="2">
         <v>6</v>
+      </c>
+      <c r="K100" s="8">
+        <v>1350</v>
       </c>
       <c r="L100" s="3">
         <v>4015</v>
@@ -18638,35 +19252,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" customHeight="1" spans="3:13">
-      <c r="C101" s="2">
+    <row r="101" s="7" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C101" s="6">
         <v>50000096</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>711</v>
-      </c>
-      <c r="E101" s="2">
-        <v>5</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>712</v>
-      </c>
-      <c r="G101" s="2">
-        <v>1</v>
-      </c>
-      <c r="H101" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I101" s="2">
-        <v>0</v>
-      </c>
-      <c r="J101" s="2">
-        <v>6</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="D101" s="9" t="s">
+        <v>730</v>
+      </c>
+      <c r="E101" s="6">
+        <v>5</v>
+      </c>
+      <c r="F101" s="6" t="s">
+        <v>731</v>
+      </c>
+      <c r="G101" s="6">
+        <v>1</v>
+      </c>
+      <c r="H101" s="6">
+        <v>99999</v>
+      </c>
+      <c r="I101" s="6">
+        <v>0</v>
+      </c>
+      <c r="J101" s="6">
+        <v>6</v>
+      </c>
+      <c r="K101" s="8">
+        <v>1350</v>
+      </c>
+      <c r="L101" s="9">
         <v>4015</v>
       </c>
-      <c r="M101" s="3">
+      <c r="M101" s="9">
         <v>1</v>
       </c>
     </row>
@@ -18675,13 +19292,13 @@
         <v>50000097</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>713</v>
+        <v>732</v>
       </c>
       <c r="E102" s="2">
         <v>5</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>714</v>
+        <v>733</v>
       </c>
       <c r="G102" s="2">
         <v>1</v>
@@ -18694,6 +19311,9 @@
       </c>
       <c r="J102" s="2">
         <v>6</v>
+      </c>
+      <c r="K102" s="8">
+        <v>1400</v>
       </c>
       <c r="L102" s="3">
         <v>4015</v>
@@ -18707,13 +19327,13 @@
         <v>50000098</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>715</v>
+        <v>734</v>
       </c>
       <c r="E103" s="2">
         <v>5</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>716</v>
+        <v>735</v>
       </c>
       <c r="G103" s="2">
         <v>1</v>
@@ -18726,6 +19346,9 @@
       </c>
       <c r="J103" s="2">
         <v>6</v>
+      </c>
+      <c r="K103" s="8">
+        <v>1400</v>
       </c>
       <c r="L103" s="3">
         <v>4015</v>
@@ -18739,13 +19362,13 @@
         <v>50000099</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>717</v>
+        <v>736</v>
       </c>
       <c r="E104" s="2">
         <v>5</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>718</v>
+        <v>737</v>
       </c>
       <c r="G104" s="2">
         <v>1</v>
@@ -18758,6 +19381,9 @@
       </c>
       <c r="J104" s="2">
         <v>6</v>
+      </c>
+      <c r="K104" s="8">
+        <v>1400</v>
       </c>
       <c r="L104" s="3">
         <v>4015</v>
@@ -18771,13 +19397,13 @@
         <v>50000100</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>719</v>
+        <v>738</v>
       </c>
       <c r="E105" s="2">
         <v>5</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>720</v>
+        <v>739</v>
       </c>
       <c r="G105" s="2">
         <v>1</v>
@@ -18790,6 +19416,9 @@
       </c>
       <c r="J105" s="2">
         <v>6</v>
+      </c>
+      <c r="K105" s="8">
+        <v>1400</v>
       </c>
       <c r="L105" s="3">
         <v>4015</v>
@@ -18803,13 +19432,13 @@
         <v>50000101</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>721</v>
+        <v>740</v>
       </c>
       <c r="E106" s="2">
         <v>5</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>722</v>
+        <v>741</v>
       </c>
       <c r="G106" s="2">
         <v>1</v>
@@ -18822,6 +19451,9 @@
       </c>
       <c r="J106" s="2">
         <v>6</v>
+      </c>
+      <c r="K106" s="8">
+        <v>1400</v>
       </c>
       <c r="L106" s="3">
         <v>4015</v>
@@ -18835,13 +19467,13 @@
         <v>50000102</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>723</v>
+        <v>742</v>
       </c>
       <c r="E107" s="2">
         <v>5</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>724</v>
+        <v>743</v>
       </c>
       <c r="G107" s="2">
         <v>1</v>
@@ -18854,6 +19486,9 @@
       </c>
       <c r="J107" s="2">
         <v>6</v>
+      </c>
+      <c r="K107" s="8">
+        <v>1400</v>
       </c>
       <c r="L107" s="3">
         <v>4015</v>
@@ -18867,13 +19502,13 @@
         <v>50000103</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>725</v>
+        <v>744</v>
       </c>
       <c r="E108" s="2">
         <v>5</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>726</v>
+        <v>745</v>
       </c>
       <c r="G108" s="2">
         <v>1</v>
@@ -18886,6 +19521,9 @@
       </c>
       <c r="J108" s="2">
         <v>6</v>
+      </c>
+      <c r="K108" s="8">
+        <v>1400</v>
       </c>
       <c r="L108" s="3">
         <v>4015</v>
@@ -18894,35 +19532,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" customHeight="1" spans="3:13">
-      <c r="C109" s="2">
+    <row r="109" s="7" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C109" s="6">
         <v>50000104</v>
       </c>
-      <c r="D109" s="3" t="s">
-        <v>727</v>
-      </c>
-      <c r="E109" s="2">
-        <v>5</v>
-      </c>
-      <c r="F109" s="2" t="s">
-        <v>728</v>
-      </c>
-      <c r="G109" s="2">
-        <v>1</v>
-      </c>
-      <c r="H109" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I109" s="2">
-        <v>0</v>
-      </c>
-      <c r="J109" s="2">
-        <v>6</v>
-      </c>
-      <c r="L109" s="3">
+      <c r="D109" s="9" t="s">
+        <v>746</v>
+      </c>
+      <c r="E109" s="6">
+        <v>5</v>
+      </c>
+      <c r="F109" s="6" t="s">
+        <v>747</v>
+      </c>
+      <c r="G109" s="6">
+        <v>1</v>
+      </c>
+      <c r="H109" s="6">
+        <v>99999</v>
+      </c>
+      <c r="I109" s="6">
+        <v>0</v>
+      </c>
+      <c r="J109" s="6">
+        <v>6</v>
+      </c>
+      <c r="K109" s="7">
+        <v>1400</v>
+      </c>
+      <c r="L109" s="9">
         <v>4015</v>
       </c>
-      <c r="M109" s="3">
+      <c r="M109" s="9">
         <v>1</v>
       </c>
     </row>
@@ -19070,13 +19711,13 @@
         <v>180001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>729</v>
+        <v>748</v>
       </c>
       <c r="E6" s="2">
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>730</v>
+        <v>749</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -19096,13 +19737,13 @@
         <v>180002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>731</v>
+        <v>750</v>
       </c>
       <c r="E7" s="2">
         <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>730</v>
+        <v>749</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -19122,13 +19763,13 @@
         <v>180003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>732</v>
+        <v>751</v>
       </c>
       <c r="E8" s="2">
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>730</v>
+        <v>749</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -19148,13 +19789,13 @@
         <v>180004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>733</v>
+        <v>752</v>
       </c>
       <c r="E9" s="2">
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>730</v>
+        <v>749</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -19174,13 +19815,13 @@
         <v>180005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>734</v>
+        <v>753</v>
       </c>
       <c r="E10" s="2">
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>730</v>
+        <v>749</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -19200,13 +19841,13 @@
         <v>180006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>735</v>
+        <v>754</v>
       </c>
       <c r="E11" s="2">
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>730</v>
+        <v>749</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -19228,13 +19869,13 @@
         <v>180007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>736</v>
+        <v>755</v>
       </c>
       <c r="E12" s="2">
         <v>18</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>730</v>
+        <v>749</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -19256,13 +19897,13 @@
         <v>180008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>737</v>
+        <v>756</v>
       </c>
       <c r="E13" s="2">
         <v>18</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>730</v>
+        <v>749</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -19284,13 +19925,13 @@
         <v>180009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>738</v>
+        <v>757</v>
       </c>
       <c r="E14" s="2">
         <v>18</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>730</v>
+        <v>749</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -19312,13 +19953,13 @@
         <v>180010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>739</v>
+        <v>758</v>
       </c>
       <c r="E15" s="2">
         <v>18</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>730</v>
+        <v>749</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -19340,13 +19981,13 @@
         <v>180011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>740</v>
+        <v>759</v>
       </c>
       <c r="E16" s="2">
         <v>18</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>730</v>
+        <v>749</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -19368,13 +20009,13 @@
         <v>180012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>741</v>
+        <v>760</v>
       </c>
       <c r="E17" s="2">
         <v>18</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>730</v>
+        <v>749</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -19396,13 +20037,13 @@
         <v>180013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>742</v>
+        <v>761</v>
       </c>
       <c r="E18" s="2">
         <v>18</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>730</v>
+        <v>749</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -19424,13 +20065,13 @@
         <v>180014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>743</v>
+        <v>762</v>
       </c>
       <c r="E19" s="2">
         <v>18</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>730</v>
+        <v>749</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -19452,13 +20093,13 @@
         <v>180015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>744</v>
+        <v>763</v>
       </c>
       <c r="E20" s="2">
         <v>18</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>730</v>
+        <v>749</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -19480,13 +20121,13 @@
         <v>180016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>745</v>
+        <v>764</v>
       </c>
       <c r="E21" s="2">
         <v>18</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>730</v>
+        <v>749</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -19508,13 +20149,13 @@
         <v>180017</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>746</v>
+        <v>765</v>
       </c>
       <c r="E22" s="2">
         <v>18</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>730</v>
+        <v>749</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -19536,13 +20177,13 @@
         <v>180018</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>747</v>
+        <v>766</v>
       </c>
       <c r="E23" s="2">
         <v>18</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>730</v>
+        <v>749</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -19564,13 +20205,13 @@
         <v>180019</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>748</v>
+        <v>767</v>
       </c>
       <c r="E24" s="2">
         <v>18</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>730</v>
+        <v>749</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -19592,13 +20233,13 @@
         <v>180020</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>749</v>
+        <v>768</v>
       </c>
       <c r="E25" s="2">
         <v>18</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>730</v>
+        <v>749</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -19620,13 +20261,13 @@
         <v>180021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>750</v>
+        <v>769</v>
       </c>
       <c r="E26" s="2">
         <v>18</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>730</v>
+        <v>749</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -19648,13 +20289,13 @@
         <v>180022</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>751</v>
+        <v>770</v>
       </c>
       <c r="E27" s="2">
         <v>18</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>730</v>
+        <v>749</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -19681,13 +20322,13 @@
         <v>180030</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>752</v>
+        <v>771</v>
       </c>
       <c r="E29" s="2">
         <v>18</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>730</v>
+        <v>749</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -19709,13 +20350,13 @@
         <v>180031</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>753</v>
+        <v>772</v>
       </c>
       <c r="E30" s="2">
         <v>18</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>730</v>
+        <v>749</v>
       </c>
       <c r="G30" s="3">
         <v>1</v>
@@ -19735,13 +20376,13 @@
         <v>180032</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>754</v>
+        <v>773</v>
       </c>
       <c r="E31" s="2">
         <v>18</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>730</v>
+        <v>749</v>
       </c>
       <c r="G31" s="3">
         <v>1</v>
@@ -19761,13 +20402,13 @@
         <v>180033</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>755</v>
+        <v>774</v>
       </c>
       <c r="E32" s="2">
         <v>18</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>730</v>
+        <v>749</v>
       </c>
       <c r="G32" s="3">
         <v>1</v>
@@ -19787,13 +20428,13 @@
         <v>180034</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>756</v>
+        <v>775</v>
       </c>
       <c r="E33" s="2">
         <v>18</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>730</v>
+        <v>749</v>
       </c>
       <c r="G33" s="3">
         <v>1</v>
@@ -19815,13 +20456,13 @@
         <v>180035</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>757</v>
+        <v>776</v>
       </c>
       <c r="E34" s="2">
         <v>18</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>730</v>
+        <v>749</v>
       </c>
       <c r="G34" s="3">
         <v>1</v>
@@ -19843,13 +20484,13 @@
         <v>180036</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>758</v>
+        <v>777</v>
       </c>
       <c r="E35" s="2">
         <v>18</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>730</v>
+        <v>749</v>
       </c>
       <c r="G35" s="3">
         <v>1</v>
@@ -19871,13 +20512,13 @@
         <v>180037</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>759</v>
+        <v>778</v>
       </c>
       <c r="E36" s="2">
         <v>18</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>730</v>
+        <v>749</v>
       </c>
       <c r="G36" s="3">
         <v>1</v>
@@ -20038,13 +20679,13 @@
         <v>190001</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>760</v>
+        <v>779</v>
       </c>
       <c r="E6" s="2">
         <v>19</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>761</v>
+        <v>780</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -20064,13 +20705,13 @@
         <v>190002</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>762</v>
+        <v>781</v>
       </c>
       <c r="E7" s="2">
         <v>19</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>761</v>
+        <v>780</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -20090,13 +20731,13 @@
         <v>190003</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>763</v>
+        <v>782</v>
       </c>
       <c r="E8" s="2">
         <v>19</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>761</v>
+        <v>780</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -20116,13 +20757,13 @@
         <v>190004</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>764</v>
+        <v>783</v>
       </c>
       <c r="E9" s="2">
         <v>19</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>761</v>
+        <v>780</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -20142,13 +20783,13 @@
         <v>190005</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>765</v>
+        <v>784</v>
       </c>
       <c r="E10" s="2">
         <v>19</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>761</v>
+        <v>780</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -20168,13 +20809,13 @@
         <v>190006</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>766</v>
+        <v>785</v>
       </c>
       <c r="E11" s="2">
         <v>19</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>761</v>
+        <v>780</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -344,7 +344,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="786">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1463" uniqueCount="802">
   <si>
     <t>_Id</t>
   </si>
@@ -2588,6 +2588,54 @@
   </si>
   <si>
     <t>红色靴子升级十四阶的材料</t>
+  </si>
+  <si>
+    <t>十五阶武器升阶石</t>
+  </si>
+  <si>
+    <t>红色武器升级十五阶的材料</t>
+  </si>
+  <si>
+    <t>十五阶衣服升阶石</t>
+  </si>
+  <si>
+    <t>红色衣服升级十五阶的材料</t>
+  </si>
+  <si>
+    <t>十五阶项链升阶石</t>
+  </si>
+  <si>
+    <t>红色项链升级十五阶的材料</t>
+  </si>
+  <si>
+    <t>十五阶头盔升阶石</t>
+  </si>
+  <si>
+    <t>红色头盔升级十五阶的材料</t>
+  </si>
+  <si>
+    <t>十五阶手镯升阶石</t>
+  </si>
+  <si>
+    <t>红色手镯升级十五阶的材料</t>
+  </si>
+  <si>
+    <t>十五阶戒指升阶石</t>
+  </si>
+  <si>
+    <t>红色戒指升级十五阶的材料</t>
+  </si>
+  <si>
+    <t>十五阶腰带升阶石</t>
+  </si>
+  <si>
+    <t>红色腰带升级十五阶的材料</t>
+  </si>
+  <si>
+    <t>十五阶靴子升阶石</t>
+  </si>
+  <si>
+    <t>红色靴子升级十五阶的材料</t>
   </si>
   <si>
     <t>BOSS杀手</t>
@@ -3396,7 +3444,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3408,10 +3456,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -3860,7 +3906,7 @@
       <c r="C6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="14" t="s">
         <v>23</v>
       </c>
       <c r="E6" s="3" t="s">
@@ -3895,7 +3941,7 @@
       <c r="C7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="14" t="s">
         <v>30</v>
       </c>
       <c r="E7" s="3" t="s">
@@ -3930,7 +3976,7 @@
       <c r="C8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="14" t="s">
         <v>34</v>
       </c>
       <c r="E8" s="3" t="s">
@@ -3965,7 +4011,7 @@
       <c r="C9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="14" t="s">
         <v>38</v>
       </c>
       <c r="E9" s="3" t="s">
@@ -4000,7 +4046,7 @@
       <c r="C10" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="14" t="s">
         <v>43</v>
       </c>
       <c r="E10" s="3" t="s">
@@ -4035,7 +4081,7 @@
       <c r="C11" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="14" t="s">
         <v>46</v>
       </c>
       <c r="E11" s="3" t="s">
@@ -4070,7 +4116,7 @@
       <c r="C12" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="14" t="s">
         <v>50</v>
       </c>
       <c r="E12" s="3" t="s">
@@ -4102,10 +4148,10 @@
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:13">
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="14" t="s">
         <v>54</v>
       </c>
       <c r="E13" s="3" t="s">
@@ -4120,7 +4166,7 @@
       <c r="H13" s="3">
         <v>99999999</v>
       </c>
-      <c r="I13" s="17" t="s">
+      <c r="I13" s="15" t="s">
         <v>56</v>
       </c>
       <c r="J13" s="3">
@@ -4137,10 +4183,10 @@
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:13">
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="14" t="s">
         <v>58</v>
       </c>
       <c r="E14" s="3" t="s">
@@ -4155,7 +4201,7 @@
       <c r="H14" s="3">
         <v>99999999</v>
       </c>
-      <c r="I14" s="17" t="s">
+      <c r="I14" s="15" t="s">
         <v>56</v>
       </c>
       <c r="J14" s="3">
@@ -4172,10 +4218,10 @@
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:13">
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="14" t="s">
         <v>61</v>
       </c>
       <c r="E15" s="3" t="s">
@@ -4190,7 +4236,7 @@
       <c r="H15" s="3">
         <v>99999999</v>
       </c>
-      <c r="I15" s="17" t="s">
+      <c r="I15" s="15" t="s">
         <v>56</v>
       </c>
       <c r="J15" s="3">
@@ -4207,10 +4253,10 @@
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:13">
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="14" t="s">
         <v>64</v>
       </c>
       <c r="E16" s="3" t="s">
@@ -4225,7 +4271,7 @@
       <c r="H16" s="3">
         <v>99999999</v>
       </c>
-      <c r="I16" s="17" t="s">
+      <c r="I16" s="15" t="s">
         <v>56</v>
       </c>
       <c r="J16" s="3">
@@ -4245,7 +4291,7 @@
       <c r="C18" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="14" t="s">
         <v>67</v>
       </c>
       <c r="E18" s="3" t="s">
@@ -4280,7 +4326,7 @@
       <c r="C19" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D19" s="16" t="s">
+      <c r="D19" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E19" s="3" t="s">
@@ -4315,7 +4361,7 @@
       <c r="C20" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="14" t="s">
         <v>73</v>
       </c>
       <c r="E20" s="3" t="s">
@@ -4350,7 +4396,7 @@
       <c r="C21" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="16" t="s">
+      <c r="D21" s="14" t="s">
         <v>76</v>
       </c>
       <c r="E21" s="3" t="s">
@@ -4385,7 +4431,7 @@
       <c r="C22" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="14" t="s">
         <v>79</v>
       </c>
       <c r="E22" s="3" t="s">
@@ -4420,7 +4466,7 @@
       <c r="C23" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D23" s="16" t="s">
+      <c r="D23" s="14" t="s">
         <v>82</v>
       </c>
       <c r="E23" s="3" t="s">
@@ -4455,7 +4501,7 @@
       <c r="C24" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="16" t="s">
+      <c r="D24" s="14" t="s">
         <v>85</v>
       </c>
       <c r="E24" s="3" t="s">
@@ -4487,10 +4533,10 @@
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:13">
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="D25" s="16" t="s">
+      <c r="D25" s="14" t="s">
         <v>88</v>
       </c>
       <c r="E25" s="3" t="s">
@@ -4505,7 +4551,7 @@
       <c r="H25" s="3">
         <v>99999999</v>
       </c>
-      <c r="I25" s="17" t="s">
+      <c r="I25" s="15" t="s">
         <v>56</v>
       </c>
       <c r="J25" s="3">
@@ -4522,10 +4568,10 @@
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:13">
-      <c r="C26" s="17" t="s">
+      <c r="C26" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="16" t="s">
+      <c r="D26" s="14" t="s">
         <v>91</v>
       </c>
       <c r="E26" s="3" t="s">
@@ -4540,7 +4586,7 @@
       <c r="H26" s="3">
         <v>99999999</v>
       </c>
-      <c r="I26" s="17" t="s">
+      <c r="I26" s="15" t="s">
         <v>56</v>
       </c>
       <c r="J26" s="3">
@@ -4557,10 +4603,10 @@
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:13">
-      <c r="C27" s="17" t="s">
+      <c r="C27" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="D27" s="16" t="s">
+      <c r="D27" s="14" t="s">
         <v>94</v>
       </c>
       <c r="E27" s="3" t="s">
@@ -4575,7 +4621,7 @@
       <c r="H27" s="3">
         <v>99999999</v>
       </c>
-      <c r="I27" s="17" t="s">
+      <c r="I27" s="15" t="s">
         <v>56</v>
       </c>
       <c r="J27" s="3">
@@ -4592,10 +4638,10 @@
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:13">
-      <c r="C28" s="17" t="s">
+      <c r="C28" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D28" s="16" t="s">
+      <c r="D28" s="14" t="s">
         <v>97</v>
       </c>
       <c r="E28" s="3" t="s">
@@ -4610,7 +4656,7 @@
       <c r="H28" s="3">
         <v>99999999</v>
       </c>
-      <c r="I28" s="17" t="s">
+      <c r="I28" s="15" t="s">
         <v>56</v>
       </c>
       <c r="J28" s="3">
@@ -4630,7 +4676,7 @@
       <c r="C30" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D30" s="16" t="s">
+      <c r="D30" s="14" t="s">
         <v>100</v>
       </c>
       <c r="E30" s="3" t="s">
@@ -4665,7 +4711,7 @@
       <c r="C31" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D31" s="16" t="s">
+      <c r="D31" s="14" t="s">
         <v>103</v>
       </c>
       <c r="E31" s="3" t="s">
@@ -4700,7 +4746,7 @@
       <c r="C32" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D32" s="16" t="s">
+      <c r="D32" s="14" t="s">
         <v>106</v>
       </c>
       <c r="E32" s="3" t="s">
@@ -4735,7 +4781,7 @@
       <c r="C33" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D33" s="16" t="s">
+      <c r="D33" s="14" t="s">
         <v>109</v>
       </c>
       <c r="E33" s="3" t="s">
@@ -4770,7 +4816,7 @@
       <c r="C34" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D34" s="16" t="s">
+      <c r="D34" s="14" t="s">
         <v>112</v>
       </c>
       <c r="E34" s="3" t="s">
@@ -4805,7 +4851,7 @@
       <c r="C35" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D35" s="16" t="s">
+      <c r="D35" s="14" t="s">
         <v>115</v>
       </c>
       <c r="E35" s="3" t="s">
@@ -4840,7 +4886,7 @@
       <c r="C36" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D36" s="16" t="s">
+      <c r="D36" s="14" t="s">
         <v>118</v>
       </c>
       <c r="E36" s="3" t="s">
@@ -4872,10 +4918,10 @@
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:13">
-      <c r="C37" s="17" t="s">
+      <c r="C37" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="D37" s="16" t="s">
+      <c r="D37" s="14" t="s">
         <v>121</v>
       </c>
       <c r="E37" s="3" t="s">
@@ -4890,7 +4936,7 @@
       <c r="H37" s="3">
         <v>99999999</v>
       </c>
-      <c r="I37" s="17" t="s">
+      <c r="I37" s="15" t="s">
         <v>56</v>
       </c>
       <c r="J37" s="3">
@@ -4907,10 +4953,10 @@
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:13">
-      <c r="C38" s="17" t="s">
+      <c r="C38" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="D38" s="16" t="s">
+      <c r="D38" s="14" t="s">
         <v>124</v>
       </c>
       <c r="E38" s="3" t="s">
@@ -4925,7 +4971,7 @@
       <c r="H38" s="3">
         <v>99999999</v>
       </c>
-      <c r="I38" s="17" t="s">
+      <c r="I38" s="15" t="s">
         <v>56</v>
       </c>
       <c r="J38" s="3">
@@ -4942,10 +4988,10 @@
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:13">
-      <c r="C39" s="17" t="s">
+      <c r="C39" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="D39" s="16" t="s">
+      <c r="D39" s="14" t="s">
         <v>127</v>
       </c>
       <c r="E39" s="3" t="s">
@@ -4960,7 +5006,7 @@
       <c r="H39" s="3">
         <v>99999999</v>
       </c>
-      <c r="I39" s="17" t="s">
+      <c r="I39" s="15" t="s">
         <v>56</v>
       </c>
       <c r="J39" s="3">
@@ -4977,10 +5023,10 @@
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:13">
-      <c r="C40" s="17" t="s">
+      <c r="C40" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="D40" s="16" t="s">
+      <c r="D40" s="14" t="s">
         <v>130</v>
       </c>
       <c r="E40" s="3" t="s">
@@ -4995,7 +5041,7 @@
       <c r="H40" s="3">
         <v>99999999</v>
       </c>
-      <c r="I40" s="17" t="s">
+      <c r="I40" s="15" t="s">
         <v>56</v>
       </c>
       <c r="J40" s="3">
@@ -7138,7 +7184,7 @@
       <c r="C74" s="3">
         <v>8101</v>
       </c>
-      <c r="D74" s="15" t="s">
+      <c r="D74" s="13" t="s">
         <v>238</v>
       </c>
       <c r="E74" s="3">
@@ -7170,7 +7216,7 @@
       <c r="C75" s="3">
         <v>8102</v>
       </c>
-      <c r="D75" s="15" t="s">
+      <c r="D75" s="13" t="s">
         <v>240</v>
       </c>
       <c r="E75" s="3">
@@ -7202,7 +7248,7 @@
       <c r="C76" s="3">
         <v>8103</v>
       </c>
-      <c r="D76" s="15" t="s">
+      <c r="D76" s="13" t="s">
         <v>241</v>
       </c>
       <c r="E76" s="3">
@@ -7234,7 +7280,7 @@
       <c r="C77" s="3">
         <v>8104</v>
       </c>
-      <c r="D77" s="15" t="s">
+      <c r="D77" s="13" t="s">
         <v>242</v>
       </c>
       <c r="E77" s="3">
@@ -7266,7 +7312,7 @@
       <c r="C78" s="3">
         <v>8105</v>
       </c>
-      <c r="D78" s="15" t="s">
+      <c r="D78" s="13" t="s">
         <v>243</v>
       </c>
       <c r="E78" s="3">
@@ -7298,7 +7344,7 @@
       <c r="C79" s="3">
         <v>8106</v>
       </c>
-      <c r="D79" s="15" t="s">
+      <c r="D79" s="13" t="s">
         <v>244</v>
       </c>
       <c r="E79" s="3">
@@ -7330,7 +7376,7 @@
       <c r="C80" s="3">
         <v>8107</v>
       </c>
-      <c r="D80" s="15" t="s">
+      <c r="D80" s="13" t="s">
         <v>245</v>
       </c>
       <c r="E80" s="3">
@@ -7362,7 +7408,7 @@
       <c r="C81" s="3">
         <v>8108</v>
       </c>
-      <c r="D81" s="15" t="s">
+      <c r="D81" s="13" t="s">
         <v>246</v>
       </c>
       <c r="E81" s="3">
@@ -7394,7 +7440,7 @@
       <c r="C83" s="3">
         <v>8201</v>
       </c>
-      <c r="D83" s="15" t="s">
+      <c r="D83" s="13" t="s">
         <v>247</v>
       </c>
       <c r="E83" s="3">
@@ -7429,7 +7475,7 @@
       <c r="C84" s="3">
         <v>8202</v>
       </c>
-      <c r="D84" s="15" t="s">
+      <c r="D84" s="13" t="s">
         <v>249</v>
       </c>
       <c r="E84" s="3">
@@ -7464,7 +7510,7 @@
       <c r="C85" s="3">
         <v>8203</v>
       </c>
-      <c r="D85" s="15" t="s">
+      <c r="D85" s="13" t="s">
         <v>251</v>
       </c>
       <c r="E85" s="3">
@@ -7499,7 +7545,7 @@
       <c r="C86" s="3">
         <v>8204</v>
       </c>
-      <c r="D86" s="15" t="s">
+      <c r="D86" s="13" t="s">
         <v>253</v>
       </c>
       <c r="E86" s="3">
@@ -7534,7 +7580,7 @@
       <c r="C87" s="3">
         <v>8205</v>
       </c>
-      <c r="D87" s="15" t="s">
+      <c r="D87" s="13" t="s">
         <v>255</v>
       </c>
       <c r="E87" s="3">
@@ -7569,7 +7615,7 @@
       <c r="C88" s="3">
         <v>8206</v>
       </c>
-      <c r="D88" s="15" t="s">
+      <c r="D88" s="13" t="s">
         <v>257</v>
       </c>
       <c r="E88" s="3">
@@ -7604,7 +7650,7 @@
       <c r="C89" s="3">
         <v>8207</v>
       </c>
-      <c r="D89" s="15" t="s">
+      <c r="D89" s="13" t="s">
         <v>259</v>
       </c>
       <c r="E89" s="3">
@@ -7636,46 +7682,46 @@
       </c>
     </row>
     <row r="91" customHeight="1" spans="4:4">
-      <c r="D91" s="15"/>
+      <c r="D91" s="13"/>
     </row>
     <row r="92" customHeight="1" spans="4:4">
-      <c r="D92" s="15"/>
+      <c r="D92" s="13"/>
     </row>
     <row r="93" customHeight="1" spans="4:4">
-      <c r="D93" s="15"/>
+      <c r="D93" s="13"/>
     </row>
     <row r="94" customHeight="1" spans="4:4">
-      <c r="D94" s="15"/>
+      <c r="D94" s="13"/>
     </row>
     <row r="95" customHeight="1" spans="4:4">
-      <c r="D95" s="15"/>
+      <c r="D95" s="13"/>
     </row>
     <row r="96" customHeight="1" spans="4:4">
-      <c r="D96" s="15"/>
+      <c r="D96" s="13"/>
     </row>
     <row r="97" customHeight="1" spans="4:4">
-      <c r="D97" s="15"/>
+      <c r="D97" s="13"/>
     </row>
     <row r="99" customHeight="1" spans="4:4">
-      <c r="D99" s="15"/>
+      <c r="D99" s="13"/>
     </row>
     <row r="100" customHeight="1" spans="4:4">
-      <c r="D100" s="15"/>
+      <c r="D100" s="13"/>
     </row>
     <row r="101" customHeight="1" spans="4:4">
-      <c r="D101" s="15"/>
+      <c r="D101" s="13"/>
     </row>
     <row r="102" customHeight="1" spans="4:4">
-      <c r="D102" s="15"/>
+      <c r="D102" s="13"/>
     </row>
     <row r="103" customHeight="1" spans="4:4">
-      <c r="D103" s="15"/>
+      <c r="D103" s="13"/>
     </row>
     <row r="104" customHeight="1" spans="4:4">
-      <c r="D104" s="15"/>
+      <c r="D104" s="13"/>
     </row>
     <row r="105" customHeight="1" spans="4:4">
-      <c r="D105" s="15"/>
+      <c r="D105" s="13"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -8553,7 +8599,7 @@
       <c r="C33" s="2">
         <v>2000011</v>
       </c>
-      <c r="D33" s="14" t="s">
+      <c r="D33" s="12" t="s">
         <v>289</v>
       </c>
       <c r="E33" s="2">
@@ -8581,7 +8627,7 @@
       <c r="C34" s="2">
         <v>2000012</v>
       </c>
-      <c r="D34" s="14" t="s">
+      <c r="D34" s="12" t="s">
         <v>290</v>
       </c>
       <c r="E34" s="2">
@@ -8609,7 +8655,7 @@
       <c r="C35" s="2">
         <v>2000013</v>
       </c>
-      <c r="D35" s="14" t="s">
+      <c r="D35" s="12" t="s">
         <v>291</v>
       </c>
       <c r="E35" s="2">
@@ -11636,7 +11682,7 @@
       <c r="C22" s="2">
         <v>3000017</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D22" s="11" t="s">
         <v>399</v>
       </c>
       <c r="E22" s="2">
@@ -11664,7 +11710,7 @@
       <c r="C23" s="2">
         <v>3000018</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="11" t="s">
         <v>400</v>
       </c>
       <c r="E23" s="2">
@@ -11692,7 +11738,7 @@
       <c r="C24" s="2">
         <v>3000019</v>
       </c>
-      <c r="D24" s="13" t="s">
+      <c r="D24" s="11" t="s">
         <v>401</v>
       </c>
       <c r="E24" s="2">
@@ -11720,7 +11766,7 @@
       <c r="C25" s="2">
         <v>3000020</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="D25" s="11" t="s">
         <v>402</v>
       </c>
       <c r="E25" s="2">
@@ -11748,7 +11794,7 @@
       <c r="C26" s="2">
         <v>3000021</v>
       </c>
-      <c r="D26" s="13" t="s">
+      <c r="D26" s="11" t="s">
         <v>403</v>
       </c>
       <c r="E26" s="2">
@@ -11776,7 +11822,7 @@
       <c r="C27" s="2">
         <v>3000022</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="D27" s="11" t="s">
         <v>404</v>
       </c>
       <c r="E27" s="2">
@@ -11804,7 +11850,7 @@
       <c r="C28" s="2">
         <v>3000023</v>
       </c>
-      <c r="D28" s="13" t="s">
+      <c r="D28" s="11" t="s">
         <v>405</v>
       </c>
       <c r="E28" s="2">
@@ -11832,7 +11878,7 @@
       <c r="C29" s="2">
         <v>3000024</v>
       </c>
-      <c r="D29" s="13" t="s">
+      <c r="D29" s="11" t="s">
         <v>406</v>
       </c>
       <c r="E29" s="2">
@@ -12547,13 +12593,13 @@
   <dimension ref="C1:M95"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="3" width="9" style="8"/>
-    <col min="4" max="4" width="9.625" style="8" customWidth="1"/>
-    <col min="5" max="5" width="9" style="8"/>
-    <col min="6" max="6" width="20.875" style="8" customWidth="1"/>
-    <col min="7" max="11" width="9" style="8"/>
+    <col min="1" max="3" width="9" style="2"/>
+    <col min="4" max="4" width="9.625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="9" style="2"/>
+    <col min="6" max="6" width="20.875" style="2" customWidth="1"/>
+    <col min="7" max="11" width="9" style="2"/>
     <col min="12" max="13" width="13.5" style="3" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="8"/>
+    <col min="14" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="12:13">
@@ -12834,7 +12880,7 @@
       <c r="J11" s="2">
         <v>6</v>
       </c>
-      <c r="K11" s="13" t="s">
+      <c r="K11" s="11" t="s">
         <v>441</v>
       </c>
       <c r="L11" s="3">
@@ -12869,7 +12915,7 @@
       <c r="J12" s="2">
         <v>6</v>
       </c>
-      <c r="K12" s="13" t="s">
+      <c r="K12" s="11" t="s">
         <v>443</v>
       </c>
       <c r="L12" s="3">
@@ -12904,7 +12950,7 @@
       <c r="J13" s="2">
         <v>6</v>
       </c>
-      <c r="K13" s="13" t="s">
+      <c r="K13" s="11" t="s">
         <v>445</v>
       </c>
       <c r="L13" s="3">
@@ -12939,7 +12985,7 @@
       <c r="J14" s="2">
         <v>6</v>
       </c>
-      <c r="K14" s="13" t="s">
+      <c r="K14" s="11" t="s">
         <v>447</v>
       </c>
       <c r="L14" s="3">
@@ -12974,7 +13020,7 @@
       <c r="J15" s="2">
         <v>6</v>
       </c>
-      <c r="K15" s="13" t="s">
+      <c r="K15" s="11" t="s">
         <v>449</v>
       </c>
       <c r="L15" s="3">
@@ -14059,7 +14105,7 @@
       <c r="J46" s="2">
         <v>6</v>
       </c>
-      <c r="K46" s="8">
+      <c r="K46" s="2">
         <v>950</v>
       </c>
       <c r="L46" s="3">
@@ -14094,7 +14140,7 @@
       <c r="J47" s="2">
         <v>6</v>
       </c>
-      <c r="K47" s="8">
+      <c r="K47" s="2">
         <v>950</v>
       </c>
       <c r="L47" s="3">
@@ -14129,7 +14175,7 @@
       <c r="J48" s="2">
         <v>6</v>
       </c>
-      <c r="K48" s="8">
+      <c r="K48" s="2">
         <v>950</v>
       </c>
       <c r="L48" s="3">
@@ -14164,7 +14210,7 @@
       <c r="J49" s="2">
         <v>6</v>
       </c>
-      <c r="K49" s="8">
+      <c r="K49" s="2">
         <v>950</v>
       </c>
       <c r="L49" s="3">
@@ -14199,7 +14245,7 @@
       <c r="J50" s="2">
         <v>6</v>
       </c>
-      <c r="K50" s="8">
+      <c r="K50" s="2">
         <v>950</v>
       </c>
       <c r="L50" s="3">
@@ -14234,7 +14280,7 @@
       <c r="J51" s="2">
         <v>6</v>
       </c>
-      <c r="K51" s="8">
+      <c r="K51" s="2">
         <v>1000</v>
       </c>
       <c r="L51" s="3">
@@ -14269,7 +14315,7 @@
       <c r="J52" s="2">
         <v>6</v>
       </c>
-      <c r="K52" s="8">
+      <c r="K52" s="2">
         <v>1000</v>
       </c>
       <c r="L52" s="3">
@@ -14304,7 +14350,7 @@
       <c r="J53" s="2">
         <v>6</v>
       </c>
-      <c r="K53" s="8">
+      <c r="K53" s="2">
         <v>1000</v>
       </c>
       <c r="L53" s="3">
@@ -14339,7 +14385,7 @@
       <c r="J54" s="2">
         <v>6</v>
       </c>
-      <c r="K54" s="8">
+      <c r="K54" s="2">
         <v>1000</v>
       </c>
       <c r="L54" s="3">
@@ -14349,7 +14395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" s="8" customFormat="1" customHeight="1" spans="3:13">
+    <row r="55" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C55" s="2">
         <v>40000099</v>
       </c>
@@ -14374,7 +14420,7 @@
       <c r="J55" s="2">
         <v>6</v>
       </c>
-      <c r="K55" s="8">
+      <c r="K55" s="2">
         <v>1000</v>
       </c>
       <c r="L55" s="3">
@@ -14384,7 +14430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" s="8" customFormat="1" customHeight="1" spans="3:13">
+    <row r="56" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C56" s="2">
         <v>40000100</v>
       </c>
@@ -14409,7 +14455,7 @@
       <c r="J56" s="2">
         <v>6</v>
       </c>
-      <c r="K56" s="8">
+      <c r="K56" s="2">
         <v>1050</v>
       </c>
       <c r="L56" s="3">
@@ -14419,7 +14465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" s="8" customFormat="1" customHeight="1" spans="3:13">
+    <row r="57" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C57" s="2">
         <v>40000101</v>
       </c>
@@ -14444,7 +14490,7 @@
       <c r="J57" s="2">
         <v>6</v>
       </c>
-      <c r="K57" s="8">
+      <c r="K57" s="2">
         <v>1050</v>
       </c>
       <c r="L57" s="3">
@@ -14454,7 +14500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" s="8" customFormat="1" customHeight="1" spans="3:13">
+    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C58" s="2">
         <v>40000102</v>
       </c>
@@ -14479,7 +14525,7 @@
       <c r="J58" s="2">
         <v>6</v>
       </c>
-      <c r="K58" s="8">
+      <c r="K58" s="2">
         <v>1050</v>
       </c>
       <c r="L58" s="3">
@@ -14489,7 +14535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" s="8" customFormat="1" customHeight="1" spans="3:13">
+    <row r="59" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C59" s="2">
         <v>40000103</v>
       </c>
@@ -14514,7 +14560,7 @@
       <c r="J59" s="2">
         <v>6</v>
       </c>
-      <c r="K59" s="8">
+      <c r="K59" s="2">
         <v>1050</v>
       </c>
       <c r="L59" s="3">
@@ -14524,7 +14570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" s="8" customFormat="1" customHeight="1" spans="3:13">
+    <row r="60" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C60" s="2">
         <v>40000104</v>
       </c>
@@ -14549,7 +14595,7 @@
       <c r="J60" s="2">
         <v>6</v>
       </c>
-      <c r="K60" s="8">
+      <c r="K60" s="2">
         <v>1050</v>
       </c>
       <c r="L60" s="3">
@@ -14559,38 +14605,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" s="10" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C61" s="11">
+    <row r="61" s="9" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C61" s="9">
         <v>40000105</v>
       </c>
-      <c r="D61" s="12" t="s">
+      <c r="D61" s="10" t="s">
         <v>505</v>
       </c>
-      <c r="E61" s="11">
+      <c r="E61" s="9">
         <v>14</v>
       </c>
-      <c r="F61" s="11" t="s">
+      <c r="F61" s="9" t="s">
         <v>432</v>
       </c>
-      <c r="G61" s="11">
-        <v>1</v>
-      </c>
-      <c r="H61" s="11">
-        <v>99999</v>
-      </c>
-      <c r="I61" s="11">
-        <v>0</v>
-      </c>
-      <c r="J61" s="11">
-        <v>6</v>
-      </c>
-      <c r="K61" s="11">
+      <c r="G61" s="9">
+        <v>1</v>
+      </c>
+      <c r="H61" s="9">
+        <v>99999</v>
+      </c>
+      <c r="I61" s="9">
+        <v>0</v>
+      </c>
+      <c r="J61" s="9">
+        <v>6</v>
+      </c>
+      <c r="K61" s="9">
         <v>1100</v>
       </c>
-      <c r="L61" s="12">
+      <c r="L61" s="10">
         <v>4018</v>
       </c>
-      <c r="M61" s="12">
+      <c r="M61" s="10">
         <v>1</v>
       </c>
     </row>
@@ -15074,7 +15120,7 @@
       <c r="J75" s="2">
         <v>6</v>
       </c>
-      <c r="K75" s="8">
+      <c r="K75" s="2">
         <v>1200</v>
       </c>
       <c r="L75" s="3">
@@ -15459,7 +15505,7 @@
       <c r="J86" s="2">
         <v>6</v>
       </c>
-      <c r="K86" s="8">
+      <c r="K86" s="2">
         <v>1350</v>
       </c>
       <c r="L86" s="3">
@@ -15494,7 +15540,7 @@
       <c r="J87" s="2">
         <v>6</v>
       </c>
-      <c r="K87" s="8">
+      <c r="K87" s="2">
         <v>1350</v>
       </c>
       <c r="L87" s="3">
@@ -15529,7 +15575,7 @@
       <c r="J88" s="2">
         <v>6</v>
       </c>
-      <c r="K88" s="8">
+      <c r="K88" s="2">
         <v>1350</v>
       </c>
       <c r="L88" s="3">
@@ -15564,7 +15610,7 @@
       <c r="J89" s="2">
         <v>6</v>
       </c>
-      <c r="K89" s="8">
+      <c r="K89" s="2">
         <v>1350</v>
       </c>
       <c r="L89" s="3">
@@ -15599,7 +15645,7 @@
       <c r="J90" s="2">
         <v>6</v>
       </c>
-      <c r="K90" s="8">
+      <c r="K90" s="2">
         <v>1350</v>
       </c>
       <c r="L90" s="3">
@@ -15634,7 +15680,7 @@
       <c r="J91" s="2">
         <v>6</v>
       </c>
-      <c r="K91" s="8">
+      <c r="K91" s="2">
         <v>1400</v>
       </c>
       <c r="L91" s="3">
@@ -15669,7 +15715,7 @@
       <c r="J92" s="2">
         <v>6</v>
       </c>
-      <c r="K92" s="8">
+      <c r="K92" s="2">
         <v>1400</v>
       </c>
       <c r="L92" s="3">
@@ -15704,7 +15750,7 @@
       <c r="J93" s="2">
         <v>6</v>
       </c>
-      <c r="K93" s="8">
+      <c r="K93" s="2">
         <v>1400</v>
       </c>
       <c r="L93" s="3">
@@ -15739,7 +15785,7 @@
       <c r="J94" s="2">
         <v>6</v>
       </c>
-      <c r="K94" s="8">
+      <c r="K94" s="2">
         <v>1400</v>
       </c>
       <c r="L94" s="3">
@@ -15774,7 +15820,7 @@
       <c r="J95" s="2">
         <v>6</v>
       </c>
-      <c r="K95" s="8">
+      <c r="K95" s="2">
         <v>1400</v>
       </c>
       <c r="L95" s="3">
@@ -15802,16 +15848,16 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:M109"/>
+  <dimension ref="C1:M117"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
-    <col min="1" max="3" width="9" style="8"/>
-    <col min="4" max="4" width="14.25" style="8" customWidth="1"/>
-    <col min="5" max="5" width="9" style="8"/>
-    <col min="6" max="6" width="20.875" style="8" customWidth="1"/>
-    <col min="7" max="11" width="9" style="8"/>
+    <col min="1" max="3" width="9" style="2"/>
+    <col min="4" max="4" width="14.25" style="2" customWidth="1"/>
+    <col min="5" max="5" width="9" style="2"/>
+    <col min="6" max="6" width="20.875" style="2" customWidth="1"/>
+    <col min="7" max="11" width="9" style="2"/>
     <col min="12" max="13" width="13.5" style="3" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="8"/>
+    <col min="14" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="12:13">
@@ -16176,7 +16222,7 @@
       <c r="C13" s="6">
         <v>50000008</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="7" t="s">
         <v>554</v>
       </c>
       <c r="E13" s="6">
@@ -16200,10 +16246,10 @@
       <c r="K13" s="6">
         <v>800</v>
       </c>
-      <c r="L13" s="9">
+      <c r="L13" s="7">
         <v>4015</v>
       </c>
-      <c r="M13" s="9">
+      <c r="M13" s="7">
         <v>1</v>
       </c>
     </row>
@@ -16456,7 +16502,7 @@
       <c r="C21" s="6">
         <v>50000016</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="7" t="s">
         <v>570</v>
       </c>
       <c r="E21" s="6">
@@ -16480,10 +16526,10 @@
       <c r="K21" s="6">
         <v>850</v>
       </c>
-      <c r="L21" s="9">
+      <c r="L21" s="7">
         <v>4015</v>
       </c>
-      <c r="M21" s="9">
+      <c r="M21" s="7">
         <v>1</v>
       </c>
     </row>
@@ -16512,7 +16558,7 @@
       <c r="J22" s="2">
         <v>6</v>
       </c>
-      <c r="K22" s="8">
+      <c r="K22" s="2">
         <v>900</v>
       </c>
       <c r="L22" s="3">
@@ -16547,7 +16593,7 @@
       <c r="J23" s="2">
         <v>6</v>
       </c>
-      <c r="K23" s="8">
+      <c r="K23" s="2">
         <v>900</v>
       </c>
       <c r="L23" s="3">
@@ -16582,7 +16628,7 @@
       <c r="J24" s="2">
         <v>6</v>
       </c>
-      <c r="K24" s="8">
+      <c r="K24" s="2">
         <v>900</v>
       </c>
       <c r="L24" s="3">
@@ -16617,7 +16663,7 @@
       <c r="J25" s="2">
         <v>6</v>
       </c>
-      <c r="K25" s="8">
+      <c r="K25" s="2">
         <v>900</v>
       </c>
       <c r="L25" s="3">
@@ -16652,7 +16698,7 @@
       <c r="J26" s="2">
         <v>6</v>
       </c>
-      <c r="K26" s="8">
+      <c r="K26" s="2">
         <v>900</v>
       </c>
       <c r="L26" s="3">
@@ -16687,7 +16733,7 @@
       <c r="J27" s="2">
         <v>6</v>
       </c>
-      <c r="K27" s="8">
+      <c r="K27" s="2">
         <v>900</v>
       </c>
       <c r="L27" s="3">
@@ -16722,7 +16768,7 @@
       <c r="J28" s="2">
         <v>6</v>
       </c>
-      <c r="K28" s="8">
+      <c r="K28" s="2">
         <v>900</v>
       </c>
       <c r="L28" s="3">
@@ -16736,7 +16782,7 @@
       <c r="C29" s="6">
         <v>50000024</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="D29" s="7" t="s">
         <v>586</v>
       </c>
       <c r="E29" s="6">
@@ -16757,13 +16803,13 @@
       <c r="J29" s="6">
         <v>6</v>
       </c>
-      <c r="K29" s="8">
+      <c r="K29" s="2">
         <v>900</v>
       </c>
-      <c r="L29" s="9">
+      <c r="L29" s="7">
         <v>4015</v>
       </c>
-      <c r="M29" s="9">
+      <c r="M29" s="7">
         <v>1</v>
       </c>
     </row>
@@ -16792,7 +16838,7 @@
       <c r="J30" s="2">
         <v>6</v>
       </c>
-      <c r="K30" s="8">
+      <c r="K30" s="2">
         <v>950</v>
       </c>
       <c r="L30" s="3">
@@ -16827,7 +16873,7 @@
       <c r="J31" s="2">
         <v>6</v>
       </c>
-      <c r="K31" s="8">
+      <c r="K31" s="2">
         <v>950</v>
       </c>
       <c r="L31" s="3">
@@ -16862,7 +16908,7 @@
       <c r="J32" s="2">
         <v>6</v>
       </c>
-      <c r="K32" s="8">
+      <c r="K32" s="2">
         <v>950</v>
       </c>
       <c r="L32" s="3">
@@ -16897,7 +16943,7 @@
       <c r="J33" s="2">
         <v>6</v>
       </c>
-      <c r="K33" s="8">
+      <c r="K33" s="2">
         <v>950</v>
       </c>
       <c r="L33" s="3">
@@ -16932,7 +16978,7 @@
       <c r="J34" s="2">
         <v>6</v>
       </c>
-      <c r="K34" s="8">
+      <c r="K34" s="2">
         <v>950</v>
       </c>
       <c r="L34" s="3">
@@ -16967,7 +17013,7 @@
       <c r="J35" s="2">
         <v>6</v>
       </c>
-      <c r="K35" s="8">
+      <c r="K35" s="2">
         <v>950</v>
       </c>
       <c r="L35" s="3">
@@ -17002,7 +17048,7 @@
       <c r="J36" s="2">
         <v>6</v>
       </c>
-      <c r="K36" s="8">
+      <c r="K36" s="2">
         <v>950</v>
       </c>
       <c r="L36" s="3">
@@ -17012,11 +17058,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" s="7" customFormat="1" customHeight="1" spans="3:13">
+    <row r="37" s="6" customFormat="1" customHeight="1" spans="3:13">
       <c r="C37" s="6">
         <v>50000032</v>
       </c>
-      <c r="D37" s="9" t="s">
+      <c r="D37" s="7" t="s">
         <v>602</v>
       </c>
       <c r="E37" s="6">
@@ -17037,13 +17083,13 @@
       <c r="J37" s="6">
         <v>6</v>
       </c>
-      <c r="K37" s="8">
+      <c r="K37" s="2">
         <v>950</v>
       </c>
-      <c r="L37" s="9">
+      <c r="L37" s="7">
         <v>4015</v>
       </c>
-      <c r="M37" s="9">
+      <c r="M37" s="7">
         <v>1</v>
       </c>
     </row>
@@ -17292,11 +17338,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" s="7" customFormat="1" customHeight="1" spans="3:13">
+    <row r="45" s="6" customFormat="1" customHeight="1" spans="3:13">
       <c r="C45" s="6">
         <v>50000040</v>
       </c>
-      <c r="D45" s="9" t="s">
+      <c r="D45" s="7" t="s">
         <v>618</v>
       </c>
       <c r="E45" s="6">
@@ -17320,10 +17366,10 @@
       <c r="K45" s="2">
         <v>1000</v>
       </c>
-      <c r="L45" s="9">
+      <c r="L45" s="7">
         <v>4015</v>
       </c>
-      <c r="M45" s="9">
+      <c r="M45" s="7">
         <v>1</v>
       </c>
     </row>
@@ -17572,11 +17618,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" s="7" customFormat="1" customHeight="1" spans="3:13">
+    <row r="53" s="6" customFormat="1" customHeight="1" spans="3:13">
       <c r="C53" s="6">
         <v>50000048</v>
       </c>
-      <c r="D53" s="9" t="s">
+      <c r="D53" s="7" t="s">
         <v>634</v>
       </c>
       <c r="E53" s="6">
@@ -17600,10 +17646,10 @@
       <c r="K53" s="2">
         <v>1050</v>
       </c>
-      <c r="L53" s="9">
+      <c r="L53" s="7">
         <v>4015</v>
       </c>
-      <c r="M53" s="9">
+      <c r="M53" s="7">
         <v>1</v>
       </c>
     </row>
@@ -17852,11 +17898,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" s="7" customFormat="1" customHeight="1" spans="3:13">
+    <row r="61" s="6" customFormat="1" customHeight="1" spans="3:13">
       <c r="C61" s="6">
         <v>50000056</v>
       </c>
-      <c r="D61" s="9" t="s">
+      <c r="D61" s="7" t="s">
         <v>650</v>
       </c>
       <c r="E61" s="6">
@@ -17880,10 +17926,10 @@
       <c r="K61" s="2">
         <v>1100</v>
       </c>
-      <c r="L61" s="9">
+      <c r="L61" s="7">
         <v>4015</v>
       </c>
-      <c r="M61" s="9">
+      <c r="M61" s="7">
         <v>1</v>
       </c>
     </row>
@@ -17912,7 +17958,7 @@
       <c r="J62" s="2">
         <v>6</v>
       </c>
-      <c r="K62" s="8">
+      <c r="K62" s="2">
         <v>1150</v>
       </c>
       <c r="L62" s="3">
@@ -17947,7 +17993,7 @@
       <c r="J63" s="2">
         <v>6</v>
       </c>
-      <c r="K63" s="8">
+      <c r="K63" s="2">
         <v>1150</v>
       </c>
       <c r="L63" s="3">
@@ -17982,7 +18028,7 @@
       <c r="J64" s="2">
         <v>6</v>
       </c>
-      <c r="K64" s="8">
+      <c r="K64" s="2">
         <v>1150</v>
       </c>
       <c r="L64" s="3">
@@ -18017,7 +18063,7 @@
       <c r="J65" s="2">
         <v>6</v>
       </c>
-      <c r="K65" s="8">
+      <c r="K65" s="2">
         <v>1150</v>
       </c>
       <c r="L65" s="3">
@@ -18052,7 +18098,7 @@
       <c r="J66" s="2">
         <v>6</v>
       </c>
-      <c r="K66" s="8">
+      <c r="K66" s="2">
         <v>1150</v>
       </c>
       <c r="L66" s="3">
@@ -18087,7 +18133,7 @@
       <c r="J67" s="2">
         <v>6</v>
       </c>
-      <c r="K67" s="8">
+      <c r="K67" s="2">
         <v>1150</v>
       </c>
       <c r="L67" s="3">
@@ -18122,7 +18168,7 @@
       <c r="J68" s="2">
         <v>6</v>
       </c>
-      <c r="K68" s="8">
+      <c r="K68" s="2">
         <v>1150</v>
       </c>
       <c r="L68" s="3">
@@ -18132,11 +18178,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" s="7" customFormat="1" customHeight="1" spans="3:13">
+    <row r="69" s="6" customFormat="1" customHeight="1" spans="3:13">
       <c r="C69" s="6">
         <v>50000064</v>
       </c>
-      <c r="D69" s="9" t="s">
+      <c r="D69" s="7" t="s">
         <v>666</v>
       </c>
       <c r="E69" s="6">
@@ -18157,13 +18203,13 @@
       <c r="J69" s="6">
         <v>6</v>
       </c>
-      <c r="K69" s="8">
+      <c r="K69" s="2">
         <v>1150</v>
       </c>
-      <c r="L69" s="9">
+      <c r="L69" s="7">
         <v>4015</v>
       </c>
-      <c r="M69" s="9">
+      <c r="M69" s="7">
         <v>1</v>
       </c>
     </row>
@@ -18192,7 +18238,7 @@
       <c r="J70" s="2">
         <v>6</v>
       </c>
-      <c r="K70" s="8">
+      <c r="K70" s="2">
         <v>1200</v>
       </c>
       <c r="L70" s="3">
@@ -18227,7 +18273,7 @@
       <c r="J71" s="2">
         <v>6</v>
       </c>
-      <c r="K71" s="8">
+      <c r="K71" s="2">
         <v>1200</v>
       </c>
       <c r="L71" s="3">
@@ -18262,7 +18308,7 @@
       <c r="J72" s="2">
         <v>6</v>
       </c>
-      <c r="K72" s="8">
+      <c r="K72" s="2">
         <v>1200</v>
       </c>
       <c r="L72" s="3">
@@ -18297,7 +18343,7 @@
       <c r="J73" s="2">
         <v>6</v>
       </c>
-      <c r="K73" s="8">
+      <c r="K73" s="2">
         <v>1200</v>
       </c>
       <c r="L73" s="3">
@@ -18332,7 +18378,7 @@
       <c r="J74" s="2">
         <v>6</v>
       </c>
-      <c r="K74" s="8">
+      <c r="K74" s="2">
         <v>1200</v>
       </c>
       <c r="L74" s="3">
@@ -18367,7 +18413,7 @@
       <c r="J75" s="2">
         <v>6</v>
       </c>
-      <c r="K75" s="8">
+      <c r="K75" s="2">
         <v>1200</v>
       </c>
       <c r="L75" s="3">
@@ -18402,7 +18448,7 @@
       <c r="J76" s="2">
         <v>6</v>
       </c>
-      <c r="K76" s="8">
+      <c r="K76" s="2">
         <v>1200</v>
       </c>
       <c r="L76" s="3">
@@ -18412,11 +18458,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" s="7" customFormat="1" customHeight="1" spans="3:13">
+    <row r="77" s="6" customFormat="1" customHeight="1" spans="3:13">
       <c r="C77" s="6">
         <v>50000072</v>
       </c>
-      <c r="D77" s="9" t="s">
+      <c r="D77" s="7" t="s">
         <v>682</v>
       </c>
       <c r="E77" s="6">
@@ -18437,13 +18483,13 @@
       <c r="J77" s="6">
         <v>6</v>
       </c>
-      <c r="K77" s="8">
+      <c r="K77" s="2">
         <v>1200</v>
       </c>
-      <c r="L77" s="9">
+      <c r="L77" s="7">
         <v>4015</v>
       </c>
-      <c r="M77" s="9">
+      <c r="M77" s="7">
         <v>1</v>
       </c>
     </row>
@@ -18472,7 +18518,7 @@
       <c r="J78" s="2">
         <v>6</v>
       </c>
-      <c r="K78" s="8">
+      <c r="K78" s="2">
         <v>1250</v>
       </c>
       <c r="L78" s="3">
@@ -18507,7 +18553,7 @@
       <c r="J79" s="2">
         <v>6</v>
       </c>
-      <c r="K79" s="8">
+      <c r="K79" s="2">
         <v>1250</v>
       </c>
       <c r="L79" s="3">
@@ -18542,7 +18588,7 @@
       <c r="J80" s="2">
         <v>6</v>
       </c>
-      <c r="K80" s="8">
+      <c r="K80" s="2">
         <v>1250</v>
       </c>
       <c r="L80" s="3">
@@ -18577,7 +18623,7 @@
       <c r="J81" s="2">
         <v>6</v>
       </c>
-      <c r="K81" s="8">
+      <c r="K81" s="2">
         <v>1250</v>
       </c>
       <c r="L81" s="3">
@@ -18612,7 +18658,7 @@
       <c r="J82" s="2">
         <v>6</v>
       </c>
-      <c r="K82" s="8">
+      <c r="K82" s="2">
         <v>1250</v>
       </c>
       <c r="L82" s="3">
@@ -18647,7 +18693,7 @@
       <c r="J83" s="2">
         <v>6</v>
       </c>
-      <c r="K83" s="8">
+      <c r="K83" s="2">
         <v>1250</v>
       </c>
       <c r="L83" s="3">
@@ -18682,7 +18728,7 @@
       <c r="J84" s="2">
         <v>6</v>
       </c>
-      <c r="K84" s="8">
+      <c r="K84" s="2">
         <v>1250</v>
       </c>
       <c r="L84" s="3">
@@ -18692,11 +18738,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" s="7" customFormat="1" customHeight="1" spans="3:13">
+    <row r="85" s="6" customFormat="1" customHeight="1" spans="3:13">
       <c r="C85" s="6">
         <v>50000080</v>
       </c>
-      <c r="D85" s="9" t="s">
+      <c r="D85" s="7" t="s">
         <v>698</v>
       </c>
       <c r="E85" s="6">
@@ -18717,13 +18763,13 @@
       <c r="J85" s="6">
         <v>6</v>
       </c>
-      <c r="K85" s="8">
+      <c r="K85" s="2">
         <v>1250</v>
       </c>
-      <c r="L85" s="9">
+      <c r="L85" s="7">
         <v>4015</v>
       </c>
-      <c r="M85" s="9">
+      <c r="M85" s="7">
         <v>1</v>
       </c>
     </row>
@@ -18752,7 +18798,7 @@
       <c r="J86" s="2">
         <v>6</v>
       </c>
-      <c r="K86" s="8">
+      <c r="K86" s="2">
         <v>1300</v>
       </c>
       <c r="L86" s="3">
@@ -18787,7 +18833,7 @@
       <c r="J87" s="2">
         <v>6</v>
       </c>
-      <c r="K87" s="8">
+      <c r="K87" s="2">
         <v>1300</v>
       </c>
       <c r="L87" s="3">
@@ -18822,7 +18868,7 @@
       <c r="J88" s="2">
         <v>6</v>
       </c>
-      <c r="K88" s="8">
+      <c r="K88" s="2">
         <v>1300</v>
       </c>
       <c r="L88" s="3">
@@ -18857,7 +18903,7 @@
       <c r="J89" s="2">
         <v>6</v>
       </c>
-      <c r="K89" s="8">
+      <c r="K89" s="2">
         <v>1300</v>
       </c>
       <c r="L89" s="3">
@@ -18892,7 +18938,7 @@
       <c r="J90" s="2">
         <v>6</v>
       </c>
-      <c r="K90" s="8">
+      <c r="K90" s="2">
         <v>1300</v>
       </c>
       <c r="L90" s="3">
@@ -18927,7 +18973,7 @@
       <c r="J91" s="2">
         <v>6</v>
       </c>
-      <c r="K91" s="8">
+      <c r="K91" s="2">
         <v>1300</v>
       </c>
       <c r="L91" s="3">
@@ -18962,7 +19008,7 @@
       <c r="J92" s="2">
         <v>6</v>
       </c>
-      <c r="K92" s="8">
+      <c r="K92" s="2">
         <v>1300</v>
       </c>
       <c r="L92" s="3">
@@ -18972,11 +19018,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" s="7" customFormat="1" customHeight="1" spans="3:13">
+    <row r="93" s="6" customFormat="1" customHeight="1" spans="3:13">
       <c r="C93" s="6">
         <v>50000088</v>
       </c>
-      <c r="D93" s="9" t="s">
+      <c r="D93" s="7" t="s">
         <v>714</v>
       </c>
       <c r="E93" s="6">
@@ -18997,13 +19043,13 @@
       <c r="J93" s="6">
         <v>6</v>
       </c>
-      <c r="K93" s="8">
+      <c r="K93" s="2">
         <v>1300</v>
       </c>
-      <c r="L93" s="9">
+      <c r="L93" s="7">
         <v>4015</v>
       </c>
-      <c r="M93" s="9">
+      <c r="M93" s="7">
         <v>1</v>
       </c>
     </row>
@@ -19032,7 +19078,7 @@
       <c r="J94" s="2">
         <v>6</v>
       </c>
-      <c r="K94" s="8">
+      <c r="K94" s="2">
         <v>1350</v>
       </c>
       <c r="L94" s="3">
@@ -19067,7 +19113,7 @@
       <c r="J95" s="2">
         <v>6</v>
       </c>
-      <c r="K95" s="8">
+      <c r="K95" s="2">
         <v>1350</v>
       </c>
       <c r="L95" s="3">
@@ -19102,7 +19148,7 @@
       <c r="J96" s="2">
         <v>6</v>
       </c>
-      <c r="K96" s="8">
+      <c r="K96" s="2">
         <v>1350</v>
       </c>
       <c r="L96" s="3">
@@ -19137,7 +19183,7 @@
       <c r="J97" s="2">
         <v>6</v>
       </c>
-      <c r="K97" s="8">
+      <c r="K97" s="2">
         <v>1350</v>
       </c>
       <c r="L97" s="3">
@@ -19172,7 +19218,7 @@
       <c r="J98" s="2">
         <v>6</v>
       </c>
-      <c r="K98" s="8">
+      <c r="K98" s="2">
         <v>1350</v>
       </c>
       <c r="L98" s="3">
@@ -19207,7 +19253,7 @@
       <c r="J99" s="2">
         <v>6</v>
       </c>
-      <c r="K99" s="8">
+      <c r="K99" s="2">
         <v>1350</v>
       </c>
       <c r="L99" s="3">
@@ -19242,7 +19288,7 @@
       <c r="J100" s="2">
         <v>6</v>
       </c>
-      <c r="K100" s="8">
+      <c r="K100" s="2">
         <v>1350</v>
       </c>
       <c r="L100" s="3">
@@ -19252,11 +19298,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" s="7" customFormat="1" customHeight="1" spans="3:13">
+    <row r="101" s="6" customFormat="1" customHeight="1" spans="3:13">
       <c r="C101" s="6">
         <v>50000096</v>
       </c>
-      <c r="D101" s="9" t="s">
+      <c r="D101" s="7" t="s">
         <v>730</v>
       </c>
       <c r="E101" s="6">
@@ -19277,13 +19323,13 @@
       <c r="J101" s="6">
         <v>6</v>
       </c>
-      <c r="K101" s="8">
+      <c r="K101" s="2">
         <v>1350</v>
       </c>
-      <c r="L101" s="9">
+      <c r="L101" s="7">
         <v>4015</v>
       </c>
-      <c r="M101" s="9">
+      <c r="M101" s="7">
         <v>1</v>
       </c>
     </row>
@@ -19312,7 +19358,7 @@
       <c r="J102" s="2">
         <v>6</v>
       </c>
-      <c r="K102" s="8">
+      <c r="K102" s="2">
         <v>1400</v>
       </c>
       <c r="L102" s="3">
@@ -19347,7 +19393,7 @@
       <c r="J103" s="2">
         <v>6</v>
       </c>
-      <c r="K103" s="8">
+      <c r="K103" s="2">
         <v>1400</v>
       </c>
       <c r="L103" s="3">
@@ -19382,7 +19428,7 @@
       <c r="J104" s="2">
         <v>6</v>
       </c>
-      <c r="K104" s="8">
+      <c r="K104" s="2">
         <v>1400</v>
       </c>
       <c r="L104" s="3">
@@ -19417,7 +19463,7 @@
       <c r="J105" s="2">
         <v>6</v>
       </c>
-      <c r="K105" s="8">
+      <c r="K105" s="2">
         <v>1400</v>
       </c>
       <c r="L105" s="3">
@@ -19452,7 +19498,7 @@
       <c r="J106" s="2">
         <v>6</v>
       </c>
-      <c r="K106" s="8">
+      <c r="K106" s="2">
         <v>1400</v>
       </c>
       <c r="L106" s="3">
@@ -19487,7 +19533,7 @@
       <c r="J107" s="2">
         <v>6</v>
       </c>
-      <c r="K107" s="8">
+      <c r="K107" s="2">
         <v>1400</v>
       </c>
       <c r="L107" s="3">
@@ -19522,7 +19568,7 @@
       <c r="J108" s="2">
         <v>6</v>
       </c>
-      <c r="K108" s="8">
+      <c r="K108" s="2">
         <v>1400</v>
       </c>
       <c r="L108" s="3">
@@ -19532,11 +19578,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" s="7" customFormat="1" customHeight="1" spans="3:13">
+    <row r="109" s="6" customFormat="1" customHeight="1" spans="3:13">
       <c r="C109" s="6">
         <v>50000104</v>
       </c>
-      <c r="D109" s="9" t="s">
+      <c r="D109" s="7" t="s">
         <v>746</v>
       </c>
       <c r="E109" s="6">
@@ -19557,13 +19603,293 @@
       <c r="J109" s="6">
         <v>6</v>
       </c>
-      <c r="K109" s="7">
+      <c r="K109" s="6">
         <v>1400</v>
       </c>
-      <c r="L109" s="9">
+      <c r="L109" s="7">
         <v>4015</v>
       </c>
-      <c r="M109" s="9">
+      <c r="M109" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" customHeight="1" spans="3:13">
+      <c r="C110" s="8">
+        <v>50000105</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="E110" s="2">
+        <v>5</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="G110" s="2">
+        <v>1</v>
+      </c>
+      <c r="H110" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I110" s="2">
+        <v>0</v>
+      </c>
+      <c r="J110" s="2">
+        <v>6</v>
+      </c>
+      <c r="K110" s="2">
+        <v>1450</v>
+      </c>
+      <c r="L110" s="3">
+        <v>4015</v>
+      </c>
+      <c r="M110" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" customHeight="1" spans="3:13">
+      <c r="C111" s="8">
+        <v>50000106</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="E111" s="2">
+        <v>5</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="G111" s="2">
+        <v>1</v>
+      </c>
+      <c r="H111" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I111" s="2">
+        <v>0</v>
+      </c>
+      <c r="J111" s="2">
+        <v>6</v>
+      </c>
+      <c r="K111" s="2">
+        <v>1450</v>
+      </c>
+      <c r="L111" s="3">
+        <v>4015</v>
+      </c>
+      <c r="M111" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" customHeight="1" spans="3:13">
+      <c r="C112" s="8">
+        <v>50000107</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>752</v>
+      </c>
+      <c r="E112" s="2">
+        <v>5</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="G112" s="2">
+        <v>1</v>
+      </c>
+      <c r="H112" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I112" s="2">
+        <v>0</v>
+      </c>
+      <c r="J112" s="2">
+        <v>6</v>
+      </c>
+      <c r="K112" s="2">
+        <v>1450</v>
+      </c>
+      <c r="L112" s="3">
+        <v>4015</v>
+      </c>
+      <c r="M112" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" customHeight="1" spans="3:13">
+      <c r="C113" s="8">
+        <v>50000108</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="E113" s="2">
+        <v>5</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="G113" s="2">
+        <v>1</v>
+      </c>
+      <c r="H113" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I113" s="2">
+        <v>0</v>
+      </c>
+      <c r="J113" s="2">
+        <v>6</v>
+      </c>
+      <c r="K113" s="2">
+        <v>1450</v>
+      </c>
+      <c r="L113" s="3">
+        <v>4015</v>
+      </c>
+      <c r="M113" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" customHeight="1" spans="3:13">
+      <c r="C114" s="8">
+        <v>50000109</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="E114" s="2">
+        <v>5</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="G114" s="2">
+        <v>1</v>
+      </c>
+      <c r="H114" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I114" s="2">
+        <v>0</v>
+      </c>
+      <c r="J114" s="2">
+        <v>6</v>
+      </c>
+      <c r="K114" s="2">
+        <v>1450</v>
+      </c>
+      <c r="L114" s="3">
+        <v>4015</v>
+      </c>
+      <c r="M114" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" customHeight="1" spans="3:13">
+      <c r="C115" s="8">
+        <v>50000110</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>758</v>
+      </c>
+      <c r="E115" s="2">
+        <v>5</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="G115" s="2">
+        <v>1</v>
+      </c>
+      <c r="H115" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I115" s="2">
+        <v>0</v>
+      </c>
+      <c r="J115" s="2">
+        <v>6</v>
+      </c>
+      <c r="K115" s="2">
+        <v>1450</v>
+      </c>
+      <c r="L115" s="3">
+        <v>4015</v>
+      </c>
+      <c r="M115" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" customHeight="1" spans="3:13">
+      <c r="C116" s="8">
+        <v>50000111</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="E116" s="2">
+        <v>5</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="G116" s="2">
+        <v>1</v>
+      </c>
+      <c r="H116" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I116" s="2">
+        <v>0</v>
+      </c>
+      <c r="J116" s="2">
+        <v>6</v>
+      </c>
+      <c r="K116" s="2">
+        <v>1450</v>
+      </c>
+      <c r="L116" s="3">
+        <v>4015</v>
+      </c>
+      <c r="M116" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" customHeight="1" spans="3:13">
+      <c r="C117" s="6">
+        <v>50000112</v>
+      </c>
+      <c r="D117" s="7" t="s">
+        <v>762</v>
+      </c>
+      <c r="E117" s="6">
+        <v>5</v>
+      </c>
+      <c r="F117" s="6" t="s">
+        <v>763</v>
+      </c>
+      <c r="G117" s="6">
+        <v>1</v>
+      </c>
+      <c r="H117" s="6">
+        <v>99999</v>
+      </c>
+      <c r="I117" s="6">
+        <v>0</v>
+      </c>
+      <c r="J117" s="6">
+        <v>6</v>
+      </c>
+      <c r="K117" s="6">
+        <v>1450</v>
+      </c>
+      <c r="L117" s="7">
+        <v>4015</v>
+      </c>
+      <c r="M117" s="7">
         <v>1</v>
       </c>
     </row>
@@ -19711,13 +20037,13 @@
         <v>180001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>748</v>
+        <v>764</v>
       </c>
       <c r="E6" s="2">
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -19737,13 +20063,13 @@
         <v>180002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>750</v>
+        <v>766</v>
       </c>
       <c r="E7" s="2">
         <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -19763,13 +20089,13 @@
         <v>180003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>751</v>
+        <v>767</v>
       </c>
       <c r="E8" s="2">
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -19789,13 +20115,13 @@
         <v>180004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>752</v>
+        <v>768</v>
       </c>
       <c r="E9" s="2">
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -19815,13 +20141,13 @@
         <v>180005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>753</v>
+        <v>769</v>
       </c>
       <c r="E10" s="2">
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -19841,13 +20167,13 @@
         <v>180006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>754</v>
+        <v>770</v>
       </c>
       <c r="E11" s="2">
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -19869,13 +20195,13 @@
         <v>180007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>755</v>
+        <v>771</v>
       </c>
       <c r="E12" s="2">
         <v>18</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -19897,13 +20223,13 @@
         <v>180008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>756</v>
+        <v>772</v>
       </c>
       <c r="E13" s="2">
         <v>18</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -19925,13 +20251,13 @@
         <v>180009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>757</v>
+        <v>773</v>
       </c>
       <c r="E14" s="2">
         <v>18</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -19953,13 +20279,13 @@
         <v>180010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>758</v>
+        <v>774</v>
       </c>
       <c r="E15" s="2">
         <v>18</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -19981,13 +20307,13 @@
         <v>180011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>759</v>
+        <v>775</v>
       </c>
       <c r="E16" s="2">
         <v>18</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -20009,13 +20335,13 @@
         <v>180012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>760</v>
+        <v>776</v>
       </c>
       <c r="E17" s="2">
         <v>18</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -20037,13 +20363,13 @@
         <v>180013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>761</v>
+        <v>777</v>
       </c>
       <c r="E18" s="2">
         <v>18</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -20065,13 +20391,13 @@
         <v>180014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>762</v>
+        <v>778</v>
       </c>
       <c r="E19" s="2">
         <v>18</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -20093,13 +20419,13 @@
         <v>180015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>763</v>
+        <v>779</v>
       </c>
       <c r="E20" s="2">
         <v>18</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -20121,13 +20447,13 @@
         <v>180016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>764</v>
+        <v>780</v>
       </c>
       <c r="E21" s="2">
         <v>18</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -20149,13 +20475,13 @@
         <v>180017</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>765</v>
+        <v>781</v>
       </c>
       <c r="E22" s="2">
         <v>18</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -20177,13 +20503,13 @@
         <v>180018</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>766</v>
+        <v>782</v>
       </c>
       <c r="E23" s="2">
         <v>18</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -20205,13 +20531,13 @@
         <v>180019</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>767</v>
+        <v>783</v>
       </c>
       <c r="E24" s="2">
         <v>18</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -20233,13 +20559,13 @@
         <v>180020</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>768</v>
+        <v>784</v>
       </c>
       <c r="E25" s="2">
         <v>18</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -20261,13 +20587,13 @@
         <v>180021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>769</v>
+        <v>785</v>
       </c>
       <c r="E26" s="2">
         <v>18</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -20289,13 +20615,13 @@
         <v>180022</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>770</v>
+        <v>786</v>
       </c>
       <c r="E27" s="2">
         <v>18</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -20322,13 +20648,13 @@
         <v>180030</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>771</v>
+        <v>787</v>
       </c>
       <c r="E29" s="2">
         <v>18</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -20350,13 +20676,13 @@
         <v>180031</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>772</v>
+        <v>788</v>
       </c>
       <c r="E30" s="2">
         <v>18</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
       <c r="G30" s="3">
         <v>1</v>
@@ -20376,13 +20702,13 @@
         <v>180032</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>773</v>
+        <v>789</v>
       </c>
       <c r="E31" s="2">
         <v>18</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
       <c r="G31" s="3">
         <v>1</v>
@@ -20402,13 +20728,13 @@
         <v>180033</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>774</v>
+        <v>790</v>
       </c>
       <c r="E32" s="2">
         <v>18</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
       <c r="G32" s="3">
         <v>1</v>
@@ -20428,13 +20754,13 @@
         <v>180034</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>775</v>
+        <v>791</v>
       </c>
       <c r="E33" s="2">
         <v>18</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
       <c r="G33" s="3">
         <v>1</v>
@@ -20456,13 +20782,13 @@
         <v>180035</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>776</v>
+        <v>792</v>
       </c>
       <c r="E34" s="2">
         <v>18</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
       <c r="G34" s="3">
         <v>1</v>
@@ -20484,13 +20810,13 @@
         <v>180036</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>777</v>
+        <v>793</v>
       </c>
       <c r="E35" s="2">
         <v>18</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
       <c r="G35" s="3">
         <v>1</v>
@@ -20512,13 +20838,13 @@
         <v>180037</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>778</v>
+        <v>794</v>
       </c>
       <c r="E36" s="2">
         <v>18</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
       <c r="G36" s="3">
         <v>1</v>
@@ -20679,13 +21005,13 @@
         <v>190001</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>779</v>
+        <v>795</v>
       </c>
       <c r="E6" s="2">
         <v>19</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>780</v>
+        <v>796</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -20705,13 +21031,13 @@
         <v>190002</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>781</v>
+        <v>797</v>
       </c>
       <c r="E7" s="2">
         <v>19</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>780</v>
+        <v>796</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -20731,13 +21057,13 @@
         <v>190003</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>782</v>
+        <v>798</v>
       </c>
       <c r="E8" s="2">
         <v>19</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>780</v>
+        <v>796</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -20757,13 +21083,13 @@
         <v>190004</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>783</v>
+        <v>799</v>
       </c>
       <c r="E9" s="2">
         <v>19</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>780</v>
+        <v>796</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -20783,13 +21109,13 @@
         <v>190005</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>784</v>
+        <v>800</v>
       </c>
       <c r="E10" s="2">
         <v>19</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>780</v>
+        <v>796</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -20809,13 +21135,13 @@
         <v>190006</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>785</v>
+        <v>801</v>
       </c>
       <c r="E11" s="2">
         <v>19</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>780</v>
+        <v>796</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="5"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -344,7 +344,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1463" uniqueCount="802">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="832">
   <si>
     <t>_Id</t>
   </si>
@@ -892,6 +892,12 @@
     <t>金色魂宠进阶材料</t>
   </si>
   <si>
+    <t>暗金精华</t>
+  </si>
+  <si>
+    <t>分解暗金装备获取，暗金装备升阶材料</t>
+  </si>
+  <si>
     <t>图鉴碎片</t>
   </si>
   <si>
@@ -1966,6 +1972,111 @@
     <t>地狱龙爪</t>
   </si>
   <si>
+    <t>深渊鸡爪</t>
+  </si>
+  <si>
+    <t>深渊鹿茸</t>
+  </si>
+  <si>
+    <t>深渊草帽</t>
+  </si>
+  <si>
+    <t>深渊猫爪</t>
+  </si>
+  <si>
+    <t>深渊花朵</t>
+  </si>
+  <si>
+    <t>深渊冰晶</t>
+  </si>
+  <si>
+    <t>深渊蝠翼</t>
+  </si>
+  <si>
+    <t>深渊魂火</t>
+  </si>
+  <si>
+    <t>深渊腐肉</t>
+  </si>
+  <si>
+    <t>深渊蛇胆</t>
+  </si>
+  <si>
+    <t>深渊狼爪</t>
+  </si>
+  <si>
+    <t>深渊虫皮</t>
+  </si>
+  <si>
+    <t>深渊鹰羽</t>
+  </si>
+  <si>
+    <t>深渊虫角</t>
+  </si>
+  <si>
+    <t>深渊蜈膏</t>
+  </si>
+  <si>
+    <t>深渊虫心</t>
+  </si>
+  <si>
+    <t>深渊龙皮</t>
+  </si>
+  <si>
+    <t>深渊猪皮</t>
+  </si>
+  <si>
+    <t>深渊猪心</t>
+  </si>
+  <si>
+    <t>深渊蝎皮</t>
+  </si>
+  <si>
+    <t>深渊宝甲</t>
+  </si>
+  <si>
+    <t>深渊号角</t>
+  </si>
+  <si>
+    <t>深渊雕像</t>
+  </si>
+  <si>
+    <t>深渊神像</t>
+  </si>
+  <si>
+    <t>深渊獠牙</t>
+  </si>
+  <si>
+    <t>深渊树心</t>
+  </si>
+  <si>
+    <t>深渊魔心</t>
+  </si>
+  <si>
+    <t>深渊尸心</t>
+  </si>
+  <si>
+    <t>深渊法杖</t>
+  </si>
+  <si>
+    <t>深渊权杖</t>
+  </si>
+  <si>
+    <t>深渊战锤</t>
+  </si>
+  <si>
+    <t>深渊血核</t>
+  </si>
+  <si>
+    <t>深渊魔核</t>
+  </si>
+  <si>
+    <t>深渊龙甲</t>
+  </si>
+  <si>
+    <t>深渊龙爪</t>
+  </si>
+  <si>
     <t>二阶武器升阶石</t>
   </si>
   <si>
@@ -2587,55 +2698,34 @@
     <t>十四阶靴子升阶石</t>
   </si>
   <si>
-    <t>红色靴子升级十四阶的材料</t>
-  </si>
-  <si>
-    <t>十五阶武器升阶石</t>
-  </si>
-  <si>
-    <t>红色武器升级十五阶的材料</t>
-  </si>
-  <si>
-    <t>十五阶衣服升阶石</t>
-  </si>
-  <si>
-    <t>红色衣服升级十五阶的材料</t>
-  </si>
-  <si>
-    <t>十五阶项链升阶石</t>
-  </si>
-  <si>
-    <t>红色项链升级十五阶的材料</t>
-  </si>
-  <si>
-    <t>十五阶头盔升阶石</t>
-  </si>
-  <si>
-    <t>红色头盔升级十五阶的材料</t>
-  </si>
-  <si>
-    <t>十五阶手镯升阶石</t>
-  </si>
-  <si>
-    <t>红色手镯升级十五阶的材料</t>
-  </si>
-  <si>
-    <t>十五阶戒指升阶石</t>
-  </si>
-  <si>
-    <t>红色戒指升级十五阶的材料</t>
-  </si>
-  <si>
-    <t>十五阶腰带升阶石</t>
-  </si>
-  <si>
-    <t>红色腰带升级十五阶的材料</t>
-  </si>
-  <si>
-    <t>十五阶靴子升阶石</t>
-  </si>
-  <si>
-    <t>红色靴子升级十五阶的材料</t>
+    <t>红色装备升级十四阶的材料</t>
+  </si>
+  <si>
+    <t>十五阶装备升阶石</t>
+  </si>
+  <si>
+    <t>红色装备升级十五阶的材料</t>
+  </si>
+  <si>
+    <t>十六阶装备升阶石</t>
+  </si>
+  <si>
+    <t>十七阶装备升阶石</t>
+  </si>
+  <si>
+    <t>十八阶装备升阶石</t>
+  </si>
+  <si>
+    <t>十九阶装备升阶石</t>
+  </si>
+  <si>
+    <t>二十阶装备升阶石</t>
+  </si>
+  <si>
+    <t>二一阶装备升阶石</t>
+  </si>
+  <si>
+    <t>二二阶装备升阶石</t>
   </si>
   <si>
     <t>BOSS杀手</t>
@@ -6000,17 +6090,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="3"/>
-      <c r="L31" s="3"/>
-      <c r="M31" s="3"/>
+    <row r="31" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C31" s="3">
+        <v>4026</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E31" s="3">
+        <v>5</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G31" s="3">
+        <v>1</v>
+      </c>
+      <c r="H31" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I31" s="3">
+        <v>0</v>
+      </c>
+      <c r="J31" s="3">
+        <v>8</v>
+      </c>
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="32" customFormat="1" customHeight="1" spans="3:13">
       <c r="C32" s="3"/>
@@ -6029,13 +6139,13 @@
         <v>4101</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E33" s="3">
         <v>5</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G33" s="3">
         <v>1</v>
@@ -6061,13 +6171,13 @@
         <v>4102</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E34" s="3">
         <v>5</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G34" s="3">
         <v>1</v>
@@ -6093,7 +6203,7 @@
         <v>4103</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E35" s="3">
         <v>5</v>
@@ -6125,7 +6235,7 @@
         <v>4104</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E36" s="3">
         <v>5</v>
@@ -6157,7 +6267,7 @@
         <v>4105</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E37" s="3">
         <v>5</v>
@@ -6189,13 +6299,13 @@
         <v>4106</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E38" s="3">
         <v>5</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G38" s="3">
         <v>1</v>
@@ -6221,13 +6331,13 @@
         <v>4107</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E39" s="3">
         <v>5</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G39" s="3">
         <v>1</v>
@@ -6253,13 +6363,13 @@
         <v>4108</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E40" s="3">
         <v>5</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G40" s="3">
         <v>1</v>
@@ -6285,13 +6395,13 @@
         <v>4109</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E41" s="3">
         <v>5</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G41" s="3">
         <v>1</v>
@@ -6317,13 +6427,13 @@
         <v>4110</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E42" s="3">
         <v>5</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G42" s="3">
         <v>1</v>
@@ -6349,13 +6459,13 @@
         <v>4111</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E43" s="3">
         <v>5</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G43" s="3">
         <v>1</v>
@@ -6381,13 +6491,13 @@
         <v>4201</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E45" s="3">
         <v>5</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G45" s="3">
         <v>1</v>
@@ -6413,13 +6523,13 @@
         <v>4202</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E46" s="3">
         <v>5</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G46" s="3">
         <v>1</v>
@@ -6445,13 +6555,13 @@
         <v>6101</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E48" s="3">
         <v>7</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G48" s="3">
         <v>1</v>
@@ -6480,13 +6590,13 @@
         <v>6102</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E49" s="3">
         <v>7</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G49" s="3">
         <v>1</v>
@@ -6515,13 +6625,13 @@
         <v>6103</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E50" s="3">
         <v>7</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G50" s="3">
         <v>1</v>
@@ -6550,13 +6660,13 @@
         <v>6104</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E51" s="3">
         <v>7</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G51" s="3">
         <v>1</v>
@@ -6585,13 +6695,13 @@
         <v>6105</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E52" s="3">
         <v>7</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G52" s="3">
         <v>1</v>
@@ -6620,13 +6730,13 @@
         <v>6106</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E53" s="3">
         <v>7</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="G53" s="3">
         <v>1</v>
@@ -6655,13 +6765,13 @@
         <v>7101</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E54" s="3">
         <v>8</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G54" s="3">
         <v>1</v>
@@ -6690,13 +6800,13 @@
         <v>7102</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E55" s="3">
         <v>8</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G55" s="3">
         <v>1</v>
@@ -6725,13 +6835,13 @@
         <v>7103</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E56" s="3">
         <v>8</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G56" s="3">
         <v>1</v>
@@ -6760,13 +6870,13 @@
         <v>7104</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E57" s="3">
         <v>8</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="G57" s="3">
         <v>1</v>
@@ -6795,13 +6905,13 @@
         <v>7105</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E58" s="3">
         <v>8</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G58" s="3">
         <v>1</v>
@@ -6830,13 +6940,13 @@
         <v>7107</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E59" s="3">
         <v>8</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G59" s="3">
         <v>1</v>
@@ -6865,13 +6975,13 @@
         <v>8001</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E63" s="3">
         <v>5</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G63" s="3">
         <v>1</v>
@@ -6897,13 +7007,13 @@
         <v>8002</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E64" s="3">
         <v>5</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G64" s="3">
         <v>1</v>
@@ -6929,13 +7039,13 @@
         <v>8003</v>
       </c>
       <c r="D65" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="E65" s="3">
+        <v>5</v>
+      </c>
+      <c r="F65" s="3" t="s">
         <v>230</v>
-      </c>
-      <c r="E65" s="3">
-        <v>5</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>228</v>
       </c>
       <c r="G65" s="3">
         <v>1</v>
@@ -6961,13 +7071,13 @@
         <v>8004</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E66" s="3">
         <v>5</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G66" s="3">
         <v>1</v>
@@ -6993,13 +7103,13 @@
         <v>8005</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E67" s="3">
         <v>5</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G67" s="3">
         <v>1</v>
@@ -7025,13 +7135,13 @@
         <v>8006</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E68" s="3">
         <v>5</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G68" s="3">
         <v>1</v>
@@ -7057,13 +7167,13 @@
         <v>8007</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E69" s="3">
         <v>5</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G69" s="3">
         <v>1</v>
@@ -7089,13 +7199,13 @@
         <v>8008</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E70" s="3">
         <v>5</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G70" s="3">
         <v>1</v>
@@ -7121,13 +7231,13 @@
         <v>8009</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E71" s="3">
         <v>5</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G71" s="3">
         <v>1</v>
@@ -7153,13 +7263,13 @@
         <v>8010</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E72" s="3">
         <v>5</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G72" s="3">
         <v>1</v>
@@ -7185,13 +7295,13 @@
         <v>8101</v>
       </c>
       <c r="D74" s="13" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E74" s="3">
         <v>5</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G74" s="3">
         <v>1</v>
@@ -7217,13 +7327,13 @@
         <v>8102</v>
       </c>
       <c r="D75" s="13" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E75" s="3">
         <v>5</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G75" s="3">
         <v>1</v>
@@ -7249,13 +7359,13 @@
         <v>8103</v>
       </c>
       <c r="D76" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="E76" s="3">
+        <v>5</v>
+      </c>
+      <c r="F76" s="3" t="s">
         <v>241</v>
-      </c>
-      <c r="E76" s="3">
-        <v>5</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>239</v>
       </c>
       <c r="G76" s="3">
         <v>1</v>
@@ -7281,13 +7391,13 @@
         <v>8104</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E77" s="3">
         <v>5</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G77" s="3">
         <v>1</v>
@@ -7313,13 +7423,13 @@
         <v>8105</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E78" s="3">
         <v>5</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G78" s="3">
         <v>1</v>
@@ -7345,13 +7455,13 @@
         <v>8106</v>
       </c>
       <c r="D79" s="13" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E79" s="3">
         <v>5</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G79" s="3">
         <v>1</v>
@@ -7377,13 +7487,13 @@
         <v>8107</v>
       </c>
       <c r="D80" s="13" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E80" s="3">
         <v>5</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G80" s="3">
         <v>1</v>
@@ -7409,13 +7519,13 @@
         <v>8108</v>
       </c>
       <c r="D81" s="13" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E81" s="3">
         <v>5</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G81" s="3">
         <v>1</v>
@@ -7441,13 +7551,13 @@
         <v>8201</v>
       </c>
       <c r="D83" s="13" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E83" s="3">
         <v>16</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="G83" s="3">
         <v>1</v>
@@ -7476,13 +7586,13 @@
         <v>8202</v>
       </c>
       <c r="D84" s="13" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E84" s="3">
         <v>16</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G84" s="3">
         <v>1</v>
@@ -7511,13 +7621,13 @@
         <v>8203</v>
       </c>
       <c r="D85" s="13" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E85" s="3">
         <v>16</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G85" s="3">
         <v>1</v>
@@ -7546,13 +7656,13 @@
         <v>8204</v>
       </c>
       <c r="D86" s="13" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E86" s="3">
         <v>16</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G86" s="3">
         <v>1</v>
@@ -7581,13 +7691,13 @@
         <v>8205</v>
       </c>
       <c r="D87" s="13" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E87" s="3">
         <v>16</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="G87" s="3">
         <v>1</v>
@@ -7616,13 +7726,13 @@
         <v>8206</v>
       </c>
       <c r="D88" s="13" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E88" s="3">
         <v>16</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="G88" s="3">
         <v>1</v>
@@ -7651,13 +7761,13 @@
         <v>8207</v>
       </c>
       <c r="D89" s="13" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E89" s="3">
         <v>16</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="G89" s="3">
         <v>1</v>
@@ -7867,13 +7977,13 @@
         <v>1999001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E6" s="2">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -7895,13 +8005,13 @@
         <v>1999002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E7" s="2">
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -7923,13 +8033,13 @@
         <v>1999003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E8" s="2">
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -7951,13 +8061,13 @@
         <v>1999004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E9" s="2">
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -7979,13 +8089,13 @@
         <v>1999005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E10" s="2">
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -8007,13 +8117,13 @@
         <v>1999006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E11" s="2">
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -8040,13 +8150,13 @@
         <v>1999989</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E13" s="2">
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -8068,13 +8178,13 @@
         <v>1999990</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E14" s="2">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -8096,13 +8206,13 @@
         <v>1999991</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E15" s="2">
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -8124,13 +8234,13 @@
         <v>1999992</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E16" s="2">
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -8152,13 +8262,13 @@
         <v>1999993</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E17" s="2">
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -8180,13 +8290,13 @@
         <v>1999994</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E18" s="2">
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -8208,13 +8318,13 @@
         <v>1999995</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E19" s="2">
         <v>11</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -8236,13 +8346,13 @@
         <v>1999996</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E20" s="2">
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -8264,13 +8374,13 @@
         <v>1999997</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E21" s="2">
         <v>11</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -8292,13 +8402,13 @@
         <v>2000000</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E22" s="2">
         <v>11</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -8320,13 +8430,13 @@
         <v>2000001</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E23" s="2">
         <v>11</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -8348,13 +8458,13 @@
         <v>2000002</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E24" s="2">
         <v>11</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -8376,13 +8486,13 @@
         <v>2000003</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E25" s="2">
         <v>11</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -8404,13 +8514,13 @@
         <v>2000004</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E26" s="2">
         <v>11</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -8432,13 +8542,13 @@
         <v>2000005</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E27" s="2">
         <v>11</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -8460,13 +8570,13 @@
         <v>2000006</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E28" s="2">
         <v>11</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -8488,13 +8598,13 @@
         <v>2000007</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E29" s="2">
         <v>11</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -8516,13 +8626,13 @@
         <v>2000008</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E30" s="2">
         <v>11</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -8544,13 +8654,13 @@
         <v>2000009</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E31" s="2">
         <v>11</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -8572,13 +8682,13 @@
         <v>2000010</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E32" s="2">
         <v>11</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -8600,13 +8710,13 @@
         <v>2000011</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E33" s="2">
         <v>11</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -8628,13 +8738,13 @@
         <v>2000012</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E34" s="2">
         <v>11</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -8656,13 +8766,13 @@
         <v>2000013</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E35" s="2">
         <v>11</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -8696,13 +8806,13 @@
         <v>2000100</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E39" s="2">
         <v>11</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -8724,13 +8834,13 @@
         <v>2000101</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E40" s="2">
         <v>11</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -8752,13 +8862,13 @@
         <v>2000102</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E41" s="2">
         <v>11</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -8780,13 +8890,13 @@
         <v>2000103</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E42" s="2">
         <v>11</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -8808,13 +8918,13 @@
         <v>2000104</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E43" s="2">
         <v>11</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -8836,13 +8946,13 @@
         <v>2000105</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E44" s="2">
         <v>11</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -8864,13 +8974,13 @@
         <v>2000106</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E45" s="2">
         <v>11</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G45" s="2">
         <v>1</v>
@@ -8892,13 +9002,13 @@
         <v>2000107</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E46" s="2">
         <v>11</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -8920,13 +9030,13 @@
         <v>2000108</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E47" s="2">
         <v>11</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -8948,13 +9058,13 @@
         <v>2000109</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E48" s="2">
         <v>11</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -8976,13 +9086,13 @@
         <v>2000110</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E49" s="2">
         <v>11</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -9004,13 +9114,13 @@
         <v>2000111</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E50" s="2">
         <v>11</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -9032,13 +9142,13 @@
         <v>2000112</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E51" s="2">
         <v>11</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -9060,13 +9170,13 @@
         <v>2000113</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E52" s="2">
         <v>11</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -9088,13 +9198,13 @@
         <v>2000114</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E53" s="2">
         <v>11</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G53" s="2">
         <v>1</v>
@@ -9116,13 +9226,13 @@
         <v>2000115</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E54" s="2">
         <v>11</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G54" s="2">
         <v>1</v>
@@ -9144,13 +9254,13 @@
         <v>2000116</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E55" s="2">
         <v>11</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G55" s="2">
         <v>1</v>
@@ -9172,13 +9282,13 @@
         <v>2000117</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E56" s="2">
         <v>11</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G56" s="2">
         <v>1</v>
@@ -9200,13 +9310,13 @@
         <v>2000118</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E57" s="2">
         <v>11</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G57" s="2">
         <v>1</v>
@@ -9228,13 +9338,13 @@
         <v>2000119</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E58" s="2">
         <v>11</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G58" s="2">
         <v>1</v>
@@ -9256,13 +9366,13 @@
         <v>2000120</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E59" s="2">
         <v>11</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G59" s="2">
         <v>1</v>
@@ -9284,13 +9394,13 @@
         <v>2000121</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E60" s="2">
         <v>11</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G60" s="2">
         <v>1</v>
@@ -9312,13 +9422,13 @@
         <v>2000122</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E61" s="2">
         <v>11</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G61" s="2">
         <v>1</v>
@@ -9340,13 +9450,13 @@
         <v>2000123</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E62" s="2">
         <v>11</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G62" s="2">
         <v>1</v>
@@ -9368,13 +9478,13 @@
         <v>2000124</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E63" s="2">
         <v>11</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G63" s="2">
         <v>1</v>
@@ -9396,13 +9506,13 @@
         <v>2000125</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E64" s="2">
         <v>11</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G64" s="2">
         <v>1</v>
@@ -9424,13 +9534,13 @@
         <v>2000126</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E65" s="2">
         <v>11</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G65" s="2">
         <v>1</v>
@@ -9452,13 +9562,13 @@
         <v>2000127</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E66" s="2">
         <v>11</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G66" s="2">
         <v>1</v>
@@ -9480,13 +9590,13 @@
         <v>2000128</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E67" s="2">
         <v>11</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G67" s="2">
         <v>1</v>
@@ -9508,13 +9618,13 @@
         <v>2000129</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E68" s="2">
         <v>11</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G68" s="2">
         <v>1</v>
@@ -9536,13 +9646,13 @@
         <v>2000200</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E70" s="2">
         <v>11</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G70" s="2">
         <v>1</v>
@@ -9562,13 +9672,13 @@
         <v>2000201</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E71" s="2">
         <v>11</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G71" s="2">
         <v>1</v>
@@ -9588,13 +9698,13 @@
         <v>2000202</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E72" s="2">
         <v>11</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G72" s="2">
         <v>1</v>
@@ -9614,13 +9724,13 @@
         <v>2000203</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E73" s="2">
         <v>11</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G73" s="2">
         <v>1</v>
@@ -9640,13 +9750,13 @@
         <v>2000204</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E74" s="2">
         <v>11</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G74" s="2">
         <v>1</v>
@@ -9666,13 +9776,13 @@
         <v>2000205</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E75" s="2">
         <v>11</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G75" s="2">
         <v>1</v>
@@ -9692,13 +9802,13 @@
         <v>2000206</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E76" s="2">
         <v>11</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G76" s="2">
         <v>1</v>
@@ -9718,13 +9828,13 @@
         <v>2000207</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E77" s="2">
         <v>11</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G77" s="2">
         <v>1</v>
@@ -9744,13 +9854,13 @@
         <v>2000208</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E78" s="2">
         <v>11</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G78" s="2">
         <v>1</v>
@@ -9770,13 +9880,13 @@
         <v>2000209</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E79" s="2">
         <v>11</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G79" s="2">
         <v>1</v>
@@ -9796,13 +9906,13 @@
         <v>2000210</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E80" s="2">
         <v>11</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G80" s="2">
         <v>1</v>
@@ -9822,13 +9932,13 @@
         <v>2000211</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E81" s="2">
         <v>11</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G81" s="2">
         <v>1</v>
@@ -9848,13 +9958,13 @@
         <v>2000212</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E82" s="2">
         <v>11</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G82" s="2">
         <v>1</v>
@@ -9874,13 +9984,13 @@
         <v>2000213</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E83" s="2">
         <v>11</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G83" s="2">
         <v>1</v>
@@ -9900,13 +10010,13 @@
         <v>2000214</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E84" s="2">
         <v>11</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G84" s="2">
         <v>1</v>
@@ -9926,13 +10036,13 @@
         <v>2000215</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E85" s="2">
         <v>11</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G85" s="2">
         <v>1</v>
@@ -9952,13 +10062,13 @@
         <v>2000216</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E86" s="2">
         <v>11</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G86" s="2">
         <v>1</v>
@@ -9978,13 +10088,13 @@
         <v>2000217</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E87" s="2">
         <v>11</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G87" s="2">
         <v>1</v>
@@ -10004,13 +10114,13 @@
         <v>2000218</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E88" s="2">
         <v>11</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G88" s="2">
         <v>1</v>
@@ -10030,13 +10140,13 @@
         <v>2000219</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E89" s="2">
         <v>11</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G89" s="2">
         <v>1</v>
@@ -10056,13 +10166,13 @@
         <v>2000220</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E90" s="2">
         <v>11</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G90" s="2">
         <v>1</v>
@@ -10082,13 +10192,13 @@
         <v>2000221</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E91" s="2">
         <v>11</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G91" s="2">
         <v>1</v>
@@ -10108,13 +10218,13 @@
         <v>2000222</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E92" s="2">
         <v>11</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G92" s="2">
         <v>1</v>
@@ -10134,13 +10244,13 @@
         <v>2000223</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E93" s="2">
         <v>11</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G93" s="2">
         <v>1</v>
@@ -10160,13 +10270,13 @@
         <v>2000224</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E94" s="2">
         <v>11</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G94" s="2">
         <v>1</v>
@@ -10186,13 +10296,13 @@
         <v>2000225</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E95" s="2">
         <v>11</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G95" s="2">
         <v>1</v>
@@ -10212,13 +10322,13 @@
         <v>2000226</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E96" s="2">
         <v>11</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G96" s="2">
         <v>1</v>
@@ -10238,13 +10348,13 @@
         <v>2000227</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E97" s="2">
         <v>11</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G97" s="2">
         <v>1</v>
@@ -10264,13 +10374,13 @@
         <v>2000228</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E98" s="2">
         <v>11</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G98" s="2">
         <v>1</v>
@@ -10290,13 +10400,13 @@
         <v>2000229</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E99" s="2">
         <v>11</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G99" s="2">
         <v>1</v>
@@ -10316,13 +10426,13 @@
         <v>2000300</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E102" s="2">
         <v>11</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G102" s="2">
         <v>1</v>
@@ -10342,13 +10452,13 @@
         <v>2000301</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E103" s="2">
         <v>11</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G103" s="2">
         <v>1</v>
@@ -10368,13 +10478,13 @@
         <v>2000302</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E104" s="2">
         <v>11</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G104" s="2">
         <v>1</v>
@@ -10394,13 +10504,13 @@
         <v>2000303</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E105" s="2">
         <v>11</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G105" s="2">
         <v>1</v>
@@ -10420,13 +10530,13 @@
         <v>2000304</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E106" s="2">
         <v>11</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G106" s="2">
         <v>1</v>
@@ -10446,13 +10556,13 @@
         <v>2000305</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E107" s="2">
         <v>11</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G107" s="2">
         <v>1</v>
@@ -10472,13 +10582,13 @@
         <v>2000306</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E108" s="2">
         <v>11</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G108" s="2">
         <v>1</v>
@@ -10498,13 +10608,13 @@
         <v>2000307</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E109" s="2">
         <v>11</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G109" s="2">
         <v>1</v>
@@ -10524,13 +10634,13 @@
         <v>2000308</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E110" s="2">
         <v>11</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G110" s="2">
         <v>1</v>
@@ -10550,13 +10660,13 @@
         <v>2000309</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E111" s="2">
         <v>11</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G111" s="2">
         <v>1</v>
@@ -10576,13 +10686,13 @@
         <v>2000310</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E112" s="2">
         <v>11</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G112" s="2">
         <v>1</v>
@@ -10602,13 +10712,13 @@
         <v>2000311</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E113" s="2">
         <v>11</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G113" s="2">
         <v>1</v>
@@ -10628,13 +10738,13 @@
         <v>2000312</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E114" s="2">
         <v>11</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G114" s="2">
         <v>1</v>
@@ -10654,13 +10764,13 @@
         <v>2000313</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E115" s="2">
         <v>11</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G115" s="2">
         <v>1</v>
@@ -10680,13 +10790,13 @@
         <v>2000314</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E116" s="2">
         <v>11</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G116" s="2">
         <v>1</v>
@@ -10706,13 +10816,13 @@
         <v>2000315</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E117" s="2">
         <v>11</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G117" s="2">
         <v>1</v>
@@ -10732,13 +10842,13 @@
         <v>2000316</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E118" s="2">
         <v>11</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G118" s="2">
         <v>1</v>
@@ -10758,13 +10868,13 @@
         <v>2000317</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E119" s="2">
         <v>11</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G119" s="2">
         <v>1</v>
@@ -10784,13 +10894,13 @@
         <v>2000318</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E120" s="2">
         <v>11</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G120" s="2">
         <v>1</v>
@@ -10810,13 +10920,13 @@
         <v>2000319</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E121" s="2">
         <v>11</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G121" s="2">
         <v>1</v>
@@ -10836,13 +10946,13 @@
         <v>2000320</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E122" s="2">
         <v>11</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G122" s="2">
         <v>1</v>
@@ -10862,13 +10972,13 @@
         <v>2000321</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E123" s="2">
         <v>11</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G123" s="2">
         <v>1</v>
@@ -10888,13 +10998,13 @@
         <v>2000322</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E124" s="2">
         <v>11</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G124" s="2">
         <v>1</v>
@@ -10914,13 +11024,13 @@
         <v>2000323</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E125" s="2">
         <v>11</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G125" s="2">
         <v>1</v>
@@ -10940,13 +11050,13 @@
         <v>2000324</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E126" s="2">
         <v>11</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G126" s="2">
         <v>1</v>
@@ -10966,13 +11076,13 @@
         <v>2000325</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E127" s="2">
         <v>11</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G127" s="2">
         <v>1</v>
@@ -10992,13 +11102,13 @@
         <v>2000326</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E128" s="2">
         <v>11</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G128" s="2">
         <v>1</v>
@@ -11018,13 +11128,13 @@
         <v>2000327</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E129" s="2">
         <v>11</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G129" s="2">
         <v>1</v>
@@ -11044,13 +11154,13 @@
         <v>2000328</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E130" s="2">
         <v>11</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G130" s="2">
         <v>1</v>
@@ -11070,13 +11180,13 @@
         <v>2000329</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E131" s="2">
         <v>11</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G131" s="2">
         <v>1</v>
@@ -11235,13 +11345,13 @@
         <v>3000001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E6" s="2">
         <v>13</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -11263,13 +11373,13 @@
         <v>3000002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E7" s="2">
         <v>13</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -11291,13 +11401,13 @@
         <v>3000003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E8" s="2">
         <v>13</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -11319,13 +11429,13 @@
         <v>3000004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E9" s="2">
         <v>13</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -11347,13 +11457,13 @@
         <v>3000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E10" s="2">
         <v>13</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -11375,13 +11485,13 @@
         <v>3000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E11" s="2">
         <v>13</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -11403,13 +11513,13 @@
         <v>3000007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E12" s="2">
         <v>13</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -11431,13 +11541,13 @@
         <v>3000008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E13" s="2">
         <v>13</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -11459,13 +11569,13 @@
         <v>3000009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E14" s="2">
         <v>13</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -11487,13 +11597,13 @@
         <v>3000010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E15" s="2">
         <v>13</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -11515,13 +11625,13 @@
         <v>3000011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E16" s="2">
         <v>13</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -11543,13 +11653,13 @@
         <v>3000012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E17" s="2">
         <v>13</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -11571,13 +11681,13 @@
         <v>3000013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E18" s="2">
         <v>13</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -11599,13 +11709,13 @@
         <v>3000014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E19" s="2">
         <v>13</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -11627,13 +11737,13 @@
         <v>3000015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E20" s="2">
         <v>13</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -11655,13 +11765,13 @@
         <v>3000016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E21" s="2">
         <v>13</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -11683,13 +11793,13 @@
         <v>3000017</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E22" s="2">
         <v>13</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -11711,13 +11821,13 @@
         <v>3000018</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E23" s="2">
         <v>13</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -11739,13 +11849,13 @@
         <v>3000019</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E24" s="2">
         <v>13</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -11767,13 +11877,13 @@
         <v>3000020</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E25" s="2">
         <v>13</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -11795,13 +11905,13 @@
         <v>3000021</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E26" s="2">
         <v>13</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -11823,13 +11933,13 @@
         <v>3000022</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E27" s="2">
         <v>13</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -11851,13 +11961,13 @@
         <v>3000023</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E28" s="2">
         <v>13</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -11879,13 +11989,13 @@
         <v>3000024</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E29" s="2">
         <v>13</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -11907,13 +12017,13 @@
         <v>3000025</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E30" s="2">
         <v>13</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -11935,13 +12045,13 @@
         <v>3000026</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E31" s="2">
         <v>13</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -11963,13 +12073,13 @@
         <v>3000027</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="E32" s="2">
         <v>13</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -11991,13 +12101,13 @@
         <v>3000028</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E33" s="2">
         <v>13</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -12019,13 +12129,13 @@
         <v>3000029</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E34" s="2">
         <v>13</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -12047,13 +12157,13 @@
         <v>3000030</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E35" s="2">
         <v>13</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -12075,13 +12185,13 @@
         <v>3000031</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E36" s="2">
         <v>13</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -12103,13 +12213,13 @@
         <v>3000032</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E37" s="2">
         <v>13</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G37" s="2">
         <v>1</v>
@@ -12131,13 +12241,13 @@
         <v>3000033</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E38" s="2">
         <v>13</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G38" s="2">
         <v>1</v>
@@ -12159,13 +12269,13 @@
         <v>3000034</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E39" s="2">
         <v>13</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -12187,13 +12297,13 @@
         <v>3000035</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E40" s="2">
         <v>13</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -12215,13 +12325,13 @@
         <v>3000036</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E41" s="2">
         <v>13</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -12243,13 +12353,13 @@
         <v>3000037</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E42" s="2">
         <v>13</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -12271,13 +12381,13 @@
         <v>3000038</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E43" s="2">
         <v>13</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -12299,13 +12409,13 @@
         <v>3000039</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E44" s="2">
         <v>13</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -12327,13 +12437,13 @@
         <v>3000040</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E45" s="2">
         <v>13</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G45" s="2">
         <v>1</v>
@@ -12355,13 +12465,13 @@
         <v>3000041</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E46" s="2">
         <v>13</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -12383,13 +12493,13 @@
         <v>3000042</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E47" s="2">
         <v>13</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -12411,13 +12521,13 @@
         <v>3000043</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E48" s="2">
         <v>13</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -12439,13 +12549,13 @@
         <v>3000044</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E49" s="2">
         <v>13</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -12467,13 +12577,13 @@
         <v>3000045</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E50" s="2">
         <v>13</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -12495,13 +12605,13 @@
         <v>3000046</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E51" s="2">
         <v>13</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -12523,13 +12633,13 @@
         <v>3000047</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E52" s="2">
         <v>13</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -12551,13 +12661,13 @@
         <v>3000048</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E53" s="2">
         <v>13</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G53" s="2">
         <v>1</v>
@@ -12590,7 +12700,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:M95"/>
+  <dimension ref="C1:M130"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="2"/>
@@ -12720,13 +12830,13 @@
         <v>40000051</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E7" s="2">
         <v>14</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -12741,7 +12851,7 @@
         <v>6</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="L7" s="3">
         <v>4018</v>
@@ -12755,13 +12865,13 @@
         <v>40000052</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E8" s="2">
         <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -12776,7 +12886,7 @@
         <v>6</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="L8" s="3">
         <v>4018</v>
@@ -12790,13 +12900,13 @@
         <v>40000053</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E9" s="2">
         <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -12811,7 +12921,7 @@
         <v>6</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="L9" s="3">
         <v>4018</v>
@@ -12825,13 +12935,13 @@
         <v>40000054</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E10" s="2">
         <v>14</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -12846,7 +12956,7 @@
         <v>6</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L10" s="3">
         <v>4018</v>
@@ -12860,13 +12970,13 @@
         <v>40000055</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E11" s="2">
         <v>14</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -12881,7 +12991,7 @@
         <v>6</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L11" s="3">
         <v>4018</v>
@@ -12895,13 +13005,13 @@
         <v>40000056</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E12" s="2">
         <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -12916,7 +13026,7 @@
         <v>6</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="L12" s="3">
         <v>4018</v>
@@ -12930,13 +13040,13 @@
         <v>40000057</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E13" s="2">
         <v>14</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -12951,7 +13061,7 @@
         <v>6</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="L13" s="3">
         <v>4018</v>
@@ -12965,13 +13075,13 @@
         <v>40000058</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E14" s="2">
         <v>14</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -12986,7 +13096,7 @@
         <v>6</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="L14" s="3">
         <v>4018</v>
@@ -13000,13 +13110,13 @@
         <v>40000059</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E15" s="2">
         <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -13021,7 +13131,7 @@
         <v>6</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L15" s="3">
         <v>4018</v>
@@ -13035,13 +13145,13 @@
         <v>40000060</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E16" s="2">
         <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -13056,7 +13166,7 @@
         <v>6</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="L16" s="3">
         <v>4018</v>
@@ -13070,13 +13180,13 @@
         <v>40000061</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E17" s="2">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -13091,7 +13201,7 @@
         <v>6</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="L17" s="3">
         <v>4018</v>
@@ -13105,13 +13215,13 @@
         <v>40000062</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E18" s="2">
         <v>14</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -13126,7 +13236,7 @@
         <v>6</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="L18" s="3">
         <v>4018</v>
@@ -13140,13 +13250,13 @@
         <v>40000063</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E19" s="2">
         <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -13161,7 +13271,7 @@
         <v>6</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="L19" s="3">
         <v>4018</v>
@@ -13175,13 +13285,13 @@
         <v>40000064</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E20" s="2">
         <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -13196,7 +13306,7 @@
         <v>6</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="L20" s="3">
         <v>4018</v>
@@ -13210,13 +13320,13 @@
         <v>40000065</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E21" s="2">
         <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -13231,7 +13341,7 @@
         <v>6</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L21" s="3">
         <v>4018</v>
@@ -13245,13 +13355,13 @@
         <v>40000066</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E22" s="2">
         <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -13266,7 +13376,7 @@
         <v>6</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="L22" s="3">
         <v>4018</v>
@@ -13280,13 +13390,13 @@
         <v>40000067</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E23" s="2">
         <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -13301,7 +13411,7 @@
         <v>6</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="L23" s="3">
         <v>4018</v>
@@ -13315,13 +13425,13 @@
         <v>40000068</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="E24" s="2">
         <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -13336,7 +13446,7 @@
         <v>6</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="L24" s="3">
         <v>4018</v>
@@ -13350,13 +13460,13 @@
         <v>40000069</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E25" s="2">
         <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -13371,7 +13481,7 @@
         <v>6</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="L25" s="3">
         <v>4018</v>
@@ -13385,13 +13495,13 @@
         <v>40000070</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E26" s="2">
         <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -13420,13 +13530,13 @@
         <v>40000071</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E27" s="2">
         <v>14</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -13455,13 +13565,13 @@
         <v>40000072</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E28" s="2">
         <v>14</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -13490,13 +13600,13 @@
         <v>40000073</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E29" s="2">
         <v>14</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -13525,13 +13635,13 @@
         <v>40000074</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E30" s="2">
         <v>14</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -13560,13 +13670,13 @@
         <v>40000075</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E31" s="2">
         <v>14</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -13595,13 +13705,13 @@
         <v>40000076</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E32" s="2">
         <v>14</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -13630,13 +13740,13 @@
         <v>40000077</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="E33" s="2">
         <v>14</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -13665,13 +13775,13 @@
         <v>40000078</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E34" s="2">
         <v>14</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -13700,13 +13810,13 @@
         <v>40000079</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E35" s="2">
         <v>14</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -13735,13 +13845,13 @@
         <v>40000080</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E36" s="2">
         <v>14</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -13770,13 +13880,13 @@
         <v>40000081</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E37" s="2">
         <v>14</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G37" s="2">
         <v>1</v>
@@ -13805,13 +13915,13 @@
         <v>40000082</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E38" s="2">
         <v>14</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G38" s="2">
         <v>1</v>
@@ -13840,13 +13950,13 @@
         <v>40000083</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E39" s="2">
         <v>14</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -13875,13 +13985,13 @@
         <v>40000084</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E40" s="2">
         <v>14</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -13910,13 +14020,13 @@
         <v>40000085</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="E41" s="2">
         <v>14</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -13945,13 +14055,13 @@
         <v>40000086</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E42" s="2">
         <v>14</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -13980,13 +14090,13 @@
         <v>40000087</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E43" s="2">
         <v>14</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -14015,13 +14125,13 @@
         <v>40000088</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="E44" s="2">
         <v>14</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -14050,13 +14160,13 @@
         <v>40000089</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E45" s="2">
         <v>14</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G45" s="2">
         <v>1</v>
@@ -14085,13 +14195,13 @@
         <v>40000090</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E46" s="2">
         <v>14</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -14120,13 +14230,13 @@
         <v>40000091</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E47" s="2">
         <v>14</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -14155,13 +14265,13 @@
         <v>40000092</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E48" s="2">
         <v>14</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -14190,13 +14300,13 @@
         <v>40000093</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="E49" s="2">
         <v>14</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -14225,13 +14335,13 @@
         <v>40000094</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E50" s="2">
         <v>14</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -14260,13 +14370,13 @@
         <v>40000095</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E51" s="2">
         <v>14</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -14295,13 +14405,13 @@
         <v>40000096</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="E52" s="2">
         <v>14</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -14330,13 +14440,13 @@
         <v>40000097</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E53" s="2">
         <v>14</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G53" s="2">
         <v>1</v>
@@ -14365,13 +14475,13 @@
         <v>40000098</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="E54" s="2">
         <v>14</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G54" s="2">
         <v>1</v>
@@ -14400,13 +14510,13 @@
         <v>40000099</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E55" s="2">
         <v>14</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G55" s="2">
         <v>1</v>
@@ -14435,13 +14545,13 @@
         <v>40000100</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="E56" s="2">
         <v>14</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G56" s="2">
         <v>1</v>
@@ -14470,13 +14580,13 @@
         <v>40000101</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="E57" s="2">
         <v>14</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G57" s="2">
         <v>1</v>
@@ -14505,13 +14615,13 @@
         <v>40000102</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="E58" s="2">
         <v>14</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G58" s="2">
         <v>1</v>
@@ -14540,13 +14650,13 @@
         <v>40000103</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E59" s="2">
         <v>14</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G59" s="2">
         <v>1</v>
@@ -14575,13 +14685,13 @@
         <v>40000104</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E60" s="2">
         <v>14</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G60" s="2">
         <v>1</v>
@@ -14610,13 +14720,13 @@
         <v>40000105</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="E61" s="9">
         <v>14</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G61" s="9">
         <v>1</v>
@@ -14645,13 +14755,13 @@
         <v>40000106</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="E62" s="2">
         <v>14</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G62" s="2">
         <v>1</v>
@@ -14680,13 +14790,13 @@
         <v>40000107</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E63" s="2">
         <v>14</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G63" s="2">
         <v>1</v>
@@ -14715,13 +14825,13 @@
         <v>40000108</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="E64" s="2">
         <v>14</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G64" s="2">
         <v>1</v>
@@ -14750,13 +14860,13 @@
         <v>40000109</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="E65" s="2">
         <v>14</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G65" s="2">
         <v>1</v>
@@ -14785,13 +14895,13 @@
         <v>40000110</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E66" s="2">
         <v>14</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G66" s="2">
         <v>1</v>
@@ -14820,13 +14930,13 @@
         <v>40000111</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="E67" s="2">
         <v>14</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G67" s="2">
         <v>1</v>
@@ -14855,13 +14965,13 @@
         <v>40000112</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E68" s="2">
         <v>14</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G68" s="2">
         <v>1</v>
@@ -14890,13 +15000,13 @@
         <v>40000113</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E69" s="2">
         <v>14</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G69" s="2">
         <v>1</v>
@@ -14925,13 +15035,13 @@
         <v>40000114</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E70" s="2">
         <v>14</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G70" s="2">
         <v>1</v>
@@ -14960,13 +15070,13 @@
         <v>40000115</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E71" s="2">
         <v>14</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G71" s="2">
         <v>1</v>
@@ -14995,13 +15105,13 @@
         <v>40000116</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E72" s="2">
         <v>14</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G72" s="2">
         <v>1</v>
@@ -15030,13 +15140,13 @@
         <v>40000117</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E73" s="2">
         <v>14</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G73" s="2">
         <v>1</v>
@@ -15065,13 +15175,13 @@
         <v>40000118</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E74" s="2">
         <v>14</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G74" s="2">
         <v>1</v>
@@ -15100,13 +15210,13 @@
         <v>40000119</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E75" s="2">
         <v>14</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G75" s="2">
         <v>1</v>
@@ -15135,13 +15245,13 @@
         <v>40000120</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="E76" s="2">
         <v>14</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G76" s="2">
         <v>1</v>
@@ -15170,13 +15280,13 @@
         <v>40000121</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E77" s="2">
         <v>14</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G77" s="2">
         <v>1</v>
@@ -15205,13 +15315,13 @@
         <v>40000122</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E78" s="2">
         <v>14</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G78" s="2">
         <v>1</v>
@@ -15240,13 +15350,13 @@
         <v>40000123</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E79" s="2">
         <v>14</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G79" s="2">
         <v>1</v>
@@ -15275,13 +15385,13 @@
         <v>40000124</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E80" s="2">
         <v>14</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G80" s="2">
         <v>1</v>
@@ -15310,13 +15420,13 @@
         <v>40000125</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="E81" s="2">
         <v>14</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G81" s="2">
         <v>1</v>
@@ -15345,13 +15455,13 @@
         <v>40000126</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E82" s="2">
         <v>14</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G82" s="2">
         <v>1</v>
@@ -15380,13 +15490,13 @@
         <v>40000127</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="E83" s="2">
         <v>14</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G83" s="2">
         <v>1</v>
@@ -15415,13 +15525,13 @@
         <v>40000128</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E84" s="2">
         <v>14</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G84" s="2">
         <v>1</v>
@@ -15450,13 +15560,13 @@
         <v>40000129</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E85" s="2">
         <v>14</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G85" s="2">
         <v>1</v>
@@ -15485,13 +15595,13 @@
         <v>40000130</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="E86" s="2">
         <v>14</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G86" s="2">
         <v>1</v>
@@ -15520,13 +15630,13 @@
         <v>40000131</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E87" s="2">
         <v>14</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G87" s="2">
         <v>1</v>
@@ -15555,13 +15665,13 @@
         <v>40000132</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E88" s="2">
         <v>14</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G88" s="2">
         <v>1</v>
@@ -15590,13 +15700,13 @@
         <v>40000133</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="E89" s="2">
         <v>14</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G89" s="2">
         <v>1</v>
@@ -15625,13 +15735,13 @@
         <v>40000134</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E90" s="2">
         <v>14</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G90" s="2">
         <v>1</v>
@@ -15660,13 +15770,13 @@
         <v>40000135</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="E91" s="2">
         <v>14</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G91" s="2">
         <v>1</v>
@@ -15695,13 +15805,13 @@
         <v>40000136</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="E92" s="2">
         <v>14</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G92" s="2">
         <v>1</v>
@@ -15730,13 +15840,13 @@
         <v>40000137</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E93" s="2">
         <v>14</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G93" s="2">
         <v>1</v>
@@ -15765,13 +15875,13 @@
         <v>40000138</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="E94" s="2">
         <v>14</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G94" s="2">
         <v>1</v>
@@ -15800,13 +15910,13 @@
         <v>40000139</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="E95" s="2">
         <v>14</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G95" s="2">
         <v>1</v>
@@ -15827,6 +15937,1231 @@
         <v>4018</v>
       </c>
       <c r="M95" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" s="9" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C96" s="9">
+        <v>40000140</v>
+      </c>
+      <c r="D96" s="10" t="s">
+        <v>542</v>
+      </c>
+      <c r="E96" s="9">
+        <v>14</v>
+      </c>
+      <c r="F96" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="G96" s="9">
+        <v>1</v>
+      </c>
+      <c r="H96" s="9">
+        <v>99999</v>
+      </c>
+      <c r="I96" s="9">
+        <v>0</v>
+      </c>
+      <c r="J96" s="9">
+        <v>6</v>
+      </c>
+      <c r="K96" s="9">
+        <v>1450</v>
+      </c>
+      <c r="L96" s="10">
+        <v>4018</v>
+      </c>
+      <c r="M96" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" customHeight="1" spans="3:13">
+      <c r="C97" s="2">
+        <v>40000141</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="E97" s="2">
+        <v>14</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G97" s="2">
+        <v>1</v>
+      </c>
+      <c r="H97" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I97" s="2">
+        <v>0</v>
+      </c>
+      <c r="J97" s="2">
+        <v>6</v>
+      </c>
+      <c r="K97" s="2">
+        <v>1450</v>
+      </c>
+      <c r="L97" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M97" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" customHeight="1" spans="3:13">
+      <c r="C98" s="2">
+        <v>40000142</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="E98" s="2">
+        <v>14</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G98" s="2">
+        <v>1</v>
+      </c>
+      <c r="H98" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I98" s="2">
+        <v>0</v>
+      </c>
+      <c r="J98" s="2">
+        <v>6</v>
+      </c>
+      <c r="K98" s="2">
+        <v>1450</v>
+      </c>
+      <c r="L98" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M98" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" customHeight="1" spans="3:13">
+      <c r="C99" s="2">
+        <v>40000143</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="E99" s="2">
+        <v>14</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G99" s="2">
+        <v>1</v>
+      </c>
+      <c r="H99" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I99" s="2">
+        <v>0</v>
+      </c>
+      <c r="J99" s="2">
+        <v>6</v>
+      </c>
+      <c r="K99" s="2">
+        <v>1450</v>
+      </c>
+      <c r="L99" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M99" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" customHeight="1" spans="3:13">
+      <c r="C100" s="2">
+        <v>40000144</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="E100" s="2">
+        <v>14</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G100" s="2">
+        <v>1</v>
+      </c>
+      <c r="H100" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I100" s="2">
+        <v>0</v>
+      </c>
+      <c r="J100" s="2">
+        <v>6</v>
+      </c>
+      <c r="K100" s="2">
+        <v>1450</v>
+      </c>
+      <c r="L100" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M100" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" customHeight="1" spans="3:13">
+      <c r="C101" s="2">
+        <v>40000145</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="E101" s="2">
+        <v>14</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G101" s="2">
+        <v>1</v>
+      </c>
+      <c r="H101" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I101" s="2">
+        <v>0</v>
+      </c>
+      <c r="J101" s="2">
+        <v>6</v>
+      </c>
+      <c r="K101" s="2">
+        <v>1500</v>
+      </c>
+      <c r="L101" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M101" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" customHeight="1" spans="3:13">
+      <c r="C102" s="2">
+        <v>40000146</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="E102" s="2">
+        <v>14</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G102" s="2">
+        <v>1</v>
+      </c>
+      <c r="H102" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I102" s="2">
+        <v>0</v>
+      </c>
+      <c r="J102" s="2">
+        <v>6</v>
+      </c>
+      <c r="K102" s="2">
+        <v>1500</v>
+      </c>
+      <c r="L102" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M102" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" customHeight="1" spans="3:13">
+      <c r="C103" s="2">
+        <v>40000147</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="E103" s="2">
+        <v>14</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G103" s="2">
+        <v>1</v>
+      </c>
+      <c r="H103" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I103" s="2">
+        <v>0</v>
+      </c>
+      <c r="J103" s="2">
+        <v>6</v>
+      </c>
+      <c r="K103" s="2">
+        <v>1500</v>
+      </c>
+      <c r="L103" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M103" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" customHeight="1" spans="3:13">
+      <c r="C104" s="2">
+        <v>40000148</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="E104" s="2">
+        <v>14</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G104" s="2">
+        <v>1</v>
+      </c>
+      <c r="H104" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I104" s="2">
+        <v>0</v>
+      </c>
+      <c r="J104" s="2">
+        <v>6</v>
+      </c>
+      <c r="K104" s="2">
+        <v>1500</v>
+      </c>
+      <c r="L104" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M104" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" customHeight="1" spans="3:13">
+      <c r="C105" s="2">
+        <v>40000149</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="E105" s="2">
+        <v>14</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G105" s="2">
+        <v>1</v>
+      </c>
+      <c r="H105" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I105" s="2">
+        <v>0</v>
+      </c>
+      <c r="J105" s="2">
+        <v>6</v>
+      </c>
+      <c r="K105" s="2">
+        <v>1500</v>
+      </c>
+      <c r="L105" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M105" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" customHeight="1" spans="3:13">
+      <c r="C106" s="2">
+        <v>40000150</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="E106" s="2">
+        <v>14</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G106" s="2">
+        <v>1</v>
+      </c>
+      <c r="H106" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I106" s="2">
+        <v>0</v>
+      </c>
+      <c r="J106" s="2">
+        <v>6</v>
+      </c>
+      <c r="K106" s="2">
+        <v>1550</v>
+      </c>
+      <c r="L106" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M106" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" customHeight="1" spans="3:13">
+      <c r="C107" s="2">
+        <v>40000151</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="E107" s="2">
+        <v>14</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G107" s="2">
+        <v>1</v>
+      </c>
+      <c r="H107" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I107" s="2">
+        <v>0</v>
+      </c>
+      <c r="J107" s="2">
+        <v>6</v>
+      </c>
+      <c r="K107" s="2">
+        <v>1550</v>
+      </c>
+      <c r="L107" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M107" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" customHeight="1" spans="3:13">
+      <c r="C108" s="2">
+        <v>40000152</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="E108" s="2">
+        <v>14</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G108" s="2">
+        <v>1</v>
+      </c>
+      <c r="H108" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I108" s="2">
+        <v>0</v>
+      </c>
+      <c r="J108" s="2">
+        <v>6</v>
+      </c>
+      <c r="K108" s="2">
+        <v>1550</v>
+      </c>
+      <c r="L108" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M108" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" customHeight="1" spans="3:13">
+      <c r="C109" s="2">
+        <v>40000153</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="E109" s="2">
+        <v>14</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G109" s="2">
+        <v>1</v>
+      </c>
+      <c r="H109" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I109" s="2">
+        <v>0</v>
+      </c>
+      <c r="J109" s="2">
+        <v>6</v>
+      </c>
+      <c r="K109" s="2">
+        <v>1550</v>
+      </c>
+      <c r="L109" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M109" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" customHeight="1" spans="3:13">
+      <c r="C110" s="2">
+        <v>40000154</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="E110" s="2">
+        <v>14</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G110" s="2">
+        <v>1</v>
+      </c>
+      <c r="H110" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I110" s="2">
+        <v>0</v>
+      </c>
+      <c r="J110" s="2">
+        <v>6</v>
+      </c>
+      <c r="K110" s="2">
+        <v>1550</v>
+      </c>
+      <c r="L110" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M110" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" customHeight="1" spans="3:13">
+      <c r="C111" s="2">
+        <v>40000155</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="E111" s="2">
+        <v>14</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G111" s="2">
+        <v>1</v>
+      </c>
+      <c r="H111" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I111" s="2">
+        <v>0</v>
+      </c>
+      <c r="J111" s="2">
+        <v>6</v>
+      </c>
+      <c r="K111" s="2">
+        <v>1600</v>
+      </c>
+      <c r="L111" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M111" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" customHeight="1" spans="3:13">
+      <c r="C112" s="2">
+        <v>40000156</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="E112" s="2">
+        <v>14</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G112" s="2">
+        <v>1</v>
+      </c>
+      <c r="H112" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I112" s="2">
+        <v>0</v>
+      </c>
+      <c r="J112" s="2">
+        <v>6</v>
+      </c>
+      <c r="K112" s="2">
+        <v>1600</v>
+      </c>
+      <c r="L112" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M112" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" customHeight="1" spans="3:13">
+      <c r="C113" s="2">
+        <v>40000157</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="E113" s="2">
+        <v>14</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G113" s="2">
+        <v>1</v>
+      </c>
+      <c r="H113" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I113" s="2">
+        <v>0</v>
+      </c>
+      <c r="J113" s="2">
+        <v>6</v>
+      </c>
+      <c r="K113" s="2">
+        <v>1600</v>
+      </c>
+      <c r="L113" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M113" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" customHeight="1" spans="3:13">
+      <c r="C114" s="2">
+        <v>40000158</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="E114" s="2">
+        <v>14</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G114" s="2">
+        <v>1</v>
+      </c>
+      <c r="H114" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I114" s="2">
+        <v>0</v>
+      </c>
+      <c r="J114" s="2">
+        <v>6</v>
+      </c>
+      <c r="K114" s="2">
+        <v>1600</v>
+      </c>
+      <c r="L114" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M114" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" customHeight="1" spans="3:13">
+      <c r="C115" s="2">
+        <v>40000159</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="E115" s="2">
+        <v>14</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G115" s="2">
+        <v>1</v>
+      </c>
+      <c r="H115" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I115" s="2">
+        <v>0</v>
+      </c>
+      <c r="J115" s="2">
+        <v>6</v>
+      </c>
+      <c r="K115" s="2">
+        <v>1600</v>
+      </c>
+      <c r="L115" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M115" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" customHeight="1" spans="3:13">
+      <c r="C116" s="2">
+        <v>40000160</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="E116" s="2">
+        <v>14</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G116" s="2">
+        <v>1</v>
+      </c>
+      <c r="H116" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I116" s="2">
+        <v>0</v>
+      </c>
+      <c r="J116" s="2">
+        <v>6</v>
+      </c>
+      <c r="K116" s="2">
+        <v>1650</v>
+      </c>
+      <c r="L116" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M116" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" customHeight="1" spans="3:13">
+      <c r="C117" s="2">
+        <v>40000161</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="E117" s="2">
+        <v>14</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G117" s="2">
+        <v>1</v>
+      </c>
+      <c r="H117" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I117" s="2">
+        <v>0</v>
+      </c>
+      <c r="J117" s="2">
+        <v>6</v>
+      </c>
+      <c r="K117" s="2">
+        <v>1650</v>
+      </c>
+      <c r="L117" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M117" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" customHeight="1" spans="3:13">
+      <c r="C118" s="2">
+        <v>40000162</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="E118" s="2">
+        <v>14</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G118" s="2">
+        <v>1</v>
+      </c>
+      <c r="H118" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I118" s="2">
+        <v>0</v>
+      </c>
+      <c r="J118" s="2">
+        <v>6</v>
+      </c>
+      <c r="K118" s="2">
+        <v>1650</v>
+      </c>
+      <c r="L118" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M118" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" customHeight="1" spans="3:13">
+      <c r="C119" s="2">
+        <v>40000163</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="E119" s="2">
+        <v>14</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G119" s="2">
+        <v>1</v>
+      </c>
+      <c r="H119" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I119" s="2">
+        <v>0</v>
+      </c>
+      <c r="J119" s="2">
+        <v>6</v>
+      </c>
+      <c r="K119" s="2">
+        <v>1650</v>
+      </c>
+      <c r="L119" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M119" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" customHeight="1" spans="3:13">
+      <c r="C120" s="2">
+        <v>40000164</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="E120" s="2">
+        <v>14</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G120" s="2">
+        <v>1</v>
+      </c>
+      <c r="H120" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I120" s="2">
+        <v>0</v>
+      </c>
+      <c r="J120" s="2">
+        <v>6</v>
+      </c>
+      <c r="K120" s="2">
+        <v>1650</v>
+      </c>
+      <c r="L120" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M120" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" customHeight="1" spans="3:13">
+      <c r="C121" s="2">
+        <v>40000165</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="E121" s="2">
+        <v>14</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G121" s="2">
+        <v>1</v>
+      </c>
+      <c r="H121" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I121" s="2">
+        <v>0</v>
+      </c>
+      <c r="J121" s="2">
+        <v>6</v>
+      </c>
+      <c r="K121" s="2">
+        <v>1700</v>
+      </c>
+      <c r="L121" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M121" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" customHeight="1" spans="3:13">
+      <c r="C122" s="2">
+        <v>40000166</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="E122" s="2">
+        <v>14</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G122" s="2">
+        <v>1</v>
+      </c>
+      <c r="H122" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I122" s="2">
+        <v>0</v>
+      </c>
+      <c r="J122" s="2">
+        <v>6</v>
+      </c>
+      <c r="K122" s="2">
+        <v>1700</v>
+      </c>
+      <c r="L122" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M122" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" customHeight="1" spans="3:13">
+      <c r="C123" s="2">
+        <v>40000167</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="E123" s="2">
+        <v>14</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G123" s="2">
+        <v>1</v>
+      </c>
+      <c r="H123" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I123" s="2">
+        <v>0</v>
+      </c>
+      <c r="J123" s="2">
+        <v>6</v>
+      </c>
+      <c r="K123" s="2">
+        <v>1700</v>
+      </c>
+      <c r="L123" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M123" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" customHeight="1" spans="3:13">
+      <c r="C124" s="2">
+        <v>40000168</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="E124" s="2">
+        <v>14</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G124" s="2">
+        <v>1</v>
+      </c>
+      <c r="H124" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I124" s="2">
+        <v>0</v>
+      </c>
+      <c r="J124" s="2">
+        <v>6</v>
+      </c>
+      <c r="K124" s="2">
+        <v>1700</v>
+      </c>
+      <c r="L124" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M124" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" customHeight="1" spans="3:13">
+      <c r="C125" s="2">
+        <v>40000169</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="E125" s="2">
+        <v>14</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G125" s="2">
+        <v>1</v>
+      </c>
+      <c r="H125" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I125" s="2">
+        <v>0</v>
+      </c>
+      <c r="J125" s="2">
+        <v>6</v>
+      </c>
+      <c r="K125" s="2">
+        <v>1700</v>
+      </c>
+      <c r="L125" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M125" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" customHeight="1" spans="3:13">
+      <c r="C126" s="2">
+        <v>40000170</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="E126" s="2">
+        <v>14</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G126" s="2">
+        <v>1</v>
+      </c>
+      <c r="H126" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I126" s="2">
+        <v>0</v>
+      </c>
+      <c r="J126" s="2">
+        <v>6</v>
+      </c>
+      <c r="K126" s="2">
+        <v>1750</v>
+      </c>
+      <c r="L126" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M126" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" customHeight="1" spans="3:13">
+      <c r="C127" s="2">
+        <v>40000171</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="E127" s="2">
+        <v>14</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G127" s="2">
+        <v>1</v>
+      </c>
+      <c r="H127" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I127" s="2">
+        <v>0</v>
+      </c>
+      <c r="J127" s="2">
+        <v>6</v>
+      </c>
+      <c r="K127" s="2">
+        <v>1750</v>
+      </c>
+      <c r="L127" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M127" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" customHeight="1" spans="3:13">
+      <c r="C128" s="2">
+        <v>40000172</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="E128" s="2">
+        <v>14</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G128" s="2">
+        <v>1</v>
+      </c>
+      <c r="H128" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I128" s="2">
+        <v>0</v>
+      </c>
+      <c r="J128" s="2">
+        <v>6</v>
+      </c>
+      <c r="K128" s="2">
+        <v>1750</v>
+      </c>
+      <c r="L128" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M128" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" customHeight="1" spans="3:13">
+      <c r="C129" s="2">
+        <v>40000173</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="E129" s="2">
+        <v>14</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G129" s="2">
+        <v>1</v>
+      </c>
+      <c r="H129" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I129" s="2">
+        <v>0</v>
+      </c>
+      <c r="J129" s="2">
+        <v>6</v>
+      </c>
+      <c r="K129" s="2">
+        <v>1750</v>
+      </c>
+      <c r="L129" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M129" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" customHeight="1" spans="3:13">
+      <c r="C130" s="2">
+        <v>40000174</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="E130" s="2">
+        <v>14</v>
+      </c>
+      <c r="F130" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G130" s="2">
+        <v>1</v>
+      </c>
+      <c r="H130" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I130" s="2">
+        <v>0</v>
+      </c>
+      <c r="J130" s="2">
+        <v>6</v>
+      </c>
+      <c r="K130" s="2">
+        <v>1750</v>
+      </c>
+      <c r="L130" s="3">
+        <v>4018</v>
+      </c>
+      <c r="M130" s="3">
         <v>1</v>
       </c>
     </row>
@@ -15978,13 +17313,13 @@
         <v>50000001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
       <c r="E6" s="2">
         <v>5</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>541</v>
+        <v>578</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -16013,13 +17348,13 @@
         <v>50000002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>542</v>
+        <v>579</v>
       </c>
       <c r="E7" s="2">
         <v>5</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>543</v>
+        <v>580</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -16048,13 +17383,13 @@
         <v>50000003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>544</v>
+        <v>581</v>
       </c>
       <c r="E8" s="2">
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>545</v>
+        <v>582</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -16083,13 +17418,13 @@
         <v>50000004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>546</v>
+        <v>583</v>
       </c>
       <c r="E9" s="2">
         <v>5</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>547</v>
+        <v>584</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -16118,13 +17453,13 @@
         <v>50000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>548</v>
+        <v>585</v>
       </c>
       <c r="E10" s="2">
         <v>5</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>549</v>
+        <v>586</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -16153,13 +17488,13 @@
         <v>50000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>550</v>
+        <v>587</v>
       </c>
       <c r="E11" s="2">
         <v>5</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>551</v>
+        <v>588</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -16188,13 +17523,13 @@
         <v>50000007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>552</v>
+        <v>589</v>
       </c>
       <c r="E12" s="2">
         <v>5</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>553</v>
+        <v>590</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -16223,13 +17558,13 @@
         <v>50000008</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>554</v>
+        <v>591</v>
       </c>
       <c r="E13" s="6">
         <v>5</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>555</v>
+        <v>592</v>
       </c>
       <c r="G13" s="6">
         <v>1</v>
@@ -16258,13 +17593,13 @@
         <v>50000009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>556</v>
+        <v>593</v>
       </c>
       <c r="E14" s="2">
         <v>5</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>557</v>
+        <v>594</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -16293,13 +17628,13 @@
         <v>50000010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>558</v>
+        <v>595</v>
       </c>
       <c r="E15" s="2">
         <v>5</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>559</v>
+        <v>596</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -16328,13 +17663,13 @@
         <v>50000011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>560</v>
+        <v>597</v>
       </c>
       <c r="E16" s="2">
         <v>5</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>561</v>
+        <v>598</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -16363,13 +17698,13 @@
         <v>50000012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>562</v>
+        <v>599</v>
       </c>
       <c r="E17" s="2">
         <v>5</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>563</v>
+        <v>600</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -16398,13 +17733,13 @@
         <v>50000013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>564</v>
+        <v>601</v>
       </c>
       <c r="E18" s="2">
         <v>5</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>565</v>
+        <v>602</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -16433,13 +17768,13 @@
         <v>50000014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>566</v>
+        <v>603</v>
       </c>
       <c r="E19" s="2">
         <v>5</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>567</v>
+        <v>604</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -16468,13 +17803,13 @@
         <v>50000015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>568</v>
+        <v>605</v>
       </c>
       <c r="E20" s="2">
         <v>5</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>569</v>
+        <v>606</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -16503,13 +17838,13 @@
         <v>50000016</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>570</v>
+        <v>607</v>
       </c>
       <c r="E21" s="6">
         <v>5</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>571</v>
+        <v>608</v>
       </c>
       <c r="G21" s="6">
         <v>1</v>
@@ -16538,13 +17873,13 @@
         <v>50000017</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>572</v>
+        <v>609</v>
       </c>
       <c r="E22" s="2">
         <v>5</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>573</v>
+        <v>610</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -16573,13 +17908,13 @@
         <v>50000018</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>574</v>
+        <v>611</v>
       </c>
       <c r="E23" s="2">
         <v>5</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>575</v>
+        <v>612</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -16608,13 +17943,13 @@
         <v>50000019</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>576</v>
+        <v>613</v>
       </c>
       <c r="E24" s="2">
         <v>5</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>577</v>
+        <v>614</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -16643,13 +17978,13 @@
         <v>50000020</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>578</v>
+        <v>615</v>
       </c>
       <c r="E25" s="2">
         <v>5</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>579</v>
+        <v>616</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -16678,13 +18013,13 @@
         <v>50000021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>580</v>
+        <v>617</v>
       </c>
       <c r="E26" s="2">
         <v>5</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>581</v>
+        <v>618</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -16713,13 +18048,13 @@
         <v>50000022</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>582</v>
+        <v>619</v>
       </c>
       <c r="E27" s="2">
         <v>5</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>583</v>
+        <v>620</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -16748,13 +18083,13 @@
         <v>50000023</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>584</v>
+        <v>621</v>
       </c>
       <c r="E28" s="2">
         <v>5</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>585</v>
+        <v>622</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -16783,13 +18118,13 @@
         <v>50000024</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>586</v>
+        <v>623</v>
       </c>
       <c r="E29" s="6">
         <v>5</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>587</v>
+        <v>624</v>
       </c>
       <c r="G29" s="6">
         <v>1</v>
@@ -16818,13 +18153,13 @@
         <v>50000025</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>588</v>
+        <v>625</v>
       </c>
       <c r="E30" s="2">
         <v>5</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>589</v>
+        <v>626</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -16853,13 +18188,13 @@
         <v>50000026</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>590</v>
+        <v>627</v>
       </c>
       <c r="E31" s="2">
         <v>5</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>591</v>
+        <v>628</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -16888,13 +18223,13 @@
         <v>50000027</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="E32" s="2">
         <v>5</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>593</v>
+        <v>630</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -16923,13 +18258,13 @@
         <v>50000028</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>594</v>
+        <v>631</v>
       </c>
       <c r="E33" s="2">
         <v>5</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>595</v>
+        <v>632</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -16958,13 +18293,13 @@
         <v>50000029</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>596</v>
+        <v>633</v>
       </c>
       <c r="E34" s="2">
         <v>5</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>597</v>
+        <v>634</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -16993,13 +18328,13 @@
         <v>50000030</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>598</v>
+        <v>635</v>
       </c>
       <c r="E35" s="2">
         <v>5</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>599</v>
+        <v>636</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -17028,13 +18363,13 @@
         <v>50000031</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>600</v>
+        <v>637</v>
       </c>
       <c r="E36" s="2">
         <v>5</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>601</v>
+        <v>638</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -17063,13 +18398,13 @@
         <v>50000032</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>602</v>
+        <v>639</v>
       </c>
       <c r="E37" s="6">
         <v>5</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>603</v>
+        <v>640</v>
       </c>
       <c r="G37" s="6">
         <v>1</v>
@@ -17098,13 +18433,13 @@
         <v>50000033</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>604</v>
+        <v>641</v>
       </c>
       <c r="E38" s="2">
         <v>5</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>605</v>
+        <v>642</v>
       </c>
       <c r="G38" s="2">
         <v>1</v>
@@ -17133,13 +18468,13 @@
         <v>50000034</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>606</v>
+        <v>643</v>
       </c>
       <c r="E39" s="2">
         <v>5</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>607</v>
+        <v>644</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -17168,13 +18503,13 @@
         <v>50000035</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>608</v>
+        <v>645</v>
       </c>
       <c r="E40" s="2">
         <v>5</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>609</v>
+        <v>646</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -17203,13 +18538,13 @@
         <v>50000036</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>610</v>
+        <v>647</v>
       </c>
       <c r="E41" s="2">
         <v>5</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>611</v>
+        <v>648</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -17238,13 +18573,13 @@
         <v>50000037</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>612</v>
+        <v>649</v>
       </c>
       <c r="E42" s="2">
         <v>5</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>613</v>
+        <v>650</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -17273,13 +18608,13 @@
         <v>50000038</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>614</v>
+        <v>651</v>
       </c>
       <c r="E43" s="2">
         <v>5</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>615</v>
+        <v>652</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -17308,13 +18643,13 @@
         <v>50000039</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>616</v>
+        <v>653</v>
       </c>
       <c r="E44" s="2">
         <v>5</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>617</v>
+        <v>654</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -17343,13 +18678,13 @@
         <v>50000040</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>618</v>
+        <v>655</v>
       </c>
       <c r="E45" s="6">
         <v>5</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>619</v>
+        <v>656</v>
       </c>
       <c r="G45" s="6">
         <v>1</v>
@@ -17378,13 +18713,13 @@
         <v>50000041</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>620</v>
+        <v>657</v>
       </c>
       <c r="E46" s="2">
         <v>5</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>621</v>
+        <v>658</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -17413,13 +18748,13 @@
         <v>50000042</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>622</v>
+        <v>659</v>
       </c>
       <c r="E47" s="2">
         <v>5</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>623</v>
+        <v>660</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -17448,13 +18783,13 @@
         <v>50000043</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>624</v>
+        <v>661</v>
       </c>
       <c r="E48" s="2">
         <v>5</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>625</v>
+        <v>662</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -17483,13 +18818,13 @@
         <v>50000044</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>626</v>
+        <v>663</v>
       </c>
       <c r="E49" s="2">
         <v>5</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>627</v>
+        <v>664</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -17518,13 +18853,13 @@
         <v>50000045</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>628</v>
+        <v>665</v>
       </c>
       <c r="E50" s="2">
         <v>5</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>629</v>
+        <v>666</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -17553,13 +18888,13 @@
         <v>50000046</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>630</v>
+        <v>667</v>
       </c>
       <c r="E51" s="2">
         <v>5</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>631</v>
+        <v>668</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -17588,13 +18923,13 @@
         <v>50000047</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>632</v>
+        <v>669</v>
       </c>
       <c r="E52" s="2">
         <v>5</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>633</v>
+        <v>670</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -17623,13 +18958,13 @@
         <v>50000048</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>634</v>
+        <v>671</v>
       </c>
       <c r="E53" s="6">
         <v>5</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>635</v>
+        <v>672</v>
       </c>
       <c r="G53" s="6">
         <v>1</v>
@@ -17658,13 +18993,13 @@
         <v>50000049</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>636</v>
+        <v>673</v>
       </c>
       <c r="E54" s="2">
         <v>5</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>637</v>
+        <v>674</v>
       </c>
       <c r="G54" s="2">
         <v>1</v>
@@ -17693,13 +19028,13 @@
         <v>50000050</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>638</v>
+        <v>675</v>
       </c>
       <c r="E55" s="2">
         <v>5</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>639</v>
+        <v>676</v>
       </c>
       <c r="G55" s="2">
         <v>1</v>
@@ -17728,13 +19063,13 @@
         <v>50000051</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>640</v>
+        <v>677</v>
       </c>
       <c r="E56" s="2">
         <v>5</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>641</v>
+        <v>678</v>
       </c>
       <c r="G56" s="2">
         <v>1</v>
@@ -17763,13 +19098,13 @@
         <v>50000052</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>642</v>
+        <v>679</v>
       </c>
       <c r="E57" s="2">
         <v>5</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>643</v>
+        <v>680</v>
       </c>
       <c r="G57" s="2">
         <v>1</v>
@@ -17798,13 +19133,13 @@
         <v>50000053</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>644</v>
+        <v>681</v>
       </c>
       <c r="E58" s="2">
         <v>5</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>645</v>
+        <v>682</v>
       </c>
       <c r="G58" s="2">
         <v>1</v>
@@ -17833,13 +19168,13 @@
         <v>50000054</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>646</v>
+        <v>683</v>
       </c>
       <c r="E59" s="2">
         <v>5</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>647</v>
+        <v>684</v>
       </c>
       <c r="G59" s="2">
         <v>1</v>
@@ -17868,13 +19203,13 @@
         <v>50000055</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>648</v>
+        <v>685</v>
       </c>
       <c r="E60" s="2">
         <v>5</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>649</v>
+        <v>686</v>
       </c>
       <c r="G60" s="2">
         <v>1</v>
@@ -17903,13 +19238,13 @@
         <v>50000056</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>650</v>
+        <v>687</v>
       </c>
       <c r="E61" s="6">
         <v>5</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>651</v>
+        <v>688</v>
       </c>
       <c r="G61" s="6">
         <v>1</v>
@@ -17938,13 +19273,13 @@
         <v>50000057</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>652</v>
+        <v>689</v>
       </c>
       <c r="E62" s="2">
         <v>5</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>653</v>
+        <v>690</v>
       </c>
       <c r="G62" s="2">
         <v>1</v>
@@ -17973,13 +19308,13 @@
         <v>50000058</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>654</v>
+        <v>691</v>
       </c>
       <c r="E63" s="2">
         <v>5</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>655</v>
+        <v>692</v>
       </c>
       <c r="G63" s="2">
         <v>1</v>
@@ -18008,13 +19343,13 @@
         <v>50000059</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>656</v>
+        <v>693</v>
       </c>
       <c r="E64" s="2">
         <v>5</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>657</v>
+        <v>694</v>
       </c>
       <c r="G64" s="2">
         <v>1</v>
@@ -18043,13 +19378,13 @@
         <v>50000060</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>658</v>
+        <v>695</v>
       </c>
       <c r="E65" s="2">
         <v>5</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>659</v>
+        <v>696</v>
       </c>
       <c r="G65" s="2">
         <v>1</v>
@@ -18078,13 +19413,13 @@
         <v>50000061</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>660</v>
+        <v>697</v>
       </c>
       <c r="E66" s="2">
         <v>5</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>661</v>
+        <v>698</v>
       </c>
       <c r="G66" s="2">
         <v>1</v>
@@ -18113,13 +19448,13 @@
         <v>50000062</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>662</v>
+        <v>699</v>
       </c>
       <c r="E67" s="2">
         <v>5</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>663</v>
+        <v>700</v>
       </c>
       <c r="G67" s="2">
         <v>1</v>
@@ -18148,13 +19483,13 @@
         <v>50000063</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>664</v>
+        <v>701</v>
       </c>
       <c r="E68" s="2">
         <v>5</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>665</v>
+        <v>702</v>
       </c>
       <c r="G68" s="2">
         <v>1</v>
@@ -18183,13 +19518,13 @@
         <v>50000064</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>666</v>
+        <v>703</v>
       </c>
       <c r="E69" s="6">
         <v>5</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="G69" s="6">
         <v>1</v>
@@ -18218,13 +19553,13 @@
         <v>50000065</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>668</v>
+        <v>705</v>
       </c>
       <c r="E70" s="2">
         <v>5</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>669</v>
+        <v>706</v>
       </c>
       <c r="G70" s="2">
         <v>1</v>
@@ -18253,13 +19588,13 @@
         <v>50000066</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>670</v>
+        <v>707</v>
       </c>
       <c r="E71" s="2">
         <v>5</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>671</v>
+        <v>708</v>
       </c>
       <c r="G71" s="2">
         <v>1</v>
@@ -18288,13 +19623,13 @@
         <v>50000067</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>672</v>
+        <v>709</v>
       </c>
       <c r="E72" s="2">
         <v>5</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="G72" s="2">
         <v>1</v>
@@ -18323,13 +19658,13 @@
         <v>50000068</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>674</v>
+        <v>711</v>
       </c>
       <c r="E73" s="2">
         <v>5</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>675</v>
+        <v>712</v>
       </c>
       <c r="G73" s="2">
         <v>1</v>
@@ -18358,13 +19693,13 @@
         <v>50000069</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>676</v>
+        <v>713</v>
       </c>
       <c r="E74" s="2">
         <v>5</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>677</v>
+        <v>714</v>
       </c>
       <c r="G74" s="2">
         <v>1</v>
@@ -18393,13 +19728,13 @@
         <v>50000070</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>678</v>
+        <v>715</v>
       </c>
       <c r="E75" s="2">
         <v>5</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>679</v>
+        <v>716</v>
       </c>
       <c r="G75" s="2">
         <v>1</v>
@@ -18428,13 +19763,13 @@
         <v>50000071</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>680</v>
+        <v>717</v>
       </c>
       <c r="E76" s="2">
         <v>5</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="G76" s="2">
         <v>1</v>
@@ -18463,13 +19798,13 @@
         <v>50000072</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>682</v>
+        <v>719</v>
       </c>
       <c r="E77" s="6">
         <v>5</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>683</v>
+        <v>720</v>
       </c>
       <c r="G77" s="6">
         <v>1</v>
@@ -18498,13 +19833,13 @@
         <v>50000073</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>684</v>
+        <v>721</v>
       </c>
       <c r="E78" s="2">
         <v>5</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>685</v>
+        <v>722</v>
       </c>
       <c r="G78" s="2">
         <v>1</v>
@@ -18533,13 +19868,13 @@
         <v>50000074</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>686</v>
+        <v>723</v>
       </c>
       <c r="E79" s="2">
         <v>5</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>687</v>
+        <v>724</v>
       </c>
       <c r="G79" s="2">
         <v>1</v>
@@ -18568,13 +19903,13 @@
         <v>50000075</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>688</v>
+        <v>725</v>
       </c>
       <c r="E80" s="2">
         <v>5</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>689</v>
+        <v>726</v>
       </c>
       <c r="G80" s="2">
         <v>1</v>
@@ -18603,13 +19938,13 @@
         <v>50000076</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>690</v>
+        <v>727</v>
       </c>
       <c r="E81" s="2">
         <v>5</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>691</v>
+        <v>728</v>
       </c>
       <c r="G81" s="2">
         <v>1</v>
@@ -18638,13 +19973,13 @@
         <v>50000077</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>692</v>
+        <v>729</v>
       </c>
       <c r="E82" s="2">
         <v>5</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>693</v>
+        <v>730</v>
       </c>
       <c r="G82" s="2">
         <v>1</v>
@@ -18673,13 +20008,13 @@
         <v>50000078</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>694</v>
+        <v>731</v>
       </c>
       <c r="E83" s="2">
         <v>5</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>695</v>
+        <v>732</v>
       </c>
       <c r="G83" s="2">
         <v>1</v>
@@ -18708,13 +20043,13 @@
         <v>50000079</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>696</v>
+        <v>733</v>
       </c>
       <c r="E84" s="2">
         <v>5</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>697</v>
+        <v>734</v>
       </c>
       <c r="G84" s="2">
         <v>1</v>
@@ -18743,13 +20078,13 @@
         <v>50000080</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>698</v>
+        <v>735</v>
       </c>
       <c r="E85" s="6">
         <v>5</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>699</v>
+        <v>736</v>
       </c>
       <c r="G85" s="6">
         <v>1</v>
@@ -18778,13 +20113,13 @@
         <v>50000081</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>700</v>
+        <v>737</v>
       </c>
       <c r="E86" s="2">
         <v>5</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>701</v>
+        <v>738</v>
       </c>
       <c r="G86" s="2">
         <v>1</v>
@@ -18813,13 +20148,13 @@
         <v>50000082</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>702</v>
+        <v>739</v>
       </c>
       <c r="E87" s="2">
         <v>5</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>703</v>
+        <v>740</v>
       </c>
       <c r="G87" s="2">
         <v>1</v>
@@ -18848,13 +20183,13 @@
         <v>50000083</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>704</v>
+        <v>741</v>
       </c>
       <c r="E88" s="2">
         <v>5</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>705</v>
+        <v>742</v>
       </c>
       <c r="G88" s="2">
         <v>1</v>
@@ -18883,13 +20218,13 @@
         <v>50000084</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>706</v>
+        <v>743</v>
       </c>
       <c r="E89" s="2">
         <v>5</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>707</v>
+        <v>744</v>
       </c>
       <c r="G89" s="2">
         <v>1</v>
@@ -18918,13 +20253,13 @@
         <v>50000085</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>708</v>
+        <v>745</v>
       </c>
       <c r="E90" s="2">
         <v>5</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>709</v>
+        <v>746</v>
       </c>
       <c r="G90" s="2">
         <v>1</v>
@@ -18953,13 +20288,13 @@
         <v>50000086</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>710</v>
+        <v>747</v>
       </c>
       <c r="E91" s="2">
         <v>5</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>711</v>
+        <v>748</v>
       </c>
       <c r="G91" s="2">
         <v>1</v>
@@ -18988,13 +20323,13 @@
         <v>50000087</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>712</v>
+        <v>749</v>
       </c>
       <c r="E92" s="2">
         <v>5</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>713</v>
+        <v>750</v>
       </c>
       <c r="G92" s="2">
         <v>1</v>
@@ -19023,13 +20358,13 @@
         <v>50000088</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>714</v>
+        <v>751</v>
       </c>
       <c r="E93" s="6">
         <v>5</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>715</v>
+        <v>752</v>
       </c>
       <c r="G93" s="6">
         <v>1</v>
@@ -19058,13 +20393,13 @@
         <v>50000089</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>716</v>
+        <v>753</v>
       </c>
       <c r="E94" s="2">
         <v>5</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>717</v>
+        <v>754</v>
       </c>
       <c r="G94" s="2">
         <v>1</v>
@@ -19093,13 +20428,13 @@
         <v>50000090</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>718</v>
+        <v>755</v>
       </c>
       <c r="E95" s="2">
         <v>5</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>719</v>
+        <v>756</v>
       </c>
       <c r="G95" s="2">
         <v>1</v>
@@ -19128,13 +20463,13 @@
         <v>50000091</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>720</v>
+        <v>757</v>
       </c>
       <c r="E96" s="2">
         <v>5</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>721</v>
+        <v>758</v>
       </c>
       <c r="G96" s="2">
         <v>1</v>
@@ -19163,13 +20498,13 @@
         <v>50000092</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>722</v>
+        <v>759</v>
       </c>
       <c r="E97" s="2">
         <v>5</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>723</v>
+        <v>760</v>
       </c>
       <c r="G97" s="2">
         <v>1</v>
@@ -19198,13 +20533,13 @@
         <v>50000093</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>724</v>
+        <v>761</v>
       </c>
       <c r="E98" s="2">
         <v>5</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>725</v>
+        <v>762</v>
       </c>
       <c r="G98" s="2">
         <v>1</v>
@@ -19233,13 +20568,13 @@
         <v>50000094</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>726</v>
+        <v>763</v>
       </c>
       <c r="E99" s="2">
         <v>5</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>727</v>
+        <v>764</v>
       </c>
       <c r="G99" s="2">
         <v>1</v>
@@ -19268,13 +20603,13 @@
         <v>50000095</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>728</v>
+        <v>765</v>
       </c>
       <c r="E100" s="2">
         <v>5</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>729</v>
+        <v>766</v>
       </c>
       <c r="G100" s="2">
         <v>1</v>
@@ -19303,13 +20638,13 @@
         <v>50000096</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>730</v>
+        <v>767</v>
       </c>
       <c r="E101" s="6">
         <v>5</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>731</v>
+        <v>768</v>
       </c>
       <c r="G101" s="6">
         <v>1</v>
@@ -19338,13 +20673,13 @@
         <v>50000097</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>732</v>
+        <v>769</v>
       </c>
       <c r="E102" s="2">
         <v>5</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>733</v>
+        <v>770</v>
       </c>
       <c r="G102" s="2">
         <v>1</v>
@@ -19373,13 +20708,13 @@
         <v>50000098</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>734</v>
+        <v>771</v>
       </c>
       <c r="E103" s="2">
         <v>5</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>735</v>
+        <v>772</v>
       </c>
       <c r="G103" s="2">
         <v>1</v>
@@ -19408,13 +20743,13 @@
         <v>50000099</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>736</v>
+        <v>773</v>
       </c>
       <c r="E104" s="2">
         <v>5</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>737</v>
+        <v>774</v>
       </c>
       <c r="G104" s="2">
         <v>1</v>
@@ -19443,13 +20778,13 @@
         <v>50000100</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>738</v>
+        <v>775</v>
       </c>
       <c r="E105" s="2">
         <v>5</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>739</v>
+        <v>776</v>
       </c>
       <c r="G105" s="2">
         <v>1</v>
@@ -19478,13 +20813,13 @@
         <v>50000101</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>740</v>
+        <v>777</v>
       </c>
       <c r="E106" s="2">
         <v>5</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>741</v>
+        <v>778</v>
       </c>
       <c r="G106" s="2">
         <v>1</v>
@@ -19513,13 +20848,13 @@
         <v>50000102</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>742</v>
+        <v>779</v>
       </c>
       <c r="E107" s="2">
         <v>5</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>743</v>
+        <v>780</v>
       </c>
       <c r="G107" s="2">
         <v>1</v>
@@ -19548,13 +20883,13 @@
         <v>50000103</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>744</v>
+        <v>781</v>
       </c>
       <c r="E108" s="2">
         <v>5</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>745</v>
+        <v>782</v>
       </c>
       <c r="G108" s="2">
         <v>1</v>
@@ -19583,13 +20918,13 @@
         <v>50000104</v>
       </c>
       <c r="D109" s="7" t="s">
-        <v>746</v>
+        <v>783</v>
       </c>
       <c r="E109" s="6">
         <v>5</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>747</v>
+        <v>784</v>
       </c>
       <c r="G109" s="6">
         <v>1</v>
@@ -19618,13 +20953,13 @@
         <v>50000105</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>748</v>
+        <v>785</v>
       </c>
       <c r="E110" s="2">
         <v>5</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>749</v>
+        <v>786</v>
       </c>
       <c r="G110" s="2">
         <v>1</v>
@@ -19653,13 +20988,13 @@
         <v>50000106</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>750</v>
+        <v>787</v>
       </c>
       <c r="E111" s="2">
         <v>5</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>751</v>
+        <v>786</v>
       </c>
       <c r="G111" s="2">
         <v>1</v>
@@ -19674,7 +21009,7 @@
         <v>6</v>
       </c>
       <c r="K111" s="2">
-        <v>1450</v>
+        <v>1500</v>
       </c>
       <c r="L111" s="3">
         <v>4015</v>
@@ -19688,13 +21023,13 @@
         <v>50000107</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="E112" s="2">
         <v>5</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>753</v>
+        <v>786</v>
       </c>
       <c r="G112" s="2">
         <v>1</v>
@@ -19709,7 +21044,7 @@
         <v>6</v>
       </c>
       <c r="K112" s="2">
-        <v>1450</v>
+        <v>1550</v>
       </c>
       <c r="L112" s="3">
         <v>4015</v>
@@ -19723,13 +21058,13 @@
         <v>50000108</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>754</v>
+        <v>789</v>
       </c>
       <c r="E113" s="2">
         <v>5</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>755</v>
+        <v>786</v>
       </c>
       <c r="G113" s="2">
         <v>1</v>
@@ -19744,7 +21079,7 @@
         <v>6</v>
       </c>
       <c r="K113" s="2">
-        <v>1450</v>
+        <v>1600</v>
       </c>
       <c r="L113" s="3">
         <v>4015</v>
@@ -19758,13 +21093,13 @@
         <v>50000109</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>756</v>
+        <v>790</v>
       </c>
       <c r="E114" s="2">
         <v>5</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>757</v>
+        <v>786</v>
       </c>
       <c r="G114" s="2">
         <v>1</v>
@@ -19779,7 +21114,7 @@
         <v>6</v>
       </c>
       <c r="K114" s="2">
-        <v>1450</v>
+        <v>1650</v>
       </c>
       <c r="L114" s="3">
         <v>4015</v>
@@ -19793,13 +21128,13 @@
         <v>50000110</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>758</v>
+        <v>791</v>
       </c>
       <c r="E115" s="2">
         <v>5</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>759</v>
+        <v>786</v>
       </c>
       <c r="G115" s="2">
         <v>1</v>
@@ -19814,7 +21149,7 @@
         <v>6</v>
       </c>
       <c r="K115" s="2">
-        <v>1450</v>
+        <v>1700</v>
       </c>
       <c r="L115" s="3">
         <v>4015</v>
@@ -19828,13 +21163,13 @@
         <v>50000111</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>760</v>
+        <v>792</v>
       </c>
       <c r="E116" s="2">
         <v>5</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>761</v>
+        <v>786</v>
       </c>
       <c r="G116" s="2">
         <v>1</v>
@@ -19849,7 +21184,7 @@
         <v>6</v>
       </c>
       <c r="K116" s="2">
-        <v>1450</v>
+        <v>1750</v>
       </c>
       <c r="L116" s="3">
         <v>4015</v>
@@ -19863,13 +21198,13 @@
         <v>50000112</v>
       </c>
       <c r="D117" s="7" t="s">
-        <v>762</v>
+        <v>793</v>
       </c>
       <c r="E117" s="6">
         <v>5</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>763</v>
+        <v>786</v>
       </c>
       <c r="G117" s="6">
         <v>1</v>
@@ -19884,7 +21219,7 @@
         <v>6</v>
       </c>
       <c r="K117" s="6">
-        <v>1450</v>
+        <v>1800</v>
       </c>
       <c r="L117" s="7">
         <v>4015</v>
@@ -20037,13 +21372,13 @@
         <v>180001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>764</v>
+        <v>794</v>
       </c>
       <c r="E6" s="2">
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>765</v>
+        <v>795</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -20063,13 +21398,13 @@
         <v>180002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>766</v>
+        <v>796</v>
       </c>
       <c r="E7" s="2">
         <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>765</v>
+        <v>795</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -20089,13 +21424,13 @@
         <v>180003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>767</v>
+        <v>797</v>
       </c>
       <c r="E8" s="2">
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>765</v>
+        <v>795</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -20115,13 +21450,13 @@
         <v>180004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>768</v>
+        <v>798</v>
       </c>
       <c r="E9" s="2">
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>765</v>
+        <v>795</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -20141,13 +21476,13 @@
         <v>180005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>769</v>
+        <v>799</v>
       </c>
       <c r="E10" s="2">
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>765</v>
+        <v>795</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -20167,13 +21502,13 @@
         <v>180006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>770</v>
+        <v>800</v>
       </c>
       <c r="E11" s="2">
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>765</v>
+        <v>795</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -20195,13 +21530,13 @@
         <v>180007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>771</v>
+        <v>801</v>
       </c>
       <c r="E12" s="2">
         <v>18</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>765</v>
+        <v>795</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -20223,13 +21558,13 @@
         <v>180008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>772</v>
+        <v>802</v>
       </c>
       <c r="E13" s="2">
         <v>18</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>765</v>
+        <v>795</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -20251,13 +21586,13 @@
         <v>180009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>773</v>
+        <v>803</v>
       </c>
       <c r="E14" s="2">
         <v>18</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>765</v>
+        <v>795</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -20279,13 +21614,13 @@
         <v>180010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>774</v>
+        <v>804</v>
       </c>
       <c r="E15" s="2">
         <v>18</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>765</v>
+        <v>795</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -20307,13 +21642,13 @@
         <v>180011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>775</v>
+        <v>805</v>
       </c>
       <c r="E16" s="2">
         <v>18</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>765</v>
+        <v>795</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -20335,13 +21670,13 @@
         <v>180012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>776</v>
+        <v>806</v>
       </c>
       <c r="E17" s="2">
         <v>18</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>765</v>
+        <v>795</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -20363,13 +21698,13 @@
         <v>180013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>777</v>
+        <v>807</v>
       </c>
       <c r="E18" s="2">
         <v>18</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>765</v>
+        <v>795</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -20391,13 +21726,13 @@
         <v>180014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>778</v>
+        <v>808</v>
       </c>
       <c r="E19" s="2">
         <v>18</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>765</v>
+        <v>795</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -20419,13 +21754,13 @@
         <v>180015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>779</v>
+        <v>809</v>
       </c>
       <c r="E20" s="2">
         <v>18</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>765</v>
+        <v>795</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -20447,13 +21782,13 @@
         <v>180016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>780</v>
+        <v>810</v>
       </c>
       <c r="E21" s="2">
         <v>18</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>765</v>
+        <v>795</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -20475,13 +21810,13 @@
         <v>180017</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="E22" s="2">
         <v>18</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>765</v>
+        <v>795</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -20503,13 +21838,13 @@
         <v>180018</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>782</v>
+        <v>812</v>
       </c>
       <c r="E23" s="2">
         <v>18</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>765</v>
+        <v>795</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -20531,13 +21866,13 @@
         <v>180019</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>783</v>
+        <v>813</v>
       </c>
       <c r="E24" s="2">
         <v>18</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>765</v>
+        <v>795</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -20559,13 +21894,13 @@
         <v>180020</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>784</v>
+        <v>814</v>
       </c>
       <c r="E25" s="2">
         <v>18</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>765</v>
+        <v>795</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -20587,13 +21922,13 @@
         <v>180021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>785</v>
+        <v>815</v>
       </c>
       <c r="E26" s="2">
         <v>18</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>765</v>
+        <v>795</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -20615,13 +21950,13 @@
         <v>180022</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>786</v>
+        <v>816</v>
       </c>
       <c r="E27" s="2">
         <v>18</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>765</v>
+        <v>795</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -20648,13 +21983,13 @@
         <v>180030</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>787</v>
+        <v>817</v>
       </c>
       <c r="E29" s="2">
         <v>18</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>765</v>
+        <v>795</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -20676,13 +22011,13 @@
         <v>180031</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>788</v>
+        <v>818</v>
       </c>
       <c r="E30" s="2">
         <v>18</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>765</v>
+        <v>795</v>
       </c>
       <c r="G30" s="3">
         <v>1</v>
@@ -20702,13 +22037,13 @@
         <v>180032</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>789</v>
+        <v>819</v>
       </c>
       <c r="E31" s="2">
         <v>18</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>765</v>
+        <v>795</v>
       </c>
       <c r="G31" s="3">
         <v>1</v>
@@ -20728,13 +22063,13 @@
         <v>180033</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>790</v>
+        <v>820</v>
       </c>
       <c r="E32" s="2">
         <v>18</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>765</v>
+        <v>795</v>
       </c>
       <c r="G32" s="3">
         <v>1</v>
@@ -20754,13 +22089,13 @@
         <v>180034</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>791</v>
+        <v>821</v>
       </c>
       <c r="E33" s="2">
         <v>18</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>765</v>
+        <v>795</v>
       </c>
       <c r="G33" s="3">
         <v>1</v>
@@ -20782,13 +22117,13 @@
         <v>180035</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>792</v>
+        <v>822</v>
       </c>
       <c r="E34" s="2">
         <v>18</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>765</v>
+        <v>795</v>
       </c>
       <c r="G34" s="3">
         <v>1</v>
@@ -20810,13 +22145,13 @@
         <v>180036</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>793</v>
+        <v>823</v>
       </c>
       <c r="E35" s="2">
         <v>18</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>765</v>
+        <v>795</v>
       </c>
       <c r="G35" s="3">
         <v>1</v>
@@ -20838,13 +22173,13 @@
         <v>180037</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>794</v>
+        <v>824</v>
       </c>
       <c r="E36" s="2">
         <v>18</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>765</v>
+        <v>795</v>
       </c>
       <c r="G36" s="3">
         <v>1</v>
@@ -21005,13 +22340,13 @@
         <v>190001</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>795</v>
+        <v>825</v>
       </c>
       <c r="E6" s="2">
         <v>19</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>796</v>
+        <v>826</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -21031,13 +22366,13 @@
         <v>190002</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="E7" s="2">
         <v>19</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>796</v>
+        <v>826</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -21057,13 +22392,13 @@
         <v>190003</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>798</v>
+        <v>828</v>
       </c>
       <c r="E8" s="2">
         <v>19</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>796</v>
+        <v>826</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -21083,13 +22418,13 @@
         <v>190004</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>799</v>
+        <v>829</v>
       </c>
       <c r="E9" s="2">
         <v>19</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>796</v>
+        <v>826</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -21109,13 +22444,13 @@
         <v>190005</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>800</v>
+        <v>830</v>
       </c>
       <c r="E10" s="2">
         <v>19</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>796</v>
+        <v>826</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -21135,13 +22470,13 @@
         <v>190006</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>801</v>
+        <v>831</v>
       </c>
       <c r="E11" s="2">
         <v>19</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>796</v>
+        <v>826</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
+    <workbookView windowHeight="17680" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -344,7 +344,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="832">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="834">
   <si>
     <t>_Id</t>
   </si>
@@ -2819,6 +2819,12 @@
   </si>
   <si>
     <t>极.传世契约</t>
+  </si>
+  <si>
+    <t>极·万界图</t>
+  </si>
+  <si>
+    <t>极·金蛟剪</t>
   </si>
   <si>
     <t>定身指环</t>
@@ -3063,12 +3069,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -21246,7 +21252,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:M36"/>
+  <dimension ref="C1:M38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="4" max="4" width="9.625" customWidth="1"/>
@@ -22195,6 +22201,62 @@
       </c>
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
+    </row>
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C37" s="2">
+        <v>180038</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>825</v>
+      </c>
+      <c r="E37" s="2">
+        <v>18</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="G37" s="3">
+        <v>1</v>
+      </c>
+      <c r="H37" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I37" s="2">
+        <v>0</v>
+      </c>
+      <c r="J37" s="2">
+        <v>7</v>
+      </c>
+      <c r="L37" s="3"/>
+      <c r="M37" s="3"/>
+    </row>
+    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C38" s="2">
+        <v>180039</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>826</v>
+      </c>
+      <c r="E38" s="2">
+        <v>18</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="G38" s="3">
+        <v>1</v>
+      </c>
+      <c r="H38" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I38" s="2">
+        <v>0</v>
+      </c>
+      <c r="J38" s="2">
+        <v>7</v>
+      </c>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -22340,13 +22402,13 @@
         <v>190001</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="E6" s="2">
         <v>19</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -22366,13 +22428,13 @@
         <v>190002</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="E7" s="2">
         <v>19</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -22392,13 +22454,13 @@
         <v>190003</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="E8" s="2">
         <v>19</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -22418,13 +22480,13 @@
         <v>190004</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="E9" s="2">
         <v>19</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -22444,13 +22506,13 @@
         <v>190005</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="E10" s="2">
         <v>19</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -22470,13 +22532,13 @@
         <v>190006</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="E11" s="2">
         <v>19</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -13,8 +13,9 @@
     <sheet name="时装" sheetId="4" r:id="rId4"/>
     <sheet name="遗物" sheetId="5" r:id="rId5"/>
     <sheet name="红装材料" sheetId="6" r:id="rId6"/>
-    <sheet name="法宝" sheetId="7" r:id="rId7"/>
-    <sheet name="神戒" sheetId="8" r:id="rId8"/>
+    <sheet name="宝石" sheetId="9" r:id="rId7"/>
+    <sheet name="法宝" sheetId="7" r:id="rId8"/>
+    <sheet name="神戒" sheetId="8" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -343,8 +344,47 @@
 </comments>
 </file>
 
+<file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>admin</author>
+  </authors>
+  <commentList>
+    <comment ref="E3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 金币
+2 装备
+3 技能书
+4.礼包
+5.材料
+6.buff
+7,金币收益
+8,经验收益</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="834">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1602" uniqueCount="851">
   <si>
     <t>_Id</t>
   </si>
@@ -2726,6 +2766,57 @@
   </si>
   <si>
     <t>二二阶装备升阶石</t>
+  </si>
+  <si>
+    <t>攻击宝石</t>
+  </si>
+  <si>
+    <t>神器上面可以镶嵌</t>
+  </si>
+  <si>
+    <t>防御宝石</t>
+  </si>
+  <si>
+    <t>生命宝石</t>
+  </si>
+  <si>
+    <t>命中宝石</t>
+  </si>
+  <si>
+    <t>闪避宝石</t>
+  </si>
+  <si>
+    <t>物理宝石</t>
+  </si>
+  <si>
+    <t>魔法宝石</t>
+  </si>
+  <si>
+    <t>道术宝石</t>
+  </si>
+  <si>
+    <t>增伤宝石</t>
+  </si>
+  <si>
+    <t>韧性宝石</t>
+  </si>
+  <si>
+    <t>盘古斧身</t>
+  </si>
+  <si>
+    <t>激活神器</t>
+  </si>
+  <si>
+    <t>盘古斧背</t>
+  </si>
+  <si>
+    <t>盘古斧柄</t>
+  </si>
+  <si>
+    <t>盘古斧刃</t>
+  </si>
+  <si>
+    <t>盘古心核</t>
   </si>
   <si>
     <t>BOSS杀手</t>
@@ -2858,7 +2949,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2901,7 +2992,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FFFF0000"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2911,12 +3001,18 @@
       <color rgb="FFFF0000"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
@@ -3069,12 +3165,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3410,16 +3506,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3428,119 +3521,122 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3554,11 +3650,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
@@ -4002,7 +4099,7 @@
       <c r="C6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="15" t="s">
         <v>23</v>
       </c>
       <c r="E6" s="3" t="s">
@@ -4037,7 +4134,7 @@
       <c r="C7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="15" t="s">
         <v>30</v>
       </c>
       <c r="E7" s="3" t="s">
@@ -4072,7 +4169,7 @@
       <c r="C8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="15" t="s">
         <v>34</v>
       </c>
       <c r="E8" s="3" t="s">
@@ -4107,7 +4204,7 @@
       <c r="C9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="15" t="s">
         <v>38</v>
       </c>
       <c r="E9" s="3" t="s">
@@ -4142,7 +4239,7 @@
       <c r="C10" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="15" t="s">
         <v>43</v>
       </c>
       <c r="E10" s="3" t="s">
@@ -4177,7 +4274,7 @@
       <c r="C11" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="15" t="s">
         <v>46</v>
       </c>
       <c r="E11" s="3" t="s">
@@ -4212,7 +4309,7 @@
       <c r="C12" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="15" t="s">
         <v>50</v>
       </c>
       <c r="E12" s="3" t="s">
@@ -4244,10 +4341,10 @@
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:13">
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="15" t="s">
         <v>54</v>
       </c>
       <c r="E13" s="3" t="s">
@@ -4262,7 +4359,7 @@
       <c r="H13" s="3">
         <v>99999999</v>
       </c>
-      <c r="I13" s="15" t="s">
+      <c r="I13" s="16" t="s">
         <v>56</v>
       </c>
       <c r="J13" s="3">
@@ -4279,10 +4376,10 @@
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:13">
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="15" t="s">
         <v>58</v>
       </c>
       <c r="E14" s="3" t="s">
@@ -4297,7 +4394,7 @@
       <c r="H14" s="3">
         <v>99999999</v>
       </c>
-      <c r="I14" s="15" t="s">
+      <c r="I14" s="16" t="s">
         <v>56</v>
       </c>
       <c r="J14" s="3">
@@ -4314,10 +4411,10 @@
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:13">
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="15" t="s">
         <v>61</v>
       </c>
       <c r="E15" s="3" t="s">
@@ -4332,7 +4429,7 @@
       <c r="H15" s="3">
         <v>99999999</v>
       </c>
-      <c r="I15" s="15" t="s">
+      <c r="I15" s="16" t="s">
         <v>56</v>
       </c>
       <c r="J15" s="3">
@@ -4349,10 +4446,10 @@
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:13">
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="15" t="s">
         <v>64</v>
       </c>
       <c r="E16" s="3" t="s">
@@ -4367,7 +4464,7 @@
       <c r="H16" s="3">
         <v>99999999</v>
       </c>
-      <c r="I16" s="15" t="s">
+      <c r="I16" s="16" t="s">
         <v>56</v>
       </c>
       <c r="J16" s="3">
@@ -4387,7 +4484,7 @@
       <c r="C18" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="15" t="s">
         <v>67</v>
       </c>
       <c r="E18" s="3" t="s">
@@ -4422,7 +4519,7 @@
       <c r="C19" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D19" s="15" t="s">
         <v>70</v>
       </c>
       <c r="E19" s="3" t="s">
@@ -4457,7 +4554,7 @@
       <c r="C20" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D20" s="15" t="s">
         <v>73</v>
       </c>
       <c r="E20" s="3" t="s">
@@ -4492,7 +4589,7 @@
       <c r="C21" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="14" t="s">
+      <c r="D21" s="15" t="s">
         <v>76</v>
       </c>
       <c r="E21" s="3" t="s">
@@ -4527,7 +4624,7 @@
       <c r="C22" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="D22" s="15" t="s">
         <v>79</v>
       </c>
       <c r="E22" s="3" t="s">
@@ -4562,7 +4659,7 @@
       <c r="C23" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D23" s="14" t="s">
+      <c r="D23" s="15" t="s">
         <v>82</v>
       </c>
       <c r="E23" s="3" t="s">
@@ -4597,7 +4694,7 @@
       <c r="C24" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="14" t="s">
+      <c r="D24" s="15" t="s">
         <v>85</v>
       </c>
       <c r="E24" s="3" t="s">
@@ -4629,10 +4726,10 @@
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:13">
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="D25" s="14" t="s">
+      <c r="D25" s="15" t="s">
         <v>88</v>
       </c>
       <c r="E25" s="3" t="s">
@@ -4647,7 +4744,7 @@
       <c r="H25" s="3">
         <v>99999999</v>
       </c>
-      <c r="I25" s="15" t="s">
+      <c r="I25" s="16" t="s">
         <v>56</v>
       </c>
       <c r="J25" s="3">
@@ -4664,10 +4761,10 @@
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:13">
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="14" t="s">
+      <c r="D26" s="15" t="s">
         <v>91</v>
       </c>
       <c r="E26" s="3" t="s">
@@ -4682,7 +4779,7 @@
       <c r="H26" s="3">
         <v>99999999</v>
       </c>
-      <c r="I26" s="15" t="s">
+      <c r="I26" s="16" t="s">
         <v>56</v>
       </c>
       <c r="J26" s="3">
@@ -4699,10 +4796,10 @@
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:13">
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="D27" s="14" t="s">
+      <c r="D27" s="15" t="s">
         <v>94</v>
       </c>
       <c r="E27" s="3" t="s">
@@ -4717,7 +4814,7 @@
       <c r="H27" s="3">
         <v>99999999</v>
       </c>
-      <c r="I27" s="15" t="s">
+      <c r="I27" s="16" t="s">
         <v>56</v>
       </c>
       <c r="J27" s="3">
@@ -4734,10 +4831,10 @@
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:13">
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="D28" s="14" t="s">
+      <c r="D28" s="15" t="s">
         <v>97</v>
       </c>
       <c r="E28" s="3" t="s">
@@ -4752,7 +4849,7 @@
       <c r="H28" s="3">
         <v>99999999</v>
       </c>
-      <c r="I28" s="15" t="s">
+      <c r="I28" s="16" t="s">
         <v>56</v>
       </c>
       <c r="J28" s="3">
@@ -4772,7 +4869,7 @@
       <c r="C30" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D30" s="14" t="s">
+      <c r="D30" s="15" t="s">
         <v>100</v>
       </c>
       <c r="E30" s="3" t="s">
@@ -4807,7 +4904,7 @@
       <c r="C31" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D31" s="14" t="s">
+      <c r="D31" s="15" t="s">
         <v>103</v>
       </c>
       <c r="E31" s="3" t="s">
@@ -4842,7 +4939,7 @@
       <c r="C32" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D32" s="14" t="s">
+      <c r="D32" s="15" t="s">
         <v>106</v>
       </c>
       <c r="E32" s="3" t="s">
@@ -4877,7 +4974,7 @@
       <c r="C33" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D33" s="14" t="s">
+      <c r="D33" s="15" t="s">
         <v>109</v>
       </c>
       <c r="E33" s="3" t="s">
@@ -4912,7 +5009,7 @@
       <c r="C34" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D34" s="14" t="s">
+      <c r="D34" s="15" t="s">
         <v>112</v>
       </c>
       <c r="E34" s="3" t="s">
@@ -4947,7 +5044,7 @@
       <c r="C35" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D35" s="14" t="s">
+      <c r="D35" s="15" t="s">
         <v>115</v>
       </c>
       <c r="E35" s="3" t="s">
@@ -4982,7 +5079,7 @@
       <c r="C36" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D36" s="14" t="s">
+      <c r="D36" s="15" t="s">
         <v>118</v>
       </c>
       <c r="E36" s="3" t="s">
@@ -5014,10 +5111,10 @@
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:13">
-      <c r="C37" s="15" t="s">
+      <c r="C37" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="D37" s="14" t="s">
+      <c r="D37" s="15" t="s">
         <v>121</v>
       </c>
       <c r="E37" s="3" t="s">
@@ -5032,7 +5129,7 @@
       <c r="H37" s="3">
         <v>99999999</v>
       </c>
-      <c r="I37" s="15" t="s">
+      <c r="I37" s="16" t="s">
         <v>56</v>
       </c>
       <c r="J37" s="3">
@@ -5049,10 +5146,10 @@
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:13">
-      <c r="C38" s="15" t="s">
+      <c r="C38" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="D38" s="14" t="s">
+      <c r="D38" s="15" t="s">
         <v>124</v>
       </c>
       <c r="E38" s="3" t="s">
@@ -5067,7 +5164,7 @@
       <c r="H38" s="3">
         <v>99999999</v>
       </c>
-      <c r="I38" s="15" t="s">
+      <c r="I38" s="16" t="s">
         <v>56</v>
       </c>
       <c r="J38" s="3">
@@ -5084,10 +5181,10 @@
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:13">
-      <c r="C39" s="15" t="s">
+      <c r="C39" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="D39" s="14" t="s">
+      <c r="D39" s="15" t="s">
         <v>127</v>
       </c>
       <c r="E39" s="3" t="s">
@@ -5102,7 +5199,7 @@
       <c r="H39" s="3">
         <v>99999999</v>
       </c>
-      <c r="I39" s="15" t="s">
+      <c r="I39" s="16" t="s">
         <v>56</v>
       </c>
       <c r="J39" s="3">
@@ -5119,10 +5216,10 @@
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:13">
-      <c r="C40" s="15" t="s">
+      <c r="C40" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="D40" s="14" t="s">
+      <c r="D40" s="15" t="s">
         <v>130</v>
       </c>
       <c r="E40" s="3" t="s">
@@ -5137,7 +5234,7 @@
       <c r="H40" s="3">
         <v>99999999</v>
       </c>
-      <c r="I40" s="15" t="s">
+      <c r="I40" s="16" t="s">
         <v>56</v>
       </c>
       <c r="J40" s="3">
@@ -5959,7 +6056,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L26" s="3">
         <v>0</v>
@@ -7300,7 +7397,7 @@
       <c r="C74" s="3">
         <v>8101</v>
       </c>
-      <c r="D74" s="13" t="s">
+      <c r="D74" s="14" t="s">
         <v>240</v>
       </c>
       <c r="E74" s="3">
@@ -7332,7 +7429,7 @@
       <c r="C75" s="3">
         <v>8102</v>
       </c>
-      <c r="D75" s="13" t="s">
+      <c r="D75" s="14" t="s">
         <v>242</v>
       </c>
       <c r="E75" s="3">
@@ -7364,7 +7461,7 @@
       <c r="C76" s="3">
         <v>8103</v>
       </c>
-      <c r="D76" s="13" t="s">
+      <c r="D76" s="14" t="s">
         <v>243</v>
       </c>
       <c r="E76" s="3">
@@ -7396,7 +7493,7 @@
       <c r="C77" s="3">
         <v>8104</v>
       </c>
-      <c r="D77" s="13" t="s">
+      <c r="D77" s="14" t="s">
         <v>244</v>
       </c>
       <c r="E77" s="3">
@@ -7428,7 +7525,7 @@
       <c r="C78" s="3">
         <v>8105</v>
       </c>
-      <c r="D78" s="13" t="s">
+      <c r="D78" s="14" t="s">
         <v>245</v>
       </c>
       <c r="E78" s="3">
@@ -7460,7 +7557,7 @@
       <c r="C79" s="3">
         <v>8106</v>
       </c>
-      <c r="D79" s="13" t="s">
+      <c r="D79" s="14" t="s">
         <v>246</v>
       </c>
       <c r="E79" s="3">
@@ -7492,7 +7589,7 @@
       <c r="C80" s="3">
         <v>8107</v>
       </c>
-      <c r="D80" s="13" t="s">
+      <c r="D80" s="14" t="s">
         <v>247</v>
       </c>
       <c r="E80" s="3">
@@ -7524,7 +7621,7 @@
       <c r="C81" s="3">
         <v>8108</v>
       </c>
-      <c r="D81" s="13" t="s">
+      <c r="D81" s="14" t="s">
         <v>248</v>
       </c>
       <c r="E81" s="3">
@@ -7556,7 +7653,7 @@
       <c r="C83" s="3">
         <v>8201</v>
       </c>
-      <c r="D83" s="13" t="s">
+      <c r="D83" s="14" t="s">
         <v>249</v>
       </c>
       <c r="E83" s="3">
@@ -7591,7 +7688,7 @@
       <c r="C84" s="3">
         <v>8202</v>
       </c>
-      <c r="D84" s="13" t="s">
+      <c r="D84" s="14" t="s">
         <v>251</v>
       </c>
       <c r="E84" s="3">
@@ -7626,7 +7723,7 @@
       <c r="C85" s="3">
         <v>8203</v>
       </c>
-      <c r="D85" s="13" t="s">
+      <c r="D85" s="14" t="s">
         <v>253</v>
       </c>
       <c r="E85" s="3">
@@ -7661,7 +7758,7 @@
       <c r="C86" s="3">
         <v>8204</v>
       </c>
-      <c r="D86" s="13" t="s">
+      <c r="D86" s="14" t="s">
         <v>255</v>
       </c>
       <c r="E86" s="3">
@@ -7696,7 +7793,7 @@
       <c r="C87" s="3">
         <v>8205</v>
       </c>
-      <c r="D87" s="13" t="s">
+      <c r="D87" s="14" t="s">
         <v>257</v>
       </c>
       <c r="E87" s="3">
@@ -7731,7 +7828,7 @@
       <c r="C88" s="3">
         <v>8206</v>
       </c>
-      <c r="D88" s="13" t="s">
+      <c r="D88" s="14" t="s">
         <v>259</v>
       </c>
       <c r="E88" s="3">
@@ -7766,7 +7863,7 @@
       <c r="C89" s="3">
         <v>8207</v>
       </c>
-      <c r="D89" s="13" t="s">
+      <c r="D89" s="14" t="s">
         <v>261</v>
       </c>
       <c r="E89" s="3">
@@ -7798,46 +7895,46 @@
       </c>
     </row>
     <row r="91" customHeight="1" spans="4:4">
-      <c r="D91" s="13"/>
+      <c r="D91" s="14"/>
     </row>
     <row r="92" customHeight="1" spans="4:4">
-      <c r="D92" s="13"/>
+      <c r="D92" s="14"/>
     </row>
     <row r="93" customHeight="1" spans="4:4">
-      <c r="D93" s="13"/>
+      <c r="D93" s="14"/>
     </row>
     <row r="94" customHeight="1" spans="4:4">
-      <c r="D94" s="13"/>
+      <c r="D94" s="14"/>
     </row>
     <row r="95" customHeight="1" spans="4:4">
-      <c r="D95" s="13"/>
+      <c r="D95" s="14"/>
     </row>
     <row r="96" customHeight="1" spans="4:4">
-      <c r="D96" s="13"/>
+      <c r="D96" s="14"/>
     </row>
     <row r="97" customHeight="1" spans="4:4">
-      <c r="D97" s="13"/>
+      <c r="D97" s="14"/>
     </row>
     <row r="99" customHeight="1" spans="4:4">
-      <c r="D99" s="13"/>
+      <c r="D99" s="14"/>
     </row>
     <row r="100" customHeight="1" spans="4:4">
-      <c r="D100" s="13"/>
+      <c r="D100" s="14"/>
     </row>
     <row r="101" customHeight="1" spans="4:4">
-      <c r="D101" s="13"/>
+      <c r="D101" s="14"/>
     </row>
     <row r="102" customHeight="1" spans="4:4">
-      <c r="D102" s="13"/>
+      <c r="D102" s="14"/>
     </row>
     <row r="103" customHeight="1" spans="4:4">
-      <c r="D103" s="13"/>
+      <c r="D103" s="14"/>
     </row>
     <row r="104" customHeight="1" spans="4:4">
-      <c r="D104" s="13"/>
+      <c r="D104" s="14"/>
     </row>
     <row r="105" customHeight="1" spans="4:4">
-      <c r="D105" s="13"/>
+      <c r="D105" s="14"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -8715,7 +8812,7 @@
       <c r="C33" s="2">
         <v>2000011</v>
       </c>
-      <c r="D33" s="12" t="s">
+      <c r="D33" s="13" t="s">
         <v>291</v>
       </c>
       <c r="E33" s="2">
@@ -8743,7 +8840,7 @@
       <c r="C34" s="2">
         <v>2000012</v>
       </c>
-      <c r="D34" s="12" t="s">
+      <c r="D34" s="13" t="s">
         <v>292</v>
       </c>
       <c r="E34" s="2">
@@ -8771,7 +8868,7 @@
       <c r="C35" s="2">
         <v>2000013</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="D35" s="13" t="s">
         <v>293</v>
       </c>
       <c r="E35" s="2">
@@ -11798,7 +11895,7 @@
       <c r="C22" s="2">
         <v>3000017</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="12" t="s">
         <v>401</v>
       </c>
       <c r="E22" s="2">
@@ -11826,7 +11923,7 @@
       <c r="C23" s="2">
         <v>3000018</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="12" t="s">
         <v>402</v>
       </c>
       <c r="E23" s="2">
@@ -11854,7 +11951,7 @@
       <c r="C24" s="2">
         <v>3000019</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="12" t="s">
         <v>403</v>
       </c>
       <c r="E24" s="2">
@@ -11882,7 +11979,7 @@
       <c r="C25" s="2">
         <v>3000020</v>
       </c>
-      <c r="D25" s="11" t="s">
+      <c r="D25" s="12" t="s">
         <v>404</v>
       </c>
       <c r="E25" s="2">
@@ -11910,7 +12007,7 @@
       <c r="C26" s="2">
         <v>3000021</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="D26" s="12" t="s">
         <v>405</v>
       </c>
       <c r="E26" s="2">
@@ -11938,7 +12035,7 @@
       <c r="C27" s="2">
         <v>3000022</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="D27" s="12" t="s">
         <v>406</v>
       </c>
       <c r="E27" s="2">
@@ -11966,7 +12063,7 @@
       <c r="C28" s="2">
         <v>3000023</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="D28" s="12" t="s">
         <v>407</v>
       </c>
       <c r="E28" s="2">
@@ -11994,7 +12091,7 @@
       <c r="C29" s="2">
         <v>3000024</v>
       </c>
-      <c r="D29" s="11" t="s">
+      <c r="D29" s="12" t="s">
         <v>408</v>
       </c>
       <c r="E29" s="2">
@@ -12996,7 +13093,7 @@
       <c r="J11" s="2">
         <v>6</v>
       </c>
-      <c r="K11" s="11" t="s">
+      <c r="K11" s="12" t="s">
         <v>443</v>
       </c>
       <c r="L11" s="3">
@@ -13031,7 +13128,7 @@
       <c r="J12" s="2">
         <v>6</v>
       </c>
-      <c r="K12" s="11" t="s">
+      <c r="K12" s="12" t="s">
         <v>445</v>
       </c>
       <c r="L12" s="3">
@@ -13066,7 +13163,7 @@
       <c r="J13" s="2">
         <v>6</v>
       </c>
-      <c r="K13" s="11" t="s">
+      <c r="K13" s="12" t="s">
         <v>447</v>
       </c>
       <c r="L13" s="3">
@@ -13101,7 +13198,7 @@
       <c r="J14" s="2">
         <v>6</v>
       </c>
-      <c r="K14" s="11" t="s">
+      <c r="K14" s="12" t="s">
         <v>449</v>
       </c>
       <c r="L14" s="3">
@@ -13136,7 +13233,7 @@
       <c r="J15" s="2">
         <v>6</v>
       </c>
-      <c r="K15" s="11" t="s">
+      <c r="K15" s="12" t="s">
         <v>451</v>
       </c>
       <c r="L15" s="3">
@@ -14721,38 +14818,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" s="9" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C61" s="9">
+    <row r="61" s="10" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C61" s="10">
         <v>40000105</v>
       </c>
-      <c r="D61" s="10" t="s">
+      <c r="D61" s="11" t="s">
         <v>507</v>
       </c>
-      <c r="E61" s="9">
+      <c r="E61" s="10">
         <v>14</v>
       </c>
-      <c r="F61" s="9" t="s">
+      <c r="F61" s="10" t="s">
         <v>434</v>
       </c>
-      <c r="G61" s="9">
-        <v>1</v>
-      </c>
-      <c r="H61" s="9">
-        <v>99999</v>
-      </c>
-      <c r="I61" s="9">
-        <v>0</v>
-      </c>
-      <c r="J61" s="9">
-        <v>6</v>
-      </c>
-      <c r="K61" s="9">
+      <c r="G61" s="10">
+        <v>1</v>
+      </c>
+      <c r="H61" s="10">
+        <v>99999</v>
+      </c>
+      <c r="I61" s="10">
+        <v>0</v>
+      </c>
+      <c r="J61" s="10">
+        <v>6</v>
+      </c>
+      <c r="K61" s="10">
         <v>1100</v>
       </c>
-      <c r="L61" s="10">
+      <c r="L61" s="11">
         <v>4018</v>
       </c>
-      <c r="M61" s="10">
+      <c r="M61" s="11">
         <v>1</v>
       </c>
     </row>
@@ -15946,38 +16043,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" s="9" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C96" s="9">
+    <row r="96" s="10" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C96" s="10">
         <v>40000140</v>
       </c>
-      <c r="D96" s="10" t="s">
+      <c r="D96" s="11" t="s">
         <v>542</v>
       </c>
-      <c r="E96" s="9">
+      <c r="E96" s="10">
         <v>14</v>
       </c>
-      <c r="F96" s="9" t="s">
+      <c r="F96" s="10" t="s">
         <v>434</v>
       </c>
-      <c r="G96" s="9">
-        <v>1</v>
-      </c>
-      <c r="H96" s="9">
-        <v>99999</v>
-      </c>
-      <c r="I96" s="9">
-        <v>0</v>
-      </c>
-      <c r="J96" s="9">
-        <v>6</v>
-      </c>
-      <c r="K96" s="9">
+      <c r="G96" s="10">
+        <v>1</v>
+      </c>
+      <c r="H96" s="10">
+        <v>99999</v>
+      </c>
+      <c r="I96" s="10">
+        <v>0</v>
+      </c>
+      <c r="J96" s="10">
+        <v>6</v>
+      </c>
+      <c r="K96" s="10">
         <v>1450</v>
       </c>
-      <c r="L96" s="10">
+      <c r="L96" s="11">
         <v>4018</v>
       </c>
-      <c r="M96" s="10">
+      <c r="M96" s="11">
         <v>1</v>
       </c>
     </row>
@@ -17559,38 +17656,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" s="6" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C13" s="6">
+    <row r="13" s="7" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C13" s="7">
         <v>50000008</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="9" t="s">
         <v>591</v>
       </c>
-      <c r="E13" s="6">
-        <v>5</v>
-      </c>
-      <c r="F13" s="6" t="s">
+      <c r="E13" s="7">
+        <v>5</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>592</v>
       </c>
-      <c r="G13" s="6">
-        <v>1</v>
-      </c>
-      <c r="H13" s="6">
-        <v>99999</v>
-      </c>
-      <c r="I13" s="6">
-        <v>0</v>
-      </c>
-      <c r="J13" s="6">
-        <v>6</v>
-      </c>
-      <c r="K13" s="6">
+      <c r="G13" s="7">
+        <v>1</v>
+      </c>
+      <c r="H13" s="7">
+        <v>99999</v>
+      </c>
+      <c r="I13" s="7">
+        <v>0</v>
+      </c>
+      <c r="J13" s="7">
+        <v>6</v>
+      </c>
+      <c r="K13" s="7">
         <v>800</v>
       </c>
-      <c r="L13" s="7">
+      <c r="L13" s="9">
         <v>4015</v>
       </c>
-      <c r="M13" s="7">
+      <c r="M13" s="9">
         <v>1</v>
       </c>
     </row>
@@ -17839,38 +17936,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" s="6" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C21" s="6">
+    <row r="21" s="7" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C21" s="7">
         <v>50000016</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="9" t="s">
         <v>607</v>
       </c>
-      <c r="E21" s="6">
-        <v>5</v>
-      </c>
-      <c r="F21" s="6" t="s">
+      <c r="E21" s="7">
+        <v>5</v>
+      </c>
+      <c r="F21" s="7" t="s">
         <v>608</v>
       </c>
-      <c r="G21" s="6">
-        <v>1</v>
-      </c>
-      <c r="H21" s="6">
-        <v>99999</v>
-      </c>
-      <c r="I21" s="6">
-        <v>0</v>
-      </c>
-      <c r="J21" s="6">
-        <v>6</v>
-      </c>
-      <c r="K21" s="6">
+      <c r="G21" s="7">
+        <v>1</v>
+      </c>
+      <c r="H21" s="7">
+        <v>99999</v>
+      </c>
+      <c r="I21" s="7">
+        <v>0</v>
+      </c>
+      <c r="J21" s="7">
+        <v>6</v>
+      </c>
+      <c r="K21" s="7">
         <v>850</v>
       </c>
-      <c r="L21" s="7">
+      <c r="L21" s="9">
         <v>4015</v>
       </c>
-      <c r="M21" s="7">
+      <c r="M21" s="9">
         <v>1</v>
       </c>
     </row>
@@ -18119,38 +18216,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" s="6" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C29" s="6">
+    <row r="29" s="7" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C29" s="7">
         <v>50000024</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="9" t="s">
         <v>623</v>
       </c>
-      <c r="E29" s="6">
-        <v>5</v>
-      </c>
-      <c r="F29" s="6" t="s">
+      <c r="E29" s="7">
+        <v>5</v>
+      </c>
+      <c r="F29" s="7" t="s">
         <v>624</v>
       </c>
-      <c r="G29" s="6">
-        <v>1</v>
-      </c>
-      <c r="H29" s="6">
-        <v>99999</v>
-      </c>
-      <c r="I29" s="6">
-        <v>0</v>
-      </c>
-      <c r="J29" s="6">
+      <c r="G29" s="7">
+        <v>1</v>
+      </c>
+      <c r="H29" s="7">
+        <v>99999</v>
+      </c>
+      <c r="I29" s="7">
+        <v>0</v>
+      </c>
+      <c r="J29" s="7">
         <v>6</v>
       </c>
       <c r="K29" s="2">
         <v>900</v>
       </c>
-      <c r="L29" s="7">
+      <c r="L29" s="9">
         <v>4015</v>
       </c>
-      <c r="M29" s="7">
+      <c r="M29" s="9">
         <v>1</v>
       </c>
     </row>
@@ -18399,38 +18496,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" s="6" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C37" s="6">
+    <row r="37" s="7" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C37" s="7">
         <v>50000032</v>
       </c>
-      <c r="D37" s="7" t="s">
+      <c r="D37" s="9" t="s">
         <v>639</v>
       </c>
-      <c r="E37" s="6">
-        <v>5</v>
-      </c>
-      <c r="F37" s="6" t="s">
+      <c r="E37" s="7">
+        <v>5</v>
+      </c>
+      <c r="F37" s="7" t="s">
         <v>640</v>
       </c>
-      <c r="G37" s="6">
-        <v>1</v>
-      </c>
-      <c r="H37" s="6">
-        <v>99999</v>
-      </c>
-      <c r="I37" s="6">
-        <v>0</v>
-      </c>
-      <c r="J37" s="6">
+      <c r="G37" s="7">
+        <v>1</v>
+      </c>
+      <c r="H37" s="7">
+        <v>99999</v>
+      </c>
+      <c r="I37" s="7">
+        <v>0</v>
+      </c>
+      <c r="J37" s="7">
         <v>6</v>
       </c>
       <c r="K37" s="2">
         <v>950</v>
       </c>
-      <c r="L37" s="7">
+      <c r="L37" s="9">
         <v>4015</v>
       </c>
-      <c r="M37" s="7">
+      <c r="M37" s="9">
         <v>1</v>
       </c>
     </row>
@@ -18679,38 +18776,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" s="6" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C45" s="6">
+    <row r="45" s="7" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C45" s="7">
         <v>50000040</v>
       </c>
-      <c r="D45" s="7" t="s">
+      <c r="D45" s="9" t="s">
         <v>655</v>
       </c>
-      <c r="E45" s="6">
-        <v>5</v>
-      </c>
-      <c r="F45" s="6" t="s">
+      <c r="E45" s="7">
+        <v>5</v>
+      </c>
+      <c r="F45" s="7" t="s">
         <v>656</v>
       </c>
-      <c r="G45" s="6">
-        <v>1</v>
-      </c>
-      <c r="H45" s="6">
-        <v>99999</v>
-      </c>
-      <c r="I45" s="6">
-        <v>0</v>
-      </c>
-      <c r="J45" s="6">
+      <c r="G45" s="7">
+        <v>1</v>
+      </c>
+      <c r="H45" s="7">
+        <v>99999</v>
+      </c>
+      <c r="I45" s="7">
+        <v>0</v>
+      </c>
+      <c r="J45" s="7">
         <v>6</v>
       </c>
       <c r="K45" s="2">
         <v>1000</v>
       </c>
-      <c r="L45" s="7">
+      <c r="L45" s="9">
         <v>4015</v>
       </c>
-      <c r="M45" s="7">
+      <c r="M45" s="9">
         <v>1</v>
       </c>
     </row>
@@ -18959,38 +19056,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" s="6" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C53" s="6">
+    <row r="53" s="7" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C53" s="7">
         <v>50000048</v>
       </c>
-      <c r="D53" s="7" t="s">
+      <c r="D53" s="9" t="s">
         <v>671</v>
       </c>
-      <c r="E53" s="6">
-        <v>5</v>
-      </c>
-      <c r="F53" s="6" t="s">
+      <c r="E53" s="7">
+        <v>5</v>
+      </c>
+      <c r="F53" s="7" t="s">
         <v>672</v>
       </c>
-      <c r="G53" s="6">
-        <v>1</v>
-      </c>
-      <c r="H53" s="6">
-        <v>99999</v>
-      </c>
-      <c r="I53" s="6">
-        <v>0</v>
-      </c>
-      <c r="J53" s="6">
+      <c r="G53" s="7">
+        <v>1</v>
+      </c>
+      <c r="H53" s="7">
+        <v>99999</v>
+      </c>
+      <c r="I53" s="7">
+        <v>0</v>
+      </c>
+      <c r="J53" s="7">
         <v>6</v>
       </c>
       <c r="K53" s="2">
         <v>1050</v>
       </c>
-      <c r="L53" s="7">
+      <c r="L53" s="9">
         <v>4015</v>
       </c>
-      <c r="M53" s="7">
+      <c r="M53" s="9">
         <v>1</v>
       </c>
     </row>
@@ -19239,38 +19336,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" s="6" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C61" s="6">
+    <row r="61" s="7" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C61" s="7">
         <v>50000056</v>
       </c>
-      <c r="D61" s="7" t="s">
+      <c r="D61" s="9" t="s">
         <v>687</v>
       </c>
-      <c r="E61" s="6">
-        <v>5</v>
-      </c>
-      <c r="F61" s="6" t="s">
+      <c r="E61" s="7">
+        <v>5</v>
+      </c>
+      <c r="F61" s="7" t="s">
         <v>688</v>
       </c>
-      <c r="G61" s="6">
-        <v>1</v>
-      </c>
-      <c r="H61" s="6">
-        <v>99999</v>
-      </c>
-      <c r="I61" s="6">
-        <v>0</v>
-      </c>
-      <c r="J61" s="6">
+      <c r="G61" s="7">
+        <v>1</v>
+      </c>
+      <c r="H61" s="7">
+        <v>99999</v>
+      </c>
+      <c r="I61" s="7">
+        <v>0</v>
+      </c>
+      <c r="J61" s="7">
         <v>6</v>
       </c>
       <c r="K61" s="2">
         <v>1100</v>
       </c>
-      <c r="L61" s="7">
+      <c r="L61" s="9">
         <v>4015</v>
       </c>
-      <c r="M61" s="7">
+      <c r="M61" s="9">
         <v>1</v>
       </c>
     </row>
@@ -19519,38 +19616,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" s="6" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C69" s="6">
+    <row r="69" s="7" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C69" s="7">
         <v>50000064</v>
       </c>
-      <c r="D69" s="7" t="s">
+      <c r="D69" s="9" t="s">
         <v>703</v>
       </c>
-      <c r="E69" s="6">
-        <v>5</v>
-      </c>
-      <c r="F69" s="6" t="s">
+      <c r="E69" s="7">
+        <v>5</v>
+      </c>
+      <c r="F69" s="7" t="s">
         <v>704</v>
       </c>
-      <c r="G69" s="6">
-        <v>1</v>
-      </c>
-      <c r="H69" s="6">
-        <v>99999</v>
-      </c>
-      <c r="I69" s="6">
-        <v>0</v>
-      </c>
-      <c r="J69" s="6">
+      <c r="G69" s="7">
+        <v>1</v>
+      </c>
+      <c r="H69" s="7">
+        <v>99999</v>
+      </c>
+      <c r="I69" s="7">
+        <v>0</v>
+      </c>
+      <c r="J69" s="7">
         <v>6</v>
       </c>
       <c r="K69" s="2">
         <v>1150</v>
       </c>
-      <c r="L69" s="7">
+      <c r="L69" s="9">
         <v>4015</v>
       </c>
-      <c r="M69" s="7">
+      <c r="M69" s="9">
         <v>1</v>
       </c>
     </row>
@@ -19799,38 +19896,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" s="6" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C77" s="6">
+    <row r="77" s="7" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C77" s="7">
         <v>50000072</v>
       </c>
-      <c r="D77" s="7" t="s">
+      <c r="D77" s="9" t="s">
         <v>719</v>
       </c>
-      <c r="E77" s="6">
-        <v>5</v>
-      </c>
-      <c r="F77" s="6" t="s">
+      <c r="E77" s="7">
+        <v>5</v>
+      </c>
+      <c r="F77" s="7" t="s">
         <v>720</v>
       </c>
-      <c r="G77" s="6">
-        <v>1</v>
-      </c>
-      <c r="H77" s="6">
-        <v>99999</v>
-      </c>
-      <c r="I77" s="6">
-        <v>0</v>
-      </c>
-      <c r="J77" s="6">
+      <c r="G77" s="7">
+        <v>1</v>
+      </c>
+      <c r="H77" s="7">
+        <v>99999</v>
+      </c>
+      <c r="I77" s="7">
+        <v>0</v>
+      </c>
+      <c r="J77" s="7">
         <v>6</v>
       </c>
       <c r="K77" s="2">
         <v>1200</v>
       </c>
-      <c r="L77" s="7">
+      <c r="L77" s="9">
         <v>4015</v>
       </c>
-      <c r="M77" s="7">
+      <c r="M77" s="9">
         <v>1</v>
       </c>
     </row>
@@ -20079,38 +20176,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" s="6" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C85" s="6">
+    <row r="85" s="7" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C85" s="7">
         <v>50000080</v>
       </c>
-      <c r="D85" s="7" t="s">
+      <c r="D85" s="9" t="s">
         <v>735</v>
       </c>
-      <c r="E85" s="6">
-        <v>5</v>
-      </c>
-      <c r="F85" s="6" t="s">
+      <c r="E85" s="7">
+        <v>5</v>
+      </c>
+      <c r="F85" s="7" t="s">
         <v>736</v>
       </c>
-      <c r="G85" s="6">
-        <v>1</v>
-      </c>
-      <c r="H85" s="6">
-        <v>99999</v>
-      </c>
-      <c r="I85" s="6">
-        <v>0</v>
-      </c>
-      <c r="J85" s="6">
+      <c r="G85" s="7">
+        <v>1</v>
+      </c>
+      <c r="H85" s="7">
+        <v>99999</v>
+      </c>
+      <c r="I85" s="7">
+        <v>0</v>
+      </c>
+      <c r="J85" s="7">
         <v>6</v>
       </c>
       <c r="K85" s="2">
         <v>1250</v>
       </c>
-      <c r="L85" s="7">
+      <c r="L85" s="9">
         <v>4015</v>
       </c>
-      <c r="M85" s="7">
+      <c r="M85" s="9">
         <v>1</v>
       </c>
     </row>
@@ -20359,38 +20456,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" s="6" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C93" s="6">
+    <row r="93" s="7" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C93" s="7">
         <v>50000088</v>
       </c>
-      <c r="D93" s="7" t="s">
+      <c r="D93" s="9" t="s">
         <v>751</v>
       </c>
-      <c r="E93" s="6">
-        <v>5</v>
-      </c>
-      <c r="F93" s="6" t="s">
+      <c r="E93" s="7">
+        <v>5</v>
+      </c>
+      <c r="F93" s="7" t="s">
         <v>752</v>
       </c>
-      <c r="G93" s="6">
-        <v>1</v>
-      </c>
-      <c r="H93" s="6">
-        <v>99999</v>
-      </c>
-      <c r="I93" s="6">
-        <v>0</v>
-      </c>
-      <c r="J93" s="6">
+      <c r="G93" s="7">
+        <v>1</v>
+      </c>
+      <c r="H93" s="7">
+        <v>99999</v>
+      </c>
+      <c r="I93" s="7">
+        <v>0</v>
+      </c>
+      <c r="J93" s="7">
         <v>6</v>
       </c>
       <c r="K93" s="2">
         <v>1300</v>
       </c>
-      <c r="L93" s="7">
+      <c r="L93" s="9">
         <v>4015</v>
       </c>
-      <c r="M93" s="7">
+      <c r="M93" s="9">
         <v>1</v>
       </c>
     </row>
@@ -20639,38 +20736,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" s="6" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C101" s="6">
+    <row r="101" s="7" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C101" s="7">
         <v>50000096</v>
       </c>
-      <c r="D101" s="7" t="s">
+      <c r="D101" s="9" t="s">
         <v>767</v>
       </c>
-      <c r="E101" s="6">
-        <v>5</v>
-      </c>
-      <c r="F101" s="6" t="s">
+      <c r="E101" s="7">
+        <v>5</v>
+      </c>
+      <c r="F101" s="7" t="s">
         <v>768</v>
       </c>
-      <c r="G101" s="6">
-        <v>1</v>
-      </c>
-      <c r="H101" s="6">
-        <v>99999</v>
-      </c>
-      <c r="I101" s="6">
-        <v>0</v>
-      </c>
-      <c r="J101" s="6">
+      <c r="G101" s="7">
+        <v>1</v>
+      </c>
+      <c r="H101" s="7">
+        <v>99999</v>
+      </c>
+      <c r="I101" s="7">
+        <v>0</v>
+      </c>
+      <c r="J101" s="7">
         <v>6</v>
       </c>
       <c r="K101" s="2">
         <v>1350</v>
       </c>
-      <c r="L101" s="7">
+      <c r="L101" s="9">
         <v>4015</v>
       </c>
-      <c r="M101" s="7">
+      <c r="M101" s="9">
         <v>1</v>
       </c>
     </row>
@@ -20919,43 +21016,43 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" s="6" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C109" s="6">
+    <row r="109" s="7" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C109" s="7">
         <v>50000104</v>
       </c>
-      <c r="D109" s="7" t="s">
+      <c r="D109" s="9" t="s">
         <v>783</v>
       </c>
-      <c r="E109" s="6">
-        <v>5</v>
-      </c>
-      <c r="F109" s="6" t="s">
+      <c r="E109" s="7">
+        <v>5</v>
+      </c>
+      <c r="F109" s="7" t="s">
         <v>784</v>
       </c>
-      <c r="G109" s="6">
-        <v>1</v>
-      </c>
-      <c r="H109" s="6">
-        <v>99999</v>
-      </c>
-      <c r="I109" s="6">
-        <v>0</v>
-      </c>
-      <c r="J109" s="6">
-        <v>6</v>
-      </c>
-      <c r="K109" s="6">
+      <c r="G109" s="7">
+        <v>1</v>
+      </c>
+      <c r="H109" s="7">
+        <v>99999</v>
+      </c>
+      <c r="I109" s="7">
+        <v>0</v>
+      </c>
+      <c r="J109" s="7">
+        <v>6</v>
+      </c>
+      <c r="K109" s="7">
         <v>1400</v>
       </c>
-      <c r="L109" s="7">
+      <c r="L109" s="9">
         <v>4015</v>
       </c>
-      <c r="M109" s="7">
+      <c r="M109" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="110" customHeight="1" spans="3:13">
-      <c r="C110" s="8">
+      <c r="C110" s="6">
         <v>50000105</v>
       </c>
       <c r="D110" s="3" t="s">
@@ -20990,7 +21087,7 @@
       </c>
     </row>
     <row r="111" customHeight="1" spans="3:13">
-      <c r="C111" s="8">
+      <c r="C111" s="6">
         <v>50000106</v>
       </c>
       <c r="D111" s="3" t="s">
@@ -21025,7 +21122,7 @@
       </c>
     </row>
     <row r="112" customHeight="1" spans="3:13">
-      <c r="C112" s="8">
+      <c r="C112" s="6">
         <v>50000107</v>
       </c>
       <c r="D112" s="3" t="s">
@@ -21060,7 +21157,7 @@
       </c>
     </row>
     <row r="113" customHeight="1" spans="3:13">
-      <c r="C113" s="8">
+      <c r="C113" s="6">
         <v>50000108</v>
       </c>
       <c r="D113" s="3" t="s">
@@ -21095,7 +21192,7 @@
       </c>
     </row>
     <row r="114" customHeight="1" spans="3:13">
-      <c r="C114" s="8">
+      <c r="C114" s="6">
         <v>50000109</v>
       </c>
       <c r="D114" s="3" t="s">
@@ -21130,7 +21227,7 @@
       </c>
     </row>
     <row r="115" customHeight="1" spans="3:13">
-      <c r="C115" s="8">
+      <c r="C115" s="6">
         <v>50000110</v>
       </c>
       <c r="D115" s="3" t="s">
@@ -21165,7 +21262,7 @@
       </c>
     </row>
     <row r="116" customHeight="1" spans="3:13">
-      <c r="C116" s="8">
+      <c r="C116" s="6">
         <v>50000111</v>
       </c>
       <c r="D116" s="3" t="s">
@@ -21200,37 +21297,37 @@
       </c>
     </row>
     <row r="117" customHeight="1" spans="3:13">
-      <c r="C117" s="6">
+      <c r="C117" s="7">
         <v>50000112</v>
       </c>
-      <c r="D117" s="7" t="s">
+      <c r="D117" s="9" t="s">
         <v>793</v>
       </c>
-      <c r="E117" s="6">
-        <v>5</v>
-      </c>
-      <c r="F117" s="6" t="s">
+      <c r="E117" s="7">
+        <v>5</v>
+      </c>
+      <c r="F117" s="7" t="s">
         <v>786</v>
       </c>
-      <c r="G117" s="6">
-        <v>1</v>
-      </c>
-      <c r="H117" s="6">
-        <v>99999</v>
-      </c>
-      <c r="I117" s="6">
-        <v>0</v>
-      </c>
-      <c r="J117" s="6">
-        <v>6</v>
-      </c>
-      <c r="K117" s="6">
+      <c r="G117" s="7">
+        <v>1</v>
+      </c>
+      <c r="H117" s="7">
+        <v>99999</v>
+      </c>
+      <c r="I117" s="7">
+        <v>0</v>
+      </c>
+      <c r="J117" s="7">
+        <v>6</v>
+      </c>
+      <c r="K117" s="7">
         <v>1800</v>
       </c>
-      <c r="L117" s="7">
+      <c r="L117" s="9">
         <v>4015</v>
       </c>
-      <c r="M117" s="7">
+      <c r="M117" s="9">
         <v>1</v>
       </c>
     </row>
@@ -21252,12 +21349,16 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:M38"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
+  <dimension ref="C1:M117"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
-    <col min="4" max="4" width="9.625" customWidth="1"/>
-    <col min="6" max="6" width="20.875" customWidth="1"/>
+    <col min="1" max="3" width="9" style="2"/>
+    <col min="4" max="4" width="14.25" style="2" customWidth="1"/>
+    <col min="5" max="5" width="9" style="2"/>
+    <col min="6" max="6" width="20.875" style="2" customWidth="1"/>
+    <col min="7" max="11" width="9" style="2"/>
     <col min="12" max="13" width="13.5" style="3" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="12:13">
@@ -21373,15 +21474,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="3:10">
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C6" s="2">
-        <v>180001</v>
+        <v>60000001</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>794</v>
       </c>
       <c r="E6" s="2">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>795</v>
@@ -21390,7 +21491,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="2">
-        <v>99999</v>
+        <v>9999999</v>
       </c>
       <c r="I6" s="2">
         <v>0</v>
@@ -21398,16 +21499,25 @@
       <c r="J6" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" customHeight="1" spans="3:10">
+      <c r="K6" s="2">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C7" s="2">
-        <v>180002</v>
+        <v>60000002</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>796</v>
       </c>
       <c r="E7" s="2">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>795</v>
@@ -21416,7 +21526,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="2">
-        <v>99999</v>
+        <v>9999999</v>
       </c>
       <c r="I7" s="2">
         <v>0</v>
@@ -21424,16 +21534,25 @@
       <c r="J7" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" customHeight="1" spans="3:10">
+      <c r="K7" s="2">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3">
+        <v>0</v>
+      </c>
+      <c r="M7" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C8" s="2">
-        <v>180003</v>
+        <v>60000003</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>797</v>
       </c>
       <c r="E8" s="2">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>795</v>
@@ -21442,7 +21561,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="2">
-        <v>99999</v>
+        <v>9999999</v>
       </c>
       <c r="I8" s="2">
         <v>0</v>
@@ -21450,16 +21569,25 @@
       <c r="J8" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" customHeight="1" spans="3:10">
+      <c r="K8" s="2">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C9" s="2">
-        <v>180004</v>
+        <v>60000004</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>798</v>
       </c>
       <c r="E9" s="2">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>795</v>
@@ -21468,7 +21596,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="2">
-        <v>99999</v>
+        <v>9999999</v>
       </c>
       <c r="I9" s="2">
         <v>0</v>
@@ -21476,16 +21604,25 @@
       <c r="J9" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" customHeight="1" spans="3:10">
+      <c r="K9" s="2">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C10" s="2">
-        <v>180005</v>
+        <v>60000005</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>799</v>
       </c>
       <c r="E10" s="2">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>795</v>
@@ -21494,24 +21631,33 @@
         <v>1</v>
       </c>
       <c r="H10" s="2">
-        <v>99999</v>
+        <v>9999999</v>
       </c>
       <c r="I10" s="2">
         <v>0</v>
       </c>
       <c r="J10" s="2">
         <v>6</v>
+      </c>
+      <c r="K10" s="2">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C11" s="2">
-        <v>180006</v>
+        <v>60000006</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>800</v>
       </c>
       <c r="E11" s="2">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>795</v>
@@ -21520,7 +21666,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="2">
-        <v>99999</v>
+        <v>9999999</v>
       </c>
       <c r="I11" s="2">
         <v>0</v>
@@ -21528,18 +21674,25 @@
       <c r="J11" s="2">
         <v>6</v>
       </c>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
+      <c r="K11" s="2">
+        <v>0</v>
+      </c>
+      <c r="L11" s="3">
+        <v>0</v>
+      </c>
+      <c r="M11" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C12" s="2">
-        <v>180007</v>
+        <v>60000007</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>801</v>
       </c>
       <c r="E12" s="2">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>795</v>
@@ -21548,7 +21701,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="2">
-        <v>99999</v>
+        <v>9999999</v>
       </c>
       <c r="I12" s="2">
         <v>0</v>
@@ -21556,46 +21709,60 @@
       <c r="J12" s="2">
         <v>6</v>
       </c>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="K12" s="2">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3">
+        <v>0</v>
+      </c>
+      <c r="M12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" s="6" customFormat="1" customHeight="1" spans="3:13">
       <c r="C13" s="2">
-        <v>180008</v>
-      </c>
-      <c r="D13" s="3" t="s">
+        <v>60000008</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>802</v>
       </c>
-      <c r="E13" s="2">
-        <v>18</v>
+      <c r="E13" s="6">
+        <v>5</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>795</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="6">
         <v>1</v>
       </c>
       <c r="H13" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I13" s="2">
-        <v>0</v>
-      </c>
-      <c r="J13" s="2">
-        <v>6</v>
-      </c>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
+        <v>9999999</v>
+      </c>
+      <c r="I13" s="6">
+        <v>0</v>
+      </c>
+      <c r="J13" s="6">
+        <v>6</v>
+      </c>
+      <c r="K13" s="2">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C14" s="2">
-        <v>180009</v>
+        <v>60000009</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>803</v>
       </c>
       <c r="E14" s="2">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>795</v>
@@ -21604,7 +21771,7 @@
         <v>1</v>
       </c>
       <c r="H14" s="2">
-        <v>99999</v>
+        <v>9999999</v>
       </c>
       <c r="I14" s="2">
         <v>0</v>
@@ -21612,18 +21779,25 @@
       <c r="J14" s="2">
         <v>6</v>
       </c>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
+      <c r="K14" s="2">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C15" s="2">
-        <v>180010</v>
+        <v>60000010</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>804</v>
       </c>
       <c r="E15" s="2">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>795</v>
@@ -21632,7 +21806,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="2">
-        <v>99999</v>
+        <v>9999999</v>
       </c>
       <c r="I15" s="2">
         <v>0</v>
@@ -21640,368 +21814,213 @@
       <c r="J15" s="2">
         <v>6</v>
       </c>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C16" s="2">
-        <v>180011</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>805</v>
-      </c>
-      <c r="E16" s="2">
-        <v>18</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="G16" s="2">
-        <v>1</v>
-      </c>
-      <c r="H16" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I16" s="2">
-        <v>0</v>
-      </c>
-      <c r="J16" s="2">
-        <v>6</v>
-      </c>
+      <c r="K15" s="2">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D16" s="3"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
     </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C17" s="2">
-        <v>180012</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>806</v>
-      </c>
-      <c r="E17" s="2">
-        <v>18</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="G17" s="2">
-        <v>1</v>
-      </c>
-      <c r="H17" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I17" s="2">
-        <v>0</v>
-      </c>
-      <c r="J17" s="2">
-        <v>6</v>
-      </c>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D17" s="3"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
     </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C18" s="2">
-        <v>180013</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>807</v>
-      </c>
-      <c r="E18" s="2">
-        <v>18</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="G18" s="2">
-        <v>1</v>
-      </c>
-      <c r="H18" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I18" s="2">
-        <v>0</v>
-      </c>
-      <c r="J18" s="2">
-        <v>6</v>
-      </c>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D18" s="3"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
     </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C19" s="2">
-        <v>180014</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>808</v>
-      </c>
-      <c r="E19" s="2">
-        <v>18</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="G19" s="2">
-        <v>1</v>
-      </c>
-      <c r="H19" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I19" s="2">
-        <v>0</v>
-      </c>
-      <c r="J19" s="2">
-        <v>6</v>
-      </c>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D19" s="3"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
     </row>
-    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C20" s="2">
-        <v>180015</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>809</v>
-      </c>
-      <c r="E20" s="2">
-        <v>18</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="G20" s="2">
-        <v>1</v>
-      </c>
-      <c r="H20" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I20" s="2">
-        <v>0</v>
-      </c>
-      <c r="J20" s="2">
-        <v>6</v>
-      </c>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D20" s="3"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
     </row>
-    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C21" s="2">
-        <v>180016</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>810</v>
-      </c>
-      <c r="E21" s="2">
-        <v>18</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="G21" s="2">
-        <v>1</v>
-      </c>
-      <c r="H21" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I21" s="2">
-        <v>0</v>
-      </c>
-      <c r="J21" s="2">
-        <v>6</v>
-      </c>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C22" s="2">
-        <v>180017</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>811</v>
-      </c>
-      <c r="E22" s="2">
-        <v>18</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="G22" s="2">
-        <v>1</v>
-      </c>
-      <c r="H22" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I22" s="2">
-        <v>0</v>
-      </c>
-      <c r="J22" s="2">
-        <v>6</v>
-      </c>
+    <row r="21" s="7" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D21" s="9"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="9"/>
+    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D22" s="3"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
     </row>
-    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C23" s="2">
-        <v>180018</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>812</v>
-      </c>
-      <c r="E23" s="2">
-        <v>18</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="G23" s="2">
-        <v>1</v>
-      </c>
-      <c r="H23" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I23" s="2">
-        <v>0</v>
-      </c>
-      <c r="J23" s="2">
-        <v>6</v>
-      </c>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D23" s="3"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
     </row>
-    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C24" s="2">
-        <v>180019</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>813</v>
-      </c>
-      <c r="E24" s="2">
-        <v>18</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="G24" s="2">
-        <v>1</v>
-      </c>
-      <c r="H24" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I24" s="2">
-        <v>0</v>
-      </c>
-      <c r="J24" s="2">
-        <v>6</v>
-      </c>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D24" s="3"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
     </row>
-    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C25" s="2">
-        <v>180020</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>814</v>
-      </c>
-      <c r="E25" s="2">
-        <v>18</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="G25" s="2">
-        <v>1</v>
-      </c>
-      <c r="H25" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I25" s="2">
-        <v>0</v>
-      </c>
-      <c r="J25" s="2">
-        <v>6</v>
-      </c>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D25" s="3"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
     </row>
-    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C26" s="2">
-        <v>180021</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>815</v>
-      </c>
-      <c r="E26" s="2">
-        <v>18</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="G26" s="2">
-        <v>1</v>
-      </c>
-      <c r="H26" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I26" s="2">
-        <v>0</v>
-      </c>
-      <c r="J26" s="2">
-        <v>6</v>
-      </c>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D26" s="3"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
     </row>
-    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C27" s="2">
-        <v>180022</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>816</v>
-      </c>
-      <c r="E27" s="2">
-        <v>18</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="G27" s="2">
-        <v>1</v>
-      </c>
-      <c r="H27" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I27" s="2">
-        <v>0</v>
-      </c>
-      <c r="J27" s="2">
-        <v>6</v>
-      </c>
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D27" s="3"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
     </row>
-    <row r="28" s="2" customFormat="1" customHeight="1" spans="4:13">
-      <c r="D28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:13">
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C28" s="2">
+        <v>61000001</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="E28" s="2">
+        <v>5</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="G28" s="2">
+        <v>1</v>
+      </c>
+      <c r="H28" s="2">
+        <v>9999999</v>
+      </c>
+      <c r="I28" s="2">
+        <v>0</v>
+      </c>
+      <c r="J28" s="2">
+        <v>7</v>
+      </c>
+      <c r="K28" s="2">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" s="7" customFormat="1" customHeight="1" spans="3:13">
       <c r="C29" s="2">
-        <v>180030</v>
+        <v>61000002</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>817</v>
+        <v>807</v>
       </c>
       <c r="E29" s="2">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>795</v>
+        <v>806</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
       </c>
       <c r="H29" s="2">
-        <v>99999</v>
+        <v>9999999</v>
       </c>
       <c r="I29" s="2">
         <v>0</v>
@@ -22009,27 +22028,34 @@
       <c r="J29" s="2">
         <v>7</v>
       </c>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" s="3" customFormat="1" customHeight="1" spans="3:10">
+      <c r="K29" s="2">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C30" s="2">
-        <v>180031</v>
+        <v>61000003</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>818</v>
+        <v>808</v>
       </c>
       <c r="E30" s="2">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="G30" s="3">
+        <v>806</v>
+      </c>
+      <c r="G30" s="2">
         <v>1</v>
       </c>
       <c r="H30" s="2">
-        <v>99999</v>
+        <v>9999999</v>
       </c>
       <c r="I30" s="2">
         <v>0</v>
@@ -22037,25 +22063,34 @@
       <c r="J30" s="2">
         <v>7</v>
       </c>
-    </row>
-    <row r="31" s="3" customFormat="1" customHeight="1" spans="3:10">
+      <c r="K30" s="2">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C31" s="2">
-        <v>180032</v>
+        <v>61000004</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>819</v>
+        <v>809</v>
       </c>
       <c r="E31" s="2">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="G31" s="3">
+        <v>806</v>
+      </c>
+      <c r="G31" s="2">
         <v>1</v>
       </c>
       <c r="H31" s="2">
-        <v>99999</v>
+        <v>9999999</v>
       </c>
       <c r="I31" s="2">
         <v>0</v>
@@ -22063,25 +22098,34 @@
       <c r="J31" s="2">
         <v>7</v>
       </c>
-    </row>
-    <row r="32" s="3" customFormat="1" customHeight="1" spans="3:10">
+      <c r="K31" s="2">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C32" s="2">
-        <v>180033</v>
+        <v>61000005</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>820</v>
+        <v>810</v>
       </c>
       <c r="E32" s="2">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="G32" s="3">
+        <v>806</v>
+      </c>
+      <c r="G32" s="2">
         <v>1</v>
       </c>
       <c r="H32" s="2">
-        <v>99999</v>
+        <v>9999999</v>
       </c>
       <c r="I32" s="2">
         <v>0</v>
@@ -22089,174 +22133,1043 @@
       <c r="J32" s="2">
         <v>7</v>
       </c>
-    </row>
-    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C33" s="2">
-        <v>180034</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>821</v>
-      </c>
-      <c r="E33" s="2">
-        <v>18</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="G33" s="3">
-        <v>1</v>
-      </c>
-      <c r="H33" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I33" s="2">
-        <v>0</v>
-      </c>
-      <c r="J33" s="2">
-        <v>7</v>
-      </c>
+      <c r="K32" s="2">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D33" s="3"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
     </row>
-    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C34" s="2">
-        <v>180035</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>822</v>
-      </c>
-      <c r="E34" s="2">
-        <v>18</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="G34" s="3">
-        <v>1</v>
-      </c>
-      <c r="H34" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I34" s="2">
-        <v>0</v>
-      </c>
-      <c r="J34" s="2">
-        <v>7</v>
-      </c>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D34" s="3"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
     </row>
-    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C35" s="2">
-        <v>180036</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>823</v>
-      </c>
-      <c r="E35" s="2">
-        <v>18</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="G35" s="3">
-        <v>1</v>
-      </c>
-      <c r="H35" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I35" s="2">
-        <v>0</v>
-      </c>
-      <c r="J35" s="2">
-        <v>7</v>
-      </c>
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D35" s="3"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="2"/>
       <c r="L35" s="3"/>
       <c r="M35" s="3"/>
     </row>
-    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C36" s="2">
-        <v>180037</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>824</v>
-      </c>
-      <c r="E36" s="2">
-        <v>18</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="G36" s="3">
-        <v>1</v>
-      </c>
-      <c r="H36" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I36" s="2">
-        <v>0</v>
-      </c>
-      <c r="J36" s="2">
-        <v>7</v>
-      </c>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D36" s="3"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
     </row>
-    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C37" s="2">
-        <v>180038</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>825</v>
-      </c>
-      <c r="E37" s="2">
-        <v>18</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="G37" s="3">
-        <v>1</v>
-      </c>
-      <c r="H37" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I37" s="2">
-        <v>0</v>
-      </c>
-      <c r="J37" s="2">
-        <v>7</v>
-      </c>
+    <row r="37" s="7" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D37" s="9"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
       <c r="L37" s="3"/>
       <c r="M37" s="3"/>
     </row>
-    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C38" s="2">
-        <v>180039</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>826</v>
-      </c>
-      <c r="E38" s="2">
-        <v>18</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="G38" s="3">
-        <v>1</v>
-      </c>
-      <c r="H38" s="2">
-        <v>99999</v>
-      </c>
-      <c r="I38" s="2">
-        <v>0</v>
-      </c>
-      <c r="J38" s="2">
-        <v>7</v>
-      </c>
+    <row r="38" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D38" s="3"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
       <c r="L38" s="3"/>
       <c r="M38" s="3"/>
+    </row>
+    <row r="39" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D39" s="3"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D40" s="3"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D41" s="3"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="3"/>
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D42" s="3"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+      <c r="L42" s="3"/>
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D43" s="3"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
+      <c r="L43" s="3"/>
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D44" s="3"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+      <c r="L44" s="3"/>
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" s="7" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D45" s="9"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="7"/>
+      <c r="H45" s="7"/>
+      <c r="I45" s="7"/>
+      <c r="J45" s="7"/>
+      <c r="K45" s="2"/>
+      <c r="L45" s="9"/>
+      <c r="M45" s="9"/>
+    </row>
+    <row r="46" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D46" s="3"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2"/>
+      <c r="L46" s="3"/>
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D47" s="3"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2"/>
+      <c r="L47" s="3"/>
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D48" s="3"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2"/>
+      <c r="L48" s="3"/>
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D49" s="3"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="2"/>
+      <c r="K49" s="2"/>
+      <c r="L49" s="3"/>
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D50" s="3"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="2"/>
+      <c r="K50" s="2"/>
+      <c r="L50" s="3"/>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D51" s="3"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2"/>
+      <c r="K51" s="2"/>
+      <c r="L51" s="3"/>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D52" s="3"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2"/>
+      <c r="L52" s="3"/>
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" s="7" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D53" s="9"/>
+      <c r="E53" s="7"/>
+      <c r="F53" s="7"/>
+      <c r="G53" s="7"/>
+      <c r="H53" s="7"/>
+      <c r="I53" s="7"/>
+      <c r="J53" s="7"/>
+      <c r="K53" s="2"/>
+      <c r="L53" s="9"/>
+      <c r="M53" s="9"/>
+    </row>
+    <row r="54" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D54" s="3"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
+      <c r="J54" s="2"/>
+      <c r="K54" s="2"/>
+      <c r="L54" s="3"/>
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D55" s="3"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+      <c r="I55" s="2"/>
+      <c r="J55" s="2"/>
+      <c r="K55" s="2"/>
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D56" s="3"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2"/>
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D57" s="3"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+      <c r="J57" s="2"/>
+      <c r="K57" s="2"/>
+      <c r="L57" s="3"/>
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D58" s="3"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
+      <c r="J58" s="2"/>
+      <c r="K58" s="2"/>
+      <c r="L58" s="3"/>
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D59" s="3"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+      <c r="I59" s="2"/>
+      <c r="J59" s="2"/>
+      <c r="K59" s="2"/>
+      <c r="L59" s="3"/>
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D60" s="3"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
+      <c r="J60" s="2"/>
+      <c r="K60" s="2"/>
+      <c r="L60" s="3"/>
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" s="7" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D61" s="9"/>
+      <c r="E61" s="7"/>
+      <c r="F61" s="7"/>
+      <c r="G61" s="7"/>
+      <c r="H61" s="7"/>
+      <c r="I61" s="7"/>
+      <c r="J61" s="7"/>
+      <c r="K61" s="2"/>
+      <c r="L61" s="9"/>
+      <c r="M61" s="9"/>
+    </row>
+    <row r="62" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D62" s="3"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2"/>
+      <c r="J62" s="2"/>
+      <c r="K62" s="2"/>
+      <c r="L62" s="3"/>
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D63" s="3"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
+      <c r="J63" s="2"/>
+      <c r="K63" s="2"/>
+      <c r="L63" s="3"/>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D64" s="3"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2"/>
+      <c r="I64" s="2"/>
+      <c r="J64" s="2"/>
+      <c r="K64" s="2"/>
+      <c r="L64" s="3"/>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D65" s="3"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
+      <c r="I65" s="2"/>
+      <c r="J65" s="2"/>
+      <c r="K65" s="2"/>
+      <c r="L65" s="3"/>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D66" s="3"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
+      <c r="I66" s="2"/>
+      <c r="J66" s="2"/>
+      <c r="K66" s="2"/>
+      <c r="L66" s="3"/>
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D67" s="3"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
+      <c r="I67" s="2"/>
+      <c r="J67" s="2"/>
+      <c r="K67" s="2"/>
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D68" s="3"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2"/>
+      <c r="L68" s="3"/>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" s="7" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D69" s="9"/>
+      <c r="E69" s="7"/>
+      <c r="F69" s="7"/>
+      <c r="G69" s="7"/>
+      <c r="H69" s="7"/>
+      <c r="I69" s="7"/>
+      <c r="J69" s="7"/>
+      <c r="K69" s="2"/>
+      <c r="L69" s="9"/>
+      <c r="M69" s="9"/>
+    </row>
+    <row r="70" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D70" s="3"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
+      <c r="I70" s="2"/>
+      <c r="J70" s="2"/>
+      <c r="K70" s="2"/>
+      <c r="L70" s="3"/>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D71" s="3"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+      <c r="I71" s="2"/>
+      <c r="J71" s="2"/>
+      <c r="K71" s="2"/>
+      <c r="L71" s="3"/>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D72" s="3"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
+      <c r="I72" s="2"/>
+      <c r="J72" s="2"/>
+      <c r="K72" s="2"/>
+      <c r="L72" s="3"/>
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D73" s="3"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
+      <c r="I73" s="2"/>
+      <c r="J73" s="2"/>
+      <c r="K73" s="2"/>
+      <c r="L73" s="3"/>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D74" s="3"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
+      <c r="I74" s="2"/>
+      <c r="J74" s="2"/>
+      <c r="K74" s="2"/>
+      <c r="L74" s="3"/>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D75" s="3"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2"/>
+      <c r="I75" s="2"/>
+      <c r="J75" s="2"/>
+      <c r="K75" s="2"/>
+      <c r="L75" s="3"/>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D76" s="3"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
+      <c r="I76" s="2"/>
+      <c r="J76" s="2"/>
+      <c r="K76" s="2"/>
+      <c r="L76" s="3"/>
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" s="7" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D77" s="9"/>
+      <c r="E77" s="7"/>
+      <c r="F77" s="7"/>
+      <c r="G77" s="7"/>
+      <c r="H77" s="7"/>
+      <c r="I77" s="7"/>
+      <c r="J77" s="7"/>
+      <c r="K77" s="2"/>
+      <c r="L77" s="9"/>
+      <c r="M77" s="9"/>
+    </row>
+    <row r="78" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D78" s="3"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2"/>
+      <c r="I78" s="2"/>
+      <c r="J78" s="2"/>
+      <c r="K78" s="2"/>
+      <c r="L78" s="3"/>
+      <c r="M78" s="3"/>
+    </row>
+    <row r="79" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D79" s="3"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
+      <c r="I79" s="2"/>
+      <c r="J79" s="2"/>
+      <c r="K79" s="2"/>
+      <c r="L79" s="3"/>
+      <c r="M79" s="3"/>
+    </row>
+    <row r="80" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D80" s="3"/>
+      <c r="E80" s="2"/>
+      <c r="F80" s="2"/>
+      <c r="G80" s="2"/>
+      <c r="H80" s="2"/>
+      <c r="I80" s="2"/>
+      <c r="J80" s="2"/>
+      <c r="K80" s="2"/>
+      <c r="L80" s="3"/>
+      <c r="M80" s="3"/>
+    </row>
+    <row r="81" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D81" s="3"/>
+      <c r="E81" s="2"/>
+      <c r="F81" s="2"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="2"/>
+      <c r="I81" s="2"/>
+      <c r="J81" s="2"/>
+      <c r="K81" s="2"/>
+      <c r="L81" s="3"/>
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D82" s="3"/>
+      <c r="E82" s="2"/>
+      <c r="F82" s="2"/>
+      <c r="G82" s="2"/>
+      <c r="H82" s="2"/>
+      <c r="I82" s="2"/>
+      <c r="J82" s="2"/>
+      <c r="K82" s="2"/>
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D83" s="3"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="2"/>
+      <c r="I83" s="2"/>
+      <c r="J83" s="2"/>
+      <c r="K83" s="2"/>
+      <c r="L83" s="3"/>
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D84" s="3"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="2"/>
+      <c r="G84" s="2"/>
+      <c r="H84" s="2"/>
+      <c r="I84" s="2"/>
+      <c r="J84" s="2"/>
+      <c r="K84" s="2"/>
+      <c r="L84" s="3"/>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" s="7" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D85" s="9"/>
+      <c r="E85" s="7"/>
+      <c r="F85" s="7"/>
+      <c r="G85" s="7"/>
+      <c r="H85" s="7"/>
+      <c r="I85" s="7"/>
+      <c r="J85" s="7"/>
+      <c r="K85" s="2"/>
+      <c r="L85" s="9"/>
+      <c r="M85" s="9"/>
+    </row>
+    <row r="86" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D86" s="3"/>
+      <c r="E86" s="2"/>
+      <c r="F86" s="2"/>
+      <c r="G86" s="2"/>
+      <c r="H86" s="2"/>
+      <c r="I86" s="2"/>
+      <c r="J86" s="2"/>
+      <c r="K86" s="2"/>
+      <c r="L86" s="3"/>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D87" s="3"/>
+      <c r="E87" s="2"/>
+      <c r="F87" s="2"/>
+      <c r="G87" s="2"/>
+      <c r="H87" s="2"/>
+      <c r="I87" s="2"/>
+      <c r="J87" s="2"/>
+      <c r="K87" s="2"/>
+      <c r="L87" s="3"/>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D88" s="3"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="2"/>
+      <c r="G88" s="2"/>
+      <c r="H88" s="2"/>
+      <c r="I88" s="2"/>
+      <c r="J88" s="2"/>
+      <c r="K88" s="2"/>
+      <c r="L88" s="3"/>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D89" s="3"/>
+      <c r="E89" s="2"/>
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="2"/>
+      <c r="I89" s="2"/>
+      <c r="J89" s="2"/>
+      <c r="K89" s="2"/>
+      <c r="L89" s="3"/>
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D90" s="3"/>
+      <c r="E90" s="2"/>
+      <c r="F90" s="2"/>
+      <c r="G90" s="2"/>
+      <c r="H90" s="2"/>
+      <c r="I90" s="2"/>
+      <c r="J90" s="2"/>
+      <c r="K90" s="2"/>
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D91" s="3"/>
+      <c r="E91" s="2"/>
+      <c r="F91" s="2"/>
+      <c r="G91" s="2"/>
+      <c r="H91" s="2"/>
+      <c r="I91" s="2"/>
+      <c r="J91" s="2"/>
+      <c r="K91" s="2"/>
+      <c r="L91" s="3"/>
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D92" s="3"/>
+      <c r="E92" s="2"/>
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
+      <c r="H92" s="2"/>
+      <c r="I92" s="2"/>
+      <c r="J92" s="2"/>
+      <c r="K92" s="2"/>
+      <c r="L92" s="3"/>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" s="7" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D93" s="9"/>
+      <c r="E93" s="7"/>
+      <c r="F93" s="7"/>
+      <c r="G93" s="7"/>
+      <c r="H93" s="7"/>
+      <c r="I93" s="7"/>
+      <c r="J93" s="7"/>
+      <c r="K93" s="2"/>
+      <c r="L93" s="9"/>
+      <c r="M93" s="9"/>
+    </row>
+    <row r="94" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D94" s="3"/>
+      <c r="E94" s="2"/>
+      <c r="F94" s="2"/>
+      <c r="G94" s="2"/>
+      <c r="H94" s="2"/>
+      <c r="I94" s="2"/>
+      <c r="J94" s="2"/>
+      <c r="K94" s="2"/>
+      <c r="L94" s="3"/>
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D95" s="3"/>
+      <c r="E95" s="2"/>
+      <c r="F95" s="2"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="2"/>
+      <c r="I95" s="2"/>
+      <c r="J95" s="2"/>
+      <c r="K95" s="2"/>
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D96" s="3"/>
+      <c r="E96" s="2"/>
+      <c r="F96" s="2"/>
+      <c r="G96" s="2"/>
+      <c r="H96" s="2"/>
+      <c r="I96" s="2"/>
+      <c r="J96" s="2"/>
+      <c r="K96" s="2"/>
+      <c r="L96" s="3"/>
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D97" s="3"/>
+      <c r="E97" s="2"/>
+      <c r="F97" s="2"/>
+      <c r="G97" s="2"/>
+      <c r="H97" s="2"/>
+      <c r="I97" s="2"/>
+      <c r="J97" s="2"/>
+      <c r="K97" s="2"/>
+      <c r="L97" s="3"/>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D98" s="3"/>
+      <c r="E98" s="2"/>
+      <c r="F98" s="2"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="2"/>
+      <c r="I98" s="2"/>
+      <c r="J98" s="2"/>
+      <c r="K98" s="2"/>
+      <c r="L98" s="3"/>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D99" s="3"/>
+      <c r="E99" s="2"/>
+      <c r="F99" s="2"/>
+      <c r="G99" s="2"/>
+      <c r="H99" s="2"/>
+      <c r="I99" s="2"/>
+      <c r="J99" s="2"/>
+      <c r="K99" s="2"/>
+      <c r="L99" s="3"/>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D100" s="3"/>
+      <c r="E100" s="2"/>
+      <c r="F100" s="2"/>
+      <c r="G100" s="2"/>
+      <c r="H100" s="2"/>
+      <c r="I100" s="2"/>
+      <c r="J100" s="2"/>
+      <c r="K100" s="2"/>
+      <c r="L100" s="3"/>
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" s="7" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D101" s="9"/>
+      <c r="E101" s="7"/>
+      <c r="F101" s="7"/>
+      <c r="G101" s="7"/>
+      <c r="H101" s="7"/>
+      <c r="I101" s="7"/>
+      <c r="J101" s="7"/>
+      <c r="K101" s="2"/>
+      <c r="L101" s="9"/>
+      <c r="M101" s="9"/>
+    </row>
+    <row r="102" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D102" s="3"/>
+      <c r="E102" s="2"/>
+      <c r="F102" s="2"/>
+      <c r="G102" s="2"/>
+      <c r="H102" s="2"/>
+      <c r="I102" s="2"/>
+      <c r="J102" s="2"/>
+      <c r="K102" s="2"/>
+      <c r="L102" s="3"/>
+      <c r="M102" s="3"/>
+    </row>
+    <row r="103" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D103" s="3"/>
+      <c r="E103" s="2"/>
+      <c r="F103" s="2"/>
+      <c r="G103" s="2"/>
+      <c r="H103" s="2"/>
+      <c r="I103" s="2"/>
+      <c r="J103" s="2"/>
+      <c r="K103" s="2"/>
+      <c r="L103" s="3"/>
+      <c r="M103" s="3"/>
+    </row>
+    <row r="104" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D104" s="3"/>
+      <c r="E104" s="2"/>
+      <c r="F104" s="2"/>
+      <c r="G104" s="2"/>
+      <c r="H104" s="2"/>
+      <c r="I104" s="2"/>
+      <c r="J104" s="2"/>
+      <c r="K104" s="2"/>
+      <c r="L104" s="3"/>
+      <c r="M104" s="3"/>
+    </row>
+    <row r="105" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D105" s="3"/>
+      <c r="E105" s="2"/>
+      <c r="F105" s="2"/>
+      <c r="G105" s="2"/>
+      <c r="H105" s="2"/>
+      <c r="I105" s="2"/>
+      <c r="J105" s="2"/>
+      <c r="K105" s="2"/>
+      <c r="L105" s="3"/>
+      <c r="M105" s="3"/>
+    </row>
+    <row r="106" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D106" s="3"/>
+      <c r="E106" s="2"/>
+      <c r="F106" s="2"/>
+      <c r="G106" s="2"/>
+      <c r="H106" s="2"/>
+      <c r="I106" s="2"/>
+      <c r="J106" s="2"/>
+      <c r="K106" s="2"/>
+      <c r="L106" s="3"/>
+      <c r="M106" s="3"/>
+    </row>
+    <row r="107" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D107" s="3"/>
+      <c r="E107" s="2"/>
+      <c r="F107" s="2"/>
+      <c r="G107" s="2"/>
+      <c r="H107" s="2"/>
+      <c r="I107" s="2"/>
+      <c r="J107" s="2"/>
+      <c r="K107" s="2"/>
+      <c r="L107" s="3"/>
+      <c r="M107" s="3"/>
+    </row>
+    <row r="108" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D108" s="3"/>
+      <c r="E108" s="2"/>
+      <c r="F108" s="2"/>
+      <c r="G108" s="2"/>
+      <c r="H108" s="2"/>
+      <c r="I108" s="2"/>
+      <c r="J108" s="2"/>
+      <c r="K108" s="2"/>
+      <c r="L108" s="3"/>
+      <c r="M108" s="3"/>
+    </row>
+    <row r="109" s="7" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D109" s="9"/>
+      <c r="E109" s="7"/>
+      <c r="F109" s="7"/>
+      <c r="G109" s="7"/>
+      <c r="H109" s="7"/>
+      <c r="I109" s="7"/>
+      <c r="J109" s="7"/>
+      <c r="K109" s="7"/>
+      <c r="L109" s="9"/>
+      <c r="M109" s="9"/>
+    </row>
+    <row r="110" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C110" s="6"/>
+      <c r="D110" s="3"/>
+      <c r="E110" s="2"/>
+      <c r="F110" s="2"/>
+      <c r="G110" s="2"/>
+      <c r="H110" s="2"/>
+      <c r="I110" s="2"/>
+      <c r="J110" s="2"/>
+      <c r="K110" s="2"/>
+      <c r="L110" s="3"/>
+      <c r="M110" s="3"/>
+    </row>
+    <row r="111" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C111" s="6"/>
+      <c r="D111" s="3"/>
+      <c r="E111" s="2"/>
+      <c r="F111" s="2"/>
+      <c r="G111" s="2"/>
+      <c r="H111" s="2"/>
+      <c r="I111" s="2"/>
+      <c r="J111" s="2"/>
+      <c r="K111" s="2"/>
+      <c r="L111" s="3"/>
+      <c r="M111" s="3"/>
+    </row>
+    <row r="112" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C112" s="6"/>
+      <c r="D112" s="3"/>
+      <c r="E112" s="2"/>
+      <c r="F112" s="2"/>
+      <c r="G112" s="2"/>
+      <c r="H112" s="2"/>
+      <c r="I112" s="2"/>
+      <c r="J112" s="2"/>
+      <c r="K112" s="2"/>
+      <c r="L112" s="3"/>
+      <c r="M112" s="3"/>
+    </row>
+    <row r="113" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C113" s="6"/>
+      <c r="D113" s="3"/>
+      <c r="E113" s="2"/>
+      <c r="F113" s="2"/>
+      <c r="G113" s="2"/>
+      <c r="H113" s="2"/>
+      <c r="I113" s="2"/>
+      <c r="J113" s="2"/>
+      <c r="K113" s="2"/>
+      <c r="L113" s="3"/>
+      <c r="M113" s="3"/>
+    </row>
+    <row r="114" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C114" s="6"/>
+      <c r="D114" s="3"/>
+      <c r="E114" s="2"/>
+      <c r="F114" s="2"/>
+      <c r="G114" s="2"/>
+      <c r="H114" s="2"/>
+      <c r="I114" s="2"/>
+      <c r="J114" s="2"/>
+      <c r="K114" s="2"/>
+      <c r="L114" s="3"/>
+      <c r="M114" s="3"/>
+    </row>
+    <row r="115" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C115" s="6"/>
+      <c r="D115" s="3"/>
+      <c r="E115" s="2"/>
+      <c r="F115" s="2"/>
+      <c r="G115" s="2"/>
+      <c r="H115" s="2"/>
+      <c r="I115" s="2"/>
+      <c r="J115" s="2"/>
+      <c r="K115" s="2"/>
+      <c r="L115" s="3"/>
+      <c r="M115" s="3"/>
+    </row>
+    <row r="116" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C116" s="6"/>
+      <c r="D116" s="3"/>
+      <c r="E116" s="2"/>
+      <c r="F116" s="2"/>
+      <c r="G116" s="2"/>
+      <c r="H116" s="2"/>
+      <c r="I116" s="2"/>
+      <c r="J116" s="2"/>
+      <c r="K116" s="2"/>
+      <c r="L116" s="3"/>
+      <c r="M116" s="3"/>
+    </row>
+    <row r="117" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C117" s="7"/>
+      <c r="D117" s="9"/>
+      <c r="E117" s="7"/>
+      <c r="F117" s="7"/>
+      <c r="G117" s="7"/>
+      <c r="H117" s="7"/>
+      <c r="I117" s="7"/>
+      <c r="J117" s="7"/>
+      <c r="K117" s="7"/>
+      <c r="L117" s="9"/>
+      <c r="M117" s="9"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -22276,6 +23189,1030 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="C1:M38"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
+  <cols>
+    <col min="4" max="4" width="9.625" customWidth="1"/>
+    <col min="6" max="6" width="20.875" customWidth="1"/>
+    <col min="12" max="13" width="13.5" style="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="12:13">
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="12:13">
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="3:10">
+      <c r="C6" s="2">
+        <v>180001</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>811</v>
+      </c>
+      <c r="E6" s="2">
+        <v>18</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="3:10">
+      <c r="C7" s="2">
+        <v>180002</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="E7" s="2">
+        <v>18</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1</v>
+      </c>
+      <c r="H7" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="3:10">
+      <c r="C8" s="2">
+        <v>180003</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>814</v>
+      </c>
+      <c r="E8" s="2">
+        <v>18</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="3:10">
+      <c r="C9" s="2">
+        <v>180004</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>815</v>
+      </c>
+      <c r="E9" s="2">
+        <v>18</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="G9" s="2">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="3:10">
+      <c r="C10" s="2">
+        <v>180005</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>816</v>
+      </c>
+      <c r="E10" s="2">
+        <v>18</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="G10" s="2">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C11" s="2">
+        <v>180006</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>817</v>
+      </c>
+      <c r="E11" s="2">
+        <v>18</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="G11" s="2">
+        <v>1</v>
+      </c>
+      <c r="H11" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2">
+        <v>6</v>
+      </c>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C12" s="2">
+        <v>180007</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>818</v>
+      </c>
+      <c r="E12" s="2">
+        <v>18</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="G12" s="2">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2">
+        <v>6</v>
+      </c>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C13" s="2">
+        <v>180008</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>819</v>
+      </c>
+      <c r="E13" s="2">
+        <v>18</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="G13" s="2">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2">
+        <v>6</v>
+      </c>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C14" s="2">
+        <v>180009</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="E14" s="2">
+        <v>18</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="G14" s="2">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2">
+        <v>6</v>
+      </c>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C15" s="2">
+        <v>180010</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>821</v>
+      </c>
+      <c r="E15" s="2">
+        <v>18</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="G15" s="2">
+        <v>1</v>
+      </c>
+      <c r="H15" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2">
+        <v>6</v>
+      </c>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C16" s="2">
+        <v>180011</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>822</v>
+      </c>
+      <c r="E16" s="2">
+        <v>18</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="G16" s="2">
+        <v>1</v>
+      </c>
+      <c r="H16" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2">
+        <v>6</v>
+      </c>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C17" s="2">
+        <v>180012</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="E17" s="2">
+        <v>18</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="G17" s="2">
+        <v>1</v>
+      </c>
+      <c r="H17" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0</v>
+      </c>
+      <c r="J17" s="2">
+        <v>6</v>
+      </c>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C18" s="2">
+        <v>180013</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>824</v>
+      </c>
+      <c r="E18" s="2">
+        <v>18</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="G18" s="2">
+        <v>1</v>
+      </c>
+      <c r="H18" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0</v>
+      </c>
+      <c r="J18" s="2">
+        <v>6</v>
+      </c>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C19" s="2">
+        <v>180014</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>825</v>
+      </c>
+      <c r="E19" s="2">
+        <v>18</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="G19" s="2">
+        <v>1</v>
+      </c>
+      <c r="H19" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0</v>
+      </c>
+      <c r="J19" s="2">
+        <v>6</v>
+      </c>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C20" s="2">
+        <v>180015</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>826</v>
+      </c>
+      <c r="E20" s="2">
+        <v>18</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="G20" s="2">
+        <v>1</v>
+      </c>
+      <c r="H20" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0</v>
+      </c>
+      <c r="J20" s="2">
+        <v>6</v>
+      </c>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C21" s="2">
+        <v>180016</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>827</v>
+      </c>
+      <c r="E21" s="2">
+        <v>18</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="G21" s="2">
+        <v>1</v>
+      </c>
+      <c r="H21" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0</v>
+      </c>
+      <c r="J21" s="2">
+        <v>6</v>
+      </c>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C22" s="2">
+        <v>180017</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>828</v>
+      </c>
+      <c r="E22" s="2">
+        <v>18</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="G22" s="2">
+        <v>1</v>
+      </c>
+      <c r="H22" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I22" s="2">
+        <v>0</v>
+      </c>
+      <c r="J22" s="2">
+        <v>6</v>
+      </c>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C23" s="2">
+        <v>180018</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>829</v>
+      </c>
+      <c r="E23" s="2">
+        <v>18</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="G23" s="2">
+        <v>1</v>
+      </c>
+      <c r="H23" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I23" s="2">
+        <v>0</v>
+      </c>
+      <c r="J23" s="2">
+        <v>6</v>
+      </c>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C24" s="2">
+        <v>180019</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>830</v>
+      </c>
+      <c r="E24" s="2">
+        <v>18</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="G24" s="2">
+        <v>1</v>
+      </c>
+      <c r="H24" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I24" s="2">
+        <v>0</v>
+      </c>
+      <c r="J24" s="2">
+        <v>6</v>
+      </c>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C25" s="2">
+        <v>180020</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>831</v>
+      </c>
+      <c r="E25" s="2">
+        <v>18</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="G25" s="2">
+        <v>1</v>
+      </c>
+      <c r="H25" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I25" s="2">
+        <v>0</v>
+      </c>
+      <c r="J25" s="2">
+        <v>6</v>
+      </c>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C26" s="2">
+        <v>180021</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>832</v>
+      </c>
+      <c r="E26" s="2">
+        <v>18</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="G26" s="2">
+        <v>1</v>
+      </c>
+      <c r="H26" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I26" s="2">
+        <v>0</v>
+      </c>
+      <c r="J26" s="2">
+        <v>6</v>
+      </c>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C27" s="2">
+        <v>180022</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>833</v>
+      </c>
+      <c r="E27" s="2">
+        <v>18</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="G27" s="2">
+        <v>1</v>
+      </c>
+      <c r="H27" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I27" s="2">
+        <v>0</v>
+      </c>
+      <c r="J27" s="2">
+        <v>6</v>
+      </c>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="4:13">
+      <c r="D28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C29" s="2">
+        <v>180030</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>834</v>
+      </c>
+      <c r="E29" s="2">
+        <v>18</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="G29" s="2">
+        <v>1</v>
+      </c>
+      <c r="H29" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I29" s="2">
+        <v>0</v>
+      </c>
+      <c r="J29" s="2">
+        <v>7</v>
+      </c>
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" s="3" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C30" s="2">
+        <v>180031</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>835</v>
+      </c>
+      <c r="E30" s="2">
+        <v>18</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="G30" s="3">
+        <v>1</v>
+      </c>
+      <c r="H30" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I30" s="2">
+        <v>0</v>
+      </c>
+      <c r="J30" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" s="3" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C31" s="2">
+        <v>180032</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>836</v>
+      </c>
+      <c r="E31" s="2">
+        <v>18</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="G31" s="3">
+        <v>1</v>
+      </c>
+      <c r="H31" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I31" s="2">
+        <v>0</v>
+      </c>
+      <c r="J31" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" s="3" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C32" s="2">
+        <v>180033</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>837</v>
+      </c>
+      <c r="E32" s="2">
+        <v>18</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="G32" s="3">
+        <v>1</v>
+      </c>
+      <c r="H32" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I32" s="2">
+        <v>0</v>
+      </c>
+      <c r="J32" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C33" s="2">
+        <v>180034</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>838</v>
+      </c>
+      <c r="E33" s="2">
+        <v>18</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="G33" s="3">
+        <v>1</v>
+      </c>
+      <c r="H33" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I33" s="2">
+        <v>0</v>
+      </c>
+      <c r="J33" s="2">
+        <v>7</v>
+      </c>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C34" s="2">
+        <v>180035</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>839</v>
+      </c>
+      <c r="E34" s="2">
+        <v>18</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="G34" s="3">
+        <v>1</v>
+      </c>
+      <c r="H34" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I34" s="2">
+        <v>0</v>
+      </c>
+      <c r="J34" s="2">
+        <v>7</v>
+      </c>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C35" s="2">
+        <v>180036</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>840</v>
+      </c>
+      <c r="E35" s="2">
+        <v>18</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="G35" s="3">
+        <v>1</v>
+      </c>
+      <c r="H35" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I35" s="2">
+        <v>0</v>
+      </c>
+      <c r="J35" s="2">
+        <v>7</v>
+      </c>
+      <c r="L35" s="3"/>
+      <c r="M35" s="3"/>
+    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C36" s="2">
+        <v>180037</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>841</v>
+      </c>
+      <c r="E36" s="2">
+        <v>18</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="G36" s="3">
+        <v>1</v>
+      </c>
+      <c r="H36" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I36" s="2">
+        <v>0</v>
+      </c>
+      <c r="J36" s="2">
+        <v>7</v>
+      </c>
+      <c r="L36" s="3"/>
+      <c r="M36" s="3"/>
+    </row>
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C37" s="2">
+        <v>180038</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>842</v>
+      </c>
+      <c r="E37" s="2">
+        <v>18</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="G37" s="3">
+        <v>1</v>
+      </c>
+      <c r="H37" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I37" s="2">
+        <v>0</v>
+      </c>
+      <c r="J37" s="2">
+        <v>7</v>
+      </c>
+      <c r="L37" s="3"/>
+      <c r="M37" s="3"/>
+    </row>
+    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C38" s="2">
+        <v>180039</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="E38" s="2">
+        <v>18</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="G38" s="3">
+        <v>1</v>
+      </c>
+      <c r="H38" s="2">
+        <v>99999</v>
+      </c>
+      <c r="I38" s="2">
+        <v>0</v>
+      </c>
+      <c r="J38" s="2">
+        <v>7</v>
+      </c>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3:M5" errorStyle="warning">
+      <formula1>COUNTIF($A:$A,L3)&lt;2</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:D5" errorStyle="warning">
+      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="C1:M34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
@@ -22402,13 +24339,13 @@
         <v>190001</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>827</v>
+        <v>844</v>
       </c>
       <c r="E6" s="2">
         <v>19</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>828</v>
+        <v>845</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -22428,13 +24365,13 @@
         <v>190002</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>829</v>
+        <v>846</v>
       </c>
       <c r="E7" s="2">
         <v>19</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>828</v>
+        <v>845</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -22454,13 +24391,13 @@
         <v>190003</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>830</v>
+        <v>847</v>
       </c>
       <c r="E8" s="2">
         <v>19</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>828</v>
+        <v>845</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -22480,13 +24417,13 @@
         <v>190004</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>831</v>
+        <v>848</v>
       </c>
       <c r="E9" s="2">
         <v>19</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>828</v>
+        <v>845</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -22506,13 +24443,13 @@
         <v>190005</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>832</v>
+        <v>849</v>
       </c>
       <c r="E10" s="2">
         <v>19</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>828</v>
+        <v>845</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -22532,13 +24469,13 @@
         <v>190006</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>833</v>
+        <v>850</v>
       </c>
       <c r="E11" s="2">
         <v>19</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>828</v>
+        <v>845</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="6"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -384,7 +384,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1602" uniqueCount="851">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="854">
   <si>
     <t>_Id</t>
   </si>
@@ -2801,22 +2801,31 @@
     <t>韧性宝石</t>
   </si>
   <si>
-    <t>盘古斧身</t>
+    <t>青龙之剑</t>
   </si>
   <si>
     <t>激活神器</t>
   </si>
   <si>
-    <t>盘古斧背</t>
-  </si>
-  <si>
-    <t>盘古斧柄</t>
-  </si>
-  <si>
-    <t>盘古斧刃</t>
-  </si>
-  <si>
-    <t>盘古心核</t>
+    <t>青龙之甲</t>
+  </si>
+  <si>
+    <t>青龙面罩</t>
+  </si>
+  <si>
+    <t>青龙项链</t>
+  </si>
+  <si>
+    <t>青龙护腕</t>
+  </si>
+  <si>
+    <t>青龙护戒</t>
+  </si>
+  <si>
+    <t>青龙腰带</t>
+  </si>
+  <si>
+    <t>青龙战靴</t>
   </si>
   <si>
     <t>BOSS杀手</t>
@@ -21826,145 +21835,61 @@
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D16" s="3"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D17" s="3"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D18" s="3"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D19" s="3"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D20" s="3"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
     </row>
     <row r="21" s="7" customFormat="1" customHeight="1" spans="4:13">
       <c r="D21" s="9"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
       <c r="L21" s="9"/>
       <c r="M21" s="9"/>
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D22" s="3"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D23" s="3"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D24" s="3"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D25" s="3"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D26" s="3"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
     </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D27" s="3"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
     </row>
@@ -22143,58 +22068,118 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" s="2" customFormat="1" customHeight="1" spans="4:13">
-      <c r="D33" s="3"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-      <c r="L33" s="3"/>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" s="2" customFormat="1" customHeight="1" spans="4:13">
-      <c r="D34" s="3"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
-      <c r="L34" s="3"/>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" s="2" customFormat="1" customHeight="1" spans="4:13">
-      <c r="D35" s="3"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="6"/>
-      <c r="K35" s="2"/>
-      <c r="L35" s="3"/>
-      <c r="M35" s="3"/>
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C33" s="2">
+        <v>61000006</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>811</v>
+      </c>
+      <c r="E33" s="2">
+        <v>5</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="G33" s="2">
+        <v>1</v>
+      </c>
+      <c r="H33" s="2">
+        <v>9999999</v>
+      </c>
+      <c r="I33" s="2">
+        <v>0</v>
+      </c>
+      <c r="J33" s="2">
+        <v>7</v>
+      </c>
+      <c r="K33" s="2">
+        <v>0</v>
+      </c>
+      <c r="L33" s="3">
+        <v>0</v>
+      </c>
+      <c r="M33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C34" s="2">
+        <v>61000007</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>812</v>
+      </c>
+      <c r="E34" s="2">
+        <v>5</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="G34" s="2">
+        <v>1</v>
+      </c>
+      <c r="H34" s="2">
+        <v>9999999</v>
+      </c>
+      <c r="I34" s="2">
+        <v>0</v>
+      </c>
+      <c r="J34" s="2">
+        <v>7</v>
+      </c>
+      <c r="K34" s="2">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C35" s="2">
+        <v>61000008</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>813</v>
+      </c>
+      <c r="E35" s="2">
+        <v>5</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="G35" s="2">
+        <v>1</v>
+      </c>
+      <c r="H35" s="2">
+        <v>9999999</v>
+      </c>
+      <c r="I35" s="2">
+        <v>0</v>
+      </c>
+      <c r="J35" s="2">
+        <v>7</v>
+      </c>
+      <c r="K35" s="2">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3">
+        <v>0</v>
+      </c>
+      <c r="M35" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D36" s="3"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
     </row>
     <row r="37" s="7" customFormat="1" customHeight="1" spans="4:13">
       <c r="D37" s="9"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
@@ -22205,956 +22190,411 @@
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D38" s="3"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
       <c r="L38" s="3"/>
       <c r="M38" s="3"/>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D39" s="3"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="2"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D40" s="3"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
-      <c r="K40" s="2"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D41" s="3"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="2"/>
-      <c r="K41" s="2"/>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D42" s="3"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="2"/>
-      <c r="K42" s="2"/>
       <c r="L42" s="3"/>
       <c r="M42" s="3"/>
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D43" s="3"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="2"/>
-      <c r="K43" s="2"/>
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D44" s="3"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="2"/>
-      <c r="K44" s="2"/>
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
     </row>
     <row r="45" s="7" customFormat="1" customHeight="1" spans="4:13">
       <c r="D45" s="9"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="7"/>
-      <c r="G45" s="7"/>
-      <c r="H45" s="7"/>
-      <c r="I45" s="7"/>
-      <c r="J45" s="7"/>
       <c r="K45" s="2"/>
       <c r="L45" s="9"/>
       <c r="M45" s="9"/>
     </row>
     <row r="46" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D46" s="3"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
-      <c r="K46" s="2"/>
       <c r="L46" s="3"/>
       <c r="M46" s="3"/>
     </row>
     <row r="47" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D47" s="3"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="2"/>
-      <c r="K47" s="2"/>
       <c r="L47" s="3"/>
       <c r="M47" s="3"/>
     </row>
     <row r="48" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D48" s="3"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
-      <c r="K48" s="2"/>
       <c r="L48" s="3"/>
       <c r="M48" s="3"/>
     </row>
     <row r="49" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D49" s="3"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="2"/>
-      <c r="K49" s="2"/>
       <c r="L49" s="3"/>
       <c r="M49" s="3"/>
     </row>
     <row r="50" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D50" s="3"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
-      <c r="K50" s="2"/>
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
     </row>
     <row r="51" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D51" s="3"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="2"/>
-      <c r="K51" s="2"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
     </row>
     <row r="52" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D52" s="3"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
-      <c r="K52" s="2"/>
       <c r="L52" s="3"/>
       <c r="M52" s="3"/>
     </row>
     <row r="53" s="7" customFormat="1" customHeight="1" spans="4:13">
       <c r="D53" s="9"/>
-      <c r="E53" s="7"/>
-      <c r="F53" s="7"/>
-      <c r="G53" s="7"/>
-      <c r="H53" s="7"/>
-      <c r="I53" s="7"/>
-      <c r="J53" s="7"/>
       <c r="K53" s="2"/>
       <c r="L53" s="9"/>
       <c r="M53" s="9"/>
     </row>
     <row r="54" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D54" s="3"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-      <c r="H54" s="2"/>
-      <c r="I54" s="2"/>
-      <c r="J54" s="2"/>
-      <c r="K54" s="2"/>
       <c r="L54" s="3"/>
       <c r="M54" s="3"/>
     </row>
     <row r="55" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D55" s="3"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
-      <c r="H55" s="2"/>
-      <c r="I55" s="2"/>
-      <c r="J55" s="2"/>
-      <c r="K55" s="2"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
     </row>
     <row r="56" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D56" s="3"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
-      <c r="H56" s="2"/>
-      <c r="I56" s="2"/>
-      <c r="J56" s="2"/>
-      <c r="K56" s="2"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
     </row>
     <row r="57" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D57" s="3"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="2"/>
-      <c r="I57" s="2"/>
-      <c r="J57" s="2"/>
-      <c r="K57" s="2"/>
       <c r="L57" s="3"/>
       <c r="M57" s="3"/>
     </row>
     <row r="58" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D58" s="3"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="2"/>
-      <c r="I58" s="2"/>
-      <c r="J58" s="2"/>
-      <c r="K58" s="2"/>
       <c r="L58" s="3"/>
       <c r="M58" s="3"/>
     </row>
     <row r="59" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D59" s="3"/>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
-      <c r="H59" s="2"/>
-      <c r="I59" s="2"/>
-      <c r="J59" s="2"/>
-      <c r="K59" s="2"/>
       <c r="L59" s="3"/>
       <c r="M59" s="3"/>
     </row>
     <row r="60" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D60" s="3"/>
-      <c r="E60" s="2"/>
-      <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
-      <c r="H60" s="2"/>
-      <c r="I60" s="2"/>
-      <c r="J60" s="2"/>
-      <c r="K60" s="2"/>
       <c r="L60" s="3"/>
       <c r="M60" s="3"/>
     </row>
     <row r="61" s="7" customFormat="1" customHeight="1" spans="4:13">
       <c r="D61" s="9"/>
-      <c r="E61" s="7"/>
-      <c r="F61" s="7"/>
-      <c r="G61" s="7"/>
-      <c r="H61" s="7"/>
-      <c r="I61" s="7"/>
-      <c r="J61" s="7"/>
       <c r="K61" s="2"/>
       <c r="L61" s="9"/>
       <c r="M61" s="9"/>
     </row>
     <row r="62" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D62" s="3"/>
-      <c r="E62" s="2"/>
-      <c r="F62" s="2"/>
-      <c r="G62" s="2"/>
-      <c r="H62" s="2"/>
-      <c r="I62" s="2"/>
-      <c r="J62" s="2"/>
-      <c r="K62" s="2"/>
       <c r="L62" s="3"/>
       <c r="M62" s="3"/>
     </row>
     <row r="63" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D63" s="3"/>
-      <c r="E63" s="2"/>
-      <c r="F63" s="2"/>
-      <c r="G63" s="2"/>
-      <c r="H63" s="2"/>
-      <c r="I63" s="2"/>
-      <c r="J63" s="2"/>
-      <c r="K63" s="2"/>
       <c r="L63" s="3"/>
       <c r="M63" s="3"/>
     </row>
     <row r="64" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D64" s="3"/>
-      <c r="E64" s="2"/>
-      <c r="F64" s="2"/>
-      <c r="G64" s="2"/>
-      <c r="H64" s="2"/>
-      <c r="I64" s="2"/>
-      <c r="J64" s="2"/>
-      <c r="K64" s="2"/>
       <c r="L64" s="3"/>
       <c r="M64" s="3"/>
     </row>
     <row r="65" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D65" s="3"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
-      <c r="H65" s="2"/>
-      <c r="I65" s="2"/>
-      <c r="J65" s="2"/>
-      <c r="K65" s="2"/>
       <c r="L65" s="3"/>
       <c r="M65" s="3"/>
     </row>
     <row r="66" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D66" s="3"/>
-      <c r="E66" s="2"/>
-      <c r="F66" s="2"/>
-      <c r="G66" s="2"/>
-      <c r="H66" s="2"/>
-      <c r="I66" s="2"/>
-      <c r="J66" s="2"/>
-      <c r="K66" s="2"/>
       <c r="L66" s="3"/>
       <c r="M66" s="3"/>
     </row>
     <row r="67" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D67" s="3"/>
-      <c r="E67" s="2"/>
-      <c r="F67" s="2"/>
-      <c r="G67" s="2"/>
-      <c r="H67" s="2"/>
-      <c r="I67" s="2"/>
-      <c r="J67" s="2"/>
-      <c r="K67" s="2"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
     </row>
     <row r="68" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D68" s="3"/>
-      <c r="E68" s="2"/>
-      <c r="F68" s="2"/>
-      <c r="G68" s="2"/>
-      <c r="H68" s="2"/>
-      <c r="I68" s="2"/>
-      <c r="J68" s="2"/>
-      <c r="K68" s="2"/>
       <c r="L68" s="3"/>
       <c r="M68" s="3"/>
     </row>
     <row r="69" s="7" customFormat="1" customHeight="1" spans="4:13">
       <c r="D69" s="9"/>
-      <c r="E69" s="7"/>
-      <c r="F69" s="7"/>
-      <c r="G69" s="7"/>
-      <c r="H69" s="7"/>
-      <c r="I69" s="7"/>
-      <c r="J69" s="7"/>
       <c r="K69" s="2"/>
       <c r="L69" s="9"/>
       <c r="M69" s="9"/>
     </row>
     <row r="70" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D70" s="3"/>
-      <c r="E70" s="2"/>
-      <c r="F70" s="2"/>
-      <c r="G70" s="2"/>
-      <c r="H70" s="2"/>
-      <c r="I70" s="2"/>
-      <c r="J70" s="2"/>
-      <c r="K70" s="2"/>
       <c r="L70" s="3"/>
       <c r="M70" s="3"/>
     </row>
     <row r="71" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D71" s="3"/>
-      <c r="E71" s="2"/>
-      <c r="F71" s="2"/>
-      <c r="G71" s="2"/>
-      <c r="H71" s="2"/>
-      <c r="I71" s="2"/>
-      <c r="J71" s="2"/>
-      <c r="K71" s="2"/>
       <c r="L71" s="3"/>
       <c r="M71" s="3"/>
     </row>
     <row r="72" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D72" s="3"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
-      <c r="H72" s="2"/>
-      <c r="I72" s="2"/>
-      <c r="J72" s="2"/>
-      <c r="K72" s="2"/>
       <c r="L72" s="3"/>
       <c r="M72" s="3"/>
     </row>
     <row r="73" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D73" s="3"/>
-      <c r="E73" s="2"/>
-      <c r="F73" s="2"/>
-      <c r="G73" s="2"/>
-      <c r="H73" s="2"/>
-      <c r="I73" s="2"/>
-      <c r="J73" s="2"/>
-      <c r="K73" s="2"/>
       <c r="L73" s="3"/>
       <c r="M73" s="3"/>
     </row>
     <row r="74" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D74" s="3"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="2"/>
-      <c r="G74" s="2"/>
-      <c r="H74" s="2"/>
-      <c r="I74" s="2"/>
-      <c r="J74" s="2"/>
-      <c r="K74" s="2"/>
       <c r="L74" s="3"/>
       <c r="M74" s="3"/>
     </row>
     <row r="75" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D75" s="3"/>
-      <c r="E75" s="2"/>
-      <c r="F75" s="2"/>
-      <c r="G75" s="2"/>
-      <c r="H75" s="2"/>
-      <c r="I75" s="2"/>
-      <c r="J75" s="2"/>
-      <c r="K75" s="2"/>
       <c r="L75" s="3"/>
       <c r="M75" s="3"/>
     </row>
     <row r="76" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D76" s="3"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
-      <c r="H76" s="2"/>
-      <c r="I76" s="2"/>
-      <c r="J76" s="2"/>
-      <c r="K76" s="2"/>
       <c r="L76" s="3"/>
       <c r="M76" s="3"/>
     </row>
     <row r="77" s="7" customFormat="1" customHeight="1" spans="4:13">
       <c r="D77" s="9"/>
-      <c r="E77" s="7"/>
-      <c r="F77" s="7"/>
-      <c r="G77" s="7"/>
-      <c r="H77" s="7"/>
-      <c r="I77" s="7"/>
-      <c r="J77" s="7"/>
       <c r="K77" s="2"/>
       <c r="L77" s="9"/>
       <c r="M77" s="9"/>
     </row>
     <row r="78" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D78" s="3"/>
-      <c r="E78" s="2"/>
-      <c r="F78" s="2"/>
-      <c r="G78" s="2"/>
-      <c r="H78" s="2"/>
-      <c r="I78" s="2"/>
-      <c r="J78" s="2"/>
-      <c r="K78" s="2"/>
       <c r="L78" s="3"/>
       <c r="M78" s="3"/>
     </row>
     <row r="79" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D79" s="3"/>
-      <c r="E79" s="2"/>
-      <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
-      <c r="H79" s="2"/>
-      <c r="I79" s="2"/>
-      <c r="J79" s="2"/>
-      <c r="K79" s="2"/>
       <c r="L79" s="3"/>
       <c r="M79" s="3"/>
     </row>
     <row r="80" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D80" s="3"/>
-      <c r="E80" s="2"/>
-      <c r="F80" s="2"/>
-      <c r="G80" s="2"/>
-      <c r="H80" s="2"/>
-      <c r="I80" s="2"/>
-      <c r="J80" s="2"/>
-      <c r="K80" s="2"/>
       <c r="L80" s="3"/>
       <c r="M80" s="3"/>
     </row>
     <row r="81" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D81" s="3"/>
-      <c r="E81" s="2"/>
-      <c r="F81" s="2"/>
-      <c r="G81" s="2"/>
-      <c r="H81" s="2"/>
-      <c r="I81" s="2"/>
-      <c r="J81" s="2"/>
-      <c r="K81" s="2"/>
       <c r="L81" s="3"/>
       <c r="M81" s="3"/>
     </row>
     <row r="82" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D82" s="3"/>
-      <c r="E82" s="2"/>
-      <c r="F82" s="2"/>
-      <c r="G82" s="2"/>
-      <c r="H82" s="2"/>
-      <c r="I82" s="2"/>
-      <c r="J82" s="2"/>
-      <c r="K82" s="2"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
     </row>
     <row r="83" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D83" s="3"/>
-      <c r="E83" s="2"/>
-      <c r="F83" s="2"/>
-      <c r="G83" s="2"/>
-      <c r="H83" s="2"/>
-      <c r="I83" s="2"/>
-      <c r="J83" s="2"/>
-      <c r="K83" s="2"/>
       <c r="L83" s="3"/>
       <c r="M83" s="3"/>
     </row>
     <row r="84" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D84" s="3"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
-      <c r="H84" s="2"/>
-      <c r="I84" s="2"/>
-      <c r="J84" s="2"/>
-      <c r="K84" s="2"/>
       <c r="L84" s="3"/>
       <c r="M84" s="3"/>
     </row>
     <row r="85" s="7" customFormat="1" customHeight="1" spans="4:13">
       <c r="D85" s="9"/>
-      <c r="E85" s="7"/>
-      <c r="F85" s="7"/>
-      <c r="G85" s="7"/>
-      <c r="H85" s="7"/>
-      <c r="I85" s="7"/>
-      <c r="J85" s="7"/>
       <c r="K85" s="2"/>
       <c r="L85" s="9"/>
       <c r="M85" s="9"/>
     </row>
     <row r="86" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D86" s="3"/>
-      <c r="E86" s="2"/>
-      <c r="F86" s="2"/>
-      <c r="G86" s="2"/>
-      <c r="H86" s="2"/>
-      <c r="I86" s="2"/>
-      <c r="J86" s="2"/>
-      <c r="K86" s="2"/>
       <c r="L86" s="3"/>
       <c r="M86" s="3"/>
     </row>
     <row r="87" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D87" s="3"/>
-      <c r="E87" s="2"/>
-      <c r="F87" s="2"/>
-      <c r="G87" s="2"/>
-      <c r="H87" s="2"/>
-      <c r="I87" s="2"/>
-      <c r="J87" s="2"/>
-      <c r="K87" s="2"/>
       <c r="L87" s="3"/>
       <c r="M87" s="3"/>
     </row>
     <row r="88" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D88" s="3"/>
-      <c r="E88" s="2"/>
-      <c r="F88" s="2"/>
-      <c r="G88" s="2"/>
-      <c r="H88" s="2"/>
-      <c r="I88" s="2"/>
-      <c r="J88" s="2"/>
-      <c r="K88" s="2"/>
       <c r="L88" s="3"/>
       <c r="M88" s="3"/>
     </row>
     <row r="89" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D89" s="3"/>
-      <c r="E89" s="2"/>
-      <c r="F89" s="2"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="2"/>
-      <c r="I89" s="2"/>
-      <c r="J89" s="2"/>
-      <c r="K89" s="2"/>
       <c r="L89" s="3"/>
       <c r="M89" s="3"/>
     </row>
     <row r="90" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D90" s="3"/>
-      <c r="E90" s="2"/>
-      <c r="F90" s="2"/>
-      <c r="G90" s="2"/>
-      <c r="H90" s="2"/>
-      <c r="I90" s="2"/>
-      <c r="J90" s="2"/>
-      <c r="K90" s="2"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
     </row>
     <row r="91" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D91" s="3"/>
-      <c r="E91" s="2"/>
-      <c r="F91" s="2"/>
-      <c r="G91" s="2"/>
-      <c r="H91" s="2"/>
-      <c r="I91" s="2"/>
-      <c r="J91" s="2"/>
-      <c r="K91" s="2"/>
       <c r="L91" s="3"/>
       <c r="M91" s="3"/>
     </row>
     <row r="92" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D92" s="3"/>
-      <c r="E92" s="2"/>
-      <c r="F92" s="2"/>
-      <c r="G92" s="2"/>
-      <c r="H92" s="2"/>
-      <c r="I92" s="2"/>
-      <c r="J92" s="2"/>
-      <c r="K92" s="2"/>
       <c r="L92" s="3"/>
       <c r="M92" s="3"/>
     </row>
     <row r="93" s="7" customFormat="1" customHeight="1" spans="4:13">
       <c r="D93" s="9"/>
-      <c r="E93" s="7"/>
-      <c r="F93" s="7"/>
-      <c r="G93" s="7"/>
-      <c r="H93" s="7"/>
-      <c r="I93" s="7"/>
-      <c r="J93" s="7"/>
       <c r="K93" s="2"/>
       <c r="L93" s="9"/>
       <c r="M93" s="9"/>
     </row>
     <row r="94" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D94" s="3"/>
-      <c r="E94" s="2"/>
-      <c r="F94" s="2"/>
-      <c r="G94" s="2"/>
-      <c r="H94" s="2"/>
-      <c r="I94" s="2"/>
-      <c r="J94" s="2"/>
-      <c r="K94" s="2"/>
       <c r="L94" s="3"/>
       <c r="M94" s="3"/>
     </row>
     <row r="95" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D95" s="3"/>
-      <c r="E95" s="2"/>
-      <c r="F95" s="2"/>
-      <c r="G95" s="2"/>
-      <c r="H95" s="2"/>
-      <c r="I95" s="2"/>
-      <c r="J95" s="2"/>
-      <c r="K95" s="2"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
     </row>
     <row r="96" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D96" s="3"/>
-      <c r="E96" s="2"/>
-      <c r="F96" s="2"/>
-      <c r="G96" s="2"/>
-      <c r="H96" s="2"/>
-      <c r="I96" s="2"/>
-      <c r="J96" s="2"/>
-      <c r="K96" s="2"/>
       <c r="L96" s="3"/>
       <c r="M96" s="3"/>
     </row>
     <row r="97" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D97" s="3"/>
-      <c r="E97" s="2"/>
-      <c r="F97" s="2"/>
-      <c r="G97" s="2"/>
-      <c r="H97" s="2"/>
-      <c r="I97" s="2"/>
-      <c r="J97" s="2"/>
-      <c r="K97" s="2"/>
       <c r="L97" s="3"/>
       <c r="M97" s="3"/>
     </row>
     <row r="98" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D98" s="3"/>
-      <c r="E98" s="2"/>
-      <c r="F98" s="2"/>
-      <c r="G98" s="2"/>
-      <c r="H98" s="2"/>
-      <c r="I98" s="2"/>
-      <c r="J98" s="2"/>
-      <c r="K98" s="2"/>
       <c r="L98" s="3"/>
       <c r="M98" s="3"/>
     </row>
     <row r="99" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D99" s="3"/>
-      <c r="E99" s="2"/>
-      <c r="F99" s="2"/>
-      <c r="G99" s="2"/>
-      <c r="H99" s="2"/>
-      <c r="I99" s="2"/>
-      <c r="J99" s="2"/>
-      <c r="K99" s="2"/>
       <c r="L99" s="3"/>
       <c r="M99" s="3"/>
     </row>
     <row r="100" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D100" s="3"/>
-      <c r="E100" s="2"/>
-      <c r="F100" s="2"/>
-      <c r="G100" s="2"/>
-      <c r="H100" s="2"/>
-      <c r="I100" s="2"/>
-      <c r="J100" s="2"/>
-      <c r="K100" s="2"/>
       <c r="L100" s="3"/>
       <c r="M100" s="3"/>
     </row>
     <row r="101" s="7" customFormat="1" customHeight="1" spans="4:13">
       <c r="D101" s="9"/>
-      <c r="E101" s="7"/>
-      <c r="F101" s="7"/>
-      <c r="G101" s="7"/>
-      <c r="H101" s="7"/>
-      <c r="I101" s="7"/>
-      <c r="J101" s="7"/>
       <c r="K101" s="2"/>
       <c r="L101" s="9"/>
       <c r="M101" s="9"/>
     </row>
     <row r="102" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D102" s="3"/>
-      <c r="E102" s="2"/>
-      <c r="F102" s="2"/>
-      <c r="G102" s="2"/>
-      <c r="H102" s="2"/>
-      <c r="I102" s="2"/>
-      <c r="J102" s="2"/>
-      <c r="K102" s="2"/>
       <c r="L102" s="3"/>
       <c r="M102" s="3"/>
     </row>
     <row r="103" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D103" s="3"/>
-      <c r="E103" s="2"/>
-      <c r="F103" s="2"/>
-      <c r="G103" s="2"/>
-      <c r="H103" s="2"/>
-      <c r="I103" s="2"/>
-      <c r="J103" s="2"/>
-      <c r="K103" s="2"/>
       <c r="L103" s="3"/>
       <c r="M103" s="3"/>
     </row>
     <row r="104" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D104" s="3"/>
-      <c r="E104" s="2"/>
-      <c r="F104" s="2"/>
-      <c r="G104" s="2"/>
-      <c r="H104" s="2"/>
-      <c r="I104" s="2"/>
-      <c r="J104" s="2"/>
-      <c r="K104" s="2"/>
       <c r="L104" s="3"/>
       <c r="M104" s="3"/>
     </row>
     <row r="105" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D105" s="3"/>
-      <c r="E105" s="2"/>
-      <c r="F105" s="2"/>
-      <c r="G105" s="2"/>
-      <c r="H105" s="2"/>
-      <c r="I105" s="2"/>
-      <c r="J105" s="2"/>
-      <c r="K105" s="2"/>
       <c r="L105" s="3"/>
       <c r="M105" s="3"/>
     </row>
     <row r="106" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D106" s="3"/>
-      <c r="E106" s="2"/>
-      <c r="F106" s="2"/>
-      <c r="G106" s="2"/>
-      <c r="H106" s="2"/>
-      <c r="I106" s="2"/>
-      <c r="J106" s="2"/>
-      <c r="K106" s="2"/>
       <c r="L106" s="3"/>
       <c r="M106" s="3"/>
     </row>
     <row r="107" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D107" s="3"/>
-      <c r="E107" s="2"/>
-      <c r="F107" s="2"/>
-      <c r="G107" s="2"/>
-      <c r="H107" s="2"/>
-      <c r="I107" s="2"/>
-      <c r="J107" s="2"/>
-      <c r="K107" s="2"/>
       <c r="L107" s="3"/>
       <c r="M107" s="3"/>
     </row>
     <row r="108" s="2" customFormat="1" customHeight="1" spans="4:13">
       <c r="D108" s="3"/>
-      <c r="E108" s="2"/>
-      <c r="F108" s="2"/>
-      <c r="G108" s="2"/>
-      <c r="H108" s="2"/>
-      <c r="I108" s="2"/>
-      <c r="J108" s="2"/>
-      <c r="K108" s="2"/>
       <c r="L108" s="3"/>
       <c r="M108" s="3"/>
     </row>
     <row r="109" s="7" customFormat="1" customHeight="1" spans="4:13">
       <c r="D109" s="9"/>
-      <c r="E109" s="7"/>
-      <c r="F109" s="7"/>
-      <c r="G109" s="7"/>
-      <c r="H109" s="7"/>
-      <c r="I109" s="7"/>
-      <c r="J109" s="7"/>
-      <c r="K109" s="7"/>
       <c r="L109" s="9"/>
       <c r="M109" s="9"/>
     </row>
     <row r="110" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C110" s="6"/>
       <c r="D110" s="3"/>
-      <c r="E110" s="2"/>
-      <c r="F110" s="2"/>
-      <c r="G110" s="2"/>
-      <c r="H110" s="2"/>
-      <c r="I110" s="2"/>
-      <c r="J110" s="2"/>
-      <c r="K110" s="2"/>
       <c r="L110" s="3"/>
       <c r="M110" s="3"/>
     </row>
     <row r="111" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C111" s="6"/>
       <c r="D111" s="3"/>
-      <c r="E111" s="2"/>
-      <c r="F111" s="2"/>
-      <c r="G111" s="2"/>
-      <c r="H111" s="2"/>
-      <c r="I111" s="2"/>
-      <c r="J111" s="2"/>
-      <c r="K111" s="2"/>
       <c r="L111" s="3"/>
       <c r="M111" s="3"/>
     </row>
     <row r="112" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C112" s="6"/>
       <c r="D112" s="3"/>
-      <c r="E112" s="2"/>
-      <c r="F112" s="2"/>
-      <c r="G112" s="2"/>
-      <c r="H112" s="2"/>
-      <c r="I112" s="2"/>
-      <c r="J112" s="2"/>
-      <c r="K112" s="2"/>
       <c r="L112" s="3"/>
       <c r="M112" s="3"/>
     </row>
     <row r="113" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C113" s="6"/>
       <c r="D113" s="3"/>
-      <c r="E113" s="2"/>
-      <c r="F113" s="2"/>
-      <c r="G113" s="2"/>
-      <c r="H113" s="2"/>
-      <c r="I113" s="2"/>
-      <c r="J113" s="2"/>
-      <c r="K113" s="2"/>
       <c r="L113" s="3"/>
       <c r="M113" s="3"/>
     </row>
     <row r="114" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C114" s="6"/>
       <c r="D114" s="3"/>
-      <c r="E114" s="2"/>
-      <c r="F114" s="2"/>
-      <c r="G114" s="2"/>
-      <c r="H114" s="2"/>
-      <c r="I114" s="2"/>
-      <c r="J114" s="2"/>
-      <c r="K114" s="2"/>
       <c r="L114" s="3"/>
       <c r="M114" s="3"/>
     </row>
     <row r="115" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C115" s="6"/>
       <c r="D115" s="3"/>
-      <c r="E115" s="2"/>
-      <c r="F115" s="2"/>
-      <c r="G115" s="2"/>
-      <c r="H115" s="2"/>
-      <c r="I115" s="2"/>
-      <c r="J115" s="2"/>
-      <c r="K115" s="2"/>
       <c r="L115" s="3"/>
       <c r="M115" s="3"/>
     </row>
     <row r="116" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C116" s="6"/>
       <c r="D116" s="3"/>
-      <c r="E116" s="2"/>
-      <c r="F116" s="2"/>
-      <c r="G116" s="2"/>
-      <c r="H116" s="2"/>
-      <c r="I116" s="2"/>
-      <c r="J116" s="2"/>
-      <c r="K116" s="2"/>
       <c r="L116" s="3"/>
       <c r="M116" s="3"/>
     </row>
@@ -23315,13 +22755,13 @@
         <v>180001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="E6" s="2">
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -23341,13 +22781,13 @@
         <v>180002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="E7" s="2">
         <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -23367,13 +22807,13 @@
         <v>180003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="E8" s="2">
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -23393,13 +22833,13 @@
         <v>180004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="E9" s="2">
         <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -23419,13 +22859,13 @@
         <v>180005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="E10" s="2">
         <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -23445,13 +22885,13 @@
         <v>180006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="E11" s="2">
         <v>18</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -23473,13 +22913,13 @@
         <v>180007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="E12" s="2">
         <v>18</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -23501,13 +22941,13 @@
         <v>180008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="E13" s="2">
         <v>18</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -23529,13 +22969,13 @@
         <v>180009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="E14" s="2">
         <v>18</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -23557,13 +22997,13 @@
         <v>180010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="E15" s="2">
         <v>18</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -23585,13 +23025,13 @@
         <v>180011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="E16" s="2">
         <v>18</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -23613,13 +23053,13 @@
         <v>180012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="E17" s="2">
         <v>18</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -23641,13 +23081,13 @@
         <v>180013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="E18" s="2">
         <v>18</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -23669,13 +23109,13 @@
         <v>180014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="E19" s="2">
         <v>18</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -23697,13 +23137,13 @@
         <v>180015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="E20" s="2">
         <v>18</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -23725,13 +23165,13 @@
         <v>180016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="E21" s="2">
         <v>18</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -23753,13 +23193,13 @@
         <v>180017</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="E22" s="2">
         <v>18</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -23781,13 +23221,13 @@
         <v>180018</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="E23" s="2">
         <v>18</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -23809,13 +23249,13 @@
         <v>180019</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="E24" s="2">
         <v>18</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -23837,13 +23277,13 @@
         <v>180020</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="E25" s="2">
         <v>18</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -23865,13 +23305,13 @@
         <v>180021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="E26" s="2">
         <v>18</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -23893,13 +23333,13 @@
         <v>180022</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="E27" s="2">
         <v>18</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -23926,13 +23366,13 @@
         <v>180030</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="E29" s="2">
         <v>18</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -23954,13 +23394,13 @@
         <v>180031</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="E30" s="2">
         <v>18</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="G30" s="3">
         <v>1</v>
@@ -23980,13 +23420,13 @@
         <v>180032</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="E31" s="2">
         <v>18</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="G31" s="3">
         <v>1</v>
@@ -24006,13 +23446,13 @@
         <v>180033</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="E32" s="2">
         <v>18</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="G32" s="3">
         <v>1</v>
@@ -24032,13 +23472,13 @@
         <v>180034</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="E33" s="2">
         <v>18</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="G33" s="3">
         <v>1</v>
@@ -24060,13 +23500,13 @@
         <v>180035</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="E34" s="2">
         <v>18</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="G34" s="3">
         <v>1</v>
@@ -24088,13 +23528,13 @@
         <v>180036</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="E35" s="2">
         <v>18</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="G35" s="3">
         <v>1</v>
@@ -24116,13 +23556,13 @@
         <v>180037</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="E36" s="2">
         <v>18</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="G36" s="3">
         <v>1</v>
@@ -24144,13 +23584,13 @@
         <v>180038</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="E37" s="2">
         <v>18</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="G37" s="3">
         <v>1</v>
@@ -24172,13 +23612,13 @@
         <v>180039</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="E38" s="2">
         <v>18</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="G38" s="3">
         <v>1</v>
@@ -24339,13 +23779,13 @@
         <v>190001</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="E6" s="2">
         <v>19</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -24365,13 +23805,13 @@
         <v>190002</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="E7" s="2">
         <v>19</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -24391,13 +23831,13 @@
         <v>190003</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="E8" s="2">
         <v>19</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -24417,13 +23857,13 @@
         <v>190004</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="E9" s="2">
         <v>19</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -24443,13 +23883,13 @@
         <v>190005</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="E10" s="2">
         <v>19</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -24469,13 +23909,13 @@
         <v>190006</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="E11" s="2">
         <v>19</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -2801,13 +2801,13 @@
     <t>韧性宝石</t>
   </si>
   <si>
-    <t>青龙之剑</t>
+    <t>青龙神剑</t>
   </si>
   <si>
     <t>激活神器</t>
   </si>
   <si>
-    <t>青龙之甲</t>
+    <t>青龙神甲</t>
   </si>
   <si>
     <t>青龙面罩</t>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="6"/>
+    <workbookView windowHeight="17680" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="6"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -384,7 +384,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="854">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1610" uniqueCount="856">
   <si>
     <t>_Id</t>
   </si>
@@ -936,6 +936,12 @@
   </si>
   <si>
     <t>分解暗金装备获取，暗金装备升阶材料</t>
+  </si>
+  <si>
+    <t>开孔石</t>
+  </si>
+  <si>
+    <t>给宝石增加镶嵌孔</t>
   </si>
   <si>
     <t>图鉴碎片</t>
@@ -5278,7 +5284,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:M105"/>
+  <dimension ref="C3:M106"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="3"/>
@@ -6234,53 +6240,53 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
-      <c r="L32" s="3"/>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C33" s="3">
-        <v>4101</v>
-      </c>
-      <c r="D33" s="3" t="s">
+    <row r="32" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C32" s="3">
+        <v>4027</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="E33" s="3">
-        <v>5</v>
-      </c>
-      <c r="F33" s="3" t="s">
+      <c r="E32" s="3">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="G33" s="3">
-        <v>1</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="G32" s="3">
+        <v>1</v>
+      </c>
+      <c r="H32" s="3">
         <v>9999999</v>
       </c>
-      <c r="I33" s="3">
-        <v>0</v>
-      </c>
-      <c r="J33" s="3">
-        <v>5</v>
-      </c>
-      <c r="L33" s="3">
-        <v>0</v>
-      </c>
-      <c r="M33" s="3">
-        <v>0</v>
-      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>7</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
     </row>
     <row r="34" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C34" s="3">
-        <v>4102</v>
+        <v>4101</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>186</v>
@@ -6312,7 +6318,7 @@
     </row>
     <row r="35" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C35" s="3">
-        <v>4103</v>
+        <v>4102</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>188</v>
@@ -6321,7 +6327,7 @@
         <v>5</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>149</v>
+        <v>189</v>
       </c>
       <c r="G35" s="3">
         <v>1</v>
@@ -6344,10 +6350,10 @@
     </row>
     <row r="36" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C36" s="3">
-        <v>4104</v>
+        <v>4103</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E36" s="3">
         <v>5</v>
@@ -6376,10 +6382,10 @@
     </row>
     <row r="37" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C37" s="3">
-        <v>4105</v>
+        <v>4104</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E37" s="3">
         <v>5</v>
@@ -6408,16 +6414,16 @@
     </row>
     <row r="38" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C38" s="3">
-        <v>4106</v>
+        <v>4105</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E38" s="3">
         <v>5</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="G38" s="3">
         <v>1</v>
@@ -6440,7 +6446,7 @@
     </row>
     <row r="39" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C39" s="3">
-        <v>4107</v>
+        <v>4106</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>191</v>
@@ -6472,7 +6478,7 @@
     </row>
     <row r="40" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C40" s="3">
-        <v>4108</v>
+        <v>4107</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>193</v>
@@ -6504,7 +6510,7 @@
     </row>
     <row r="41" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C41" s="3">
-        <v>4109</v>
+        <v>4108</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>195</v>
@@ -6536,7 +6542,7 @@
     </row>
     <row r="42" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C42" s="3">
-        <v>4110</v>
+        <v>4109</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>197</v>
@@ -6568,7 +6574,7 @@
     </row>
     <row r="43" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C43" s="3">
-        <v>4111</v>
+        <v>4110</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>199</v>
@@ -6598,41 +6604,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C45" s="3">
-        <v>4201</v>
-      </c>
-      <c r="D45" s="3" t="s">
+    <row r="44" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C44" s="3">
+        <v>4111</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="E45" s="3">
-        <v>5</v>
-      </c>
-      <c r="F45" s="3" t="s">
+      <c r="E44" s="3">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="G45" s="3">
-        <v>1</v>
-      </c>
-      <c r="H45" s="3">
-        <v>2000000</v>
-      </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3">
-        <v>5</v>
-      </c>
-      <c r="L45" s="3">
-        <v>4002</v>
-      </c>
-      <c r="M45" s="3">
-        <v>1000</v>
+      <c r="G44" s="3">
+        <v>1</v>
+      </c>
+      <c r="H44" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I44" s="3">
+        <v>0</v>
+      </c>
+      <c r="J44" s="3">
+        <v>5</v>
+      </c>
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="46" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C46" s="3">
-        <v>4202</v>
+        <v>4201</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>203</v>
@@ -6647,7 +6653,7 @@
         <v>1</v>
       </c>
       <c r="H46" s="3">
-        <v>99999</v>
+        <v>2000000</v>
       </c>
       <c r="I46" s="3">
         <v>0</v>
@@ -6656,50 +6662,47 @@
         <v>5</v>
       </c>
       <c r="L46" s="3">
-        <v>0</v>
+        <v>4002</v>
       </c>
       <c r="M46" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C48" s="3">
-        <v>6101</v>
-      </c>
-      <c r="D48" s="3" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="47" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C47" s="3">
+        <v>4202</v>
+      </c>
+      <c r="D47" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="E48" s="3">
-        <v>7</v>
-      </c>
-      <c r="F48" s="3" t="s">
+      <c r="E47" s="3">
+        <v>5</v>
+      </c>
+      <c r="F47" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="G48" s="3">
-        <v>1</v>
-      </c>
-      <c r="H48" s="3">
-        <v>99999</v>
-      </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3">
-        <v>4</v>
-      </c>
-      <c r="K48" s="3">
-        <v>1</v>
-      </c>
-      <c r="L48" s="3">
-        <v>0</v>
-      </c>
-      <c r="M48" s="3">
+      <c r="G47" s="3">
+        <v>1</v>
+      </c>
+      <c r="H47" s="3">
+        <v>99999</v>
+      </c>
+      <c r="I47" s="3">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3">
+        <v>5</v>
+      </c>
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="49" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C49" s="3">
-        <v>6102</v>
+        <v>6101</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>207</v>
@@ -6723,7 +6726,7 @@
         <v>4</v>
       </c>
       <c r="K49" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
@@ -6734,7 +6737,7 @@
     </row>
     <row r="50" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C50" s="3">
-        <v>6103</v>
+        <v>6102</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>209</v>
@@ -6758,7 +6761,7 @@
         <v>4</v>
       </c>
       <c r="K50" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L50" s="3">
         <v>0</v>
@@ -6769,7 +6772,7 @@
     </row>
     <row r="51" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C51" s="3">
-        <v>6104</v>
+        <v>6103</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>211</v>
@@ -6793,7 +6796,7 @@
         <v>4</v>
       </c>
       <c r="K51" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L51" s="3">
         <v>0</v>
@@ -6802,9 +6805,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" customHeight="1" spans="3:13">
+    <row r="52" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C52" s="3">
-        <v>6105</v>
+        <v>6104</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>213</v>
@@ -6828,7 +6831,7 @@
         <v>4</v>
       </c>
       <c r="K52" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -6837,9 +6840,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" s="3" customFormat="1" customHeight="1" spans="3:13">
+    <row r="53" customHeight="1" spans="3:13">
       <c r="C53" s="3">
-        <v>6106</v>
+        <v>6105</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>215</v>
@@ -6863,7 +6866,7 @@
         <v>4</v>
       </c>
       <c r="K53" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L53" s="3">
         <v>0</v>
@@ -6872,15 +6875,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" customHeight="1" spans="3:13">
+    <row r="54" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C54" s="3">
-        <v>7101</v>
+        <v>6106</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>217</v>
       </c>
       <c r="E54" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>218</v>
@@ -6898,7 +6901,7 @@
         <v>4</v>
       </c>
       <c r="K54" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L54" s="3">
         <v>0</v>
@@ -6909,7 +6912,7 @@
     </row>
     <row r="55" customHeight="1" spans="3:13">
       <c r="C55" s="3">
-        <v>7102</v>
+        <v>7101</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>219</v>
@@ -6933,7 +6936,7 @@
         <v>4</v>
       </c>
       <c r="K55" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L55" s="3">
         <v>0</v>
@@ -6944,7 +6947,7 @@
     </row>
     <row r="56" customHeight="1" spans="3:13">
       <c r="C56" s="3">
-        <v>7103</v>
+        <v>7102</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>221</v>
@@ -6968,7 +6971,7 @@
         <v>4</v>
       </c>
       <c r="K56" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L56" s="3">
         <v>0</v>
@@ -6979,7 +6982,7 @@
     </row>
     <row r="57" customHeight="1" spans="3:13">
       <c r="C57" s="3">
-        <v>7104</v>
+        <v>7103</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>223</v>
@@ -7003,7 +7006,7 @@
         <v>4</v>
       </c>
       <c r="K57" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L57" s="3">
         <v>0</v>
@@ -7014,7 +7017,7 @@
     </row>
     <row r="58" customHeight="1" spans="3:13">
       <c r="C58" s="3">
-        <v>7105</v>
+        <v>7104</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>225</v>
@@ -7038,7 +7041,7 @@
         <v>4</v>
       </c>
       <c r="K58" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -7049,7 +7052,7 @@
     </row>
     <row r="59" customHeight="1" spans="3:13">
       <c r="C59" s="3">
-        <v>7107</v>
+        <v>7105</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>227</v>
@@ -7073,7 +7076,7 @@
         <v>4</v>
       </c>
       <c r="K59" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L59" s="3">
         <v>0</v>
@@ -7082,41 +7085,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C63" s="3">
-        <v>8001</v>
-      </c>
-      <c r="D63" s="3" t="s">
+    <row r="60" customHeight="1" spans="3:13">
+      <c r="C60" s="3">
+        <v>7107</v>
+      </c>
+      <c r="D60" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E63" s="3">
-        <v>5</v>
-      </c>
-      <c r="F63" s="3" t="s">
+      <c r="E60" s="3">
+        <v>8</v>
+      </c>
+      <c r="F60" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="G63" s="3">
-        <v>1</v>
-      </c>
-      <c r="H63" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="I63" s="3">
-        <v>0</v>
-      </c>
-      <c r="J63" s="3">
-        <v>6</v>
-      </c>
-      <c r="L63" s="3">
-        <v>0</v>
-      </c>
-      <c r="M63" s="3">
+      <c r="G60" s="3">
+        <v>1</v>
+      </c>
+      <c r="H60" s="3">
+        <v>99999</v>
+      </c>
+      <c r="I60" s="3">
+        <v>0</v>
+      </c>
+      <c r="J60" s="3">
+        <v>4</v>
+      </c>
+      <c r="K60" s="3">
+        <v>6</v>
+      </c>
+      <c r="L60" s="3">
+        <v>0</v>
+      </c>
+      <c r="M60" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="64" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C64" s="3">
-        <v>8002</v>
+        <v>8001</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>231</v>
@@ -7125,7 +7131,7 @@
         <v>5</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="G64" s="3">
         <v>1</v>
@@ -7148,16 +7154,16 @@
     </row>
     <row r="65" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C65" s="3">
-        <v>8003</v>
+        <v>8002</v>
       </c>
       <c r="D65" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E65" s="3">
+        <v>5</v>
+      </c>
+      <c r="F65" s="3" t="s">
         <v>232</v>
-      </c>
-      <c r="E65" s="3">
-        <v>5</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>230</v>
       </c>
       <c r="G65" s="3">
         <v>1</v>
@@ -7180,16 +7186,16 @@
     </row>
     <row r="66" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C66" s="3">
-        <v>8004</v>
+        <v>8003</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E66" s="3">
         <v>5</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="G66" s="3">
         <v>1</v>
@@ -7212,16 +7218,16 @@
     </row>
     <row r="67" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C67" s="3">
-        <v>8005</v>
+        <v>8004</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E67" s="3">
         <v>5</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="G67" s="3">
         <v>1</v>
@@ -7244,16 +7250,16 @@
     </row>
     <row r="68" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C68" s="3">
-        <v>8006</v>
+        <v>8005</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E68" s="3">
         <v>5</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="G68" s="3">
         <v>1</v>
@@ -7276,16 +7282,16 @@
     </row>
     <row r="69" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C69" s="3">
-        <v>8007</v>
+        <v>8006</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E69" s="3">
         <v>5</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="G69" s="3">
         <v>1</v>
@@ -7308,16 +7314,16 @@
     </row>
     <row r="70" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C70" s="3">
-        <v>8008</v>
+        <v>8007</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E70" s="3">
         <v>5</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="G70" s="3">
         <v>1</v>
@@ -7340,16 +7346,16 @@
     </row>
     <row r="71" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C71" s="3">
-        <v>8009</v>
+        <v>8008</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E71" s="3">
         <v>5</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="G71" s="3">
         <v>1</v>
@@ -7372,16 +7378,16 @@
     </row>
     <row r="72" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C72" s="3">
-        <v>8010</v>
+        <v>8009</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E72" s="3">
         <v>5</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="G72" s="3">
         <v>1</v>
@@ -7402,41 +7408,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C74" s="3">
-        <v>8101</v>
-      </c>
-      <c r="D74" s="14" t="s">
-        <v>240</v>
-      </c>
-      <c r="E74" s="3">
-        <v>5</v>
-      </c>
-      <c r="F74" s="3" t="s">
+    <row r="73" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C73" s="3">
+        <v>8010</v>
+      </c>
+      <c r="D73" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="G74" s="3">
-        <v>1</v>
-      </c>
-      <c r="H74" s="3">
+      <c r="E73" s="3">
+        <v>5</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="G73" s="3">
+        <v>1</v>
+      </c>
+      <c r="H73" s="3">
         <v>9999999</v>
       </c>
-      <c r="I74" s="3">
-        <v>0</v>
-      </c>
-      <c r="J74" s="3">
-        <v>7</v>
-      </c>
-      <c r="L74" s="3">
-        <v>0</v>
-      </c>
-      <c r="M74" s="3">
+      <c r="I73" s="3">
+        <v>0</v>
+      </c>
+      <c r="J73" s="3">
+        <v>6</v>
+      </c>
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="75" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C75" s="3">
-        <v>8102</v>
+        <v>8101</v>
       </c>
       <c r="D75" s="14" t="s">
         <v>242</v>
@@ -7445,7 +7451,7 @@
         <v>5</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G75" s="3">
         <v>1</v>
@@ -7468,16 +7474,16 @@
     </row>
     <row r="76" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C76" s="3">
-        <v>8103</v>
+        <v>8102</v>
       </c>
       <c r="D76" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="E76" s="3">
+        <v>5</v>
+      </c>
+      <c r="F76" s="3" t="s">
         <v>243</v>
-      </c>
-      <c r="E76" s="3">
-        <v>5</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>241</v>
       </c>
       <c r="G76" s="3">
         <v>1</v>
@@ -7500,16 +7506,16 @@
     </row>
     <row r="77" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C77" s="3">
-        <v>8104</v>
+        <v>8103</v>
       </c>
       <c r="D77" s="14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E77" s="3">
         <v>5</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G77" s="3">
         <v>1</v>
@@ -7532,16 +7538,16 @@
     </row>
     <row r="78" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C78" s="3">
-        <v>8105</v>
+        <v>8104</v>
       </c>
       <c r="D78" s="14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E78" s="3">
         <v>5</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G78" s="3">
         <v>1</v>
@@ -7564,16 +7570,16 @@
     </row>
     <row r="79" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C79" s="3">
-        <v>8106</v>
+        <v>8105</v>
       </c>
       <c r="D79" s="14" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E79" s="3">
         <v>5</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G79" s="3">
         <v>1</v>
@@ -7596,16 +7602,16 @@
     </row>
     <row r="80" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C80" s="3">
-        <v>8107</v>
+        <v>8106</v>
       </c>
       <c r="D80" s="14" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E80" s="3">
         <v>5</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G80" s="3">
         <v>1</v>
@@ -7628,16 +7634,16 @@
     </row>
     <row r="81" s="3" customFormat="1" customHeight="1" spans="3:13">
       <c r="C81" s="3">
-        <v>8108</v>
+        <v>8107</v>
       </c>
       <c r="D81" s="14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E81" s="3">
         <v>5</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G81" s="3">
         <v>1</v>
@@ -7658,44 +7664,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" customHeight="1" spans="3:13">
-      <c r="C83" s="3">
-        <v>8201</v>
-      </c>
-      <c r="D83" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="E83" s="3">
-        <v>16</v>
-      </c>
-      <c r="F83" s="3" t="s">
+    <row r="82" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C82" s="3">
+        <v>8108</v>
+      </c>
+      <c r="D82" s="14" t="s">
         <v>250</v>
       </c>
-      <c r="G83" s="3">
-        <v>1</v>
-      </c>
-      <c r="H83" s="3">
-        <v>1</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>1</v>
-      </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="E82" s="3">
+        <v>5</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="G82" s="3">
+        <v>1</v>
+      </c>
+      <c r="H82" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="I82" s="3">
+        <v>0</v>
+      </c>
+      <c r="J82" s="3">
+        <v>7</v>
+      </c>
+      <c r="L82" s="3">
+        <v>0</v>
+      </c>
+      <c r="M82" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="3:13">
       <c r="C84" s="3">
-        <v>8202</v>
+        <v>8201</v>
       </c>
       <c r="D84" s="14" t="s">
         <v>251</v>
@@ -7716,7 +7719,7 @@
         <v>0</v>
       </c>
       <c r="J84" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K84" s="3">
         <v>0</v>
@@ -7730,7 +7733,7 @@
     </row>
     <row r="85" customHeight="1" spans="3:13">
       <c r="C85" s="3">
-        <v>8203</v>
+        <v>8202</v>
       </c>
       <c r="D85" s="14" t="s">
         <v>253</v>
@@ -7751,7 +7754,7 @@
         <v>0</v>
       </c>
       <c r="J85" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K85" s="3">
         <v>0</v>
@@ -7765,7 +7768,7 @@
     </row>
     <row r="86" customHeight="1" spans="3:13">
       <c r="C86" s="3">
-        <v>8204</v>
+        <v>8203</v>
       </c>
       <c r="D86" s="14" t="s">
         <v>255</v>
@@ -7786,7 +7789,7 @@
         <v>0</v>
       </c>
       <c r="J86" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K86" s="3">
         <v>0</v>
@@ -7800,7 +7803,7 @@
     </row>
     <row r="87" customHeight="1" spans="3:13">
       <c r="C87" s="3">
-        <v>8205</v>
+        <v>8204</v>
       </c>
       <c r="D87" s="14" t="s">
         <v>257</v>
@@ -7821,7 +7824,7 @@
         <v>0</v>
       </c>
       <c r="J87" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K87" s="3">
         <v>0</v>
@@ -7835,7 +7838,7 @@
     </row>
     <row r="88" customHeight="1" spans="3:13">
       <c r="C88" s="3">
-        <v>8206</v>
+        <v>8205</v>
       </c>
       <c r="D88" s="14" t="s">
         <v>259</v>
@@ -7856,7 +7859,7 @@
         <v>0</v>
       </c>
       <c r="J88" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K88" s="3">
         <v>0</v>
@@ -7870,7 +7873,7 @@
     </row>
     <row r="89" customHeight="1" spans="3:13">
       <c r="C89" s="3">
-        <v>8207</v>
+        <v>8206</v>
       </c>
       <c r="D89" s="14" t="s">
         <v>261</v>
@@ -7891,20 +7894,52 @@
         <v>0</v>
       </c>
       <c r="J89" s="3">
+        <v>6</v>
+      </c>
+      <c r="K89" s="3">
+        <v>0</v>
+      </c>
+      <c r="L89" s="3">
+        <v>0</v>
+      </c>
+      <c r="M89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" customHeight="1" spans="3:13">
+      <c r="C90" s="3">
+        <v>8207</v>
+      </c>
+      <c r="D90" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="E90" s="3">
+        <v>16</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="G90" s="3">
+        <v>1</v>
+      </c>
+      <c r="H90" s="3">
+        <v>1</v>
+      </c>
+      <c r="I90" s="3">
+        <v>0</v>
+      </c>
+      <c r="J90" s="3">
         <v>7</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" customHeight="1" spans="4:4">
-      <c r="D91" s="14"/>
+      <c r="K90" s="3">
+        <v>0</v>
+      </c>
+      <c r="L90" s="3">
+        <v>0</v>
+      </c>
+      <c r="M90" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="92" customHeight="1" spans="4:4">
       <c r="D92" s="14"/>
@@ -7924,8 +7959,8 @@
     <row r="97" customHeight="1" spans="4:4">
       <c r="D97" s="14"/>
     </row>
-    <row r="99" customHeight="1" spans="4:4">
-      <c r="D99" s="14"/>
+    <row r="98" customHeight="1" spans="4:4">
+      <c r="D98" s="14"/>
     </row>
     <row r="100" customHeight="1" spans="4:4">
       <c r="D100" s="14"/>
@@ -7944,6 +7979,9 @@
     </row>
     <row r="105" customHeight="1" spans="4:4">
       <c r="D105" s="14"/>
+    </row>
+    <row r="106" customHeight="1" spans="4:4">
+      <c r="D106" s="14"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -8089,13 +8127,13 @@
         <v>1999001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E6" s="2">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -8117,13 +8155,13 @@
         <v>1999002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E7" s="2">
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -8145,13 +8183,13 @@
         <v>1999003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E8" s="2">
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -8173,13 +8211,13 @@
         <v>1999004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E9" s="2">
         <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -8201,13 +8239,13 @@
         <v>1999005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E10" s="2">
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -8229,13 +8267,13 @@
         <v>1999006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E11" s="2">
         <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -8262,13 +8300,13 @@
         <v>1999989</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E13" s="2">
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -8290,13 +8328,13 @@
         <v>1999990</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E14" s="2">
         <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -8318,13 +8356,13 @@
         <v>1999991</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E15" s="2">
         <v>11</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -8346,13 +8384,13 @@
         <v>1999992</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E16" s="2">
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -8374,13 +8412,13 @@
         <v>1999993</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E17" s="2">
         <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -8402,13 +8440,13 @@
         <v>1999994</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E18" s="2">
         <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -8430,13 +8468,13 @@
         <v>1999995</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E19" s="2">
         <v>11</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -8458,13 +8496,13 @@
         <v>1999996</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E20" s="2">
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -8486,13 +8524,13 @@
         <v>1999997</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E21" s="2">
         <v>11</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -8514,13 +8552,13 @@
         <v>2000000</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E22" s="2">
         <v>11</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -8542,13 +8580,13 @@
         <v>2000001</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E23" s="2">
         <v>11</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -8570,13 +8608,13 @@
         <v>2000002</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E24" s="2">
         <v>11</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -8598,13 +8636,13 @@
         <v>2000003</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E25" s="2">
         <v>11</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -8626,13 +8664,13 @@
         <v>2000004</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E26" s="2">
         <v>11</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -8654,13 +8692,13 @@
         <v>2000005</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E27" s="2">
         <v>11</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -8682,13 +8720,13 @@
         <v>2000006</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E28" s="2">
         <v>11</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -8710,13 +8748,13 @@
         <v>2000007</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E29" s="2">
         <v>11</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -8738,13 +8776,13 @@
         <v>2000008</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E30" s="2">
         <v>11</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -8766,13 +8804,13 @@
         <v>2000009</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E31" s="2">
         <v>11</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -8794,13 +8832,13 @@
         <v>2000010</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E32" s="2">
         <v>11</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -8822,13 +8860,13 @@
         <v>2000011</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E33" s="2">
         <v>11</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -8850,13 +8888,13 @@
         <v>2000012</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E34" s="2">
         <v>11</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -8878,13 +8916,13 @@
         <v>2000013</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E35" s="2">
         <v>11</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -8918,13 +8956,13 @@
         <v>2000100</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E39" s="2">
         <v>11</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -8946,13 +8984,13 @@
         <v>2000101</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E40" s="2">
         <v>11</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -8974,13 +9012,13 @@
         <v>2000102</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E41" s="2">
         <v>11</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -9002,13 +9040,13 @@
         <v>2000103</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E42" s="2">
         <v>11</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -9030,13 +9068,13 @@
         <v>2000104</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E43" s="2">
         <v>11</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -9058,13 +9096,13 @@
         <v>2000105</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E44" s="2">
         <v>11</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -9086,13 +9124,13 @@
         <v>2000106</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E45" s="2">
         <v>11</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G45" s="2">
         <v>1</v>
@@ -9114,13 +9152,13 @@
         <v>2000107</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E46" s="2">
         <v>11</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -9142,13 +9180,13 @@
         <v>2000108</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E47" s="2">
         <v>11</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -9170,13 +9208,13 @@
         <v>2000109</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E48" s="2">
         <v>11</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -9198,13 +9236,13 @@
         <v>2000110</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E49" s="2">
         <v>11</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -9226,13 +9264,13 @@
         <v>2000111</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E50" s="2">
         <v>11</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -9254,13 +9292,13 @@
         <v>2000112</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E51" s="2">
         <v>11</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -9282,13 +9320,13 @@
         <v>2000113</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E52" s="2">
         <v>11</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -9310,13 +9348,13 @@
         <v>2000114</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E53" s="2">
         <v>11</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G53" s="2">
         <v>1</v>
@@ -9338,13 +9376,13 @@
         <v>2000115</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E54" s="2">
         <v>11</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G54" s="2">
         <v>1</v>
@@ -9366,13 +9404,13 @@
         <v>2000116</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E55" s="2">
         <v>11</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G55" s="2">
         <v>1</v>
@@ -9394,13 +9432,13 @@
         <v>2000117</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E56" s="2">
         <v>11</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G56" s="2">
         <v>1</v>
@@ -9422,13 +9460,13 @@
         <v>2000118</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E57" s="2">
         <v>11</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G57" s="2">
         <v>1</v>
@@ -9450,13 +9488,13 @@
         <v>2000119</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E58" s="2">
         <v>11</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G58" s="2">
         <v>1</v>
@@ -9478,13 +9516,13 @@
         <v>2000120</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E59" s="2">
         <v>11</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G59" s="2">
         <v>1</v>
@@ -9506,13 +9544,13 @@
         <v>2000121</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E60" s="2">
         <v>11</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G60" s="2">
         <v>1</v>
@@ -9534,13 +9572,13 @@
         <v>2000122</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E61" s="2">
         <v>11</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G61" s="2">
         <v>1</v>
@@ -9562,13 +9600,13 @@
         <v>2000123</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E62" s="2">
         <v>11</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G62" s="2">
         <v>1</v>
@@ -9590,13 +9628,13 @@
         <v>2000124</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E63" s="2">
         <v>11</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G63" s="2">
         <v>1</v>
@@ -9618,13 +9656,13 @@
         <v>2000125</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E64" s="2">
         <v>11</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G64" s="2">
         <v>1</v>
@@ -9646,13 +9684,13 @@
         <v>2000126</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E65" s="2">
         <v>11</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G65" s="2">
         <v>1</v>
@@ -9674,13 +9712,13 @@
         <v>2000127</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E66" s="2">
         <v>11</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G66" s="2">
         <v>1</v>
@@ -9702,13 +9740,13 @@
         <v>2000128</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E67" s="2">
         <v>11</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G67" s="2">
         <v>1</v>
@@ -9730,13 +9768,13 @@
         <v>2000129</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E68" s="2">
         <v>11</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G68" s="2">
         <v>1</v>
@@ -9758,13 +9796,13 @@
         <v>2000200</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E70" s="2">
         <v>11</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G70" s="2">
         <v>1</v>
@@ -9784,13 +9822,13 @@
         <v>2000201</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E71" s="2">
         <v>11</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G71" s="2">
         <v>1</v>
@@ -9810,13 +9848,13 @@
         <v>2000202</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E72" s="2">
         <v>11</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G72" s="2">
         <v>1</v>
@@ -9836,13 +9874,13 @@
         <v>2000203</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E73" s="2">
         <v>11</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G73" s="2">
         <v>1</v>
@@ -9862,13 +9900,13 @@
         <v>2000204</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E74" s="2">
         <v>11</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G74" s="2">
         <v>1</v>
@@ -9888,13 +9926,13 @@
         <v>2000205</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E75" s="2">
         <v>11</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G75" s="2">
         <v>1</v>
@@ -9914,13 +9952,13 @@
         <v>2000206</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E76" s="2">
         <v>11</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G76" s="2">
         <v>1</v>
@@ -9940,13 +9978,13 @@
         <v>2000207</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E77" s="2">
         <v>11</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G77" s="2">
         <v>1</v>
@@ -9966,13 +10004,13 @@
         <v>2000208</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E78" s="2">
         <v>11</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G78" s="2">
         <v>1</v>
@@ -9992,13 +10030,13 @@
         <v>2000209</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E79" s="2">
         <v>11</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G79" s="2">
         <v>1</v>
@@ -10018,13 +10056,13 @@
         <v>2000210</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E80" s="2">
         <v>11</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G80" s="2">
         <v>1</v>
@@ -10044,13 +10082,13 @@
         <v>2000211</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E81" s="2">
         <v>11</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G81" s="2">
         <v>1</v>
@@ -10070,13 +10108,13 @@
         <v>2000212</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E82" s="2">
         <v>11</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G82" s="2">
         <v>1</v>
@@ -10096,13 +10134,13 @@
         <v>2000213</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E83" s="2">
         <v>11</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G83" s="2">
         <v>1</v>
@@ -10122,13 +10160,13 @@
         <v>2000214</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E84" s="2">
         <v>11</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G84" s="2">
         <v>1</v>
@@ -10148,13 +10186,13 @@
         <v>2000215</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E85" s="2">
         <v>11</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G85" s="2">
         <v>1</v>
@@ -10174,13 +10212,13 @@
         <v>2000216</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E86" s="2">
         <v>11</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G86" s="2">
         <v>1</v>
@@ -10200,13 +10238,13 @@
         <v>2000217</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E87" s="2">
         <v>11</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G87" s="2">
         <v>1</v>
@@ -10226,13 +10264,13 @@
         <v>2000218</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E88" s="2">
         <v>11</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G88" s="2">
         <v>1</v>
@@ -10252,13 +10290,13 @@
         <v>2000219</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E89" s="2">
         <v>11</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G89" s="2">
         <v>1</v>
@@ -10278,13 +10316,13 @@
         <v>2000220</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E90" s="2">
         <v>11</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G90" s="2">
         <v>1</v>
@@ -10304,13 +10342,13 @@
         <v>2000221</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E91" s="2">
         <v>11</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G91" s="2">
         <v>1</v>
@@ -10330,13 +10368,13 @@
         <v>2000222</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E92" s="2">
         <v>11</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G92" s="2">
         <v>1</v>
@@ -10356,13 +10394,13 @@
         <v>2000223</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E93" s="2">
         <v>11</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G93" s="2">
         <v>1</v>
@@ -10382,13 +10420,13 @@
         <v>2000224</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E94" s="2">
         <v>11</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G94" s="2">
         <v>1</v>
@@ -10408,13 +10446,13 @@
         <v>2000225</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E95" s="2">
         <v>11</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G95" s="2">
         <v>1</v>
@@ -10434,13 +10472,13 @@
         <v>2000226</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E96" s="2">
         <v>11</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G96" s="2">
         <v>1</v>
@@ -10460,13 +10498,13 @@
         <v>2000227</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E97" s="2">
         <v>11</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G97" s="2">
         <v>1</v>
@@ -10486,13 +10524,13 @@
         <v>2000228</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E98" s="2">
         <v>11</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G98" s="2">
         <v>1</v>
@@ -10512,13 +10550,13 @@
         <v>2000229</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E99" s="2">
         <v>11</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G99" s="2">
         <v>1</v>
@@ -10538,13 +10576,13 @@
         <v>2000300</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E102" s="2">
         <v>11</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G102" s="2">
         <v>1</v>
@@ -10564,13 +10602,13 @@
         <v>2000301</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E103" s="2">
         <v>11</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G103" s="2">
         <v>1</v>
@@ -10590,13 +10628,13 @@
         <v>2000302</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E104" s="2">
         <v>11</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G104" s="2">
         <v>1</v>
@@ -10616,13 +10654,13 @@
         <v>2000303</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E105" s="2">
         <v>11</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G105" s="2">
         <v>1</v>
@@ -10642,13 +10680,13 @@
         <v>2000304</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E106" s="2">
         <v>11</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G106" s="2">
         <v>1</v>
@@ -10668,13 +10706,13 @@
         <v>2000305</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E107" s="2">
         <v>11</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G107" s="2">
         <v>1</v>
@@ -10694,13 +10732,13 @@
         <v>2000306</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E108" s="2">
         <v>11</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G108" s="2">
         <v>1</v>
@@ -10720,13 +10758,13 @@
         <v>2000307</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E109" s="2">
         <v>11</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G109" s="2">
         <v>1</v>
@@ -10746,13 +10784,13 @@
         <v>2000308</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E110" s="2">
         <v>11</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G110" s="2">
         <v>1</v>
@@ -10772,13 +10810,13 @@
         <v>2000309</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E111" s="2">
         <v>11</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G111" s="2">
         <v>1</v>
@@ -10798,13 +10836,13 @@
         <v>2000310</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E112" s="2">
         <v>11</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G112" s="2">
         <v>1</v>
@@ -10824,13 +10862,13 @@
         <v>2000311</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E113" s="2">
         <v>11</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G113" s="2">
         <v>1</v>
@@ -10850,13 +10888,13 @@
         <v>2000312</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E114" s="2">
         <v>11</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G114" s="2">
         <v>1</v>
@@ -10876,13 +10914,13 @@
         <v>2000313</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E115" s="2">
         <v>11</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G115" s="2">
         <v>1</v>
@@ -10902,13 +10940,13 @@
         <v>2000314</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E116" s="2">
         <v>11</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G116" s="2">
         <v>1</v>
@@ -10928,13 +10966,13 @@
         <v>2000315</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E117" s="2">
         <v>11</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G117" s="2">
         <v>1</v>
@@ -10954,13 +10992,13 @@
         <v>2000316</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E118" s="2">
         <v>11</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G118" s="2">
         <v>1</v>
@@ -10980,13 +11018,13 @@
         <v>2000317</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E119" s="2">
         <v>11</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G119" s="2">
         <v>1</v>
@@ -11006,13 +11044,13 @@
         <v>2000318</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E120" s="2">
         <v>11</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G120" s="2">
         <v>1</v>
@@ -11032,13 +11070,13 @@
         <v>2000319</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E121" s="2">
         <v>11</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G121" s="2">
         <v>1</v>
@@ -11058,13 +11096,13 @@
         <v>2000320</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E122" s="2">
         <v>11</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G122" s="2">
         <v>1</v>
@@ -11084,13 +11122,13 @@
         <v>2000321</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E123" s="2">
         <v>11</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G123" s="2">
         <v>1</v>
@@ -11110,13 +11148,13 @@
         <v>2000322</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E124" s="2">
         <v>11</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G124" s="2">
         <v>1</v>
@@ -11136,13 +11174,13 @@
         <v>2000323</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E125" s="2">
         <v>11</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G125" s="2">
         <v>1</v>
@@ -11162,13 +11200,13 @@
         <v>2000324</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E126" s="2">
         <v>11</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G126" s="2">
         <v>1</v>
@@ -11188,13 +11226,13 @@
         <v>2000325</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E127" s="2">
         <v>11</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G127" s="2">
         <v>1</v>
@@ -11214,13 +11252,13 @@
         <v>2000326</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E128" s="2">
         <v>11</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G128" s="2">
         <v>1</v>
@@ -11240,13 +11278,13 @@
         <v>2000327</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E129" s="2">
         <v>11</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G129" s="2">
         <v>1</v>
@@ -11266,13 +11304,13 @@
         <v>2000328</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E130" s="2">
         <v>11</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G130" s="2">
         <v>1</v>
@@ -11292,13 +11330,13 @@
         <v>2000329</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E131" s="2">
         <v>11</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G131" s="2">
         <v>1</v>
@@ -11457,13 +11495,13 @@
         <v>3000001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E6" s="2">
         <v>13</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -11485,13 +11523,13 @@
         <v>3000002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E7" s="2">
         <v>13</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -11513,13 +11551,13 @@
         <v>3000003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E8" s="2">
         <v>13</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -11541,13 +11579,13 @@
         <v>3000004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E9" s="2">
         <v>13</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -11569,13 +11607,13 @@
         <v>3000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E10" s="2">
         <v>13</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -11597,13 +11635,13 @@
         <v>3000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E11" s="2">
         <v>13</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -11625,13 +11663,13 @@
         <v>3000007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E12" s="2">
         <v>13</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -11653,13 +11691,13 @@
         <v>3000008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E13" s="2">
         <v>13</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -11681,13 +11719,13 @@
         <v>3000009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E14" s="2">
         <v>13</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -11709,13 +11747,13 @@
         <v>3000010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E15" s="2">
         <v>13</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -11737,13 +11775,13 @@
         <v>3000011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E16" s="2">
         <v>13</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -11765,13 +11803,13 @@
         <v>3000012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E17" s="2">
         <v>13</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -11793,13 +11831,13 @@
         <v>3000013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E18" s="2">
         <v>13</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -11821,13 +11859,13 @@
         <v>3000014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E19" s="2">
         <v>13</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -11849,13 +11887,13 @@
         <v>3000015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E20" s="2">
         <v>13</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -11877,13 +11915,13 @@
         <v>3000016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E21" s="2">
         <v>13</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -11905,13 +11943,13 @@
         <v>3000017</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E22" s="2">
         <v>13</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -11933,13 +11971,13 @@
         <v>3000018</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E23" s="2">
         <v>13</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -11961,13 +11999,13 @@
         <v>3000019</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E24" s="2">
         <v>13</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -11989,13 +12027,13 @@
         <v>3000020</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E25" s="2">
         <v>13</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -12017,13 +12055,13 @@
         <v>3000021</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E26" s="2">
         <v>13</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -12045,13 +12083,13 @@
         <v>3000022</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E27" s="2">
         <v>13</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -12073,13 +12111,13 @@
         <v>3000023</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E28" s="2">
         <v>13</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -12101,13 +12139,13 @@
         <v>3000024</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E29" s="2">
         <v>13</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -12129,13 +12167,13 @@
         <v>3000025</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="E30" s="2">
         <v>13</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -12157,13 +12195,13 @@
         <v>3000026</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E31" s="2">
         <v>13</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -12185,13 +12223,13 @@
         <v>3000027</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E32" s="2">
         <v>13</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -12213,13 +12251,13 @@
         <v>3000028</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E33" s="2">
         <v>13</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -12241,13 +12279,13 @@
         <v>3000029</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E34" s="2">
         <v>13</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -12269,13 +12307,13 @@
         <v>3000030</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E35" s="2">
         <v>13</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -12297,13 +12335,13 @@
         <v>3000031</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E36" s="2">
         <v>13</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -12325,13 +12363,13 @@
         <v>3000032</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E37" s="2">
         <v>13</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G37" s="2">
         <v>1</v>
@@ -12353,13 +12391,13 @@
         <v>3000033</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E38" s="2">
         <v>13</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G38" s="2">
         <v>1</v>
@@ -12381,13 +12419,13 @@
         <v>3000034</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E39" s="2">
         <v>13</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -12409,13 +12447,13 @@
         <v>3000035</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E40" s="2">
         <v>13</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -12437,13 +12475,13 @@
         <v>3000036</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E41" s="2">
         <v>13</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -12465,13 +12503,13 @@
         <v>3000037</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E42" s="2">
         <v>13</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -12493,13 +12531,13 @@
         <v>3000038</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E43" s="2">
         <v>13</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -12521,13 +12559,13 @@
         <v>3000039</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E44" s="2">
         <v>13</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -12549,13 +12587,13 @@
         <v>3000040</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E45" s="2">
         <v>13</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G45" s="2">
         <v>1</v>
@@ -12577,13 +12615,13 @@
         <v>3000041</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E46" s="2">
         <v>13</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -12605,13 +12643,13 @@
         <v>3000042</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E47" s="2">
         <v>13</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -12633,13 +12671,13 @@
         <v>3000043</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E48" s="2">
         <v>13</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -12661,13 +12699,13 @@
         <v>3000044</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E49" s="2">
         <v>13</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -12689,13 +12727,13 @@
         <v>3000045</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E50" s="2">
         <v>13</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -12717,13 +12755,13 @@
         <v>3000046</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E51" s="2">
         <v>13</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -12745,13 +12783,13 @@
         <v>3000047</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E52" s="2">
         <v>13</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -12773,13 +12811,13 @@
         <v>3000048</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E53" s="2">
         <v>13</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G53" s="2">
         <v>1</v>
@@ -12942,13 +12980,13 @@
         <v>40000051</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E7" s="2">
         <v>14</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -12963,7 +13001,7 @@
         <v>6</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="L7" s="3">
         <v>4018</v>
@@ -12977,13 +13015,13 @@
         <v>40000052</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E8" s="2">
         <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -12998,7 +13036,7 @@
         <v>6</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="L8" s="3">
         <v>4018</v>
@@ -13012,13 +13050,13 @@
         <v>40000053</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E9" s="2">
         <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -13033,7 +13071,7 @@
         <v>6</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L9" s="3">
         <v>4018</v>
@@ -13047,13 +13085,13 @@
         <v>40000054</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E10" s="2">
         <v>14</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -13068,7 +13106,7 @@
         <v>6</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L10" s="3">
         <v>4018</v>
@@ -13082,13 +13120,13 @@
         <v>40000055</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E11" s="2">
         <v>14</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -13103,7 +13141,7 @@
         <v>6</v>
       </c>
       <c r="K11" s="12" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="L11" s="3">
         <v>4018</v>
@@ -13117,13 +13155,13 @@
         <v>40000056</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E12" s="2">
         <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -13138,7 +13176,7 @@
         <v>6</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="L12" s="3">
         <v>4018</v>
@@ -13152,13 +13190,13 @@
         <v>40000057</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E13" s="2">
         <v>14</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -13173,7 +13211,7 @@
         <v>6</v>
       </c>
       <c r="K13" s="12" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="L13" s="3">
         <v>4018</v>
@@ -13187,13 +13225,13 @@
         <v>40000058</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E14" s="2">
         <v>14</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -13208,7 +13246,7 @@
         <v>6</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L14" s="3">
         <v>4018</v>
@@ -13222,13 +13260,13 @@
         <v>40000059</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E15" s="2">
         <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -13243,7 +13281,7 @@
         <v>6</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="L15" s="3">
         <v>4018</v>
@@ -13257,13 +13295,13 @@
         <v>40000060</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E16" s="2">
         <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -13278,7 +13316,7 @@
         <v>6</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="L16" s="3">
         <v>4018</v>
@@ -13292,13 +13330,13 @@
         <v>40000061</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E17" s="2">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -13313,7 +13351,7 @@
         <v>6</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="L17" s="3">
         <v>4018</v>
@@ -13327,13 +13365,13 @@
         <v>40000062</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E18" s="2">
         <v>14</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -13348,7 +13386,7 @@
         <v>6</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="L18" s="3">
         <v>4018</v>
@@ -13362,13 +13400,13 @@
         <v>40000063</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E19" s="2">
         <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -13383,7 +13421,7 @@
         <v>6</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="L19" s="3">
         <v>4018</v>
@@ -13397,13 +13435,13 @@
         <v>40000064</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E20" s="2">
         <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -13418,7 +13456,7 @@
         <v>6</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L20" s="3">
         <v>4018</v>
@@ -13432,13 +13470,13 @@
         <v>40000065</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E21" s="2">
         <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
@@ -13453,7 +13491,7 @@
         <v>6</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="L21" s="3">
         <v>4018</v>
@@ -13467,13 +13505,13 @@
         <v>40000066</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E22" s="2">
         <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -13488,7 +13526,7 @@
         <v>6</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="L22" s="3">
         <v>4018</v>
@@ -13502,13 +13540,13 @@
         <v>40000067</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="E23" s="2">
         <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -13523,7 +13561,7 @@
         <v>6</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="L23" s="3">
         <v>4018</v>
@@ -13537,13 +13575,13 @@
         <v>40000068</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E24" s="2">
         <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -13558,7 +13596,7 @@
         <v>6</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="L24" s="3">
         <v>4018</v>
@@ -13572,13 +13610,13 @@
         <v>40000069</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E25" s="2">
         <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -13593,7 +13631,7 @@
         <v>6</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="L25" s="3">
         <v>4018</v>
@@ -13607,13 +13645,13 @@
         <v>40000070</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E26" s="2">
         <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -13642,13 +13680,13 @@
         <v>40000071</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E27" s="2">
         <v>14</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -13677,13 +13715,13 @@
         <v>40000072</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E28" s="2">
         <v>14</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -13712,13 +13750,13 @@
         <v>40000073</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E29" s="2">
         <v>14</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -13747,13 +13785,13 @@
         <v>40000074</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E30" s="2">
         <v>14</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -13782,13 +13820,13 @@
         <v>40000075</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="E31" s="2">
         <v>14</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -13817,13 +13855,13 @@
         <v>40000076</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E32" s="2">
         <v>14</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -13852,13 +13890,13 @@
         <v>40000077</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E33" s="2">
         <v>14</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -13887,13 +13925,13 @@
         <v>40000078</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E34" s="2">
         <v>14</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -13922,13 +13960,13 @@
         <v>40000079</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E35" s="2">
         <v>14</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -13957,13 +13995,13 @@
         <v>40000080</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E36" s="2">
         <v>14</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -13992,13 +14030,13 @@
         <v>40000081</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E37" s="2">
         <v>14</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G37" s="2">
         <v>1</v>
@@ -14027,13 +14065,13 @@
         <v>40000082</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E38" s="2">
         <v>14</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G38" s="2">
         <v>1</v>
@@ -14062,13 +14100,13 @@
         <v>40000083</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="E39" s="2">
         <v>14</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -14097,13 +14135,13 @@
         <v>40000084</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E40" s="2">
         <v>14</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -14132,13 +14170,13 @@
         <v>40000085</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E41" s="2">
         <v>14</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -14167,13 +14205,13 @@
         <v>40000086</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="E42" s="2">
         <v>14</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -14202,13 +14240,13 @@
         <v>40000087</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E43" s="2">
         <v>14</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G43" s="2">
         <v>1</v>
@@ -14237,13 +14275,13 @@
         <v>40000088</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E44" s="2">
         <v>14</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
@@ -14272,13 +14310,13 @@
         <v>40000089</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E45" s="2">
         <v>14</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G45" s="2">
         <v>1</v>
@@ -14307,13 +14345,13 @@
         <v>40000090</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E46" s="2">
         <v>14</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -14342,13 +14380,13 @@
         <v>40000091</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="E47" s="2">
         <v>14</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -14377,13 +14415,13 @@
         <v>40000092</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E48" s="2">
         <v>14</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G48" s="2">
         <v>1</v>
@@ -14412,13 +14450,13 @@
         <v>40000093</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E49" s="2">
         <v>14</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
@@ -14447,13 +14485,13 @@
         <v>40000094</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="E50" s="2">
         <v>14</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
@@ -14482,13 +14520,13 @@
         <v>40000095</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E51" s="2">
         <v>14</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G51" s="2">
         <v>1</v>
@@ -14517,13 +14555,13 @@
         <v>40000096</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="E52" s="2">
         <v>14</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G52" s="2">
         <v>1</v>
@@ -14552,13 +14590,13 @@
         <v>40000097</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E53" s="2">
         <v>14</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G53" s="2">
         <v>1</v>
@@ -14587,13 +14625,13 @@
         <v>40000098</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="E54" s="2">
         <v>14</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G54" s="2">
         <v>1</v>
@@ -14622,13 +14660,13 @@
         <v>40000099</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="E55" s="2">
         <v>14</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G55" s="2">
         <v>1</v>
@@ -14657,13 +14695,13 @@
         <v>40000100</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="E56" s="2">
         <v>14</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G56" s="2">
         <v>1</v>
@@ -14692,13 +14730,13 @@
         <v>40000101</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E57" s="2">
         <v>14</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G57" s="2">
         <v>1</v>
@@ -14727,13 +14765,13 @@
         <v>40000102</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E58" s="2">
         <v>14</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G58" s="2">
         <v>1</v>
@@ -14762,13 +14800,13 @@
         <v>40000103</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="E59" s="2">
         <v>14</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G59" s="2">
         <v>1</v>
@@ -14797,13 +14835,13 @@
         <v>40000104</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="E60" s="2">
         <v>14</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G60" s="2">
         <v>1</v>
@@ -14832,13 +14870,13 @@
         <v>40000105</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E61" s="10">
         <v>14</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G61" s="10">
         <v>1</v>
@@ -14867,13 +14905,13 @@
         <v>40000106</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="E62" s="2">
         <v>14</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G62" s="2">
         <v>1</v>
@@ -14902,13 +14940,13 @@
         <v>40000107</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="E63" s="2">
         <v>14</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G63" s="2">
         <v>1</v>
@@ -14937,13 +14975,13 @@
         <v>40000108</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E64" s="2">
         <v>14</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G64" s="2">
         <v>1</v>
@@ -14972,13 +15010,13 @@
         <v>40000109</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="E65" s="2">
         <v>14</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G65" s="2">
         <v>1</v>
@@ -15007,13 +15045,13 @@
         <v>40000110</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E66" s="2">
         <v>14</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G66" s="2">
         <v>1</v>
@@ -15042,13 +15080,13 @@
         <v>40000111</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E67" s="2">
         <v>14</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G67" s="2">
         <v>1</v>
@@ -15077,13 +15115,13 @@
         <v>40000112</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E68" s="2">
         <v>14</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G68" s="2">
         <v>1</v>
@@ -15112,13 +15150,13 @@
         <v>40000113</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E69" s="2">
         <v>14</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G69" s="2">
         <v>1</v>
@@ -15147,13 +15185,13 @@
         <v>40000114</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E70" s="2">
         <v>14</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G70" s="2">
         <v>1</v>
@@ -15182,13 +15220,13 @@
         <v>40000115</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E71" s="2">
         <v>14</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G71" s="2">
         <v>1</v>
@@ -15217,13 +15255,13 @@
         <v>40000116</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E72" s="2">
         <v>14</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G72" s="2">
         <v>1</v>
@@ -15252,13 +15290,13 @@
         <v>40000117</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E73" s="2">
         <v>14</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G73" s="2">
         <v>1</v>
@@ -15287,13 +15325,13 @@
         <v>40000118</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="E74" s="2">
         <v>14</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G74" s="2">
         <v>1</v>
@@ -15322,13 +15360,13 @@
         <v>40000119</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E75" s="2">
         <v>14</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G75" s="2">
         <v>1</v>
@@ -15357,13 +15395,13 @@
         <v>40000120</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E76" s="2">
         <v>14</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G76" s="2">
         <v>1</v>
@@ -15392,13 +15430,13 @@
         <v>40000121</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E77" s="2">
         <v>14</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G77" s="2">
         <v>1</v>
@@ -15427,13 +15465,13 @@
         <v>40000122</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E78" s="2">
         <v>14</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G78" s="2">
         <v>1</v>
@@ -15462,13 +15500,13 @@
         <v>40000123</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="E79" s="2">
         <v>14</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G79" s="2">
         <v>1</v>
@@ -15497,13 +15535,13 @@
         <v>40000124</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E80" s="2">
         <v>14</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G80" s="2">
         <v>1</v>
@@ -15532,13 +15570,13 @@
         <v>40000125</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="E81" s="2">
         <v>14</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G81" s="2">
         <v>1</v>
@@ -15567,13 +15605,13 @@
         <v>40000126</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E82" s="2">
         <v>14</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G82" s="2">
         <v>1</v>
@@ -15602,13 +15640,13 @@
         <v>40000127</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E83" s="2">
         <v>14</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G83" s="2">
         <v>1</v>
@@ -15637,13 +15675,13 @@
         <v>40000128</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="E84" s="2">
         <v>14</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G84" s="2">
         <v>1</v>
@@ -15672,13 +15710,13 @@
         <v>40000129</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E85" s="2">
         <v>14</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G85" s="2">
         <v>1</v>
@@ -15707,13 +15745,13 @@
         <v>40000130</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E86" s="2">
         <v>14</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G86" s="2">
         <v>1</v>
@@ -15742,13 +15780,13 @@
         <v>40000131</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="E87" s="2">
         <v>14</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G87" s="2">
         <v>1</v>
@@ -15777,13 +15815,13 @@
         <v>40000132</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E88" s="2">
         <v>14</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G88" s="2">
         <v>1</v>
@@ -15812,13 +15850,13 @@
         <v>40000133</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="E89" s="2">
         <v>14</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G89" s="2">
         <v>1</v>
@@ -15847,13 +15885,13 @@
         <v>40000134</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="E90" s="2">
         <v>14</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G90" s="2">
         <v>1</v>
@@ -15882,13 +15920,13 @@
         <v>40000135</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E91" s="2">
         <v>14</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G91" s="2">
         <v>1</v>
@@ -15917,13 +15955,13 @@
         <v>40000136</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="E92" s="2">
         <v>14</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G92" s="2">
         <v>1</v>
@@ -15952,13 +15990,13 @@
         <v>40000137</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="E93" s="2">
         <v>14</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G93" s="2">
         <v>1</v>
@@ -15987,13 +16025,13 @@
         <v>40000138</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="E94" s="2">
         <v>14</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G94" s="2">
         <v>1</v>
@@ -16022,13 +16060,13 @@
         <v>40000139</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="E95" s="2">
         <v>14</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G95" s="2">
         <v>1</v>
@@ -16057,13 +16095,13 @@
         <v>40000140</v>
       </c>
       <c r="D96" s="11" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="E96" s="10">
         <v>14</v>
       </c>
       <c r="F96" s="10" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G96" s="10">
         <v>1</v>
@@ -16092,13 +16130,13 @@
         <v>40000141</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E97" s="2">
         <v>14</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G97" s="2">
         <v>1</v>
@@ -16127,13 +16165,13 @@
         <v>40000142</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E98" s="2">
         <v>14</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G98" s="2">
         <v>1</v>
@@ -16162,13 +16200,13 @@
         <v>40000143</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="E99" s="2">
         <v>14</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G99" s="2">
         <v>1</v>
@@ -16197,13 +16235,13 @@
         <v>40000144</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="E100" s="2">
         <v>14</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G100" s="2">
         <v>1</v>
@@ -16232,13 +16270,13 @@
         <v>40000145</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E101" s="2">
         <v>14</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G101" s="2">
         <v>1</v>
@@ -16267,13 +16305,13 @@
         <v>40000146</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E102" s="2">
         <v>14</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G102" s="2">
         <v>1</v>
@@ -16302,13 +16340,13 @@
         <v>40000147</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="E103" s="2">
         <v>14</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G103" s="2">
         <v>1</v>
@@ -16337,13 +16375,13 @@
         <v>40000148</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="E104" s="2">
         <v>14</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G104" s="2">
         <v>1</v>
@@ -16372,13 +16410,13 @@
         <v>40000149</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="E105" s="2">
         <v>14</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G105" s="2">
         <v>1</v>
@@ -16407,13 +16445,13 @@
         <v>40000150</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E106" s="2">
         <v>14</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G106" s="2">
         <v>1</v>
@@ -16442,13 +16480,13 @@
         <v>40000151</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="E107" s="2">
         <v>14</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G107" s="2">
         <v>1</v>
@@ -16477,13 +16515,13 @@
         <v>40000152</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="E108" s="2">
         <v>14</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G108" s="2">
         <v>1</v>
@@ -16512,13 +16550,13 @@
         <v>40000153</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="E109" s="2">
         <v>14</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G109" s="2">
         <v>1</v>
@@ -16547,13 +16585,13 @@
         <v>40000154</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="E110" s="2">
         <v>14</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G110" s="2">
         <v>1</v>
@@ -16582,13 +16620,13 @@
         <v>40000155</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E111" s="2">
         <v>14</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G111" s="2">
         <v>1</v>
@@ -16617,13 +16655,13 @@
         <v>40000156</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="E112" s="2">
         <v>14</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G112" s="2">
         <v>1</v>
@@ -16652,13 +16690,13 @@
         <v>40000157</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E113" s="2">
         <v>14</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G113" s="2">
         <v>1</v>
@@ -16687,13 +16725,13 @@
         <v>40000158</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="E114" s="2">
         <v>14</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G114" s="2">
         <v>1</v>
@@ -16722,13 +16760,13 @@
         <v>40000159</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="E115" s="2">
         <v>14</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G115" s="2">
         <v>1</v>
@@ -16757,13 +16795,13 @@
         <v>40000160</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="E116" s="2">
         <v>14</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G116" s="2">
         <v>1</v>
@@ -16792,13 +16830,13 @@
         <v>40000161</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="E117" s="2">
         <v>14</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G117" s="2">
         <v>1</v>
@@ -16827,13 +16865,13 @@
         <v>40000162</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E118" s="2">
         <v>14</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G118" s="2">
         <v>1</v>
@@ -16862,13 +16900,13 @@
         <v>40000163</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E119" s="2">
         <v>14</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G119" s="2">
         <v>1</v>
@@ -16897,13 +16935,13 @@
         <v>40000164</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="E120" s="2">
         <v>14</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G120" s="2">
         <v>1</v>
@@ -16932,13 +16970,13 @@
         <v>40000165</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="E121" s="2">
         <v>14</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G121" s="2">
         <v>1</v>
@@ -16967,13 +17005,13 @@
         <v>40000166</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E122" s="2">
         <v>14</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G122" s="2">
         <v>1</v>
@@ -17002,13 +17040,13 @@
         <v>40000167</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E123" s="2">
         <v>14</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G123" s="2">
         <v>1</v>
@@ -17037,13 +17075,13 @@
         <v>40000168</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E124" s="2">
         <v>14</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G124" s="2">
         <v>1</v>
@@ -17072,13 +17110,13 @@
         <v>40000169</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E125" s="2">
         <v>14</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G125" s="2">
         <v>1</v>
@@ -17107,13 +17145,13 @@
         <v>40000170</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="E126" s="2">
         <v>14</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G126" s="2">
         <v>1</v>
@@ -17142,13 +17180,13 @@
         <v>40000171</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E127" s="2">
         <v>14</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G127" s="2">
         <v>1</v>
@@ -17177,13 +17215,13 @@
         <v>40000172</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="E128" s="2">
         <v>14</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G128" s="2">
         <v>1</v>
@@ -17212,13 +17250,13 @@
         <v>40000173</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="E129" s="2">
         <v>14</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G129" s="2">
         <v>1</v>
@@ -17247,13 +17285,13 @@
         <v>40000174</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="E130" s="2">
         <v>14</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G130" s="2">
         <v>1</v>
@@ -17425,13 +17463,13 @@
         <v>50000001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="E6" s="2">
         <v>5</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -17460,13 +17498,13 @@
         <v>50000002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="E7" s="2">
         <v>5</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -17495,13 +17533,13 @@
         <v>50000003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="E8" s="2">
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -17530,13 +17568,13 @@
         <v>50000004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="E9" s="2">
         <v>5</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -17565,13 +17603,13 @@
         <v>50000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="E10" s="2">
         <v>5</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -17600,13 +17638,13 @@
         <v>50000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="E11" s="2">
         <v>5</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -17635,13 +17673,13 @@
         <v>50000007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="E12" s="2">
         <v>5</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -17670,13 +17708,13 @@
         <v>50000008</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E13" s="7">
         <v>5</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="G13" s="7">
         <v>1</v>
@@ -17705,13 +17743,13 @@
         <v>50000009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="E14" s="2">
         <v>5</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -17740,13 +17778,13 @@
         <v>50000010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="E15" s="2">
         <v>5</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -17775,13 +17813,13 @@
         <v>50000011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="E16" s="2">
         <v>5</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -17810,13 +17848,13 @@
         <v>50000012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="E17" s="2">
         <v>5</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -17845,13 +17883,13 @@
         <v>50000013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E18" s="2">
         <v>5</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -17880,13 +17918,13 @@
         <v>50000014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="E19" s="2">
         <v>5</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -17915,13 +17953,13 @@
         <v>50000015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="E20" s="2">
         <v>5</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -17950,13 +17988,13 @@
         <v>50000016</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E21" s="7">
         <v>5</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="G21" s="7">
         <v>1</v>
@@ -17985,13 +18023,13 @@
         <v>50000017</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="E22" s="2">
         <v>5</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -18020,13 +18058,13 @@
         <v>50000018</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="E23" s="2">
         <v>5</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -18055,13 +18093,13 @@
         <v>50000019</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="E24" s="2">
         <v>5</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -18090,13 +18128,13 @@
         <v>50000020</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="E25" s="2">
         <v>5</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -18125,13 +18163,13 @@
         <v>50000021</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="E26" s="2">
         <v>5</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -18160,13 +18198,13 @@
         <v>50000022</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="E27" s="2">
         <v>5</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -18195,13 +18233,13 @@
         <v>50000023</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="E28" s="2">
         <v>5</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -18230,13 +18268,13 @@
         <v>50000024</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="E29" s="7">
         <v>5</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="G29" s="7">
         <v>1</v>
@@ -18265,13 +18303,13 @@
         <v>50000025</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="E30" s="2">
         <v>5</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -18300,13 +18338,13 @@
         <v>50000026</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="E31" s="2">
         <v>5</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -18335,13 +18373,13 @@
         <v>50000027</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="E32" s="2">
         <v>5</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -18370,13 +18408,13 @@
         <v>50000028</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="E33" s="2">
         <v>5</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -18405,13 +18443,13 @@
         <v>50000029</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="E34" s="2">
         <v>5</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -18440,13 +18478,13 @@
         <v>50000030</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="E35" s="2">
         <v>5</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -18475,13 +18513,13 @@
         <v>50000031</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E36" s="2">
         <v>5</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -18510,13 +18548,13 @@
         <v>50000032</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="E37" s="7">
         <v>5</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="G37" s="7">
         <v>1</v>
@@ -18545,13 +18583,13 @@
         <v>50000033</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="E38" s="2">
         <v>5</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="G38" s="2">
         <v>1</v>
@@ -18580,13 +18618,13 @@
         <v>50000034</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="E39" s="2">
         <v>5</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -18615,13 +18653,13 @@
         <v>50000035</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="E40" s="2">
         <v>5</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -18650,13 +18688,13 @@
         <v>50000036</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="E41" s="2">
         <v>5</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -18685,13 +18723,13 @@
         <v>50000037</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="E42" s="2">
         <v>5</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -18720,13 +18758,13 @@
         <v>50000038</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E43" s="2">
         <v>5</v>
       </c>
       <c r="F43"